--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -8051,19 +8051,19 @@
         <v>2526.74</v>
       </c>
       <c r="D91" t="n">
-        <v>2473.83</v>
+        <v>2466.28</v>
       </c>
       <c r="E91" t="n">
-        <v>2474.37</v>
+        <v>2493.1</v>
       </c>
       <c r="F91" t="n">
-        <v>-51.57</v>
+        <v>-32.84</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.0204</v>
+        <v>-0.013</v>
       </c>
       <c r="H91" t="n">
-        <v>52.9</v>
+        <v>60.46</v>
       </c>
       <c r="I91" t="n">
         <v>2473.13</v>
@@ -8088,19 +8088,19 @@
       </c>
       <c r="P91" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q91" s="6" t="inlineStr">
+      <c r="R91" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R91" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S91" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -8115,12 +8115,16 @@
       <c r="V91" s="8" t="n">
         <v/>
       </c>
-      <c r="W91" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr"/>
+      <c r="W91" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -8129,25 +8133,25 @@
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>2420.93</v>
+        <v>2405.82</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>2408.51</v>
+        <v>2430.94</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>2447.92</v>
+        <v>2462.87</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>2487.33</v>
+        <v>2494.8</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>2500.82</v>
+        <v>2523.33</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>2514.32</v>
+        <v>2551.85</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>2579.64</v>
+        <v>2587.19</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1794.94</v>
+        <v>1790.4</v>
       </c>
       <c r="C2" t="n">
-        <v>1837.2</v>
+        <v>1807.28</v>
       </c>
       <c r="D2" t="n">
-        <v>1758.13</v>
+        <v>1724.72</v>
       </c>
       <c r="E2" t="n">
-        <v>1790.4</v>
+        <v>1747.89</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.56</v>
+        <v>-42.51</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0237</v>
       </c>
       <c r="H2" t="n">
-        <v>79.06999999999999</v>
+        <v>82.56</v>
       </c>
       <c r="I2" t="n">
-        <v>1570.74</v>
+        <v>1679.06</v>
       </c>
       <c r="J2" t="n">
-        <v>1664.67</v>
+        <v>1707.69</v>
       </c>
       <c r="K2" t="n">
-        <v>1725.7</v>
+        <v>1750.86</v>
       </c>
       <c r="L2" t="n">
-        <v>1786.74</v>
+        <v>1794.03</v>
       </c>
       <c r="M2" t="n">
-        <v>1864.22</v>
+        <v>1829.94</v>
       </c>
       <c r="N2" t="n">
-        <v>1941.7</v>
+        <v>1865.84</v>
       </c>
       <c r="O2" t="n">
-        <v>1986.29</v>
+        <v>1916.28</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,12 +692,14 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -716,57 +718,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1790.4</v>
+        <v>1747.88</v>
       </c>
       <c r="C3" t="n">
-        <v>1807.28</v>
+        <v>1760.88</v>
       </c>
       <c r="D3" t="n">
-        <v>1724.72</v>
+        <v>1670.1</v>
       </c>
       <c r="E3" t="n">
-        <v>1747.89</v>
+        <v>1709.53</v>
       </c>
       <c r="F3" t="n">
-        <v>-42.51</v>
+        <v>-38.35</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0237</v>
+        <v>-0.0219</v>
       </c>
       <c r="H3" t="n">
-        <v>82.56</v>
+        <v>90.78</v>
       </c>
       <c r="I3" t="n">
-        <v>1679.06</v>
+        <v>1642.15</v>
       </c>
       <c r="J3" t="n">
-        <v>1707.69</v>
+        <v>1656.26</v>
       </c>
       <c r="K3" t="n">
-        <v>1750.86</v>
+        <v>1706.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1794.03</v>
+        <v>1756.94</v>
       </c>
       <c r="M3" t="n">
-        <v>1829.94</v>
+        <v>1789.17</v>
       </c>
       <c r="N3" t="n">
-        <v>1865.84</v>
+        <v>1821.39</v>
       </c>
       <c r="O3" t="n">
-        <v>1916.28</v>
+        <v>1889.85</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,7 +781,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -807,50 +809,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1747.88</v>
+        <v>1709.5</v>
       </c>
       <c r="C4" t="n">
-        <v>1760.88</v>
+        <v>1717.19</v>
       </c>
       <c r="D4" t="n">
-        <v>1670.1</v>
+        <v>1678.2</v>
       </c>
       <c r="E4" t="n">
-        <v>1709.53</v>
+        <v>1710.98</v>
       </c>
       <c r="F4" t="n">
-        <v>-38.35</v>
+        <v>1.45</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0219</v>
+        <v>0.0008</v>
       </c>
       <c r="H4" t="n">
-        <v>90.78</v>
+        <v>39</v>
       </c>
       <c r="I4" t="n">
-        <v>1642.15</v>
+        <v>1579.33</v>
       </c>
       <c r="J4" t="n">
-        <v>1656.26</v>
+        <v>1615.78</v>
       </c>
       <c r="K4" t="n">
-        <v>1706.6</v>
+        <v>1664.14</v>
       </c>
       <c r="L4" t="n">
-        <v>1756.94</v>
+        <v>1712.51</v>
       </c>
       <c r="M4" t="n">
-        <v>1789.17</v>
+        <v>1754.92</v>
       </c>
       <c r="N4" t="n">
-        <v>1821.39</v>
+        <v>1797.33</v>
       </c>
       <c r="O4" t="n">
-        <v>1889.85</v>
+        <v>1851.66</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,14 +860,12 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -884,57 +884,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1709.5</v>
+        <v>1710.98</v>
       </c>
       <c r="C5" t="n">
-        <v>1717.19</v>
+        <v>1747.26</v>
       </c>
       <c r="D5" t="n">
-        <v>1678.2</v>
+        <v>1702.8</v>
       </c>
       <c r="E5" t="n">
-        <v>1710.98</v>
+        <v>1739.3</v>
       </c>
       <c r="F5" t="n">
-        <v>1.45</v>
+        <v>28.32</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0166</v>
       </c>
       <c r="H5" t="n">
-        <v>39</v>
+        <v>44.46</v>
       </c>
       <c r="I5" t="n">
-        <v>1579.33</v>
+        <v>1639.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1615.78</v>
+        <v>1678.63</v>
       </c>
       <c r="K5" t="n">
-        <v>1664.14</v>
+        <v>1691.48</v>
       </c>
       <c r="L5" t="n">
-        <v>1712.51</v>
+        <v>1704.34</v>
       </c>
       <c r="M5" t="n">
-        <v>1754.92</v>
+        <v>1730.48</v>
       </c>
       <c r="N5" t="n">
-        <v>1797.33</v>
+        <v>1756.62</v>
       </c>
       <c r="O5" t="n">
-        <v>1851.66</v>
+        <v>1756.19</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -947,11 +947,13 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -964,78 +966,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1710.98</v>
+        <v>1739.34</v>
       </c>
       <c r="C6" t="n">
-        <v>1747.26</v>
+        <v>1739.49</v>
       </c>
       <c r="D6" t="n">
-        <v>1702.8</v>
+        <v>1701.94</v>
       </c>
       <c r="E6" t="n">
-        <v>1739.3</v>
+        <v>1704.58</v>
       </c>
       <c r="F6" t="n">
-        <v>28.32</v>
+        <v>-34.72</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.02</v>
       </c>
       <c r="H6" t="n">
-        <v>44.46</v>
+        <v>37.55</v>
       </c>
       <c r="I6" t="n">
-        <v>1639.2</v>
+        <v>1658.34</v>
       </c>
       <c r="J6" t="n">
-        <v>1678.63</v>
+        <v>1701.98</v>
       </c>
       <c r="K6" t="n">
-        <v>1691.48</v>
+        <v>1717.07</v>
       </c>
       <c r="L6" t="n">
-        <v>1704.34</v>
+        <v>1732.17</v>
       </c>
       <c r="M6" t="n">
-        <v>1730.48</v>
+        <v>1761.53</v>
       </c>
       <c r="N6" t="n">
-        <v>1756.62</v>
+        <v>1790.89</v>
       </c>
       <c r="O6" t="n">
-        <v>1756.19</v>
+        <v>1791.72</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1048,80 +1048,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1739.34</v>
+        <v>1704.63</v>
       </c>
       <c r="C7" t="n">
-        <v>1739.49</v>
+        <v>1776.83</v>
       </c>
       <c r="D7" t="n">
-        <v>1701.94</v>
+        <v>1704.52</v>
       </c>
       <c r="E7" t="n">
-        <v>1704.58</v>
+        <v>1726.51</v>
       </c>
       <c r="F7" t="n">
-        <v>-34.72</v>
+        <v>21.93</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0129</v>
       </c>
       <c r="H7" t="n">
-        <v>37.55</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1658.34</v>
+        <v>1664.39</v>
       </c>
       <c r="J7" t="n">
-        <v>1701.98</v>
+        <v>1658.97</v>
       </c>
       <c r="K7" t="n">
-        <v>1717.07</v>
+        <v>1685.81</v>
       </c>
       <c r="L7" t="n">
-        <v>1732.17</v>
+        <v>1712.65</v>
       </c>
       <c r="M7" t="n">
-        <v>1761.53</v>
+        <v>1723.36</v>
       </c>
       <c r="N7" t="n">
-        <v>1790.89</v>
+        <v>1734.06</v>
       </c>
       <c r="O7" t="n">
-        <v>1791.72</v>
+        <v>1777.04</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1130,83 +1134,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1704.63</v>
+        <v>1726.52</v>
       </c>
       <c r="C8" t="n">
-        <v>1776.83</v>
+        <v>1733.61</v>
       </c>
       <c r="D8" t="n">
-        <v>1704.52</v>
+        <v>1638.25</v>
       </c>
       <c r="E8" t="n">
-        <v>1726.51</v>
+        <v>1665.44</v>
       </c>
       <c r="F8" t="n">
-        <v>21.93</v>
+        <v>-61.07</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0354</v>
       </c>
       <c r="H8" t="n">
-        <v>72.31999999999999</v>
+        <v>95.36</v>
       </c>
       <c r="I8" t="n">
-        <v>1664.39</v>
+        <v>1632.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1658.97</v>
+        <v>1647.11</v>
       </c>
       <c r="K8" t="n">
-        <v>1685.81</v>
+        <v>1690.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1712.65</v>
+        <v>1733.59</v>
       </c>
       <c r="M8" t="n">
-        <v>1723.36</v>
+        <v>1762.67</v>
       </c>
       <c r="N8" t="n">
-        <v>1734.06</v>
+        <v>1791.74</v>
       </c>
       <c r="O8" t="n">
-        <v>1777.04</v>
+        <v>1849.15</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1216,70 +1216,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1726.52</v>
+        <v>1665.31</v>
       </c>
       <c r="C9" t="n">
-        <v>1733.61</v>
+        <v>1687.49</v>
       </c>
       <c r="D9" t="n">
-        <v>1638.25</v>
+        <v>1551.48</v>
       </c>
       <c r="E9" t="n">
-        <v>1665.44</v>
+        <v>1619.92</v>
       </c>
       <c r="F9" t="n">
-        <v>-61.07</v>
+        <v>-45.51</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0354</v>
+        <v>-0.0273</v>
       </c>
       <c r="H9" t="n">
-        <v>95.36</v>
+        <v>136.01</v>
       </c>
       <c r="I9" t="n">
-        <v>1632.2</v>
+        <v>1542.89</v>
       </c>
       <c r="J9" t="n">
-        <v>1647.11</v>
+        <v>1559.83</v>
       </c>
       <c r="K9" t="n">
-        <v>1690.35</v>
+        <v>1617.76</v>
       </c>
       <c r="L9" t="n">
-        <v>1733.59</v>
+        <v>1675.68</v>
       </c>
       <c r="M9" t="n">
-        <v>1762.67</v>
+        <v>1713.12</v>
       </c>
       <c r="N9" t="n">
-        <v>1791.74</v>
+        <v>1750.55</v>
       </c>
       <c r="O9" t="n">
-        <v>1849.15</v>
+        <v>1828.97</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1307,65 +1311,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1665.31</v>
+        <v>1619.89</v>
       </c>
       <c r="C10" t="n">
-        <v>1687.49</v>
+        <v>1656.65</v>
       </c>
       <c r="D10" t="n">
-        <v>1551.48</v>
+        <v>1531.78</v>
       </c>
       <c r="E10" t="n">
-        <v>1619.92</v>
+        <v>1564.82</v>
       </c>
       <c r="F10" t="n">
-        <v>-45.51</v>
+        <v>-55.11</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.034</v>
       </c>
       <c r="H10" t="n">
-        <v>136.01</v>
+        <v>124.87</v>
       </c>
       <c r="I10" t="n">
-        <v>1542.89</v>
+        <v>1415.48</v>
       </c>
       <c r="J10" t="n">
-        <v>1559.83</v>
+        <v>1484.14</v>
       </c>
       <c r="K10" t="n">
-        <v>1617.76</v>
+        <v>1551.92</v>
       </c>
       <c r="L10" t="n">
-        <v>1675.68</v>
+        <v>1619.71</v>
       </c>
       <c r="M10" t="n">
-        <v>1713.12</v>
+        <v>1687.93</v>
       </c>
       <c r="N10" t="n">
-        <v>1750.55</v>
+        <v>1756.15</v>
       </c>
       <c r="O10" t="n">
-        <v>1828.97</v>
+        <v>1823.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q10" s="6" t="n">
+        <v/>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1393,50 +1395,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1619.89</v>
+        <v>1564.61</v>
       </c>
       <c r="C11" t="n">
-        <v>1656.65</v>
+        <v>1590.2</v>
       </c>
       <c r="D11" t="n">
-        <v>1531.78</v>
+        <v>1510.51</v>
       </c>
       <c r="E11" t="n">
-        <v>1564.82</v>
+        <v>1576.62</v>
       </c>
       <c r="F11" t="n">
-        <v>-55.11</v>
+        <v>11.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.034</v>
+        <v>0.0075</v>
       </c>
       <c r="H11" t="n">
-        <v>124.87</v>
+        <v>79.69</v>
       </c>
       <c r="I11" t="n">
-        <v>1415.48</v>
+        <v>1406.91</v>
       </c>
       <c r="J11" t="n">
-        <v>1484.14</v>
+        <v>1425.25</v>
       </c>
       <c r="K11" t="n">
-        <v>1551.92</v>
+        <v>1502.38</v>
       </c>
       <c r="L11" t="n">
-        <v>1619.71</v>
+        <v>1579.52</v>
       </c>
       <c r="M11" t="n">
-        <v>1687.93</v>
+        <v>1627.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1756.15</v>
+        <v>1674.98</v>
       </c>
       <c r="O11" t="n">
-        <v>1823.5</v>
+        <v>1781.51</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1444,14 +1446,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1564.61</v>
+        <v>1576.59</v>
       </c>
       <c r="C12" t="n">
-        <v>1590.2</v>
+        <v>1607.87</v>
       </c>
       <c r="D12" t="n">
-        <v>1510.51</v>
+        <v>1561.97</v>
       </c>
       <c r="E12" t="n">
-        <v>1576.62</v>
+        <v>1571.59</v>
       </c>
       <c r="F12" t="n">
-        <v>11.8</v>
+        <v>-5.03</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0032</v>
       </c>
       <c r="H12" t="n">
-        <v>79.69</v>
+        <v>45.89</v>
       </c>
       <c r="I12" t="n">
-        <v>1406.91</v>
+        <v>1430.81</v>
       </c>
       <c r="J12" t="n">
-        <v>1425.25</v>
+        <v>1510.05</v>
       </c>
       <c r="K12" t="n">
-        <v>1502.38</v>
+        <v>1536.77</v>
       </c>
       <c r="L12" t="n">
-        <v>1579.52</v>
+        <v>1563.48</v>
       </c>
       <c r="M12" t="n">
-        <v>1627.25</v>
+        <v>1616.46</v>
       </c>
       <c r="N12" t="n">
-        <v>1674.98</v>
+        <v>1669.44</v>
       </c>
       <c r="O12" t="n">
-        <v>1781.51</v>
+        <v>1669.89</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1552,57 +1552,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1576.59</v>
+        <v>1571.56</v>
       </c>
       <c r="C13" t="n">
-        <v>1607.87</v>
+        <v>1585.22</v>
       </c>
       <c r="D13" t="n">
-        <v>1561.97</v>
+        <v>1548.76</v>
       </c>
       <c r="E13" t="n">
-        <v>1571.59</v>
+        <v>1570.36</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.03</v>
+        <v>-1.23</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.0008</v>
       </c>
       <c r="H13" t="n">
-        <v>45.89</v>
+        <v>36.46</v>
       </c>
       <c r="I13" t="n">
-        <v>1430.81</v>
+        <v>1516.08</v>
       </c>
       <c r="J13" t="n">
-        <v>1510.05</v>
+        <v>1519.03</v>
       </c>
       <c r="K13" t="n">
-        <v>1536.77</v>
+        <v>1548.64</v>
       </c>
       <c r="L13" t="n">
-        <v>1563.48</v>
+        <v>1578.25</v>
       </c>
       <c r="M13" t="n">
-        <v>1616.46</v>
+        <v>1594.53</v>
       </c>
       <c r="N13" t="n">
-        <v>1669.44</v>
+        <v>1610.82</v>
       </c>
       <c r="O13" t="n">
-        <v>1669.89</v>
+        <v>1653.76</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1571.56</v>
+        <v>1569.99</v>
       </c>
       <c r="C14" t="n">
-        <v>1585.22</v>
+        <v>1633.65</v>
       </c>
       <c r="D14" t="n">
-        <v>1548.76</v>
+        <v>1550.04</v>
       </c>
       <c r="E14" t="n">
-        <v>1570.36</v>
+        <v>1610.21</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.23</v>
+        <v>39.84</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0254</v>
       </c>
       <c r="H14" t="n">
-        <v>36.46</v>
+        <v>83.61</v>
       </c>
       <c r="I14" t="n">
-        <v>1516.08</v>
+        <v>1512.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1519.03</v>
+        <v>1535.59</v>
       </c>
       <c r="K14" t="n">
-        <v>1548.64</v>
+        <v>1552.13</v>
       </c>
       <c r="L14" t="n">
-        <v>1578.25</v>
+        <v>1568.68</v>
       </c>
       <c r="M14" t="n">
-        <v>1594.53</v>
+        <v>1588.59</v>
       </c>
       <c r="N14" t="n">
-        <v>1610.82</v>
+        <v>1608.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1653.76</v>
+        <v>1621.68</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1692,81 +1692,85 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1569.99</v>
+        <v>1610.16</v>
       </c>
       <c r="C15" t="n">
-        <v>1633.65</v>
+        <v>1611.35</v>
       </c>
       <c r="D15" t="n">
-        <v>1550.04</v>
+        <v>1549.25</v>
       </c>
       <c r="E15" t="n">
-        <v>1610.21</v>
+        <v>1569.58</v>
       </c>
       <c r="F15" t="n">
-        <v>39.84</v>
+        <v>-40.62</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0254</v>
+        <v>-0.0252</v>
       </c>
       <c r="H15" t="n">
-        <v>83.61</v>
+        <v>62.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1512.3</v>
+        <v>1466.43</v>
       </c>
       <c r="J15" t="n">
-        <v>1535.59</v>
+        <v>1535.78</v>
       </c>
       <c r="K15" t="n">
-        <v>1552.13</v>
+        <v>1568.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1568.68</v>
+        <v>1601.02</v>
       </c>
       <c r="M15" t="n">
-        <v>1588.59</v>
+        <v>1652.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1608.5</v>
+        <v>1703</v>
       </c>
       <c r="O15" t="n">
-        <v>1621.68</v>
+        <v>1717.25</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1776,83 +1780,81 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1610.16</v>
+        <v>1569.91</v>
       </c>
       <c r="C16" t="n">
-        <v>1611.35</v>
+        <v>1642.45</v>
       </c>
       <c r="D16" t="n">
-        <v>1549.25</v>
+        <v>1551.14</v>
       </c>
       <c r="E16" t="n">
-        <v>1569.58</v>
+        <v>1608.96</v>
       </c>
       <c r="F16" t="n">
-        <v>-40.62</v>
+        <v>39.38</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0252</v>
+        <v>0.0251</v>
       </c>
       <c r="H16" t="n">
-        <v>62.1</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>1466.43</v>
+        <v>1487.16</v>
       </c>
       <c r="J16" t="n">
-        <v>1535.78</v>
+        <v>1502.13</v>
       </c>
       <c r="K16" t="n">
-        <v>1568.4</v>
+        <v>1538.54</v>
       </c>
       <c r="L16" t="n">
-        <v>1601.02</v>
+        <v>1574.94</v>
       </c>
       <c r="M16" t="n">
-        <v>1652.01</v>
+        <v>1600.63</v>
       </c>
       <c r="N16" t="n">
-        <v>1703</v>
+        <v>1626.32</v>
       </c>
       <c r="O16" t="n">
-        <v>1717.25</v>
+        <v>1673.44</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,21 +1862,23 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1884,59 +1888,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1569.91</v>
+        <v>1609.01</v>
       </c>
       <c r="C17" t="n">
-        <v>1642.45</v>
+        <v>1720.34</v>
       </c>
       <c r="D17" t="n">
-        <v>1551.14</v>
+        <v>1595.94</v>
       </c>
       <c r="E17" t="n">
-        <v>1608.96</v>
+        <v>1698.17</v>
       </c>
       <c r="F17" t="n">
-        <v>39.38</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0554</v>
       </c>
       <c r="H17" t="n">
-        <v>91.31999999999999</v>
+        <v>124.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1487.16</v>
+        <v>1459.82</v>
       </c>
       <c r="J17" t="n">
-        <v>1502.13</v>
+        <v>1523.73</v>
       </c>
       <c r="K17" t="n">
-        <v>1538.54</v>
+        <v>1563.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1574.94</v>
+        <v>1602.88</v>
       </c>
       <c r="M17" t="n">
-        <v>1600.63</v>
+        <v>1654.62</v>
       </c>
       <c r="N17" t="n">
-        <v>1626.32</v>
+        <v>1706.36</v>
       </c>
       <c r="O17" t="n">
-        <v>1673.44</v>
+        <v>1733.77</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1947,19 +1947,19 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V17" s="8" t="n">
@@ -1975,50 +1975,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1609.01</v>
+        <v>1698.42</v>
       </c>
       <c r="C18" t="n">
-        <v>1720.34</v>
+        <v>1772.54</v>
       </c>
       <c r="D18" t="n">
-        <v>1595.94</v>
+        <v>1693.04</v>
       </c>
       <c r="E18" t="n">
-        <v>1698.17</v>
+        <v>1756.52</v>
       </c>
       <c r="F18" t="n">
-        <v>89.20999999999999</v>
+        <v>58.35</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0344</v>
       </c>
       <c r="H18" t="n">
-        <v>124.4</v>
+        <v>79.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1459.82</v>
+        <v>1471.54</v>
       </c>
       <c r="J18" t="n">
-        <v>1523.73</v>
+        <v>1593.78</v>
       </c>
       <c r="K18" t="n">
-        <v>1563.3</v>
+        <v>1635.97</v>
       </c>
       <c r="L18" t="n">
-        <v>1602.88</v>
+        <v>1678.16</v>
       </c>
       <c r="M18" t="n">
-        <v>1654.62</v>
+        <v>1760.37</v>
       </c>
       <c r="N18" t="n">
-        <v>1706.36</v>
+        <v>1842.59</v>
       </c>
       <c r="O18" t="n">
-        <v>1733.77</v>
+        <v>1844.75</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2029,20 +2029,18 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2057,50 +2055,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1698.42</v>
+        <v>1756.58</v>
       </c>
       <c r="C19" t="n">
-        <v>1772.54</v>
+        <v>1804.59</v>
       </c>
       <c r="D19" t="n">
-        <v>1693.04</v>
+        <v>1743.56</v>
       </c>
       <c r="E19" t="n">
-        <v>1756.52</v>
+        <v>1779.03</v>
       </c>
       <c r="F19" t="n">
-        <v>58.35</v>
+        <v>22.51</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0128</v>
       </c>
       <c r="H19" t="n">
-        <v>79.5</v>
+        <v>61.02</v>
       </c>
       <c r="I19" t="n">
-        <v>1471.54</v>
+        <v>1613.53</v>
       </c>
       <c r="J19" t="n">
-        <v>1593.78</v>
+        <v>1688.88</v>
       </c>
       <c r="K19" t="n">
-        <v>1635.97</v>
+        <v>1716.77</v>
       </c>
       <c r="L19" t="n">
-        <v>1678.16</v>
+        <v>1744.65</v>
       </c>
       <c r="M19" t="n">
-        <v>1760.37</v>
+        <v>1796.27</v>
       </c>
       <c r="N19" t="n">
-        <v>1842.59</v>
+        <v>1847.89</v>
       </c>
       <c r="O19" t="n">
-        <v>1844.75</v>
+        <v>1852.05</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2111,7 +2109,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2137,50 +2135,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1756.58</v>
+        <v>1779.04</v>
       </c>
       <c r="C20" t="n">
-        <v>1804.59</v>
+        <v>1805.91</v>
       </c>
       <c r="D20" t="n">
-        <v>1743.56</v>
+        <v>1749.14</v>
       </c>
       <c r="E20" t="n">
-        <v>1779.03</v>
+        <v>1783.01</v>
       </c>
       <c r="F20" t="n">
-        <v>22.51</v>
+        <v>3.97</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0022</v>
       </c>
       <c r="H20" t="n">
-        <v>61.02</v>
+        <v>56.78</v>
       </c>
       <c r="I20" t="n">
-        <v>1613.53</v>
+        <v>1682.54</v>
       </c>
       <c r="J20" t="n">
-        <v>1688.88</v>
+        <v>1720.49</v>
       </c>
       <c r="K20" t="n">
-        <v>1716.77</v>
+        <v>1748.52</v>
       </c>
       <c r="L20" t="n">
-        <v>1744.65</v>
+        <v>1776.55</v>
       </c>
       <c r="M20" t="n">
-        <v>1796.27</v>
+        <v>1809.55</v>
       </c>
       <c r="N20" t="n">
-        <v>1847.89</v>
+        <v>1842.54</v>
       </c>
       <c r="O20" t="n">
-        <v>1852.05</v>
+        <v>1865.61</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2191,15 +2189,13 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2217,67 +2213,73 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779.04</v>
+        <v>1783</v>
       </c>
       <c r="C21" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D21" t="n">
-        <v>1749.14</v>
+        <v>1728.97</v>
       </c>
       <c r="E21" t="n">
-        <v>1783.01</v>
+        <v>1797.57</v>
       </c>
       <c r="F21" t="n">
-        <v>3.97</v>
+        <v>14.57</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>56.78</v>
+        <v>100.55</v>
       </c>
       <c r="I21" t="n">
-        <v>1682.54</v>
+        <v>1692.36</v>
       </c>
       <c r="J21" t="n">
-        <v>1720.49</v>
+        <v>1728.97</v>
       </c>
       <c r="K21" t="n">
-        <v>1748.52</v>
+        <v>1754.62</v>
       </c>
       <c r="L21" t="n">
-        <v>1776.55</v>
+        <v>1780.27</v>
       </c>
       <c r="M21" t="n">
-        <v>1809.55</v>
+        <v>1811.39</v>
       </c>
       <c r="N21" t="n">
-        <v>1842.54</v>
+        <v>1842.52</v>
       </c>
       <c r="O21" t="n">
-        <v>1865.61</v>
+        <v>1862.69</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2290,78 +2292,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1783</v>
+        <v>1797.56</v>
       </c>
       <c r="C22" t="n">
-        <v>1829.51</v>
+        <v>1810.33</v>
       </c>
       <c r="D22" t="n">
-        <v>1728.97</v>
+        <v>1756.71</v>
       </c>
       <c r="E22" t="n">
-        <v>1797.57</v>
+        <v>1768.51</v>
       </c>
       <c r="F22" t="n">
-        <v>14.57</v>
+        <v>-29.06</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0162</v>
       </c>
       <c r="H22" t="n">
-        <v>100.55</v>
+        <v>53.62</v>
       </c>
       <c r="I22" t="n">
-        <v>1692.36</v>
+        <v>1628.42</v>
       </c>
       <c r="J22" t="n">
-        <v>1728.97</v>
+        <v>1706.19</v>
       </c>
       <c r="K22" t="n">
-        <v>1754.62</v>
+        <v>1747.3</v>
       </c>
       <c r="L22" t="n">
-        <v>1780.27</v>
+        <v>1788.41</v>
       </c>
       <c r="M22" t="n">
-        <v>1811.39</v>
+        <v>1847.85</v>
       </c>
       <c r="N22" t="n">
-        <v>1842.52</v>
+        <v>1907.29</v>
       </c>
       <c r="O22" t="n">
-        <v>1862.69</v>
+        <v>1930.06</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2376,57 +2376,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1797.56</v>
+        <v>1768.39</v>
       </c>
       <c r="C23" t="n">
-        <v>1810.33</v>
+        <v>1782.86</v>
       </c>
       <c r="D23" t="n">
-        <v>1756.71</v>
+        <v>1711.9</v>
       </c>
       <c r="E23" t="n">
-        <v>1768.51</v>
+        <v>1742.68</v>
       </c>
       <c r="F23" t="n">
-        <v>-29.06</v>
+        <v>-25.83</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0146</v>
       </c>
       <c r="H23" t="n">
-        <v>53.62</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1628.42</v>
+        <v>1703.1</v>
       </c>
       <c r="J23" t="n">
-        <v>1706.19</v>
+        <v>1707.39</v>
       </c>
       <c r="K23" t="n">
-        <v>1747.3</v>
+        <v>1741.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1788.41</v>
+        <v>1776.02</v>
       </c>
       <c r="M23" t="n">
-        <v>1847.85</v>
+        <v>1795.32</v>
       </c>
       <c r="N23" t="n">
-        <v>1907.29</v>
+        <v>1814.62</v>
       </c>
       <c r="O23" t="n">
-        <v>1930.06</v>
+        <v>1863.95</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2434,12 +2434,14 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2458,57 +2460,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1768.39</v>
+        <v>1742.66</v>
       </c>
       <c r="C24" t="n">
-        <v>1782.86</v>
+        <v>1760.21</v>
       </c>
       <c r="D24" t="n">
-        <v>1711.9</v>
+        <v>1721.3</v>
       </c>
       <c r="E24" t="n">
-        <v>1742.68</v>
+        <v>1744.48</v>
       </c>
       <c r="F24" t="n">
-        <v>-25.83</v>
+        <v>1.81</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>70.95999999999999</v>
+        <v>38.91</v>
       </c>
       <c r="I24" t="n">
-        <v>1703.1</v>
+        <v>1640.94</v>
       </c>
       <c r="J24" t="n">
-        <v>1707.39</v>
+        <v>1669.37</v>
       </c>
       <c r="K24" t="n">
-        <v>1741.7</v>
+        <v>1707.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1776.02</v>
+        <v>1745.03</v>
       </c>
       <c r="M24" t="n">
-        <v>1795.32</v>
+        <v>1778.16</v>
       </c>
       <c r="N24" t="n">
-        <v>1814.62</v>
+        <v>1811.29</v>
       </c>
       <c r="O24" t="n">
-        <v>1863.95</v>
+        <v>1853.82</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2516,14 +2518,12 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2542,57 +2542,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1742.66</v>
+        <v>1744.47</v>
       </c>
       <c r="C25" t="n">
-        <v>1760.21</v>
+        <v>1809.76</v>
       </c>
       <c r="D25" t="n">
-        <v>1721.3</v>
+        <v>1736.72</v>
       </c>
       <c r="E25" t="n">
-        <v>1744.48</v>
+        <v>1795.69</v>
       </c>
       <c r="F25" t="n">
-        <v>1.81</v>
+        <v>51.21</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0294</v>
       </c>
       <c r="H25" t="n">
-        <v>38.91</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>1640.94</v>
+        <v>1682.39</v>
       </c>
       <c r="J25" t="n">
-        <v>1669.37</v>
+        <v>1707.44</v>
       </c>
       <c r="K25" t="n">
-        <v>1707.2</v>
+        <v>1725.03</v>
       </c>
       <c r="L25" t="n">
-        <v>1745.03</v>
+        <v>1742.62</v>
       </c>
       <c r="M25" t="n">
-        <v>1778.16</v>
+        <v>1763.94</v>
       </c>
       <c r="N25" t="n">
-        <v>1811.29</v>
+        <v>1785.26</v>
       </c>
       <c r="O25" t="n">
-        <v>1853.82</v>
+        <v>1799.11</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,76 +2605,78 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1744.47</v>
+        <v>1795.82</v>
       </c>
       <c r="C26" t="n">
-        <v>1809.76</v>
+        <v>1827.83</v>
       </c>
       <c r="D26" t="n">
-        <v>1736.72</v>
+        <v>1786.3</v>
       </c>
       <c r="E26" t="n">
-        <v>1795.69</v>
+        <v>1788.1</v>
       </c>
       <c r="F26" t="n">
-        <v>51.21</v>
+        <v>-7.59</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0294</v>
+        <v>-0.0042</v>
       </c>
       <c r="H26" t="n">
-        <v>73.04000000000001</v>
+        <v>41.54</v>
       </c>
       <c r="I26" t="n">
-        <v>1682.39</v>
+        <v>1663.69</v>
       </c>
       <c r="J26" t="n">
-        <v>1707.44</v>
+        <v>1733.88</v>
       </c>
       <c r="K26" t="n">
-        <v>1725.03</v>
+        <v>1759.18</v>
       </c>
       <c r="L26" t="n">
-        <v>1742.62</v>
+        <v>1784.47</v>
       </c>
       <c r="M26" t="n">
-        <v>1763.94</v>
+        <v>1832.21</v>
       </c>
       <c r="N26" t="n">
-        <v>1785.26</v>
+        <v>1879.95</v>
       </c>
       <c r="O26" t="n">
-        <v>1799.11</v>
+        <v>1882.79</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2685,80 +2687,78 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1795.82</v>
+        <v>1787.57</v>
       </c>
       <c r="C27" t="n">
-        <v>1827.83</v>
+        <v>1824.98</v>
       </c>
       <c r="D27" t="n">
-        <v>1786.3</v>
+        <v>1779.64</v>
       </c>
       <c r="E27" t="n">
-        <v>1788.1</v>
+        <v>1805.79</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.59</v>
+        <v>17.69</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>41.54</v>
+        <v>45.34</v>
       </c>
       <c r="I27" t="n">
-        <v>1663.69</v>
+        <v>1744.76</v>
       </c>
       <c r="J27" t="n">
-        <v>1733.88</v>
+        <v>1737.08</v>
       </c>
       <c r="K27" t="n">
-        <v>1759.18</v>
+        <v>1767.33</v>
       </c>
       <c r="L27" t="n">
-        <v>1784.47</v>
+        <v>1797.58</v>
       </c>
       <c r="M27" t="n">
-        <v>1832.21</v>
+        <v>1808.87</v>
       </c>
       <c r="N27" t="n">
-        <v>1879.95</v>
+        <v>1820.15</v>
       </c>
       <c r="O27" t="n">
-        <v>1882.79</v>
+        <v>1869.37</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2769,16 +2769,20 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2790,81 +2794,83 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1787.57</v>
+        <v>1805.76</v>
       </c>
       <c r="C28" t="n">
-        <v>1824.98</v>
+        <v>1842.46</v>
       </c>
       <c r="D28" t="n">
-        <v>1779.64</v>
+        <v>1749.35</v>
       </c>
       <c r="E28" t="n">
-        <v>1805.79</v>
+        <v>1773.5</v>
       </c>
       <c r="F28" t="n">
-        <v>17.69</v>
+        <v>-32.29</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.0179</v>
       </c>
       <c r="H28" t="n">
-        <v>45.34</v>
+        <v>93.11</v>
       </c>
       <c r="I28" t="n">
-        <v>1744.76</v>
+        <v>1734.29</v>
       </c>
       <c r="J28" t="n">
-        <v>1737.08</v>
+        <v>1762.18</v>
       </c>
       <c r="K28" t="n">
-        <v>1767.33</v>
+        <v>1783.12</v>
       </c>
       <c r="L28" t="n">
-        <v>1797.58</v>
+        <v>1804.05</v>
       </c>
       <c r="M28" t="n">
-        <v>1808.87</v>
+        <v>1828.46</v>
       </c>
       <c r="N28" t="n">
-        <v>1820.15</v>
+        <v>1852.87</v>
       </c>
       <c r="O28" t="n">
-        <v>1869.37</v>
+        <v>1870.32</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2883,77 +2889,75 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1805.76</v>
+        <v>1773.47</v>
       </c>
       <c r="C29" t="n">
-        <v>1842.46</v>
+        <v>1894.06</v>
       </c>
       <c r="D29" t="n">
-        <v>1749.35</v>
+        <v>1772.02</v>
       </c>
       <c r="E29" t="n">
-        <v>1773.5</v>
+        <v>1889.48</v>
       </c>
       <c r="F29" t="n">
-        <v>-32.29</v>
+        <v>115.98</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0654</v>
       </c>
       <c r="H29" t="n">
-        <v>93.11</v>
+        <v>122.04</v>
       </c>
       <c r="I29" t="n">
-        <v>1734.29</v>
+        <v>1656.24</v>
       </c>
       <c r="J29" t="n">
-        <v>1762.18</v>
+        <v>1669.19</v>
       </c>
       <c r="K29" t="n">
-        <v>1783.12</v>
+        <v>1726.95</v>
       </c>
       <c r="L29" t="n">
-        <v>1804.05</v>
+        <v>1784.7</v>
       </c>
       <c r="M29" t="n">
-        <v>1828.46</v>
+        <v>1820.05</v>
       </c>
       <c r="N29" t="n">
-        <v>1852.87</v>
+        <v>1855.41</v>
       </c>
       <c r="O29" t="n">
-        <v>1870.32</v>
+        <v>1935.56</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
@@ -2962,59 +2966,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1773.47</v>
+        <v>1889.5</v>
       </c>
       <c r="C30" t="n">
-        <v>1894.06</v>
+        <v>1944.16</v>
       </c>
       <c r="D30" t="n">
-        <v>1772.02</v>
+        <v>1863.64</v>
       </c>
       <c r="E30" t="n">
-        <v>1889.48</v>
+        <v>1916.94</v>
       </c>
       <c r="F30" t="n">
-        <v>115.98</v>
+        <v>27.46</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0654</v>
+        <v>0.0145</v>
       </c>
       <c r="H30" t="n">
-        <v>122.04</v>
+        <v>80.53</v>
       </c>
       <c r="I30" t="n">
-        <v>1656.24</v>
+        <v>1649.97</v>
       </c>
       <c r="J30" t="n">
-        <v>1669.19</v>
+        <v>1795.66</v>
       </c>
       <c r="K30" t="n">
-        <v>1726.95</v>
+        <v>1828.46</v>
       </c>
       <c r="L30" t="n">
-        <v>1784.7</v>
+        <v>1861.26</v>
       </c>
       <c r="M30" t="n">
-        <v>1820.05</v>
+        <v>1950.5</v>
       </c>
       <c r="N30" t="n">
-        <v>1855.41</v>
+        <v>2039.74</v>
       </c>
       <c r="O30" t="n">
-        <v>1935.56</v>
+        <v>2016.11</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3025,20 +3025,18 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3053,50 +3051,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1889.5</v>
+        <v>1916.98</v>
       </c>
       <c r="C31" t="n">
-        <v>1944.16</v>
+        <v>1927.09</v>
       </c>
       <c r="D31" t="n">
-        <v>1863.64</v>
+        <v>1856.78</v>
       </c>
       <c r="E31" t="n">
-        <v>1916.94</v>
+        <v>1863.19</v>
       </c>
       <c r="F31" t="n">
-        <v>27.46</v>
+        <v>-53.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0145</v>
+        <v>-0.028</v>
       </c>
       <c r="H31" t="n">
-        <v>80.53</v>
+        <v>70.31</v>
       </c>
       <c r="I31" t="n">
-        <v>1649.97</v>
+        <v>1783.11</v>
       </c>
       <c r="J31" t="n">
-        <v>1795.66</v>
+        <v>1842.94</v>
       </c>
       <c r="K31" t="n">
-        <v>1828.46</v>
+        <v>1876.68</v>
       </c>
       <c r="L31" t="n">
-        <v>1861.26</v>
+        <v>1910.42</v>
       </c>
       <c r="M31" t="n">
-        <v>1950.5</v>
+        <v>1957.21</v>
       </c>
       <c r="N31" t="n">
-        <v>2039.74</v>
+        <v>2003.99</v>
       </c>
       <c r="O31" t="n">
-        <v>2016.11</v>
+        <v>2024.69</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3104,18 +3102,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3128,55 +3126,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1916.98</v>
+        <v>1863.22</v>
       </c>
       <c r="C32" t="n">
-        <v>1927.09</v>
+        <v>1869.07</v>
       </c>
       <c r="D32" t="n">
-        <v>1856.78</v>
+        <v>1803.05</v>
       </c>
       <c r="E32" t="n">
-        <v>1863.19</v>
+        <v>1840.99</v>
       </c>
       <c r="F32" t="n">
-        <v>-53.75</v>
+        <v>-22.21</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.0119</v>
       </c>
       <c r="H32" t="n">
-        <v>70.31</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>1783.11</v>
+        <v>1786.47</v>
       </c>
       <c r="J32" t="n">
-        <v>1842.94</v>
+        <v>1778.51</v>
       </c>
       <c r="K32" t="n">
-        <v>1876.68</v>
+        <v>1828.04</v>
       </c>
       <c r="L32" t="n">
-        <v>1910.42</v>
+        <v>1877.56</v>
       </c>
       <c r="M32" t="n">
-        <v>1957.21</v>
+        <v>1898.35</v>
       </c>
       <c r="N32" t="n">
-        <v>2003.99</v>
+        <v>1919.13</v>
       </c>
       <c r="O32" t="n">
-        <v>2024.69</v>
+        <v>1997.4</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3189,7 +3191,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3217,50 +3219,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1863.22</v>
+        <v>1841.1</v>
       </c>
       <c r="C33" t="n">
-        <v>1869.07</v>
+        <v>1864.13</v>
       </c>
       <c r="D33" t="n">
-        <v>1803.05</v>
+        <v>1836.61</v>
       </c>
       <c r="E33" t="n">
-        <v>1840.99</v>
+        <v>1861.39</v>
       </c>
       <c r="F33" t="n">
-        <v>-22.21</v>
+        <v>20.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0111</v>
       </c>
       <c r="H33" t="n">
-        <v>66.01000000000001</v>
+        <v>27.52</v>
       </c>
       <c r="I33" t="n">
-        <v>1786.47</v>
+        <v>1737.04</v>
       </c>
       <c r="J33" t="n">
-        <v>1778.51</v>
+        <v>1777.44</v>
       </c>
       <c r="K33" t="n">
-        <v>1828.04</v>
+        <v>1807.98</v>
       </c>
       <c r="L33" t="n">
-        <v>1877.56</v>
+        <v>1838.52</v>
       </c>
       <c r="M33" t="n">
-        <v>1898.35</v>
+        <v>1873.99</v>
       </c>
       <c r="N33" t="n">
-        <v>1919.13</v>
+        <v>1909.47</v>
       </c>
       <c r="O33" t="n">
-        <v>1997.4</v>
+        <v>1935.08</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3268,19 +3270,19 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3294,57 +3296,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1841.1</v>
+        <v>1861.42</v>
       </c>
       <c r="C34" t="n">
-        <v>1864.13</v>
+        <v>1877.03</v>
       </c>
       <c r="D34" t="n">
-        <v>1836.61</v>
+        <v>1852.73</v>
       </c>
       <c r="E34" t="n">
-        <v>1861.39</v>
+        <v>1871.51</v>
       </c>
       <c r="F34" t="n">
-        <v>20.4</v>
+        <v>10.12</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0054</v>
       </c>
       <c r="H34" t="n">
-        <v>27.52</v>
+        <v>24.3</v>
       </c>
       <c r="I34" t="n">
-        <v>1737.04</v>
+        <v>1809.09</v>
       </c>
       <c r="J34" t="n">
-        <v>1777.44</v>
+        <v>1839.38</v>
       </c>
       <c r="K34" t="n">
-        <v>1807.98</v>
+        <v>1847.63</v>
       </c>
       <c r="L34" t="n">
-        <v>1838.52</v>
+        <v>1855.88</v>
       </c>
       <c r="M34" t="n">
-        <v>1873.99</v>
+        <v>1875.15</v>
       </c>
       <c r="N34" t="n">
-        <v>1909.47</v>
+        <v>1894.43</v>
       </c>
       <c r="O34" t="n">
-        <v>1935.08</v>
+        <v>1891.66</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3355,7 +3357,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3376,231 +3378,227 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1861.42</v>
+        <v>1871.28</v>
       </c>
       <c r="C35" t="n">
-        <v>1877.03</v>
+        <v>1916.24</v>
       </c>
       <c r="D35" t="n">
-        <v>1852.73</v>
+        <v>1842.82</v>
       </c>
       <c r="E35" t="n">
-        <v>1871.51</v>
+        <v>1903.76</v>
       </c>
       <c r="F35" t="n">
-        <v>10.12</v>
+        <v>32.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0172</v>
       </c>
       <c r="H35" t="n">
-        <v>24.3</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>1809.09</v>
+        <v>1828.42</v>
       </c>
       <c r="J35" t="n">
-        <v>1839.38</v>
+        <v>1850.52</v>
       </c>
       <c r="K35" t="n">
-        <v>1847.63</v>
+        <v>1859.36</v>
       </c>
       <c r="L35" t="n">
-        <v>1855.88</v>
+        <v>1868.19</v>
       </c>
       <c r="M35" t="n">
-        <v>1875.15</v>
+        <v>1883.66</v>
       </c>
       <c r="N35" t="n">
-        <v>1894.43</v>
+        <v>1899.13</v>
       </c>
       <c r="O35" t="n">
-        <v>1891.66</v>
+        <v>1901.34</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1871.28</v>
+        <v>1903.69</v>
       </c>
       <c r="C36" t="n">
-        <v>1916.24</v>
+        <v>1949.55</v>
       </c>
       <c r="D36" t="n">
-        <v>1842.82</v>
+        <v>1900.07</v>
       </c>
       <c r="E36" t="n">
-        <v>1903.76</v>
+        <v>1928.38</v>
       </c>
       <c r="F36" t="n">
-        <v>32.25</v>
+        <v>24.62</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0129</v>
       </c>
       <c r="H36" t="n">
-        <v>73.43000000000001</v>
+        <v>49.48</v>
       </c>
       <c r="I36" t="n">
-        <v>1828.42</v>
+        <v>1769.39</v>
       </c>
       <c r="J36" t="n">
-        <v>1850.52</v>
+        <v>1842.45</v>
       </c>
       <c r="K36" t="n">
-        <v>1859.36</v>
+        <v>1867.05</v>
       </c>
       <c r="L36" t="n">
-        <v>1868.19</v>
+        <v>1891.64</v>
       </c>
       <c r="M36" t="n">
-        <v>1883.66</v>
+        <v>1940.47</v>
       </c>
       <c r="N36" t="n">
-        <v>1899.13</v>
+        <v>1989.3</v>
       </c>
       <c r="O36" t="n">
-        <v>1901.34</v>
+        <v>1989.67</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1903.69</v>
+        <v>1928.2</v>
       </c>
       <c r="C37" t="n">
-        <v>1949.55</v>
+        <v>1955.15</v>
       </c>
       <c r="D37" t="n">
-        <v>1900.07</v>
+        <v>1909.61</v>
       </c>
       <c r="E37" t="n">
-        <v>1928.38</v>
+        <v>1933.49</v>
       </c>
       <c r="F37" t="n">
-        <v>24.62</v>
+        <v>5.11</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0026</v>
       </c>
       <c r="H37" t="n">
-        <v>49.48</v>
+        <v>45.54</v>
       </c>
       <c r="I37" t="n">
-        <v>1769.39</v>
+        <v>1850.58</v>
       </c>
       <c r="J37" t="n">
-        <v>1842.45</v>
+        <v>1880.69</v>
       </c>
       <c r="K37" t="n">
-        <v>1867.05</v>
+        <v>1903.64</v>
       </c>
       <c r="L37" t="n">
-        <v>1891.64</v>
+        <v>1926.6</v>
       </c>
       <c r="M37" t="n">
-        <v>1940.47</v>
+        <v>1953.12</v>
       </c>
       <c r="N37" t="n">
-        <v>1989.3</v>
+        <v>1979.65</v>
       </c>
       <c r="O37" t="n">
-        <v>1989.67</v>
+        <v>1999.03</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3611,14 +3609,14 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U37" s="8" t="n">
@@ -3637,69 +3635,71 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1928.2</v>
+        <v>1933.47</v>
       </c>
       <c r="C38" t="n">
-        <v>1955.15</v>
+        <v>1940.28</v>
       </c>
       <c r="D38" t="n">
-        <v>1909.61</v>
+        <v>1868.52</v>
       </c>
       <c r="E38" t="n">
-        <v>1933.49</v>
+        <v>1877.1</v>
       </c>
       <c r="F38" t="n">
-        <v>5.11</v>
+        <v>-56.39</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0292</v>
       </c>
       <c r="H38" t="n">
-        <v>45.54</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>1850.58</v>
+        <v>1864.07</v>
       </c>
       <c r="J38" t="n">
-        <v>1880.69</v>
+        <v>1888.51</v>
       </c>
       <c r="K38" t="n">
-        <v>1903.64</v>
+        <v>1910.72</v>
       </c>
       <c r="L38" t="n">
-        <v>1926.6</v>
+        <v>1932.93</v>
       </c>
       <c r="M38" t="n">
-        <v>1953.12</v>
+        <v>1956.26</v>
       </c>
       <c r="N38" t="n">
-        <v>1979.65</v>
+        <v>1979.58</v>
       </c>
       <c r="O38" t="n">
-        <v>1999.03</v>
+        <v>2000.68</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3707,9 +3707,9 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3717,65 +3717,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1933.47</v>
+        <v>1877.1</v>
       </c>
       <c r="C39" t="n">
-        <v>1940.28</v>
+        <v>1907.54</v>
       </c>
       <c r="D39" t="n">
-        <v>1868.52</v>
+        <v>1846.82</v>
       </c>
       <c r="E39" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="F39" t="n">
-        <v>-56.39</v>
+        <v>-16.92</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0292</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>71.76000000000001</v>
+        <v>60.72</v>
       </c>
       <c r="I39" t="n">
-        <v>1864.07</v>
+        <v>1796.76</v>
       </c>
       <c r="J39" t="n">
-        <v>1888.51</v>
+        <v>1791.69</v>
       </c>
       <c r="K39" t="n">
-        <v>1910.72</v>
+        <v>1841.22</v>
       </c>
       <c r="L39" t="n">
-        <v>1932.93</v>
+        <v>1890.75</v>
       </c>
       <c r="M39" t="n">
-        <v>1956.26</v>
+        <v>1912.98</v>
       </c>
       <c r="N39" t="n">
-        <v>1979.58</v>
+        <v>1935.21</v>
       </c>
       <c r="O39" t="n">
-        <v>2000.68</v>
+        <v>2012.05</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3799,50 +3797,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="C40" t="n">
-        <v>1907.54</v>
+        <v>1875.14</v>
       </c>
       <c r="D40" t="n">
-        <v>1846.82</v>
+        <v>1849.83</v>
       </c>
       <c r="E40" t="n">
-        <v>1860.18</v>
+        <v>1873.22</v>
       </c>
       <c r="F40" t="n">
-        <v>-16.92</v>
+        <v>13.05</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H40" t="n">
-        <v>60.72</v>
+        <v>25.32</v>
       </c>
       <c r="I40" t="n">
-        <v>1796.76</v>
+        <v>1786.1</v>
       </c>
       <c r="J40" t="n">
-        <v>1791.69</v>
+        <v>1790.95</v>
       </c>
       <c r="K40" t="n">
-        <v>1841.22</v>
+        <v>1829.82</v>
       </c>
       <c r="L40" t="n">
-        <v>1890.75</v>
+        <v>1868.68</v>
       </c>
       <c r="M40" t="n">
-        <v>1912.98</v>
+        <v>1890.54</v>
       </c>
       <c r="N40" t="n">
-        <v>1935.21</v>
+        <v>1912.39</v>
       </c>
       <c r="O40" t="n">
-        <v>2012.05</v>
+        <v>1968.26</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3850,14 +3848,12 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3874,55 +3870,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1860.18</v>
+        <v>1873.24</v>
       </c>
       <c r="C41" t="n">
-        <v>1875.14</v>
+        <v>1963.25</v>
       </c>
       <c r="D41" t="n">
-        <v>1849.83</v>
+        <v>1872.38</v>
       </c>
       <c r="E41" t="n">
-        <v>1873.22</v>
+        <v>1953.41</v>
       </c>
       <c r="F41" t="n">
-        <v>13.05</v>
+        <v>80.19</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0428</v>
       </c>
       <c r="H41" t="n">
-        <v>25.32</v>
+        <v>90.86</v>
       </c>
       <c r="I41" t="n">
-        <v>1786.1</v>
+        <v>1824.51</v>
       </c>
       <c r="J41" t="n">
-        <v>1790.95</v>
+        <v>1853.27</v>
       </c>
       <c r="K41" t="n">
-        <v>1829.82</v>
+        <v>1860.56</v>
       </c>
       <c r="L41" t="n">
-        <v>1868.68</v>
+        <v>1867.85</v>
       </c>
       <c r="M41" t="n">
-        <v>1890.54</v>
+        <v>1885.88</v>
       </c>
       <c r="N41" t="n">
-        <v>1912.39</v>
+        <v>1903.91</v>
       </c>
       <c r="O41" t="n">
-        <v>1968.26</v>
+        <v>1900.46</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3933,179 +3933,179 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W41" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1873.24</v>
+        <v>1953.41</v>
       </c>
       <c r="C42" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D42" t="n">
-        <v>1872.38</v>
+        <v>1882.42</v>
       </c>
       <c r="E42" t="n">
-        <v>1953.41</v>
+        <v>1890.61</v>
       </c>
       <c r="F42" t="n">
-        <v>80.19</v>
+        <v>-62.8</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0428</v>
+        <v>-0.0321</v>
       </c>
       <c r="H42" t="n">
-        <v>90.86</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>1824.51</v>
+        <v>1781.52</v>
       </c>
       <c r="J42" t="n">
-        <v>1853.27</v>
+        <v>1880.35</v>
       </c>
       <c r="K42" t="n">
-        <v>1860.56</v>
+        <v>1907.98</v>
       </c>
       <c r="L42" t="n">
-        <v>1867.85</v>
+        <v>1935.61</v>
       </c>
       <c r="M42" t="n">
-        <v>1885.88</v>
+        <v>1998.84</v>
       </c>
       <c r="N42" t="n">
-        <v>1903.91</v>
+        <v>2062.07</v>
       </c>
       <c r="O42" t="n">
-        <v>1900.46</v>
+        <v>2054.11</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1953.41</v>
+        <v>1890.63</v>
       </c>
       <c r="C43" t="n">
-        <v>1976.46</v>
+        <v>1926.5</v>
       </c>
       <c r="D43" t="n">
-        <v>1882.42</v>
+        <v>1856.34</v>
       </c>
       <c r="E43" t="n">
-        <v>1890.61</v>
+        <v>1919.95</v>
       </c>
       <c r="F43" t="n">
-        <v>-62.8</v>
+        <v>29.33</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0321</v>
+        <v>0.0155</v>
       </c>
       <c r="H43" t="n">
-        <v>94.04000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="I43" t="n">
-        <v>1781.52</v>
+        <v>1788.38</v>
       </c>
       <c r="J43" t="n">
-        <v>1880.35</v>
+        <v>1777.16</v>
       </c>
       <c r="K43" t="n">
-        <v>1907.98</v>
+        <v>1843.59</v>
       </c>
       <c r="L43" t="n">
-        <v>1935.61</v>
+        <v>1910.03</v>
       </c>
       <c r="M43" t="n">
-        <v>1998.84</v>
+        <v>1937.63</v>
       </c>
       <c r="N43" t="n">
-        <v>2062.07</v>
+        <v>1965.24</v>
       </c>
       <c r="O43" t="n">
-        <v>2054.11</v>
+        <v>2070.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4124,57 +4124,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1890.63</v>
+        <v>1919.99</v>
       </c>
       <c r="C44" t="n">
-        <v>1926.5</v>
+        <v>1929.9</v>
       </c>
       <c r="D44" t="n">
-        <v>1856.34</v>
+        <v>1873.62</v>
       </c>
       <c r="E44" t="n">
-        <v>1919.95</v>
+        <v>1908.52</v>
       </c>
       <c r="F44" t="n">
-        <v>29.33</v>
+        <v>-11.43</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.006</v>
       </c>
       <c r="H44" t="n">
-        <v>70.16</v>
+        <v>56.28</v>
       </c>
       <c r="I44" t="n">
-        <v>1788.38</v>
+        <v>1786.18</v>
       </c>
       <c r="J44" t="n">
-        <v>1777.16</v>
+        <v>1864.05</v>
       </c>
       <c r="K44" t="n">
-        <v>1843.59</v>
+        <v>1884.87</v>
       </c>
       <c r="L44" t="n">
-        <v>1910.03</v>
+        <v>1905.69</v>
       </c>
       <c r="M44" t="n">
-        <v>1937.63</v>
+        <v>1955.03</v>
       </c>
       <c r="N44" t="n">
-        <v>1965.24</v>
+        <v>2004.37</v>
       </c>
       <c r="O44" t="n">
-        <v>2070.5</v>
+        <v>1996.67</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4182,10 +4182,12 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4206,57 +4208,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1919.99</v>
+        <v>1908.59</v>
       </c>
       <c r="C45" t="n">
-        <v>1929.9</v>
+        <v>1934.58</v>
       </c>
       <c r="D45" t="n">
-        <v>1873.62</v>
+        <v>1892.2</v>
       </c>
       <c r="E45" t="n">
-        <v>1908.52</v>
+        <v>1917.37</v>
       </c>
       <c r="F45" t="n">
-        <v>-11.43</v>
+        <v>8.85</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0046</v>
       </c>
       <c r="H45" t="n">
-        <v>56.28</v>
+        <v>42.38</v>
       </c>
       <c r="I45" t="n">
-        <v>1786.18</v>
+        <v>1817.34</v>
       </c>
       <c r="J45" t="n">
-        <v>1864.05</v>
+        <v>1855.62</v>
       </c>
       <c r="K45" t="n">
-        <v>1884.87</v>
+        <v>1880.38</v>
       </c>
       <c r="L45" t="n">
-        <v>1905.69</v>
+        <v>1905.14</v>
       </c>
       <c r="M45" t="n">
-        <v>1955.03</v>
+        <v>1936.66</v>
       </c>
       <c r="N45" t="n">
-        <v>2004.37</v>
+        <v>1968.18</v>
       </c>
       <c r="O45" t="n">
-        <v>1996.67</v>
+        <v>1986.18</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4264,12 +4266,10 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4288,72 +4288,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1908.59</v>
+        <v>1917.14</v>
       </c>
       <c r="C46" t="n">
-        <v>1934.58</v>
+        <v>1933.78</v>
       </c>
       <c r="D46" t="n">
-        <v>1892.2</v>
+        <v>1847.47</v>
       </c>
       <c r="E46" t="n">
-        <v>1917.37</v>
+        <v>1860.35</v>
       </c>
       <c r="F46" t="n">
-        <v>8.85</v>
+        <v>-57.03</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0297</v>
       </c>
       <c r="H46" t="n">
-        <v>42.38</v>
+        <v>86.31</v>
       </c>
       <c r="I46" t="n">
-        <v>1817.34</v>
+        <v>1849.82</v>
       </c>
       <c r="J46" t="n">
-        <v>1855.62</v>
+        <v>1876.99</v>
       </c>
       <c r="K46" t="n">
-        <v>1880.38</v>
+        <v>1896.18</v>
       </c>
       <c r="L46" t="n">
-        <v>1905.14</v>
+        <v>1915.38</v>
       </c>
       <c r="M46" t="n">
-        <v>1936.66</v>
+        <v>1938.56</v>
       </c>
       <c r="N46" t="n">
-        <v>1968.18</v>
+        <v>1961.75</v>
       </c>
       <c r="O46" t="n">
-        <v>1986.18</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+        <v>1976.96</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4365,9 +4367,9 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
@@ -4375,67 +4377,63 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1917.14</v>
+        <v>1860.37</v>
       </c>
       <c r="C47" t="n">
-        <v>1933.78</v>
+        <v>1873.17</v>
       </c>
       <c r="D47" t="n">
-        <v>1847.47</v>
+        <v>1821.49</v>
       </c>
       <c r="E47" t="n">
-        <v>1860.35</v>
+        <v>1843.42</v>
       </c>
       <c r="F47" t="n">
-        <v>-57.03</v>
+        <v>-16.93</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0297</v>
+        <v>-0.0091</v>
       </c>
       <c r="H47" t="n">
-        <v>86.31</v>
+        <v>51.69</v>
       </c>
       <c r="I47" t="n">
-        <v>1849.82</v>
+        <v>1761.16</v>
       </c>
       <c r="J47" t="n">
-        <v>1876.99</v>
+        <v>1758.9</v>
       </c>
       <c r="K47" t="n">
-        <v>1896.18</v>
+        <v>1817.19</v>
       </c>
       <c r="L47" t="n">
-        <v>1915.38</v>
+        <v>1875.48</v>
       </c>
       <c r="M47" t="n">
-        <v>1938.56</v>
+        <v>1903.5</v>
       </c>
       <c r="N47" t="n">
-        <v>1961.75</v>
+        <v>1931.52</v>
       </c>
       <c r="O47" t="n">
-        <v>1976.96</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
+        <v>2020.09</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4459,50 +4457,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1860.37</v>
+        <v>1843.42</v>
       </c>
       <c r="C48" t="n">
-        <v>1873.17</v>
+        <v>1895.77</v>
       </c>
       <c r="D48" t="n">
-        <v>1821.49</v>
+        <v>1842.15</v>
       </c>
       <c r="E48" t="n">
-        <v>1843.42</v>
+        <v>1882.52</v>
       </c>
       <c r="F48" t="n">
-        <v>-16.93</v>
+        <v>39.1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0212</v>
       </c>
       <c r="H48" t="n">
-        <v>51.69</v>
+        <v>53.61</v>
       </c>
       <c r="I48" t="n">
-        <v>1761.16</v>
+        <v>1769.8</v>
       </c>
       <c r="J48" t="n">
-        <v>1758.9</v>
+        <v>1789.78</v>
       </c>
       <c r="K48" t="n">
-        <v>1817.19</v>
+        <v>1817.57</v>
       </c>
       <c r="L48" t="n">
-        <v>1875.48</v>
+        <v>1845.37</v>
       </c>
       <c r="M48" t="n">
-        <v>1903.5</v>
+        <v>1869.26</v>
       </c>
       <c r="N48" t="n">
-        <v>1931.52</v>
+        <v>1893.15</v>
       </c>
       <c r="O48" t="n">
-        <v>2020.09</v>
+        <v>1924.86</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4510,22 +4508,24 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4534,79 +4534,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1843.42</v>
+        <v>1882.78</v>
       </c>
       <c r="C49" t="n">
-        <v>1895.77</v>
+        <v>1883.44</v>
       </c>
       <c r="D49" t="n">
-        <v>1842.15</v>
+        <v>1827.7</v>
       </c>
       <c r="E49" t="n">
-        <v>1882.52</v>
+        <v>1858.26</v>
       </c>
       <c r="F49" t="n">
-        <v>39.1</v>
+        <v>-24.27</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0129</v>
       </c>
       <c r="H49" t="n">
-        <v>53.61</v>
+        <v>55.74</v>
       </c>
       <c r="I49" t="n">
-        <v>1769.8</v>
+        <v>1788.54</v>
       </c>
       <c r="J49" t="n">
-        <v>1789.78</v>
+        <v>1835.69</v>
       </c>
       <c r="K49" t="n">
-        <v>1817.57</v>
+        <v>1855.72</v>
       </c>
       <c r="L49" t="n">
-        <v>1845.37</v>
+        <v>1875.74</v>
       </c>
       <c r="M49" t="n">
-        <v>1869.26</v>
+        <v>1909.33</v>
       </c>
       <c r="N49" t="n">
-        <v>1893.15</v>
+        <v>1942.91</v>
       </c>
       <c r="O49" t="n">
-        <v>1924.86</v>
+        <v>1949.38</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4616,76 +4620,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1882.78</v>
+        <v>1858.22</v>
       </c>
       <c r="C50" t="n">
-        <v>1883.44</v>
+        <v>1879.54</v>
       </c>
       <c r="D50" t="n">
-        <v>1827.7</v>
+        <v>1847.17</v>
       </c>
       <c r="E50" t="n">
-        <v>1858.26</v>
+        <v>1868.39</v>
       </c>
       <c r="F50" t="n">
-        <v>-24.27</v>
+        <v>10.13</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0055</v>
       </c>
       <c r="H50" t="n">
-        <v>55.74</v>
+        <v>32.36</v>
       </c>
       <c r="I50" t="n">
-        <v>1788.54</v>
+        <v>1771.96</v>
       </c>
       <c r="J50" t="n">
-        <v>1835.69</v>
+        <v>1803.86</v>
       </c>
       <c r="K50" t="n">
-        <v>1855.72</v>
+        <v>1830.39</v>
       </c>
       <c r="L50" t="n">
-        <v>1875.74</v>
+        <v>1856.91</v>
       </c>
       <c r="M50" t="n">
-        <v>1909.33</v>
+        <v>1886.13</v>
       </c>
       <c r="N50" t="n">
-        <v>1942.91</v>
+        <v>1915.34</v>
       </c>
       <c r="O50" t="n">
-        <v>1949.38</v>
+        <v>1939.18</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4702,55 +4698,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1858.22</v>
+        <v>1868.49</v>
       </c>
       <c r="C51" t="n">
-        <v>1879.54</v>
+        <v>1922.64</v>
       </c>
       <c r="D51" t="n">
-        <v>1847.17</v>
+        <v>1854.34</v>
       </c>
       <c r="E51" t="n">
-        <v>1868.39</v>
+        <v>1906.53</v>
       </c>
       <c r="F51" t="n">
-        <v>10.13</v>
+        <v>38.14</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0204</v>
       </c>
       <c r="H51" t="n">
-        <v>32.36</v>
+        <v>68.3</v>
       </c>
       <c r="I51" t="n">
-        <v>1771.96</v>
+        <v>1814.81</v>
       </c>
       <c r="J51" t="n">
-        <v>1803.86</v>
+        <v>1838.54</v>
       </c>
       <c r="K51" t="n">
-        <v>1830.39</v>
+        <v>1852.2</v>
       </c>
       <c r="L51" t="n">
-        <v>1856.91</v>
+        <v>1865.87</v>
       </c>
       <c r="M51" t="n">
-        <v>1886.13</v>
+        <v>1884.57</v>
       </c>
       <c r="N51" t="n">
-        <v>1915.34</v>
+        <v>1903.26</v>
       </c>
       <c r="O51" t="n">
-        <v>1939.18</v>
+        <v>1911.9</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4761,78 +4761,80 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1868.49</v>
+        <v>1906.44</v>
       </c>
       <c r="C52" t="n">
-        <v>1922.64</v>
+        <v>1917.7</v>
       </c>
       <c r="D52" t="n">
-        <v>1854.34</v>
+        <v>1890.96</v>
       </c>
       <c r="E52" t="n">
-        <v>1906.53</v>
+        <v>1902.06</v>
       </c>
       <c r="F52" t="n">
-        <v>38.14</v>
+        <v>-4.47</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.0023</v>
       </c>
       <c r="H52" t="n">
-        <v>68.3</v>
+        <v>26.74</v>
       </c>
       <c r="I52" t="n">
-        <v>1814.81</v>
+        <v>1786.04</v>
       </c>
       <c r="J52" t="n">
-        <v>1838.54</v>
+        <v>1847.24</v>
       </c>
       <c r="K52" t="n">
-        <v>1852.2</v>
+        <v>1872.38</v>
       </c>
       <c r="L52" t="n">
-        <v>1865.87</v>
+        <v>1897.51</v>
       </c>
       <c r="M52" t="n">
-        <v>1884.57</v>
+        <v>1940.68</v>
       </c>
       <c r="N52" t="n">
-        <v>1903.26</v>
+        <v>1983.84</v>
       </c>
       <c r="O52" t="n">
-        <v>1911.9</v>
+        <v>1990.94</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4843,80 +4845,78 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1906.44</v>
+        <v>1902.14</v>
       </c>
       <c r="C53" t="n">
-        <v>1917.7</v>
+        <v>1937.17</v>
       </c>
       <c r="D53" t="n">
-        <v>1890.96</v>
+        <v>1893.08</v>
       </c>
       <c r="E53" t="n">
-        <v>1902.06</v>
+        <v>1913.28</v>
       </c>
       <c r="F53" t="n">
-        <v>-4.47</v>
+        <v>11.22</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0059</v>
       </c>
       <c r="H53" t="n">
-        <v>26.74</v>
+        <v>44.08</v>
       </c>
       <c r="I53" t="n">
-        <v>1786.04</v>
+        <v>1864.23</v>
       </c>
       <c r="J53" t="n">
-        <v>1847.24</v>
+        <v>1874.18</v>
       </c>
       <c r="K53" t="n">
-        <v>1872.38</v>
+        <v>1888.69</v>
       </c>
       <c r="L53" t="n">
-        <v>1897.51</v>
+        <v>1903.19</v>
       </c>
       <c r="M53" t="n">
-        <v>1940.68</v>
+        <v>1915.43</v>
       </c>
       <c r="N53" t="n">
-        <v>1983.84</v>
+        <v>1927.66</v>
       </c>
       <c r="O53" t="n">
-        <v>1990.94</v>
+        <v>1944.44</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4927,16 +4927,20 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4946,59 +4950,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1902.14</v>
+        <v>1913.32</v>
       </c>
       <c r="C54" t="n">
-        <v>1937.17</v>
+        <v>1924.62</v>
       </c>
       <c r="D54" t="n">
-        <v>1893.08</v>
+        <v>1911.48</v>
       </c>
       <c r="E54" t="n">
-        <v>1913.28</v>
+        <v>1915.53</v>
       </c>
       <c r="F54" t="n">
-        <v>11.22</v>
+        <v>2.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0012</v>
       </c>
       <c r="H54" t="n">
-        <v>44.08</v>
+        <v>13.13</v>
       </c>
       <c r="I54" t="n">
-        <v>1864.23</v>
+        <v>1849</v>
       </c>
       <c r="J54" t="n">
-        <v>1874.18</v>
+        <v>1868.27</v>
       </c>
       <c r="K54" t="n">
-        <v>1888.69</v>
+        <v>1891.24</v>
       </c>
       <c r="L54" t="n">
-        <v>1903.19</v>
+        <v>1914.2</v>
       </c>
       <c r="M54" t="n">
-        <v>1915.43</v>
+        <v>1935.32</v>
       </c>
       <c r="N54" t="n">
-        <v>1927.66</v>
+        <v>1956.44</v>
       </c>
       <c r="O54" t="n">
-        <v>1944.44</v>
+        <v>1981.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5009,20 +5009,16 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5032,55 +5028,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1913.32</v>
+        <v>1915.46</v>
       </c>
       <c r="C55" t="n">
-        <v>1924.62</v>
+        <v>1935.53</v>
       </c>
       <c r="D55" t="n">
-        <v>1911.48</v>
+        <v>1907.03</v>
       </c>
       <c r="E55" t="n">
-        <v>1915.53</v>
+        <v>1908.68</v>
       </c>
       <c r="F55" t="n">
-        <v>2.25</v>
+        <v>-6.85</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0036</v>
       </c>
       <c r="H55" t="n">
-        <v>13.13</v>
+        <v>28.5</v>
       </c>
       <c r="I55" t="n">
-        <v>1849</v>
+        <v>1898.35</v>
       </c>
       <c r="J55" t="n">
-        <v>1868.27</v>
+        <v>1901.14</v>
       </c>
       <c r="K55" t="n">
-        <v>1891.24</v>
+        <v>1908.97</v>
       </c>
       <c r="L55" t="n">
-        <v>1914.2</v>
+        <v>1916.79</v>
       </c>
       <c r="M55" t="n">
-        <v>1935.32</v>
+        <v>1922.1</v>
       </c>
       <c r="N55" t="n">
-        <v>1956.44</v>
+        <v>1927.4</v>
       </c>
       <c r="O55" t="n">
-        <v>1981.25</v>
+        <v>1937.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5088,19 +5088,25 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5112,70 +5118,74 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1915.46</v>
+        <v>1908.72</v>
       </c>
       <c r="C56" t="n">
-        <v>1935.53</v>
+        <v>1928.99</v>
       </c>
       <c r="D56" t="n">
-        <v>1907.03</v>
+        <v>1866.79</v>
       </c>
       <c r="E56" t="n">
-        <v>1908.68</v>
+        <v>1871.28</v>
       </c>
       <c r="F56" t="n">
-        <v>-6.85</v>
+        <v>-37.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0196</v>
       </c>
       <c r="H56" t="n">
-        <v>28.5</v>
+        <v>62.2</v>
       </c>
       <c r="I56" t="n">
-        <v>1898.35</v>
+        <v>1878.52</v>
       </c>
       <c r="J56" t="n">
-        <v>1901.14</v>
+        <v>1873.88</v>
       </c>
       <c r="K56" t="n">
-        <v>1908.97</v>
+        <v>1894.43</v>
       </c>
       <c r="L56" t="n">
-        <v>1916.79</v>
+        <v>1914.98</v>
       </c>
       <c r="M56" t="n">
-        <v>1922.1</v>
+        <v>1922.93</v>
       </c>
       <c r="N56" t="n">
-        <v>1927.4</v>
+        <v>1930.89</v>
       </c>
       <c r="O56" t="n">
-        <v>1937.75</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+        <v>1964.03</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5185,97 +5195,83 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1908.72</v>
+        <v>1871.26</v>
       </c>
       <c r="C57" t="n">
-        <v>1928.99</v>
+        <v>1895.75</v>
       </c>
       <c r="D57" t="n">
-        <v>1866.79</v>
+        <v>1852.84</v>
       </c>
       <c r="E57" t="n">
-        <v>1871.28</v>
+        <v>1881.37</v>
       </c>
       <c r="F57" t="n">
-        <v>-37.4</v>
+        <v>10.09</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0196</v>
+        <v>0.0054</v>
       </c>
       <c r="H57" t="n">
-        <v>62.2</v>
+        <v>42.91</v>
       </c>
       <c r="I57" t="n">
-        <v>1878.52</v>
+        <v>1804.59</v>
       </c>
       <c r="J57" t="n">
-        <v>1873.88</v>
+        <v>1795.77</v>
       </c>
       <c r="K57" t="n">
-        <v>1894.43</v>
+        <v>1840.18</v>
       </c>
       <c r="L57" t="n">
-        <v>1914.98</v>
+        <v>1884.59</v>
       </c>
       <c r="M57" t="n">
-        <v>1922.93</v>
+        <v>1902.38</v>
       </c>
       <c r="N57" t="n">
-        <v>1930.89</v>
+        <v>1920.18</v>
       </c>
       <c r="O57" t="n">
-        <v>1964.03</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>1991.2</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5288,55 +5284,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1871.26</v>
+        <v>1881.37</v>
       </c>
       <c r="C58" t="n">
-        <v>1895.75</v>
+        <v>1921.78</v>
       </c>
       <c r="D58" t="n">
-        <v>1852.84</v>
+        <v>1873.35</v>
       </c>
       <c r="E58" t="n">
-        <v>1881.37</v>
+        <v>1878.14</v>
       </c>
       <c r="F58" t="n">
-        <v>10.09</v>
+        <v>-3.24</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0017</v>
       </c>
       <c r="H58" t="n">
-        <v>42.91</v>
+        <v>48.43</v>
       </c>
       <c r="I58" t="n">
-        <v>1804.59</v>
+        <v>1809.93</v>
       </c>
       <c r="J58" t="n">
-        <v>1795.77</v>
+        <v>1842</v>
       </c>
       <c r="K58" t="n">
-        <v>1840.18</v>
+        <v>1859.92</v>
       </c>
       <c r="L58" t="n">
-        <v>1884.59</v>
+        <v>1877.83</v>
       </c>
       <c r="M58" t="n">
-        <v>1902.38</v>
+        <v>1902.83</v>
       </c>
       <c r="N58" t="n">
-        <v>1920.18</v>
+        <v>1927.82</v>
       </c>
       <c r="O58" t="n">
-        <v>1991.2</v>
+        <v>1938.66</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5349,11 +5349,13 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5368,57 +5370,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1881.37</v>
+        <v>1878.19</v>
       </c>
       <c r="C59" t="n">
-        <v>1921.78</v>
+        <v>1898.23</v>
       </c>
       <c r="D59" t="n">
-        <v>1873.35</v>
+        <v>1861.92</v>
       </c>
       <c r="E59" t="n">
-        <v>1878.14</v>
+        <v>1883.99</v>
       </c>
       <c r="F59" t="n">
-        <v>-3.24</v>
+        <v>5.86</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="H59" t="n">
-        <v>48.43</v>
+        <v>36.3</v>
       </c>
       <c r="I59" t="n">
-        <v>1809.93</v>
+        <v>1824.92</v>
       </c>
       <c r="J59" t="n">
-        <v>1842</v>
+        <v>1819.99</v>
       </c>
       <c r="K59" t="n">
-        <v>1859.92</v>
+        <v>1853.92</v>
       </c>
       <c r="L59" t="n">
-        <v>1877.83</v>
+        <v>1887.85</v>
       </c>
       <c r="M59" t="n">
-        <v>1902.83</v>
+        <v>1902.35</v>
       </c>
       <c r="N59" t="n">
-        <v>1927.82</v>
+        <v>1916.85</v>
       </c>
       <c r="O59" t="n">
-        <v>1938.66</v>
+        <v>1970.2</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5431,13 +5433,11 @@
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5452,57 +5452,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1878.19</v>
+        <v>1884.02</v>
       </c>
       <c r="C60" t="n">
-        <v>1898.23</v>
+        <v>1889.27</v>
       </c>
       <c r="D60" t="n">
-        <v>1861.92</v>
+        <v>1862.56</v>
       </c>
       <c r="E60" t="n">
-        <v>1883.99</v>
+        <v>1880.65</v>
       </c>
       <c r="F60" t="n">
-        <v>5.86</v>
+        <v>-3.34</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0018</v>
       </c>
       <c r="H60" t="n">
-        <v>36.3</v>
+        <v>26.71</v>
       </c>
       <c r="I60" t="n">
-        <v>1824.92</v>
+        <v>1825.62</v>
       </c>
       <c r="J60" t="n">
-        <v>1819.99</v>
+        <v>1849.65</v>
       </c>
       <c r="K60" t="n">
-        <v>1853.92</v>
+        <v>1865.84</v>
       </c>
       <c r="L60" t="n">
-        <v>1887.85</v>
+        <v>1882.03</v>
       </c>
       <c r="M60" t="n">
-        <v>1902.35</v>
+        <v>1902.14</v>
       </c>
       <c r="N60" t="n">
-        <v>1916.85</v>
+        <v>1922.26</v>
       </c>
       <c r="O60" t="n">
-        <v>1970.2</v>
+        <v>1934.53</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5510,10 +5510,12 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5541,50 +5543,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1884.02</v>
+        <v>1880.61</v>
       </c>
       <c r="C61" t="n">
-        <v>1889.27</v>
+        <v>1884.72</v>
       </c>
       <c r="D61" t="n">
-        <v>1862.56</v>
+        <v>1874.33</v>
       </c>
       <c r="E61" t="n">
-        <v>1880.65</v>
+        <v>1880.91</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.34</v>
+        <v>0.26</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0001</v>
       </c>
       <c r="H61" t="n">
-        <v>26.71</v>
+        <v>10.39</v>
       </c>
       <c r="I61" t="n">
-        <v>1825.62</v>
+        <v>1835.86</v>
       </c>
       <c r="J61" t="n">
-        <v>1849.65</v>
+        <v>1856.31</v>
       </c>
       <c r="K61" t="n">
-        <v>1865.84</v>
+        <v>1867.3</v>
       </c>
       <c r="L61" t="n">
-        <v>1882.03</v>
+        <v>1878.28</v>
       </c>
       <c r="M61" t="n">
-        <v>1902.14</v>
+        <v>1894</v>
       </c>
       <c r="N61" t="n">
-        <v>1922.26</v>
+        <v>1909.72</v>
       </c>
       <c r="O61" t="n">
-        <v>1934.53</v>
+        <v>1915.98</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5592,14 +5594,12 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5618,74 +5618,80 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1880.61</v>
+        <v>1880.89</v>
       </c>
       <c r="C62" t="n">
-        <v>1884.72</v>
+        <v>1889.61</v>
       </c>
       <c r="D62" t="n">
-        <v>1874.33</v>
+        <v>1867.89</v>
       </c>
       <c r="E62" t="n">
-        <v>1880.91</v>
+        <v>1873.94</v>
       </c>
       <c r="F62" t="n">
-        <v>0.26</v>
+        <v>-6.97</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0037</v>
       </c>
       <c r="H62" t="n">
-        <v>10.39</v>
+        <v>21.71</v>
       </c>
       <c r="I62" t="n">
-        <v>1835.86</v>
+        <v>1863.94</v>
       </c>
       <c r="J62" t="n">
-        <v>1856.31</v>
+        <v>1871.21</v>
       </c>
       <c r="K62" t="n">
-        <v>1867.3</v>
+        <v>1875.71</v>
       </c>
       <c r="L62" t="n">
-        <v>1878.28</v>
+        <v>1880.22</v>
       </c>
       <c r="M62" t="n">
-        <v>1894</v>
+        <v>1886.1</v>
       </c>
       <c r="N62" t="n">
-        <v>1909.72</v>
+        <v>1891.99</v>
       </c>
       <c r="O62" t="n">
-        <v>1915.98</v>
+        <v>1895.11</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5700,145 +5706,141 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1880.89</v>
+        <v>1873.97</v>
       </c>
       <c r="C63" t="n">
-        <v>1889.61</v>
+        <v>1916.66</v>
       </c>
       <c r="D63" t="n">
-        <v>1867.89</v>
+        <v>1870.75</v>
       </c>
       <c r="E63" t="n">
-        <v>1873.94</v>
+        <v>1912.2</v>
       </c>
       <c r="F63" t="n">
-        <v>-6.97</v>
+        <v>38.26</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0204</v>
       </c>
       <c r="H63" t="n">
-        <v>21.71</v>
+        <v>45.91</v>
       </c>
       <c r="I63" t="n">
-        <v>1863.94</v>
+        <v>1846.18</v>
       </c>
       <c r="J63" t="n">
-        <v>1871.21</v>
+        <v>1849.83</v>
       </c>
       <c r="K63" t="n">
-        <v>1875.71</v>
+        <v>1863.09</v>
       </c>
       <c r="L63" t="n">
-        <v>1880.22</v>
+        <v>1876.35</v>
       </c>
       <c r="M63" t="n">
-        <v>1886.1</v>
+        <v>1884.8</v>
       </c>
       <c r="N63" t="n">
-        <v>1891.99</v>
+        <v>1893.25</v>
       </c>
       <c r="O63" t="n">
-        <v>1895.11</v>
+        <v>1911.32</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R63" s="6" t="inlineStr">
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1873.97</v>
+        <v>1912.21</v>
       </c>
       <c r="C64" t="n">
-        <v>1916.66</v>
+        <v>1920.52</v>
       </c>
       <c r="D64" t="n">
-        <v>1870.75</v>
+        <v>1884.48</v>
       </c>
       <c r="E64" t="n">
-        <v>1912.2</v>
+        <v>1916.46</v>
       </c>
       <c r="F64" t="n">
-        <v>38.26</v>
+        <v>4.26</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.0022</v>
       </c>
       <c r="H64" t="n">
-        <v>45.91</v>
+        <v>36.05</v>
       </c>
       <c r="I64" t="n">
-        <v>1846.18</v>
+        <v>1824.84</v>
       </c>
       <c r="J64" t="n">
-        <v>1849.83</v>
+        <v>1875.54</v>
       </c>
       <c r="K64" t="n">
-        <v>1863.09</v>
+        <v>1889.25</v>
       </c>
       <c r="L64" t="n">
-        <v>1876.35</v>
+        <v>1902.95</v>
       </c>
       <c r="M64" t="n">
-        <v>1884.8</v>
+        <v>1935.16</v>
       </c>
       <c r="N64" t="n">
-        <v>1893.25</v>
+        <v>1967.36</v>
       </c>
       <c r="O64" t="n">
-        <v>1911.32</v>
+        <v>1962.57</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5846,28 +5848,24 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
+      <c r="R64" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
       </c>
       <c r="W64" s="9" t="inlineStr">
         <is>
@@ -5879,50 +5877,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1912.21</v>
+        <v>1916.43</v>
       </c>
       <c r="C65" t="n">
-        <v>1920.52</v>
+        <v>2327.7</v>
       </c>
       <c r="D65" t="n">
-        <v>1884.48</v>
+        <v>1905.08</v>
       </c>
       <c r="E65" t="n">
-        <v>1916.46</v>
+        <v>2251.46</v>
       </c>
       <c r="F65" t="n">
-        <v>4.26</v>
+        <v>335</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.1748</v>
       </c>
       <c r="H65" t="n">
-        <v>36.05</v>
+        <v>422.62</v>
       </c>
       <c r="I65" t="n">
-        <v>1824.84</v>
+        <v>1848.43</v>
       </c>
       <c r="J65" t="n">
-        <v>1875.54</v>
+        <v>1887.39</v>
       </c>
       <c r="K65" t="n">
-        <v>1889.25</v>
+        <v>1898.44</v>
       </c>
       <c r="L65" t="n">
-        <v>1902.95</v>
+        <v>1909.48</v>
       </c>
       <c r="M65" t="n">
-        <v>1935.16</v>
+        <v>1934.48</v>
       </c>
       <c r="N65" t="n">
-        <v>1967.36</v>
+        <v>1959.48</v>
       </c>
       <c r="O65" t="n">
-        <v>1962.57</v>
+        <v>1956.57</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5930,24 +5928,28 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="inlineStr">
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W65" s="9" t="inlineStr">
         <is>
@@ -5959,50 +5961,50 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1916.43</v>
+        <v>2251.44</v>
       </c>
       <c r="C66" t="n">
-        <v>2327.7</v>
+        <v>2357.23</v>
       </c>
       <c r="D66" t="n">
-        <v>1905.08</v>
+        <v>2222.57</v>
       </c>
       <c r="E66" t="n">
-        <v>2251.46</v>
+        <v>2326.38</v>
       </c>
       <c r="F66" t="n">
-        <v>335</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.1748</v>
+        <v>0.0333</v>
       </c>
       <c r="H66" t="n">
-        <v>422.62</v>
+        <v>134.65</v>
       </c>
       <c r="I66" t="n">
-        <v>1848.43</v>
+        <v>1482.46</v>
       </c>
       <c r="J66" t="n">
-        <v>1887.39</v>
+        <v>1896.37</v>
       </c>
       <c r="K66" t="n">
-        <v>1898.44</v>
+        <v>2040.15</v>
       </c>
       <c r="L66" t="n">
-        <v>1909.48</v>
+        <v>2183.92</v>
       </c>
       <c r="M66" t="n">
-        <v>1934.48</v>
+        <v>2462.77</v>
       </c>
       <c r="N66" t="n">
-        <v>1959.48</v>
+        <v>2741.61</v>
       </c>
       <c r="O66" t="n">
-        <v>1956.57</v>
+        <v>2750.32</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6013,25 +6015,21 @@
       <c r="R66" s="6" t="n">
         <v/>
       </c>
-      <c r="S66" s="7" t="inlineStr">
+      <c r="S66" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T66" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U66" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V66" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U66" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V66" s="8" t="n">
+        <v/>
       </c>
       <c r="W66" s="9" t="inlineStr">
         <is>
@@ -6043,50 +6041,50 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2251.44</v>
+        <v>2326.38</v>
       </c>
       <c r="C67" t="n">
-        <v>2357.23</v>
+        <v>2545.88</v>
       </c>
       <c r="D67" t="n">
-        <v>2222.57</v>
+        <v>2324.71</v>
       </c>
       <c r="E67" t="n">
-        <v>2326.38</v>
+        <v>2515.28</v>
       </c>
       <c r="F67" t="n">
-        <v>74.93000000000001</v>
+        <v>188.9</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.0333</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H67" t="n">
-        <v>134.65</v>
+        <v>221.17</v>
       </c>
       <c r="I67" t="n">
-        <v>1482.46</v>
+        <v>2087.92</v>
       </c>
       <c r="J67" t="n">
-        <v>1896.37</v>
+        <v>2209.97</v>
       </c>
       <c r="K67" t="n">
-        <v>2040.15</v>
+        <v>2259.06</v>
       </c>
       <c r="L67" t="n">
-        <v>2183.92</v>
+        <v>2308.14</v>
       </c>
       <c r="M67" t="n">
-        <v>2462.77</v>
+        <v>2393.71</v>
       </c>
       <c r="N67" t="n">
-        <v>2741.61</v>
+        <v>2479.28</v>
       </c>
       <c r="O67" t="n">
-        <v>2750.32</v>
+        <v>2491.88</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6097,21 +6095,25 @@
       <c r="R67" s="6" t="n">
         <v/>
       </c>
-      <c r="S67" s="7" t="inlineStr">
+      <c r="S67" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T67" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V67" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U67" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V67" s="8" t="n">
-        <v/>
       </c>
       <c r="W67" s="9" t="inlineStr">
         <is>
@@ -6123,50 +6125,50 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2326.38</v>
+        <v>2515.39</v>
       </c>
       <c r="C68" t="n">
-        <v>2545.88</v>
+        <v>2528.9</v>
       </c>
       <c r="D68" t="n">
-        <v>2324.71</v>
+        <v>2389.9</v>
       </c>
       <c r="E68" t="n">
-        <v>2515.28</v>
+        <v>2424.25</v>
       </c>
       <c r="F68" t="n">
-        <v>188.9</v>
+        <v>-91.03</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0362</v>
       </c>
       <c r="H68" t="n">
-        <v>221.17</v>
+        <v>138.99</v>
       </c>
       <c r="I68" t="n">
-        <v>2087.92</v>
+        <v>2103.54</v>
       </c>
       <c r="J68" t="n">
-        <v>2209.97</v>
+        <v>2334.1</v>
       </c>
       <c r="K68" t="n">
-        <v>2259.06</v>
+        <v>2404.7</v>
       </c>
       <c r="L68" t="n">
-        <v>2308.14</v>
+        <v>2475.29</v>
       </c>
       <c r="M68" t="n">
-        <v>2393.71</v>
+        <v>2625.87</v>
       </c>
       <c r="N68" t="n">
-        <v>2479.28</v>
+        <v>2776.45</v>
       </c>
       <c r="O68" t="n">
-        <v>2491.88</v>
+        <v>2767.05</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
@@ -6174,83 +6176,83 @@
       <c r="Q68" s="6" t="n">
         <v/>
       </c>
-      <c r="R68" s="6" t="n">
-        <v/>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V68" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U68" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V68" s="8" t="n">
+        <v/>
       </c>
       <c r="W68" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr"/>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2515.39</v>
+        <v>2424.22</v>
       </c>
       <c r="C69" t="n">
-        <v>2528.9</v>
+        <v>2483.93</v>
       </c>
       <c r="D69" t="n">
-        <v>2389.9</v>
+        <v>2357.14</v>
       </c>
       <c r="E69" t="n">
-        <v>2424.25</v>
+        <v>2463.82</v>
       </c>
       <c r="F69" t="n">
-        <v>-91.03</v>
+        <v>39.56</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.0362</v>
+        <v>0.0163</v>
       </c>
       <c r="H69" t="n">
-        <v>138.99</v>
+        <v>126.79</v>
       </c>
       <c r="I69" t="n">
-        <v>2103.54</v>
+        <v>2250.91</v>
       </c>
       <c r="J69" t="n">
-        <v>2334.1</v>
+        <v>2267.68</v>
       </c>
       <c r="K69" t="n">
-        <v>2404.7</v>
+        <v>2354.75</v>
       </c>
       <c r="L69" t="n">
-        <v>2475.29</v>
+        <v>2441.83</v>
       </c>
       <c r="M69" t="n">
-        <v>2625.87</v>
+        <v>2493.75</v>
       </c>
       <c r="N69" t="n">
-        <v>2776.45</v>
+        <v>2545.67</v>
       </c>
       <c r="O69" t="n">
-        <v>2767.05</v>
+        <v>2667.89</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6258,14 +6260,12 @@
       <c r="Q69" s="6" t="n">
         <v/>
       </c>
-      <c r="R69" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R69" s="6" t="n">
+        <v/>
       </c>
       <c r="S69" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T69" s="8" t="n">
@@ -6291,50 +6291,50 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2424.22</v>
+        <v>2463.64</v>
       </c>
       <c r="C70" t="n">
-        <v>2483.93</v>
+        <v>2531.74</v>
       </c>
       <c r="D70" t="n">
-        <v>2357.14</v>
+        <v>2425.39</v>
       </c>
       <c r="E70" t="n">
-        <v>2463.82</v>
+        <v>2481.83</v>
       </c>
       <c r="F70" t="n">
-        <v>39.56</v>
+        <v>18.02</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0073</v>
       </c>
       <c r="H70" t="n">
-        <v>126.79</v>
+        <v>106.36</v>
       </c>
       <c r="I70" t="n">
-        <v>2250.91</v>
+        <v>2230.35</v>
       </c>
       <c r="J70" t="n">
-        <v>2267.68</v>
+        <v>2358.67</v>
       </c>
       <c r="K70" t="n">
-        <v>2354.75</v>
+        <v>2400.42</v>
       </c>
       <c r="L70" t="n">
-        <v>2441.83</v>
+        <v>2442.18</v>
       </c>
       <c r="M70" t="n">
-        <v>2493.75</v>
+        <v>2527.21</v>
       </c>
       <c r="N70" t="n">
-        <v>2545.67</v>
+        <v>2612.25</v>
       </c>
       <c r="O70" t="n">
-        <v>2667.89</v>
+        <v>2610.72</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
@@ -6345,13 +6345,15 @@
       <c r="R70" s="6" t="n">
         <v/>
       </c>
-      <c r="S70" s="7" t="inlineStr">
+      <c r="S70" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T70" s="8" t="n">
-        <v/>
+      <c r="T70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U70" s="8" t="n">
         <v/>
@@ -6364,59 +6366,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2463.64</v>
+        <v>2481.78</v>
       </c>
       <c r="C71" t="n">
-        <v>2531.74</v>
+        <v>2531.08</v>
       </c>
       <c r="D71" t="n">
-        <v>2425.39</v>
+        <v>2416.6</v>
       </c>
       <c r="E71" t="n">
-        <v>2481.83</v>
+        <v>2443.16</v>
       </c>
       <c r="F71" t="n">
-        <v>18.02</v>
+        <v>-38.67</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0156</v>
       </c>
       <c r="H71" t="n">
-        <v>106.36</v>
+        <v>114.48</v>
       </c>
       <c r="I71" t="n">
-        <v>2230.35</v>
+        <v>2319.03</v>
       </c>
       <c r="J71" t="n">
-        <v>2358.67</v>
+        <v>2377.11</v>
       </c>
       <c r="K71" t="n">
-        <v>2400.42</v>
+        <v>2428.65</v>
       </c>
       <c r="L71" t="n">
-        <v>2442.18</v>
+        <v>2480.2</v>
       </c>
       <c r="M71" t="n">
-        <v>2527.21</v>
+        <v>2535.01</v>
       </c>
       <c r="N71" t="n">
-        <v>2612.25</v>
+        <v>2589.82</v>
       </c>
       <c r="O71" t="n">
-        <v>2610.72</v>
+        <v>2638.1</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6424,18 +6422,18 @@
       <c r="Q71" s="6" t="n">
         <v/>
       </c>
-      <c r="R71" s="6" t="n">
-        <v/>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="n">
+        <v/>
       </c>
       <c r="U71" s="8" t="n">
         <v/>
@@ -6448,55 +6446,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr"/>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2481.78</v>
+        <v>2442.49</v>
       </c>
       <c r="C72" t="n">
-        <v>2531.08</v>
+        <v>2514.67</v>
       </c>
       <c r="D72" t="n">
-        <v>2416.6</v>
+        <v>2432.51</v>
       </c>
       <c r="E72" t="n">
-        <v>2443.16</v>
+        <v>2506.26</v>
       </c>
       <c r="F72" t="n">
-        <v>-38.67</v>
+        <v>63.1</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0258</v>
       </c>
       <c r="H72" t="n">
-        <v>114.48</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>2319.03</v>
+        <v>2302.12</v>
       </c>
       <c r="J72" t="n">
-        <v>2377.11</v>
+        <v>2313.34</v>
       </c>
       <c r="K72" t="n">
-        <v>2428.65</v>
+        <v>2385.92</v>
       </c>
       <c r="L72" t="n">
-        <v>2480.2</v>
+        <v>2458.5</v>
       </c>
       <c r="M72" t="n">
-        <v>2535.01</v>
+        <v>2500.4</v>
       </c>
       <c r="N72" t="n">
-        <v>2589.82</v>
+        <v>2542.3</v>
       </c>
       <c r="O72" t="n">
-        <v>2638.1</v>
+        <v>2645.57</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
@@ -6504,19 +6506,19 @@
       <c r="Q72" s="6" t="n">
         <v/>
       </c>
-      <c r="R72" s="6" t="inlineStr">
+      <c r="R72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S72" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S72" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T72" s="8" t="n">
-        <v/>
-      </c>
       <c r="U72" s="8" t="n">
         <v/>
       </c>
@@ -6530,57 +6532,57 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2442.49</v>
+        <v>2506.24</v>
       </c>
       <c r="C73" t="n">
-        <v>2514.67</v>
+        <v>2564.27</v>
       </c>
       <c r="D73" t="n">
-        <v>2432.51</v>
+        <v>2481.94</v>
       </c>
       <c r="E73" t="n">
-        <v>2506.26</v>
+        <v>2510.41</v>
       </c>
       <c r="F73" t="n">
-        <v>63.1</v>
+        <v>4.15</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0258</v>
+        <v>0.0017</v>
       </c>
       <c r="H73" t="n">
-        <v>82.15000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="I73" t="n">
-        <v>2302.12</v>
+        <v>2350.36</v>
       </c>
       <c r="J73" t="n">
-        <v>2313.34</v>
+        <v>2440.44</v>
       </c>
       <c r="K73" t="n">
-        <v>2385.92</v>
+        <v>2465.18</v>
       </c>
       <c r="L73" t="n">
-        <v>2458.5</v>
+        <v>2489.93</v>
       </c>
       <c r="M73" t="n">
-        <v>2500.4</v>
+        <v>2547.34</v>
       </c>
       <c r="N73" t="n">
-        <v>2542.3</v>
+        <v>2604.75</v>
       </c>
       <c r="O73" t="n">
-        <v>2645.57</v>
+        <v>2596.82</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6591,14 +6593,14 @@
       <c r="R73" s="6" t="n">
         <v/>
       </c>
-      <c r="S73" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T73" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U73" s="8" t="n">
@@ -6612,78 +6614,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2506.24</v>
+        <v>2510.67</v>
       </c>
       <c r="C74" t="n">
-        <v>2564.27</v>
+        <v>2534.01</v>
       </c>
       <c r="D74" t="n">
-        <v>2481.94</v>
+        <v>2408.72</v>
       </c>
       <c r="E74" t="n">
-        <v>2510.41</v>
+        <v>2442.54</v>
       </c>
       <c r="F74" t="n">
-        <v>4.15</v>
+        <v>-67.87</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.027</v>
       </c>
       <c r="H74" t="n">
-        <v>82.33</v>
+        <v>125.29</v>
       </c>
       <c r="I74" t="n">
-        <v>2350.36</v>
+        <v>2399.62</v>
       </c>
       <c r="J74" t="n">
-        <v>2440.44</v>
+        <v>2421.73</v>
       </c>
       <c r="K74" t="n">
-        <v>2465.18</v>
+        <v>2469.25</v>
       </c>
       <c r="L74" t="n">
-        <v>2489.93</v>
+        <v>2516.76</v>
       </c>
       <c r="M74" t="n">
-        <v>2547.34</v>
+        <v>2551.57</v>
       </c>
       <c r="N74" t="n">
-        <v>2604.75</v>
+        <v>2586.39</v>
       </c>
       <c r="O74" t="n">
-        <v>2596.82</v>
+        <v>2646.6</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
       </c>
-      <c r="Q74" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R74" s="6" t="n">
-        <v/>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="n">
+        <v/>
       </c>
       <c r="U74" s="8" t="n">
         <v/>
@@ -6696,72 +6696,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr"/>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2510.67</v>
+        <v>2442.56</v>
       </c>
       <c r="C75" t="n">
-        <v>2534.01</v>
+        <v>2459.63</v>
       </c>
       <c r="D75" t="n">
-        <v>2408.72</v>
+        <v>2430.81</v>
       </c>
       <c r="E75" t="n">
-        <v>2442.54</v>
+        <v>2457.69</v>
       </c>
       <c r="F75" t="n">
-        <v>-67.87</v>
+        <v>15.15</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.027</v>
+        <v>0.0062</v>
       </c>
       <c r="H75" t="n">
-        <v>125.29</v>
+        <v>28.82</v>
       </c>
       <c r="I75" t="n">
-        <v>2399.62</v>
+        <v>2283.43</v>
       </c>
       <c r="J75" t="n">
-        <v>2421.73</v>
+        <v>2302.83</v>
       </c>
       <c r="K75" t="n">
-        <v>2469.25</v>
+        <v>2379.89</v>
       </c>
       <c r="L75" t="n">
-        <v>2516.76</v>
+        <v>2456.95</v>
       </c>
       <c r="M75" t="n">
-        <v>2551.57</v>
+        <v>2505.18</v>
       </c>
       <c r="N75" t="n">
-        <v>2586.39</v>
+        <v>2553.41</v>
       </c>
       <c r="O75" t="n">
-        <v>2646.6</v>
+        <v>2659.3</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
       </c>
-      <c r="Q75" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R75" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R75" s="6" t="n">
+        <v/>
       </c>
       <c r="S75" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T75" s="8" t="n">
@@ -6780,84 +6780,96 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2442.56</v>
+        <v>2457.69</v>
       </c>
       <c r="C76" t="n">
-        <v>2459.63</v>
+        <v>2532.96</v>
       </c>
       <c r="D76" t="n">
-        <v>2430.81</v>
+        <v>2389.47</v>
       </c>
       <c r="E76" t="n">
-        <v>2457.69</v>
+        <v>2417.94</v>
       </c>
       <c r="F76" t="n">
-        <v>15.15</v>
+        <v>-39.75</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H76" t="n">
-        <v>28.82</v>
+        <v>143.49</v>
       </c>
       <c r="I76" t="n">
-        <v>2283.43</v>
+        <v>2401.99</v>
       </c>
       <c r="J76" t="n">
-        <v>2302.83</v>
+        <v>2435.1</v>
       </c>
       <c r="K76" t="n">
-        <v>2379.89</v>
+        <v>2443.28</v>
       </c>
       <c r="L76" t="n">
-        <v>2456.95</v>
+        <v>2451.45</v>
       </c>
       <c r="M76" t="n">
-        <v>2505.18</v>
+        <v>2472.1</v>
       </c>
       <c r="N76" t="n">
-        <v>2553.41</v>
+        <v>2492.74</v>
       </c>
       <c r="O76" t="n">
-        <v>2659.3</v>
-      </c>
-      <c r="P76" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q76" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R76" s="6" t="n">
-        <v/>
+        <v>2488.45</v>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U76" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V76" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W76" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W76" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -6869,85 +6881,75 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2457.69</v>
+        <v>2417.9</v>
       </c>
       <c r="C77" t="n">
-        <v>2532.96</v>
+        <v>2488.92</v>
       </c>
       <c r="D77" t="n">
-        <v>2389.47</v>
+        <v>2401.81</v>
       </c>
       <c r="E77" t="n">
-        <v>2417.94</v>
+        <v>2466.82</v>
       </c>
       <c r="F77" t="n">
-        <v>-39.75</v>
+        <v>48.88</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.0202</v>
       </c>
       <c r="H77" t="n">
-        <v>143.49</v>
+        <v>87.11</v>
       </c>
       <c r="I77" t="n">
-        <v>2401.99</v>
+        <v>2245.98</v>
       </c>
       <c r="J77" t="n">
-        <v>2435.1</v>
+        <v>2252.81</v>
       </c>
       <c r="K77" t="n">
-        <v>2443.28</v>
+        <v>2346.19</v>
       </c>
       <c r="L77" t="n">
-        <v>2451.45</v>
+        <v>2439.58</v>
       </c>
       <c r="M77" t="n">
-        <v>2472.1</v>
+        <v>2489.68</v>
       </c>
       <c r="N77" t="n">
-        <v>2492.74</v>
+        <v>2539.79</v>
       </c>
       <c r="O77" t="n">
-        <v>2488.45</v>
-      </c>
-      <c r="P77" s="6" t="inlineStr">
+        <v>2676.45</v>
+      </c>
+      <c r="P77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S77" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q77" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R77" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S77" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U77" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V77" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U77" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V77" s="8" t="n">
+        <v/>
       </c>
       <c r="W77" s="11" t="inlineStr">
         <is>
@@ -6956,76 +6958,78 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2417.9</v>
+        <v>2466.58</v>
       </c>
       <c r="C78" t="n">
-        <v>2488.92</v>
+        <v>2484.4</v>
       </c>
       <c r="D78" t="n">
-        <v>2401.81</v>
+        <v>2383.8</v>
       </c>
       <c r="E78" t="n">
-        <v>2466.82</v>
+        <v>2417.84</v>
       </c>
       <c r="F78" t="n">
-        <v>48.88</v>
+        <v>-48.98</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.0202</v>
+        <v>-0.0199</v>
       </c>
       <c r="H78" t="n">
-        <v>87.11</v>
+        <v>100.6</v>
       </c>
       <c r="I78" t="n">
-        <v>2245.98</v>
+        <v>2314.69</v>
       </c>
       <c r="J78" t="n">
-        <v>2252.81</v>
+        <v>2390.43</v>
       </c>
       <c r="K78" t="n">
-        <v>2346.19</v>
+        <v>2423.26</v>
       </c>
       <c r="L78" t="n">
-        <v>2439.58</v>
+        <v>2456.09</v>
       </c>
       <c r="M78" t="n">
-        <v>2489.68</v>
+        <v>2510.38</v>
       </c>
       <c r="N78" t="n">
-        <v>2539.79</v>
+        <v>2564.66</v>
       </c>
       <c r="O78" t="n">
-        <v>2676.45</v>
+        <v>2576.04</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
       </c>
-      <c r="Q78" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R78" s="6" t="n">
-        <v/>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T78" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="n">
+        <v/>
       </c>
       <c r="U78" s="8" t="n">
         <v/>
@@ -7038,74 +7042,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2466.58</v>
+        <v>2417.83</v>
       </c>
       <c r="C79" t="n">
-        <v>2484.4</v>
+        <v>2427.4</v>
       </c>
       <c r="D79" t="n">
-        <v>2383.8</v>
+        <v>2356.19</v>
       </c>
       <c r="E79" t="n">
-        <v>2417.84</v>
+        <v>2391.5</v>
       </c>
       <c r="F79" t="n">
-        <v>-48.98</v>
+        <v>-26.34</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.0109</v>
       </c>
       <c r="H79" t="n">
-        <v>100.6</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>2314.69</v>
+        <v>2283.21</v>
       </c>
       <c r="J79" t="n">
-        <v>2390.43</v>
+        <v>2309.12</v>
       </c>
       <c r="K79" t="n">
-        <v>2423.26</v>
+        <v>2367.54</v>
       </c>
       <c r="L79" t="n">
-        <v>2456.09</v>
+        <v>2425.97</v>
       </c>
       <c r="M79" t="n">
-        <v>2510.38</v>
+        <v>2468.14</v>
       </c>
       <c r="N79" t="n">
-        <v>2564.66</v>
+        <v>2510.31</v>
       </c>
       <c r="O79" t="n">
-        <v>2576.04</v>
+        <v>2584.99</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
       </c>
-      <c r="Q79" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q79" s="6" t="n">
+        <v/>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S79" s="10" t="inlineStr">
+      <c r="S79" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -7129,50 +7127,50 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2417.83</v>
+        <v>2391.6</v>
       </c>
       <c r="C80" t="n">
-        <v>2427.4</v>
+        <v>2526.95</v>
       </c>
       <c r="D80" t="n">
-        <v>2356.19</v>
+        <v>2370.42</v>
       </c>
       <c r="E80" t="n">
-        <v>2391.5</v>
+        <v>2508.02</v>
       </c>
       <c r="F80" t="n">
-        <v>-26.34</v>
+        <v>116.52</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.0109</v>
+        <v>0.0487</v>
       </c>
       <c r="H80" t="n">
-        <v>71.20999999999999</v>
+        <v>156.53</v>
       </c>
       <c r="I80" t="n">
-        <v>2283.21</v>
+        <v>2284.97</v>
       </c>
       <c r="J80" t="n">
-        <v>2309.12</v>
+        <v>2320.14</v>
       </c>
       <c r="K80" t="n">
-        <v>2367.54</v>
+        <v>2355.89</v>
       </c>
       <c r="L80" t="n">
-        <v>2425.97</v>
+        <v>2391.65</v>
       </c>
       <c r="M80" t="n">
-        <v>2468.14</v>
+        <v>2427.11</v>
       </c>
       <c r="N80" t="n">
-        <v>2510.31</v>
+        <v>2462.57</v>
       </c>
       <c r="O80" t="n">
-        <v>2584.99</v>
+        <v>2498.61</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7180,28 +7178,32 @@
       <c r="Q80" s="6" t="n">
         <v/>
       </c>
-      <c r="R80" s="6" t="inlineStr">
+      <c r="R80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S80" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V80" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S80" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W80" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W80" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X80" t="inlineStr"/>
@@ -7209,50 +7211,50 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2391.6</v>
+        <v>2508.02</v>
       </c>
       <c r="C81" t="n">
-        <v>2526.95</v>
+        <v>2545.62</v>
       </c>
       <c r="D81" t="n">
-        <v>2370.42</v>
+        <v>2432.35</v>
       </c>
       <c r="E81" t="n">
-        <v>2508.02</v>
+        <v>2456.08</v>
       </c>
       <c r="F81" t="n">
-        <v>116.52</v>
+        <v>-51.94</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.0487</v>
+        <v>-0.0207</v>
       </c>
       <c r="H81" t="n">
-        <v>156.53</v>
+        <v>113.27</v>
       </c>
       <c r="I81" t="n">
-        <v>2284.97</v>
+        <v>2213.88</v>
       </c>
       <c r="J81" t="n">
-        <v>2320.14</v>
+        <v>2381.16</v>
       </c>
       <c r="K81" t="n">
-        <v>2355.89</v>
+        <v>2429.75</v>
       </c>
       <c r="L81" t="n">
-        <v>2391.65</v>
+        <v>2478.35</v>
       </c>
       <c r="M81" t="n">
-        <v>2427.11</v>
+        <v>2586.29</v>
       </c>
       <c r="N81" t="n">
-        <v>2462.57</v>
+        <v>2694.22</v>
       </c>
       <c r="O81" t="n">
-        <v>2498.61</v>
+        <v>2683.48</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7265,78 +7267,76 @@
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U81" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V81" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U81" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V81" s="8" t="n">
+        <v/>
       </c>
       <c r="W81" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr"/>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2508.02</v>
+        <v>2455.99</v>
       </c>
       <c r="C82" t="n">
-        <v>2545.62</v>
+        <v>2492.01</v>
       </c>
       <c r="D82" t="n">
-        <v>2432.35</v>
+        <v>2445.69</v>
       </c>
       <c r="E82" t="n">
-        <v>2456.08</v>
+        <v>2480.74</v>
       </c>
       <c r="F82" t="n">
-        <v>-51.94</v>
+        <v>24.66</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.0207</v>
+        <v>0.01</v>
       </c>
       <c r="H82" t="n">
-        <v>113.27</v>
+        <v>46.32</v>
       </c>
       <c r="I82" t="n">
-        <v>2213.88</v>
+        <v>2319.08</v>
       </c>
       <c r="J82" t="n">
-        <v>2381.16</v>
+        <v>2326.35</v>
       </c>
       <c r="K82" t="n">
-        <v>2429.75</v>
+        <v>2399.44</v>
       </c>
       <c r="L82" t="n">
-        <v>2478.35</v>
+        <v>2472.53</v>
       </c>
       <c r="M82" t="n">
-        <v>2586.29</v>
+        <v>2512.71</v>
       </c>
       <c r="N82" t="n">
-        <v>2694.22</v>
+        <v>2552.89</v>
       </c>
       <c r="O82" t="n">
-        <v>2683.48</v>
+        <v>2658.89</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="S82" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T82" s="8" t="n">
@@ -7375,50 +7375,50 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2455.99</v>
+        <v>2480.82</v>
       </c>
       <c r="C83" t="n">
-        <v>2492.01</v>
+        <v>2525.32</v>
       </c>
       <c r="D83" t="n">
-        <v>2445.69</v>
+        <v>2468.19</v>
       </c>
       <c r="E83" t="n">
-        <v>2480.74</v>
+        <v>2514.55</v>
       </c>
       <c r="F83" t="n">
-        <v>24.66</v>
+        <v>33.81</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0136</v>
       </c>
       <c r="H83" t="n">
-        <v>46.32</v>
+        <v>57.13</v>
       </c>
       <c r="I83" t="n">
-        <v>2319.08</v>
+        <v>2399.37</v>
       </c>
       <c r="J83" t="n">
-        <v>2326.35</v>
+        <v>2440.36</v>
       </c>
       <c r="K83" t="n">
-        <v>2399.44</v>
+        <v>2457.58</v>
       </c>
       <c r="L83" t="n">
-        <v>2472.53</v>
+        <v>2474.79</v>
       </c>
       <c r="M83" t="n">
-        <v>2512.71</v>
+        <v>2503.9</v>
       </c>
       <c r="N83" t="n">
-        <v>2552.89</v>
+        <v>2533</v>
       </c>
       <c r="O83" t="n">
-        <v>2658.89</v>
+        <v>2538.33</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
@@ -7429,13 +7429,15 @@
       <c r="R83" s="6" t="n">
         <v/>
       </c>
-      <c r="S83" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="n">
-        <v/>
+      <c r="S83" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U83" s="8" t="n">
         <v/>
@@ -7448,59 +7450,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2480.82</v>
+        <v>2514.58</v>
       </c>
       <c r="C84" t="n">
-        <v>2525.32</v>
+        <v>2534.86</v>
       </c>
       <c r="D84" t="n">
-        <v>2468.19</v>
+        <v>2466.91</v>
       </c>
       <c r="E84" t="n">
-        <v>2514.55</v>
+        <v>2490.96</v>
       </c>
       <c r="F84" t="n">
-        <v>33.81</v>
+        <v>-23.59</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0094</v>
       </c>
       <c r="H84" t="n">
-        <v>57.13</v>
+        <v>67.95</v>
       </c>
       <c r="I84" t="n">
-        <v>2399.37</v>
+        <v>2411.07</v>
       </c>
       <c r="J84" t="n">
-        <v>2440.36</v>
+        <v>2466.32</v>
       </c>
       <c r="K84" t="n">
-        <v>2457.58</v>
+        <v>2485.99</v>
       </c>
       <c r="L84" t="n">
-        <v>2474.79</v>
+        <v>2505.65</v>
       </c>
       <c r="M84" t="n">
-        <v>2503.9</v>
+        <v>2543.11</v>
       </c>
       <c r="N84" t="n">
-        <v>2533</v>
+        <v>2580.57</v>
       </c>
       <c r="O84" t="n">
-        <v>2538.33</v>
+        <v>2582.45</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
@@ -7508,18 +7506,18 @@
       <c r="Q84" s="6" t="n">
         <v/>
       </c>
-      <c r="R84" s="6" t="n">
-        <v/>
+      <c r="R84" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="n">
+        <v/>
       </c>
       <c r="U84" s="8" t="n">
         <v/>
@@ -7532,55 +7530,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr"/>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2514.58</v>
+        <v>2490.92</v>
       </c>
       <c r="C85" t="n">
-        <v>2534.86</v>
+        <v>2506.75</v>
       </c>
       <c r="D85" t="n">
-        <v>2466.91</v>
+        <v>2441.33</v>
       </c>
       <c r="E85" t="n">
-        <v>2490.96</v>
+        <v>2484.94</v>
       </c>
       <c r="F85" t="n">
-        <v>-23.59</v>
+        <v>-6.02</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0024</v>
       </c>
       <c r="H85" t="n">
-        <v>67.95</v>
+        <v>65.42</v>
       </c>
       <c r="I85" t="n">
-        <v>2411.07</v>
+        <v>2398.96</v>
       </c>
       <c r="J85" t="n">
-        <v>2466.32</v>
+        <v>2418.04</v>
       </c>
       <c r="K85" t="n">
-        <v>2485.99</v>
+        <v>2456.98</v>
       </c>
       <c r="L85" t="n">
-        <v>2505.65</v>
+        <v>2495.92</v>
       </c>
       <c r="M85" t="n">
-        <v>2543.11</v>
+        <v>2524.93</v>
       </c>
       <c r="N85" t="n">
-        <v>2580.57</v>
+        <v>2553.94</v>
       </c>
       <c r="O85" t="n">
-        <v>2582.45</v>
+        <v>2602.81</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7590,12 +7592,12 @@
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S85" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S85" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T85" s="8" t="n">
@@ -7614,57 +7616,57 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2490.92</v>
+        <v>2484.89</v>
       </c>
       <c r="C86" t="n">
-        <v>2506.75</v>
+        <v>2522.37</v>
       </c>
       <c r="D86" t="n">
-        <v>2441.33</v>
+        <v>2443.7</v>
       </c>
       <c r="E86" t="n">
-        <v>2484.94</v>
+        <v>2466.91</v>
       </c>
       <c r="F86" t="n">
-        <v>-6.02</v>
+        <v>-18.03</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0073</v>
       </c>
       <c r="H86" t="n">
-        <v>65.42</v>
+        <v>78.67</v>
       </c>
       <c r="I86" t="n">
-        <v>2398.96</v>
+        <v>2375.9</v>
       </c>
       <c r="J86" t="n">
-        <v>2418.04</v>
+        <v>2424.97</v>
       </c>
       <c r="K86" t="n">
-        <v>2456.98</v>
+        <v>2452.23</v>
       </c>
       <c r="L86" t="n">
-        <v>2495.92</v>
+        <v>2479.49</v>
       </c>
       <c r="M86" t="n">
-        <v>2524.93</v>
+        <v>2517.65</v>
       </c>
       <c r="N86" t="n">
-        <v>2553.94</v>
+        <v>2555.82</v>
       </c>
       <c r="O86" t="n">
-        <v>2602.81</v>
+        <v>2572.18</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7677,13 +7679,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S86" s="10" t="inlineStr">
+      <c r="S86" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T86" s="8" t="n">
-        <v/>
+      <c r="T86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U86" s="8" t="n">
         <v/>
@@ -7698,57 +7702,57 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2484.89</v>
+        <v>2466.91</v>
       </c>
       <c r="C87" t="n">
-        <v>2522.37</v>
+        <v>2483.72</v>
       </c>
       <c r="D87" t="n">
-        <v>2443.7</v>
+        <v>2406.91</v>
       </c>
       <c r="E87" t="n">
-        <v>2466.91</v>
+        <v>2437.1</v>
       </c>
       <c r="F87" t="n">
-        <v>-18.03</v>
+        <v>-29.82</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0121</v>
       </c>
       <c r="H87" t="n">
-        <v>78.67</v>
+        <v>76.81</v>
       </c>
       <c r="I87" t="n">
-        <v>2375.9</v>
+        <v>2365.04</v>
       </c>
       <c r="J87" t="n">
-        <v>2424.97</v>
+        <v>2380.19</v>
       </c>
       <c r="K87" t="n">
-        <v>2452.23</v>
+        <v>2427.58</v>
       </c>
       <c r="L87" t="n">
-        <v>2479.49</v>
+        <v>2474.97</v>
       </c>
       <c r="M87" t="n">
-        <v>2517.65</v>
+        <v>2506.25</v>
       </c>
       <c r="N87" t="n">
-        <v>2555.82</v>
+        <v>2537.52</v>
       </c>
       <c r="O87" t="n">
-        <v>2572.18</v>
+        <v>2601.04</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7758,18 +7762,16 @@
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S87" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S87" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="n">
+        <v/>
       </c>
       <c r="U87" s="8" t="n">
         <v/>
@@ -7784,57 +7786,57 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2466.91</v>
+        <v>2437.14</v>
       </c>
       <c r="C88" t="n">
-        <v>2483.72</v>
+        <v>2663.05</v>
       </c>
       <c r="D88" t="n">
-        <v>2406.91</v>
+        <v>2435.29</v>
       </c>
       <c r="E88" t="n">
-        <v>2437.1</v>
+        <v>2514.73</v>
       </c>
       <c r="F88" t="n">
-        <v>-29.82</v>
+        <v>77.64</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-0.0121</v>
+        <v>0.0319</v>
       </c>
       <c r="H88" t="n">
-        <v>76.81</v>
+        <v>227.76</v>
       </c>
       <c r="I88" t="n">
-        <v>2365.04</v>
+        <v>2330.09</v>
       </c>
       <c r="J88" t="n">
-        <v>2380.19</v>
+        <v>2356.18</v>
       </c>
       <c r="K88" t="n">
-        <v>2427.58</v>
+        <v>2398.69</v>
       </c>
       <c r="L88" t="n">
-        <v>2474.97</v>
+        <v>2441.21</v>
       </c>
       <c r="M88" t="n">
-        <v>2506.25</v>
+        <v>2475.51</v>
       </c>
       <c r="N88" t="n">
-        <v>2537.52</v>
+        <v>2509.8</v>
       </c>
       <c r="O88" t="n">
-        <v>2601.04</v>
+        <v>2560.53</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
@@ -7842,83 +7844,83 @@
       <c r="Q88" s="6" t="n">
         <v/>
       </c>
-      <c r="R88" s="6" t="inlineStr">
+      <c r="R88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S88" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U88" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S88" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V88" s="8" t="n">
-        <v/>
+      <c r="V88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W88" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2437.14</v>
+        <v>2514.77</v>
       </c>
       <c r="C89" t="n">
-        <v>2663.05</v>
+        <v>2544.47</v>
       </c>
       <c r="D89" t="n">
-        <v>2435.29</v>
+        <v>2508.8</v>
       </c>
       <c r="E89" t="n">
-        <v>2514.73</v>
+        <v>2525.94</v>
       </c>
       <c r="F89" t="n">
-        <v>77.64</v>
+        <v>11.21</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.0319</v>
+        <v>0.0045</v>
       </c>
       <c r="H89" t="n">
-        <v>227.76</v>
+        <v>35.67</v>
       </c>
       <c r="I89" t="n">
-        <v>2330.09</v>
+        <v>2207.52</v>
       </c>
       <c r="J89" t="n">
-        <v>2356.18</v>
+        <v>2269.75</v>
       </c>
       <c r="K89" t="n">
-        <v>2398.69</v>
+        <v>2400.85</v>
       </c>
       <c r="L89" t="n">
-        <v>2441.21</v>
+        <v>2531.95</v>
       </c>
       <c r="M89" t="n">
-        <v>2475.51</v>
+        <v>2628.62</v>
       </c>
       <c r="N89" t="n">
-        <v>2509.8</v>
+        <v>2725.28</v>
       </c>
       <c r="O89" t="n">
-        <v>2560.53</v>
+        <v>2890.82</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7931,91 +7933,95 @@
       </c>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U89" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V89" s="8" t="n">
+        <v/>
       </c>
       <c r="W89" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr"/>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2514.77</v>
+        <v>2525.94</v>
       </c>
       <c r="C90" t="n">
-        <v>2544.47</v>
+        <v>2526.85</v>
       </c>
       <c r="D90" t="n">
-        <v>2508.8</v>
+        <v>2462.84</v>
       </c>
       <c r="E90" t="n">
-        <v>2525.94</v>
+        <v>2477.02</v>
       </c>
       <c r="F90" t="n">
-        <v>11.21</v>
+        <v>-48.92</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0194</v>
       </c>
       <c r="H90" t="n">
-        <v>35.67</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>2207.52</v>
+        <v>2473.13</v>
       </c>
       <c r="J90" t="n">
-        <v>2269.75</v>
+        <v>2489.93</v>
       </c>
       <c r="K90" t="n">
-        <v>2400.85</v>
+        <v>2508.11</v>
       </c>
       <c r="L90" t="n">
-        <v>2531.95</v>
+        <v>2526.29</v>
       </c>
       <c r="M90" t="n">
-        <v>2628.62</v>
+        <v>2543.78</v>
       </c>
       <c r="N90" t="n">
-        <v>2725.28</v>
+        <v>2561.27</v>
       </c>
       <c r="O90" t="n">
-        <v>2890.82</v>
-      </c>
-      <c r="P90" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q90" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R90" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S90" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>2580.14</v>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S90" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T90" s="8" t="n">
@@ -8027,104 +8033,96 @@
       <c r="V90" s="8" t="n">
         <v/>
       </c>
-      <c r="W90" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W90" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2525.68</v>
+        <v>2475.82</v>
       </c>
       <c r="C91" t="n">
-        <v>2526.74</v>
+        <v>2605.78</v>
       </c>
       <c r="D91" t="n">
-        <v>2466.28</v>
+        <v>2468.6</v>
       </c>
       <c r="E91" t="n">
-        <v>2493.1</v>
+        <v>2548.83</v>
       </c>
       <c r="F91" t="n">
-        <v>-32.84</v>
+        <v>71.81</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.013</v>
+        <v>0.029</v>
       </c>
       <c r="H91" t="n">
-        <v>60.46</v>
+        <v>137.18</v>
       </c>
       <c r="I91" t="n">
-        <v>2473.13</v>
+        <v>2398.83</v>
       </c>
       <c r="J91" t="n">
-        <v>2489.93</v>
+        <v>2404.09</v>
       </c>
       <c r="K91" t="n">
-        <v>2508.11</v>
+        <v>2445.01</v>
       </c>
       <c r="L91" t="n">
-        <v>2526.29</v>
+        <v>2485.93</v>
       </c>
       <c r="M91" t="n">
-        <v>2543.78</v>
+        <v>2509.03</v>
       </c>
       <c r="N91" t="n">
-        <v>2561.27</v>
+        <v>2532.12</v>
       </c>
       <c r="O91" t="n">
-        <v>2580.14</v>
-      </c>
-      <c r="P91" s="6" t="inlineStr">
+        <v>2590.87</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S91" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q91" s="6" t="inlineStr">
+      <c r="U91" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R91" s="6" t="inlineStr">
+      <c r="V91" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S91" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
-      </c>
       <c r="W91" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
@@ -8133,25 +8131,25 @@
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>2405.82</v>
+        <v>2331.42</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>2430.94</v>
+        <v>2417.47</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>2462.87</v>
+        <v>2480.24</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>2494.8</v>
+        <v>2543.01</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>2523.33</v>
+        <v>2617.42</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>2551.85</v>
+        <v>2691.83</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>2587.19</v>
+        <v>2742.96</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1790.4</v>
+        <v>1747.88</v>
       </c>
       <c r="C2" t="n">
-        <v>1807.28</v>
+        <v>1760.88</v>
       </c>
       <c r="D2" t="n">
-        <v>1724.72</v>
+        <v>1670.1</v>
       </c>
       <c r="E2" t="n">
-        <v>1747.89</v>
+        <v>1709.53</v>
       </c>
       <c r="F2" t="n">
-        <v>-42.51</v>
+        <v>-38.35</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0237</v>
+        <v>-0.0219</v>
       </c>
       <c r="H2" t="n">
-        <v>82.56</v>
+        <v>90.78</v>
       </c>
       <c r="I2" t="n">
-        <v>1679.06</v>
+        <v>1642.15</v>
       </c>
       <c r="J2" t="n">
-        <v>1707.69</v>
+        <v>1656.26</v>
       </c>
       <c r="K2" t="n">
-        <v>1750.86</v>
+        <v>1706.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1794.03</v>
+        <v>1756.94</v>
       </c>
       <c r="M2" t="n">
-        <v>1829.94</v>
+        <v>1789.17</v>
       </c>
       <c r="N2" t="n">
-        <v>1865.84</v>
+        <v>1821.39</v>
       </c>
       <c r="O2" t="n">
-        <v>1916.28</v>
+        <v>1889.85</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -725,50 +725,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1747.88</v>
+        <v>1709.5</v>
       </c>
       <c r="C3" t="n">
-        <v>1760.88</v>
+        <v>1717.19</v>
       </c>
       <c r="D3" t="n">
-        <v>1670.1</v>
+        <v>1678.2</v>
       </c>
       <c r="E3" t="n">
-        <v>1709.53</v>
+        <v>1710.98</v>
       </c>
       <c r="F3" t="n">
-        <v>-38.35</v>
+        <v>1.45</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0219</v>
+        <v>0.0008</v>
       </c>
       <c r="H3" t="n">
-        <v>90.78</v>
+        <v>39</v>
       </c>
       <c r="I3" t="n">
-        <v>1642.15</v>
+        <v>1579.33</v>
       </c>
       <c r="J3" t="n">
-        <v>1656.26</v>
+        <v>1615.78</v>
       </c>
       <c r="K3" t="n">
-        <v>1706.6</v>
+        <v>1664.14</v>
       </c>
       <c r="L3" t="n">
-        <v>1756.94</v>
+        <v>1712.51</v>
       </c>
       <c r="M3" t="n">
-        <v>1789.17</v>
+        <v>1754.92</v>
       </c>
       <c r="N3" t="n">
-        <v>1821.39</v>
+        <v>1797.33</v>
       </c>
       <c r="O3" t="n">
-        <v>1889.85</v>
+        <v>1851.66</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -776,14 +776,12 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -802,57 +800,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1709.5</v>
+        <v>1710.98</v>
       </c>
       <c r="C4" t="n">
-        <v>1717.19</v>
+        <v>1747.26</v>
       </c>
       <c r="D4" t="n">
-        <v>1678.2</v>
+        <v>1702.8</v>
       </c>
       <c r="E4" t="n">
-        <v>1710.98</v>
+        <v>1739.3</v>
       </c>
       <c r="F4" t="n">
-        <v>1.45</v>
+        <v>28.32</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0166</v>
       </c>
       <c r="H4" t="n">
-        <v>39</v>
+        <v>44.46</v>
       </c>
       <c r="I4" t="n">
-        <v>1579.33</v>
+        <v>1639.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1615.78</v>
+        <v>1678.63</v>
       </c>
       <c r="K4" t="n">
-        <v>1664.14</v>
+        <v>1691.48</v>
       </c>
       <c r="L4" t="n">
-        <v>1712.51</v>
+        <v>1704.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1754.92</v>
+        <v>1730.48</v>
       </c>
       <c r="N4" t="n">
-        <v>1797.33</v>
+        <v>1756.62</v>
       </c>
       <c r="O4" t="n">
-        <v>1851.66</v>
+        <v>1756.19</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -863,13 +861,15 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -882,79 +882,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1710.98</v>
+        <v>1739.34</v>
       </c>
       <c r="C5" t="n">
-        <v>1747.26</v>
+        <v>1739.49</v>
       </c>
       <c r="D5" t="n">
-        <v>1702.8</v>
+        <v>1701.94</v>
       </c>
       <c r="E5" t="n">
-        <v>1739.3</v>
+        <v>1704.58</v>
       </c>
       <c r="F5" t="n">
-        <v>28.32</v>
+        <v>-34.72</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.02</v>
       </c>
       <c r="H5" t="n">
-        <v>44.46</v>
+        <v>37.55</v>
       </c>
       <c r="I5" t="n">
-        <v>1639.2</v>
+        <v>1658.34</v>
       </c>
       <c r="J5" t="n">
-        <v>1678.63</v>
+        <v>1701.98</v>
       </c>
       <c r="K5" t="n">
-        <v>1691.48</v>
+        <v>1717.07</v>
       </c>
       <c r="L5" t="n">
-        <v>1704.34</v>
+        <v>1732.17</v>
       </c>
       <c r="M5" t="n">
-        <v>1730.48</v>
+        <v>1761.53</v>
       </c>
       <c r="N5" t="n">
-        <v>1756.62</v>
+        <v>1790.89</v>
       </c>
       <c r="O5" t="n">
-        <v>1756.19</v>
+        <v>1791.72</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -966,80 +964,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1739.34</v>
+        <v>1704.63</v>
       </c>
       <c r="C6" t="n">
-        <v>1739.49</v>
+        <v>1776.83</v>
       </c>
       <c r="D6" t="n">
-        <v>1701.94</v>
+        <v>1704.52</v>
       </c>
       <c r="E6" t="n">
-        <v>1704.58</v>
+        <v>1726.51</v>
       </c>
       <c r="F6" t="n">
-        <v>-34.72</v>
+        <v>21.93</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0129</v>
       </c>
       <c r="H6" t="n">
-        <v>37.55</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>1658.34</v>
+        <v>1664.39</v>
       </c>
       <c r="J6" t="n">
-        <v>1701.98</v>
+        <v>1658.97</v>
       </c>
       <c r="K6" t="n">
-        <v>1717.07</v>
+        <v>1685.81</v>
       </c>
       <c r="L6" t="n">
-        <v>1732.17</v>
+        <v>1712.65</v>
       </c>
       <c r="M6" t="n">
-        <v>1761.53</v>
+        <v>1723.36</v>
       </c>
       <c r="N6" t="n">
-        <v>1790.89</v>
+        <v>1734.06</v>
       </c>
       <c r="O6" t="n">
-        <v>1791.72</v>
+        <v>1777.04</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1048,84 +1050,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1704.63</v>
+        <v>1726.52</v>
       </c>
       <c r="C7" t="n">
-        <v>1776.83</v>
+        <v>1733.61</v>
       </c>
       <c r="D7" t="n">
-        <v>1704.52</v>
+        <v>1638.25</v>
       </c>
       <c r="E7" t="n">
-        <v>1726.51</v>
+        <v>1665.44</v>
       </c>
       <c r="F7" t="n">
-        <v>21.93</v>
+        <v>-61.07</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0354</v>
       </c>
       <c r="H7" t="n">
-        <v>72.31999999999999</v>
+        <v>95.36</v>
       </c>
       <c r="I7" t="n">
-        <v>1664.39</v>
+        <v>1632.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1658.97</v>
+        <v>1647.11</v>
       </c>
       <c r="K7" t="n">
-        <v>1685.81</v>
+        <v>1690.35</v>
       </c>
       <c r="L7" t="n">
-        <v>1712.65</v>
+        <v>1733.59</v>
       </c>
       <c r="M7" t="n">
-        <v>1723.36</v>
+        <v>1762.67</v>
       </c>
       <c r="N7" t="n">
-        <v>1734.06</v>
+        <v>1791.74</v>
       </c>
       <c r="O7" t="n">
-        <v>1777.04</v>
+        <v>1849.15</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1134,67 +1132,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1726.52</v>
+        <v>1665.31</v>
       </c>
       <c r="C8" t="n">
-        <v>1733.61</v>
+        <v>1687.49</v>
       </c>
       <c r="D8" t="n">
-        <v>1638.25</v>
+        <v>1551.48</v>
       </c>
       <c r="E8" t="n">
-        <v>1665.44</v>
+        <v>1619.92</v>
       </c>
       <c r="F8" t="n">
-        <v>-61.07</v>
+        <v>-45.51</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0354</v>
+        <v>-0.0273</v>
       </c>
       <c r="H8" t="n">
-        <v>95.36</v>
+        <v>136.01</v>
       </c>
       <c r="I8" t="n">
-        <v>1632.2</v>
+        <v>1542.89</v>
       </c>
       <c r="J8" t="n">
-        <v>1647.11</v>
+        <v>1559.83</v>
       </c>
       <c r="K8" t="n">
-        <v>1690.35</v>
+        <v>1617.76</v>
       </c>
       <c r="L8" t="n">
-        <v>1733.59</v>
+        <v>1675.68</v>
       </c>
       <c r="M8" t="n">
-        <v>1762.67</v>
+        <v>1713.12</v>
       </c>
       <c r="N8" t="n">
-        <v>1791.74</v>
+        <v>1750.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1849.15</v>
+        <v>1828.97</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
@@ -1225,58 +1227,56 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1665.31</v>
+        <v>1619.89</v>
       </c>
       <c r="C9" t="n">
-        <v>1687.49</v>
+        <v>1656.65</v>
       </c>
       <c r="D9" t="n">
-        <v>1551.48</v>
+        <v>1531.78</v>
       </c>
       <c r="E9" t="n">
-        <v>1619.92</v>
+        <v>1564.82</v>
       </c>
       <c r="F9" t="n">
-        <v>-45.51</v>
+        <v>-55.11</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.034</v>
       </c>
       <c r="H9" t="n">
-        <v>136.01</v>
+        <v>124.87</v>
       </c>
       <c r="I9" t="n">
-        <v>1542.89</v>
+        <v>1415.48</v>
       </c>
       <c r="J9" t="n">
-        <v>1559.83</v>
+        <v>1484.14</v>
       </c>
       <c r="K9" t="n">
-        <v>1617.76</v>
+        <v>1551.92</v>
       </c>
       <c r="L9" t="n">
-        <v>1675.68</v>
+        <v>1619.71</v>
       </c>
       <c r="M9" t="n">
-        <v>1713.12</v>
+        <v>1687.93</v>
       </c>
       <c r="N9" t="n">
-        <v>1750.55</v>
+        <v>1756.15</v>
       </c>
       <c r="O9" t="n">
-        <v>1828.97</v>
+        <v>1823.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q9" s="6" t="n">
+        <v/>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
@@ -1311,50 +1311,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1619.89</v>
+        <v>1564.61</v>
       </c>
       <c r="C10" t="n">
-        <v>1656.65</v>
+        <v>1590.2</v>
       </c>
       <c r="D10" t="n">
-        <v>1531.78</v>
+        <v>1510.51</v>
       </c>
       <c r="E10" t="n">
-        <v>1564.82</v>
+        <v>1576.62</v>
       </c>
       <c r="F10" t="n">
-        <v>-55.11</v>
+        <v>11.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.034</v>
+        <v>0.0075</v>
       </c>
       <c r="H10" t="n">
-        <v>124.87</v>
+        <v>79.69</v>
       </c>
       <c r="I10" t="n">
-        <v>1415.48</v>
+        <v>1406.91</v>
       </c>
       <c r="J10" t="n">
-        <v>1484.14</v>
+        <v>1425.25</v>
       </c>
       <c r="K10" t="n">
-        <v>1551.92</v>
+        <v>1502.38</v>
       </c>
       <c r="L10" t="n">
-        <v>1619.71</v>
+        <v>1579.52</v>
       </c>
       <c r="M10" t="n">
-        <v>1687.93</v>
+        <v>1627.25</v>
       </c>
       <c r="N10" t="n">
-        <v>1756.15</v>
+        <v>1674.98</v>
       </c>
       <c r="O10" t="n">
-        <v>1823.5</v>
+        <v>1781.51</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1362,14 +1362,12 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1388,57 +1386,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1564.61</v>
+        <v>1576.59</v>
       </c>
       <c r="C11" t="n">
-        <v>1590.2</v>
+        <v>1607.87</v>
       </c>
       <c r="D11" t="n">
-        <v>1510.51</v>
+        <v>1561.97</v>
       </c>
       <c r="E11" t="n">
-        <v>1576.62</v>
+        <v>1571.59</v>
       </c>
       <c r="F11" t="n">
-        <v>11.8</v>
+        <v>-5.03</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0032</v>
       </c>
       <c r="H11" t="n">
-        <v>79.69</v>
+        <v>45.89</v>
       </c>
       <c r="I11" t="n">
-        <v>1406.91</v>
+        <v>1430.81</v>
       </c>
       <c r="J11" t="n">
-        <v>1425.25</v>
+        <v>1510.05</v>
       </c>
       <c r="K11" t="n">
-        <v>1502.38</v>
+        <v>1536.77</v>
       </c>
       <c r="L11" t="n">
-        <v>1579.52</v>
+        <v>1563.48</v>
       </c>
       <c r="M11" t="n">
-        <v>1627.25</v>
+        <v>1616.46</v>
       </c>
       <c r="N11" t="n">
-        <v>1674.98</v>
+        <v>1669.44</v>
       </c>
       <c r="O11" t="n">
-        <v>1781.51</v>
+        <v>1669.89</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1449,9 +1447,9 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1470,57 +1468,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1576.59</v>
+        <v>1571.56</v>
       </c>
       <c r="C12" t="n">
-        <v>1607.87</v>
+        <v>1585.22</v>
       </c>
       <c r="D12" t="n">
-        <v>1561.97</v>
+        <v>1548.76</v>
       </c>
       <c r="E12" t="n">
-        <v>1571.59</v>
+        <v>1570.36</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.03</v>
+        <v>-1.23</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.0008</v>
       </c>
       <c r="H12" t="n">
-        <v>45.89</v>
+        <v>36.46</v>
       </c>
       <c r="I12" t="n">
-        <v>1430.81</v>
+        <v>1516.08</v>
       </c>
       <c r="J12" t="n">
-        <v>1510.05</v>
+        <v>1519.03</v>
       </c>
       <c r="K12" t="n">
-        <v>1536.77</v>
+        <v>1548.64</v>
       </c>
       <c r="L12" t="n">
-        <v>1563.48</v>
+        <v>1578.25</v>
       </c>
       <c r="M12" t="n">
-        <v>1616.46</v>
+        <v>1594.53</v>
       </c>
       <c r="N12" t="n">
-        <v>1669.44</v>
+        <v>1610.82</v>
       </c>
       <c r="O12" t="n">
-        <v>1669.89</v>
+        <v>1653.76</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1531,9 +1529,9 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1552,57 +1550,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1571.56</v>
+        <v>1569.99</v>
       </c>
       <c r="C13" t="n">
-        <v>1585.22</v>
+        <v>1633.65</v>
       </c>
       <c r="D13" t="n">
-        <v>1548.76</v>
+        <v>1550.04</v>
       </c>
       <c r="E13" t="n">
-        <v>1570.36</v>
+        <v>1610.21</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.23</v>
+        <v>39.84</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0254</v>
       </c>
       <c r="H13" t="n">
-        <v>36.46</v>
+        <v>83.61</v>
       </c>
       <c r="I13" t="n">
-        <v>1516.08</v>
+        <v>1512.3</v>
       </c>
       <c r="J13" t="n">
-        <v>1519.03</v>
+        <v>1535.59</v>
       </c>
       <c r="K13" t="n">
-        <v>1548.64</v>
+        <v>1552.13</v>
       </c>
       <c r="L13" t="n">
-        <v>1578.25</v>
+        <v>1568.68</v>
       </c>
       <c r="M13" t="n">
-        <v>1594.53</v>
+        <v>1588.59</v>
       </c>
       <c r="N13" t="n">
-        <v>1610.82</v>
+        <v>1608.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1653.76</v>
+        <v>1621.68</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1610,81 +1608,85 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1569.99</v>
+        <v>1610.16</v>
       </c>
       <c r="C14" t="n">
-        <v>1633.65</v>
+        <v>1611.35</v>
       </c>
       <c r="D14" t="n">
-        <v>1550.04</v>
+        <v>1549.25</v>
       </c>
       <c r="E14" t="n">
-        <v>1610.21</v>
+        <v>1569.58</v>
       </c>
       <c r="F14" t="n">
-        <v>39.84</v>
+        <v>-40.62</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0254</v>
+        <v>-0.0252</v>
       </c>
       <c r="H14" t="n">
-        <v>83.61</v>
+        <v>62.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1512.3</v>
+        <v>1466.43</v>
       </c>
       <c r="J14" t="n">
-        <v>1535.59</v>
+        <v>1535.78</v>
       </c>
       <c r="K14" t="n">
-        <v>1552.13</v>
+        <v>1568.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1568.68</v>
+        <v>1601.02</v>
       </c>
       <c r="M14" t="n">
-        <v>1588.59</v>
+        <v>1652.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1608.5</v>
+        <v>1703</v>
       </c>
       <c r="O14" t="n">
-        <v>1621.68</v>
+        <v>1717.25</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,83 +1696,81 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1610.16</v>
+        <v>1569.91</v>
       </c>
       <c r="C15" t="n">
-        <v>1611.35</v>
+        <v>1642.45</v>
       </c>
       <c r="D15" t="n">
-        <v>1549.25</v>
+        <v>1551.14</v>
       </c>
       <c r="E15" t="n">
-        <v>1569.58</v>
+        <v>1608.96</v>
       </c>
       <c r="F15" t="n">
-        <v>-40.62</v>
+        <v>39.38</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0252</v>
+        <v>0.0251</v>
       </c>
       <c r="H15" t="n">
-        <v>62.1</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>1466.43</v>
+        <v>1487.16</v>
       </c>
       <c r="J15" t="n">
-        <v>1535.78</v>
+        <v>1502.13</v>
       </c>
       <c r="K15" t="n">
-        <v>1568.4</v>
+        <v>1538.54</v>
       </c>
       <c r="L15" t="n">
-        <v>1601.02</v>
+        <v>1574.94</v>
       </c>
       <c r="M15" t="n">
-        <v>1652.01</v>
+        <v>1600.63</v>
       </c>
       <c r="N15" t="n">
-        <v>1703</v>
+        <v>1626.32</v>
       </c>
       <c r="O15" t="n">
-        <v>1717.25</v>
+        <v>1673.44</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1778,21 +1778,23 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1802,59 +1804,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1569.91</v>
+        <v>1609.01</v>
       </c>
       <c r="C16" t="n">
-        <v>1642.45</v>
+        <v>1720.34</v>
       </c>
       <c r="D16" t="n">
-        <v>1551.14</v>
+        <v>1595.94</v>
       </c>
       <c r="E16" t="n">
-        <v>1608.96</v>
+        <v>1698.17</v>
       </c>
       <c r="F16" t="n">
-        <v>39.38</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0554</v>
       </c>
       <c r="H16" t="n">
-        <v>91.31999999999999</v>
+        <v>124.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1487.16</v>
+        <v>1459.82</v>
       </c>
       <c r="J16" t="n">
-        <v>1502.13</v>
+        <v>1523.73</v>
       </c>
       <c r="K16" t="n">
-        <v>1538.54</v>
+        <v>1563.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1574.94</v>
+        <v>1602.88</v>
       </c>
       <c r="M16" t="n">
-        <v>1600.63</v>
+        <v>1654.62</v>
       </c>
       <c r="N16" t="n">
-        <v>1626.32</v>
+        <v>1706.36</v>
       </c>
       <c r="O16" t="n">
-        <v>1673.44</v>
+        <v>1733.77</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1872,12 +1870,12 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V16" s="8" t="n">
@@ -1893,50 +1891,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1609.01</v>
+        <v>1698.42</v>
       </c>
       <c r="C17" t="n">
-        <v>1720.34</v>
+        <v>1772.54</v>
       </c>
       <c r="D17" t="n">
-        <v>1595.94</v>
+        <v>1693.04</v>
       </c>
       <c r="E17" t="n">
-        <v>1698.17</v>
+        <v>1756.52</v>
       </c>
       <c r="F17" t="n">
-        <v>89.20999999999999</v>
+        <v>58.35</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0344</v>
       </c>
       <c r="H17" t="n">
-        <v>124.4</v>
+        <v>79.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1459.82</v>
+        <v>1471.54</v>
       </c>
       <c r="J17" t="n">
-        <v>1523.73</v>
+        <v>1593.78</v>
       </c>
       <c r="K17" t="n">
-        <v>1563.3</v>
+        <v>1635.97</v>
       </c>
       <c r="L17" t="n">
-        <v>1602.88</v>
+        <v>1678.16</v>
       </c>
       <c r="M17" t="n">
-        <v>1654.62</v>
+        <v>1760.37</v>
       </c>
       <c r="N17" t="n">
-        <v>1706.36</v>
+        <v>1842.59</v>
       </c>
       <c r="O17" t="n">
-        <v>1733.77</v>
+        <v>1844.75</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1954,13 +1952,11 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1975,50 +1971,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1698.42</v>
+        <v>1756.58</v>
       </c>
       <c r="C18" t="n">
-        <v>1772.54</v>
+        <v>1804.59</v>
       </c>
       <c r="D18" t="n">
-        <v>1693.04</v>
+        <v>1743.56</v>
       </c>
       <c r="E18" t="n">
-        <v>1756.52</v>
+        <v>1779.03</v>
       </c>
       <c r="F18" t="n">
-        <v>58.35</v>
+        <v>22.51</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0128</v>
       </c>
       <c r="H18" t="n">
-        <v>79.5</v>
+        <v>61.02</v>
       </c>
       <c r="I18" t="n">
-        <v>1471.54</v>
+        <v>1613.53</v>
       </c>
       <c r="J18" t="n">
-        <v>1593.78</v>
+        <v>1688.88</v>
       </c>
       <c r="K18" t="n">
-        <v>1635.97</v>
+        <v>1716.77</v>
       </c>
       <c r="L18" t="n">
-        <v>1678.16</v>
+        <v>1744.65</v>
       </c>
       <c r="M18" t="n">
-        <v>1760.37</v>
+        <v>1796.27</v>
       </c>
       <c r="N18" t="n">
-        <v>1842.59</v>
+        <v>1847.89</v>
       </c>
       <c r="O18" t="n">
-        <v>1844.75</v>
+        <v>1852.05</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2055,50 +2051,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1756.58</v>
+        <v>1779.04</v>
       </c>
       <c r="C19" t="n">
-        <v>1804.59</v>
+        <v>1805.91</v>
       </c>
       <c r="D19" t="n">
-        <v>1743.56</v>
+        <v>1749.14</v>
       </c>
       <c r="E19" t="n">
-        <v>1779.03</v>
+        <v>1783.01</v>
       </c>
       <c r="F19" t="n">
-        <v>22.51</v>
+        <v>3.97</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0022</v>
       </c>
       <c r="H19" t="n">
-        <v>61.02</v>
+        <v>56.78</v>
       </c>
       <c r="I19" t="n">
-        <v>1613.53</v>
+        <v>1682.54</v>
       </c>
       <c r="J19" t="n">
-        <v>1688.88</v>
+        <v>1720.49</v>
       </c>
       <c r="K19" t="n">
-        <v>1716.77</v>
+        <v>1748.52</v>
       </c>
       <c r="L19" t="n">
-        <v>1744.65</v>
+        <v>1776.55</v>
       </c>
       <c r="M19" t="n">
-        <v>1796.27</v>
+        <v>1809.55</v>
       </c>
       <c r="N19" t="n">
-        <v>1847.89</v>
+        <v>1842.54</v>
       </c>
       <c r="O19" t="n">
-        <v>1852.05</v>
+        <v>1865.61</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2111,13 +2107,11 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2135,67 +2129,73 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779.04</v>
+        <v>1783</v>
       </c>
       <c r="C20" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D20" t="n">
-        <v>1749.14</v>
+        <v>1728.97</v>
       </c>
       <c r="E20" t="n">
-        <v>1783.01</v>
+        <v>1797.57</v>
       </c>
       <c r="F20" t="n">
-        <v>3.97</v>
+        <v>14.57</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>56.78</v>
+        <v>100.55</v>
       </c>
       <c r="I20" t="n">
-        <v>1682.54</v>
+        <v>1692.36</v>
       </c>
       <c r="J20" t="n">
-        <v>1720.49</v>
+        <v>1728.97</v>
       </c>
       <c r="K20" t="n">
-        <v>1748.52</v>
+        <v>1754.62</v>
       </c>
       <c r="L20" t="n">
-        <v>1776.55</v>
+        <v>1780.27</v>
       </c>
       <c r="M20" t="n">
-        <v>1809.55</v>
+        <v>1811.39</v>
       </c>
       <c r="N20" t="n">
-        <v>1842.54</v>
+        <v>1842.52</v>
       </c>
       <c r="O20" t="n">
-        <v>1865.61</v>
+        <v>1862.69</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2208,78 +2208,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1783</v>
+        <v>1797.56</v>
       </c>
       <c r="C21" t="n">
-        <v>1829.51</v>
+        <v>1810.33</v>
       </c>
       <c r="D21" t="n">
-        <v>1728.97</v>
+        <v>1756.71</v>
       </c>
       <c r="E21" t="n">
-        <v>1797.57</v>
+        <v>1768.51</v>
       </c>
       <c r="F21" t="n">
-        <v>14.57</v>
+        <v>-29.06</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0162</v>
       </c>
       <c r="H21" t="n">
-        <v>100.55</v>
+        <v>53.62</v>
       </c>
       <c r="I21" t="n">
-        <v>1692.36</v>
+        <v>1628.42</v>
       </c>
       <c r="J21" t="n">
-        <v>1728.97</v>
+        <v>1706.19</v>
       </c>
       <c r="K21" t="n">
-        <v>1754.62</v>
+        <v>1747.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1780.27</v>
+        <v>1788.41</v>
       </c>
       <c r="M21" t="n">
-        <v>1811.39</v>
+        <v>1847.85</v>
       </c>
       <c r="N21" t="n">
-        <v>1842.52</v>
+        <v>1907.29</v>
       </c>
       <c r="O21" t="n">
-        <v>1862.69</v>
+        <v>1930.06</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2294,57 +2292,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1797.56</v>
+        <v>1768.39</v>
       </c>
       <c r="C22" t="n">
-        <v>1810.33</v>
+        <v>1782.86</v>
       </c>
       <c r="D22" t="n">
-        <v>1756.71</v>
+        <v>1711.9</v>
       </c>
       <c r="E22" t="n">
-        <v>1768.51</v>
+        <v>1742.68</v>
       </c>
       <c r="F22" t="n">
-        <v>-29.06</v>
+        <v>-25.83</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0146</v>
       </c>
       <c r="H22" t="n">
-        <v>53.62</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>1628.42</v>
+        <v>1703.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1706.19</v>
+        <v>1707.39</v>
       </c>
       <c r="K22" t="n">
-        <v>1747.3</v>
+        <v>1741.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1788.41</v>
+        <v>1776.02</v>
       </c>
       <c r="M22" t="n">
-        <v>1847.85</v>
+        <v>1795.32</v>
       </c>
       <c r="N22" t="n">
-        <v>1907.29</v>
+        <v>1814.62</v>
       </c>
       <c r="O22" t="n">
-        <v>1930.06</v>
+        <v>1863.95</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2352,12 +2350,14 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2376,57 +2376,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1768.39</v>
+        <v>1742.66</v>
       </c>
       <c r="C23" t="n">
-        <v>1782.86</v>
+        <v>1760.21</v>
       </c>
       <c r="D23" t="n">
-        <v>1711.9</v>
+        <v>1721.3</v>
       </c>
       <c r="E23" t="n">
-        <v>1742.68</v>
+        <v>1744.48</v>
       </c>
       <c r="F23" t="n">
-        <v>-25.83</v>
+        <v>1.81</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>70.95999999999999</v>
+        <v>38.91</v>
       </c>
       <c r="I23" t="n">
-        <v>1703.1</v>
+        <v>1640.94</v>
       </c>
       <c r="J23" t="n">
-        <v>1707.39</v>
+        <v>1669.37</v>
       </c>
       <c r="K23" t="n">
-        <v>1741.7</v>
+        <v>1707.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1776.02</v>
+        <v>1745.03</v>
       </c>
       <c r="M23" t="n">
-        <v>1795.32</v>
+        <v>1778.16</v>
       </c>
       <c r="N23" t="n">
-        <v>1814.62</v>
+        <v>1811.29</v>
       </c>
       <c r="O23" t="n">
-        <v>1863.95</v>
+        <v>1853.82</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2434,14 +2434,12 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2460,57 +2458,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1742.66</v>
+        <v>1744.47</v>
       </c>
       <c r="C24" t="n">
-        <v>1760.21</v>
+        <v>1809.76</v>
       </c>
       <c r="D24" t="n">
-        <v>1721.3</v>
+        <v>1736.72</v>
       </c>
       <c r="E24" t="n">
-        <v>1744.48</v>
+        <v>1795.69</v>
       </c>
       <c r="F24" t="n">
-        <v>1.81</v>
+        <v>51.21</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0294</v>
       </c>
       <c r="H24" t="n">
-        <v>38.91</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>1640.94</v>
+        <v>1682.39</v>
       </c>
       <c r="J24" t="n">
-        <v>1669.37</v>
+        <v>1707.44</v>
       </c>
       <c r="K24" t="n">
-        <v>1707.2</v>
+        <v>1725.03</v>
       </c>
       <c r="L24" t="n">
-        <v>1745.03</v>
+        <v>1742.62</v>
       </c>
       <c r="M24" t="n">
-        <v>1778.16</v>
+        <v>1763.94</v>
       </c>
       <c r="N24" t="n">
-        <v>1811.29</v>
+        <v>1785.26</v>
       </c>
       <c r="O24" t="n">
-        <v>1853.82</v>
+        <v>1799.11</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2521,78 +2519,80 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1744.47</v>
+        <v>1795.82</v>
       </c>
       <c r="C25" t="n">
-        <v>1809.76</v>
+        <v>1827.83</v>
       </c>
       <c r="D25" t="n">
-        <v>1736.72</v>
+        <v>1786.3</v>
       </c>
       <c r="E25" t="n">
-        <v>1795.69</v>
+        <v>1788.1</v>
       </c>
       <c r="F25" t="n">
-        <v>51.21</v>
+        <v>-7.59</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0294</v>
+        <v>-0.0042</v>
       </c>
       <c r="H25" t="n">
-        <v>73.04000000000001</v>
+        <v>41.54</v>
       </c>
       <c r="I25" t="n">
-        <v>1682.39</v>
+        <v>1663.69</v>
       </c>
       <c r="J25" t="n">
-        <v>1707.44</v>
+        <v>1733.88</v>
       </c>
       <c r="K25" t="n">
-        <v>1725.03</v>
+        <v>1759.18</v>
       </c>
       <c r="L25" t="n">
-        <v>1742.62</v>
+        <v>1784.47</v>
       </c>
       <c r="M25" t="n">
-        <v>1763.94</v>
+        <v>1832.21</v>
       </c>
       <c r="N25" t="n">
-        <v>1785.26</v>
+        <v>1879.95</v>
       </c>
       <c r="O25" t="n">
-        <v>1799.11</v>
+        <v>1882.79</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,78 +2605,76 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1795.82</v>
+        <v>1787.57</v>
       </c>
       <c r="C26" t="n">
-        <v>1827.83</v>
+        <v>1824.98</v>
       </c>
       <c r="D26" t="n">
-        <v>1786.3</v>
+        <v>1779.64</v>
       </c>
       <c r="E26" t="n">
-        <v>1788.1</v>
+        <v>1805.79</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.59</v>
+        <v>17.69</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>41.54</v>
+        <v>45.34</v>
       </c>
       <c r="I26" t="n">
-        <v>1663.69</v>
+        <v>1744.76</v>
       </c>
       <c r="J26" t="n">
-        <v>1733.88</v>
+        <v>1737.08</v>
       </c>
       <c r="K26" t="n">
-        <v>1759.18</v>
+        <v>1767.33</v>
       </c>
       <c r="L26" t="n">
-        <v>1784.47</v>
+        <v>1797.58</v>
       </c>
       <c r="M26" t="n">
-        <v>1832.21</v>
+        <v>1808.87</v>
       </c>
       <c r="N26" t="n">
-        <v>1879.95</v>
+        <v>1820.15</v>
       </c>
       <c r="O26" t="n">
-        <v>1882.79</v>
+        <v>1869.37</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2689,14 +2687,18 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2708,81 +2710,83 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1787.57</v>
+        <v>1805.76</v>
       </c>
       <c r="C27" t="n">
-        <v>1824.98</v>
+        <v>1842.46</v>
       </c>
       <c r="D27" t="n">
-        <v>1779.64</v>
+        <v>1749.35</v>
       </c>
       <c r="E27" t="n">
-        <v>1805.79</v>
+        <v>1773.5</v>
       </c>
       <c r="F27" t="n">
-        <v>17.69</v>
+        <v>-32.29</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.0179</v>
       </c>
       <c r="H27" t="n">
-        <v>45.34</v>
+        <v>93.11</v>
       </c>
       <c r="I27" t="n">
-        <v>1744.76</v>
+        <v>1734.29</v>
       </c>
       <c r="J27" t="n">
-        <v>1737.08</v>
+        <v>1762.18</v>
       </c>
       <c r="K27" t="n">
-        <v>1767.33</v>
+        <v>1783.12</v>
       </c>
       <c r="L27" t="n">
-        <v>1797.58</v>
+        <v>1804.05</v>
       </c>
       <c r="M27" t="n">
-        <v>1808.87</v>
+        <v>1828.46</v>
       </c>
       <c r="N27" t="n">
-        <v>1820.15</v>
+        <v>1852.87</v>
       </c>
       <c r="O27" t="n">
-        <v>1869.37</v>
+        <v>1870.32</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2801,77 +2805,75 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1805.76</v>
+        <v>1773.47</v>
       </c>
       <c r="C28" t="n">
-        <v>1842.46</v>
+        <v>1894.06</v>
       </c>
       <c r="D28" t="n">
-        <v>1749.35</v>
+        <v>1772.02</v>
       </c>
       <c r="E28" t="n">
-        <v>1773.5</v>
+        <v>1889.48</v>
       </c>
       <c r="F28" t="n">
-        <v>-32.29</v>
+        <v>115.98</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0654</v>
       </c>
       <c r="H28" t="n">
-        <v>93.11</v>
+        <v>122.04</v>
       </c>
       <c r="I28" t="n">
-        <v>1734.29</v>
+        <v>1656.24</v>
       </c>
       <c r="J28" t="n">
-        <v>1762.18</v>
+        <v>1669.19</v>
       </c>
       <c r="K28" t="n">
-        <v>1783.12</v>
+        <v>1726.95</v>
       </c>
       <c r="L28" t="n">
-        <v>1804.05</v>
+        <v>1784.7</v>
       </c>
       <c r="M28" t="n">
-        <v>1828.46</v>
+        <v>1820.05</v>
       </c>
       <c r="N28" t="n">
-        <v>1852.87</v>
+        <v>1855.41</v>
       </c>
       <c r="O28" t="n">
-        <v>1870.32</v>
+        <v>1935.56</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
@@ -2880,59 +2882,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1773.47</v>
+        <v>1889.5</v>
       </c>
       <c r="C29" t="n">
-        <v>1894.06</v>
+        <v>1944.16</v>
       </c>
       <c r="D29" t="n">
-        <v>1772.02</v>
+        <v>1863.64</v>
       </c>
       <c r="E29" t="n">
-        <v>1889.48</v>
+        <v>1916.94</v>
       </c>
       <c r="F29" t="n">
-        <v>115.98</v>
+        <v>27.46</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0654</v>
+        <v>0.0145</v>
       </c>
       <c r="H29" t="n">
-        <v>122.04</v>
+        <v>80.53</v>
       </c>
       <c r="I29" t="n">
-        <v>1656.24</v>
+        <v>1649.97</v>
       </c>
       <c r="J29" t="n">
-        <v>1669.19</v>
+        <v>1795.66</v>
       </c>
       <c r="K29" t="n">
-        <v>1726.95</v>
+        <v>1828.46</v>
       </c>
       <c r="L29" t="n">
-        <v>1784.7</v>
+        <v>1861.26</v>
       </c>
       <c r="M29" t="n">
-        <v>1820.05</v>
+        <v>1950.5</v>
       </c>
       <c r="N29" t="n">
-        <v>1855.41</v>
+        <v>2039.74</v>
       </c>
       <c r="O29" t="n">
-        <v>1935.56</v>
+        <v>2016.11</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2950,13 +2948,11 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2971,50 +2967,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1889.5</v>
+        <v>1916.98</v>
       </c>
       <c r="C30" t="n">
-        <v>1944.16</v>
+        <v>1927.09</v>
       </c>
       <c r="D30" t="n">
-        <v>1863.64</v>
+        <v>1856.78</v>
       </c>
       <c r="E30" t="n">
-        <v>1916.94</v>
+        <v>1863.19</v>
       </c>
       <c r="F30" t="n">
-        <v>27.46</v>
+        <v>-53.75</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0145</v>
+        <v>-0.028</v>
       </c>
       <c r="H30" t="n">
-        <v>80.53</v>
+        <v>70.31</v>
       </c>
       <c r="I30" t="n">
-        <v>1649.97</v>
+        <v>1783.11</v>
       </c>
       <c r="J30" t="n">
-        <v>1795.66</v>
+        <v>1842.94</v>
       </c>
       <c r="K30" t="n">
-        <v>1828.46</v>
+        <v>1876.68</v>
       </c>
       <c r="L30" t="n">
-        <v>1861.26</v>
+        <v>1910.42</v>
       </c>
       <c r="M30" t="n">
-        <v>1950.5</v>
+        <v>1957.21</v>
       </c>
       <c r="N30" t="n">
-        <v>2039.74</v>
+        <v>2003.99</v>
       </c>
       <c r="O30" t="n">
-        <v>2016.11</v>
+        <v>2024.69</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3022,19 +3018,19 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3046,55 +3042,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1916.98</v>
+        <v>1863.22</v>
       </c>
       <c r="C31" t="n">
-        <v>1927.09</v>
+        <v>1869.07</v>
       </c>
       <c r="D31" t="n">
-        <v>1856.78</v>
+        <v>1803.05</v>
       </c>
       <c r="E31" t="n">
-        <v>1863.19</v>
+        <v>1840.99</v>
       </c>
       <c r="F31" t="n">
-        <v>-53.75</v>
+        <v>-22.21</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.0119</v>
       </c>
       <c r="H31" t="n">
-        <v>70.31</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>1783.11</v>
+        <v>1786.47</v>
       </c>
       <c r="J31" t="n">
-        <v>1842.94</v>
+        <v>1778.51</v>
       </c>
       <c r="K31" t="n">
-        <v>1876.68</v>
+        <v>1828.04</v>
       </c>
       <c r="L31" t="n">
-        <v>1910.42</v>
+        <v>1877.56</v>
       </c>
       <c r="M31" t="n">
-        <v>1957.21</v>
+        <v>1898.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2003.99</v>
+        <v>1919.13</v>
       </c>
       <c r="O31" t="n">
-        <v>2024.69</v>
+        <v>1997.4</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3135,50 +3135,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1863.22</v>
+        <v>1841.1</v>
       </c>
       <c r="C32" t="n">
-        <v>1869.07</v>
+        <v>1864.13</v>
       </c>
       <c r="D32" t="n">
-        <v>1803.05</v>
+        <v>1836.61</v>
       </c>
       <c r="E32" t="n">
-        <v>1840.99</v>
+        <v>1861.39</v>
       </c>
       <c r="F32" t="n">
-        <v>-22.21</v>
+        <v>20.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0111</v>
       </c>
       <c r="H32" t="n">
-        <v>66.01000000000001</v>
+        <v>27.52</v>
       </c>
       <c r="I32" t="n">
-        <v>1786.47</v>
+        <v>1737.04</v>
       </c>
       <c r="J32" t="n">
-        <v>1778.51</v>
+        <v>1777.44</v>
       </c>
       <c r="K32" t="n">
-        <v>1828.04</v>
+        <v>1807.98</v>
       </c>
       <c r="L32" t="n">
-        <v>1877.56</v>
+        <v>1838.52</v>
       </c>
       <c r="M32" t="n">
-        <v>1898.35</v>
+        <v>1873.99</v>
       </c>
       <c r="N32" t="n">
-        <v>1919.13</v>
+        <v>1909.47</v>
       </c>
       <c r="O32" t="n">
-        <v>1997.4</v>
+        <v>1935.08</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3186,19 +3186,19 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3212,57 +3212,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1841.1</v>
+        <v>1861.42</v>
       </c>
       <c r="C33" t="n">
-        <v>1864.13</v>
+        <v>1877.03</v>
       </c>
       <c r="D33" t="n">
-        <v>1836.61</v>
+        <v>1852.73</v>
       </c>
       <c r="E33" t="n">
-        <v>1861.39</v>
+        <v>1871.51</v>
       </c>
       <c r="F33" t="n">
-        <v>20.4</v>
+        <v>10.12</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0054</v>
       </c>
       <c r="H33" t="n">
-        <v>27.52</v>
+        <v>24.3</v>
       </c>
       <c r="I33" t="n">
-        <v>1737.04</v>
+        <v>1809.09</v>
       </c>
       <c r="J33" t="n">
-        <v>1777.44</v>
+        <v>1839.38</v>
       </c>
       <c r="K33" t="n">
-        <v>1807.98</v>
+        <v>1847.63</v>
       </c>
       <c r="L33" t="n">
-        <v>1838.52</v>
+        <v>1855.88</v>
       </c>
       <c r="M33" t="n">
-        <v>1873.99</v>
+        <v>1875.15</v>
       </c>
       <c r="N33" t="n">
-        <v>1909.47</v>
+        <v>1894.43</v>
       </c>
       <c r="O33" t="n">
-        <v>1935.08</v>
+        <v>1891.66</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3294,68 +3294,68 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1861.42</v>
+        <v>1871.28</v>
       </c>
       <c r="C34" t="n">
-        <v>1877.03</v>
+        <v>1916.24</v>
       </c>
       <c r="D34" t="n">
-        <v>1852.73</v>
+        <v>1842.82</v>
       </c>
       <c r="E34" t="n">
-        <v>1871.51</v>
+        <v>1903.76</v>
       </c>
       <c r="F34" t="n">
-        <v>10.12</v>
+        <v>32.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0172</v>
       </c>
       <c r="H34" t="n">
-        <v>24.3</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>1809.09</v>
+        <v>1828.42</v>
       </c>
       <c r="J34" t="n">
-        <v>1839.38</v>
+        <v>1850.52</v>
       </c>
       <c r="K34" t="n">
-        <v>1847.63</v>
+        <v>1859.36</v>
       </c>
       <c r="L34" t="n">
-        <v>1855.88</v>
+        <v>1868.19</v>
       </c>
       <c r="M34" t="n">
-        <v>1875.15</v>
+        <v>1883.66</v>
       </c>
       <c r="N34" t="n">
-        <v>1894.43</v>
+        <v>1899.13</v>
       </c>
       <c r="O34" t="n">
-        <v>1891.66</v>
+        <v>1901.34</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
@@ -3364,82 +3364,86 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1871.28</v>
+        <v>1903.69</v>
       </c>
       <c r="C35" t="n">
-        <v>1916.24</v>
+        <v>1949.55</v>
       </c>
       <c r="D35" t="n">
-        <v>1842.82</v>
+        <v>1900.07</v>
       </c>
       <c r="E35" t="n">
-        <v>1903.76</v>
+        <v>1928.38</v>
       </c>
       <c r="F35" t="n">
-        <v>32.25</v>
+        <v>24.62</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0129</v>
       </c>
       <c r="H35" t="n">
-        <v>73.43000000000001</v>
+        <v>49.48</v>
       </c>
       <c r="I35" t="n">
-        <v>1828.42</v>
+        <v>1769.39</v>
       </c>
       <c r="J35" t="n">
-        <v>1850.52</v>
+        <v>1842.45</v>
       </c>
       <c r="K35" t="n">
-        <v>1859.36</v>
+        <v>1867.05</v>
       </c>
       <c r="L35" t="n">
-        <v>1868.19</v>
+        <v>1891.64</v>
       </c>
       <c r="M35" t="n">
-        <v>1883.66</v>
+        <v>1940.47</v>
       </c>
       <c r="N35" t="n">
-        <v>1899.13</v>
+        <v>1989.3</v>
       </c>
       <c r="O35" t="n">
-        <v>1901.34</v>
+        <v>1989.67</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
@@ -3448,77 +3452,69 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1903.69</v>
+        <v>1928.2</v>
       </c>
       <c r="C36" t="n">
-        <v>1949.55</v>
+        <v>1955.15</v>
       </c>
       <c r="D36" t="n">
-        <v>1900.07</v>
+        <v>1909.61</v>
       </c>
       <c r="E36" t="n">
-        <v>1928.38</v>
+        <v>1933.49</v>
       </c>
       <c r="F36" t="n">
-        <v>24.62</v>
+        <v>5.11</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0026</v>
       </c>
       <c r="H36" t="n">
-        <v>49.48</v>
+        <v>45.54</v>
       </c>
       <c r="I36" t="n">
-        <v>1769.39</v>
+        <v>1850.58</v>
       </c>
       <c r="J36" t="n">
-        <v>1842.45</v>
+        <v>1880.69</v>
       </c>
       <c r="K36" t="n">
-        <v>1867.05</v>
+        <v>1903.64</v>
       </c>
       <c r="L36" t="n">
-        <v>1891.64</v>
+        <v>1926.6</v>
       </c>
       <c r="M36" t="n">
-        <v>1940.47</v>
+        <v>1953.12</v>
       </c>
       <c r="N36" t="n">
-        <v>1989.3</v>
+        <v>1979.65</v>
       </c>
       <c r="O36" t="n">
-        <v>1989.67</v>
+        <v>1999.03</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3531,12 +3527,12 @@
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
@@ -3555,79 +3551,81 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1928.2</v>
+        <v>1933.47</v>
       </c>
       <c r="C37" t="n">
-        <v>1955.15</v>
+        <v>1940.28</v>
       </c>
       <c r="D37" t="n">
-        <v>1909.61</v>
+        <v>1868.52</v>
       </c>
       <c r="E37" t="n">
-        <v>1933.49</v>
+        <v>1877.1</v>
       </c>
       <c r="F37" t="n">
-        <v>5.11</v>
+        <v>-56.39</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0292</v>
       </c>
       <c r="H37" t="n">
-        <v>45.54</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>1850.58</v>
+        <v>1864.07</v>
       </c>
       <c r="J37" t="n">
-        <v>1880.69</v>
+        <v>1888.51</v>
       </c>
       <c r="K37" t="n">
-        <v>1903.64</v>
+        <v>1910.72</v>
       </c>
       <c r="L37" t="n">
-        <v>1926.6</v>
+        <v>1932.93</v>
       </c>
       <c r="M37" t="n">
-        <v>1953.12</v>
+        <v>1956.26</v>
       </c>
       <c r="N37" t="n">
-        <v>1979.65</v>
+        <v>1979.58</v>
       </c>
       <c r="O37" t="n">
-        <v>1999.03</v>
+        <v>2000.68</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3635,62 +3633,60 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1933.47</v>
+        <v>1877.1</v>
       </c>
       <c r="C38" t="n">
-        <v>1940.28</v>
+        <v>1907.54</v>
       </c>
       <c r="D38" t="n">
-        <v>1868.52</v>
+        <v>1846.82</v>
       </c>
       <c r="E38" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="F38" t="n">
-        <v>-56.39</v>
+        <v>-16.92</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0292</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>71.76000000000001</v>
+        <v>60.72</v>
       </c>
       <c r="I38" t="n">
-        <v>1864.07</v>
+        <v>1796.76</v>
       </c>
       <c r="J38" t="n">
-        <v>1888.51</v>
+        <v>1791.69</v>
       </c>
       <c r="K38" t="n">
-        <v>1910.72</v>
+        <v>1841.22</v>
       </c>
       <c r="L38" t="n">
-        <v>1932.93</v>
+        <v>1890.75</v>
       </c>
       <c r="M38" t="n">
-        <v>1956.26</v>
+        <v>1912.98</v>
       </c>
       <c r="N38" t="n">
-        <v>1979.58</v>
+        <v>1935.21</v>
       </c>
       <c r="O38" t="n">
-        <v>2000.68</v>
+        <v>2012.05</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
@@ -3717,50 +3713,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="C39" t="n">
-        <v>1907.54</v>
+        <v>1875.14</v>
       </c>
       <c r="D39" t="n">
-        <v>1846.82</v>
+        <v>1849.83</v>
       </c>
       <c r="E39" t="n">
-        <v>1860.18</v>
+        <v>1873.22</v>
       </c>
       <c r="F39" t="n">
-        <v>-16.92</v>
+        <v>13.05</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H39" t="n">
-        <v>60.72</v>
+        <v>25.32</v>
       </c>
       <c r="I39" t="n">
-        <v>1796.76</v>
+        <v>1786.1</v>
       </c>
       <c r="J39" t="n">
-        <v>1791.69</v>
+        <v>1790.95</v>
       </c>
       <c r="K39" t="n">
-        <v>1841.22</v>
+        <v>1829.82</v>
       </c>
       <c r="L39" t="n">
-        <v>1890.75</v>
+        <v>1868.68</v>
       </c>
       <c r="M39" t="n">
-        <v>1912.98</v>
+        <v>1890.54</v>
       </c>
       <c r="N39" t="n">
-        <v>1935.21</v>
+        <v>1912.39</v>
       </c>
       <c r="O39" t="n">
-        <v>2012.05</v>
+        <v>1968.26</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3768,14 +3764,12 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3792,55 +3786,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1860.18</v>
+        <v>1873.24</v>
       </c>
       <c r="C40" t="n">
-        <v>1875.14</v>
+        <v>1963.25</v>
       </c>
       <c r="D40" t="n">
-        <v>1849.83</v>
+        <v>1872.38</v>
       </c>
       <c r="E40" t="n">
-        <v>1873.22</v>
+        <v>1953.41</v>
       </c>
       <c r="F40" t="n">
-        <v>13.05</v>
+        <v>80.19</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0428</v>
       </c>
       <c r="H40" t="n">
-        <v>25.32</v>
+        <v>90.86</v>
       </c>
       <c r="I40" t="n">
-        <v>1786.1</v>
+        <v>1824.51</v>
       </c>
       <c r="J40" t="n">
-        <v>1790.95</v>
+        <v>1853.27</v>
       </c>
       <c r="K40" t="n">
-        <v>1829.82</v>
+        <v>1860.56</v>
       </c>
       <c r="L40" t="n">
-        <v>1868.68</v>
+        <v>1867.85</v>
       </c>
       <c r="M40" t="n">
-        <v>1890.54</v>
+        <v>1885.88</v>
       </c>
       <c r="N40" t="n">
-        <v>1912.39</v>
+        <v>1903.91</v>
       </c>
       <c r="O40" t="n">
-        <v>1968.26</v>
+        <v>1900.46</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3853,177 +3851,177 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1873.24</v>
+        <v>1953.41</v>
       </c>
       <c r="C41" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D41" t="n">
-        <v>1872.38</v>
+        <v>1882.42</v>
       </c>
       <c r="E41" t="n">
-        <v>1953.41</v>
+        <v>1890.61</v>
       </c>
       <c r="F41" t="n">
-        <v>80.19</v>
+        <v>-62.8</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0428</v>
+        <v>-0.0321</v>
       </c>
       <c r="H41" t="n">
-        <v>90.86</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>1824.51</v>
+        <v>1781.52</v>
       </c>
       <c r="J41" t="n">
-        <v>1853.27</v>
+        <v>1880.35</v>
       </c>
       <c r="K41" t="n">
-        <v>1860.56</v>
+        <v>1907.98</v>
       </c>
       <c r="L41" t="n">
-        <v>1867.85</v>
+        <v>1935.61</v>
       </c>
       <c r="M41" t="n">
-        <v>1885.88</v>
+        <v>1998.84</v>
       </c>
       <c r="N41" t="n">
-        <v>1903.91</v>
+        <v>2062.07</v>
       </c>
       <c r="O41" t="n">
-        <v>1900.46</v>
+        <v>2054.11</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1953.41</v>
+        <v>1890.63</v>
       </c>
       <c r="C42" t="n">
-        <v>1976.46</v>
+        <v>1926.5</v>
       </c>
       <c r="D42" t="n">
-        <v>1882.42</v>
+        <v>1856.34</v>
       </c>
       <c r="E42" t="n">
-        <v>1890.61</v>
+        <v>1919.95</v>
       </c>
       <c r="F42" t="n">
-        <v>-62.8</v>
+        <v>29.33</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0321</v>
+        <v>0.0155</v>
       </c>
       <c r="H42" t="n">
-        <v>94.04000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="I42" t="n">
-        <v>1781.52</v>
+        <v>1788.38</v>
       </c>
       <c r="J42" t="n">
-        <v>1880.35</v>
+        <v>1777.16</v>
       </c>
       <c r="K42" t="n">
-        <v>1907.98</v>
+        <v>1843.59</v>
       </c>
       <c r="L42" t="n">
-        <v>1935.61</v>
+        <v>1910.03</v>
       </c>
       <c r="M42" t="n">
-        <v>1998.84</v>
+        <v>1937.63</v>
       </c>
       <c r="N42" t="n">
-        <v>2062.07</v>
+        <v>1965.24</v>
       </c>
       <c r="O42" t="n">
-        <v>2054.11</v>
+        <v>2070.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4042,57 +4040,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1890.63</v>
+        <v>1919.99</v>
       </c>
       <c r="C43" t="n">
-        <v>1926.5</v>
+        <v>1929.9</v>
       </c>
       <c r="D43" t="n">
-        <v>1856.34</v>
+        <v>1873.62</v>
       </c>
       <c r="E43" t="n">
-        <v>1919.95</v>
+        <v>1908.52</v>
       </c>
       <c r="F43" t="n">
-        <v>29.33</v>
+        <v>-11.43</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.006</v>
       </c>
       <c r="H43" t="n">
-        <v>70.16</v>
+        <v>56.28</v>
       </c>
       <c r="I43" t="n">
-        <v>1788.38</v>
+        <v>1786.18</v>
       </c>
       <c r="J43" t="n">
-        <v>1777.16</v>
+        <v>1864.05</v>
       </c>
       <c r="K43" t="n">
-        <v>1843.59</v>
+        <v>1884.87</v>
       </c>
       <c r="L43" t="n">
-        <v>1910.03</v>
+        <v>1905.69</v>
       </c>
       <c r="M43" t="n">
-        <v>1937.63</v>
+        <v>1955.03</v>
       </c>
       <c r="N43" t="n">
-        <v>1965.24</v>
+        <v>2004.37</v>
       </c>
       <c r="O43" t="n">
-        <v>2070.5</v>
+        <v>1996.67</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4100,8 +4098,10 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
@@ -4124,57 +4124,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1919.99</v>
+        <v>1908.59</v>
       </c>
       <c r="C44" t="n">
-        <v>1929.9</v>
+        <v>1934.58</v>
       </c>
       <c r="D44" t="n">
-        <v>1873.62</v>
+        <v>1892.2</v>
       </c>
       <c r="E44" t="n">
-        <v>1908.52</v>
+        <v>1917.37</v>
       </c>
       <c r="F44" t="n">
-        <v>-11.43</v>
+        <v>8.85</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0046</v>
       </c>
       <c r="H44" t="n">
-        <v>56.28</v>
+        <v>42.38</v>
       </c>
       <c r="I44" t="n">
-        <v>1786.18</v>
+        <v>1817.34</v>
       </c>
       <c r="J44" t="n">
-        <v>1864.05</v>
+        <v>1855.62</v>
       </c>
       <c r="K44" t="n">
-        <v>1884.87</v>
+        <v>1880.38</v>
       </c>
       <c r="L44" t="n">
-        <v>1905.69</v>
+        <v>1905.14</v>
       </c>
       <c r="M44" t="n">
-        <v>1955.03</v>
+        <v>1936.66</v>
       </c>
       <c r="N44" t="n">
-        <v>2004.37</v>
+        <v>1968.18</v>
       </c>
       <c r="O44" t="n">
-        <v>1996.67</v>
+        <v>1986.18</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4182,10 +4182,8 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
@@ -4206,72 +4204,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1908.59</v>
+        <v>1917.14</v>
       </c>
       <c r="C45" t="n">
-        <v>1934.58</v>
+        <v>1933.78</v>
       </c>
       <c r="D45" t="n">
-        <v>1892.2</v>
+        <v>1847.47</v>
       </c>
       <c r="E45" t="n">
-        <v>1917.37</v>
+        <v>1860.35</v>
       </c>
       <c r="F45" t="n">
-        <v>8.85</v>
+        <v>-57.03</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0297</v>
       </c>
       <c r="H45" t="n">
-        <v>42.38</v>
+        <v>86.31</v>
       </c>
       <c r="I45" t="n">
-        <v>1817.34</v>
+        <v>1849.82</v>
       </c>
       <c r="J45" t="n">
-        <v>1855.62</v>
+        <v>1876.99</v>
       </c>
       <c r="K45" t="n">
-        <v>1880.38</v>
+        <v>1896.18</v>
       </c>
       <c r="L45" t="n">
-        <v>1905.14</v>
+        <v>1915.38</v>
       </c>
       <c r="M45" t="n">
-        <v>1936.66</v>
+        <v>1938.56</v>
       </c>
       <c r="N45" t="n">
-        <v>1968.18</v>
+        <v>1961.75</v>
       </c>
       <c r="O45" t="n">
-        <v>1986.18</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>1976.96</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4283,9 +4283,9 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr"/>
@@ -4293,64 +4293,60 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1917.14</v>
+        <v>1860.37</v>
       </c>
       <c r="C46" t="n">
-        <v>1933.78</v>
+        <v>1873.17</v>
       </c>
       <c r="D46" t="n">
-        <v>1847.47</v>
+        <v>1821.49</v>
       </c>
       <c r="E46" t="n">
-        <v>1860.35</v>
+        <v>1843.42</v>
       </c>
       <c r="F46" t="n">
-        <v>-57.03</v>
+        <v>-16.93</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0297</v>
+        <v>-0.0091</v>
       </c>
       <c r="H46" t="n">
-        <v>86.31</v>
+        <v>51.69</v>
       </c>
       <c r="I46" t="n">
-        <v>1849.82</v>
+        <v>1761.16</v>
       </c>
       <c r="J46" t="n">
-        <v>1876.99</v>
+        <v>1758.9</v>
       </c>
       <c r="K46" t="n">
-        <v>1896.18</v>
+        <v>1817.19</v>
       </c>
       <c r="L46" t="n">
-        <v>1915.38</v>
+        <v>1875.48</v>
       </c>
       <c r="M46" t="n">
-        <v>1938.56</v>
+        <v>1903.5</v>
       </c>
       <c r="N46" t="n">
-        <v>1961.75</v>
+        <v>1931.52</v>
       </c>
       <c r="O46" t="n">
-        <v>1976.96</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
+        <v>2020.09</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
@@ -4377,50 +4373,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1860.37</v>
+        <v>1843.42</v>
       </c>
       <c r="C47" t="n">
-        <v>1873.17</v>
+        <v>1895.77</v>
       </c>
       <c r="D47" t="n">
-        <v>1821.49</v>
+        <v>1842.15</v>
       </c>
       <c r="E47" t="n">
-        <v>1843.42</v>
+        <v>1882.52</v>
       </c>
       <c r="F47" t="n">
-        <v>-16.93</v>
+        <v>39.1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0212</v>
       </c>
       <c r="H47" t="n">
-        <v>51.69</v>
+        <v>53.61</v>
       </c>
       <c r="I47" t="n">
-        <v>1761.16</v>
+        <v>1769.8</v>
       </c>
       <c r="J47" t="n">
-        <v>1758.9</v>
+        <v>1789.78</v>
       </c>
       <c r="K47" t="n">
-        <v>1817.19</v>
+        <v>1817.57</v>
       </c>
       <c r="L47" t="n">
-        <v>1875.48</v>
+        <v>1845.37</v>
       </c>
       <c r="M47" t="n">
-        <v>1903.5</v>
+        <v>1869.26</v>
       </c>
       <c r="N47" t="n">
-        <v>1931.52</v>
+        <v>1893.15</v>
       </c>
       <c r="O47" t="n">
-        <v>2020.09</v>
+        <v>1924.86</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4428,22 +4424,24 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4452,80 +4450,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1843.42</v>
+        <v>1882.78</v>
       </c>
       <c r="C48" t="n">
-        <v>1895.77</v>
+        <v>1883.44</v>
       </c>
       <c r="D48" t="n">
-        <v>1842.15</v>
+        <v>1827.7</v>
       </c>
       <c r="E48" t="n">
-        <v>1882.52</v>
+        <v>1858.26</v>
       </c>
       <c r="F48" t="n">
-        <v>39.1</v>
+        <v>-24.27</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0129</v>
       </c>
       <c r="H48" t="n">
-        <v>53.61</v>
+        <v>55.74</v>
       </c>
       <c r="I48" t="n">
-        <v>1769.8</v>
+        <v>1788.54</v>
       </c>
       <c r="J48" t="n">
-        <v>1789.78</v>
+        <v>1835.69</v>
       </c>
       <c r="K48" t="n">
-        <v>1817.57</v>
+        <v>1855.72</v>
       </c>
       <c r="L48" t="n">
-        <v>1845.37</v>
+        <v>1875.74</v>
       </c>
       <c r="M48" t="n">
-        <v>1869.26</v>
+        <v>1909.33</v>
       </c>
       <c r="N48" t="n">
-        <v>1893.15</v>
+        <v>1942.91</v>
       </c>
       <c r="O48" t="n">
-        <v>1924.86</v>
+        <v>1949.38</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="Q48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr">
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4534,76 +4536,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1882.78</v>
+        <v>1858.22</v>
       </c>
       <c r="C49" t="n">
-        <v>1883.44</v>
+        <v>1879.54</v>
       </c>
       <c r="D49" t="n">
-        <v>1827.7</v>
+        <v>1847.17</v>
       </c>
       <c r="E49" t="n">
-        <v>1858.26</v>
+        <v>1868.39</v>
       </c>
       <c r="F49" t="n">
-        <v>-24.27</v>
+        <v>10.13</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0055</v>
       </c>
       <c r="H49" t="n">
-        <v>55.74</v>
+        <v>32.36</v>
       </c>
       <c r="I49" t="n">
-        <v>1788.54</v>
+        <v>1771.96</v>
       </c>
       <c r="J49" t="n">
-        <v>1835.69</v>
+        <v>1803.86</v>
       </c>
       <c r="K49" t="n">
-        <v>1855.72</v>
+        <v>1830.39</v>
       </c>
       <c r="L49" t="n">
-        <v>1875.74</v>
+        <v>1856.91</v>
       </c>
       <c r="M49" t="n">
-        <v>1909.33</v>
+        <v>1886.13</v>
       </c>
       <c r="N49" t="n">
-        <v>1942.91</v>
+        <v>1915.34</v>
       </c>
       <c r="O49" t="n">
-        <v>1949.38</v>
+        <v>1939.18</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4620,55 +4614,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1858.22</v>
+        <v>1868.49</v>
       </c>
       <c r="C50" t="n">
-        <v>1879.54</v>
+        <v>1922.64</v>
       </c>
       <c r="D50" t="n">
-        <v>1847.17</v>
+        <v>1854.34</v>
       </c>
       <c r="E50" t="n">
-        <v>1868.39</v>
+        <v>1906.53</v>
       </c>
       <c r="F50" t="n">
-        <v>10.13</v>
+        <v>38.14</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0204</v>
       </c>
       <c r="H50" t="n">
-        <v>32.36</v>
+        <v>68.3</v>
       </c>
       <c r="I50" t="n">
-        <v>1771.96</v>
+        <v>1814.81</v>
       </c>
       <c r="J50" t="n">
-        <v>1803.86</v>
+        <v>1838.54</v>
       </c>
       <c r="K50" t="n">
-        <v>1830.39</v>
+        <v>1852.2</v>
       </c>
       <c r="L50" t="n">
-        <v>1856.91</v>
+        <v>1865.87</v>
       </c>
       <c r="M50" t="n">
-        <v>1886.13</v>
+        <v>1884.57</v>
       </c>
       <c r="N50" t="n">
-        <v>1915.34</v>
+        <v>1903.26</v>
       </c>
       <c r="O50" t="n">
-        <v>1939.18</v>
+        <v>1911.9</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4681,76 +4679,78 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1868.49</v>
+        <v>1906.44</v>
       </c>
       <c r="C51" t="n">
-        <v>1922.64</v>
+        <v>1917.7</v>
       </c>
       <c r="D51" t="n">
-        <v>1854.34</v>
+        <v>1890.96</v>
       </c>
       <c r="E51" t="n">
-        <v>1906.53</v>
+        <v>1902.06</v>
       </c>
       <c r="F51" t="n">
-        <v>38.14</v>
+        <v>-4.47</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.0023</v>
       </c>
       <c r="H51" t="n">
-        <v>68.3</v>
+        <v>26.74</v>
       </c>
       <c r="I51" t="n">
-        <v>1814.81</v>
+        <v>1786.04</v>
       </c>
       <c r="J51" t="n">
-        <v>1838.54</v>
+        <v>1847.24</v>
       </c>
       <c r="K51" t="n">
-        <v>1852.2</v>
+        <v>1872.38</v>
       </c>
       <c r="L51" t="n">
-        <v>1865.87</v>
+        <v>1897.51</v>
       </c>
       <c r="M51" t="n">
-        <v>1884.57</v>
+        <v>1940.68</v>
       </c>
       <c r="N51" t="n">
-        <v>1903.26</v>
+        <v>1983.84</v>
       </c>
       <c r="O51" t="n">
-        <v>1911.9</v>
+        <v>1990.94</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4763,78 +4763,76 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1906.44</v>
+        <v>1902.14</v>
       </c>
       <c r="C52" t="n">
-        <v>1917.7</v>
+        <v>1937.17</v>
       </c>
       <c r="D52" t="n">
-        <v>1890.96</v>
+        <v>1893.08</v>
       </c>
       <c r="E52" t="n">
-        <v>1902.06</v>
+        <v>1913.28</v>
       </c>
       <c r="F52" t="n">
-        <v>-4.47</v>
+        <v>11.22</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0059</v>
       </c>
       <c r="H52" t="n">
-        <v>26.74</v>
+        <v>44.08</v>
       </c>
       <c r="I52" t="n">
-        <v>1786.04</v>
+        <v>1864.23</v>
       </c>
       <c r="J52" t="n">
-        <v>1847.24</v>
+        <v>1874.18</v>
       </c>
       <c r="K52" t="n">
-        <v>1872.38</v>
+        <v>1888.69</v>
       </c>
       <c r="L52" t="n">
-        <v>1897.51</v>
+        <v>1903.19</v>
       </c>
       <c r="M52" t="n">
-        <v>1940.68</v>
+        <v>1915.43</v>
       </c>
       <c r="N52" t="n">
-        <v>1983.84</v>
+        <v>1927.66</v>
       </c>
       <c r="O52" t="n">
-        <v>1990.94</v>
+        <v>1944.44</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4847,14 +4845,18 @@
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4864,59 +4866,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1902.14</v>
+        <v>1913.32</v>
       </c>
       <c r="C53" t="n">
-        <v>1937.17</v>
+        <v>1924.62</v>
       </c>
       <c r="D53" t="n">
-        <v>1893.08</v>
+        <v>1911.48</v>
       </c>
       <c r="E53" t="n">
-        <v>1913.28</v>
+        <v>1915.53</v>
       </c>
       <c r="F53" t="n">
-        <v>11.22</v>
+        <v>2.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0012</v>
       </c>
       <c r="H53" t="n">
-        <v>44.08</v>
+        <v>13.13</v>
       </c>
       <c r="I53" t="n">
-        <v>1864.23</v>
+        <v>1849</v>
       </c>
       <c r="J53" t="n">
-        <v>1874.18</v>
+        <v>1868.27</v>
       </c>
       <c r="K53" t="n">
-        <v>1888.69</v>
+        <v>1891.24</v>
       </c>
       <c r="L53" t="n">
-        <v>1903.19</v>
+        <v>1914.2</v>
       </c>
       <c r="M53" t="n">
-        <v>1915.43</v>
+        <v>1935.32</v>
       </c>
       <c r="N53" t="n">
-        <v>1927.66</v>
+        <v>1956.44</v>
       </c>
       <c r="O53" t="n">
-        <v>1944.44</v>
+        <v>1981.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4929,18 +4927,14 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4950,55 +4944,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1913.32</v>
+        <v>1915.46</v>
       </c>
       <c r="C54" t="n">
-        <v>1924.62</v>
+        <v>1935.53</v>
       </c>
       <c r="D54" t="n">
-        <v>1911.48</v>
+        <v>1907.03</v>
       </c>
       <c r="E54" t="n">
-        <v>1915.53</v>
+        <v>1908.68</v>
       </c>
       <c r="F54" t="n">
-        <v>2.25</v>
+        <v>-6.85</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0036</v>
       </c>
       <c r="H54" t="n">
-        <v>13.13</v>
+        <v>28.5</v>
       </c>
       <c r="I54" t="n">
-        <v>1849</v>
+        <v>1898.35</v>
       </c>
       <c r="J54" t="n">
-        <v>1868.27</v>
+        <v>1901.14</v>
       </c>
       <c r="K54" t="n">
-        <v>1891.24</v>
+        <v>1908.97</v>
       </c>
       <c r="L54" t="n">
-        <v>1914.2</v>
+        <v>1916.79</v>
       </c>
       <c r="M54" t="n">
-        <v>1935.32</v>
+        <v>1922.1</v>
       </c>
       <c r="N54" t="n">
-        <v>1956.44</v>
+        <v>1927.4</v>
       </c>
       <c r="O54" t="n">
-        <v>1981.25</v>
+        <v>1937.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5006,19 +5004,25 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5030,67 +5034,71 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1915.46</v>
+        <v>1908.72</v>
       </c>
       <c r="C55" t="n">
-        <v>1935.53</v>
+        <v>1928.99</v>
       </c>
       <c r="D55" t="n">
-        <v>1907.03</v>
+        <v>1866.79</v>
       </c>
       <c r="E55" t="n">
-        <v>1908.68</v>
+        <v>1871.28</v>
       </c>
       <c r="F55" t="n">
-        <v>-6.85</v>
+        <v>-37.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0196</v>
       </c>
       <c r="H55" t="n">
-        <v>28.5</v>
+        <v>62.2</v>
       </c>
       <c r="I55" t="n">
-        <v>1898.35</v>
+        <v>1878.52</v>
       </c>
       <c r="J55" t="n">
-        <v>1901.14</v>
+        <v>1873.88</v>
       </c>
       <c r="K55" t="n">
-        <v>1908.97</v>
+        <v>1894.43</v>
       </c>
       <c r="L55" t="n">
-        <v>1916.79</v>
+        <v>1914.98</v>
       </c>
       <c r="M55" t="n">
-        <v>1922.1</v>
+        <v>1922.93</v>
       </c>
       <c r="N55" t="n">
-        <v>1927.4</v>
+        <v>1930.89</v>
       </c>
       <c r="O55" t="n">
-        <v>1937.75</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+        <v>1964.03</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
@@ -5103,97 +5111,83 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1908.72</v>
+        <v>1871.26</v>
       </c>
       <c r="C56" t="n">
-        <v>1928.99</v>
+        <v>1895.75</v>
       </c>
       <c r="D56" t="n">
-        <v>1866.79</v>
+        <v>1852.84</v>
       </c>
       <c r="E56" t="n">
-        <v>1871.28</v>
+        <v>1881.37</v>
       </c>
       <c r="F56" t="n">
-        <v>-37.4</v>
+        <v>10.09</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0196</v>
+        <v>0.0054</v>
       </c>
       <c r="H56" t="n">
-        <v>62.2</v>
+        <v>42.91</v>
       </c>
       <c r="I56" t="n">
-        <v>1878.52</v>
+        <v>1804.59</v>
       </c>
       <c r="J56" t="n">
-        <v>1873.88</v>
+        <v>1795.77</v>
       </c>
       <c r="K56" t="n">
-        <v>1894.43</v>
+        <v>1840.18</v>
       </c>
       <c r="L56" t="n">
-        <v>1914.98</v>
+        <v>1884.59</v>
       </c>
       <c r="M56" t="n">
-        <v>1922.93</v>
+        <v>1902.38</v>
       </c>
       <c r="N56" t="n">
-        <v>1930.89</v>
+        <v>1920.18</v>
       </c>
       <c r="O56" t="n">
-        <v>1964.03</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>1991.2</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5206,55 +5200,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1871.26</v>
+        <v>1881.37</v>
       </c>
       <c r="C57" t="n">
-        <v>1895.75</v>
+        <v>1921.78</v>
       </c>
       <c r="D57" t="n">
-        <v>1852.84</v>
+        <v>1873.35</v>
       </c>
       <c r="E57" t="n">
-        <v>1881.37</v>
+        <v>1878.14</v>
       </c>
       <c r="F57" t="n">
-        <v>10.09</v>
+        <v>-3.24</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0017</v>
       </c>
       <c r="H57" t="n">
-        <v>42.91</v>
+        <v>48.43</v>
       </c>
       <c r="I57" t="n">
-        <v>1804.59</v>
+        <v>1809.93</v>
       </c>
       <c r="J57" t="n">
-        <v>1795.77</v>
+        <v>1842</v>
       </c>
       <c r="K57" t="n">
-        <v>1840.18</v>
+        <v>1859.92</v>
       </c>
       <c r="L57" t="n">
-        <v>1884.59</v>
+        <v>1877.83</v>
       </c>
       <c r="M57" t="n">
-        <v>1902.38</v>
+        <v>1902.83</v>
       </c>
       <c r="N57" t="n">
-        <v>1920.18</v>
+        <v>1927.82</v>
       </c>
       <c r="O57" t="n">
-        <v>1991.2</v>
+        <v>1938.66</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5265,13 +5263,15 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5286,57 +5286,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1881.37</v>
+        <v>1878.19</v>
       </c>
       <c r="C58" t="n">
-        <v>1921.78</v>
+        <v>1898.23</v>
       </c>
       <c r="D58" t="n">
-        <v>1873.35</v>
+        <v>1861.92</v>
       </c>
       <c r="E58" t="n">
-        <v>1878.14</v>
+        <v>1883.99</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.24</v>
+        <v>5.86</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="H58" t="n">
-        <v>48.43</v>
+        <v>36.3</v>
       </c>
       <c r="I58" t="n">
-        <v>1809.93</v>
+        <v>1824.92</v>
       </c>
       <c r="J58" t="n">
-        <v>1842</v>
+        <v>1819.99</v>
       </c>
       <c r="K58" t="n">
-        <v>1859.92</v>
+        <v>1853.92</v>
       </c>
       <c r="L58" t="n">
-        <v>1877.83</v>
+        <v>1887.85</v>
       </c>
       <c r="M58" t="n">
-        <v>1902.83</v>
+        <v>1902.35</v>
       </c>
       <c r="N58" t="n">
-        <v>1927.82</v>
+        <v>1916.85</v>
       </c>
       <c r="O58" t="n">
-        <v>1938.66</v>
+        <v>1970.2</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5347,15 +5347,13 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5370,57 +5368,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1878.19</v>
+        <v>1884.02</v>
       </c>
       <c r="C59" t="n">
-        <v>1898.23</v>
+        <v>1889.27</v>
       </c>
       <c r="D59" t="n">
-        <v>1861.92</v>
+        <v>1862.56</v>
       </c>
       <c r="E59" t="n">
-        <v>1883.99</v>
+        <v>1880.65</v>
       </c>
       <c r="F59" t="n">
-        <v>5.86</v>
+        <v>-3.34</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0018</v>
       </c>
       <c r="H59" t="n">
-        <v>36.3</v>
+        <v>26.71</v>
       </c>
       <c r="I59" t="n">
-        <v>1824.92</v>
+        <v>1825.62</v>
       </c>
       <c r="J59" t="n">
-        <v>1819.99</v>
+        <v>1849.65</v>
       </c>
       <c r="K59" t="n">
-        <v>1853.92</v>
+        <v>1865.84</v>
       </c>
       <c r="L59" t="n">
-        <v>1887.85</v>
+        <v>1882.03</v>
       </c>
       <c r="M59" t="n">
-        <v>1902.35</v>
+        <v>1902.14</v>
       </c>
       <c r="N59" t="n">
-        <v>1916.85</v>
+        <v>1922.26</v>
       </c>
       <c r="O59" t="n">
-        <v>1970.2</v>
+        <v>1934.53</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5428,8 +5426,10 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
@@ -5459,50 +5459,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1884.02</v>
+        <v>1880.61</v>
       </c>
       <c r="C60" t="n">
-        <v>1889.27</v>
+        <v>1884.72</v>
       </c>
       <c r="D60" t="n">
-        <v>1862.56</v>
+        <v>1874.33</v>
       </c>
       <c r="E60" t="n">
-        <v>1880.65</v>
+        <v>1880.91</v>
       </c>
       <c r="F60" t="n">
-        <v>-3.34</v>
+        <v>0.26</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0001</v>
       </c>
       <c r="H60" t="n">
-        <v>26.71</v>
+        <v>10.39</v>
       </c>
       <c r="I60" t="n">
-        <v>1825.62</v>
+        <v>1835.86</v>
       </c>
       <c r="J60" t="n">
-        <v>1849.65</v>
+        <v>1856.31</v>
       </c>
       <c r="K60" t="n">
-        <v>1865.84</v>
+        <v>1867.3</v>
       </c>
       <c r="L60" t="n">
-        <v>1882.03</v>
+        <v>1878.28</v>
       </c>
       <c r="M60" t="n">
-        <v>1902.14</v>
+        <v>1894</v>
       </c>
       <c r="N60" t="n">
-        <v>1922.26</v>
+        <v>1909.72</v>
       </c>
       <c r="O60" t="n">
-        <v>1934.53</v>
+        <v>1915.98</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5510,14 +5510,12 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5536,74 +5534,80 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1880.61</v>
+        <v>1880.89</v>
       </c>
       <c r="C61" t="n">
-        <v>1884.72</v>
+        <v>1889.61</v>
       </c>
       <c r="D61" t="n">
-        <v>1874.33</v>
+        <v>1867.89</v>
       </c>
       <c r="E61" t="n">
-        <v>1880.91</v>
+        <v>1873.94</v>
       </c>
       <c r="F61" t="n">
-        <v>0.26</v>
+        <v>-6.97</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0037</v>
       </c>
       <c r="H61" t="n">
-        <v>10.39</v>
+        <v>21.71</v>
       </c>
       <c r="I61" t="n">
-        <v>1835.86</v>
+        <v>1863.94</v>
       </c>
       <c r="J61" t="n">
-        <v>1856.31</v>
+        <v>1871.21</v>
       </c>
       <c r="K61" t="n">
-        <v>1867.3</v>
+        <v>1875.71</v>
       </c>
       <c r="L61" t="n">
-        <v>1878.28</v>
+        <v>1880.22</v>
       </c>
       <c r="M61" t="n">
-        <v>1894</v>
+        <v>1886.1</v>
       </c>
       <c r="N61" t="n">
-        <v>1909.72</v>
+        <v>1891.99</v>
       </c>
       <c r="O61" t="n">
-        <v>1915.98</v>
+        <v>1895.11</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5618,145 +5622,141 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1880.89</v>
+        <v>1873.97</v>
       </c>
       <c r="C62" t="n">
-        <v>1889.61</v>
+        <v>1916.66</v>
       </c>
       <c r="D62" t="n">
-        <v>1867.89</v>
+        <v>1870.75</v>
       </c>
       <c r="E62" t="n">
-        <v>1873.94</v>
+        <v>1912.2</v>
       </c>
       <c r="F62" t="n">
-        <v>-6.97</v>
+        <v>38.26</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0204</v>
       </c>
       <c r="H62" t="n">
-        <v>21.71</v>
+        <v>45.91</v>
       </c>
       <c r="I62" t="n">
-        <v>1863.94</v>
+        <v>1846.18</v>
       </c>
       <c r="J62" t="n">
-        <v>1871.21</v>
+        <v>1849.83</v>
       </c>
       <c r="K62" t="n">
-        <v>1875.71</v>
+        <v>1863.09</v>
       </c>
       <c r="L62" t="n">
-        <v>1880.22</v>
+        <v>1876.35</v>
       </c>
       <c r="M62" t="n">
-        <v>1886.1</v>
+        <v>1884.8</v>
       </c>
       <c r="N62" t="n">
-        <v>1891.99</v>
+        <v>1893.25</v>
       </c>
       <c r="O62" t="n">
-        <v>1895.11</v>
+        <v>1911.32</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1873.97</v>
+        <v>1912.21</v>
       </c>
       <c r="C63" t="n">
-        <v>1916.66</v>
+        <v>1920.52</v>
       </c>
       <c r="D63" t="n">
-        <v>1870.75</v>
+        <v>1884.48</v>
       </c>
       <c r="E63" t="n">
-        <v>1912.2</v>
+        <v>1916.46</v>
       </c>
       <c r="F63" t="n">
-        <v>38.26</v>
+        <v>4.26</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.0022</v>
       </c>
       <c r="H63" t="n">
-        <v>45.91</v>
+        <v>36.05</v>
       </c>
       <c r="I63" t="n">
-        <v>1846.18</v>
+        <v>1824.84</v>
       </c>
       <c r="J63" t="n">
-        <v>1849.83</v>
+        <v>1875.54</v>
       </c>
       <c r="K63" t="n">
-        <v>1863.09</v>
+        <v>1889.25</v>
       </c>
       <c r="L63" t="n">
-        <v>1876.35</v>
+        <v>1902.95</v>
       </c>
       <c r="M63" t="n">
-        <v>1884.8</v>
+        <v>1935.16</v>
       </c>
       <c r="N63" t="n">
-        <v>1893.25</v>
+        <v>1967.36</v>
       </c>
       <c r="O63" t="n">
-        <v>1911.32</v>
+        <v>1962.57</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5764,28 +5764,24 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
       </c>
       <c r="W63" s="9" t="inlineStr">
         <is>
@@ -5797,50 +5793,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1912.21</v>
+        <v>1916.43</v>
       </c>
       <c r="C64" t="n">
-        <v>1920.52</v>
+        <v>2327.7</v>
       </c>
       <c r="D64" t="n">
-        <v>1884.48</v>
+        <v>1905.08</v>
       </c>
       <c r="E64" t="n">
-        <v>1916.46</v>
+        <v>2251.46</v>
       </c>
       <c r="F64" t="n">
-        <v>4.26</v>
+        <v>335</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.1748</v>
       </c>
       <c r="H64" t="n">
-        <v>36.05</v>
+        <v>422.62</v>
       </c>
       <c r="I64" t="n">
-        <v>1824.84</v>
+        <v>1848.43</v>
       </c>
       <c r="J64" t="n">
-        <v>1875.54</v>
+        <v>1887.39</v>
       </c>
       <c r="K64" t="n">
-        <v>1889.25</v>
+        <v>1898.44</v>
       </c>
       <c r="L64" t="n">
-        <v>1902.95</v>
+        <v>1909.48</v>
       </c>
       <c r="M64" t="n">
-        <v>1935.16</v>
+        <v>1934.48</v>
       </c>
       <c r="N64" t="n">
-        <v>1967.36</v>
+        <v>1959.48</v>
       </c>
       <c r="O64" t="n">
-        <v>1962.57</v>
+        <v>1956.57</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5848,24 +5844,28 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="inlineStr">
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W64" s="9" t="inlineStr">
         <is>
@@ -5877,50 +5877,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1916.43</v>
+        <v>2251.44</v>
       </c>
       <c r="C65" t="n">
-        <v>2327.7</v>
+        <v>2357.23</v>
       </c>
       <c r="D65" t="n">
-        <v>1905.08</v>
+        <v>2222.57</v>
       </c>
       <c r="E65" t="n">
-        <v>2251.46</v>
+        <v>2326.38</v>
       </c>
       <c r="F65" t="n">
-        <v>335</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.1748</v>
+        <v>0.0333</v>
       </c>
       <c r="H65" t="n">
-        <v>422.62</v>
+        <v>134.65</v>
       </c>
       <c r="I65" t="n">
-        <v>1848.43</v>
+        <v>1482.46</v>
       </c>
       <c r="J65" t="n">
-        <v>1887.39</v>
+        <v>1896.37</v>
       </c>
       <c r="K65" t="n">
-        <v>1898.44</v>
+        <v>2040.15</v>
       </c>
       <c r="L65" t="n">
-        <v>1909.48</v>
+        <v>2183.92</v>
       </c>
       <c r="M65" t="n">
-        <v>1934.48</v>
+        <v>2462.77</v>
       </c>
       <c r="N65" t="n">
-        <v>1959.48</v>
+        <v>2741.61</v>
       </c>
       <c r="O65" t="n">
-        <v>1956.57</v>
+        <v>2750.32</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5938,18 +5938,14 @@
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
       </c>
       <c r="W65" s="9" t="inlineStr">
         <is>
@@ -5961,50 +5957,50 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2251.44</v>
+        <v>2326.38</v>
       </c>
       <c r="C66" t="n">
-        <v>2357.23</v>
+        <v>2545.88</v>
       </c>
       <c r="D66" t="n">
-        <v>2222.57</v>
+        <v>2324.71</v>
       </c>
       <c r="E66" t="n">
-        <v>2326.38</v>
+        <v>2515.28</v>
       </c>
       <c r="F66" t="n">
-        <v>74.93000000000001</v>
+        <v>188.9</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0333</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>134.65</v>
+        <v>221.17</v>
       </c>
       <c r="I66" t="n">
-        <v>1482.46</v>
+        <v>2087.92</v>
       </c>
       <c r="J66" t="n">
-        <v>1896.37</v>
+        <v>2209.97</v>
       </c>
       <c r="K66" t="n">
-        <v>2040.15</v>
+        <v>2259.06</v>
       </c>
       <c r="L66" t="n">
-        <v>2183.92</v>
+        <v>2308.14</v>
       </c>
       <c r="M66" t="n">
-        <v>2462.77</v>
+        <v>2393.71</v>
       </c>
       <c r="N66" t="n">
-        <v>2741.61</v>
+        <v>2479.28</v>
       </c>
       <c r="O66" t="n">
-        <v>2750.32</v>
+        <v>2491.88</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6022,14 +6018,18 @@
       </c>
       <c r="T66" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V66" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U66" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V66" s="8" t="n">
-        <v/>
       </c>
       <c r="W66" s="9" t="inlineStr">
         <is>
@@ -6041,50 +6041,50 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2326.38</v>
+        <v>2515.39</v>
       </c>
       <c r="C67" t="n">
-        <v>2545.88</v>
+        <v>2528.9</v>
       </c>
       <c r="D67" t="n">
-        <v>2324.71</v>
+        <v>2389.9</v>
       </c>
       <c r="E67" t="n">
-        <v>2515.28</v>
+        <v>2424.25</v>
       </c>
       <c r="F67" t="n">
-        <v>188.9</v>
+        <v>-91.03</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0362</v>
       </c>
       <c r="H67" t="n">
-        <v>221.17</v>
+        <v>138.99</v>
       </c>
       <c r="I67" t="n">
-        <v>2087.92</v>
+        <v>2103.54</v>
       </c>
       <c r="J67" t="n">
-        <v>2209.97</v>
+        <v>2334.1</v>
       </c>
       <c r="K67" t="n">
-        <v>2259.06</v>
+        <v>2404.7</v>
       </c>
       <c r="L67" t="n">
-        <v>2308.14</v>
+        <v>2475.29</v>
       </c>
       <c r="M67" t="n">
-        <v>2393.71</v>
+        <v>2625.87</v>
       </c>
       <c r="N67" t="n">
-        <v>2479.28</v>
+        <v>2776.45</v>
       </c>
       <c r="O67" t="n">
-        <v>2491.88</v>
+        <v>2767.05</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6092,83 +6092,83 @@
       <c r="Q67" s="6" t="n">
         <v/>
       </c>
-      <c r="R67" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S67" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V67" s="8" t="inlineStr">
+      <c r="R67" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U67" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V67" s="8" t="n">
+        <v/>
+      </c>
       <c r="W67" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr"/>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2515.39</v>
+        <v>2424.22</v>
       </c>
       <c r="C68" t="n">
-        <v>2528.9</v>
+        <v>2483.93</v>
       </c>
       <c r="D68" t="n">
-        <v>2389.9</v>
+        <v>2357.14</v>
       </c>
       <c r="E68" t="n">
-        <v>2424.25</v>
+        <v>2463.82</v>
       </c>
       <c r="F68" t="n">
-        <v>-91.03</v>
+        <v>39.56</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.0362</v>
+        <v>0.0163</v>
       </c>
       <c r="H68" t="n">
-        <v>138.99</v>
+        <v>126.79</v>
       </c>
       <c r="I68" t="n">
-        <v>2103.54</v>
+        <v>2250.91</v>
       </c>
       <c r="J68" t="n">
-        <v>2334.1</v>
+        <v>2267.68</v>
       </c>
       <c r="K68" t="n">
-        <v>2404.7</v>
+        <v>2354.75</v>
       </c>
       <c r="L68" t="n">
-        <v>2475.29</v>
+        <v>2441.83</v>
       </c>
       <c r="M68" t="n">
-        <v>2625.87</v>
+        <v>2493.75</v>
       </c>
       <c r="N68" t="n">
-        <v>2776.45</v>
+        <v>2545.67</v>
       </c>
       <c r="O68" t="n">
-        <v>2767.05</v>
+        <v>2667.89</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
@@ -6176,14 +6176,12 @@
       <c r="Q68" s="6" t="n">
         <v/>
       </c>
-      <c r="R68" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S68" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S68" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T68" s="8" t="n">
@@ -6209,50 +6207,50 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2424.22</v>
+        <v>2463.64</v>
       </c>
       <c r="C69" t="n">
-        <v>2483.93</v>
+        <v>2531.74</v>
       </c>
       <c r="D69" t="n">
-        <v>2357.14</v>
+        <v>2425.39</v>
       </c>
       <c r="E69" t="n">
-        <v>2463.82</v>
+        <v>2481.83</v>
       </c>
       <c r="F69" t="n">
-        <v>39.56</v>
+        <v>18.02</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0073</v>
       </c>
       <c r="H69" t="n">
-        <v>126.79</v>
+        <v>106.36</v>
       </c>
       <c r="I69" t="n">
-        <v>2250.91</v>
+        <v>2230.35</v>
       </c>
       <c r="J69" t="n">
-        <v>2267.68</v>
+        <v>2358.67</v>
       </c>
       <c r="K69" t="n">
-        <v>2354.75</v>
+        <v>2400.42</v>
       </c>
       <c r="L69" t="n">
-        <v>2441.83</v>
+        <v>2442.18</v>
       </c>
       <c r="M69" t="n">
-        <v>2493.75</v>
+        <v>2527.21</v>
       </c>
       <c r="N69" t="n">
-        <v>2545.67</v>
+        <v>2612.25</v>
       </c>
       <c r="O69" t="n">
-        <v>2667.89</v>
+        <v>2610.72</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6268,8 +6266,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T69" s="8" t="n">
-        <v/>
+      <c r="T69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U69" s="8" t="n">
         <v/>
@@ -6282,59 +6282,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2463.64</v>
+        <v>2481.78</v>
       </c>
       <c r="C70" t="n">
-        <v>2531.74</v>
+        <v>2531.08</v>
       </c>
       <c r="D70" t="n">
-        <v>2425.39</v>
+        <v>2416.6</v>
       </c>
       <c r="E70" t="n">
-        <v>2481.83</v>
+        <v>2443.16</v>
       </c>
       <c r="F70" t="n">
-        <v>18.02</v>
+        <v>-38.67</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0156</v>
       </c>
       <c r="H70" t="n">
-        <v>106.36</v>
+        <v>114.48</v>
       </c>
       <c r="I70" t="n">
-        <v>2230.35</v>
+        <v>2319.03</v>
       </c>
       <c r="J70" t="n">
-        <v>2358.67</v>
+        <v>2377.11</v>
       </c>
       <c r="K70" t="n">
-        <v>2400.42</v>
+        <v>2428.65</v>
       </c>
       <c r="L70" t="n">
-        <v>2442.18</v>
+        <v>2480.2</v>
       </c>
       <c r="M70" t="n">
-        <v>2527.21</v>
+        <v>2535.01</v>
       </c>
       <c r="N70" t="n">
-        <v>2612.25</v>
+        <v>2589.82</v>
       </c>
       <c r="O70" t="n">
-        <v>2610.72</v>
+        <v>2638.1</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
@@ -6342,18 +6338,18 @@
       <c r="Q70" s="6" t="n">
         <v/>
       </c>
-      <c r="R70" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S70" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="n">
+        <v/>
       </c>
       <c r="U70" s="8" t="n">
         <v/>
@@ -6366,55 +6362,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr"/>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2481.78</v>
+        <v>2442.49</v>
       </c>
       <c r="C71" t="n">
-        <v>2531.08</v>
+        <v>2514.67</v>
       </c>
       <c r="D71" t="n">
-        <v>2416.6</v>
+        <v>2432.51</v>
       </c>
       <c r="E71" t="n">
-        <v>2443.16</v>
+        <v>2506.26</v>
       </c>
       <c r="F71" t="n">
-        <v>-38.67</v>
+        <v>63.1</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0258</v>
       </c>
       <c r="H71" t="n">
-        <v>114.48</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>2319.03</v>
+        <v>2302.12</v>
       </c>
       <c r="J71" t="n">
-        <v>2377.11</v>
+        <v>2313.34</v>
       </c>
       <c r="K71" t="n">
-        <v>2428.65</v>
+        <v>2385.92</v>
       </c>
       <c r="L71" t="n">
-        <v>2480.2</v>
+        <v>2458.5</v>
       </c>
       <c r="M71" t="n">
-        <v>2535.01</v>
+        <v>2500.4</v>
       </c>
       <c r="N71" t="n">
-        <v>2589.82</v>
+        <v>2542.3</v>
       </c>
       <c r="O71" t="n">
-        <v>2638.1</v>
+        <v>2645.57</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6422,19 +6422,19 @@
       <c r="Q71" s="6" t="n">
         <v/>
       </c>
-      <c r="R71" s="6" t="inlineStr">
+      <c r="R71" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S71" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S71" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="n">
-        <v/>
-      </c>
       <c r="U71" s="8" t="n">
         <v/>
       </c>
@@ -6448,57 +6448,57 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2442.49</v>
+        <v>2506.24</v>
       </c>
       <c r="C72" t="n">
-        <v>2514.67</v>
+        <v>2564.27</v>
       </c>
       <c r="D72" t="n">
-        <v>2432.51</v>
+        <v>2481.94</v>
       </c>
       <c r="E72" t="n">
-        <v>2506.26</v>
+        <v>2510.41</v>
       </c>
       <c r="F72" t="n">
-        <v>63.1</v>
+        <v>4.15</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.0258</v>
+        <v>0.0017</v>
       </c>
       <c r="H72" t="n">
-        <v>82.15000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="I72" t="n">
-        <v>2302.12</v>
+        <v>2350.36</v>
       </c>
       <c r="J72" t="n">
-        <v>2313.34</v>
+        <v>2440.44</v>
       </c>
       <c r="K72" t="n">
-        <v>2385.92</v>
+        <v>2465.18</v>
       </c>
       <c r="L72" t="n">
-        <v>2458.5</v>
+        <v>2489.93</v>
       </c>
       <c r="M72" t="n">
-        <v>2500.4</v>
+        <v>2547.34</v>
       </c>
       <c r="N72" t="n">
-        <v>2542.3</v>
+        <v>2604.75</v>
       </c>
       <c r="O72" t="n">
-        <v>2645.57</v>
+        <v>2596.82</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S72" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T72" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U72" s="8" t="n">
@@ -6530,79 +6530,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2506.24</v>
+        <v>2510.67</v>
       </c>
       <c r="C73" t="n">
-        <v>2564.27</v>
+        <v>2534.01</v>
       </c>
       <c r="D73" t="n">
-        <v>2481.94</v>
+        <v>2408.72</v>
       </c>
       <c r="E73" t="n">
-        <v>2510.41</v>
+        <v>2442.54</v>
       </c>
       <c r="F73" t="n">
-        <v>4.15</v>
+        <v>-67.87</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.027</v>
       </c>
       <c r="H73" t="n">
-        <v>82.33</v>
+        <v>125.29</v>
       </c>
       <c r="I73" t="n">
-        <v>2350.36</v>
+        <v>2399.62</v>
       </c>
       <c r="J73" t="n">
-        <v>2440.44</v>
+        <v>2421.73</v>
       </c>
       <c r="K73" t="n">
-        <v>2465.18</v>
+        <v>2469.25</v>
       </c>
       <c r="L73" t="n">
-        <v>2489.93</v>
+        <v>2516.76</v>
       </c>
       <c r="M73" t="n">
-        <v>2547.34</v>
+        <v>2551.57</v>
       </c>
       <c r="N73" t="n">
-        <v>2604.75</v>
+        <v>2586.39</v>
       </c>
       <c r="O73" t="n">
-        <v>2596.82</v>
+        <v>2646.6</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
       </c>
-      <c r="Q73" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R73" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S73" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="inlineStr">
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R73" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S73" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="n">
+        <v/>
+      </c>
       <c r="U73" s="8" t="n">
         <v/>
       </c>
@@ -6614,72 +6612,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr"/>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2510.67</v>
+        <v>2442.56</v>
       </c>
       <c r="C74" t="n">
-        <v>2534.01</v>
+        <v>2459.63</v>
       </c>
       <c r="D74" t="n">
-        <v>2408.72</v>
+        <v>2430.81</v>
       </c>
       <c r="E74" t="n">
-        <v>2442.54</v>
+        <v>2457.69</v>
       </c>
       <c r="F74" t="n">
-        <v>-67.87</v>
+        <v>15.15</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.027</v>
+        <v>0.0062</v>
       </c>
       <c r="H74" t="n">
-        <v>125.29</v>
+        <v>28.82</v>
       </c>
       <c r="I74" t="n">
-        <v>2399.62</v>
+        <v>2283.43</v>
       </c>
       <c r="J74" t="n">
-        <v>2421.73</v>
+        <v>2302.83</v>
       </c>
       <c r="K74" t="n">
-        <v>2469.25</v>
+        <v>2379.89</v>
       </c>
       <c r="L74" t="n">
-        <v>2516.76</v>
+        <v>2456.95</v>
       </c>
       <c r="M74" t="n">
-        <v>2551.57</v>
+        <v>2505.18</v>
       </c>
       <c r="N74" t="n">
-        <v>2586.39</v>
+        <v>2553.41</v>
       </c>
       <c r="O74" t="n">
-        <v>2646.6</v>
+        <v>2659.3</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
       </c>
-      <c r="Q74" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R74" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S74" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S74" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T74" s="8" t="n">
@@ -6698,84 +6696,96 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2442.56</v>
+        <v>2457.69</v>
       </c>
       <c r="C75" t="n">
-        <v>2459.63</v>
+        <v>2532.96</v>
       </c>
       <c r="D75" t="n">
-        <v>2430.81</v>
+        <v>2389.47</v>
       </c>
       <c r="E75" t="n">
-        <v>2457.69</v>
+        <v>2417.94</v>
       </c>
       <c r="F75" t="n">
-        <v>15.15</v>
+        <v>-39.75</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H75" t="n">
-        <v>28.82</v>
+        <v>143.49</v>
       </c>
       <c r="I75" t="n">
-        <v>2283.43</v>
+        <v>2401.99</v>
       </c>
       <c r="J75" t="n">
-        <v>2302.83</v>
+        <v>2435.1</v>
       </c>
       <c r="K75" t="n">
-        <v>2379.89</v>
+        <v>2443.28</v>
       </c>
       <c r="L75" t="n">
-        <v>2456.95</v>
+        <v>2451.45</v>
       </c>
       <c r="M75" t="n">
-        <v>2505.18</v>
+        <v>2472.1</v>
       </c>
       <c r="N75" t="n">
-        <v>2553.41</v>
+        <v>2492.74</v>
       </c>
       <c r="O75" t="n">
-        <v>2659.3</v>
-      </c>
-      <c r="P75" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q75" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R75" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S75" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T75" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U75" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V75" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W75" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+        <v>2488.45</v>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S75" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W75" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -6787,85 +6797,75 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2457.69</v>
+        <v>2417.9</v>
       </c>
       <c r="C76" t="n">
-        <v>2532.96</v>
+        <v>2488.92</v>
       </c>
       <c r="D76" t="n">
-        <v>2389.47</v>
+        <v>2401.81</v>
       </c>
       <c r="E76" t="n">
-        <v>2417.94</v>
+        <v>2466.82</v>
       </c>
       <c r="F76" t="n">
-        <v>-39.75</v>
+        <v>48.88</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.0202</v>
       </c>
       <c r="H76" t="n">
-        <v>143.49</v>
+        <v>87.11</v>
       </c>
       <c r="I76" t="n">
-        <v>2401.99</v>
+        <v>2245.98</v>
       </c>
       <c r="J76" t="n">
-        <v>2435.1</v>
+        <v>2252.81</v>
       </c>
       <c r="K76" t="n">
-        <v>2443.28</v>
+        <v>2346.19</v>
       </c>
       <c r="L76" t="n">
-        <v>2451.45</v>
+        <v>2439.58</v>
       </c>
       <c r="M76" t="n">
-        <v>2472.1</v>
+        <v>2489.68</v>
       </c>
       <c r="N76" t="n">
-        <v>2492.74</v>
+        <v>2539.79</v>
       </c>
       <c r="O76" t="n">
-        <v>2488.45</v>
-      </c>
-      <c r="P76" s="6" t="inlineStr">
+        <v>2676.45</v>
+      </c>
+      <c r="P76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S76" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q76" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R76" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S76" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U76" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V76" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U76" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V76" s="8" t="n">
+        <v/>
       </c>
       <c r="W76" s="11" t="inlineStr">
         <is>
@@ -6874,77 +6874,79 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2417.9</v>
+        <v>2466.58</v>
       </c>
       <c r="C77" t="n">
-        <v>2488.92</v>
+        <v>2484.4</v>
       </c>
       <c r="D77" t="n">
-        <v>2401.81</v>
+        <v>2383.8</v>
       </c>
       <c r="E77" t="n">
-        <v>2466.82</v>
+        <v>2417.84</v>
       </c>
       <c r="F77" t="n">
-        <v>48.88</v>
+        <v>-48.98</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.0202</v>
+        <v>-0.0199</v>
       </c>
       <c r="H77" t="n">
-        <v>87.11</v>
+        <v>100.6</v>
       </c>
       <c r="I77" t="n">
-        <v>2245.98</v>
+        <v>2314.69</v>
       </c>
       <c r="J77" t="n">
-        <v>2252.81</v>
+        <v>2390.43</v>
       </c>
       <c r="K77" t="n">
-        <v>2346.19</v>
+        <v>2423.26</v>
       </c>
       <c r="L77" t="n">
-        <v>2439.58</v>
+        <v>2456.09</v>
       </c>
       <c r="M77" t="n">
-        <v>2489.68</v>
+        <v>2510.38</v>
       </c>
       <c r="N77" t="n">
-        <v>2539.79</v>
+        <v>2564.66</v>
       </c>
       <c r="O77" t="n">
-        <v>2676.45</v>
+        <v>2576.04</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
       </c>
-      <c r="Q77" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R77" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S77" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="inlineStr">
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S77" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="n">
+        <v/>
+      </c>
       <c r="U77" s="8" t="n">
         <v/>
       </c>
@@ -6956,67 +6958,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2466.58</v>
+        <v>2417.83</v>
       </c>
       <c r="C78" t="n">
-        <v>2484.4</v>
+        <v>2427.4</v>
       </c>
       <c r="D78" t="n">
-        <v>2383.8</v>
+        <v>2356.19</v>
       </c>
       <c r="E78" t="n">
-        <v>2417.84</v>
+        <v>2391.5</v>
       </c>
       <c r="F78" t="n">
-        <v>-48.98</v>
+        <v>-26.34</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.0109</v>
       </c>
       <c r="H78" t="n">
-        <v>100.6</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>2314.69</v>
+        <v>2283.21</v>
       </c>
       <c r="J78" t="n">
-        <v>2390.43</v>
+        <v>2309.12</v>
       </c>
       <c r="K78" t="n">
-        <v>2423.26</v>
+        <v>2367.54</v>
       </c>
       <c r="L78" t="n">
-        <v>2456.09</v>
+        <v>2425.97</v>
       </c>
       <c r="M78" t="n">
-        <v>2510.38</v>
+        <v>2468.14</v>
       </c>
       <c r="N78" t="n">
-        <v>2564.66</v>
+        <v>2510.31</v>
       </c>
       <c r="O78" t="n">
-        <v>2576.04</v>
+        <v>2584.99</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
       </c>
-      <c r="Q78" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q78" s="6" t="n">
+        <v/>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
@@ -7047,50 +7043,50 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2417.83</v>
+        <v>2391.6</v>
       </c>
       <c r="C79" t="n">
-        <v>2427.4</v>
+        <v>2526.95</v>
       </c>
       <c r="D79" t="n">
-        <v>2356.19</v>
+        <v>2370.42</v>
       </c>
       <c r="E79" t="n">
-        <v>2391.5</v>
+        <v>2508.02</v>
       </c>
       <c r="F79" t="n">
-        <v>-26.34</v>
+        <v>116.52</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0109</v>
+        <v>0.0487</v>
       </c>
       <c r="H79" t="n">
-        <v>71.20999999999999</v>
+        <v>156.53</v>
       </c>
       <c r="I79" t="n">
-        <v>2283.21</v>
+        <v>2284.97</v>
       </c>
       <c r="J79" t="n">
-        <v>2309.12</v>
+        <v>2320.14</v>
       </c>
       <c r="K79" t="n">
-        <v>2367.54</v>
+        <v>2355.89</v>
       </c>
       <c r="L79" t="n">
-        <v>2425.97</v>
+        <v>2391.65</v>
       </c>
       <c r="M79" t="n">
-        <v>2468.14</v>
+        <v>2427.11</v>
       </c>
       <c r="N79" t="n">
-        <v>2510.31</v>
+        <v>2462.57</v>
       </c>
       <c r="O79" t="n">
-        <v>2584.99</v>
+        <v>2498.61</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7098,28 +7094,32 @@
       <c r="Q79" s="6" t="n">
         <v/>
       </c>
-      <c r="R79" s="6" t="inlineStr">
+      <c r="R79" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S79" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V79" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S79" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U79" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V79" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W79" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W79" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X79" t="inlineStr"/>
@@ -7127,50 +7127,50 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2391.6</v>
+        <v>2508.02</v>
       </c>
       <c r="C80" t="n">
-        <v>2526.95</v>
+        <v>2545.62</v>
       </c>
       <c r="D80" t="n">
-        <v>2370.42</v>
+        <v>2432.35</v>
       </c>
       <c r="E80" t="n">
-        <v>2508.02</v>
+        <v>2456.08</v>
       </c>
       <c r="F80" t="n">
-        <v>116.52</v>
+        <v>-51.94</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.0487</v>
+        <v>-0.0207</v>
       </c>
       <c r="H80" t="n">
-        <v>156.53</v>
+        <v>113.27</v>
       </c>
       <c r="I80" t="n">
-        <v>2284.97</v>
+        <v>2213.88</v>
       </c>
       <c r="J80" t="n">
-        <v>2320.14</v>
+        <v>2381.16</v>
       </c>
       <c r="K80" t="n">
-        <v>2355.89</v>
+        <v>2429.75</v>
       </c>
       <c r="L80" t="n">
-        <v>2391.65</v>
+        <v>2478.35</v>
       </c>
       <c r="M80" t="n">
-        <v>2427.11</v>
+        <v>2586.29</v>
       </c>
       <c r="N80" t="n">
-        <v>2462.57</v>
+        <v>2694.22</v>
       </c>
       <c r="O80" t="n">
-        <v>2498.61</v>
+        <v>2683.48</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7181,80 +7181,78 @@
       <c r="R80" s="6" t="n">
         <v/>
       </c>
-      <c r="S80" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U80" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V80" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S80" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V80" s="8" t="n">
+        <v/>
       </c>
       <c r="W80" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr"/>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2508.02</v>
+        <v>2455.99</v>
       </c>
       <c r="C81" t="n">
-        <v>2545.62</v>
+        <v>2492.01</v>
       </c>
       <c r="D81" t="n">
-        <v>2432.35</v>
+        <v>2445.69</v>
       </c>
       <c r="E81" t="n">
-        <v>2456.08</v>
+        <v>2480.74</v>
       </c>
       <c r="F81" t="n">
-        <v>-51.94</v>
+        <v>24.66</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0207</v>
+        <v>0.01</v>
       </c>
       <c r="H81" t="n">
-        <v>113.27</v>
+        <v>46.32</v>
       </c>
       <c r="I81" t="n">
-        <v>2213.88</v>
+        <v>2319.08</v>
       </c>
       <c r="J81" t="n">
-        <v>2381.16</v>
+        <v>2326.35</v>
       </c>
       <c r="K81" t="n">
-        <v>2429.75</v>
+        <v>2399.44</v>
       </c>
       <c r="L81" t="n">
-        <v>2478.35</v>
+        <v>2472.53</v>
       </c>
       <c r="M81" t="n">
-        <v>2586.29</v>
+        <v>2512.71</v>
       </c>
       <c r="N81" t="n">
-        <v>2694.22</v>
+        <v>2552.89</v>
       </c>
       <c r="O81" t="n">
-        <v>2683.48</v>
+        <v>2658.89</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7265,9 +7263,9 @@
       <c r="R81" s="6" t="n">
         <v/>
       </c>
-      <c r="S81" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S81" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T81" s="8" t="n">
@@ -7293,50 +7291,50 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2455.99</v>
+        <v>2480.82</v>
       </c>
       <c r="C82" t="n">
-        <v>2492.01</v>
+        <v>2525.32</v>
       </c>
       <c r="D82" t="n">
-        <v>2445.69</v>
+        <v>2468.19</v>
       </c>
       <c r="E82" t="n">
-        <v>2480.74</v>
+        <v>2514.55</v>
       </c>
       <c r="F82" t="n">
-        <v>24.66</v>
+        <v>33.81</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0136</v>
       </c>
       <c r="H82" t="n">
-        <v>46.32</v>
+        <v>57.13</v>
       </c>
       <c r="I82" t="n">
-        <v>2319.08</v>
+        <v>2399.37</v>
       </c>
       <c r="J82" t="n">
-        <v>2326.35</v>
+        <v>2440.36</v>
       </c>
       <c r="K82" t="n">
-        <v>2399.44</v>
+        <v>2457.58</v>
       </c>
       <c r="L82" t="n">
-        <v>2472.53</v>
+        <v>2474.79</v>
       </c>
       <c r="M82" t="n">
-        <v>2512.71</v>
+        <v>2503.9</v>
       </c>
       <c r="N82" t="n">
-        <v>2552.89</v>
+        <v>2533</v>
       </c>
       <c r="O82" t="n">
-        <v>2658.89</v>
+        <v>2538.33</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7349,11 +7347,13 @@
       </c>
       <c r="S82" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U82" s="8" t="n">
         <v/>
@@ -7366,59 +7366,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2480.82</v>
+        <v>2514.58</v>
       </c>
       <c r="C83" t="n">
-        <v>2525.32</v>
+        <v>2534.86</v>
       </c>
       <c r="D83" t="n">
-        <v>2468.19</v>
+        <v>2466.91</v>
       </c>
       <c r="E83" t="n">
-        <v>2514.55</v>
+        <v>2490.96</v>
       </c>
       <c r="F83" t="n">
-        <v>33.81</v>
+        <v>-23.59</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0094</v>
       </c>
       <c r="H83" t="n">
-        <v>57.13</v>
+        <v>67.95</v>
       </c>
       <c r="I83" t="n">
-        <v>2399.37</v>
+        <v>2411.07</v>
       </c>
       <c r="J83" t="n">
-        <v>2440.36</v>
+        <v>2466.32</v>
       </c>
       <c r="K83" t="n">
-        <v>2457.58</v>
+        <v>2485.99</v>
       </c>
       <c r="L83" t="n">
-        <v>2474.79</v>
+        <v>2505.65</v>
       </c>
       <c r="M83" t="n">
-        <v>2503.9</v>
+        <v>2543.11</v>
       </c>
       <c r="N83" t="n">
-        <v>2533</v>
+        <v>2580.57</v>
       </c>
       <c r="O83" t="n">
-        <v>2538.33</v>
+        <v>2582.45</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
@@ -7426,19 +7422,19 @@
       <c r="Q83" s="6" t="n">
         <v/>
       </c>
-      <c r="R83" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S83" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="inlineStr">
+      <c r="R83" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S83" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="n">
+        <v/>
+      </c>
       <c r="U83" s="8" t="n">
         <v/>
       </c>
@@ -7450,55 +7446,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr"/>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2514.58</v>
+        <v>2490.92</v>
       </c>
       <c r="C84" t="n">
-        <v>2534.86</v>
+        <v>2506.75</v>
       </c>
       <c r="D84" t="n">
-        <v>2466.91</v>
+        <v>2441.33</v>
       </c>
       <c r="E84" t="n">
-        <v>2490.96</v>
+        <v>2484.94</v>
       </c>
       <c r="F84" t="n">
-        <v>-23.59</v>
+        <v>-6.02</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0024</v>
       </c>
       <c r="H84" t="n">
-        <v>67.95</v>
+        <v>65.42</v>
       </c>
       <c r="I84" t="n">
-        <v>2411.07</v>
+        <v>2398.96</v>
       </c>
       <c r="J84" t="n">
-        <v>2466.32</v>
+        <v>2418.04</v>
       </c>
       <c r="K84" t="n">
-        <v>2485.99</v>
+        <v>2456.98</v>
       </c>
       <c r="L84" t="n">
-        <v>2505.65</v>
+        <v>2495.92</v>
       </c>
       <c r="M84" t="n">
-        <v>2543.11</v>
+        <v>2524.93</v>
       </c>
       <c r="N84" t="n">
-        <v>2580.57</v>
+        <v>2553.94</v>
       </c>
       <c r="O84" t="n">
-        <v>2582.45</v>
+        <v>2602.81</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
@@ -7508,12 +7508,12 @@
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T84" s="8" t="n">
@@ -7532,57 +7532,57 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2490.92</v>
+        <v>2484.89</v>
       </c>
       <c r="C85" t="n">
-        <v>2506.75</v>
+        <v>2522.37</v>
       </c>
       <c r="D85" t="n">
-        <v>2441.33</v>
+        <v>2443.7</v>
       </c>
       <c r="E85" t="n">
-        <v>2484.94</v>
+        <v>2466.91</v>
       </c>
       <c r="F85" t="n">
-        <v>-6.02</v>
+        <v>-18.03</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0073</v>
       </c>
       <c r="H85" t="n">
-        <v>65.42</v>
+        <v>78.67</v>
       </c>
       <c r="I85" t="n">
-        <v>2398.96</v>
+        <v>2375.9</v>
       </c>
       <c r="J85" t="n">
-        <v>2418.04</v>
+        <v>2424.97</v>
       </c>
       <c r="K85" t="n">
-        <v>2456.98</v>
+        <v>2452.23</v>
       </c>
       <c r="L85" t="n">
-        <v>2495.92</v>
+        <v>2479.49</v>
       </c>
       <c r="M85" t="n">
-        <v>2524.93</v>
+        <v>2517.65</v>
       </c>
       <c r="N85" t="n">
-        <v>2553.94</v>
+        <v>2555.82</v>
       </c>
       <c r="O85" t="n">
-        <v>2602.81</v>
+        <v>2572.18</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7600,8 +7600,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T85" s="8" t="n">
-        <v/>
+      <c r="T85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U85" s="8" t="n">
         <v/>
@@ -7616,57 +7618,57 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2484.89</v>
+        <v>2466.91</v>
       </c>
       <c r="C86" t="n">
-        <v>2522.37</v>
+        <v>2483.72</v>
       </c>
       <c r="D86" t="n">
-        <v>2443.7</v>
+        <v>2406.91</v>
       </c>
       <c r="E86" t="n">
-        <v>2466.91</v>
+        <v>2437.1</v>
       </c>
       <c r="F86" t="n">
-        <v>-18.03</v>
+        <v>-29.82</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0121</v>
       </c>
       <c r="H86" t="n">
-        <v>78.67</v>
+        <v>76.81</v>
       </c>
       <c r="I86" t="n">
-        <v>2375.9</v>
+        <v>2365.04</v>
       </c>
       <c r="J86" t="n">
-        <v>2424.97</v>
+        <v>2380.19</v>
       </c>
       <c r="K86" t="n">
-        <v>2452.23</v>
+        <v>2427.58</v>
       </c>
       <c r="L86" t="n">
-        <v>2479.49</v>
+        <v>2474.97</v>
       </c>
       <c r="M86" t="n">
-        <v>2517.65</v>
+        <v>2506.25</v>
       </c>
       <c r="N86" t="n">
-        <v>2555.82</v>
+        <v>2537.52</v>
       </c>
       <c r="O86" t="n">
-        <v>2572.18</v>
+        <v>2601.04</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7676,18 +7678,16 @@
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="n">
+        <v/>
       </c>
       <c r="U86" s="8" t="n">
         <v/>
@@ -7702,57 +7702,57 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2466.91</v>
+        <v>2437.14</v>
       </c>
       <c r="C87" t="n">
-        <v>2483.72</v>
+        <v>2663.05</v>
       </c>
       <c r="D87" t="n">
-        <v>2406.91</v>
+        <v>2435.29</v>
       </c>
       <c r="E87" t="n">
-        <v>2437.1</v>
+        <v>2514.73</v>
       </c>
       <c r="F87" t="n">
-        <v>-29.82</v>
+        <v>77.64</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.0121</v>
+        <v>0.0319</v>
       </c>
       <c r="H87" t="n">
-        <v>76.81</v>
+        <v>227.76</v>
       </c>
       <c r="I87" t="n">
-        <v>2365.04</v>
+        <v>2330.09</v>
       </c>
       <c r="J87" t="n">
-        <v>2380.19</v>
+        <v>2356.18</v>
       </c>
       <c r="K87" t="n">
-        <v>2427.58</v>
+        <v>2398.69</v>
       </c>
       <c r="L87" t="n">
-        <v>2474.97</v>
+        <v>2441.21</v>
       </c>
       <c r="M87" t="n">
-        <v>2506.25</v>
+        <v>2475.51</v>
       </c>
       <c r="N87" t="n">
-        <v>2537.52</v>
+        <v>2509.8</v>
       </c>
       <c r="O87" t="n">
-        <v>2601.04</v>
+        <v>2560.53</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7760,83 +7760,83 @@
       <c r="Q87" s="6" t="n">
         <v/>
       </c>
-      <c r="R87" s="6" t="inlineStr">
+      <c r="R87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S87" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U87" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S87" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V87" s="8" t="n">
-        <v/>
+      <c r="V87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W87" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2437.14</v>
+        <v>2514.77</v>
       </c>
       <c r="C88" t="n">
-        <v>2663.05</v>
+        <v>2544.47</v>
       </c>
       <c r="D88" t="n">
-        <v>2435.29</v>
+        <v>2508.8</v>
       </c>
       <c r="E88" t="n">
-        <v>2514.73</v>
+        <v>2525.94</v>
       </c>
       <c r="F88" t="n">
-        <v>77.64</v>
+        <v>11.21</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.0319</v>
+        <v>0.0045</v>
       </c>
       <c r="H88" t="n">
-        <v>227.76</v>
+        <v>35.67</v>
       </c>
       <c r="I88" t="n">
-        <v>2330.09</v>
+        <v>2207.52</v>
       </c>
       <c r="J88" t="n">
-        <v>2356.18</v>
+        <v>2269.75</v>
       </c>
       <c r="K88" t="n">
-        <v>2398.69</v>
+        <v>2400.85</v>
       </c>
       <c r="L88" t="n">
-        <v>2441.21</v>
+        <v>2531.95</v>
       </c>
       <c r="M88" t="n">
-        <v>2475.51</v>
+        <v>2628.62</v>
       </c>
       <c r="N88" t="n">
-        <v>2509.8</v>
+        <v>2725.28</v>
       </c>
       <c r="O88" t="n">
-        <v>2560.53</v>
+        <v>2890.82</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
@@ -7847,93 +7847,97 @@
       <c r="R88" s="6" t="n">
         <v/>
       </c>
-      <c r="S88" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U88" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S88" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V88" s="8" t="n">
+        <v/>
       </c>
       <c r="W88" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr"/>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2514.77</v>
+        <v>2525.94</v>
       </c>
       <c r="C89" t="n">
-        <v>2544.47</v>
+        <v>2526.85</v>
       </c>
       <c r="D89" t="n">
-        <v>2508.8</v>
+        <v>2462.84</v>
       </c>
       <c r="E89" t="n">
-        <v>2525.94</v>
+        <v>2477.02</v>
       </c>
       <c r="F89" t="n">
-        <v>11.21</v>
+        <v>-48.92</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0194</v>
       </c>
       <c r="H89" t="n">
-        <v>35.67</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>2207.52</v>
+        <v>2473.13</v>
       </c>
       <c r="J89" t="n">
-        <v>2269.75</v>
+        <v>2489.93</v>
       </c>
       <c r="K89" t="n">
-        <v>2400.85</v>
+        <v>2508.11</v>
       </c>
       <c r="L89" t="n">
-        <v>2531.95</v>
+        <v>2526.29</v>
       </c>
       <c r="M89" t="n">
-        <v>2628.62</v>
+        <v>2543.78</v>
       </c>
       <c r="N89" t="n">
-        <v>2725.28</v>
+        <v>2561.27</v>
       </c>
       <c r="O89" t="n">
-        <v>2890.82</v>
-      </c>
-      <c r="P89" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q89" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R89" s="6" t="n">
-        <v/>
+        <v>2580.14</v>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T89" s="8" t="n">
@@ -7945,88 +7949,80 @@
       <c r="V89" s="8" t="n">
         <v/>
       </c>
-      <c r="W89" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W89" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2525.94</v>
+        <v>2515.17</v>
       </c>
       <c r="C90" t="n">
-        <v>2526.85</v>
+        <v>2517.18</v>
       </c>
       <c r="D90" t="n">
-        <v>2462.84</v>
+        <v>2508.21</v>
       </c>
       <c r="E90" t="n">
-        <v>2477.02</v>
+        <v>2516.14</v>
       </c>
       <c r="F90" t="n">
-        <v>-48.92</v>
+        <v>39.12</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0194</v>
+        <v>0.0158</v>
       </c>
       <c r="H90" t="n">
-        <v>64.01000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>2473.13</v>
+        <v>2398.83</v>
       </c>
       <c r="J90" t="n">
-        <v>2489.93</v>
+        <v>2404.09</v>
       </c>
       <c r="K90" t="n">
-        <v>2508.11</v>
+        <v>2445.01</v>
       </c>
       <c r="L90" t="n">
-        <v>2526.29</v>
+        <v>2485.93</v>
       </c>
       <c r="M90" t="n">
-        <v>2543.78</v>
+        <v>2509.03</v>
       </c>
       <c r="N90" t="n">
-        <v>2561.27</v>
+        <v>2532.12</v>
       </c>
       <c r="O90" t="n">
-        <v>2580.14</v>
-      </c>
-      <c r="P90" s="6" t="inlineStr">
+        <v>2590.87</v>
+      </c>
+      <c r="P90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S90" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q90" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R90" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S90" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="n">
-        <v/>
-      </c>
       <c r="U90" s="8" t="n">
         <v/>
       </c>
@@ -8038,118 +8034,38 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr"/>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>2475.82</v>
-      </c>
-      <c r="C91" t="n">
-        <v>2605.78</v>
-      </c>
-      <c r="D91" t="n">
-        <v>2468.6</v>
-      </c>
-      <c r="E91" t="n">
-        <v>2548.83</v>
-      </c>
-      <c r="F91" t="n">
-        <v>71.81</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="H91" t="n">
-        <v>137.18</v>
-      </c>
-      <c r="I91" t="n">
-        <v>2398.83</v>
-      </c>
-      <c r="J91" t="n">
-        <v>2404.09</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2445.01</v>
-      </c>
-      <c r="L91" t="n">
-        <v>2485.93</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2509.03</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2532.12</v>
-      </c>
-      <c r="O91" t="n">
-        <v>2590.87</v>
-      </c>
-      <c r="P91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S91" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U91" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W91" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I92" s="13" t="n">
-        <v>2331.42</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>2417.47</v>
-      </c>
-      <c r="K92" s="13" t="n">
-        <v>2480.24</v>
-      </c>
-      <c r="L92" s="13" t="n">
-        <v>2543.01</v>
-      </c>
-      <c r="M92" s="13" t="n">
-        <v>2617.42</v>
-      </c>
-      <c r="N92" s="13" t="n">
-        <v>2691.83</v>
-      </c>
-      <c r="O92" s="13" t="n">
-        <v>2742.96</v>
+      <c r="I91" s="13" t="n">
+        <v>2499.24</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>2508.89</v>
+      </c>
+      <c r="K91" s="13" t="n">
+        <v>2511.65</v>
+      </c>
+      <c r="L91" s="13" t="n">
+        <v>2514.42</v>
+      </c>
+      <c r="M91" s="13" t="n">
+        <v>2520.63</v>
+      </c>
+      <c r="N91" s="13" t="n">
+        <v>2526.83</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>2526.16</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -7966,22 +7966,22 @@
         <v>2515.17</v>
       </c>
       <c r="C90" t="n">
-        <v>2517.18</v>
+        <v>2518.69</v>
       </c>
       <c r="D90" t="n">
         <v>2508.21</v>
       </c>
       <c r="E90" t="n">
-        <v>2516.14</v>
+        <v>2516.7</v>
       </c>
       <c r="F90" t="n">
-        <v>39.12</v>
+        <v>39.68</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.016</v>
       </c>
       <c r="H90" t="n">
-        <v>8.970000000000001</v>
+        <v>10.47</v>
       </c>
       <c r="I90" t="n">
         <v>2398.83</v>
@@ -8047,25 +8047,25 @@
         </is>
       </c>
       <c r="I91" s="13" t="n">
-        <v>2499.24</v>
+        <v>2497.74</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>2508.89</v>
+        <v>2507.85</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>2511.65</v>
+        <v>2511.46</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>2514.42</v>
+        <v>2515.07</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>2520.63</v>
+        <v>2521.94</v>
       </c>
       <c r="N91" s="13" t="n">
-        <v>2526.83</v>
+        <v>2528.8</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>2526.16</v>
+        <v>2529.16</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -7969,19 +7969,19 @@
         <v>2518.69</v>
       </c>
       <c r="D90" t="n">
-        <v>2508.21</v>
+        <v>2497.06</v>
       </c>
       <c r="E90" t="n">
-        <v>2516.7</v>
+        <v>2498.84</v>
       </c>
       <c r="F90" t="n">
-        <v>39.68</v>
+        <v>21.82</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.016</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H90" t="n">
-        <v>10.47</v>
+        <v>21.63</v>
       </c>
       <c r="I90" t="n">
         <v>2398.83</v>
@@ -8047,25 +8047,25 @@
         </is>
       </c>
       <c r="I91" s="13" t="n">
-        <v>2497.74</v>
+        <v>2475.43</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>2507.85</v>
+        <v>2472.69</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>2511.46</v>
+        <v>2488.02</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>2515.07</v>
+        <v>2503.36</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>2521.94</v>
+        <v>2509.66</v>
       </c>
       <c r="N91" s="13" t="n">
-        <v>2528.8</v>
+        <v>2515.95</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>2529.16</v>
+        <v>2540.32</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -7969,19 +7969,19 @@
         <v>2518.69</v>
       </c>
       <c r="D90" t="n">
-        <v>2497.06</v>
+        <v>2497.89</v>
       </c>
       <c r="E90" t="n">
-        <v>2498.84</v>
+        <v>2498.33</v>
       </c>
       <c r="F90" t="n">
-        <v>21.82</v>
+        <v>21.31</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0086</v>
       </c>
       <c r="H90" t="n">
-        <v>21.63</v>
+        <v>20.79</v>
       </c>
       <c r="I90" t="n">
         <v>2398.83</v>
@@ -8047,25 +8047,25 @@
         </is>
       </c>
       <c r="I91" s="13" t="n">
-        <v>2475.43</v>
+        <v>2477.1</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>2472.69</v>
+        <v>2472.56</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>2488.02</v>
+        <v>2487.93</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>2503.36</v>
+        <v>2503.31</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>2509.66</v>
+        <v>2508.73</v>
       </c>
       <c r="N91" s="13" t="n">
-        <v>2515.95</v>
+        <v>2514.14</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>2540.32</v>
+        <v>2539.48</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X91"/>
+  <dimension ref="A1:X92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7959,29 +7959,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2515.17</v>
+        <v>2476.6</v>
       </c>
       <c r="C90" t="n">
-        <v>2518.69</v>
+        <v>2612.4</v>
       </c>
       <c r="D90" t="n">
-        <v>2497.89</v>
+        <v>2465.43</v>
       </c>
       <c r="E90" t="n">
-        <v>2498.33</v>
+        <v>2514.41</v>
       </c>
       <c r="F90" t="n">
-        <v>21.31</v>
+        <v>37.39</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0151</v>
       </c>
       <c r="H90" t="n">
-        <v>20.79</v>
+        <v>146.98</v>
       </c>
       <c r="I90" t="n">
         <v>2398.83</v>
@@ -8023,11 +8023,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U90" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V90" s="8" t="n">
-        <v/>
+      <c r="U90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W90" s="11" t="inlineStr">
         <is>
@@ -8036,36 +8040,118 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="inlineStr">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2515.17</v>
+      </c>
+      <c r="C91" t="n">
+        <v>2518.69</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2358.66</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2387.94</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-126.47</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-0.0503</v>
+      </c>
+      <c r="H91" t="n">
+        <v>160.03</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2318.45</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2355.18</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2440.92</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2526.66</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2587.9</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2649.13</v>
+      </c>
+      <c r="O91" t="n">
+        <v>2759.38</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W91" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I91" s="13" t="n">
-        <v>2477.1</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>2472.56</v>
-      </c>
-      <c r="K91" s="13" t="n">
-        <v>2487.93</v>
-      </c>
-      <c r="L91" s="13" t="n">
-        <v>2503.31</v>
-      </c>
-      <c r="M91" s="13" t="n">
-        <v>2508.73</v>
-      </c>
-      <c r="N91" s="13" t="n">
-        <v>2514.14</v>
-      </c>
-      <c r="O91" s="13" t="n">
-        <v>2539.48</v>
+      <c r="I92" s="13" t="n">
+        <v>2198.62</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>2202.54</v>
+      </c>
+      <c r="K92" s="13" t="n">
+        <v>2307.92</v>
+      </c>
+      <c r="L92" s="13" t="n">
+        <v>2413.31</v>
+      </c>
+      <c r="M92" s="13" t="n">
+        <v>2467.96</v>
+      </c>
+      <c r="N92" s="13" t="n">
+        <v>2522.61</v>
+      </c>
+      <c r="O92" s="13" t="n">
+        <v>2678.72</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1747.88</v>
+        <v>1709.5</v>
       </c>
       <c r="C2" t="n">
-        <v>1760.88</v>
+        <v>1717.19</v>
       </c>
       <c r="D2" t="n">
-        <v>1670.1</v>
+        <v>1678.2</v>
       </c>
       <c r="E2" t="n">
-        <v>1709.53</v>
+        <v>1710.98</v>
       </c>
       <c r="F2" t="n">
-        <v>-38.35</v>
+        <v>1.45</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0219</v>
+        <v>0.0008</v>
       </c>
       <c r="H2" t="n">
-        <v>90.78</v>
+        <v>39</v>
       </c>
       <c r="I2" t="n">
-        <v>1642.15</v>
+        <v>1579.33</v>
       </c>
       <c r="J2" t="n">
-        <v>1656.26</v>
+        <v>1615.78</v>
       </c>
       <c r="K2" t="n">
-        <v>1706.6</v>
+        <v>1664.14</v>
       </c>
       <c r="L2" t="n">
-        <v>1756.94</v>
+        <v>1712.51</v>
       </c>
       <c r="M2" t="n">
-        <v>1789.17</v>
+        <v>1754.92</v>
       </c>
       <c r="N2" t="n">
-        <v>1821.39</v>
+        <v>1797.33</v>
       </c>
       <c r="O2" t="n">
-        <v>1889.85</v>
+        <v>1851.66</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,14 +692,12 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -718,57 +716,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1709.5</v>
+        <v>1710.98</v>
       </c>
       <c r="C3" t="n">
-        <v>1717.19</v>
+        <v>1747.26</v>
       </c>
       <c r="D3" t="n">
-        <v>1678.2</v>
+        <v>1702.8</v>
       </c>
       <c r="E3" t="n">
-        <v>1710.98</v>
+        <v>1739.3</v>
       </c>
       <c r="F3" t="n">
-        <v>1.45</v>
+        <v>28.32</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0166</v>
       </c>
       <c r="H3" t="n">
-        <v>39</v>
+        <v>44.46</v>
       </c>
       <c r="I3" t="n">
-        <v>1579.33</v>
+        <v>1639.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1615.78</v>
+        <v>1678.63</v>
       </c>
       <c r="K3" t="n">
-        <v>1664.14</v>
+        <v>1691.48</v>
       </c>
       <c r="L3" t="n">
-        <v>1712.51</v>
+        <v>1704.34</v>
       </c>
       <c r="M3" t="n">
-        <v>1754.92</v>
+        <v>1730.48</v>
       </c>
       <c r="N3" t="n">
-        <v>1797.33</v>
+        <v>1756.62</v>
       </c>
       <c r="O3" t="n">
-        <v>1851.66</v>
+        <v>1756.19</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,13 +777,15 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -798,79 +798,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1710.98</v>
+        <v>1739.34</v>
       </c>
       <c r="C4" t="n">
-        <v>1747.26</v>
+        <v>1739.49</v>
       </c>
       <c r="D4" t="n">
-        <v>1702.8</v>
+        <v>1701.94</v>
       </c>
       <c r="E4" t="n">
-        <v>1739.3</v>
+        <v>1704.58</v>
       </c>
       <c r="F4" t="n">
-        <v>28.32</v>
+        <v>-34.72</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.02</v>
       </c>
       <c r="H4" t="n">
-        <v>44.46</v>
+        <v>37.55</v>
       </c>
       <c r="I4" t="n">
-        <v>1639.2</v>
+        <v>1658.34</v>
       </c>
       <c r="J4" t="n">
-        <v>1678.63</v>
+        <v>1701.98</v>
       </c>
       <c r="K4" t="n">
-        <v>1691.48</v>
+        <v>1717.07</v>
       </c>
       <c r="L4" t="n">
-        <v>1704.34</v>
+        <v>1732.17</v>
       </c>
       <c r="M4" t="n">
-        <v>1730.48</v>
+        <v>1761.53</v>
       </c>
       <c r="N4" t="n">
-        <v>1756.62</v>
+        <v>1790.89</v>
       </c>
       <c r="O4" t="n">
-        <v>1756.19</v>
+        <v>1791.72</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -882,80 +880,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1739.34</v>
+        <v>1704.63</v>
       </c>
       <c r="C5" t="n">
-        <v>1739.49</v>
+        <v>1776.83</v>
       </c>
       <c r="D5" t="n">
-        <v>1701.94</v>
+        <v>1704.52</v>
       </c>
       <c r="E5" t="n">
-        <v>1704.58</v>
+        <v>1726.51</v>
       </c>
       <c r="F5" t="n">
-        <v>-34.72</v>
+        <v>21.93</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0129</v>
       </c>
       <c r="H5" t="n">
-        <v>37.55</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1658.34</v>
+        <v>1664.39</v>
       </c>
       <c r="J5" t="n">
-        <v>1701.98</v>
+        <v>1658.97</v>
       </c>
       <c r="K5" t="n">
-        <v>1717.07</v>
+        <v>1685.81</v>
       </c>
       <c r="L5" t="n">
-        <v>1732.17</v>
+        <v>1712.65</v>
       </c>
       <c r="M5" t="n">
-        <v>1761.53</v>
+        <v>1723.36</v>
       </c>
       <c r="N5" t="n">
-        <v>1790.89</v>
+        <v>1734.06</v>
       </c>
       <c r="O5" t="n">
-        <v>1791.72</v>
+        <v>1777.04</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
@@ -964,84 +966,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1704.63</v>
+        <v>1726.52</v>
       </c>
       <c r="C6" t="n">
-        <v>1776.83</v>
+        <v>1733.61</v>
       </c>
       <c r="D6" t="n">
-        <v>1704.52</v>
+        <v>1638.25</v>
       </c>
       <c r="E6" t="n">
-        <v>1726.51</v>
+        <v>1665.44</v>
       </c>
       <c r="F6" t="n">
-        <v>21.93</v>
+        <v>-61.07</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0354</v>
       </c>
       <c r="H6" t="n">
-        <v>72.31999999999999</v>
+        <v>95.36</v>
       </c>
       <c r="I6" t="n">
-        <v>1664.39</v>
+        <v>1632.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1658.97</v>
+        <v>1647.11</v>
       </c>
       <c r="K6" t="n">
-        <v>1685.81</v>
+        <v>1690.35</v>
       </c>
       <c r="L6" t="n">
-        <v>1712.65</v>
+        <v>1733.59</v>
       </c>
       <c r="M6" t="n">
-        <v>1723.36</v>
+        <v>1762.67</v>
       </c>
       <c r="N6" t="n">
-        <v>1734.06</v>
+        <v>1791.74</v>
       </c>
       <c r="O6" t="n">
-        <v>1777.04</v>
+        <v>1849.15</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1050,67 +1048,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1726.52</v>
+        <v>1665.31</v>
       </c>
       <c r="C7" t="n">
-        <v>1733.61</v>
+        <v>1687.49</v>
       </c>
       <c r="D7" t="n">
-        <v>1638.25</v>
+        <v>1551.48</v>
       </c>
       <c r="E7" t="n">
-        <v>1665.44</v>
+        <v>1619.92</v>
       </c>
       <c r="F7" t="n">
-        <v>-61.07</v>
+        <v>-45.51</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0354</v>
+        <v>-0.0273</v>
       </c>
       <c r="H7" t="n">
-        <v>95.36</v>
+        <v>136.01</v>
       </c>
       <c r="I7" t="n">
-        <v>1632.2</v>
+        <v>1542.89</v>
       </c>
       <c r="J7" t="n">
-        <v>1647.11</v>
+        <v>1559.83</v>
       </c>
       <c r="K7" t="n">
-        <v>1690.35</v>
+        <v>1617.76</v>
       </c>
       <c r="L7" t="n">
-        <v>1733.59</v>
+        <v>1675.68</v>
       </c>
       <c r="M7" t="n">
-        <v>1762.67</v>
+        <v>1713.12</v>
       </c>
       <c r="N7" t="n">
-        <v>1791.74</v>
+        <v>1750.55</v>
       </c>
       <c r="O7" t="n">
-        <v>1849.15</v>
+        <v>1828.97</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
@@ -1141,58 +1143,56 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1665.31</v>
+        <v>1619.89</v>
       </c>
       <c r="C8" t="n">
-        <v>1687.49</v>
+        <v>1656.65</v>
       </c>
       <c r="D8" t="n">
-        <v>1551.48</v>
+        <v>1531.78</v>
       </c>
       <c r="E8" t="n">
-        <v>1619.92</v>
+        <v>1564.82</v>
       </c>
       <c r="F8" t="n">
-        <v>-45.51</v>
+        <v>-55.11</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.034</v>
       </c>
       <c r="H8" t="n">
-        <v>136.01</v>
+        <v>124.87</v>
       </c>
       <c r="I8" t="n">
-        <v>1542.89</v>
+        <v>1415.48</v>
       </c>
       <c r="J8" t="n">
-        <v>1559.83</v>
+        <v>1484.14</v>
       </c>
       <c r="K8" t="n">
-        <v>1617.76</v>
+        <v>1551.92</v>
       </c>
       <c r="L8" t="n">
-        <v>1675.68</v>
+        <v>1619.71</v>
       </c>
       <c r="M8" t="n">
-        <v>1713.12</v>
+        <v>1687.93</v>
       </c>
       <c r="N8" t="n">
-        <v>1750.55</v>
+        <v>1756.15</v>
       </c>
       <c r="O8" t="n">
-        <v>1828.97</v>
+        <v>1823.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q8" s="6" t="n">
+        <v/>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
@@ -1227,50 +1227,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1619.89</v>
+        <v>1564.61</v>
       </c>
       <c r="C9" t="n">
-        <v>1656.65</v>
+        <v>1590.2</v>
       </c>
       <c r="D9" t="n">
-        <v>1531.78</v>
+        <v>1510.51</v>
       </c>
       <c r="E9" t="n">
-        <v>1564.82</v>
+        <v>1576.62</v>
       </c>
       <c r="F9" t="n">
-        <v>-55.11</v>
+        <v>11.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.034</v>
+        <v>0.0075</v>
       </c>
       <c r="H9" t="n">
-        <v>124.87</v>
+        <v>79.69</v>
       </c>
       <c r="I9" t="n">
-        <v>1415.48</v>
+        <v>1406.91</v>
       </c>
       <c r="J9" t="n">
-        <v>1484.14</v>
+        <v>1425.25</v>
       </c>
       <c r="K9" t="n">
-        <v>1551.92</v>
+        <v>1502.38</v>
       </c>
       <c r="L9" t="n">
-        <v>1619.71</v>
+        <v>1579.52</v>
       </c>
       <c r="M9" t="n">
-        <v>1687.93</v>
+        <v>1627.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1756.15</v>
+        <v>1674.98</v>
       </c>
       <c r="O9" t="n">
-        <v>1823.5</v>
+        <v>1781.51</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1278,14 +1278,12 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1304,57 +1302,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1564.61</v>
+        <v>1576.59</v>
       </c>
       <c r="C10" t="n">
-        <v>1590.2</v>
+        <v>1607.87</v>
       </c>
       <c r="D10" t="n">
-        <v>1510.51</v>
+        <v>1561.97</v>
       </c>
       <c r="E10" t="n">
-        <v>1576.62</v>
+        <v>1571.59</v>
       </c>
       <c r="F10" t="n">
-        <v>11.8</v>
+        <v>-5.03</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0032</v>
       </c>
       <c r="H10" t="n">
-        <v>79.69</v>
+        <v>45.89</v>
       </c>
       <c r="I10" t="n">
-        <v>1406.91</v>
+        <v>1430.81</v>
       </c>
       <c r="J10" t="n">
-        <v>1425.25</v>
+        <v>1510.05</v>
       </c>
       <c r="K10" t="n">
-        <v>1502.38</v>
+        <v>1536.77</v>
       </c>
       <c r="L10" t="n">
-        <v>1579.52</v>
+        <v>1563.48</v>
       </c>
       <c r="M10" t="n">
-        <v>1627.25</v>
+        <v>1616.46</v>
       </c>
       <c r="N10" t="n">
-        <v>1674.98</v>
+        <v>1669.44</v>
       </c>
       <c r="O10" t="n">
-        <v>1781.51</v>
+        <v>1669.89</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1365,9 +1363,9 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1386,57 +1384,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1576.59</v>
+        <v>1571.56</v>
       </c>
       <c r="C11" t="n">
-        <v>1607.87</v>
+        <v>1585.22</v>
       </c>
       <c r="D11" t="n">
-        <v>1561.97</v>
+        <v>1548.76</v>
       </c>
       <c r="E11" t="n">
-        <v>1571.59</v>
+        <v>1570.36</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.03</v>
+        <v>-1.23</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.0008</v>
       </c>
       <c r="H11" t="n">
-        <v>45.89</v>
+        <v>36.46</v>
       </c>
       <c r="I11" t="n">
-        <v>1430.81</v>
+        <v>1516.08</v>
       </c>
       <c r="J11" t="n">
-        <v>1510.05</v>
+        <v>1519.03</v>
       </c>
       <c r="K11" t="n">
-        <v>1536.77</v>
+        <v>1548.64</v>
       </c>
       <c r="L11" t="n">
-        <v>1563.48</v>
+        <v>1578.25</v>
       </c>
       <c r="M11" t="n">
-        <v>1616.46</v>
+        <v>1594.53</v>
       </c>
       <c r="N11" t="n">
-        <v>1669.44</v>
+        <v>1610.82</v>
       </c>
       <c r="O11" t="n">
-        <v>1669.89</v>
+        <v>1653.76</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1447,9 +1445,9 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1468,57 +1466,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1571.56</v>
+        <v>1569.99</v>
       </c>
       <c r="C12" t="n">
-        <v>1585.22</v>
+        <v>1633.65</v>
       </c>
       <c r="D12" t="n">
-        <v>1548.76</v>
+        <v>1550.04</v>
       </c>
       <c r="E12" t="n">
-        <v>1570.36</v>
+        <v>1610.21</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.23</v>
+        <v>39.84</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0254</v>
       </c>
       <c r="H12" t="n">
-        <v>36.46</v>
+        <v>83.61</v>
       </c>
       <c r="I12" t="n">
-        <v>1516.08</v>
+        <v>1512.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1519.03</v>
+        <v>1535.59</v>
       </c>
       <c r="K12" t="n">
-        <v>1548.64</v>
+        <v>1552.13</v>
       </c>
       <c r="L12" t="n">
-        <v>1578.25</v>
+        <v>1568.68</v>
       </c>
       <c r="M12" t="n">
-        <v>1594.53</v>
+        <v>1588.59</v>
       </c>
       <c r="N12" t="n">
-        <v>1610.82</v>
+        <v>1608.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1653.76</v>
+        <v>1621.68</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1526,81 +1524,85 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1569.99</v>
+        <v>1610.16</v>
       </c>
       <c r="C13" t="n">
-        <v>1633.65</v>
+        <v>1611.35</v>
       </c>
       <c r="D13" t="n">
-        <v>1550.04</v>
+        <v>1549.25</v>
       </c>
       <c r="E13" t="n">
-        <v>1610.21</v>
+        <v>1569.58</v>
       </c>
       <c r="F13" t="n">
-        <v>39.84</v>
+        <v>-40.62</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0254</v>
+        <v>-0.0252</v>
       </c>
       <c r="H13" t="n">
-        <v>83.61</v>
+        <v>62.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1512.3</v>
+        <v>1466.43</v>
       </c>
       <c r="J13" t="n">
-        <v>1535.59</v>
+        <v>1535.78</v>
       </c>
       <c r="K13" t="n">
-        <v>1552.13</v>
+        <v>1568.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1568.68</v>
+        <v>1601.02</v>
       </c>
       <c r="M13" t="n">
-        <v>1588.59</v>
+        <v>1652.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1608.5</v>
+        <v>1703</v>
       </c>
       <c r="O13" t="n">
-        <v>1621.68</v>
+        <v>1717.25</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1610,83 +1612,81 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1610.16</v>
+        <v>1569.91</v>
       </c>
       <c r="C14" t="n">
-        <v>1611.35</v>
+        <v>1642.45</v>
       </c>
       <c r="D14" t="n">
-        <v>1549.25</v>
+        <v>1551.14</v>
       </c>
       <c r="E14" t="n">
-        <v>1569.58</v>
+        <v>1608.96</v>
       </c>
       <c r="F14" t="n">
-        <v>-40.62</v>
+        <v>39.38</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0252</v>
+        <v>0.0251</v>
       </c>
       <c r="H14" t="n">
-        <v>62.1</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1466.43</v>
+        <v>1487.16</v>
       </c>
       <c r="J14" t="n">
-        <v>1535.78</v>
+        <v>1502.13</v>
       </c>
       <c r="K14" t="n">
-        <v>1568.4</v>
+        <v>1538.54</v>
       </c>
       <c r="L14" t="n">
-        <v>1601.02</v>
+        <v>1574.94</v>
       </c>
       <c r="M14" t="n">
-        <v>1652.01</v>
+        <v>1600.63</v>
       </c>
       <c r="N14" t="n">
-        <v>1703</v>
+        <v>1626.32</v>
       </c>
       <c r="O14" t="n">
-        <v>1717.25</v>
+        <v>1673.44</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,21 +1694,23 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1718,59 +1720,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1569.91</v>
+        <v>1609.01</v>
       </c>
       <c r="C15" t="n">
-        <v>1642.45</v>
+        <v>1720.34</v>
       </c>
       <c r="D15" t="n">
-        <v>1551.14</v>
+        <v>1595.94</v>
       </c>
       <c r="E15" t="n">
-        <v>1608.96</v>
+        <v>1698.17</v>
       </c>
       <c r="F15" t="n">
-        <v>39.38</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0554</v>
       </c>
       <c r="H15" t="n">
-        <v>91.31999999999999</v>
+        <v>124.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1487.16</v>
+        <v>1459.82</v>
       </c>
       <c r="J15" t="n">
-        <v>1502.13</v>
+        <v>1523.73</v>
       </c>
       <c r="K15" t="n">
-        <v>1538.54</v>
+        <v>1563.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1574.94</v>
+        <v>1602.88</v>
       </c>
       <c r="M15" t="n">
-        <v>1600.63</v>
+        <v>1654.62</v>
       </c>
       <c r="N15" t="n">
-        <v>1626.32</v>
+        <v>1706.36</v>
       </c>
       <c r="O15" t="n">
-        <v>1673.44</v>
+        <v>1733.77</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1788,12 +1786,12 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V15" s="8" t="n">
@@ -1809,50 +1807,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1609.01</v>
+        <v>1698.42</v>
       </c>
       <c r="C16" t="n">
-        <v>1720.34</v>
+        <v>1772.54</v>
       </c>
       <c r="D16" t="n">
-        <v>1595.94</v>
+        <v>1693.04</v>
       </c>
       <c r="E16" t="n">
-        <v>1698.17</v>
+        <v>1756.52</v>
       </c>
       <c r="F16" t="n">
-        <v>89.20999999999999</v>
+        <v>58.35</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0344</v>
       </c>
       <c r="H16" t="n">
-        <v>124.4</v>
+        <v>79.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1459.82</v>
+        <v>1471.54</v>
       </c>
       <c r="J16" t="n">
-        <v>1523.73</v>
+        <v>1593.78</v>
       </c>
       <c r="K16" t="n">
-        <v>1563.3</v>
+        <v>1635.97</v>
       </c>
       <c r="L16" t="n">
-        <v>1602.88</v>
+        <v>1678.16</v>
       </c>
       <c r="M16" t="n">
-        <v>1654.62</v>
+        <v>1760.37</v>
       </c>
       <c r="N16" t="n">
-        <v>1706.36</v>
+        <v>1842.59</v>
       </c>
       <c r="O16" t="n">
-        <v>1733.77</v>
+        <v>1844.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1870,13 +1868,11 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1891,50 +1887,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1698.42</v>
+        <v>1756.58</v>
       </c>
       <c r="C17" t="n">
-        <v>1772.54</v>
+        <v>1804.59</v>
       </c>
       <c r="D17" t="n">
-        <v>1693.04</v>
+        <v>1743.56</v>
       </c>
       <c r="E17" t="n">
-        <v>1756.52</v>
+        <v>1779.03</v>
       </c>
       <c r="F17" t="n">
-        <v>58.35</v>
+        <v>22.51</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0128</v>
       </c>
       <c r="H17" t="n">
-        <v>79.5</v>
+        <v>61.02</v>
       </c>
       <c r="I17" t="n">
-        <v>1471.54</v>
+        <v>1613.53</v>
       </c>
       <c r="J17" t="n">
-        <v>1593.78</v>
+        <v>1688.88</v>
       </c>
       <c r="K17" t="n">
-        <v>1635.97</v>
+        <v>1716.77</v>
       </c>
       <c r="L17" t="n">
-        <v>1678.16</v>
+        <v>1744.65</v>
       </c>
       <c r="M17" t="n">
-        <v>1760.37</v>
+        <v>1796.27</v>
       </c>
       <c r="N17" t="n">
-        <v>1842.59</v>
+        <v>1847.89</v>
       </c>
       <c r="O17" t="n">
-        <v>1844.75</v>
+        <v>1852.05</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1971,50 +1967,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1756.58</v>
+        <v>1779.04</v>
       </c>
       <c r="C18" t="n">
-        <v>1804.59</v>
+        <v>1805.91</v>
       </c>
       <c r="D18" t="n">
-        <v>1743.56</v>
+        <v>1749.14</v>
       </c>
       <c r="E18" t="n">
-        <v>1779.03</v>
+        <v>1783.01</v>
       </c>
       <c r="F18" t="n">
-        <v>22.51</v>
+        <v>3.97</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0022</v>
       </c>
       <c r="H18" t="n">
-        <v>61.02</v>
+        <v>56.78</v>
       </c>
       <c r="I18" t="n">
-        <v>1613.53</v>
+        <v>1682.54</v>
       </c>
       <c r="J18" t="n">
-        <v>1688.88</v>
+        <v>1720.49</v>
       </c>
       <c r="K18" t="n">
-        <v>1716.77</v>
+        <v>1748.52</v>
       </c>
       <c r="L18" t="n">
-        <v>1744.65</v>
+        <v>1776.55</v>
       </c>
       <c r="M18" t="n">
-        <v>1796.27</v>
+        <v>1809.55</v>
       </c>
       <c r="N18" t="n">
-        <v>1847.89</v>
+        <v>1842.54</v>
       </c>
       <c r="O18" t="n">
-        <v>1852.05</v>
+        <v>1865.61</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2027,13 +2023,11 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2051,67 +2045,73 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779.04</v>
+        <v>1783</v>
       </c>
       <c r="C19" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D19" t="n">
-        <v>1749.14</v>
+        <v>1728.97</v>
       </c>
       <c r="E19" t="n">
-        <v>1783.01</v>
+        <v>1797.57</v>
       </c>
       <c r="F19" t="n">
-        <v>3.97</v>
+        <v>14.57</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>56.78</v>
+        <v>100.55</v>
       </c>
       <c r="I19" t="n">
-        <v>1682.54</v>
+        <v>1692.36</v>
       </c>
       <c r="J19" t="n">
-        <v>1720.49</v>
+        <v>1728.97</v>
       </c>
       <c r="K19" t="n">
-        <v>1748.52</v>
+        <v>1754.62</v>
       </c>
       <c r="L19" t="n">
-        <v>1776.55</v>
+        <v>1780.27</v>
       </c>
       <c r="M19" t="n">
-        <v>1809.55</v>
+        <v>1811.39</v>
       </c>
       <c r="N19" t="n">
-        <v>1842.54</v>
+        <v>1842.52</v>
       </c>
       <c r="O19" t="n">
-        <v>1865.61</v>
+        <v>1862.69</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2124,78 +2124,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1783</v>
+        <v>1797.56</v>
       </c>
       <c r="C20" t="n">
-        <v>1829.51</v>
+        <v>1810.33</v>
       </c>
       <c r="D20" t="n">
-        <v>1728.97</v>
+        <v>1756.71</v>
       </c>
       <c r="E20" t="n">
-        <v>1797.57</v>
+        <v>1768.51</v>
       </c>
       <c r="F20" t="n">
-        <v>14.57</v>
+        <v>-29.06</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0162</v>
       </c>
       <c r="H20" t="n">
-        <v>100.55</v>
+        <v>53.62</v>
       </c>
       <c r="I20" t="n">
-        <v>1692.36</v>
+        <v>1628.42</v>
       </c>
       <c r="J20" t="n">
-        <v>1728.97</v>
+        <v>1706.19</v>
       </c>
       <c r="K20" t="n">
-        <v>1754.62</v>
+        <v>1747.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1780.27</v>
+        <v>1788.41</v>
       </c>
       <c r="M20" t="n">
-        <v>1811.39</v>
+        <v>1847.85</v>
       </c>
       <c r="N20" t="n">
-        <v>1842.52</v>
+        <v>1907.29</v>
       </c>
       <c r="O20" t="n">
-        <v>1862.69</v>
+        <v>1930.06</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2210,57 +2208,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1797.56</v>
+        <v>1768.39</v>
       </c>
       <c r="C21" t="n">
-        <v>1810.33</v>
+        <v>1782.86</v>
       </c>
       <c r="D21" t="n">
-        <v>1756.71</v>
+        <v>1711.9</v>
       </c>
       <c r="E21" t="n">
-        <v>1768.51</v>
+        <v>1742.68</v>
       </c>
       <c r="F21" t="n">
-        <v>-29.06</v>
+        <v>-25.83</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0146</v>
       </c>
       <c r="H21" t="n">
-        <v>53.62</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>1628.42</v>
+        <v>1703.1</v>
       </c>
       <c r="J21" t="n">
-        <v>1706.19</v>
+        <v>1707.39</v>
       </c>
       <c r="K21" t="n">
-        <v>1747.3</v>
+        <v>1741.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1788.41</v>
+        <v>1776.02</v>
       </c>
       <c r="M21" t="n">
-        <v>1847.85</v>
+        <v>1795.32</v>
       </c>
       <c r="N21" t="n">
-        <v>1907.29</v>
+        <v>1814.62</v>
       </c>
       <c r="O21" t="n">
-        <v>1930.06</v>
+        <v>1863.95</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2268,12 +2266,14 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2292,57 +2292,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1768.39</v>
+        <v>1742.66</v>
       </c>
       <c r="C22" t="n">
-        <v>1782.86</v>
+        <v>1760.21</v>
       </c>
       <c r="D22" t="n">
-        <v>1711.9</v>
+        <v>1721.3</v>
       </c>
       <c r="E22" t="n">
-        <v>1742.68</v>
+        <v>1744.48</v>
       </c>
       <c r="F22" t="n">
-        <v>-25.83</v>
+        <v>1.81</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>70.95999999999999</v>
+        <v>38.91</v>
       </c>
       <c r="I22" t="n">
-        <v>1703.1</v>
+        <v>1640.94</v>
       </c>
       <c r="J22" t="n">
-        <v>1707.39</v>
+        <v>1669.37</v>
       </c>
       <c r="K22" t="n">
-        <v>1741.7</v>
+        <v>1707.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1776.02</v>
+        <v>1745.03</v>
       </c>
       <c r="M22" t="n">
-        <v>1795.32</v>
+        <v>1778.16</v>
       </c>
       <c r="N22" t="n">
-        <v>1814.62</v>
+        <v>1811.29</v>
       </c>
       <c r="O22" t="n">
-        <v>1863.95</v>
+        <v>1853.82</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2350,14 +2350,12 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2376,57 +2374,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1742.66</v>
+        <v>1744.47</v>
       </c>
       <c r="C23" t="n">
-        <v>1760.21</v>
+        <v>1809.76</v>
       </c>
       <c r="D23" t="n">
-        <v>1721.3</v>
+        <v>1736.72</v>
       </c>
       <c r="E23" t="n">
-        <v>1744.48</v>
+        <v>1795.69</v>
       </c>
       <c r="F23" t="n">
-        <v>1.81</v>
+        <v>51.21</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0294</v>
       </c>
       <c r="H23" t="n">
-        <v>38.91</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1640.94</v>
+        <v>1682.39</v>
       </c>
       <c r="J23" t="n">
-        <v>1669.37</v>
+        <v>1707.44</v>
       </c>
       <c r="K23" t="n">
-        <v>1707.2</v>
+        <v>1725.03</v>
       </c>
       <c r="L23" t="n">
-        <v>1745.03</v>
+        <v>1742.62</v>
       </c>
       <c r="M23" t="n">
-        <v>1778.16</v>
+        <v>1763.94</v>
       </c>
       <c r="N23" t="n">
-        <v>1811.29</v>
+        <v>1785.26</v>
       </c>
       <c r="O23" t="n">
-        <v>1853.82</v>
+        <v>1799.11</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2437,78 +2435,80 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1744.47</v>
+        <v>1795.82</v>
       </c>
       <c r="C24" t="n">
-        <v>1809.76</v>
+        <v>1827.83</v>
       </c>
       <c r="D24" t="n">
-        <v>1736.72</v>
+        <v>1786.3</v>
       </c>
       <c r="E24" t="n">
-        <v>1795.69</v>
+        <v>1788.1</v>
       </c>
       <c r="F24" t="n">
-        <v>51.21</v>
+        <v>-7.59</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0294</v>
+        <v>-0.0042</v>
       </c>
       <c r="H24" t="n">
-        <v>73.04000000000001</v>
+        <v>41.54</v>
       </c>
       <c r="I24" t="n">
-        <v>1682.39</v>
+        <v>1663.69</v>
       </c>
       <c r="J24" t="n">
-        <v>1707.44</v>
+        <v>1733.88</v>
       </c>
       <c r="K24" t="n">
-        <v>1725.03</v>
+        <v>1759.18</v>
       </c>
       <c r="L24" t="n">
-        <v>1742.62</v>
+        <v>1784.47</v>
       </c>
       <c r="M24" t="n">
-        <v>1763.94</v>
+        <v>1832.21</v>
       </c>
       <c r="N24" t="n">
-        <v>1785.26</v>
+        <v>1879.95</v>
       </c>
       <c r="O24" t="n">
-        <v>1799.11</v>
+        <v>1882.79</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2521,78 +2521,76 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1795.82</v>
+        <v>1787.57</v>
       </c>
       <c r="C25" t="n">
-        <v>1827.83</v>
+        <v>1824.98</v>
       </c>
       <c r="D25" t="n">
-        <v>1786.3</v>
+        <v>1779.64</v>
       </c>
       <c r="E25" t="n">
-        <v>1788.1</v>
+        <v>1805.79</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.59</v>
+        <v>17.69</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>41.54</v>
+        <v>45.34</v>
       </c>
       <c r="I25" t="n">
-        <v>1663.69</v>
+        <v>1744.76</v>
       </c>
       <c r="J25" t="n">
-        <v>1733.88</v>
+        <v>1737.08</v>
       </c>
       <c r="K25" t="n">
-        <v>1759.18</v>
+        <v>1767.33</v>
       </c>
       <c r="L25" t="n">
-        <v>1784.47</v>
+        <v>1797.58</v>
       </c>
       <c r="M25" t="n">
-        <v>1832.21</v>
+        <v>1808.87</v>
       </c>
       <c r="N25" t="n">
-        <v>1879.95</v>
+        <v>1820.15</v>
       </c>
       <c r="O25" t="n">
-        <v>1882.79</v>
+        <v>1869.37</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,14 +2603,18 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2624,81 +2626,83 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1787.57</v>
+        <v>1805.76</v>
       </c>
       <c r="C26" t="n">
-        <v>1824.98</v>
+        <v>1842.46</v>
       </c>
       <c r="D26" t="n">
-        <v>1779.64</v>
+        <v>1749.35</v>
       </c>
       <c r="E26" t="n">
-        <v>1805.79</v>
+        <v>1773.5</v>
       </c>
       <c r="F26" t="n">
-        <v>17.69</v>
+        <v>-32.29</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.0179</v>
       </c>
       <c r="H26" t="n">
-        <v>45.34</v>
+        <v>93.11</v>
       </c>
       <c r="I26" t="n">
-        <v>1744.76</v>
+        <v>1734.29</v>
       </c>
       <c r="J26" t="n">
-        <v>1737.08</v>
+        <v>1762.18</v>
       </c>
       <c r="K26" t="n">
-        <v>1767.33</v>
+        <v>1783.12</v>
       </c>
       <c r="L26" t="n">
-        <v>1797.58</v>
+        <v>1804.05</v>
       </c>
       <c r="M26" t="n">
-        <v>1808.87</v>
+        <v>1828.46</v>
       </c>
       <c r="N26" t="n">
-        <v>1820.15</v>
+        <v>1852.87</v>
       </c>
       <c r="O26" t="n">
-        <v>1869.37</v>
+        <v>1870.32</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2717,77 +2721,75 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1805.76</v>
+        <v>1773.47</v>
       </c>
       <c r="C27" t="n">
-        <v>1842.46</v>
+        <v>1894.06</v>
       </c>
       <c r="D27" t="n">
-        <v>1749.35</v>
+        <v>1772.02</v>
       </c>
       <c r="E27" t="n">
-        <v>1773.5</v>
+        <v>1889.48</v>
       </c>
       <c r="F27" t="n">
-        <v>-32.29</v>
+        <v>115.98</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0654</v>
       </c>
       <c r="H27" t="n">
-        <v>93.11</v>
+        <v>122.04</v>
       </c>
       <c r="I27" t="n">
-        <v>1734.29</v>
+        <v>1656.24</v>
       </c>
       <c r="J27" t="n">
-        <v>1762.18</v>
+        <v>1669.19</v>
       </c>
       <c r="K27" t="n">
-        <v>1783.12</v>
+        <v>1726.95</v>
       </c>
       <c r="L27" t="n">
-        <v>1804.05</v>
+        <v>1784.7</v>
       </c>
       <c r="M27" t="n">
-        <v>1828.46</v>
+        <v>1820.05</v>
       </c>
       <c r="N27" t="n">
-        <v>1852.87</v>
+        <v>1855.41</v>
       </c>
       <c r="O27" t="n">
-        <v>1870.32</v>
+        <v>1935.56</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
@@ -2796,59 +2798,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1773.47</v>
+        <v>1889.5</v>
       </c>
       <c r="C28" t="n">
-        <v>1894.06</v>
+        <v>1944.16</v>
       </c>
       <c r="D28" t="n">
-        <v>1772.02</v>
+        <v>1863.64</v>
       </c>
       <c r="E28" t="n">
-        <v>1889.48</v>
+        <v>1916.94</v>
       </c>
       <c r="F28" t="n">
-        <v>115.98</v>
+        <v>27.46</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0654</v>
+        <v>0.0145</v>
       </c>
       <c r="H28" t="n">
-        <v>122.04</v>
+        <v>80.53</v>
       </c>
       <c r="I28" t="n">
-        <v>1656.24</v>
+        <v>1649.97</v>
       </c>
       <c r="J28" t="n">
-        <v>1669.19</v>
+        <v>1795.66</v>
       </c>
       <c r="K28" t="n">
-        <v>1726.95</v>
+        <v>1828.46</v>
       </c>
       <c r="L28" t="n">
-        <v>1784.7</v>
+        <v>1861.26</v>
       </c>
       <c r="M28" t="n">
-        <v>1820.05</v>
+        <v>1950.5</v>
       </c>
       <c r="N28" t="n">
-        <v>1855.41</v>
+        <v>2039.74</v>
       </c>
       <c r="O28" t="n">
-        <v>1935.56</v>
+        <v>2016.11</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2866,13 +2864,11 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2887,50 +2883,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1889.5</v>
+        <v>1916.98</v>
       </c>
       <c r="C29" t="n">
-        <v>1944.16</v>
+        <v>1927.09</v>
       </c>
       <c r="D29" t="n">
-        <v>1863.64</v>
+        <v>1856.78</v>
       </c>
       <c r="E29" t="n">
-        <v>1916.94</v>
+        <v>1863.19</v>
       </c>
       <c r="F29" t="n">
-        <v>27.46</v>
+        <v>-53.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0145</v>
+        <v>-0.028</v>
       </c>
       <c r="H29" t="n">
-        <v>80.53</v>
+        <v>70.31</v>
       </c>
       <c r="I29" t="n">
-        <v>1649.97</v>
+        <v>1783.11</v>
       </c>
       <c r="J29" t="n">
-        <v>1795.66</v>
+        <v>1842.94</v>
       </c>
       <c r="K29" t="n">
-        <v>1828.46</v>
+        <v>1876.68</v>
       </c>
       <c r="L29" t="n">
-        <v>1861.26</v>
+        <v>1910.42</v>
       </c>
       <c r="M29" t="n">
-        <v>1950.5</v>
+        <v>1957.21</v>
       </c>
       <c r="N29" t="n">
-        <v>2039.74</v>
+        <v>2003.99</v>
       </c>
       <c r="O29" t="n">
-        <v>2016.11</v>
+        <v>2024.69</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2938,19 +2934,19 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2962,55 +2958,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1916.98</v>
+        <v>1863.22</v>
       </c>
       <c r="C30" t="n">
-        <v>1927.09</v>
+        <v>1869.07</v>
       </c>
       <c r="D30" t="n">
-        <v>1856.78</v>
+        <v>1803.05</v>
       </c>
       <c r="E30" t="n">
-        <v>1863.19</v>
+        <v>1840.99</v>
       </c>
       <c r="F30" t="n">
-        <v>-53.75</v>
+        <v>-22.21</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.0119</v>
       </c>
       <c r="H30" t="n">
-        <v>70.31</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>1783.11</v>
+        <v>1786.47</v>
       </c>
       <c r="J30" t="n">
-        <v>1842.94</v>
+        <v>1778.51</v>
       </c>
       <c r="K30" t="n">
-        <v>1876.68</v>
+        <v>1828.04</v>
       </c>
       <c r="L30" t="n">
-        <v>1910.42</v>
+        <v>1877.56</v>
       </c>
       <c r="M30" t="n">
-        <v>1957.21</v>
+        <v>1898.35</v>
       </c>
       <c r="N30" t="n">
-        <v>2003.99</v>
+        <v>1919.13</v>
       </c>
       <c r="O30" t="n">
-        <v>2024.69</v>
+        <v>1997.4</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3051,50 +3051,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1863.22</v>
+        <v>1841.1</v>
       </c>
       <c r="C31" t="n">
-        <v>1869.07</v>
+        <v>1864.13</v>
       </c>
       <c r="D31" t="n">
-        <v>1803.05</v>
+        <v>1836.61</v>
       </c>
       <c r="E31" t="n">
-        <v>1840.99</v>
+        <v>1861.39</v>
       </c>
       <c r="F31" t="n">
-        <v>-22.21</v>
+        <v>20.4</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0111</v>
       </c>
       <c r="H31" t="n">
-        <v>66.01000000000001</v>
+        <v>27.52</v>
       </c>
       <c r="I31" t="n">
-        <v>1786.47</v>
+        <v>1737.04</v>
       </c>
       <c r="J31" t="n">
-        <v>1778.51</v>
+        <v>1777.44</v>
       </c>
       <c r="K31" t="n">
-        <v>1828.04</v>
+        <v>1807.98</v>
       </c>
       <c r="L31" t="n">
-        <v>1877.56</v>
+        <v>1838.52</v>
       </c>
       <c r="M31" t="n">
-        <v>1898.35</v>
+        <v>1873.99</v>
       </c>
       <c r="N31" t="n">
-        <v>1919.13</v>
+        <v>1909.47</v>
       </c>
       <c r="O31" t="n">
-        <v>1997.4</v>
+        <v>1935.08</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3102,19 +3102,19 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3128,57 +3128,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1841.1</v>
+        <v>1861.42</v>
       </c>
       <c r="C32" t="n">
-        <v>1864.13</v>
+        <v>1877.03</v>
       </c>
       <c r="D32" t="n">
-        <v>1836.61</v>
+        <v>1852.73</v>
       </c>
       <c r="E32" t="n">
-        <v>1861.39</v>
+        <v>1871.51</v>
       </c>
       <c r="F32" t="n">
-        <v>20.4</v>
+        <v>10.12</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0054</v>
       </c>
       <c r="H32" t="n">
-        <v>27.52</v>
+        <v>24.3</v>
       </c>
       <c r="I32" t="n">
-        <v>1737.04</v>
+        <v>1809.09</v>
       </c>
       <c r="J32" t="n">
-        <v>1777.44</v>
+        <v>1839.38</v>
       </c>
       <c r="K32" t="n">
-        <v>1807.98</v>
+        <v>1847.63</v>
       </c>
       <c r="L32" t="n">
-        <v>1838.52</v>
+        <v>1855.88</v>
       </c>
       <c r="M32" t="n">
-        <v>1873.99</v>
+        <v>1875.15</v>
       </c>
       <c r="N32" t="n">
-        <v>1909.47</v>
+        <v>1894.43</v>
       </c>
       <c r="O32" t="n">
-        <v>1935.08</v>
+        <v>1891.66</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3210,68 +3210,68 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1861.42</v>
+        <v>1871.28</v>
       </c>
       <c r="C33" t="n">
-        <v>1877.03</v>
+        <v>1916.24</v>
       </c>
       <c r="D33" t="n">
-        <v>1852.73</v>
+        <v>1842.82</v>
       </c>
       <c r="E33" t="n">
-        <v>1871.51</v>
+        <v>1903.76</v>
       </c>
       <c r="F33" t="n">
-        <v>10.12</v>
+        <v>32.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0172</v>
       </c>
       <c r="H33" t="n">
-        <v>24.3</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>1809.09</v>
+        <v>1828.42</v>
       </c>
       <c r="J33" t="n">
-        <v>1839.38</v>
+        <v>1850.52</v>
       </c>
       <c r="K33" t="n">
-        <v>1847.63</v>
+        <v>1859.36</v>
       </c>
       <c r="L33" t="n">
-        <v>1855.88</v>
+        <v>1868.19</v>
       </c>
       <c r="M33" t="n">
-        <v>1875.15</v>
+        <v>1883.66</v>
       </c>
       <c r="N33" t="n">
-        <v>1894.43</v>
+        <v>1899.13</v>
       </c>
       <c r="O33" t="n">
-        <v>1891.66</v>
+        <v>1901.34</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
@@ -3280,82 +3280,86 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1871.28</v>
+        <v>1903.69</v>
       </c>
       <c r="C34" t="n">
-        <v>1916.24</v>
+        <v>1949.55</v>
       </c>
       <c r="D34" t="n">
-        <v>1842.82</v>
+        <v>1900.07</v>
       </c>
       <c r="E34" t="n">
-        <v>1903.76</v>
+        <v>1928.38</v>
       </c>
       <c r="F34" t="n">
-        <v>32.25</v>
+        <v>24.62</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0129</v>
       </c>
       <c r="H34" t="n">
-        <v>73.43000000000001</v>
+        <v>49.48</v>
       </c>
       <c r="I34" t="n">
-        <v>1828.42</v>
+        <v>1769.39</v>
       </c>
       <c r="J34" t="n">
-        <v>1850.52</v>
+        <v>1842.45</v>
       </c>
       <c r="K34" t="n">
-        <v>1859.36</v>
+        <v>1867.05</v>
       </c>
       <c r="L34" t="n">
-        <v>1868.19</v>
+        <v>1891.64</v>
       </c>
       <c r="M34" t="n">
-        <v>1883.66</v>
+        <v>1940.47</v>
       </c>
       <c r="N34" t="n">
-        <v>1899.13</v>
+        <v>1989.3</v>
       </c>
       <c r="O34" t="n">
-        <v>1901.34</v>
+        <v>1989.67</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
@@ -3364,77 +3368,69 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1903.69</v>
+        <v>1928.2</v>
       </c>
       <c r="C35" t="n">
-        <v>1949.55</v>
+        <v>1955.15</v>
       </c>
       <c r="D35" t="n">
-        <v>1900.07</v>
+        <v>1909.61</v>
       </c>
       <c r="E35" t="n">
-        <v>1928.38</v>
+        <v>1933.49</v>
       </c>
       <c r="F35" t="n">
-        <v>24.62</v>
+        <v>5.11</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0026</v>
       </c>
       <c r="H35" t="n">
-        <v>49.48</v>
+        <v>45.54</v>
       </c>
       <c r="I35" t="n">
-        <v>1769.39</v>
+        <v>1850.58</v>
       </c>
       <c r="J35" t="n">
-        <v>1842.45</v>
+        <v>1880.69</v>
       </c>
       <c r="K35" t="n">
-        <v>1867.05</v>
+        <v>1903.64</v>
       </c>
       <c r="L35" t="n">
-        <v>1891.64</v>
+        <v>1926.6</v>
       </c>
       <c r="M35" t="n">
-        <v>1940.47</v>
+        <v>1953.12</v>
       </c>
       <c r="N35" t="n">
-        <v>1989.3</v>
+        <v>1979.65</v>
       </c>
       <c r="O35" t="n">
-        <v>1989.67</v>
+        <v>1999.03</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3447,12 +3443,12 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U35" s="8" t="n">
@@ -3471,79 +3467,81 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1928.2</v>
+        <v>1933.47</v>
       </c>
       <c r="C36" t="n">
-        <v>1955.15</v>
+        <v>1940.28</v>
       </c>
       <c r="D36" t="n">
-        <v>1909.61</v>
+        <v>1868.52</v>
       </c>
       <c r="E36" t="n">
-        <v>1933.49</v>
+        <v>1877.1</v>
       </c>
       <c r="F36" t="n">
-        <v>5.11</v>
+        <v>-56.39</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0292</v>
       </c>
       <c r="H36" t="n">
-        <v>45.54</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>1850.58</v>
+        <v>1864.07</v>
       </c>
       <c r="J36" t="n">
-        <v>1880.69</v>
+        <v>1888.51</v>
       </c>
       <c r="K36" t="n">
-        <v>1903.64</v>
+        <v>1910.72</v>
       </c>
       <c r="L36" t="n">
-        <v>1926.6</v>
+        <v>1932.93</v>
       </c>
       <c r="M36" t="n">
-        <v>1953.12</v>
+        <v>1956.26</v>
       </c>
       <c r="N36" t="n">
-        <v>1979.65</v>
+        <v>1979.58</v>
       </c>
       <c r="O36" t="n">
-        <v>1999.03</v>
+        <v>2000.68</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3551,62 +3549,60 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1933.47</v>
+        <v>1877.1</v>
       </c>
       <c r="C37" t="n">
-        <v>1940.28</v>
+        <v>1907.54</v>
       </c>
       <c r="D37" t="n">
-        <v>1868.52</v>
+        <v>1846.82</v>
       </c>
       <c r="E37" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="F37" t="n">
-        <v>-56.39</v>
+        <v>-16.92</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0292</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>71.76000000000001</v>
+        <v>60.72</v>
       </c>
       <c r="I37" t="n">
-        <v>1864.07</v>
+        <v>1796.76</v>
       </c>
       <c r="J37" t="n">
-        <v>1888.51</v>
+        <v>1791.69</v>
       </c>
       <c r="K37" t="n">
-        <v>1910.72</v>
+        <v>1841.22</v>
       </c>
       <c r="L37" t="n">
-        <v>1932.93</v>
+        <v>1890.75</v>
       </c>
       <c r="M37" t="n">
-        <v>1956.26</v>
+        <v>1912.98</v>
       </c>
       <c r="N37" t="n">
-        <v>1979.58</v>
+        <v>1935.21</v>
       </c>
       <c r="O37" t="n">
-        <v>2000.68</v>
+        <v>2012.05</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
@@ -3633,50 +3629,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="C38" t="n">
-        <v>1907.54</v>
+        <v>1875.14</v>
       </c>
       <c r="D38" t="n">
-        <v>1846.82</v>
+        <v>1849.83</v>
       </c>
       <c r="E38" t="n">
-        <v>1860.18</v>
+        <v>1873.22</v>
       </c>
       <c r="F38" t="n">
-        <v>-16.92</v>
+        <v>13.05</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H38" t="n">
-        <v>60.72</v>
+        <v>25.32</v>
       </c>
       <c r="I38" t="n">
-        <v>1796.76</v>
+        <v>1786.1</v>
       </c>
       <c r="J38" t="n">
-        <v>1791.69</v>
+        <v>1790.95</v>
       </c>
       <c r="K38" t="n">
-        <v>1841.22</v>
+        <v>1829.82</v>
       </c>
       <c r="L38" t="n">
-        <v>1890.75</v>
+        <v>1868.68</v>
       </c>
       <c r="M38" t="n">
-        <v>1912.98</v>
+        <v>1890.54</v>
       </c>
       <c r="N38" t="n">
-        <v>1935.21</v>
+        <v>1912.39</v>
       </c>
       <c r="O38" t="n">
-        <v>2012.05</v>
+        <v>1968.26</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3684,14 +3680,12 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3708,55 +3702,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1860.18</v>
+        <v>1873.24</v>
       </c>
       <c r="C39" t="n">
-        <v>1875.14</v>
+        <v>1963.25</v>
       </c>
       <c r="D39" t="n">
-        <v>1849.83</v>
+        <v>1872.38</v>
       </c>
       <c r="E39" t="n">
-        <v>1873.22</v>
+        <v>1953.41</v>
       </c>
       <c r="F39" t="n">
-        <v>13.05</v>
+        <v>80.19</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0428</v>
       </c>
       <c r="H39" t="n">
-        <v>25.32</v>
+        <v>90.86</v>
       </c>
       <c r="I39" t="n">
-        <v>1786.1</v>
+        <v>1824.51</v>
       </c>
       <c r="J39" t="n">
-        <v>1790.95</v>
+        <v>1853.27</v>
       </c>
       <c r="K39" t="n">
-        <v>1829.82</v>
+        <v>1860.56</v>
       </c>
       <c r="L39" t="n">
-        <v>1868.68</v>
+        <v>1867.85</v>
       </c>
       <c r="M39" t="n">
-        <v>1890.54</v>
+        <v>1885.88</v>
       </c>
       <c r="N39" t="n">
-        <v>1912.39</v>
+        <v>1903.91</v>
       </c>
       <c r="O39" t="n">
-        <v>1968.26</v>
+        <v>1900.46</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3769,177 +3767,177 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W39" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W39" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1873.24</v>
+        <v>1953.41</v>
       </c>
       <c r="C40" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D40" t="n">
-        <v>1872.38</v>
+        <v>1882.42</v>
       </c>
       <c r="E40" t="n">
-        <v>1953.41</v>
+        <v>1890.61</v>
       </c>
       <c r="F40" t="n">
-        <v>80.19</v>
+        <v>-62.8</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0428</v>
+        <v>-0.0321</v>
       </c>
       <c r="H40" t="n">
-        <v>90.86</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>1824.51</v>
+        <v>1781.52</v>
       </c>
       <c r="J40" t="n">
-        <v>1853.27</v>
+        <v>1880.35</v>
       </c>
       <c r="K40" t="n">
-        <v>1860.56</v>
+        <v>1907.98</v>
       </c>
       <c r="L40" t="n">
-        <v>1867.85</v>
+        <v>1935.61</v>
       </c>
       <c r="M40" t="n">
-        <v>1885.88</v>
+        <v>1998.84</v>
       </c>
       <c r="N40" t="n">
-        <v>1903.91</v>
+        <v>2062.07</v>
       </c>
       <c r="O40" t="n">
-        <v>1900.46</v>
+        <v>2054.11</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1953.41</v>
+        <v>1890.63</v>
       </c>
       <c r="C41" t="n">
-        <v>1976.46</v>
+        <v>1926.5</v>
       </c>
       <c r="D41" t="n">
-        <v>1882.42</v>
+        <v>1856.34</v>
       </c>
       <c r="E41" t="n">
-        <v>1890.61</v>
+        <v>1919.95</v>
       </c>
       <c r="F41" t="n">
-        <v>-62.8</v>
+        <v>29.33</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0321</v>
+        <v>0.0155</v>
       </c>
       <c r="H41" t="n">
-        <v>94.04000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="I41" t="n">
-        <v>1781.52</v>
+        <v>1788.38</v>
       </c>
       <c r="J41" t="n">
-        <v>1880.35</v>
+        <v>1777.16</v>
       </c>
       <c r="K41" t="n">
-        <v>1907.98</v>
+        <v>1843.59</v>
       </c>
       <c r="L41" t="n">
-        <v>1935.61</v>
+        <v>1910.03</v>
       </c>
       <c r="M41" t="n">
-        <v>1998.84</v>
+        <v>1937.63</v>
       </c>
       <c r="N41" t="n">
-        <v>2062.07</v>
+        <v>1965.24</v>
       </c>
       <c r="O41" t="n">
-        <v>2054.11</v>
+        <v>2070.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3958,57 +3956,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1890.63</v>
+        <v>1919.99</v>
       </c>
       <c r="C42" t="n">
-        <v>1926.5</v>
+        <v>1929.9</v>
       </c>
       <c r="D42" t="n">
-        <v>1856.34</v>
+        <v>1873.62</v>
       </c>
       <c r="E42" t="n">
-        <v>1919.95</v>
+        <v>1908.52</v>
       </c>
       <c r="F42" t="n">
-        <v>29.33</v>
+        <v>-11.43</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.006</v>
       </c>
       <c r="H42" t="n">
-        <v>70.16</v>
+        <v>56.28</v>
       </c>
       <c r="I42" t="n">
-        <v>1788.38</v>
+        <v>1786.18</v>
       </c>
       <c r="J42" t="n">
-        <v>1777.16</v>
+        <v>1864.05</v>
       </c>
       <c r="K42" t="n">
-        <v>1843.59</v>
+        <v>1884.87</v>
       </c>
       <c r="L42" t="n">
-        <v>1910.03</v>
+        <v>1905.69</v>
       </c>
       <c r="M42" t="n">
-        <v>1937.63</v>
+        <v>1955.03</v>
       </c>
       <c r="N42" t="n">
-        <v>1965.24</v>
+        <v>2004.37</v>
       </c>
       <c r="O42" t="n">
-        <v>2070.5</v>
+        <v>1996.67</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4016,8 +4014,10 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
@@ -4040,57 +4040,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1919.99</v>
+        <v>1908.59</v>
       </c>
       <c r="C43" t="n">
-        <v>1929.9</v>
+        <v>1934.58</v>
       </c>
       <c r="D43" t="n">
-        <v>1873.62</v>
+        <v>1892.2</v>
       </c>
       <c r="E43" t="n">
-        <v>1908.52</v>
+        <v>1917.37</v>
       </c>
       <c r="F43" t="n">
-        <v>-11.43</v>
+        <v>8.85</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0046</v>
       </c>
       <c r="H43" t="n">
-        <v>56.28</v>
+        <v>42.38</v>
       </c>
       <c r="I43" t="n">
-        <v>1786.18</v>
+        <v>1817.34</v>
       </c>
       <c r="J43" t="n">
-        <v>1864.05</v>
+        <v>1855.62</v>
       </c>
       <c r="K43" t="n">
-        <v>1884.87</v>
+        <v>1880.38</v>
       </c>
       <c r="L43" t="n">
-        <v>1905.69</v>
+        <v>1905.14</v>
       </c>
       <c r="M43" t="n">
-        <v>1955.03</v>
+        <v>1936.66</v>
       </c>
       <c r="N43" t="n">
-        <v>2004.37</v>
+        <v>1968.18</v>
       </c>
       <c r="O43" t="n">
-        <v>1996.67</v>
+        <v>1986.18</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4098,10 +4098,8 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
@@ -4122,72 +4120,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1908.59</v>
+        <v>1917.14</v>
       </c>
       <c r="C44" t="n">
-        <v>1934.58</v>
+        <v>1933.78</v>
       </c>
       <c r="D44" t="n">
-        <v>1892.2</v>
+        <v>1847.47</v>
       </c>
       <c r="E44" t="n">
-        <v>1917.37</v>
+        <v>1860.35</v>
       </c>
       <c r="F44" t="n">
-        <v>8.85</v>
+        <v>-57.03</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0297</v>
       </c>
       <c r="H44" t="n">
-        <v>42.38</v>
+        <v>86.31</v>
       </c>
       <c r="I44" t="n">
-        <v>1817.34</v>
+        <v>1849.82</v>
       </c>
       <c r="J44" t="n">
-        <v>1855.62</v>
+        <v>1876.99</v>
       </c>
       <c r="K44" t="n">
-        <v>1880.38</v>
+        <v>1896.18</v>
       </c>
       <c r="L44" t="n">
-        <v>1905.14</v>
+        <v>1915.38</v>
       </c>
       <c r="M44" t="n">
-        <v>1936.66</v>
+        <v>1938.56</v>
       </c>
       <c r="N44" t="n">
-        <v>1968.18</v>
+        <v>1961.75</v>
       </c>
       <c r="O44" t="n">
-        <v>1986.18</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>1976.96</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4199,9 +4199,9 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr"/>
@@ -4209,64 +4209,60 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1917.14</v>
+        <v>1860.37</v>
       </c>
       <c r="C45" t="n">
-        <v>1933.78</v>
+        <v>1873.17</v>
       </c>
       <c r="D45" t="n">
-        <v>1847.47</v>
+        <v>1821.49</v>
       </c>
       <c r="E45" t="n">
-        <v>1860.35</v>
+        <v>1843.42</v>
       </c>
       <c r="F45" t="n">
-        <v>-57.03</v>
+        <v>-16.93</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0297</v>
+        <v>-0.0091</v>
       </c>
       <c r="H45" t="n">
-        <v>86.31</v>
+        <v>51.69</v>
       </c>
       <c r="I45" t="n">
-        <v>1849.82</v>
+        <v>1761.16</v>
       </c>
       <c r="J45" t="n">
-        <v>1876.99</v>
+        <v>1758.9</v>
       </c>
       <c r="K45" t="n">
-        <v>1896.18</v>
+        <v>1817.19</v>
       </c>
       <c r="L45" t="n">
-        <v>1915.38</v>
+        <v>1875.48</v>
       </c>
       <c r="M45" t="n">
-        <v>1938.56</v>
+        <v>1903.5</v>
       </c>
       <c r="N45" t="n">
-        <v>1961.75</v>
+        <v>1931.52</v>
       </c>
       <c r="O45" t="n">
-        <v>1976.96</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
+        <v>2020.09</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
@@ -4293,50 +4289,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1860.37</v>
+        <v>1843.42</v>
       </c>
       <c r="C46" t="n">
-        <v>1873.17</v>
+        <v>1895.77</v>
       </c>
       <c r="D46" t="n">
-        <v>1821.49</v>
+        <v>1842.15</v>
       </c>
       <c r="E46" t="n">
-        <v>1843.42</v>
+        <v>1882.52</v>
       </c>
       <c r="F46" t="n">
-        <v>-16.93</v>
+        <v>39.1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0212</v>
       </c>
       <c r="H46" t="n">
-        <v>51.69</v>
+        <v>53.61</v>
       </c>
       <c r="I46" t="n">
-        <v>1761.16</v>
+        <v>1769.8</v>
       </c>
       <c r="J46" t="n">
-        <v>1758.9</v>
+        <v>1789.78</v>
       </c>
       <c r="K46" t="n">
-        <v>1817.19</v>
+        <v>1817.57</v>
       </c>
       <c r="L46" t="n">
-        <v>1875.48</v>
+        <v>1845.37</v>
       </c>
       <c r="M46" t="n">
-        <v>1903.5</v>
+        <v>1869.26</v>
       </c>
       <c r="N46" t="n">
-        <v>1931.52</v>
+        <v>1893.15</v>
       </c>
       <c r="O46" t="n">
-        <v>2020.09</v>
+        <v>1924.86</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4344,22 +4340,24 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4368,80 +4366,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1843.42</v>
+        <v>1882.78</v>
       </c>
       <c r="C47" t="n">
-        <v>1895.77</v>
+        <v>1883.44</v>
       </c>
       <c r="D47" t="n">
-        <v>1842.15</v>
+        <v>1827.7</v>
       </c>
       <c r="E47" t="n">
-        <v>1882.52</v>
+        <v>1858.26</v>
       </c>
       <c r="F47" t="n">
-        <v>39.1</v>
+        <v>-24.27</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0129</v>
       </c>
       <c r="H47" t="n">
-        <v>53.61</v>
+        <v>55.74</v>
       </c>
       <c r="I47" t="n">
-        <v>1769.8</v>
+        <v>1788.54</v>
       </c>
       <c r="J47" t="n">
-        <v>1789.78</v>
+        <v>1835.69</v>
       </c>
       <c r="K47" t="n">
-        <v>1817.57</v>
+        <v>1855.72</v>
       </c>
       <c r="L47" t="n">
-        <v>1845.37</v>
+        <v>1875.74</v>
       </c>
       <c r="M47" t="n">
-        <v>1869.26</v>
+        <v>1909.33</v>
       </c>
       <c r="N47" t="n">
-        <v>1893.15</v>
+        <v>1942.91</v>
       </c>
       <c r="O47" t="n">
-        <v>1924.86</v>
+        <v>1949.38</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
+      <c r="Q47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4450,76 +4452,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1882.78</v>
+        <v>1858.22</v>
       </c>
       <c r="C48" t="n">
-        <v>1883.44</v>
+        <v>1879.54</v>
       </c>
       <c r="D48" t="n">
-        <v>1827.7</v>
+        <v>1847.17</v>
       </c>
       <c r="E48" t="n">
-        <v>1858.26</v>
+        <v>1868.39</v>
       </c>
       <c r="F48" t="n">
-        <v>-24.27</v>
+        <v>10.13</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0055</v>
       </c>
       <c r="H48" t="n">
-        <v>55.74</v>
+        <v>32.36</v>
       </c>
       <c r="I48" t="n">
-        <v>1788.54</v>
+        <v>1771.96</v>
       </c>
       <c r="J48" t="n">
-        <v>1835.69</v>
+        <v>1803.86</v>
       </c>
       <c r="K48" t="n">
-        <v>1855.72</v>
+        <v>1830.39</v>
       </c>
       <c r="L48" t="n">
-        <v>1875.74</v>
+        <v>1856.91</v>
       </c>
       <c r="M48" t="n">
-        <v>1909.33</v>
+        <v>1886.13</v>
       </c>
       <c r="N48" t="n">
-        <v>1942.91</v>
+        <v>1915.34</v>
       </c>
       <c r="O48" t="n">
-        <v>1949.38</v>
+        <v>1939.18</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4536,55 +4530,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1858.22</v>
+        <v>1868.49</v>
       </c>
       <c r="C49" t="n">
-        <v>1879.54</v>
+        <v>1922.64</v>
       </c>
       <c r="D49" t="n">
-        <v>1847.17</v>
+        <v>1854.34</v>
       </c>
       <c r="E49" t="n">
-        <v>1868.39</v>
+        <v>1906.53</v>
       </c>
       <c r="F49" t="n">
-        <v>10.13</v>
+        <v>38.14</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0204</v>
       </c>
       <c r="H49" t="n">
-        <v>32.36</v>
+        <v>68.3</v>
       </c>
       <c r="I49" t="n">
-        <v>1771.96</v>
+        <v>1814.81</v>
       </c>
       <c r="J49" t="n">
-        <v>1803.86</v>
+        <v>1838.54</v>
       </c>
       <c r="K49" t="n">
-        <v>1830.39</v>
+        <v>1852.2</v>
       </c>
       <c r="L49" t="n">
-        <v>1856.91</v>
+        <v>1865.87</v>
       </c>
       <c r="M49" t="n">
-        <v>1886.13</v>
+        <v>1884.57</v>
       </c>
       <c r="N49" t="n">
-        <v>1915.34</v>
+        <v>1903.26</v>
       </c>
       <c r="O49" t="n">
-        <v>1939.18</v>
+        <v>1911.9</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4597,76 +4595,78 @@
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1868.49</v>
+        <v>1906.44</v>
       </c>
       <c r="C50" t="n">
-        <v>1922.64</v>
+        <v>1917.7</v>
       </c>
       <c r="D50" t="n">
-        <v>1854.34</v>
+        <v>1890.96</v>
       </c>
       <c r="E50" t="n">
-        <v>1906.53</v>
+        <v>1902.06</v>
       </c>
       <c r="F50" t="n">
-        <v>38.14</v>
+        <v>-4.47</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.0023</v>
       </c>
       <c r="H50" t="n">
-        <v>68.3</v>
+        <v>26.74</v>
       </c>
       <c r="I50" t="n">
-        <v>1814.81</v>
+        <v>1786.04</v>
       </c>
       <c r="J50" t="n">
-        <v>1838.54</v>
+        <v>1847.24</v>
       </c>
       <c r="K50" t="n">
-        <v>1852.2</v>
+        <v>1872.38</v>
       </c>
       <c r="L50" t="n">
-        <v>1865.87</v>
+        <v>1897.51</v>
       </c>
       <c r="M50" t="n">
-        <v>1884.57</v>
+        <v>1940.68</v>
       </c>
       <c r="N50" t="n">
-        <v>1903.26</v>
+        <v>1983.84</v>
       </c>
       <c r="O50" t="n">
-        <v>1911.9</v>
+        <v>1990.94</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4679,78 +4679,76 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1906.44</v>
+        <v>1902.14</v>
       </c>
       <c r="C51" t="n">
-        <v>1917.7</v>
+        <v>1937.17</v>
       </c>
       <c r="D51" t="n">
-        <v>1890.96</v>
+        <v>1893.08</v>
       </c>
       <c r="E51" t="n">
-        <v>1902.06</v>
+        <v>1913.28</v>
       </c>
       <c r="F51" t="n">
-        <v>-4.47</v>
+        <v>11.22</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0059</v>
       </c>
       <c r="H51" t="n">
-        <v>26.74</v>
+        <v>44.08</v>
       </c>
       <c r="I51" t="n">
-        <v>1786.04</v>
+        <v>1864.23</v>
       </c>
       <c r="J51" t="n">
-        <v>1847.24</v>
+        <v>1874.18</v>
       </c>
       <c r="K51" t="n">
-        <v>1872.38</v>
+        <v>1888.69</v>
       </c>
       <c r="L51" t="n">
-        <v>1897.51</v>
+        <v>1903.19</v>
       </c>
       <c r="M51" t="n">
-        <v>1940.68</v>
+        <v>1915.43</v>
       </c>
       <c r="N51" t="n">
-        <v>1983.84</v>
+        <v>1927.66</v>
       </c>
       <c r="O51" t="n">
-        <v>1990.94</v>
+        <v>1944.44</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4763,14 +4761,18 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4780,59 +4782,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1902.14</v>
+        <v>1913.32</v>
       </c>
       <c r="C52" t="n">
-        <v>1937.17</v>
+        <v>1924.62</v>
       </c>
       <c r="D52" t="n">
-        <v>1893.08</v>
+        <v>1911.48</v>
       </c>
       <c r="E52" t="n">
-        <v>1913.28</v>
+        <v>1915.53</v>
       </c>
       <c r="F52" t="n">
-        <v>11.22</v>
+        <v>2.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0012</v>
       </c>
       <c r="H52" t="n">
-        <v>44.08</v>
+        <v>13.13</v>
       </c>
       <c r="I52" t="n">
-        <v>1864.23</v>
+        <v>1849</v>
       </c>
       <c r="J52" t="n">
-        <v>1874.18</v>
+        <v>1868.27</v>
       </c>
       <c r="K52" t="n">
-        <v>1888.69</v>
+        <v>1891.24</v>
       </c>
       <c r="L52" t="n">
-        <v>1903.19</v>
+        <v>1914.2</v>
       </c>
       <c r="M52" t="n">
-        <v>1915.43</v>
+        <v>1935.32</v>
       </c>
       <c r="N52" t="n">
-        <v>1927.66</v>
+        <v>1956.44</v>
       </c>
       <c r="O52" t="n">
-        <v>1944.44</v>
+        <v>1981.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4845,18 +4843,14 @@
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4866,55 +4860,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1913.32</v>
+        <v>1915.46</v>
       </c>
       <c r="C53" t="n">
-        <v>1924.62</v>
+        <v>1935.53</v>
       </c>
       <c r="D53" t="n">
-        <v>1911.48</v>
+        <v>1907.03</v>
       </c>
       <c r="E53" t="n">
-        <v>1915.53</v>
+        <v>1908.68</v>
       </c>
       <c r="F53" t="n">
-        <v>2.25</v>
+        <v>-6.85</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0036</v>
       </c>
       <c r="H53" t="n">
-        <v>13.13</v>
+        <v>28.5</v>
       </c>
       <c r="I53" t="n">
-        <v>1849</v>
+        <v>1898.35</v>
       </c>
       <c r="J53" t="n">
-        <v>1868.27</v>
+        <v>1901.14</v>
       </c>
       <c r="K53" t="n">
-        <v>1891.24</v>
+        <v>1908.97</v>
       </c>
       <c r="L53" t="n">
-        <v>1914.2</v>
+        <v>1916.79</v>
       </c>
       <c r="M53" t="n">
-        <v>1935.32</v>
+        <v>1922.1</v>
       </c>
       <c r="N53" t="n">
-        <v>1956.44</v>
+        <v>1927.4</v>
       </c>
       <c r="O53" t="n">
-        <v>1981.25</v>
+        <v>1937.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4922,19 +4920,25 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4946,67 +4950,71 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1915.46</v>
+        <v>1908.72</v>
       </c>
       <c r="C54" t="n">
-        <v>1935.53</v>
+        <v>1928.99</v>
       </c>
       <c r="D54" t="n">
-        <v>1907.03</v>
+        <v>1866.79</v>
       </c>
       <c r="E54" t="n">
-        <v>1908.68</v>
+        <v>1871.28</v>
       </c>
       <c r="F54" t="n">
-        <v>-6.85</v>
+        <v>-37.4</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0196</v>
       </c>
       <c r="H54" t="n">
-        <v>28.5</v>
+        <v>62.2</v>
       </c>
       <c r="I54" t="n">
-        <v>1898.35</v>
+        <v>1878.52</v>
       </c>
       <c r="J54" t="n">
-        <v>1901.14</v>
+        <v>1873.88</v>
       </c>
       <c r="K54" t="n">
-        <v>1908.97</v>
+        <v>1894.43</v>
       </c>
       <c r="L54" t="n">
-        <v>1916.79</v>
+        <v>1914.98</v>
       </c>
       <c r="M54" t="n">
-        <v>1922.1</v>
+        <v>1922.93</v>
       </c>
       <c r="N54" t="n">
-        <v>1927.4</v>
+        <v>1930.89</v>
       </c>
       <c r="O54" t="n">
-        <v>1937.75</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+        <v>1964.03</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
@@ -5019,97 +5027,83 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1908.72</v>
+        <v>1871.26</v>
       </c>
       <c r="C55" t="n">
-        <v>1928.99</v>
+        <v>1895.75</v>
       </c>
       <c r="D55" t="n">
-        <v>1866.79</v>
+        <v>1852.84</v>
       </c>
       <c r="E55" t="n">
-        <v>1871.28</v>
+        <v>1881.37</v>
       </c>
       <c r="F55" t="n">
-        <v>-37.4</v>
+        <v>10.09</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0196</v>
+        <v>0.0054</v>
       </c>
       <c r="H55" t="n">
-        <v>62.2</v>
+        <v>42.91</v>
       </c>
       <c r="I55" t="n">
-        <v>1878.52</v>
+        <v>1804.59</v>
       </c>
       <c r="J55" t="n">
-        <v>1873.88</v>
+        <v>1795.77</v>
       </c>
       <c r="K55" t="n">
-        <v>1894.43</v>
+        <v>1840.18</v>
       </c>
       <c r="L55" t="n">
-        <v>1914.98</v>
+        <v>1884.59</v>
       </c>
       <c r="M55" t="n">
-        <v>1922.93</v>
+        <v>1902.38</v>
       </c>
       <c r="N55" t="n">
-        <v>1930.89</v>
+        <v>1920.18</v>
       </c>
       <c r="O55" t="n">
-        <v>1964.03</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>1991.2</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5122,55 +5116,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1871.26</v>
+        <v>1881.37</v>
       </c>
       <c r="C56" t="n">
-        <v>1895.75</v>
+        <v>1921.78</v>
       </c>
       <c r="D56" t="n">
-        <v>1852.84</v>
+        <v>1873.35</v>
       </c>
       <c r="E56" t="n">
-        <v>1881.37</v>
+        <v>1878.14</v>
       </c>
       <c r="F56" t="n">
-        <v>10.09</v>
+        <v>-3.24</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0017</v>
       </c>
       <c r="H56" t="n">
-        <v>42.91</v>
+        <v>48.43</v>
       </c>
       <c r="I56" t="n">
-        <v>1804.59</v>
+        <v>1809.93</v>
       </c>
       <c r="J56" t="n">
-        <v>1795.77</v>
+        <v>1842</v>
       </c>
       <c r="K56" t="n">
-        <v>1840.18</v>
+        <v>1859.92</v>
       </c>
       <c r="L56" t="n">
-        <v>1884.59</v>
+        <v>1877.83</v>
       </c>
       <c r="M56" t="n">
-        <v>1902.38</v>
+        <v>1902.83</v>
       </c>
       <c r="N56" t="n">
-        <v>1920.18</v>
+        <v>1927.82</v>
       </c>
       <c r="O56" t="n">
-        <v>1991.2</v>
+        <v>1938.66</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5181,13 +5179,15 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5202,57 +5202,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1881.37</v>
+        <v>1878.19</v>
       </c>
       <c r="C57" t="n">
-        <v>1921.78</v>
+        <v>1898.23</v>
       </c>
       <c r="D57" t="n">
-        <v>1873.35</v>
+        <v>1861.92</v>
       </c>
       <c r="E57" t="n">
-        <v>1878.14</v>
+        <v>1883.99</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.24</v>
+        <v>5.86</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="H57" t="n">
-        <v>48.43</v>
+        <v>36.3</v>
       </c>
       <c r="I57" t="n">
-        <v>1809.93</v>
+        <v>1824.92</v>
       </c>
       <c r="J57" t="n">
-        <v>1842</v>
+        <v>1819.99</v>
       </c>
       <c r="K57" t="n">
-        <v>1859.92</v>
+        <v>1853.92</v>
       </c>
       <c r="L57" t="n">
-        <v>1877.83</v>
+        <v>1887.85</v>
       </c>
       <c r="M57" t="n">
-        <v>1902.83</v>
+        <v>1902.35</v>
       </c>
       <c r="N57" t="n">
-        <v>1927.82</v>
+        <v>1916.85</v>
       </c>
       <c r="O57" t="n">
-        <v>1938.66</v>
+        <v>1970.2</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5263,15 +5263,13 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5286,57 +5284,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1878.19</v>
+        <v>1884.02</v>
       </c>
       <c r="C58" t="n">
-        <v>1898.23</v>
+        <v>1889.27</v>
       </c>
       <c r="D58" t="n">
-        <v>1861.92</v>
+        <v>1862.56</v>
       </c>
       <c r="E58" t="n">
-        <v>1883.99</v>
+        <v>1880.65</v>
       </c>
       <c r="F58" t="n">
-        <v>5.86</v>
+        <v>-3.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0018</v>
       </c>
       <c r="H58" t="n">
-        <v>36.3</v>
+        <v>26.71</v>
       </c>
       <c r="I58" t="n">
-        <v>1824.92</v>
+        <v>1825.62</v>
       </c>
       <c r="J58" t="n">
-        <v>1819.99</v>
+        <v>1849.65</v>
       </c>
       <c r="K58" t="n">
-        <v>1853.92</v>
+        <v>1865.84</v>
       </c>
       <c r="L58" t="n">
-        <v>1887.85</v>
+        <v>1882.03</v>
       </c>
       <c r="M58" t="n">
-        <v>1902.35</v>
+        <v>1902.14</v>
       </c>
       <c r="N58" t="n">
-        <v>1916.85</v>
+        <v>1922.26</v>
       </c>
       <c r="O58" t="n">
-        <v>1970.2</v>
+        <v>1934.53</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5344,8 +5342,10 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
@@ -5375,50 +5375,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1884.02</v>
+        <v>1880.61</v>
       </c>
       <c r="C59" t="n">
-        <v>1889.27</v>
+        <v>1884.72</v>
       </c>
       <c r="D59" t="n">
-        <v>1862.56</v>
+        <v>1874.33</v>
       </c>
       <c r="E59" t="n">
-        <v>1880.65</v>
+        <v>1880.91</v>
       </c>
       <c r="F59" t="n">
-        <v>-3.34</v>
+        <v>0.26</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0001</v>
       </c>
       <c r="H59" t="n">
-        <v>26.71</v>
+        <v>10.39</v>
       </c>
       <c r="I59" t="n">
-        <v>1825.62</v>
+        <v>1835.86</v>
       </c>
       <c r="J59" t="n">
-        <v>1849.65</v>
+        <v>1856.31</v>
       </c>
       <c r="K59" t="n">
-        <v>1865.84</v>
+        <v>1867.3</v>
       </c>
       <c r="L59" t="n">
-        <v>1882.03</v>
+        <v>1878.28</v>
       </c>
       <c r="M59" t="n">
-        <v>1902.14</v>
+        <v>1894</v>
       </c>
       <c r="N59" t="n">
-        <v>1922.26</v>
+        <v>1909.72</v>
       </c>
       <c r="O59" t="n">
-        <v>1934.53</v>
+        <v>1915.98</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5426,14 +5426,12 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5452,74 +5450,80 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1880.61</v>
+        <v>1880.89</v>
       </c>
       <c r="C60" t="n">
-        <v>1884.72</v>
+        <v>1889.61</v>
       </c>
       <c r="D60" t="n">
-        <v>1874.33</v>
+        <v>1867.89</v>
       </c>
       <c r="E60" t="n">
-        <v>1880.91</v>
+        <v>1873.94</v>
       </c>
       <c r="F60" t="n">
-        <v>0.26</v>
+        <v>-6.97</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0037</v>
       </c>
       <c r="H60" t="n">
-        <v>10.39</v>
+        <v>21.71</v>
       </c>
       <c r="I60" t="n">
-        <v>1835.86</v>
+        <v>1863.94</v>
       </c>
       <c r="J60" t="n">
-        <v>1856.31</v>
+        <v>1871.21</v>
       </c>
       <c r="K60" t="n">
-        <v>1867.3</v>
+        <v>1875.71</v>
       </c>
       <c r="L60" t="n">
-        <v>1878.28</v>
+        <v>1880.22</v>
       </c>
       <c r="M60" t="n">
-        <v>1894</v>
+        <v>1886.1</v>
       </c>
       <c r="N60" t="n">
-        <v>1909.72</v>
+        <v>1891.99</v>
       </c>
       <c r="O60" t="n">
-        <v>1915.98</v>
+        <v>1895.11</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5534,145 +5538,141 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1880.89</v>
+        <v>1873.97</v>
       </c>
       <c r="C61" t="n">
-        <v>1889.61</v>
+        <v>1916.66</v>
       </c>
       <c r="D61" t="n">
-        <v>1867.89</v>
+        <v>1870.75</v>
       </c>
       <c r="E61" t="n">
-        <v>1873.94</v>
+        <v>1912.2</v>
       </c>
       <c r="F61" t="n">
-        <v>-6.97</v>
+        <v>38.26</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0204</v>
       </c>
       <c r="H61" t="n">
-        <v>21.71</v>
+        <v>45.91</v>
       </c>
       <c r="I61" t="n">
-        <v>1863.94</v>
+        <v>1846.18</v>
       </c>
       <c r="J61" t="n">
-        <v>1871.21</v>
+        <v>1849.83</v>
       </c>
       <c r="K61" t="n">
-        <v>1875.71</v>
+        <v>1863.09</v>
       </c>
       <c r="L61" t="n">
-        <v>1880.22</v>
+        <v>1876.35</v>
       </c>
       <c r="M61" t="n">
-        <v>1886.1</v>
+        <v>1884.8</v>
       </c>
       <c r="N61" t="n">
-        <v>1891.99</v>
+        <v>1893.25</v>
       </c>
       <c r="O61" t="n">
-        <v>1895.11</v>
+        <v>1911.32</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1873.97</v>
+        <v>1912.21</v>
       </c>
       <c r="C62" t="n">
-        <v>1916.66</v>
+        <v>1920.52</v>
       </c>
       <c r="D62" t="n">
-        <v>1870.75</v>
+        <v>1884.48</v>
       </c>
       <c r="E62" t="n">
-        <v>1912.2</v>
+        <v>1916.46</v>
       </c>
       <c r="F62" t="n">
-        <v>38.26</v>
+        <v>4.26</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.0022</v>
       </c>
       <c r="H62" t="n">
-        <v>45.91</v>
+        <v>36.05</v>
       </c>
       <c r="I62" t="n">
-        <v>1846.18</v>
+        <v>1824.84</v>
       </c>
       <c r="J62" t="n">
-        <v>1849.83</v>
+        <v>1875.54</v>
       </c>
       <c r="K62" t="n">
-        <v>1863.09</v>
+        <v>1889.25</v>
       </c>
       <c r="L62" t="n">
-        <v>1876.35</v>
+        <v>1902.95</v>
       </c>
       <c r="M62" t="n">
-        <v>1884.8</v>
+        <v>1935.16</v>
       </c>
       <c r="N62" t="n">
-        <v>1893.25</v>
+        <v>1967.36</v>
       </c>
       <c r="O62" t="n">
-        <v>1911.32</v>
+        <v>1962.57</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5680,28 +5680,24 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
@@ -5713,50 +5709,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1912.21</v>
+        <v>1916.43</v>
       </c>
       <c r="C63" t="n">
-        <v>1920.52</v>
+        <v>2327.7</v>
       </c>
       <c r="D63" t="n">
-        <v>1884.48</v>
+        <v>1905.08</v>
       </c>
       <c r="E63" t="n">
-        <v>1916.46</v>
+        <v>2251.46</v>
       </c>
       <c r="F63" t="n">
-        <v>4.26</v>
+        <v>335</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.1748</v>
       </c>
       <c r="H63" t="n">
-        <v>36.05</v>
+        <v>422.62</v>
       </c>
       <c r="I63" t="n">
-        <v>1824.84</v>
+        <v>1848.43</v>
       </c>
       <c r="J63" t="n">
-        <v>1875.54</v>
+        <v>1887.39</v>
       </c>
       <c r="K63" t="n">
-        <v>1889.25</v>
+        <v>1898.44</v>
       </c>
       <c r="L63" t="n">
-        <v>1902.95</v>
+        <v>1909.48</v>
       </c>
       <c r="M63" t="n">
-        <v>1935.16</v>
+        <v>1934.48</v>
       </c>
       <c r="N63" t="n">
-        <v>1967.36</v>
+        <v>1959.48</v>
       </c>
       <c r="O63" t="n">
-        <v>1962.57</v>
+        <v>1956.57</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5764,24 +5760,28 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W63" s="9" t="inlineStr">
         <is>
@@ -5793,50 +5793,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1916.43</v>
+        <v>2251.44</v>
       </c>
       <c r="C64" t="n">
-        <v>2327.7</v>
+        <v>2357.23</v>
       </c>
       <c r="D64" t="n">
-        <v>1905.08</v>
+        <v>2222.57</v>
       </c>
       <c r="E64" t="n">
-        <v>2251.46</v>
+        <v>2326.38</v>
       </c>
       <c r="F64" t="n">
-        <v>335</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.1748</v>
+        <v>0.0333</v>
       </c>
       <c r="H64" t="n">
-        <v>422.62</v>
+        <v>134.65</v>
       </c>
       <c r="I64" t="n">
-        <v>1848.43</v>
+        <v>1482.46</v>
       </c>
       <c r="J64" t="n">
-        <v>1887.39</v>
+        <v>1896.37</v>
       </c>
       <c r="K64" t="n">
-        <v>1898.44</v>
+        <v>2040.15</v>
       </c>
       <c r="L64" t="n">
-        <v>1909.48</v>
+        <v>2183.92</v>
       </c>
       <c r="M64" t="n">
-        <v>1934.48</v>
+        <v>2462.77</v>
       </c>
       <c r="N64" t="n">
-        <v>1959.48</v>
+        <v>2741.61</v>
       </c>
       <c r="O64" t="n">
-        <v>1956.57</v>
+        <v>2750.32</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5854,18 +5854,14 @@
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
       </c>
       <c r="W64" s="9" t="inlineStr">
         <is>
@@ -5877,50 +5873,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2251.44</v>
+        <v>2326.38</v>
       </c>
       <c r="C65" t="n">
-        <v>2357.23</v>
+        <v>2545.88</v>
       </c>
       <c r="D65" t="n">
-        <v>2222.57</v>
+        <v>2324.71</v>
       </c>
       <c r="E65" t="n">
-        <v>2326.38</v>
+        <v>2515.28</v>
       </c>
       <c r="F65" t="n">
-        <v>74.93000000000001</v>
+        <v>188.9</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0333</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>134.65</v>
+        <v>221.17</v>
       </c>
       <c r="I65" t="n">
-        <v>1482.46</v>
+        <v>2087.92</v>
       </c>
       <c r="J65" t="n">
-        <v>1896.37</v>
+        <v>2209.97</v>
       </c>
       <c r="K65" t="n">
-        <v>2040.15</v>
+        <v>2259.06</v>
       </c>
       <c r="L65" t="n">
-        <v>2183.92</v>
+        <v>2308.14</v>
       </c>
       <c r="M65" t="n">
-        <v>2462.77</v>
+        <v>2393.71</v>
       </c>
       <c r="N65" t="n">
-        <v>2741.61</v>
+        <v>2479.28</v>
       </c>
       <c r="O65" t="n">
-        <v>2750.32</v>
+        <v>2491.88</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5938,14 +5934,18 @@
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V65" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
       </c>
       <c r="W65" s="9" t="inlineStr">
         <is>
@@ -5957,50 +5957,50 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2326.38</v>
+        <v>2515.39</v>
       </c>
       <c r="C66" t="n">
-        <v>2545.88</v>
+        <v>2528.9</v>
       </c>
       <c r="D66" t="n">
-        <v>2324.71</v>
+        <v>2389.9</v>
       </c>
       <c r="E66" t="n">
-        <v>2515.28</v>
+        <v>2424.25</v>
       </c>
       <c r="F66" t="n">
-        <v>188.9</v>
+        <v>-91.03</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0362</v>
       </c>
       <c r="H66" t="n">
-        <v>221.17</v>
+        <v>138.99</v>
       </c>
       <c r="I66" t="n">
-        <v>2087.92</v>
+        <v>2103.54</v>
       </c>
       <c r="J66" t="n">
-        <v>2209.97</v>
+        <v>2334.1</v>
       </c>
       <c r="K66" t="n">
-        <v>2259.06</v>
+        <v>2404.7</v>
       </c>
       <c r="L66" t="n">
-        <v>2308.14</v>
+        <v>2475.29</v>
       </c>
       <c r="M66" t="n">
-        <v>2393.71</v>
+        <v>2625.87</v>
       </c>
       <c r="N66" t="n">
-        <v>2479.28</v>
+        <v>2776.45</v>
       </c>
       <c r="O66" t="n">
-        <v>2491.88</v>
+        <v>2767.05</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6008,83 +6008,83 @@
       <c r="Q66" s="6" t="n">
         <v/>
       </c>
-      <c r="R66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S66" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T66" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U66" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V66" s="8" t="inlineStr">
+      <c r="R66" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U66" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V66" s="8" t="n">
+        <v/>
+      </c>
       <c r="W66" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2515.39</v>
+        <v>2424.22</v>
       </c>
       <c r="C67" t="n">
-        <v>2528.9</v>
+        <v>2483.93</v>
       </c>
       <c r="D67" t="n">
-        <v>2389.9</v>
+        <v>2357.14</v>
       </c>
       <c r="E67" t="n">
-        <v>2424.25</v>
+        <v>2463.82</v>
       </c>
       <c r="F67" t="n">
-        <v>-91.03</v>
+        <v>39.56</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.0362</v>
+        <v>0.0163</v>
       </c>
       <c r="H67" t="n">
-        <v>138.99</v>
+        <v>126.79</v>
       </c>
       <c r="I67" t="n">
-        <v>2103.54</v>
+        <v>2250.91</v>
       </c>
       <c r="J67" t="n">
-        <v>2334.1</v>
+        <v>2267.68</v>
       </c>
       <c r="K67" t="n">
-        <v>2404.7</v>
+        <v>2354.75</v>
       </c>
       <c r="L67" t="n">
-        <v>2475.29</v>
+        <v>2441.83</v>
       </c>
       <c r="M67" t="n">
-        <v>2625.87</v>
+        <v>2493.75</v>
       </c>
       <c r="N67" t="n">
-        <v>2776.45</v>
+        <v>2545.67</v>
       </c>
       <c r="O67" t="n">
-        <v>2767.05</v>
+        <v>2667.89</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6092,14 +6092,12 @@
       <c r="Q67" s="6" t="n">
         <v/>
       </c>
-      <c r="R67" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S67" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S67" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T67" s="8" t="n">
@@ -6125,50 +6123,50 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2424.22</v>
+        <v>2463.64</v>
       </c>
       <c r="C68" t="n">
-        <v>2483.93</v>
+        <v>2531.74</v>
       </c>
       <c r="D68" t="n">
-        <v>2357.14</v>
+        <v>2425.39</v>
       </c>
       <c r="E68" t="n">
-        <v>2463.82</v>
+        <v>2481.83</v>
       </c>
       <c r="F68" t="n">
-        <v>39.56</v>
+        <v>18.02</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0073</v>
       </c>
       <c r="H68" t="n">
-        <v>126.79</v>
+        <v>106.36</v>
       </c>
       <c r="I68" t="n">
-        <v>2250.91</v>
+        <v>2230.35</v>
       </c>
       <c r="J68" t="n">
-        <v>2267.68</v>
+        <v>2358.67</v>
       </c>
       <c r="K68" t="n">
-        <v>2354.75</v>
+        <v>2400.42</v>
       </c>
       <c r="L68" t="n">
-        <v>2441.83</v>
+        <v>2442.18</v>
       </c>
       <c r="M68" t="n">
-        <v>2493.75</v>
+        <v>2527.21</v>
       </c>
       <c r="N68" t="n">
-        <v>2545.67</v>
+        <v>2612.25</v>
       </c>
       <c r="O68" t="n">
-        <v>2667.89</v>
+        <v>2610.72</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
@@ -6184,8 +6182,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T68" s="8" t="n">
-        <v/>
+      <c r="T68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U68" s="8" t="n">
         <v/>
@@ -6198,59 +6198,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2463.64</v>
+        <v>2481.78</v>
       </c>
       <c r="C69" t="n">
-        <v>2531.74</v>
+        <v>2531.08</v>
       </c>
       <c r="D69" t="n">
-        <v>2425.39</v>
+        <v>2416.6</v>
       </c>
       <c r="E69" t="n">
-        <v>2481.83</v>
+        <v>2443.16</v>
       </c>
       <c r="F69" t="n">
-        <v>18.02</v>
+        <v>-38.67</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0156</v>
       </c>
       <c r="H69" t="n">
-        <v>106.36</v>
+        <v>114.48</v>
       </c>
       <c r="I69" t="n">
-        <v>2230.35</v>
+        <v>2319.03</v>
       </c>
       <c r="J69" t="n">
-        <v>2358.67</v>
+        <v>2377.11</v>
       </c>
       <c r="K69" t="n">
-        <v>2400.42</v>
+        <v>2428.65</v>
       </c>
       <c r="L69" t="n">
-        <v>2442.18</v>
+        <v>2480.2</v>
       </c>
       <c r="M69" t="n">
-        <v>2527.21</v>
+        <v>2535.01</v>
       </c>
       <c r="N69" t="n">
-        <v>2612.25</v>
+        <v>2589.82</v>
       </c>
       <c r="O69" t="n">
-        <v>2610.72</v>
+        <v>2638.1</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6258,18 +6254,18 @@
       <c r="Q69" s="6" t="n">
         <v/>
       </c>
-      <c r="R69" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S69" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T69" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S69" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="n">
+        <v/>
       </c>
       <c r="U69" s="8" t="n">
         <v/>
@@ -6282,55 +6278,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr"/>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2481.78</v>
+        <v>2442.49</v>
       </c>
       <c r="C70" t="n">
-        <v>2531.08</v>
+        <v>2514.67</v>
       </c>
       <c r="D70" t="n">
-        <v>2416.6</v>
+        <v>2432.51</v>
       </c>
       <c r="E70" t="n">
-        <v>2443.16</v>
+        <v>2506.26</v>
       </c>
       <c r="F70" t="n">
-        <v>-38.67</v>
+        <v>63.1</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0258</v>
       </c>
       <c r="H70" t="n">
-        <v>114.48</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>2319.03</v>
+        <v>2302.12</v>
       </c>
       <c r="J70" t="n">
-        <v>2377.11</v>
+        <v>2313.34</v>
       </c>
       <c r="K70" t="n">
-        <v>2428.65</v>
+        <v>2385.92</v>
       </c>
       <c r="L70" t="n">
-        <v>2480.2</v>
+        <v>2458.5</v>
       </c>
       <c r="M70" t="n">
-        <v>2535.01</v>
+        <v>2500.4</v>
       </c>
       <c r="N70" t="n">
-        <v>2589.82</v>
+        <v>2542.3</v>
       </c>
       <c r="O70" t="n">
-        <v>2638.1</v>
+        <v>2645.57</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
@@ -6338,19 +6338,19 @@
       <c r="Q70" s="6" t="n">
         <v/>
       </c>
-      <c r="R70" s="6" t="inlineStr">
+      <c r="R70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S70" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S70" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="n">
-        <v/>
-      </c>
       <c r="U70" s="8" t="n">
         <v/>
       </c>
@@ -6364,57 +6364,57 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2442.49</v>
+        <v>2506.24</v>
       </c>
       <c r="C71" t="n">
-        <v>2514.67</v>
+        <v>2564.27</v>
       </c>
       <c r="D71" t="n">
-        <v>2432.51</v>
+        <v>2481.94</v>
       </c>
       <c r="E71" t="n">
-        <v>2506.26</v>
+        <v>2510.41</v>
       </c>
       <c r="F71" t="n">
-        <v>63.1</v>
+        <v>4.15</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0258</v>
+        <v>0.0017</v>
       </c>
       <c r="H71" t="n">
-        <v>82.15000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="I71" t="n">
-        <v>2302.12</v>
+        <v>2350.36</v>
       </c>
       <c r="J71" t="n">
-        <v>2313.34</v>
+        <v>2440.44</v>
       </c>
       <c r="K71" t="n">
-        <v>2385.92</v>
+        <v>2465.18</v>
       </c>
       <c r="L71" t="n">
-        <v>2458.5</v>
+        <v>2489.93</v>
       </c>
       <c r="M71" t="n">
-        <v>2500.4</v>
+        <v>2547.34</v>
       </c>
       <c r="N71" t="n">
-        <v>2542.3</v>
+        <v>2604.75</v>
       </c>
       <c r="O71" t="n">
-        <v>2645.57</v>
+        <v>2596.82</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="S71" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T71" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U71" s="8" t="n">
@@ -6446,79 +6446,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2506.24</v>
+        <v>2510.67</v>
       </c>
       <c r="C72" t="n">
-        <v>2564.27</v>
+        <v>2534.01</v>
       </c>
       <c r="D72" t="n">
-        <v>2481.94</v>
+        <v>2408.72</v>
       </c>
       <c r="E72" t="n">
-        <v>2510.41</v>
+        <v>2442.54</v>
       </c>
       <c r="F72" t="n">
-        <v>4.15</v>
+        <v>-67.87</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.027</v>
       </c>
       <c r="H72" t="n">
-        <v>82.33</v>
+        <v>125.29</v>
       </c>
       <c r="I72" t="n">
-        <v>2350.36</v>
+        <v>2399.62</v>
       </c>
       <c r="J72" t="n">
-        <v>2440.44</v>
+        <v>2421.73</v>
       </c>
       <c r="K72" t="n">
-        <v>2465.18</v>
+        <v>2469.25</v>
       </c>
       <c r="L72" t="n">
-        <v>2489.93</v>
+        <v>2516.76</v>
       </c>
       <c r="M72" t="n">
-        <v>2547.34</v>
+        <v>2551.57</v>
       </c>
       <c r="N72" t="n">
-        <v>2604.75</v>
+        <v>2586.39</v>
       </c>
       <c r="O72" t="n">
-        <v>2596.82</v>
+        <v>2646.6</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
       </c>
-      <c r="Q72" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R72" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S72" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T72" s="8" t="inlineStr">
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S72" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="n">
+        <v/>
+      </c>
       <c r="U72" s="8" t="n">
         <v/>
       </c>
@@ -6530,72 +6528,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr"/>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2510.67</v>
+        <v>2442.56</v>
       </c>
       <c r="C73" t="n">
-        <v>2534.01</v>
+        <v>2459.63</v>
       </c>
       <c r="D73" t="n">
-        <v>2408.72</v>
+        <v>2430.81</v>
       </c>
       <c r="E73" t="n">
-        <v>2442.54</v>
+        <v>2457.69</v>
       </c>
       <c r="F73" t="n">
-        <v>-67.87</v>
+        <v>15.15</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.027</v>
+        <v>0.0062</v>
       </c>
       <c r="H73" t="n">
-        <v>125.29</v>
+        <v>28.82</v>
       </c>
       <c r="I73" t="n">
-        <v>2399.62</v>
+        <v>2283.43</v>
       </c>
       <c r="J73" t="n">
-        <v>2421.73</v>
+        <v>2302.83</v>
       </c>
       <c r="K73" t="n">
-        <v>2469.25</v>
+        <v>2379.89</v>
       </c>
       <c r="L73" t="n">
-        <v>2516.76</v>
+        <v>2456.95</v>
       </c>
       <c r="M73" t="n">
-        <v>2551.57</v>
+        <v>2505.18</v>
       </c>
       <c r="N73" t="n">
-        <v>2586.39</v>
+        <v>2553.41</v>
       </c>
       <c r="O73" t="n">
-        <v>2646.6</v>
+        <v>2659.3</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
       </c>
-      <c r="Q73" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R73" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S73" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T73" s="8" t="n">
@@ -6614,84 +6612,96 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2442.56</v>
+        <v>2457.69</v>
       </c>
       <c r="C74" t="n">
-        <v>2459.63</v>
+        <v>2532.96</v>
       </c>
       <c r="D74" t="n">
-        <v>2430.81</v>
+        <v>2389.47</v>
       </c>
       <c r="E74" t="n">
-        <v>2457.69</v>
+        <v>2417.94</v>
       </c>
       <c r="F74" t="n">
-        <v>15.15</v>
+        <v>-39.75</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H74" t="n">
-        <v>28.82</v>
+        <v>143.49</v>
       </c>
       <c r="I74" t="n">
-        <v>2283.43</v>
+        <v>2401.99</v>
       </c>
       <c r="J74" t="n">
-        <v>2302.83</v>
+        <v>2435.1</v>
       </c>
       <c r="K74" t="n">
-        <v>2379.89</v>
+        <v>2443.28</v>
       </c>
       <c r="L74" t="n">
-        <v>2456.95</v>
+        <v>2451.45</v>
       </c>
       <c r="M74" t="n">
-        <v>2505.18</v>
+        <v>2472.1</v>
       </c>
       <c r="N74" t="n">
-        <v>2553.41</v>
+        <v>2492.74</v>
       </c>
       <c r="O74" t="n">
-        <v>2659.3</v>
-      </c>
-      <c r="P74" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q74" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R74" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S74" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U74" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V74" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W74" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+        <v>2488.45</v>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S74" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W74" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -6703,85 +6713,75 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2457.69</v>
+        <v>2417.9</v>
       </c>
       <c r="C75" t="n">
-        <v>2532.96</v>
+        <v>2488.92</v>
       </c>
       <c r="D75" t="n">
-        <v>2389.47</v>
+        <v>2401.81</v>
       </c>
       <c r="E75" t="n">
-        <v>2417.94</v>
+        <v>2466.82</v>
       </c>
       <c r="F75" t="n">
-        <v>-39.75</v>
+        <v>48.88</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.0202</v>
       </c>
       <c r="H75" t="n">
-        <v>143.49</v>
+        <v>87.11</v>
       </c>
       <c r="I75" t="n">
-        <v>2401.99</v>
+        <v>2245.98</v>
       </c>
       <c r="J75" t="n">
-        <v>2435.1</v>
+        <v>2252.81</v>
       </c>
       <c r="K75" t="n">
-        <v>2443.28</v>
+        <v>2346.19</v>
       </c>
       <c r="L75" t="n">
-        <v>2451.45</v>
+        <v>2439.58</v>
       </c>
       <c r="M75" t="n">
-        <v>2472.1</v>
+        <v>2489.68</v>
       </c>
       <c r="N75" t="n">
-        <v>2492.74</v>
+        <v>2539.79</v>
       </c>
       <c r="O75" t="n">
-        <v>2488.45</v>
-      </c>
-      <c r="P75" s="6" t="inlineStr">
+        <v>2676.45</v>
+      </c>
+      <c r="P75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R75" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S75" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q75" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R75" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S75" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T75" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U75" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V75" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U75" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V75" s="8" t="n">
+        <v/>
       </c>
       <c r="W75" s="11" t="inlineStr">
         <is>
@@ -6790,77 +6790,79 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2417.9</v>
+        <v>2466.58</v>
       </c>
       <c r="C76" t="n">
-        <v>2488.92</v>
+        <v>2484.4</v>
       </c>
       <c r="D76" t="n">
-        <v>2401.81</v>
+        <v>2383.8</v>
       </c>
       <c r="E76" t="n">
-        <v>2466.82</v>
+        <v>2417.84</v>
       </c>
       <c r="F76" t="n">
-        <v>48.88</v>
+        <v>-48.98</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.0202</v>
+        <v>-0.0199</v>
       </c>
       <c r="H76" t="n">
-        <v>87.11</v>
+        <v>100.6</v>
       </c>
       <c r="I76" t="n">
-        <v>2245.98</v>
+        <v>2314.69</v>
       </c>
       <c r="J76" t="n">
-        <v>2252.81</v>
+        <v>2390.43</v>
       </c>
       <c r="K76" t="n">
-        <v>2346.19</v>
+        <v>2423.26</v>
       </c>
       <c r="L76" t="n">
-        <v>2439.58</v>
+        <v>2456.09</v>
       </c>
       <c r="M76" t="n">
-        <v>2489.68</v>
+        <v>2510.38</v>
       </c>
       <c r="N76" t="n">
-        <v>2539.79</v>
+        <v>2564.66</v>
       </c>
       <c r="O76" t="n">
-        <v>2676.45</v>
+        <v>2576.04</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
       </c>
-      <c r="Q76" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R76" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S76" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="inlineStr">
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S76" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="n">
+        <v/>
+      </c>
       <c r="U76" s="8" t="n">
         <v/>
       </c>
@@ -6872,67 +6874,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2466.58</v>
+        <v>2417.83</v>
       </c>
       <c r="C77" t="n">
-        <v>2484.4</v>
+        <v>2427.4</v>
       </c>
       <c r="D77" t="n">
-        <v>2383.8</v>
+        <v>2356.19</v>
       </c>
       <c r="E77" t="n">
-        <v>2417.84</v>
+        <v>2391.5</v>
       </c>
       <c r="F77" t="n">
-        <v>-48.98</v>
+        <v>-26.34</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.0109</v>
       </c>
       <c r="H77" t="n">
-        <v>100.6</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>2314.69</v>
+        <v>2283.21</v>
       </c>
       <c r="J77" t="n">
-        <v>2390.43</v>
+        <v>2309.12</v>
       </c>
       <c r="K77" t="n">
-        <v>2423.26</v>
+        <v>2367.54</v>
       </c>
       <c r="L77" t="n">
-        <v>2456.09</v>
+        <v>2425.97</v>
       </c>
       <c r="M77" t="n">
-        <v>2510.38</v>
+        <v>2468.14</v>
       </c>
       <c r="N77" t="n">
-        <v>2564.66</v>
+        <v>2510.31</v>
       </c>
       <c r="O77" t="n">
-        <v>2576.04</v>
+        <v>2584.99</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
       </c>
-      <c r="Q77" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q77" s="6" t="n">
+        <v/>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
@@ -6963,50 +6959,50 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2417.83</v>
+        <v>2391.6</v>
       </c>
       <c r="C78" t="n">
-        <v>2427.4</v>
+        <v>2526.95</v>
       </c>
       <c r="D78" t="n">
-        <v>2356.19</v>
+        <v>2370.42</v>
       </c>
       <c r="E78" t="n">
-        <v>2391.5</v>
+        <v>2508.02</v>
       </c>
       <c r="F78" t="n">
-        <v>-26.34</v>
+        <v>116.52</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0109</v>
+        <v>0.0487</v>
       </c>
       <c r="H78" t="n">
-        <v>71.20999999999999</v>
+        <v>156.53</v>
       </c>
       <c r="I78" t="n">
-        <v>2283.21</v>
+        <v>2284.97</v>
       </c>
       <c r="J78" t="n">
-        <v>2309.12</v>
+        <v>2320.14</v>
       </c>
       <c r="K78" t="n">
-        <v>2367.54</v>
+        <v>2355.89</v>
       </c>
       <c r="L78" t="n">
-        <v>2425.97</v>
+        <v>2391.65</v>
       </c>
       <c r="M78" t="n">
-        <v>2468.14</v>
+        <v>2427.11</v>
       </c>
       <c r="N78" t="n">
-        <v>2510.31</v>
+        <v>2462.57</v>
       </c>
       <c r="O78" t="n">
-        <v>2584.99</v>
+        <v>2498.61</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -7014,28 +7010,32 @@
       <c r="Q78" s="6" t="n">
         <v/>
       </c>
-      <c r="R78" s="6" t="inlineStr">
+      <c r="R78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S78" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V78" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S78" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T78" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U78" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V78" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W78" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W78" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X78" t="inlineStr"/>
@@ -7043,50 +7043,50 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2391.6</v>
+        <v>2508.02</v>
       </c>
       <c r="C79" t="n">
-        <v>2526.95</v>
+        <v>2545.62</v>
       </c>
       <c r="D79" t="n">
-        <v>2370.42</v>
+        <v>2432.35</v>
       </c>
       <c r="E79" t="n">
-        <v>2508.02</v>
+        <v>2456.08</v>
       </c>
       <c r="F79" t="n">
-        <v>116.52</v>
+        <v>-51.94</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.0487</v>
+        <v>-0.0207</v>
       </c>
       <c r="H79" t="n">
-        <v>156.53</v>
+        <v>113.27</v>
       </c>
       <c r="I79" t="n">
-        <v>2284.97</v>
+        <v>2213.88</v>
       </c>
       <c r="J79" t="n">
-        <v>2320.14</v>
+        <v>2381.16</v>
       </c>
       <c r="K79" t="n">
-        <v>2355.89</v>
+        <v>2429.75</v>
       </c>
       <c r="L79" t="n">
-        <v>2391.65</v>
+        <v>2478.35</v>
       </c>
       <c r="M79" t="n">
-        <v>2427.11</v>
+        <v>2586.29</v>
       </c>
       <c r="N79" t="n">
-        <v>2462.57</v>
+        <v>2694.22</v>
       </c>
       <c r="O79" t="n">
-        <v>2498.61</v>
+        <v>2683.48</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7097,80 +7097,78 @@
       <c r="R79" s="6" t="n">
         <v/>
       </c>
-      <c r="S79" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U79" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V79" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S79" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U79" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V79" s="8" t="n">
+        <v/>
       </c>
       <c r="W79" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr"/>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2508.02</v>
+        <v>2455.99</v>
       </c>
       <c r="C80" t="n">
-        <v>2545.62</v>
+        <v>2492.01</v>
       </c>
       <c r="D80" t="n">
-        <v>2432.35</v>
+        <v>2445.69</v>
       </c>
       <c r="E80" t="n">
-        <v>2456.08</v>
+        <v>2480.74</v>
       </c>
       <c r="F80" t="n">
-        <v>-51.94</v>
+        <v>24.66</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.0207</v>
+        <v>0.01</v>
       </c>
       <c r="H80" t="n">
-        <v>113.27</v>
+        <v>46.32</v>
       </c>
       <c r="I80" t="n">
-        <v>2213.88</v>
+        <v>2319.08</v>
       </c>
       <c r="J80" t="n">
-        <v>2381.16</v>
+        <v>2326.35</v>
       </c>
       <c r="K80" t="n">
-        <v>2429.75</v>
+        <v>2399.44</v>
       </c>
       <c r="L80" t="n">
-        <v>2478.35</v>
+        <v>2472.53</v>
       </c>
       <c r="M80" t="n">
-        <v>2586.29</v>
+        <v>2512.71</v>
       </c>
       <c r="N80" t="n">
-        <v>2694.22</v>
+        <v>2552.89</v>
       </c>
       <c r="O80" t="n">
-        <v>2683.48</v>
+        <v>2658.89</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7181,9 +7179,9 @@
       <c r="R80" s="6" t="n">
         <v/>
       </c>
-      <c r="S80" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S80" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T80" s="8" t="n">
@@ -7209,50 +7207,50 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2455.99</v>
+        <v>2480.82</v>
       </c>
       <c r="C81" t="n">
-        <v>2492.01</v>
+        <v>2525.32</v>
       </c>
       <c r="D81" t="n">
-        <v>2445.69</v>
+        <v>2468.19</v>
       </c>
       <c r="E81" t="n">
-        <v>2480.74</v>
+        <v>2514.55</v>
       </c>
       <c r="F81" t="n">
-        <v>24.66</v>
+        <v>33.81</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0136</v>
       </c>
       <c r="H81" t="n">
-        <v>46.32</v>
+        <v>57.13</v>
       </c>
       <c r="I81" t="n">
-        <v>2319.08</v>
+        <v>2399.37</v>
       </c>
       <c r="J81" t="n">
-        <v>2326.35</v>
+        <v>2440.36</v>
       </c>
       <c r="K81" t="n">
-        <v>2399.44</v>
+        <v>2457.58</v>
       </c>
       <c r="L81" t="n">
-        <v>2472.53</v>
+        <v>2474.79</v>
       </c>
       <c r="M81" t="n">
-        <v>2512.71</v>
+        <v>2503.9</v>
       </c>
       <c r="N81" t="n">
-        <v>2552.89</v>
+        <v>2533</v>
       </c>
       <c r="O81" t="n">
-        <v>2658.89</v>
+        <v>2538.33</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7265,11 +7263,13 @@
       </c>
       <c r="S81" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U81" s="8" t="n">
         <v/>
@@ -7282,59 +7282,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2480.82</v>
+        <v>2514.58</v>
       </c>
       <c r="C82" t="n">
-        <v>2525.32</v>
+        <v>2534.86</v>
       </c>
       <c r="D82" t="n">
-        <v>2468.19</v>
+        <v>2466.91</v>
       </c>
       <c r="E82" t="n">
-        <v>2514.55</v>
+        <v>2490.96</v>
       </c>
       <c r="F82" t="n">
-        <v>33.81</v>
+        <v>-23.59</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0094</v>
       </c>
       <c r="H82" t="n">
-        <v>57.13</v>
+        <v>67.95</v>
       </c>
       <c r="I82" t="n">
-        <v>2399.37</v>
+        <v>2411.07</v>
       </c>
       <c r="J82" t="n">
-        <v>2440.36</v>
+        <v>2466.32</v>
       </c>
       <c r="K82" t="n">
-        <v>2457.58</v>
+        <v>2485.99</v>
       </c>
       <c r="L82" t="n">
-        <v>2474.79</v>
+        <v>2505.65</v>
       </c>
       <c r="M82" t="n">
-        <v>2503.9</v>
+        <v>2543.11</v>
       </c>
       <c r="N82" t="n">
-        <v>2533</v>
+        <v>2580.57</v>
       </c>
       <c r="O82" t="n">
-        <v>2538.33</v>
+        <v>2582.45</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7342,19 +7338,19 @@
       <c r="Q82" s="6" t="n">
         <v/>
       </c>
-      <c r="R82" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S82" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="inlineStr">
+      <c r="R82" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S82" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="n">
+        <v/>
+      </c>
       <c r="U82" s="8" t="n">
         <v/>
       </c>
@@ -7366,55 +7362,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr"/>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2514.58</v>
+        <v>2490.92</v>
       </c>
       <c r="C83" t="n">
-        <v>2534.86</v>
+        <v>2506.75</v>
       </c>
       <c r="D83" t="n">
-        <v>2466.91</v>
+        <v>2441.33</v>
       </c>
       <c r="E83" t="n">
-        <v>2490.96</v>
+        <v>2484.94</v>
       </c>
       <c r="F83" t="n">
-        <v>-23.59</v>
+        <v>-6.02</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0024</v>
       </c>
       <c r="H83" t="n">
-        <v>67.95</v>
+        <v>65.42</v>
       </c>
       <c r="I83" t="n">
-        <v>2411.07</v>
+        <v>2398.96</v>
       </c>
       <c r="J83" t="n">
-        <v>2466.32</v>
+        <v>2418.04</v>
       </c>
       <c r="K83" t="n">
-        <v>2485.99</v>
+        <v>2456.98</v>
       </c>
       <c r="L83" t="n">
-        <v>2505.65</v>
+        <v>2495.92</v>
       </c>
       <c r="M83" t="n">
-        <v>2543.11</v>
+        <v>2524.93</v>
       </c>
       <c r="N83" t="n">
-        <v>2580.57</v>
+        <v>2553.94</v>
       </c>
       <c r="O83" t="n">
-        <v>2582.45</v>
+        <v>2602.81</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T83" s="8" t="n">
@@ -7448,57 +7448,57 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2490.92</v>
+        <v>2484.89</v>
       </c>
       <c r="C84" t="n">
-        <v>2506.75</v>
+        <v>2522.37</v>
       </c>
       <c r="D84" t="n">
-        <v>2441.33</v>
+        <v>2443.7</v>
       </c>
       <c r="E84" t="n">
-        <v>2484.94</v>
+        <v>2466.91</v>
       </c>
       <c r="F84" t="n">
-        <v>-6.02</v>
+        <v>-18.03</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0073</v>
       </c>
       <c r="H84" t="n">
-        <v>65.42</v>
+        <v>78.67</v>
       </c>
       <c r="I84" t="n">
-        <v>2398.96</v>
+        <v>2375.9</v>
       </c>
       <c r="J84" t="n">
-        <v>2418.04</v>
+        <v>2424.97</v>
       </c>
       <c r="K84" t="n">
-        <v>2456.98</v>
+        <v>2452.23</v>
       </c>
       <c r="L84" t="n">
-        <v>2495.92</v>
+        <v>2479.49</v>
       </c>
       <c r="M84" t="n">
-        <v>2524.93</v>
+        <v>2517.65</v>
       </c>
       <c r="N84" t="n">
-        <v>2553.94</v>
+        <v>2555.82</v>
       </c>
       <c r="O84" t="n">
-        <v>2602.81</v>
+        <v>2572.18</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
@@ -7516,8 +7516,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T84" s="8" t="n">
-        <v/>
+      <c r="T84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U84" s="8" t="n">
         <v/>
@@ -7532,57 +7534,57 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2484.89</v>
+        <v>2466.91</v>
       </c>
       <c r="C85" t="n">
-        <v>2522.37</v>
+        <v>2483.72</v>
       </c>
       <c r="D85" t="n">
-        <v>2443.7</v>
+        <v>2406.91</v>
       </c>
       <c r="E85" t="n">
-        <v>2466.91</v>
+        <v>2437.1</v>
       </c>
       <c r="F85" t="n">
-        <v>-18.03</v>
+        <v>-29.82</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0121</v>
       </c>
       <c r="H85" t="n">
-        <v>78.67</v>
+        <v>76.81</v>
       </c>
       <c r="I85" t="n">
-        <v>2375.9</v>
+        <v>2365.04</v>
       </c>
       <c r="J85" t="n">
-        <v>2424.97</v>
+        <v>2380.19</v>
       </c>
       <c r="K85" t="n">
-        <v>2452.23</v>
+        <v>2427.58</v>
       </c>
       <c r="L85" t="n">
-        <v>2479.49</v>
+        <v>2474.97</v>
       </c>
       <c r="M85" t="n">
-        <v>2517.65</v>
+        <v>2506.25</v>
       </c>
       <c r="N85" t="n">
-        <v>2555.82</v>
+        <v>2537.52</v>
       </c>
       <c r="O85" t="n">
-        <v>2572.18</v>
+        <v>2601.04</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7592,18 +7594,16 @@
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="n">
+        <v/>
       </c>
       <c r="U85" s="8" t="n">
         <v/>
@@ -7618,57 +7618,57 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2466.91</v>
+        <v>2437.14</v>
       </c>
       <c r="C86" t="n">
-        <v>2483.72</v>
+        <v>2663.05</v>
       </c>
       <c r="D86" t="n">
-        <v>2406.91</v>
+        <v>2435.29</v>
       </c>
       <c r="E86" t="n">
-        <v>2437.1</v>
+        <v>2514.73</v>
       </c>
       <c r="F86" t="n">
-        <v>-29.82</v>
+        <v>77.64</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.0121</v>
+        <v>0.0319</v>
       </c>
       <c r="H86" t="n">
-        <v>76.81</v>
+        <v>227.76</v>
       </c>
       <c r="I86" t="n">
-        <v>2365.04</v>
+        <v>2330.09</v>
       </c>
       <c r="J86" t="n">
-        <v>2380.19</v>
+        <v>2356.18</v>
       </c>
       <c r="K86" t="n">
-        <v>2427.58</v>
+        <v>2398.69</v>
       </c>
       <c r="L86" t="n">
-        <v>2474.97</v>
+        <v>2441.21</v>
       </c>
       <c r="M86" t="n">
-        <v>2506.25</v>
+        <v>2475.51</v>
       </c>
       <c r="N86" t="n">
-        <v>2537.52</v>
+        <v>2509.8</v>
       </c>
       <c r="O86" t="n">
-        <v>2601.04</v>
+        <v>2560.53</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7676,83 +7676,83 @@
       <c r="Q86" s="6" t="n">
         <v/>
       </c>
-      <c r="R86" s="6" t="inlineStr">
+      <c r="R86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S86" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U86" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S86" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T86" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U86" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V86" s="8" t="n">
-        <v/>
+      <c r="V86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W86" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2437.14</v>
+        <v>2514.77</v>
       </c>
       <c r="C87" t="n">
-        <v>2663.05</v>
+        <v>2544.47</v>
       </c>
       <c r="D87" t="n">
-        <v>2435.29</v>
+        <v>2508.8</v>
       </c>
       <c r="E87" t="n">
-        <v>2514.73</v>
+        <v>2525.94</v>
       </c>
       <c r="F87" t="n">
-        <v>77.64</v>
+        <v>11.21</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.0319</v>
+        <v>0.0045</v>
       </c>
       <c r="H87" t="n">
-        <v>227.76</v>
+        <v>35.67</v>
       </c>
       <c r="I87" t="n">
-        <v>2330.09</v>
+        <v>2207.52</v>
       </c>
       <c r="J87" t="n">
-        <v>2356.18</v>
+        <v>2269.75</v>
       </c>
       <c r="K87" t="n">
-        <v>2398.69</v>
+        <v>2400.85</v>
       </c>
       <c r="L87" t="n">
-        <v>2441.21</v>
+        <v>2531.95</v>
       </c>
       <c r="M87" t="n">
-        <v>2475.51</v>
+        <v>2628.62</v>
       </c>
       <c r="N87" t="n">
-        <v>2509.8</v>
+        <v>2725.28</v>
       </c>
       <c r="O87" t="n">
-        <v>2560.53</v>
+        <v>2890.82</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7763,93 +7763,97 @@
       <c r="R87" s="6" t="n">
         <v/>
       </c>
-      <c r="S87" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U87" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S87" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V87" s="8" t="n">
+        <v/>
       </c>
       <c r="W87" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr"/>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2514.77</v>
+        <v>2525.94</v>
       </c>
       <c r="C88" t="n">
-        <v>2544.47</v>
+        <v>2526.85</v>
       </c>
       <c r="D88" t="n">
-        <v>2508.8</v>
+        <v>2462.84</v>
       </c>
       <c r="E88" t="n">
-        <v>2525.94</v>
+        <v>2477.02</v>
       </c>
       <c r="F88" t="n">
-        <v>11.21</v>
+        <v>-48.92</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0194</v>
       </c>
       <c r="H88" t="n">
-        <v>35.67</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>2207.52</v>
+        <v>2473.13</v>
       </c>
       <c r="J88" t="n">
-        <v>2269.75</v>
+        <v>2489.93</v>
       </c>
       <c r="K88" t="n">
-        <v>2400.85</v>
+        <v>2508.11</v>
       </c>
       <c r="L88" t="n">
-        <v>2531.95</v>
+        <v>2526.29</v>
       </c>
       <c r="M88" t="n">
-        <v>2628.62</v>
+        <v>2543.78</v>
       </c>
       <c r="N88" t="n">
-        <v>2725.28</v>
+        <v>2561.27</v>
       </c>
       <c r="O88" t="n">
-        <v>2890.82</v>
-      </c>
-      <c r="P88" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q88" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R88" s="6" t="n">
-        <v/>
+        <v>2580.14</v>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T88" s="8" t="n">
@@ -7861,297 +7865,209 @@
       <c r="V88" s="8" t="n">
         <v/>
       </c>
-      <c r="W88" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W88" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2525.94</v>
+        <v>2476.6</v>
       </c>
       <c r="C89" t="n">
-        <v>2526.85</v>
+        <v>2612.4</v>
       </c>
       <c r="D89" t="n">
-        <v>2462.84</v>
+        <v>2465.43</v>
       </c>
       <c r="E89" t="n">
-        <v>2477.02</v>
+        <v>2514.41</v>
       </c>
       <c r="F89" t="n">
-        <v>-48.92</v>
+        <v>37.39</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-0.0194</v>
+        <v>0.0151</v>
       </c>
       <c r="H89" t="n">
-        <v>64.01000000000001</v>
+        <v>146.98</v>
       </c>
       <c r="I89" t="n">
-        <v>2473.13</v>
+        <v>2398.83</v>
       </c>
       <c r="J89" t="n">
-        <v>2489.93</v>
+        <v>2404.09</v>
       </c>
       <c r="K89" t="n">
-        <v>2508.11</v>
+        <v>2445.01</v>
       </c>
       <c r="L89" t="n">
-        <v>2526.29</v>
+        <v>2485.93</v>
       </c>
       <c r="M89" t="n">
-        <v>2543.78</v>
+        <v>2509.03</v>
       </c>
       <c r="N89" t="n">
-        <v>2561.27</v>
+        <v>2532.12</v>
       </c>
       <c r="O89" t="n">
-        <v>2580.14</v>
-      </c>
-      <c r="P89" s="6" t="inlineStr">
+        <v>2590.87</v>
+      </c>
+      <c r="P89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S89" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q89" s="6" t="inlineStr">
+      <c r="U89" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R89" s="6" t="inlineStr">
+      <c r="V89" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S89" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V89" s="8" t="n">
-        <v/>
-      </c>
       <c r="W89" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr"/>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2476.6</v>
+        <v>2397.64</v>
       </c>
       <c r="C90" t="n">
-        <v>2612.4</v>
+        <v>2404.25</v>
       </c>
       <c r="D90" t="n">
-        <v>2465.43</v>
+        <v>2389.14</v>
       </c>
       <c r="E90" t="n">
-        <v>2514.41</v>
+        <v>2390.21</v>
       </c>
       <c r="F90" t="n">
-        <v>37.39</v>
+        <v>-124.2</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.0494</v>
       </c>
       <c r="H90" t="n">
-        <v>146.98</v>
+        <v>15.11</v>
       </c>
       <c r="I90" t="n">
-        <v>2398.83</v>
+        <v>2318.45</v>
       </c>
       <c r="J90" t="n">
-        <v>2404.09</v>
+        <v>2355.18</v>
       </c>
       <c r="K90" t="n">
-        <v>2445.01</v>
+        <v>2440.92</v>
       </c>
       <c r="L90" t="n">
-        <v>2485.93</v>
+        <v>2526.66</v>
       </c>
       <c r="M90" t="n">
-        <v>2509.03</v>
+        <v>2587.9</v>
       </c>
       <c r="N90" t="n">
-        <v>2532.12</v>
+        <v>2649.13</v>
       </c>
       <c r="O90" t="n">
-        <v>2590.87</v>
+        <v>2759.38</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
       </c>
-      <c r="Q90" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R90" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S90" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="inlineStr">
+      <c r="Q90" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U90" s="8" t="inlineStr">
+      <c r="R90" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S90" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U90" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V90" s="8" t="n">
+        <v/>
       </c>
       <c r="W90" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>2515.17</v>
-      </c>
-      <c r="C91" t="n">
-        <v>2518.69</v>
-      </c>
-      <c r="D91" t="n">
-        <v>2358.66</v>
-      </c>
-      <c r="E91" t="n">
-        <v>2387.94</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-126.47</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>-0.0503</v>
-      </c>
-      <c r="H91" t="n">
-        <v>160.03</v>
-      </c>
-      <c r="I91" t="n">
-        <v>2318.45</v>
-      </c>
-      <c r="J91" t="n">
-        <v>2355.18</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2440.92</v>
-      </c>
-      <c r="L91" t="n">
-        <v>2526.66</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2587.9</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2649.13</v>
-      </c>
-      <c r="O91" t="n">
-        <v>2759.38</v>
-      </c>
-      <c r="P91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q91" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R91" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S91" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W91" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I92" s="13" t="n">
-        <v>2198.62</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>2202.54</v>
-      </c>
-      <c r="K92" s="13" t="n">
-        <v>2307.92</v>
-      </c>
-      <c r="L92" s="13" t="n">
-        <v>2413.31</v>
-      </c>
-      <c r="M92" s="13" t="n">
-        <v>2467.96</v>
-      </c>
-      <c r="N92" s="13" t="n">
-        <v>2522.61</v>
-      </c>
-      <c r="O92" s="13" t="n">
-        <v>2678.72</v>
+      <c r="I91" s="13" t="n">
+        <v>2374.02</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>2371.85</v>
+      </c>
+      <c r="K91" s="13" t="n">
+        <v>2382.65</v>
+      </c>
+      <c r="L91" s="13" t="n">
+        <v>2393.45</v>
+      </c>
+      <c r="M91" s="13" t="n">
+        <v>2397.77</v>
+      </c>
+      <c r="N91" s="13" t="n">
+        <v>2402.08</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>2419.36</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -7970,22 +7970,22 @@
         <v>2397.64</v>
       </c>
       <c r="C90" t="n">
-        <v>2404.25</v>
+        <v>2408.58</v>
       </c>
       <c r="D90" t="n">
-        <v>2389.14</v>
+        <v>2389.89</v>
       </c>
       <c r="E90" t="n">
-        <v>2390.21</v>
+        <v>2405.93</v>
       </c>
       <c r="F90" t="n">
-        <v>-124.2</v>
+        <v>-108.48</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0494</v>
+        <v>-0.0431</v>
       </c>
       <c r="H90" t="n">
-        <v>15.11</v>
+        <v>18.7</v>
       </c>
       <c r="I90" t="n">
         <v>2318.45</v>
@@ -8011,14 +8011,12 @@
       <c r="P90" s="6" t="n">
         <v/>
       </c>
-      <c r="Q90" s="6" t="inlineStr">
+      <c r="Q90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R90" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S90" s="7" t="inlineStr">
@@ -8049,25 +8047,25 @@
         </is>
       </c>
       <c r="I91" s="13" t="n">
-        <v>2374.02</v>
+        <v>2371.19</v>
       </c>
       <c r="J91" s="13" t="n">
-        <v>2371.85</v>
+        <v>2390.58</v>
       </c>
       <c r="K91" s="13" t="n">
-        <v>2382.65</v>
+        <v>2396.58</v>
       </c>
       <c r="L91" s="13" t="n">
-        <v>2393.45</v>
+        <v>2402.58</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>2397.77</v>
+        <v>2415.28</v>
       </c>
       <c r="N91" s="13" t="n">
-        <v>2402.08</v>
+        <v>2427.97</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>2419.36</v>
+        <v>2427.28</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X91"/>
+  <dimension ref="A1:X92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7963,29 +7963,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2397.64</v>
+        <v>2514.36</v>
       </c>
       <c r="C90" t="n">
-        <v>2408.58</v>
+        <v>2519.32</v>
       </c>
       <c r="D90" t="n">
-        <v>2389.89</v>
+        <v>2357.96</v>
       </c>
       <c r="E90" t="n">
-        <v>2405.93</v>
+        <v>2399.09</v>
       </c>
       <c r="F90" t="n">
-        <v>-108.48</v>
+        <v>-115.32</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0431</v>
+        <v>-0.0459</v>
       </c>
       <c r="H90" t="n">
-        <v>18.7</v>
+        <v>161.36</v>
       </c>
       <c r="I90" t="n">
         <v>2318.45</v>
@@ -8041,31 +8041,113 @@
       <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="inlineStr">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2397.64</v>
+      </c>
+      <c r="C91" t="n">
+        <v>2411.55</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2385.07</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2411.88</v>
+      </c>
+      <c r="F91" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="H91" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2196.6</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2217.95</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2318.41</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2418.86</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2479.77</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2540.67</v>
+      </c>
+      <c r="O91" t="n">
+        <v>2680.68</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W91" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I91" s="13" t="n">
-        <v>2371.19</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>2390.58</v>
-      </c>
-      <c r="K91" s="13" t="n">
-        <v>2396.58</v>
-      </c>
-      <c r="L91" s="13" t="n">
-        <v>2402.58</v>
-      </c>
-      <c r="M91" s="13" t="n">
-        <v>2415.28</v>
-      </c>
-      <c r="N91" s="13" t="n">
-        <v>2427.97</v>
-      </c>
-      <c r="O91" s="13" t="n">
-        <v>2427.28</v>
+      <c r="I92" s="13" t="n">
+        <v>2358.58</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>2392.18</v>
+      </c>
+      <c r="K92" s="13" t="n">
+        <v>2398.64</v>
+      </c>
+      <c r="L92" s="13" t="n">
+        <v>2405.1</v>
+      </c>
+      <c r="M92" s="13" t="n">
+        <v>2425.12</v>
+      </c>
+      <c r="N92" s="13" t="n">
+        <v>2445.15</v>
+      </c>
+      <c r="O92" s="13" t="n">
+        <v>2438.04</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -8050,22 +8050,22 @@
         <v>2397.64</v>
       </c>
       <c r="C91" t="n">
-        <v>2411.55</v>
+        <v>2424.1</v>
       </c>
       <c r="D91" t="n">
         <v>2385.07</v>
       </c>
       <c r="E91" t="n">
-        <v>2411.88</v>
+        <v>2417.66</v>
       </c>
       <c r="F91" t="n">
-        <v>12.79</v>
+        <v>18.57</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.0077</v>
       </c>
       <c r="H91" t="n">
-        <v>26.49</v>
+        <v>39.03</v>
       </c>
       <c r="I91" t="n">
         <v>2196.6</v>
@@ -8129,25 +8129,25 @@
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>2358.58</v>
+        <v>2346.03</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>2392.18</v>
+        <v>2385.17</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>2398.64</v>
+        <v>2398.14</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>2405.1</v>
+        <v>2411.12</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>2425.12</v>
+        <v>2437.18</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>2445.15</v>
+        <v>2463.23</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>2438.04</v>
+        <v>2463.13</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -8056,13 +8056,13 @@
         <v>2385.07</v>
       </c>
       <c r="E91" t="n">
-        <v>2417.66</v>
+        <v>2412.24</v>
       </c>
       <c r="F91" t="n">
-        <v>18.57</v>
+        <v>13.15</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H91" t="n">
         <v>39.03</v>
@@ -8132,19 +8132,19 @@
         <v>2346.03</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>2385.17</v>
+        <v>2377.04</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>2398.14</v>
+        <v>2392.72</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>2411.12</v>
+        <v>2408.41</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>2437.18</v>
+        <v>2431.76</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>2463.23</v>
+        <v>2455.1</v>
       </c>
       <c r="O92" s="13" t="n">
         <v>2463.13</v>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -8053,19 +8053,19 @@
         <v>2424.1</v>
       </c>
       <c r="D91" t="n">
-        <v>2385.07</v>
+        <v>2370.11</v>
       </c>
       <c r="E91" t="n">
-        <v>2412.24</v>
+        <v>2396.95</v>
       </c>
       <c r="F91" t="n">
-        <v>13.15</v>
+        <v>-2.14</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.0009</v>
       </c>
       <c r="H91" t="n">
-        <v>39.03</v>
+        <v>53.99</v>
       </c>
       <c r="I91" t="n">
         <v>2196.6</v>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -8129,25 +8129,25 @@
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>2346.03</v>
+        <v>2316.12</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>2377.04</v>
+        <v>2342.88</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>2392.72</v>
+        <v>2369.95</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>2408.41</v>
+        <v>2397.03</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>2431.76</v>
+        <v>2423.95</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>2455.1</v>
+        <v>2450.86</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>2463.13</v>
+        <v>2478.09</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1709.5</v>
+        <v>1710.98</v>
       </c>
       <c r="C2" t="n">
-        <v>1717.19</v>
+        <v>1747.26</v>
       </c>
       <c r="D2" t="n">
-        <v>1678.2</v>
+        <v>1702.8</v>
       </c>
       <c r="E2" t="n">
-        <v>1710.98</v>
+        <v>1739.3</v>
       </c>
       <c r="F2" t="n">
-        <v>1.45</v>
+        <v>28.32</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0008</v>
+        <v>0.0166</v>
       </c>
       <c r="H2" t="n">
-        <v>39</v>
+        <v>44.46</v>
       </c>
       <c r="I2" t="n">
-        <v>1579.33</v>
+        <v>1639.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1615.78</v>
+        <v>1678.63</v>
       </c>
       <c r="K2" t="n">
-        <v>1664.14</v>
+        <v>1691.48</v>
       </c>
       <c r="L2" t="n">
-        <v>1712.51</v>
+        <v>1704.34</v>
       </c>
       <c r="M2" t="n">
-        <v>1754.92</v>
+        <v>1730.48</v>
       </c>
       <c r="N2" t="n">
-        <v>1797.33</v>
+        <v>1756.62</v>
       </c>
       <c r="O2" t="n">
-        <v>1851.66</v>
+        <v>1756.19</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -697,11 +697,13 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -714,78 +716,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1710.98</v>
+        <v>1739.34</v>
       </c>
       <c r="C3" t="n">
-        <v>1747.26</v>
+        <v>1739.49</v>
       </c>
       <c r="D3" t="n">
-        <v>1702.8</v>
+        <v>1701.94</v>
       </c>
       <c r="E3" t="n">
-        <v>1739.3</v>
+        <v>1704.58</v>
       </c>
       <c r="F3" t="n">
-        <v>28.32</v>
+        <v>-34.72</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.02</v>
       </c>
       <c r="H3" t="n">
-        <v>44.46</v>
+        <v>37.55</v>
       </c>
       <c r="I3" t="n">
-        <v>1639.2</v>
+        <v>1658.34</v>
       </c>
       <c r="J3" t="n">
-        <v>1678.63</v>
+        <v>1701.98</v>
       </c>
       <c r="K3" t="n">
-        <v>1691.48</v>
+        <v>1717.07</v>
       </c>
       <c r="L3" t="n">
-        <v>1704.34</v>
+        <v>1732.17</v>
       </c>
       <c r="M3" t="n">
-        <v>1730.48</v>
+        <v>1761.53</v>
       </c>
       <c r="N3" t="n">
-        <v>1756.62</v>
+        <v>1790.89</v>
       </c>
       <c r="O3" t="n">
-        <v>1756.19</v>
+        <v>1791.72</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -798,80 +798,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1739.34</v>
+        <v>1704.63</v>
       </c>
       <c r="C4" t="n">
-        <v>1739.49</v>
+        <v>1776.83</v>
       </c>
       <c r="D4" t="n">
-        <v>1701.94</v>
+        <v>1704.52</v>
       </c>
       <c r="E4" t="n">
-        <v>1704.58</v>
+        <v>1726.51</v>
       </c>
       <c r="F4" t="n">
-        <v>-34.72</v>
+        <v>21.93</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0129</v>
       </c>
       <c r="H4" t="n">
-        <v>37.55</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>1658.34</v>
+        <v>1664.39</v>
       </c>
       <c r="J4" t="n">
-        <v>1701.98</v>
+        <v>1658.97</v>
       </c>
       <c r="K4" t="n">
-        <v>1717.07</v>
+        <v>1685.81</v>
       </c>
       <c r="L4" t="n">
-        <v>1732.17</v>
+        <v>1712.65</v>
       </c>
       <c r="M4" t="n">
-        <v>1761.53</v>
+        <v>1723.36</v>
       </c>
       <c r="N4" t="n">
-        <v>1790.89</v>
+        <v>1734.06</v>
       </c>
       <c r="O4" t="n">
-        <v>1791.72</v>
+        <v>1777.04</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
@@ -880,83 +884,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1704.63</v>
+        <v>1726.52</v>
       </c>
       <c r="C5" t="n">
-        <v>1776.83</v>
+        <v>1733.61</v>
       </c>
       <c r="D5" t="n">
-        <v>1704.52</v>
+        <v>1638.25</v>
       </c>
       <c r="E5" t="n">
-        <v>1726.51</v>
+        <v>1665.44</v>
       </c>
       <c r="F5" t="n">
-        <v>21.93</v>
+        <v>-61.07</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0354</v>
       </c>
       <c r="H5" t="n">
-        <v>72.31999999999999</v>
+        <v>95.36</v>
       </c>
       <c r="I5" t="n">
-        <v>1664.39</v>
+        <v>1632.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1658.97</v>
+        <v>1647.11</v>
       </c>
       <c r="K5" t="n">
-        <v>1685.81</v>
+        <v>1690.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1712.65</v>
+        <v>1733.59</v>
       </c>
       <c r="M5" t="n">
-        <v>1723.36</v>
+        <v>1762.67</v>
       </c>
       <c r="N5" t="n">
-        <v>1734.06</v>
+        <v>1791.74</v>
       </c>
       <c r="O5" t="n">
-        <v>1777.04</v>
+        <v>1849.15</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -966,70 +966,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1726.52</v>
+        <v>1665.31</v>
       </c>
       <c r="C6" t="n">
-        <v>1733.61</v>
+        <v>1687.49</v>
       </c>
       <c r="D6" t="n">
-        <v>1638.25</v>
+        <v>1551.48</v>
       </c>
       <c r="E6" t="n">
-        <v>1665.44</v>
+        <v>1619.92</v>
       </c>
       <c r="F6" t="n">
-        <v>-61.07</v>
+        <v>-45.51</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0354</v>
+        <v>-0.0273</v>
       </c>
       <c r="H6" t="n">
-        <v>95.36</v>
+        <v>136.01</v>
       </c>
       <c r="I6" t="n">
-        <v>1632.2</v>
+        <v>1542.89</v>
       </c>
       <c r="J6" t="n">
-        <v>1647.11</v>
+        <v>1559.83</v>
       </c>
       <c r="K6" t="n">
-        <v>1690.35</v>
+        <v>1617.76</v>
       </c>
       <c r="L6" t="n">
-        <v>1733.59</v>
+        <v>1675.68</v>
       </c>
       <c r="M6" t="n">
-        <v>1762.67</v>
+        <v>1713.12</v>
       </c>
       <c r="N6" t="n">
-        <v>1791.74</v>
+        <v>1750.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1849.15</v>
+        <v>1828.97</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
       <c r="Q6" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1057,65 +1061,63 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1665.31</v>
+        <v>1619.89</v>
       </c>
       <c r="C7" t="n">
-        <v>1687.49</v>
+        <v>1656.65</v>
       </c>
       <c r="D7" t="n">
-        <v>1551.48</v>
+        <v>1531.78</v>
       </c>
       <c r="E7" t="n">
-        <v>1619.92</v>
+        <v>1564.82</v>
       </c>
       <c r="F7" t="n">
-        <v>-45.51</v>
+        <v>-55.11</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.034</v>
       </c>
       <c r="H7" t="n">
-        <v>136.01</v>
+        <v>124.87</v>
       </c>
       <c r="I7" t="n">
-        <v>1542.89</v>
+        <v>1415.48</v>
       </c>
       <c r="J7" t="n">
-        <v>1559.83</v>
+        <v>1484.14</v>
       </c>
       <c r="K7" t="n">
-        <v>1617.76</v>
+        <v>1551.92</v>
       </c>
       <c r="L7" t="n">
-        <v>1675.68</v>
+        <v>1619.71</v>
       </c>
       <c r="M7" t="n">
-        <v>1713.12</v>
+        <v>1687.93</v>
       </c>
       <c r="N7" t="n">
-        <v>1750.55</v>
+        <v>1756.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1828.97</v>
+        <v>1823.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q7" s="6" t="n">
+        <v/>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1143,50 +1145,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1619.89</v>
+        <v>1564.61</v>
       </c>
       <c r="C8" t="n">
-        <v>1656.65</v>
+        <v>1590.2</v>
       </c>
       <c r="D8" t="n">
-        <v>1531.78</v>
+        <v>1510.51</v>
       </c>
       <c r="E8" t="n">
-        <v>1564.82</v>
+        <v>1576.62</v>
       </c>
       <c r="F8" t="n">
-        <v>-55.11</v>
+        <v>11.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.034</v>
+        <v>0.0075</v>
       </c>
       <c r="H8" t="n">
-        <v>124.87</v>
+        <v>79.69</v>
       </c>
       <c r="I8" t="n">
-        <v>1415.48</v>
+        <v>1406.91</v>
       </c>
       <c r="J8" t="n">
-        <v>1484.14</v>
+        <v>1425.25</v>
       </c>
       <c r="K8" t="n">
-        <v>1551.92</v>
+        <v>1502.38</v>
       </c>
       <c r="L8" t="n">
-        <v>1619.71</v>
+        <v>1579.52</v>
       </c>
       <c r="M8" t="n">
-        <v>1687.93</v>
+        <v>1627.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1756.15</v>
+        <v>1674.98</v>
       </c>
       <c r="O8" t="n">
-        <v>1823.5</v>
+        <v>1781.51</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1194,14 +1196,12 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1220,57 +1220,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1564.61</v>
+        <v>1576.59</v>
       </c>
       <c r="C9" t="n">
-        <v>1590.2</v>
+        <v>1607.87</v>
       </c>
       <c r="D9" t="n">
-        <v>1510.51</v>
+        <v>1561.97</v>
       </c>
       <c r="E9" t="n">
-        <v>1576.62</v>
+        <v>1571.59</v>
       </c>
       <c r="F9" t="n">
-        <v>11.8</v>
+        <v>-5.03</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0032</v>
       </c>
       <c r="H9" t="n">
-        <v>79.69</v>
+        <v>45.89</v>
       </c>
       <c r="I9" t="n">
-        <v>1406.91</v>
+        <v>1430.81</v>
       </c>
       <c r="J9" t="n">
-        <v>1425.25</v>
+        <v>1510.05</v>
       </c>
       <c r="K9" t="n">
-        <v>1502.38</v>
+        <v>1536.77</v>
       </c>
       <c r="L9" t="n">
-        <v>1579.52</v>
+        <v>1563.48</v>
       </c>
       <c r="M9" t="n">
-        <v>1627.25</v>
+        <v>1616.46</v>
       </c>
       <c r="N9" t="n">
-        <v>1674.98</v>
+        <v>1669.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1781.51</v>
+        <v>1669.89</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1302,57 +1302,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1576.59</v>
+        <v>1571.56</v>
       </c>
       <c r="C10" t="n">
-        <v>1607.87</v>
+        <v>1585.22</v>
       </c>
       <c r="D10" t="n">
-        <v>1561.97</v>
+        <v>1548.76</v>
       </c>
       <c r="E10" t="n">
-        <v>1571.59</v>
+        <v>1570.36</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.03</v>
+        <v>-1.23</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.0008</v>
       </c>
       <c r="H10" t="n">
-        <v>45.89</v>
+        <v>36.46</v>
       </c>
       <c r="I10" t="n">
-        <v>1430.81</v>
+        <v>1516.08</v>
       </c>
       <c r="J10" t="n">
-        <v>1510.05</v>
+        <v>1519.03</v>
       </c>
       <c r="K10" t="n">
-        <v>1536.77</v>
+        <v>1548.64</v>
       </c>
       <c r="L10" t="n">
-        <v>1563.48</v>
+        <v>1578.25</v>
       </c>
       <c r="M10" t="n">
-        <v>1616.46</v>
+        <v>1594.53</v>
       </c>
       <c r="N10" t="n">
-        <v>1669.44</v>
+        <v>1610.82</v>
       </c>
       <c r="O10" t="n">
-        <v>1669.89</v>
+        <v>1653.76</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1384,57 +1384,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1571.56</v>
+        <v>1569.99</v>
       </c>
       <c r="C11" t="n">
-        <v>1585.22</v>
+        <v>1633.65</v>
       </c>
       <c r="D11" t="n">
-        <v>1548.76</v>
+        <v>1550.04</v>
       </c>
       <c r="E11" t="n">
-        <v>1570.36</v>
+        <v>1610.21</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.23</v>
+        <v>39.84</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0254</v>
       </c>
       <c r="H11" t="n">
-        <v>36.46</v>
+        <v>83.61</v>
       </c>
       <c r="I11" t="n">
-        <v>1516.08</v>
+        <v>1512.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1519.03</v>
+        <v>1535.59</v>
       </c>
       <c r="K11" t="n">
-        <v>1548.64</v>
+        <v>1552.13</v>
       </c>
       <c r="L11" t="n">
-        <v>1578.25</v>
+        <v>1568.68</v>
       </c>
       <c r="M11" t="n">
-        <v>1594.53</v>
+        <v>1588.59</v>
       </c>
       <c r="N11" t="n">
-        <v>1610.82</v>
+        <v>1608.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1653.76</v>
+        <v>1621.68</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,81 +1442,85 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1569.99</v>
+        <v>1610.16</v>
       </c>
       <c r="C12" t="n">
-        <v>1633.65</v>
+        <v>1611.35</v>
       </c>
       <c r="D12" t="n">
-        <v>1550.04</v>
+        <v>1549.25</v>
       </c>
       <c r="E12" t="n">
-        <v>1610.21</v>
+        <v>1569.58</v>
       </c>
       <c r="F12" t="n">
-        <v>39.84</v>
+        <v>-40.62</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0254</v>
+        <v>-0.0252</v>
       </c>
       <c r="H12" t="n">
-        <v>83.61</v>
+        <v>62.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1512.3</v>
+        <v>1466.43</v>
       </c>
       <c r="J12" t="n">
-        <v>1535.59</v>
+        <v>1535.78</v>
       </c>
       <c r="K12" t="n">
-        <v>1552.13</v>
+        <v>1568.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1568.68</v>
+        <v>1601.02</v>
       </c>
       <c r="M12" t="n">
-        <v>1588.59</v>
+        <v>1652.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1608.5</v>
+        <v>1703</v>
       </c>
       <c r="O12" t="n">
-        <v>1621.68</v>
+        <v>1717.25</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1526,83 +1530,81 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1610.16</v>
+        <v>1569.91</v>
       </c>
       <c r="C13" t="n">
-        <v>1611.35</v>
+        <v>1642.45</v>
       </c>
       <c r="D13" t="n">
-        <v>1549.25</v>
+        <v>1551.14</v>
       </c>
       <c r="E13" t="n">
-        <v>1569.58</v>
+        <v>1608.96</v>
       </c>
       <c r="F13" t="n">
-        <v>-40.62</v>
+        <v>39.38</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0252</v>
+        <v>0.0251</v>
       </c>
       <c r="H13" t="n">
-        <v>62.1</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>1466.43</v>
+        <v>1487.16</v>
       </c>
       <c r="J13" t="n">
-        <v>1535.78</v>
+        <v>1502.13</v>
       </c>
       <c r="K13" t="n">
-        <v>1568.4</v>
+        <v>1538.54</v>
       </c>
       <c r="L13" t="n">
-        <v>1601.02</v>
+        <v>1574.94</v>
       </c>
       <c r="M13" t="n">
-        <v>1652.01</v>
+        <v>1600.63</v>
       </c>
       <c r="N13" t="n">
-        <v>1703</v>
+        <v>1626.32</v>
       </c>
       <c r="O13" t="n">
-        <v>1717.25</v>
+        <v>1673.44</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1610,21 +1612,23 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1634,59 +1638,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1569.91</v>
+        <v>1609.01</v>
       </c>
       <c r="C14" t="n">
-        <v>1642.45</v>
+        <v>1720.34</v>
       </c>
       <c r="D14" t="n">
-        <v>1551.14</v>
+        <v>1595.94</v>
       </c>
       <c r="E14" t="n">
-        <v>1608.96</v>
+        <v>1698.17</v>
       </c>
       <c r="F14" t="n">
-        <v>39.38</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0554</v>
       </c>
       <c r="H14" t="n">
-        <v>91.31999999999999</v>
+        <v>124.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1487.16</v>
+        <v>1459.82</v>
       </c>
       <c r="J14" t="n">
-        <v>1502.13</v>
+        <v>1523.73</v>
       </c>
       <c r="K14" t="n">
-        <v>1538.54</v>
+        <v>1563.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1574.94</v>
+        <v>1602.88</v>
       </c>
       <c r="M14" t="n">
-        <v>1600.63</v>
+        <v>1654.62</v>
       </c>
       <c r="N14" t="n">
-        <v>1626.32</v>
+        <v>1706.36</v>
       </c>
       <c r="O14" t="n">
-        <v>1673.44</v>
+        <v>1733.77</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1697,19 +1697,19 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V14" s="8" t="n">
@@ -1725,50 +1725,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1609.01</v>
+        <v>1698.42</v>
       </c>
       <c r="C15" t="n">
-        <v>1720.34</v>
+        <v>1772.54</v>
       </c>
       <c r="D15" t="n">
-        <v>1595.94</v>
+        <v>1693.04</v>
       </c>
       <c r="E15" t="n">
-        <v>1698.17</v>
+        <v>1756.52</v>
       </c>
       <c r="F15" t="n">
-        <v>89.20999999999999</v>
+        <v>58.35</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0344</v>
       </c>
       <c r="H15" t="n">
-        <v>124.4</v>
+        <v>79.5</v>
       </c>
       <c r="I15" t="n">
-        <v>1459.82</v>
+        <v>1471.54</v>
       </c>
       <c r="J15" t="n">
-        <v>1523.73</v>
+        <v>1593.78</v>
       </c>
       <c r="K15" t="n">
-        <v>1563.3</v>
+        <v>1635.97</v>
       </c>
       <c r="L15" t="n">
-        <v>1602.88</v>
+        <v>1678.16</v>
       </c>
       <c r="M15" t="n">
-        <v>1654.62</v>
+        <v>1760.37</v>
       </c>
       <c r="N15" t="n">
-        <v>1706.36</v>
+        <v>1842.59</v>
       </c>
       <c r="O15" t="n">
-        <v>1733.77</v>
+        <v>1844.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1779,20 +1779,18 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1807,50 +1805,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1698.42</v>
+        <v>1756.58</v>
       </c>
       <c r="C16" t="n">
-        <v>1772.54</v>
+        <v>1804.59</v>
       </c>
       <c r="D16" t="n">
-        <v>1693.04</v>
+        <v>1743.56</v>
       </c>
       <c r="E16" t="n">
-        <v>1756.52</v>
+        <v>1779.03</v>
       </c>
       <c r="F16" t="n">
-        <v>58.35</v>
+        <v>22.51</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0128</v>
       </c>
       <c r="H16" t="n">
-        <v>79.5</v>
+        <v>61.02</v>
       </c>
       <c r="I16" t="n">
-        <v>1471.54</v>
+        <v>1613.53</v>
       </c>
       <c r="J16" t="n">
-        <v>1593.78</v>
+        <v>1688.88</v>
       </c>
       <c r="K16" t="n">
-        <v>1635.97</v>
+        <v>1716.77</v>
       </c>
       <c r="L16" t="n">
-        <v>1678.16</v>
+        <v>1744.65</v>
       </c>
       <c r="M16" t="n">
-        <v>1760.37</v>
+        <v>1796.27</v>
       </c>
       <c r="N16" t="n">
-        <v>1842.59</v>
+        <v>1847.89</v>
       </c>
       <c r="O16" t="n">
-        <v>1844.75</v>
+        <v>1852.05</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1861,7 +1859,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1887,50 +1885,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1756.58</v>
+        <v>1779.04</v>
       </c>
       <c r="C17" t="n">
-        <v>1804.59</v>
+        <v>1805.91</v>
       </c>
       <c r="D17" t="n">
-        <v>1743.56</v>
+        <v>1749.14</v>
       </c>
       <c r="E17" t="n">
-        <v>1779.03</v>
+        <v>1783.01</v>
       </c>
       <c r="F17" t="n">
-        <v>22.51</v>
+        <v>3.97</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0022</v>
       </c>
       <c r="H17" t="n">
-        <v>61.02</v>
+        <v>56.78</v>
       </c>
       <c r="I17" t="n">
-        <v>1613.53</v>
+        <v>1682.54</v>
       </c>
       <c r="J17" t="n">
-        <v>1688.88</v>
+        <v>1720.49</v>
       </c>
       <c r="K17" t="n">
-        <v>1716.77</v>
+        <v>1748.52</v>
       </c>
       <c r="L17" t="n">
-        <v>1744.65</v>
+        <v>1776.55</v>
       </c>
       <c r="M17" t="n">
-        <v>1796.27</v>
+        <v>1809.55</v>
       </c>
       <c r="N17" t="n">
-        <v>1847.89</v>
+        <v>1842.54</v>
       </c>
       <c r="O17" t="n">
-        <v>1852.05</v>
+        <v>1865.61</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1941,15 +1939,13 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1967,67 +1963,73 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779.04</v>
+        <v>1783</v>
       </c>
       <c r="C18" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D18" t="n">
-        <v>1749.14</v>
+        <v>1728.97</v>
       </c>
       <c r="E18" t="n">
-        <v>1783.01</v>
+        <v>1797.57</v>
       </c>
       <c r="F18" t="n">
-        <v>3.97</v>
+        <v>14.57</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>56.78</v>
+        <v>100.55</v>
       </c>
       <c r="I18" t="n">
-        <v>1682.54</v>
+        <v>1692.36</v>
       </c>
       <c r="J18" t="n">
-        <v>1720.49</v>
+        <v>1728.97</v>
       </c>
       <c r="K18" t="n">
-        <v>1748.52</v>
+        <v>1754.62</v>
       </c>
       <c r="L18" t="n">
-        <v>1776.55</v>
+        <v>1780.27</v>
       </c>
       <c r="M18" t="n">
-        <v>1809.55</v>
+        <v>1811.39</v>
       </c>
       <c r="N18" t="n">
-        <v>1842.54</v>
+        <v>1842.52</v>
       </c>
       <c r="O18" t="n">
-        <v>1865.61</v>
+        <v>1862.69</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2040,78 +2042,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1783</v>
+        <v>1797.56</v>
       </c>
       <c r="C19" t="n">
-        <v>1829.51</v>
+        <v>1810.33</v>
       </c>
       <c r="D19" t="n">
-        <v>1728.97</v>
+        <v>1756.71</v>
       </c>
       <c r="E19" t="n">
-        <v>1797.57</v>
+        <v>1768.51</v>
       </c>
       <c r="F19" t="n">
-        <v>14.57</v>
+        <v>-29.06</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0162</v>
       </c>
       <c r="H19" t="n">
-        <v>100.55</v>
+        <v>53.62</v>
       </c>
       <c r="I19" t="n">
-        <v>1692.36</v>
+        <v>1628.42</v>
       </c>
       <c r="J19" t="n">
-        <v>1728.97</v>
+        <v>1706.19</v>
       </c>
       <c r="K19" t="n">
-        <v>1754.62</v>
+        <v>1747.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1780.27</v>
+        <v>1788.41</v>
       </c>
       <c r="M19" t="n">
-        <v>1811.39</v>
+        <v>1847.85</v>
       </c>
       <c r="N19" t="n">
-        <v>1842.52</v>
+        <v>1907.29</v>
       </c>
       <c r="O19" t="n">
-        <v>1862.69</v>
+        <v>1930.06</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2126,57 +2126,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1797.56</v>
+        <v>1768.39</v>
       </c>
       <c r="C20" t="n">
-        <v>1810.33</v>
+        <v>1782.86</v>
       </c>
       <c r="D20" t="n">
-        <v>1756.71</v>
+        <v>1711.9</v>
       </c>
       <c r="E20" t="n">
-        <v>1768.51</v>
+        <v>1742.68</v>
       </c>
       <c r="F20" t="n">
-        <v>-29.06</v>
+        <v>-25.83</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0146</v>
       </c>
       <c r="H20" t="n">
-        <v>53.62</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>1628.42</v>
+        <v>1703.1</v>
       </c>
       <c r="J20" t="n">
-        <v>1706.19</v>
+        <v>1707.39</v>
       </c>
       <c r="K20" t="n">
-        <v>1747.3</v>
+        <v>1741.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1788.41</v>
+        <v>1776.02</v>
       </c>
       <c r="M20" t="n">
-        <v>1847.85</v>
+        <v>1795.32</v>
       </c>
       <c r="N20" t="n">
-        <v>1907.29</v>
+        <v>1814.62</v>
       </c>
       <c r="O20" t="n">
-        <v>1930.06</v>
+        <v>1863.95</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2184,12 +2184,14 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2208,57 +2210,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1768.39</v>
+        <v>1742.66</v>
       </c>
       <c r="C21" t="n">
-        <v>1782.86</v>
+        <v>1760.21</v>
       </c>
       <c r="D21" t="n">
-        <v>1711.9</v>
+        <v>1721.3</v>
       </c>
       <c r="E21" t="n">
-        <v>1742.68</v>
+        <v>1744.48</v>
       </c>
       <c r="F21" t="n">
-        <v>-25.83</v>
+        <v>1.81</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>70.95999999999999</v>
+        <v>38.91</v>
       </c>
       <c r="I21" t="n">
-        <v>1703.1</v>
+        <v>1640.94</v>
       </c>
       <c r="J21" t="n">
-        <v>1707.39</v>
+        <v>1669.37</v>
       </c>
       <c r="K21" t="n">
-        <v>1741.7</v>
+        <v>1707.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1776.02</v>
+        <v>1745.03</v>
       </c>
       <c r="M21" t="n">
-        <v>1795.32</v>
+        <v>1778.16</v>
       </c>
       <c r="N21" t="n">
-        <v>1814.62</v>
+        <v>1811.29</v>
       </c>
       <c r="O21" t="n">
-        <v>1863.95</v>
+        <v>1853.82</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2266,14 +2268,12 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2292,57 +2292,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1742.66</v>
+        <v>1744.47</v>
       </c>
       <c r="C22" t="n">
-        <v>1760.21</v>
+        <v>1809.76</v>
       </c>
       <c r="D22" t="n">
-        <v>1721.3</v>
+        <v>1736.72</v>
       </c>
       <c r="E22" t="n">
-        <v>1744.48</v>
+        <v>1795.69</v>
       </c>
       <c r="F22" t="n">
-        <v>1.81</v>
+        <v>51.21</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0294</v>
       </c>
       <c r="H22" t="n">
-        <v>38.91</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>1640.94</v>
+        <v>1682.39</v>
       </c>
       <c r="J22" t="n">
-        <v>1669.37</v>
+        <v>1707.44</v>
       </c>
       <c r="K22" t="n">
-        <v>1707.2</v>
+        <v>1725.03</v>
       </c>
       <c r="L22" t="n">
-        <v>1745.03</v>
+        <v>1742.62</v>
       </c>
       <c r="M22" t="n">
-        <v>1778.16</v>
+        <v>1763.94</v>
       </c>
       <c r="N22" t="n">
-        <v>1811.29</v>
+        <v>1785.26</v>
       </c>
       <c r="O22" t="n">
-        <v>1853.82</v>
+        <v>1799.11</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,76 +2355,78 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1744.47</v>
+        <v>1795.82</v>
       </c>
       <c r="C23" t="n">
-        <v>1809.76</v>
+        <v>1827.83</v>
       </c>
       <c r="D23" t="n">
-        <v>1736.72</v>
+        <v>1786.3</v>
       </c>
       <c r="E23" t="n">
-        <v>1795.69</v>
+        <v>1788.1</v>
       </c>
       <c r="F23" t="n">
-        <v>51.21</v>
+        <v>-7.59</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0294</v>
+        <v>-0.0042</v>
       </c>
       <c r="H23" t="n">
-        <v>73.04000000000001</v>
+        <v>41.54</v>
       </c>
       <c r="I23" t="n">
-        <v>1682.39</v>
+        <v>1663.69</v>
       </c>
       <c r="J23" t="n">
-        <v>1707.44</v>
+        <v>1733.88</v>
       </c>
       <c r="K23" t="n">
-        <v>1725.03</v>
+        <v>1759.18</v>
       </c>
       <c r="L23" t="n">
-        <v>1742.62</v>
+        <v>1784.47</v>
       </c>
       <c r="M23" t="n">
-        <v>1763.94</v>
+        <v>1832.21</v>
       </c>
       <c r="N23" t="n">
-        <v>1785.26</v>
+        <v>1879.95</v>
       </c>
       <c r="O23" t="n">
-        <v>1799.11</v>
+        <v>1882.79</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2435,80 +2437,78 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1795.82</v>
+        <v>1787.57</v>
       </c>
       <c r="C24" t="n">
-        <v>1827.83</v>
+        <v>1824.98</v>
       </c>
       <c r="D24" t="n">
-        <v>1786.3</v>
+        <v>1779.64</v>
       </c>
       <c r="E24" t="n">
-        <v>1788.1</v>
+        <v>1805.79</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.59</v>
+        <v>17.69</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>41.54</v>
+        <v>45.34</v>
       </c>
       <c r="I24" t="n">
-        <v>1663.69</v>
+        <v>1744.76</v>
       </c>
       <c r="J24" t="n">
-        <v>1733.88</v>
+        <v>1737.08</v>
       </c>
       <c r="K24" t="n">
-        <v>1759.18</v>
+        <v>1767.33</v>
       </c>
       <c r="L24" t="n">
-        <v>1784.47</v>
+        <v>1797.58</v>
       </c>
       <c r="M24" t="n">
-        <v>1832.21</v>
+        <v>1808.87</v>
       </c>
       <c r="N24" t="n">
-        <v>1879.95</v>
+        <v>1820.15</v>
       </c>
       <c r="O24" t="n">
-        <v>1882.79</v>
+        <v>1869.37</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2519,16 +2519,20 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2540,81 +2544,83 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1787.57</v>
+        <v>1805.76</v>
       </c>
       <c r="C25" t="n">
-        <v>1824.98</v>
+        <v>1842.46</v>
       </c>
       <c r="D25" t="n">
-        <v>1779.64</v>
+        <v>1749.35</v>
       </c>
       <c r="E25" t="n">
-        <v>1805.79</v>
+        <v>1773.5</v>
       </c>
       <c r="F25" t="n">
-        <v>17.69</v>
+        <v>-32.29</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.0179</v>
       </c>
       <c r="H25" t="n">
-        <v>45.34</v>
+        <v>93.11</v>
       </c>
       <c r="I25" t="n">
-        <v>1744.76</v>
+        <v>1734.29</v>
       </c>
       <c r="J25" t="n">
-        <v>1737.08</v>
+        <v>1762.18</v>
       </c>
       <c r="K25" t="n">
-        <v>1767.33</v>
+        <v>1783.12</v>
       </c>
       <c r="L25" t="n">
-        <v>1797.58</v>
+        <v>1804.05</v>
       </c>
       <c r="M25" t="n">
-        <v>1808.87</v>
+        <v>1828.46</v>
       </c>
       <c r="N25" t="n">
-        <v>1820.15</v>
+        <v>1852.87</v>
       </c>
       <c r="O25" t="n">
-        <v>1869.37</v>
+        <v>1870.32</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2633,77 +2639,75 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1805.76</v>
+        <v>1773.47</v>
       </c>
       <c r="C26" t="n">
-        <v>1842.46</v>
+        <v>1894.06</v>
       </c>
       <c r="D26" t="n">
-        <v>1749.35</v>
+        <v>1772.02</v>
       </c>
       <c r="E26" t="n">
-        <v>1773.5</v>
+        <v>1889.48</v>
       </c>
       <c r="F26" t="n">
-        <v>-32.29</v>
+        <v>115.98</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0654</v>
       </c>
       <c r="H26" t="n">
-        <v>93.11</v>
+        <v>122.04</v>
       </c>
       <c r="I26" t="n">
-        <v>1734.29</v>
+        <v>1656.24</v>
       </c>
       <c r="J26" t="n">
-        <v>1762.18</v>
+        <v>1669.19</v>
       </c>
       <c r="K26" t="n">
-        <v>1783.12</v>
+        <v>1726.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1804.05</v>
+        <v>1784.7</v>
       </c>
       <c r="M26" t="n">
-        <v>1828.46</v>
+        <v>1820.05</v>
       </c>
       <c r="N26" t="n">
-        <v>1852.87</v>
+        <v>1855.41</v>
       </c>
       <c r="O26" t="n">
-        <v>1870.32</v>
+        <v>1935.56</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2712,59 +2716,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1773.47</v>
+        <v>1889.5</v>
       </c>
       <c r="C27" t="n">
-        <v>1894.06</v>
+        <v>1944.16</v>
       </c>
       <c r="D27" t="n">
-        <v>1772.02</v>
+        <v>1863.64</v>
       </c>
       <c r="E27" t="n">
-        <v>1889.48</v>
+        <v>1916.94</v>
       </c>
       <c r="F27" t="n">
-        <v>115.98</v>
+        <v>27.46</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0654</v>
+        <v>0.0145</v>
       </c>
       <c r="H27" t="n">
-        <v>122.04</v>
+        <v>80.53</v>
       </c>
       <c r="I27" t="n">
-        <v>1656.24</v>
+        <v>1649.97</v>
       </c>
       <c r="J27" t="n">
-        <v>1669.19</v>
+        <v>1795.66</v>
       </c>
       <c r="K27" t="n">
-        <v>1726.95</v>
+        <v>1828.46</v>
       </c>
       <c r="L27" t="n">
-        <v>1784.7</v>
+        <v>1861.26</v>
       </c>
       <c r="M27" t="n">
-        <v>1820.05</v>
+        <v>1950.5</v>
       </c>
       <c r="N27" t="n">
-        <v>1855.41</v>
+        <v>2039.74</v>
       </c>
       <c r="O27" t="n">
-        <v>1935.56</v>
+        <v>2016.11</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2775,20 +2775,18 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2803,50 +2801,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1889.5</v>
+        <v>1916.98</v>
       </c>
       <c r="C28" t="n">
-        <v>1944.16</v>
+        <v>1927.09</v>
       </c>
       <c r="D28" t="n">
-        <v>1863.64</v>
+        <v>1856.78</v>
       </c>
       <c r="E28" t="n">
-        <v>1916.94</v>
+        <v>1863.19</v>
       </c>
       <c r="F28" t="n">
-        <v>27.46</v>
+        <v>-53.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0145</v>
+        <v>-0.028</v>
       </c>
       <c r="H28" t="n">
-        <v>80.53</v>
+        <v>70.31</v>
       </c>
       <c r="I28" t="n">
-        <v>1649.97</v>
+        <v>1783.11</v>
       </c>
       <c r="J28" t="n">
-        <v>1795.66</v>
+        <v>1842.94</v>
       </c>
       <c r="K28" t="n">
-        <v>1828.46</v>
+        <v>1876.68</v>
       </c>
       <c r="L28" t="n">
-        <v>1861.26</v>
+        <v>1910.42</v>
       </c>
       <c r="M28" t="n">
-        <v>1950.5</v>
+        <v>1957.21</v>
       </c>
       <c r="N28" t="n">
-        <v>2039.74</v>
+        <v>2003.99</v>
       </c>
       <c r="O28" t="n">
-        <v>2016.11</v>
+        <v>2024.69</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2854,18 +2852,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2878,55 +2876,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1916.98</v>
+        <v>1863.22</v>
       </c>
       <c r="C29" t="n">
-        <v>1927.09</v>
+        <v>1869.07</v>
       </c>
       <c r="D29" t="n">
-        <v>1856.78</v>
+        <v>1803.05</v>
       </c>
       <c r="E29" t="n">
-        <v>1863.19</v>
+        <v>1840.99</v>
       </c>
       <c r="F29" t="n">
-        <v>-53.75</v>
+        <v>-22.21</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.0119</v>
       </c>
       <c r="H29" t="n">
-        <v>70.31</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>1783.11</v>
+        <v>1786.47</v>
       </c>
       <c r="J29" t="n">
-        <v>1842.94</v>
+        <v>1778.51</v>
       </c>
       <c r="K29" t="n">
-        <v>1876.68</v>
+        <v>1828.04</v>
       </c>
       <c r="L29" t="n">
-        <v>1910.42</v>
+        <v>1877.56</v>
       </c>
       <c r="M29" t="n">
-        <v>1957.21</v>
+        <v>1898.35</v>
       </c>
       <c r="N29" t="n">
-        <v>2003.99</v>
+        <v>1919.13</v>
       </c>
       <c r="O29" t="n">
-        <v>2024.69</v>
+        <v>1997.4</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2939,7 +2941,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2967,50 +2969,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1863.22</v>
+        <v>1841.1</v>
       </c>
       <c r="C30" t="n">
-        <v>1869.07</v>
+        <v>1864.13</v>
       </c>
       <c r="D30" t="n">
-        <v>1803.05</v>
+        <v>1836.61</v>
       </c>
       <c r="E30" t="n">
-        <v>1840.99</v>
+        <v>1861.39</v>
       </c>
       <c r="F30" t="n">
-        <v>-22.21</v>
+        <v>20.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0111</v>
       </c>
       <c r="H30" t="n">
-        <v>66.01000000000001</v>
+        <v>27.52</v>
       </c>
       <c r="I30" t="n">
-        <v>1786.47</v>
+        <v>1737.04</v>
       </c>
       <c r="J30" t="n">
-        <v>1778.51</v>
+        <v>1777.44</v>
       </c>
       <c r="K30" t="n">
-        <v>1828.04</v>
+        <v>1807.98</v>
       </c>
       <c r="L30" t="n">
-        <v>1877.56</v>
+        <v>1838.52</v>
       </c>
       <c r="M30" t="n">
-        <v>1898.35</v>
+        <v>1873.99</v>
       </c>
       <c r="N30" t="n">
-        <v>1919.13</v>
+        <v>1909.47</v>
       </c>
       <c r="O30" t="n">
-        <v>1997.4</v>
+        <v>1935.08</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3018,19 +3020,19 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3044,57 +3046,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1841.1</v>
+        <v>1861.42</v>
       </c>
       <c r="C31" t="n">
-        <v>1864.13</v>
+        <v>1877.03</v>
       </c>
       <c r="D31" t="n">
-        <v>1836.61</v>
+        <v>1852.73</v>
       </c>
       <c r="E31" t="n">
-        <v>1861.39</v>
+        <v>1871.51</v>
       </c>
       <c r="F31" t="n">
-        <v>20.4</v>
+        <v>10.12</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0054</v>
       </c>
       <c r="H31" t="n">
-        <v>27.52</v>
+        <v>24.3</v>
       </c>
       <c r="I31" t="n">
-        <v>1737.04</v>
+        <v>1809.09</v>
       </c>
       <c r="J31" t="n">
-        <v>1777.44</v>
+        <v>1839.38</v>
       </c>
       <c r="K31" t="n">
-        <v>1807.98</v>
+        <v>1847.63</v>
       </c>
       <c r="L31" t="n">
-        <v>1838.52</v>
+        <v>1855.88</v>
       </c>
       <c r="M31" t="n">
-        <v>1873.99</v>
+        <v>1875.15</v>
       </c>
       <c r="N31" t="n">
-        <v>1909.47</v>
+        <v>1894.43</v>
       </c>
       <c r="O31" t="n">
-        <v>1935.08</v>
+        <v>1891.66</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3105,7 +3107,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3126,231 +3128,227 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1861.42</v>
+        <v>1871.28</v>
       </c>
       <c r="C32" t="n">
-        <v>1877.03</v>
+        <v>1916.24</v>
       </c>
       <c r="D32" t="n">
-        <v>1852.73</v>
+        <v>1842.82</v>
       </c>
       <c r="E32" t="n">
-        <v>1871.51</v>
+        <v>1903.76</v>
       </c>
       <c r="F32" t="n">
-        <v>10.12</v>
+        <v>32.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0172</v>
       </c>
       <c r="H32" t="n">
-        <v>24.3</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>1809.09</v>
+        <v>1828.42</v>
       </c>
       <c r="J32" t="n">
-        <v>1839.38</v>
+        <v>1850.52</v>
       </c>
       <c r="K32" t="n">
-        <v>1847.63</v>
+        <v>1859.36</v>
       </c>
       <c r="L32" t="n">
-        <v>1855.88</v>
+        <v>1868.19</v>
       </c>
       <c r="M32" t="n">
-        <v>1875.15</v>
+        <v>1883.66</v>
       </c>
       <c r="N32" t="n">
-        <v>1894.43</v>
+        <v>1899.13</v>
       </c>
       <c r="O32" t="n">
-        <v>1891.66</v>
+        <v>1901.34</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1871.28</v>
+        <v>1903.69</v>
       </c>
       <c r="C33" t="n">
-        <v>1916.24</v>
+        <v>1949.55</v>
       </c>
       <c r="D33" t="n">
-        <v>1842.82</v>
+        <v>1900.07</v>
       </c>
       <c r="E33" t="n">
-        <v>1903.76</v>
+        <v>1928.38</v>
       </c>
       <c r="F33" t="n">
-        <v>32.25</v>
+        <v>24.62</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0129</v>
       </c>
       <c r="H33" t="n">
-        <v>73.43000000000001</v>
+        <v>49.48</v>
       </c>
       <c r="I33" t="n">
-        <v>1828.42</v>
+        <v>1769.39</v>
       </c>
       <c r="J33" t="n">
-        <v>1850.52</v>
+        <v>1842.45</v>
       </c>
       <c r="K33" t="n">
-        <v>1859.36</v>
+        <v>1867.05</v>
       </c>
       <c r="L33" t="n">
-        <v>1868.19</v>
+        <v>1891.64</v>
       </c>
       <c r="M33" t="n">
-        <v>1883.66</v>
+        <v>1940.47</v>
       </c>
       <c r="N33" t="n">
-        <v>1899.13</v>
+        <v>1989.3</v>
       </c>
       <c r="O33" t="n">
-        <v>1901.34</v>
+        <v>1989.67</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1903.69</v>
+        <v>1928.2</v>
       </c>
       <c r="C34" t="n">
-        <v>1949.55</v>
+        <v>1955.15</v>
       </c>
       <c r="D34" t="n">
-        <v>1900.07</v>
+        <v>1909.61</v>
       </c>
       <c r="E34" t="n">
-        <v>1928.38</v>
+        <v>1933.49</v>
       </c>
       <c r="F34" t="n">
-        <v>24.62</v>
+        <v>5.11</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0026</v>
       </c>
       <c r="H34" t="n">
-        <v>49.48</v>
+        <v>45.54</v>
       </c>
       <c r="I34" t="n">
-        <v>1769.39</v>
+        <v>1850.58</v>
       </c>
       <c r="J34" t="n">
-        <v>1842.45</v>
+        <v>1880.69</v>
       </c>
       <c r="K34" t="n">
-        <v>1867.05</v>
+        <v>1903.64</v>
       </c>
       <c r="L34" t="n">
-        <v>1891.64</v>
+        <v>1926.6</v>
       </c>
       <c r="M34" t="n">
-        <v>1940.47</v>
+        <v>1953.12</v>
       </c>
       <c r="N34" t="n">
-        <v>1989.3</v>
+        <v>1979.65</v>
       </c>
       <c r="O34" t="n">
-        <v>1989.67</v>
+        <v>1999.03</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3361,14 +3359,14 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U34" s="8" t="n">
@@ -3387,69 +3385,71 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1928.2</v>
+        <v>1933.47</v>
       </c>
       <c r="C35" t="n">
-        <v>1955.15</v>
+        <v>1940.28</v>
       </c>
       <c r="D35" t="n">
-        <v>1909.61</v>
+        <v>1868.52</v>
       </c>
       <c r="E35" t="n">
-        <v>1933.49</v>
+        <v>1877.1</v>
       </c>
       <c r="F35" t="n">
-        <v>5.11</v>
+        <v>-56.39</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0292</v>
       </c>
       <c r="H35" t="n">
-        <v>45.54</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>1850.58</v>
+        <v>1864.07</v>
       </c>
       <c r="J35" t="n">
-        <v>1880.69</v>
+        <v>1888.51</v>
       </c>
       <c r="K35" t="n">
-        <v>1903.64</v>
+        <v>1910.72</v>
       </c>
       <c r="L35" t="n">
-        <v>1926.6</v>
+        <v>1932.93</v>
       </c>
       <c r="M35" t="n">
-        <v>1953.12</v>
+        <v>1956.26</v>
       </c>
       <c r="N35" t="n">
-        <v>1979.65</v>
+        <v>1979.58</v>
       </c>
       <c r="O35" t="n">
-        <v>1999.03</v>
+        <v>2000.68</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3457,9 +3457,9 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3467,65 +3467,63 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1933.47</v>
+        <v>1877.1</v>
       </c>
       <c r="C36" t="n">
-        <v>1940.28</v>
+        <v>1907.54</v>
       </c>
       <c r="D36" t="n">
-        <v>1868.52</v>
+        <v>1846.82</v>
       </c>
       <c r="E36" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="F36" t="n">
-        <v>-56.39</v>
+        <v>-16.92</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0292</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>71.76000000000001</v>
+        <v>60.72</v>
       </c>
       <c r="I36" t="n">
-        <v>1864.07</v>
+        <v>1796.76</v>
       </c>
       <c r="J36" t="n">
-        <v>1888.51</v>
+        <v>1791.69</v>
       </c>
       <c r="K36" t="n">
-        <v>1910.72</v>
+        <v>1841.22</v>
       </c>
       <c r="L36" t="n">
-        <v>1932.93</v>
+        <v>1890.75</v>
       </c>
       <c r="M36" t="n">
-        <v>1956.26</v>
+        <v>1912.98</v>
       </c>
       <c r="N36" t="n">
-        <v>1979.58</v>
+        <v>1935.21</v>
       </c>
       <c r="O36" t="n">
-        <v>2000.68</v>
+        <v>2012.05</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3549,50 +3547,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="C37" t="n">
-        <v>1907.54</v>
+        <v>1875.14</v>
       </c>
       <c r="D37" t="n">
-        <v>1846.82</v>
+        <v>1849.83</v>
       </c>
       <c r="E37" t="n">
-        <v>1860.18</v>
+        <v>1873.22</v>
       </c>
       <c r="F37" t="n">
-        <v>-16.92</v>
+        <v>13.05</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H37" t="n">
-        <v>60.72</v>
+        <v>25.32</v>
       </c>
       <c r="I37" t="n">
-        <v>1796.76</v>
+        <v>1786.1</v>
       </c>
       <c r="J37" t="n">
-        <v>1791.69</v>
+        <v>1790.95</v>
       </c>
       <c r="K37" t="n">
-        <v>1841.22</v>
+        <v>1829.82</v>
       </c>
       <c r="L37" t="n">
-        <v>1890.75</v>
+        <v>1868.68</v>
       </c>
       <c r="M37" t="n">
-        <v>1912.98</v>
+        <v>1890.54</v>
       </c>
       <c r="N37" t="n">
-        <v>1935.21</v>
+        <v>1912.39</v>
       </c>
       <c r="O37" t="n">
-        <v>2012.05</v>
+        <v>1968.26</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3600,14 +3598,12 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3624,55 +3620,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1860.18</v>
+        <v>1873.24</v>
       </c>
       <c r="C38" t="n">
-        <v>1875.14</v>
+        <v>1963.25</v>
       </c>
       <c r="D38" t="n">
-        <v>1849.83</v>
+        <v>1872.38</v>
       </c>
       <c r="E38" t="n">
-        <v>1873.22</v>
+        <v>1953.41</v>
       </c>
       <c r="F38" t="n">
-        <v>13.05</v>
+        <v>80.19</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0428</v>
       </c>
       <c r="H38" t="n">
-        <v>25.32</v>
+        <v>90.86</v>
       </c>
       <c r="I38" t="n">
-        <v>1786.1</v>
+        <v>1824.51</v>
       </c>
       <c r="J38" t="n">
-        <v>1790.95</v>
+        <v>1853.27</v>
       </c>
       <c r="K38" t="n">
-        <v>1829.82</v>
+        <v>1860.56</v>
       </c>
       <c r="L38" t="n">
-        <v>1868.68</v>
+        <v>1867.85</v>
       </c>
       <c r="M38" t="n">
-        <v>1890.54</v>
+        <v>1885.88</v>
       </c>
       <c r="N38" t="n">
-        <v>1912.39</v>
+        <v>1903.91</v>
       </c>
       <c r="O38" t="n">
-        <v>1968.26</v>
+        <v>1900.46</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3683,179 +3683,179 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W38" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1873.24</v>
+        <v>1953.41</v>
       </c>
       <c r="C39" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D39" t="n">
-        <v>1872.38</v>
+        <v>1882.42</v>
       </c>
       <c r="E39" t="n">
-        <v>1953.41</v>
+        <v>1890.61</v>
       </c>
       <c r="F39" t="n">
-        <v>80.19</v>
+        <v>-62.8</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0428</v>
+        <v>-0.0321</v>
       </c>
       <c r="H39" t="n">
-        <v>90.86</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>1824.51</v>
+        <v>1781.52</v>
       </c>
       <c r="J39" t="n">
-        <v>1853.27</v>
+        <v>1880.35</v>
       </c>
       <c r="K39" t="n">
-        <v>1860.56</v>
+        <v>1907.98</v>
       </c>
       <c r="L39" t="n">
-        <v>1867.85</v>
+        <v>1935.61</v>
       </c>
       <c r="M39" t="n">
-        <v>1885.88</v>
+        <v>1998.84</v>
       </c>
       <c r="N39" t="n">
-        <v>1903.91</v>
+        <v>2062.07</v>
       </c>
       <c r="O39" t="n">
-        <v>1900.46</v>
+        <v>2054.11</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1953.41</v>
+        <v>1890.63</v>
       </c>
       <c r="C40" t="n">
-        <v>1976.46</v>
+        <v>1926.5</v>
       </c>
       <c r="D40" t="n">
-        <v>1882.42</v>
+        <v>1856.34</v>
       </c>
       <c r="E40" t="n">
-        <v>1890.61</v>
+        <v>1919.95</v>
       </c>
       <c r="F40" t="n">
-        <v>-62.8</v>
+        <v>29.33</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0321</v>
+        <v>0.0155</v>
       </c>
       <c r="H40" t="n">
-        <v>94.04000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="I40" t="n">
-        <v>1781.52</v>
+        <v>1788.38</v>
       </c>
       <c r="J40" t="n">
-        <v>1880.35</v>
+        <v>1777.16</v>
       </c>
       <c r="K40" t="n">
-        <v>1907.98</v>
+        <v>1843.59</v>
       </c>
       <c r="L40" t="n">
-        <v>1935.61</v>
+        <v>1910.03</v>
       </c>
       <c r="M40" t="n">
-        <v>1998.84</v>
+        <v>1937.63</v>
       </c>
       <c r="N40" t="n">
-        <v>2062.07</v>
+        <v>1965.24</v>
       </c>
       <c r="O40" t="n">
-        <v>2054.11</v>
+        <v>2070.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3874,57 +3874,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1890.63</v>
+        <v>1919.99</v>
       </c>
       <c r="C41" t="n">
-        <v>1926.5</v>
+        <v>1929.9</v>
       </c>
       <c r="D41" t="n">
-        <v>1856.34</v>
+        <v>1873.62</v>
       </c>
       <c r="E41" t="n">
-        <v>1919.95</v>
+        <v>1908.52</v>
       </c>
       <c r="F41" t="n">
-        <v>29.33</v>
+        <v>-11.43</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.006</v>
       </c>
       <c r="H41" t="n">
-        <v>70.16</v>
+        <v>56.28</v>
       </c>
       <c r="I41" t="n">
-        <v>1788.38</v>
+        <v>1786.18</v>
       </c>
       <c r="J41" t="n">
-        <v>1777.16</v>
+        <v>1864.05</v>
       </c>
       <c r="K41" t="n">
-        <v>1843.59</v>
+        <v>1884.87</v>
       </c>
       <c r="L41" t="n">
-        <v>1910.03</v>
+        <v>1905.69</v>
       </c>
       <c r="M41" t="n">
-        <v>1937.63</v>
+        <v>1955.03</v>
       </c>
       <c r="N41" t="n">
-        <v>1965.24</v>
+        <v>2004.37</v>
       </c>
       <c r="O41" t="n">
-        <v>2070.5</v>
+        <v>1996.67</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3932,10 +3932,12 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3956,57 +3958,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1919.99</v>
+        <v>1908.59</v>
       </c>
       <c r="C42" t="n">
-        <v>1929.9</v>
+        <v>1934.58</v>
       </c>
       <c r="D42" t="n">
-        <v>1873.62</v>
+        <v>1892.2</v>
       </c>
       <c r="E42" t="n">
-        <v>1908.52</v>
+        <v>1917.37</v>
       </c>
       <c r="F42" t="n">
-        <v>-11.43</v>
+        <v>8.85</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0046</v>
       </c>
       <c r="H42" t="n">
-        <v>56.28</v>
+        <v>42.38</v>
       </c>
       <c r="I42" t="n">
-        <v>1786.18</v>
+        <v>1817.34</v>
       </c>
       <c r="J42" t="n">
-        <v>1864.05</v>
+        <v>1855.62</v>
       </c>
       <c r="K42" t="n">
-        <v>1884.87</v>
+        <v>1880.38</v>
       </c>
       <c r="L42" t="n">
-        <v>1905.69</v>
+        <v>1905.14</v>
       </c>
       <c r="M42" t="n">
-        <v>1955.03</v>
+        <v>1936.66</v>
       </c>
       <c r="N42" t="n">
-        <v>2004.37</v>
+        <v>1968.18</v>
       </c>
       <c r="O42" t="n">
-        <v>1996.67</v>
+        <v>1986.18</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4014,12 +4016,10 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4038,72 +4038,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1908.59</v>
+        <v>1917.14</v>
       </c>
       <c r="C43" t="n">
-        <v>1934.58</v>
+        <v>1933.78</v>
       </c>
       <c r="D43" t="n">
-        <v>1892.2</v>
+        <v>1847.47</v>
       </c>
       <c r="E43" t="n">
-        <v>1917.37</v>
+        <v>1860.35</v>
       </c>
       <c r="F43" t="n">
-        <v>8.85</v>
+        <v>-57.03</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0297</v>
       </c>
       <c r="H43" t="n">
-        <v>42.38</v>
+        <v>86.31</v>
       </c>
       <c r="I43" t="n">
-        <v>1817.34</v>
+        <v>1849.82</v>
       </c>
       <c r="J43" t="n">
-        <v>1855.62</v>
+        <v>1876.99</v>
       </c>
       <c r="K43" t="n">
-        <v>1880.38</v>
+        <v>1896.18</v>
       </c>
       <c r="L43" t="n">
-        <v>1905.14</v>
+        <v>1915.38</v>
       </c>
       <c r="M43" t="n">
-        <v>1936.66</v>
+        <v>1938.56</v>
       </c>
       <c r="N43" t="n">
-        <v>1968.18</v>
+        <v>1961.75</v>
       </c>
       <c r="O43" t="n">
-        <v>1986.18</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+        <v>1976.96</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4115,9 +4117,9 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
@@ -4125,67 +4127,63 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1917.14</v>
+        <v>1860.37</v>
       </c>
       <c r="C44" t="n">
-        <v>1933.78</v>
+        <v>1873.17</v>
       </c>
       <c r="D44" t="n">
-        <v>1847.47</v>
+        <v>1821.49</v>
       </c>
       <c r="E44" t="n">
-        <v>1860.35</v>
+        <v>1843.42</v>
       </c>
       <c r="F44" t="n">
-        <v>-57.03</v>
+        <v>-16.93</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0297</v>
+        <v>-0.0091</v>
       </c>
       <c r="H44" t="n">
-        <v>86.31</v>
+        <v>51.69</v>
       </c>
       <c r="I44" t="n">
-        <v>1849.82</v>
+        <v>1761.16</v>
       </c>
       <c r="J44" t="n">
-        <v>1876.99</v>
+        <v>1758.9</v>
       </c>
       <c r="K44" t="n">
-        <v>1896.18</v>
+        <v>1817.19</v>
       </c>
       <c r="L44" t="n">
-        <v>1915.38</v>
+        <v>1875.48</v>
       </c>
       <c r="M44" t="n">
-        <v>1938.56</v>
+        <v>1903.5</v>
       </c>
       <c r="N44" t="n">
-        <v>1961.75</v>
+        <v>1931.52</v>
       </c>
       <c r="O44" t="n">
-        <v>1976.96</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
+        <v>2020.09</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4209,50 +4207,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1860.37</v>
+        <v>1843.42</v>
       </c>
       <c r="C45" t="n">
-        <v>1873.17</v>
+        <v>1895.77</v>
       </c>
       <c r="D45" t="n">
-        <v>1821.49</v>
+        <v>1842.15</v>
       </c>
       <c r="E45" t="n">
-        <v>1843.42</v>
+        <v>1882.52</v>
       </c>
       <c r="F45" t="n">
-        <v>-16.93</v>
+        <v>39.1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0212</v>
       </c>
       <c r="H45" t="n">
-        <v>51.69</v>
+        <v>53.61</v>
       </c>
       <c r="I45" t="n">
-        <v>1761.16</v>
+        <v>1769.8</v>
       </c>
       <c r="J45" t="n">
-        <v>1758.9</v>
+        <v>1789.78</v>
       </c>
       <c r="K45" t="n">
-        <v>1817.19</v>
+        <v>1817.57</v>
       </c>
       <c r="L45" t="n">
-        <v>1875.48</v>
+        <v>1845.37</v>
       </c>
       <c r="M45" t="n">
-        <v>1903.5</v>
+        <v>1869.26</v>
       </c>
       <c r="N45" t="n">
-        <v>1931.52</v>
+        <v>1893.15</v>
       </c>
       <c r="O45" t="n">
-        <v>2020.09</v>
+        <v>1924.86</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4260,22 +4258,24 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4284,79 +4284,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1843.42</v>
+        <v>1882.78</v>
       </c>
       <c r="C46" t="n">
-        <v>1895.77</v>
+        <v>1883.44</v>
       </c>
       <c r="D46" t="n">
-        <v>1842.15</v>
+        <v>1827.7</v>
       </c>
       <c r="E46" t="n">
-        <v>1882.52</v>
+        <v>1858.26</v>
       </c>
       <c r="F46" t="n">
-        <v>39.1</v>
+        <v>-24.27</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0129</v>
       </c>
       <c r="H46" t="n">
-        <v>53.61</v>
+        <v>55.74</v>
       </c>
       <c r="I46" t="n">
-        <v>1769.8</v>
+        <v>1788.54</v>
       </c>
       <c r="J46" t="n">
-        <v>1789.78</v>
+        <v>1835.69</v>
       </c>
       <c r="K46" t="n">
-        <v>1817.57</v>
+        <v>1855.72</v>
       </c>
       <c r="L46" t="n">
-        <v>1845.37</v>
+        <v>1875.74</v>
       </c>
       <c r="M46" t="n">
-        <v>1869.26</v>
+        <v>1909.33</v>
       </c>
       <c r="N46" t="n">
-        <v>1893.15</v>
+        <v>1942.91</v>
       </c>
       <c r="O46" t="n">
-        <v>1924.86</v>
+        <v>1949.38</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4366,76 +4370,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1882.78</v>
+        <v>1858.22</v>
       </c>
       <c r="C47" t="n">
-        <v>1883.44</v>
+        <v>1879.54</v>
       </c>
       <c r="D47" t="n">
-        <v>1827.7</v>
+        <v>1847.17</v>
       </c>
       <c r="E47" t="n">
-        <v>1858.26</v>
+        <v>1868.39</v>
       </c>
       <c r="F47" t="n">
-        <v>-24.27</v>
+        <v>10.13</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0055</v>
       </c>
       <c r="H47" t="n">
-        <v>55.74</v>
+        <v>32.36</v>
       </c>
       <c r="I47" t="n">
-        <v>1788.54</v>
+        <v>1771.96</v>
       </c>
       <c r="J47" t="n">
-        <v>1835.69</v>
+        <v>1803.86</v>
       </c>
       <c r="K47" t="n">
-        <v>1855.72</v>
+        <v>1830.39</v>
       </c>
       <c r="L47" t="n">
-        <v>1875.74</v>
+        <v>1856.91</v>
       </c>
       <c r="M47" t="n">
-        <v>1909.33</v>
+        <v>1886.13</v>
       </c>
       <c r="N47" t="n">
-        <v>1942.91</v>
+        <v>1915.34</v>
       </c>
       <c r="O47" t="n">
-        <v>1949.38</v>
+        <v>1939.18</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4452,55 +4448,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1858.22</v>
+        <v>1868.49</v>
       </c>
       <c r="C48" t="n">
-        <v>1879.54</v>
+        <v>1922.64</v>
       </c>
       <c r="D48" t="n">
-        <v>1847.17</v>
+        <v>1854.34</v>
       </c>
       <c r="E48" t="n">
-        <v>1868.39</v>
+        <v>1906.53</v>
       </c>
       <c r="F48" t="n">
-        <v>10.13</v>
+        <v>38.14</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0204</v>
       </c>
       <c r="H48" t="n">
-        <v>32.36</v>
+        <v>68.3</v>
       </c>
       <c r="I48" t="n">
-        <v>1771.96</v>
+        <v>1814.81</v>
       </c>
       <c r="J48" t="n">
-        <v>1803.86</v>
+        <v>1838.54</v>
       </c>
       <c r="K48" t="n">
-        <v>1830.39</v>
+        <v>1852.2</v>
       </c>
       <c r="L48" t="n">
-        <v>1856.91</v>
+        <v>1865.87</v>
       </c>
       <c r="M48" t="n">
-        <v>1886.13</v>
+        <v>1884.57</v>
       </c>
       <c r="N48" t="n">
-        <v>1915.34</v>
+        <v>1903.26</v>
       </c>
       <c r="O48" t="n">
-        <v>1939.18</v>
+        <v>1911.9</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4511,78 +4511,80 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1868.49</v>
+        <v>1906.44</v>
       </c>
       <c r="C49" t="n">
-        <v>1922.64</v>
+        <v>1917.7</v>
       </c>
       <c r="D49" t="n">
-        <v>1854.34</v>
+        <v>1890.96</v>
       </c>
       <c r="E49" t="n">
-        <v>1906.53</v>
+        <v>1902.06</v>
       </c>
       <c r="F49" t="n">
-        <v>38.14</v>
+        <v>-4.47</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.0023</v>
       </c>
       <c r="H49" t="n">
-        <v>68.3</v>
+        <v>26.74</v>
       </c>
       <c r="I49" t="n">
-        <v>1814.81</v>
+        <v>1786.04</v>
       </c>
       <c r="J49" t="n">
-        <v>1838.54</v>
+        <v>1847.24</v>
       </c>
       <c r="K49" t="n">
-        <v>1852.2</v>
+        <v>1872.38</v>
       </c>
       <c r="L49" t="n">
-        <v>1865.87</v>
+        <v>1897.51</v>
       </c>
       <c r="M49" t="n">
-        <v>1884.57</v>
+        <v>1940.68</v>
       </c>
       <c r="N49" t="n">
-        <v>1903.26</v>
+        <v>1983.84</v>
       </c>
       <c r="O49" t="n">
-        <v>1911.9</v>
+        <v>1990.94</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4593,80 +4595,78 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1906.44</v>
+        <v>1902.14</v>
       </c>
       <c r="C50" t="n">
-        <v>1917.7</v>
+        <v>1937.17</v>
       </c>
       <c r="D50" t="n">
-        <v>1890.96</v>
+        <v>1893.08</v>
       </c>
       <c r="E50" t="n">
-        <v>1902.06</v>
+        <v>1913.28</v>
       </c>
       <c r="F50" t="n">
-        <v>-4.47</v>
+        <v>11.22</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0059</v>
       </c>
       <c r="H50" t="n">
-        <v>26.74</v>
+        <v>44.08</v>
       </c>
       <c r="I50" t="n">
-        <v>1786.04</v>
+        <v>1864.23</v>
       </c>
       <c r="J50" t="n">
-        <v>1847.24</v>
+        <v>1874.18</v>
       </c>
       <c r="K50" t="n">
-        <v>1872.38</v>
+        <v>1888.69</v>
       </c>
       <c r="L50" t="n">
-        <v>1897.51</v>
+        <v>1903.19</v>
       </c>
       <c r="M50" t="n">
-        <v>1940.68</v>
+        <v>1915.43</v>
       </c>
       <c r="N50" t="n">
-        <v>1983.84</v>
+        <v>1927.66</v>
       </c>
       <c r="O50" t="n">
-        <v>1990.94</v>
+        <v>1944.44</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4677,16 +4677,20 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4696,59 +4700,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1902.14</v>
+        <v>1913.32</v>
       </c>
       <c r="C51" t="n">
-        <v>1937.17</v>
+        <v>1924.62</v>
       </c>
       <c r="D51" t="n">
-        <v>1893.08</v>
+        <v>1911.48</v>
       </c>
       <c r="E51" t="n">
-        <v>1913.28</v>
+        <v>1915.53</v>
       </c>
       <c r="F51" t="n">
-        <v>11.22</v>
+        <v>2.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0012</v>
       </c>
       <c r="H51" t="n">
-        <v>44.08</v>
+        <v>13.13</v>
       </c>
       <c r="I51" t="n">
-        <v>1864.23</v>
+        <v>1849</v>
       </c>
       <c r="J51" t="n">
-        <v>1874.18</v>
+        <v>1868.27</v>
       </c>
       <c r="K51" t="n">
-        <v>1888.69</v>
+        <v>1891.24</v>
       </c>
       <c r="L51" t="n">
-        <v>1903.19</v>
+        <v>1914.2</v>
       </c>
       <c r="M51" t="n">
-        <v>1915.43</v>
+        <v>1935.32</v>
       </c>
       <c r="N51" t="n">
-        <v>1927.66</v>
+        <v>1956.44</v>
       </c>
       <c r="O51" t="n">
-        <v>1944.44</v>
+        <v>1981.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4759,20 +4759,16 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4782,55 +4778,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1913.32</v>
+        <v>1915.46</v>
       </c>
       <c r="C52" t="n">
-        <v>1924.62</v>
+        <v>1935.53</v>
       </c>
       <c r="D52" t="n">
-        <v>1911.48</v>
+        <v>1907.03</v>
       </c>
       <c r="E52" t="n">
-        <v>1915.53</v>
+        <v>1908.68</v>
       </c>
       <c r="F52" t="n">
-        <v>2.25</v>
+        <v>-6.85</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0036</v>
       </c>
       <c r="H52" t="n">
-        <v>13.13</v>
+        <v>28.5</v>
       </c>
       <c r="I52" t="n">
-        <v>1849</v>
+        <v>1898.35</v>
       </c>
       <c r="J52" t="n">
-        <v>1868.27</v>
+        <v>1901.14</v>
       </c>
       <c r="K52" t="n">
-        <v>1891.24</v>
+        <v>1908.97</v>
       </c>
       <c r="L52" t="n">
-        <v>1914.2</v>
+        <v>1916.79</v>
       </c>
       <c r="M52" t="n">
-        <v>1935.32</v>
+        <v>1922.1</v>
       </c>
       <c r="N52" t="n">
-        <v>1956.44</v>
+        <v>1927.4</v>
       </c>
       <c r="O52" t="n">
-        <v>1981.25</v>
+        <v>1937.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4838,19 +4838,25 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4862,70 +4868,74 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1915.46</v>
+        <v>1908.72</v>
       </c>
       <c r="C53" t="n">
-        <v>1935.53</v>
+        <v>1928.99</v>
       </c>
       <c r="D53" t="n">
-        <v>1907.03</v>
+        <v>1866.79</v>
       </c>
       <c r="E53" t="n">
-        <v>1908.68</v>
+        <v>1871.28</v>
       </c>
       <c r="F53" t="n">
-        <v>-6.85</v>
+        <v>-37.4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0196</v>
       </c>
       <c r="H53" t="n">
-        <v>28.5</v>
+        <v>62.2</v>
       </c>
       <c r="I53" t="n">
-        <v>1898.35</v>
+        <v>1878.52</v>
       </c>
       <c r="J53" t="n">
-        <v>1901.14</v>
+        <v>1873.88</v>
       </c>
       <c r="K53" t="n">
-        <v>1908.97</v>
+        <v>1894.43</v>
       </c>
       <c r="L53" t="n">
-        <v>1916.79</v>
+        <v>1914.98</v>
       </c>
       <c r="M53" t="n">
-        <v>1922.1</v>
+        <v>1922.93</v>
       </c>
       <c r="N53" t="n">
-        <v>1927.4</v>
+        <v>1930.89</v>
       </c>
       <c r="O53" t="n">
-        <v>1937.75</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+        <v>1964.03</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4935,97 +4945,83 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1908.72</v>
+        <v>1871.26</v>
       </c>
       <c r="C54" t="n">
-        <v>1928.99</v>
+        <v>1895.75</v>
       </c>
       <c r="D54" t="n">
-        <v>1866.79</v>
+        <v>1852.84</v>
       </c>
       <c r="E54" t="n">
-        <v>1871.28</v>
+        <v>1881.37</v>
       </c>
       <c r="F54" t="n">
-        <v>-37.4</v>
+        <v>10.09</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0196</v>
+        <v>0.0054</v>
       </c>
       <c r="H54" t="n">
-        <v>62.2</v>
+        <v>42.91</v>
       </c>
       <c r="I54" t="n">
-        <v>1878.52</v>
+        <v>1804.59</v>
       </c>
       <c r="J54" t="n">
-        <v>1873.88</v>
+        <v>1795.77</v>
       </c>
       <c r="K54" t="n">
-        <v>1894.43</v>
+        <v>1840.18</v>
       </c>
       <c r="L54" t="n">
-        <v>1914.98</v>
+        <v>1884.59</v>
       </c>
       <c r="M54" t="n">
-        <v>1922.93</v>
+        <v>1902.38</v>
       </c>
       <c r="N54" t="n">
-        <v>1930.89</v>
+        <v>1920.18</v>
       </c>
       <c r="O54" t="n">
-        <v>1964.03</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>1991.2</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5038,55 +5034,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1871.26</v>
+        <v>1881.37</v>
       </c>
       <c r="C55" t="n">
-        <v>1895.75</v>
+        <v>1921.78</v>
       </c>
       <c r="D55" t="n">
-        <v>1852.84</v>
+        <v>1873.35</v>
       </c>
       <c r="E55" t="n">
-        <v>1881.37</v>
+        <v>1878.14</v>
       </c>
       <c r="F55" t="n">
-        <v>10.09</v>
+        <v>-3.24</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0017</v>
       </c>
       <c r="H55" t="n">
-        <v>42.91</v>
+        <v>48.43</v>
       </c>
       <c r="I55" t="n">
-        <v>1804.59</v>
+        <v>1809.93</v>
       </c>
       <c r="J55" t="n">
-        <v>1795.77</v>
+        <v>1842</v>
       </c>
       <c r="K55" t="n">
-        <v>1840.18</v>
+        <v>1859.92</v>
       </c>
       <c r="L55" t="n">
-        <v>1884.59</v>
+        <v>1877.83</v>
       </c>
       <c r="M55" t="n">
-        <v>1902.38</v>
+        <v>1902.83</v>
       </c>
       <c r="N55" t="n">
-        <v>1920.18</v>
+        <v>1927.82</v>
       </c>
       <c r="O55" t="n">
-        <v>1991.2</v>
+        <v>1938.66</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5099,11 +5099,13 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5118,57 +5120,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1881.37</v>
+        <v>1878.19</v>
       </c>
       <c r="C56" t="n">
-        <v>1921.78</v>
+        <v>1898.23</v>
       </c>
       <c r="D56" t="n">
-        <v>1873.35</v>
+        <v>1861.92</v>
       </c>
       <c r="E56" t="n">
-        <v>1878.14</v>
+        <v>1883.99</v>
       </c>
       <c r="F56" t="n">
-        <v>-3.24</v>
+        <v>5.86</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="H56" t="n">
-        <v>48.43</v>
+        <v>36.3</v>
       </c>
       <c r="I56" t="n">
-        <v>1809.93</v>
+        <v>1824.92</v>
       </c>
       <c r="J56" t="n">
-        <v>1842</v>
+        <v>1819.99</v>
       </c>
       <c r="K56" t="n">
-        <v>1859.92</v>
+        <v>1853.92</v>
       </c>
       <c r="L56" t="n">
-        <v>1877.83</v>
+        <v>1887.85</v>
       </c>
       <c r="M56" t="n">
-        <v>1902.83</v>
+        <v>1902.35</v>
       </c>
       <c r="N56" t="n">
-        <v>1927.82</v>
+        <v>1916.85</v>
       </c>
       <c r="O56" t="n">
-        <v>1938.66</v>
+        <v>1970.2</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5181,13 +5183,11 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5202,57 +5202,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1878.19</v>
+        <v>1884.02</v>
       </c>
       <c r="C57" t="n">
-        <v>1898.23</v>
+        <v>1889.27</v>
       </c>
       <c r="D57" t="n">
-        <v>1861.92</v>
+        <v>1862.56</v>
       </c>
       <c r="E57" t="n">
-        <v>1883.99</v>
+        <v>1880.65</v>
       </c>
       <c r="F57" t="n">
-        <v>5.86</v>
+        <v>-3.34</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0018</v>
       </c>
       <c r="H57" t="n">
-        <v>36.3</v>
+        <v>26.71</v>
       </c>
       <c r="I57" t="n">
-        <v>1824.92</v>
+        <v>1825.62</v>
       </c>
       <c r="J57" t="n">
-        <v>1819.99</v>
+        <v>1849.65</v>
       </c>
       <c r="K57" t="n">
-        <v>1853.92</v>
+        <v>1865.84</v>
       </c>
       <c r="L57" t="n">
-        <v>1887.85</v>
+        <v>1882.03</v>
       </c>
       <c r="M57" t="n">
-        <v>1902.35</v>
+        <v>1902.14</v>
       </c>
       <c r="N57" t="n">
-        <v>1916.85</v>
+        <v>1922.26</v>
       </c>
       <c r="O57" t="n">
-        <v>1970.2</v>
+        <v>1934.53</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5260,10 +5260,12 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5291,50 +5293,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1884.02</v>
+        <v>1880.61</v>
       </c>
       <c r="C58" t="n">
-        <v>1889.27</v>
+        <v>1884.72</v>
       </c>
       <c r="D58" t="n">
-        <v>1862.56</v>
+        <v>1874.33</v>
       </c>
       <c r="E58" t="n">
-        <v>1880.65</v>
+        <v>1880.91</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.34</v>
+        <v>0.26</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0001</v>
       </c>
       <c r="H58" t="n">
-        <v>26.71</v>
+        <v>10.39</v>
       </c>
       <c r="I58" t="n">
-        <v>1825.62</v>
+        <v>1835.86</v>
       </c>
       <c r="J58" t="n">
-        <v>1849.65</v>
+        <v>1856.31</v>
       </c>
       <c r="K58" t="n">
-        <v>1865.84</v>
+        <v>1867.3</v>
       </c>
       <c r="L58" t="n">
-        <v>1882.03</v>
+        <v>1878.28</v>
       </c>
       <c r="M58" t="n">
-        <v>1902.14</v>
+        <v>1894</v>
       </c>
       <c r="N58" t="n">
-        <v>1922.26</v>
+        <v>1909.72</v>
       </c>
       <c r="O58" t="n">
-        <v>1934.53</v>
+        <v>1915.98</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5342,14 +5344,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5368,74 +5368,80 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1880.61</v>
+        <v>1880.89</v>
       </c>
       <c r="C59" t="n">
-        <v>1884.72</v>
+        <v>1889.61</v>
       </c>
       <c r="D59" t="n">
-        <v>1874.33</v>
+        <v>1867.89</v>
       </c>
       <c r="E59" t="n">
-        <v>1880.91</v>
+        <v>1873.94</v>
       </c>
       <c r="F59" t="n">
-        <v>0.26</v>
+        <v>-6.97</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0037</v>
       </c>
       <c r="H59" t="n">
-        <v>10.39</v>
+        <v>21.71</v>
       </c>
       <c r="I59" t="n">
-        <v>1835.86</v>
+        <v>1863.94</v>
       </c>
       <c r="J59" t="n">
-        <v>1856.31</v>
+        <v>1871.21</v>
       </c>
       <c r="K59" t="n">
-        <v>1867.3</v>
+        <v>1875.71</v>
       </c>
       <c r="L59" t="n">
-        <v>1878.28</v>
+        <v>1880.22</v>
       </c>
       <c r="M59" t="n">
-        <v>1894</v>
+        <v>1886.1</v>
       </c>
       <c r="N59" t="n">
-        <v>1909.72</v>
+        <v>1891.99</v>
       </c>
       <c r="O59" t="n">
-        <v>1915.98</v>
+        <v>1895.11</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5450,145 +5456,141 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1880.89</v>
+        <v>1873.97</v>
       </c>
       <c r="C60" t="n">
-        <v>1889.61</v>
+        <v>1916.66</v>
       </c>
       <c r="D60" t="n">
-        <v>1867.89</v>
+        <v>1870.75</v>
       </c>
       <c r="E60" t="n">
-        <v>1873.94</v>
+        <v>1912.2</v>
       </c>
       <c r="F60" t="n">
-        <v>-6.97</v>
+        <v>38.26</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0204</v>
       </c>
       <c r="H60" t="n">
-        <v>21.71</v>
+        <v>45.91</v>
       </c>
       <c r="I60" t="n">
-        <v>1863.94</v>
+        <v>1846.18</v>
       </c>
       <c r="J60" t="n">
-        <v>1871.21</v>
+        <v>1849.83</v>
       </c>
       <c r="K60" t="n">
-        <v>1875.71</v>
+        <v>1863.09</v>
       </c>
       <c r="L60" t="n">
-        <v>1880.22</v>
+        <v>1876.35</v>
       </c>
       <c r="M60" t="n">
-        <v>1886.1</v>
+        <v>1884.8</v>
       </c>
       <c r="N60" t="n">
-        <v>1891.99</v>
+        <v>1893.25</v>
       </c>
       <c r="O60" t="n">
-        <v>1895.11</v>
+        <v>1911.32</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W60" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W60" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1873.97</v>
+        <v>1912.21</v>
       </c>
       <c r="C61" t="n">
-        <v>1916.66</v>
+        <v>1920.52</v>
       </c>
       <c r="D61" t="n">
-        <v>1870.75</v>
+        <v>1884.48</v>
       </c>
       <c r="E61" t="n">
-        <v>1912.2</v>
+        <v>1916.46</v>
       </c>
       <c r="F61" t="n">
-        <v>38.26</v>
+        <v>4.26</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.0022</v>
       </c>
       <c r="H61" t="n">
-        <v>45.91</v>
+        <v>36.05</v>
       </c>
       <c r="I61" t="n">
-        <v>1846.18</v>
+        <v>1824.84</v>
       </c>
       <c r="J61" t="n">
-        <v>1849.83</v>
+        <v>1875.54</v>
       </c>
       <c r="K61" t="n">
-        <v>1863.09</v>
+        <v>1889.25</v>
       </c>
       <c r="L61" t="n">
-        <v>1876.35</v>
+        <v>1902.95</v>
       </c>
       <c r="M61" t="n">
-        <v>1884.8</v>
+        <v>1935.16</v>
       </c>
       <c r="N61" t="n">
-        <v>1893.25</v>
+        <v>1967.36</v>
       </c>
       <c r="O61" t="n">
-        <v>1911.32</v>
+        <v>1962.57</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5596,28 +5598,24 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
@@ -5629,50 +5627,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1912.21</v>
+        <v>1916.43</v>
       </c>
       <c r="C62" t="n">
-        <v>1920.52</v>
+        <v>2327.7</v>
       </c>
       <c r="D62" t="n">
-        <v>1884.48</v>
+        <v>1905.08</v>
       </c>
       <c r="E62" t="n">
-        <v>1916.46</v>
+        <v>2251.46</v>
       </c>
       <c r="F62" t="n">
-        <v>4.26</v>
+        <v>335</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.1748</v>
       </c>
       <c r="H62" t="n">
-        <v>36.05</v>
+        <v>422.62</v>
       </c>
       <c r="I62" t="n">
-        <v>1824.84</v>
+        <v>1848.43</v>
       </c>
       <c r="J62" t="n">
-        <v>1875.54</v>
+        <v>1887.39</v>
       </c>
       <c r="K62" t="n">
-        <v>1889.25</v>
+        <v>1898.44</v>
       </c>
       <c r="L62" t="n">
-        <v>1902.95</v>
+        <v>1909.48</v>
       </c>
       <c r="M62" t="n">
-        <v>1935.16</v>
+        <v>1934.48</v>
       </c>
       <c r="N62" t="n">
-        <v>1967.36</v>
+        <v>1959.48</v>
       </c>
       <c r="O62" t="n">
-        <v>1962.57</v>
+        <v>1956.57</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5680,24 +5678,28 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
@@ -5709,50 +5711,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1916.43</v>
+        <v>2251.44</v>
       </c>
       <c r="C63" t="n">
-        <v>2327.7</v>
+        <v>2357.23</v>
       </c>
       <c r="D63" t="n">
-        <v>1905.08</v>
+        <v>2222.57</v>
       </c>
       <c r="E63" t="n">
-        <v>2251.46</v>
+        <v>2326.38</v>
       </c>
       <c r="F63" t="n">
-        <v>335</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.1748</v>
+        <v>0.0333</v>
       </c>
       <c r="H63" t="n">
-        <v>422.62</v>
+        <v>134.65</v>
       </c>
       <c r="I63" t="n">
-        <v>1848.43</v>
+        <v>1482.46</v>
       </c>
       <c r="J63" t="n">
-        <v>1887.39</v>
+        <v>1896.37</v>
       </c>
       <c r="K63" t="n">
-        <v>1898.44</v>
+        <v>2040.15</v>
       </c>
       <c r="L63" t="n">
-        <v>1909.48</v>
+        <v>2183.92</v>
       </c>
       <c r="M63" t="n">
-        <v>1934.48</v>
+        <v>2462.77</v>
       </c>
       <c r="N63" t="n">
-        <v>1959.48</v>
+        <v>2741.61</v>
       </c>
       <c r="O63" t="n">
-        <v>1956.57</v>
+        <v>2750.32</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5763,25 +5765,21 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="10" t="inlineStr">
+      <c r="S63" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
       </c>
       <c r="W63" s="9" t="inlineStr">
         <is>
@@ -5793,50 +5791,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2251.44</v>
+        <v>2326.38</v>
       </c>
       <c r="C64" t="n">
-        <v>2357.23</v>
+        <v>2545.88</v>
       </c>
       <c r="D64" t="n">
-        <v>2222.57</v>
+        <v>2324.71</v>
       </c>
       <c r="E64" t="n">
-        <v>2326.38</v>
+        <v>2515.28</v>
       </c>
       <c r="F64" t="n">
-        <v>74.93000000000001</v>
+        <v>188.9</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0333</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>134.65</v>
+        <v>221.17</v>
       </c>
       <c r="I64" t="n">
-        <v>1482.46</v>
+        <v>2087.92</v>
       </c>
       <c r="J64" t="n">
-        <v>1896.37</v>
+        <v>2209.97</v>
       </c>
       <c r="K64" t="n">
-        <v>2040.15</v>
+        <v>2259.06</v>
       </c>
       <c r="L64" t="n">
-        <v>2183.92</v>
+        <v>2308.14</v>
       </c>
       <c r="M64" t="n">
-        <v>2462.77</v>
+        <v>2393.71</v>
       </c>
       <c r="N64" t="n">
-        <v>2741.61</v>
+        <v>2479.28</v>
       </c>
       <c r="O64" t="n">
-        <v>2750.32</v>
+        <v>2491.88</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5847,21 +5845,25 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="10" t="inlineStr">
+      <c r="S64" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V64" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
       </c>
       <c r="W64" s="9" t="inlineStr">
         <is>
@@ -5873,50 +5875,50 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2326.38</v>
+        <v>2515.39</v>
       </c>
       <c r="C65" t="n">
-        <v>2545.88</v>
+        <v>2528.9</v>
       </c>
       <c r="D65" t="n">
-        <v>2324.71</v>
+        <v>2389.9</v>
       </c>
       <c r="E65" t="n">
-        <v>2515.28</v>
+        <v>2424.25</v>
       </c>
       <c r="F65" t="n">
-        <v>188.9</v>
+        <v>-91.03</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0362</v>
       </c>
       <c r="H65" t="n">
-        <v>221.17</v>
+        <v>138.99</v>
       </c>
       <c r="I65" t="n">
-        <v>2087.92</v>
+        <v>2103.54</v>
       </c>
       <c r="J65" t="n">
-        <v>2209.97</v>
+        <v>2334.1</v>
       </c>
       <c r="K65" t="n">
-        <v>2259.06</v>
+        <v>2404.7</v>
       </c>
       <c r="L65" t="n">
-        <v>2308.14</v>
+        <v>2475.29</v>
       </c>
       <c r="M65" t="n">
-        <v>2393.71</v>
+        <v>2625.87</v>
       </c>
       <c r="N65" t="n">
-        <v>2479.28</v>
+        <v>2776.45</v>
       </c>
       <c r="O65" t="n">
-        <v>2491.88</v>
+        <v>2767.05</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5924,83 +5926,83 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="n">
-        <v/>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S65" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V65" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
       </c>
       <c r="W65" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2515.39</v>
+        <v>2424.22</v>
       </c>
       <c r="C66" t="n">
-        <v>2528.9</v>
+        <v>2483.93</v>
       </c>
       <c r="D66" t="n">
-        <v>2389.9</v>
+        <v>2357.14</v>
       </c>
       <c r="E66" t="n">
-        <v>2424.25</v>
+        <v>2463.82</v>
       </c>
       <c r="F66" t="n">
-        <v>-91.03</v>
+        <v>39.56</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>-0.0362</v>
+        <v>0.0163</v>
       </c>
       <c r="H66" t="n">
-        <v>138.99</v>
+        <v>126.79</v>
       </c>
       <c r="I66" t="n">
-        <v>2103.54</v>
+        <v>2250.91</v>
       </c>
       <c r="J66" t="n">
-        <v>2334.1</v>
+        <v>2267.68</v>
       </c>
       <c r="K66" t="n">
-        <v>2404.7</v>
+        <v>2354.75</v>
       </c>
       <c r="L66" t="n">
-        <v>2475.29</v>
+        <v>2441.83</v>
       </c>
       <c r="M66" t="n">
-        <v>2625.87</v>
+        <v>2493.75</v>
       </c>
       <c r="N66" t="n">
-        <v>2776.45</v>
+        <v>2545.67</v>
       </c>
       <c r="O66" t="n">
-        <v>2767.05</v>
+        <v>2667.89</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6008,14 +6010,12 @@
       <c r="Q66" s="6" t="n">
         <v/>
       </c>
-      <c r="R66" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R66" s="6" t="n">
+        <v/>
       </c>
       <c r="S66" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T66" s="8" t="n">
@@ -6041,50 +6041,50 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2424.22</v>
+        <v>2463.64</v>
       </c>
       <c r="C67" t="n">
-        <v>2483.93</v>
+        <v>2531.74</v>
       </c>
       <c r="D67" t="n">
-        <v>2357.14</v>
+        <v>2425.39</v>
       </c>
       <c r="E67" t="n">
-        <v>2463.82</v>
+        <v>2481.83</v>
       </c>
       <c r="F67" t="n">
-        <v>39.56</v>
+        <v>18.02</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0073</v>
       </c>
       <c r="H67" t="n">
-        <v>126.79</v>
+        <v>106.36</v>
       </c>
       <c r="I67" t="n">
-        <v>2250.91</v>
+        <v>2230.35</v>
       </c>
       <c r="J67" t="n">
-        <v>2267.68</v>
+        <v>2358.67</v>
       </c>
       <c r="K67" t="n">
-        <v>2354.75</v>
+        <v>2400.42</v>
       </c>
       <c r="L67" t="n">
-        <v>2441.83</v>
+        <v>2442.18</v>
       </c>
       <c r="M67" t="n">
-        <v>2493.75</v>
+        <v>2527.21</v>
       </c>
       <c r="N67" t="n">
-        <v>2545.67</v>
+        <v>2612.25</v>
       </c>
       <c r="O67" t="n">
-        <v>2667.89</v>
+        <v>2610.72</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6095,13 +6095,15 @@
       <c r="R67" s="6" t="n">
         <v/>
       </c>
-      <c r="S67" s="10" t="inlineStr">
+      <c r="S67" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T67" s="8" t="n">
-        <v/>
+      <c r="T67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U67" s="8" t="n">
         <v/>
@@ -6114,59 +6116,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2463.64</v>
+        <v>2481.78</v>
       </c>
       <c r="C68" t="n">
-        <v>2531.74</v>
+        <v>2531.08</v>
       </c>
       <c r="D68" t="n">
-        <v>2425.39</v>
+        <v>2416.6</v>
       </c>
       <c r="E68" t="n">
-        <v>2481.83</v>
+        <v>2443.16</v>
       </c>
       <c r="F68" t="n">
-        <v>18.02</v>
+        <v>-38.67</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0156</v>
       </c>
       <c r="H68" t="n">
-        <v>106.36</v>
+        <v>114.48</v>
       </c>
       <c r="I68" t="n">
-        <v>2230.35</v>
+        <v>2319.03</v>
       </c>
       <c r="J68" t="n">
-        <v>2358.67</v>
+        <v>2377.11</v>
       </c>
       <c r="K68" t="n">
-        <v>2400.42</v>
+        <v>2428.65</v>
       </c>
       <c r="L68" t="n">
-        <v>2442.18</v>
+        <v>2480.2</v>
       </c>
       <c r="M68" t="n">
-        <v>2527.21</v>
+        <v>2535.01</v>
       </c>
       <c r="N68" t="n">
-        <v>2612.25</v>
+        <v>2589.82</v>
       </c>
       <c r="O68" t="n">
-        <v>2610.72</v>
+        <v>2638.1</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
@@ -6174,18 +6172,18 @@
       <c r="Q68" s="6" t="n">
         <v/>
       </c>
-      <c r="R68" s="6" t="n">
-        <v/>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S68" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="n">
+        <v/>
       </c>
       <c r="U68" s="8" t="n">
         <v/>
@@ -6198,55 +6196,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr"/>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2481.78</v>
+        <v>2442.49</v>
       </c>
       <c r="C69" t="n">
-        <v>2531.08</v>
+        <v>2514.67</v>
       </c>
       <c r="D69" t="n">
-        <v>2416.6</v>
+        <v>2432.51</v>
       </c>
       <c r="E69" t="n">
-        <v>2443.16</v>
+        <v>2506.26</v>
       </c>
       <c r="F69" t="n">
-        <v>-38.67</v>
+        <v>63.1</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0258</v>
       </c>
       <c r="H69" t="n">
-        <v>114.48</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>2319.03</v>
+        <v>2302.12</v>
       </c>
       <c r="J69" t="n">
-        <v>2377.11</v>
+        <v>2313.34</v>
       </c>
       <c r="K69" t="n">
-        <v>2428.65</v>
+        <v>2385.92</v>
       </c>
       <c r="L69" t="n">
-        <v>2480.2</v>
+        <v>2458.5</v>
       </c>
       <c r="M69" t="n">
-        <v>2535.01</v>
+        <v>2500.4</v>
       </c>
       <c r="N69" t="n">
-        <v>2589.82</v>
+        <v>2542.3</v>
       </c>
       <c r="O69" t="n">
-        <v>2638.1</v>
+        <v>2645.57</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6254,19 +6256,19 @@
       <c r="Q69" s="6" t="n">
         <v/>
       </c>
-      <c r="R69" s="6" t="inlineStr">
+      <c r="R69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S69" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S69" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T69" s="8" t="n">
-        <v/>
-      </c>
       <c r="U69" s="8" t="n">
         <v/>
       </c>
@@ -6280,57 +6282,57 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2442.49</v>
+        <v>2506.24</v>
       </c>
       <c r="C70" t="n">
-        <v>2514.67</v>
+        <v>2564.27</v>
       </c>
       <c r="D70" t="n">
-        <v>2432.51</v>
+        <v>2481.94</v>
       </c>
       <c r="E70" t="n">
-        <v>2506.26</v>
+        <v>2510.41</v>
       </c>
       <c r="F70" t="n">
-        <v>63.1</v>
+        <v>4.15</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.0258</v>
+        <v>0.0017</v>
       </c>
       <c r="H70" t="n">
-        <v>82.15000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="I70" t="n">
-        <v>2302.12</v>
+        <v>2350.36</v>
       </c>
       <c r="J70" t="n">
-        <v>2313.34</v>
+        <v>2440.44</v>
       </c>
       <c r="K70" t="n">
-        <v>2385.92</v>
+        <v>2465.18</v>
       </c>
       <c r="L70" t="n">
-        <v>2458.5</v>
+        <v>2489.93</v>
       </c>
       <c r="M70" t="n">
-        <v>2500.4</v>
+        <v>2547.34</v>
       </c>
       <c r="N70" t="n">
-        <v>2542.3</v>
+        <v>2604.75</v>
       </c>
       <c r="O70" t="n">
-        <v>2645.57</v>
+        <v>2596.82</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
@@ -6341,14 +6343,14 @@
       <c r="R70" s="6" t="n">
         <v/>
       </c>
-      <c r="S70" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T70" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U70" s="8" t="n">
@@ -6362,78 +6364,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2506.24</v>
+        <v>2510.67</v>
       </c>
       <c r="C71" t="n">
-        <v>2564.27</v>
+        <v>2534.01</v>
       </c>
       <c r="D71" t="n">
-        <v>2481.94</v>
+        <v>2408.72</v>
       </c>
       <c r="E71" t="n">
-        <v>2510.41</v>
+        <v>2442.54</v>
       </c>
       <c r="F71" t="n">
-        <v>4.15</v>
+        <v>-67.87</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.027</v>
       </c>
       <c r="H71" t="n">
-        <v>82.33</v>
+        <v>125.29</v>
       </c>
       <c r="I71" t="n">
-        <v>2350.36</v>
+        <v>2399.62</v>
       </c>
       <c r="J71" t="n">
-        <v>2440.44</v>
+        <v>2421.73</v>
       </c>
       <c r="K71" t="n">
-        <v>2465.18</v>
+        <v>2469.25</v>
       </c>
       <c r="L71" t="n">
-        <v>2489.93</v>
+        <v>2516.76</v>
       </c>
       <c r="M71" t="n">
-        <v>2547.34</v>
+        <v>2551.57</v>
       </c>
       <c r="N71" t="n">
-        <v>2604.75</v>
+        <v>2586.39</v>
       </c>
       <c r="O71" t="n">
-        <v>2596.82</v>
+        <v>2646.6</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
       </c>
-      <c r="Q71" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R71" s="6" t="n">
-        <v/>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S71" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="n">
+        <v/>
       </c>
       <c r="U71" s="8" t="n">
         <v/>
@@ -6446,72 +6446,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr"/>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2510.67</v>
+        <v>2442.56</v>
       </c>
       <c r="C72" t="n">
-        <v>2534.01</v>
+        <v>2459.63</v>
       </c>
       <c r="D72" t="n">
-        <v>2408.72</v>
+        <v>2430.81</v>
       </c>
       <c r="E72" t="n">
-        <v>2442.54</v>
+        <v>2457.69</v>
       </c>
       <c r="F72" t="n">
-        <v>-67.87</v>
+        <v>15.15</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.027</v>
+        <v>0.0062</v>
       </c>
       <c r="H72" t="n">
-        <v>125.29</v>
+        <v>28.82</v>
       </c>
       <c r="I72" t="n">
-        <v>2399.62</v>
+        <v>2283.43</v>
       </c>
       <c r="J72" t="n">
-        <v>2421.73</v>
+        <v>2302.83</v>
       </c>
       <c r="K72" t="n">
-        <v>2469.25</v>
+        <v>2379.89</v>
       </c>
       <c r="L72" t="n">
-        <v>2516.76</v>
+        <v>2456.95</v>
       </c>
       <c r="M72" t="n">
-        <v>2551.57</v>
+        <v>2505.18</v>
       </c>
       <c r="N72" t="n">
-        <v>2586.39</v>
+        <v>2553.41</v>
       </c>
       <c r="O72" t="n">
-        <v>2646.6</v>
+        <v>2659.3</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
       </c>
-      <c r="Q72" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R72" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R72" s="6" t="n">
+        <v/>
       </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T72" s="8" t="n">
@@ -6530,84 +6530,96 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2442.56</v>
+        <v>2457.69</v>
       </c>
       <c r="C73" t="n">
-        <v>2459.63</v>
+        <v>2532.96</v>
       </c>
       <c r="D73" t="n">
-        <v>2430.81</v>
+        <v>2389.47</v>
       </c>
       <c r="E73" t="n">
-        <v>2457.69</v>
+        <v>2417.94</v>
       </c>
       <c r="F73" t="n">
-        <v>15.15</v>
+        <v>-39.75</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H73" t="n">
-        <v>28.82</v>
+        <v>143.49</v>
       </c>
       <c r="I73" t="n">
-        <v>2283.43</v>
+        <v>2401.99</v>
       </c>
       <c r="J73" t="n">
-        <v>2302.83</v>
+        <v>2435.1</v>
       </c>
       <c r="K73" t="n">
-        <v>2379.89</v>
+        <v>2443.28</v>
       </c>
       <c r="L73" t="n">
-        <v>2456.95</v>
+        <v>2451.45</v>
       </c>
       <c r="M73" t="n">
-        <v>2505.18</v>
+        <v>2472.1</v>
       </c>
       <c r="N73" t="n">
-        <v>2553.41</v>
+        <v>2492.74</v>
       </c>
       <c r="O73" t="n">
-        <v>2659.3</v>
-      </c>
-      <c r="P73" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q73" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R73" s="6" t="n">
-        <v/>
+        <v>2488.45</v>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R73" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S73" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U73" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V73" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W73" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W73" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -6619,85 +6631,75 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2457.69</v>
+        <v>2417.9</v>
       </c>
       <c r="C74" t="n">
-        <v>2532.96</v>
+        <v>2488.92</v>
       </c>
       <c r="D74" t="n">
-        <v>2389.47</v>
+        <v>2401.81</v>
       </c>
       <c r="E74" t="n">
-        <v>2417.94</v>
+        <v>2466.82</v>
       </c>
       <c r="F74" t="n">
-        <v>-39.75</v>
+        <v>48.88</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.0202</v>
       </c>
       <c r="H74" t="n">
-        <v>143.49</v>
+        <v>87.11</v>
       </c>
       <c r="I74" t="n">
-        <v>2401.99</v>
+        <v>2245.98</v>
       </c>
       <c r="J74" t="n">
-        <v>2435.1</v>
+        <v>2252.81</v>
       </c>
       <c r="K74" t="n">
-        <v>2443.28</v>
+        <v>2346.19</v>
       </c>
       <c r="L74" t="n">
-        <v>2451.45</v>
+        <v>2439.58</v>
       </c>
       <c r="M74" t="n">
-        <v>2472.1</v>
+        <v>2489.68</v>
       </c>
       <c r="N74" t="n">
-        <v>2492.74</v>
+        <v>2539.79</v>
       </c>
       <c r="O74" t="n">
-        <v>2488.45</v>
-      </c>
-      <c r="P74" s="6" t="inlineStr">
+        <v>2676.45</v>
+      </c>
+      <c r="P74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S74" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q74" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R74" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S74" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U74" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V74" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U74" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V74" s="8" t="n">
+        <v/>
       </c>
       <c r="W74" s="11" t="inlineStr">
         <is>
@@ -6706,76 +6708,78 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2417.9</v>
+        <v>2466.58</v>
       </c>
       <c r="C75" t="n">
-        <v>2488.92</v>
+        <v>2484.4</v>
       </c>
       <c r="D75" t="n">
-        <v>2401.81</v>
+        <v>2383.8</v>
       </c>
       <c r="E75" t="n">
-        <v>2466.82</v>
+        <v>2417.84</v>
       </c>
       <c r="F75" t="n">
-        <v>48.88</v>
+        <v>-48.98</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.0202</v>
+        <v>-0.0199</v>
       </c>
       <c r="H75" t="n">
-        <v>87.11</v>
+        <v>100.6</v>
       </c>
       <c r="I75" t="n">
-        <v>2245.98</v>
+        <v>2314.69</v>
       </c>
       <c r="J75" t="n">
-        <v>2252.81</v>
+        <v>2390.43</v>
       </c>
       <c r="K75" t="n">
-        <v>2346.19</v>
+        <v>2423.26</v>
       </c>
       <c r="L75" t="n">
-        <v>2439.58</v>
+        <v>2456.09</v>
       </c>
       <c r="M75" t="n">
-        <v>2489.68</v>
+        <v>2510.38</v>
       </c>
       <c r="N75" t="n">
-        <v>2539.79</v>
+        <v>2564.66</v>
       </c>
       <c r="O75" t="n">
-        <v>2676.45</v>
+        <v>2576.04</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
       </c>
-      <c r="Q75" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R75" s="6" t="n">
-        <v/>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R75" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S75" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T75" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="n">
+        <v/>
       </c>
       <c r="U75" s="8" t="n">
         <v/>
@@ -6788,74 +6792,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2466.58</v>
+        <v>2417.83</v>
       </c>
       <c r="C76" t="n">
-        <v>2484.4</v>
+        <v>2427.4</v>
       </c>
       <c r="D76" t="n">
-        <v>2383.8</v>
+        <v>2356.19</v>
       </c>
       <c r="E76" t="n">
-        <v>2417.84</v>
+        <v>2391.5</v>
       </c>
       <c r="F76" t="n">
-        <v>-48.98</v>
+        <v>-26.34</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.0109</v>
       </c>
       <c r="H76" t="n">
-        <v>100.6</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>2314.69</v>
+        <v>2283.21</v>
       </c>
       <c r="J76" t="n">
-        <v>2390.43</v>
+        <v>2309.12</v>
       </c>
       <c r="K76" t="n">
-        <v>2423.26</v>
+        <v>2367.54</v>
       </c>
       <c r="L76" t="n">
-        <v>2456.09</v>
+        <v>2425.97</v>
       </c>
       <c r="M76" t="n">
-        <v>2510.38</v>
+        <v>2468.14</v>
       </c>
       <c r="N76" t="n">
-        <v>2564.66</v>
+        <v>2510.31</v>
       </c>
       <c r="O76" t="n">
-        <v>2576.04</v>
+        <v>2584.99</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
       </c>
-      <c r="Q76" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q76" s="6" t="n">
+        <v/>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S76" s="7" t="inlineStr">
+      <c r="S76" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -6879,50 +6877,50 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2417.83</v>
+        <v>2391.6</v>
       </c>
       <c r="C77" t="n">
-        <v>2427.4</v>
+        <v>2526.95</v>
       </c>
       <c r="D77" t="n">
-        <v>2356.19</v>
+        <v>2370.42</v>
       </c>
       <c r="E77" t="n">
-        <v>2391.5</v>
+        <v>2508.02</v>
       </c>
       <c r="F77" t="n">
-        <v>-26.34</v>
+        <v>116.52</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0109</v>
+        <v>0.0487</v>
       </c>
       <c r="H77" t="n">
-        <v>71.20999999999999</v>
+        <v>156.53</v>
       </c>
       <c r="I77" t="n">
-        <v>2283.21</v>
+        <v>2284.97</v>
       </c>
       <c r="J77" t="n">
-        <v>2309.12</v>
+        <v>2320.14</v>
       </c>
       <c r="K77" t="n">
-        <v>2367.54</v>
+        <v>2355.89</v>
       </c>
       <c r="L77" t="n">
-        <v>2425.97</v>
+        <v>2391.65</v>
       </c>
       <c r="M77" t="n">
-        <v>2468.14</v>
+        <v>2427.11</v>
       </c>
       <c r="N77" t="n">
-        <v>2510.31</v>
+        <v>2462.57</v>
       </c>
       <c r="O77" t="n">
-        <v>2584.99</v>
+        <v>2498.61</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
@@ -6930,28 +6928,32 @@
       <c r="Q77" s="6" t="n">
         <v/>
       </c>
-      <c r="R77" s="6" t="inlineStr">
+      <c r="R77" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S77" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V77" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S77" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U77" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V77" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W77" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W77" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X77" t="inlineStr"/>
@@ -6959,50 +6961,50 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2391.6</v>
+        <v>2508.02</v>
       </c>
       <c r="C78" t="n">
-        <v>2526.95</v>
+        <v>2545.62</v>
       </c>
       <c r="D78" t="n">
-        <v>2370.42</v>
+        <v>2432.35</v>
       </c>
       <c r="E78" t="n">
-        <v>2508.02</v>
+        <v>2456.08</v>
       </c>
       <c r="F78" t="n">
-        <v>116.52</v>
+        <v>-51.94</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.0487</v>
+        <v>-0.0207</v>
       </c>
       <c r="H78" t="n">
-        <v>156.53</v>
+        <v>113.27</v>
       </c>
       <c r="I78" t="n">
-        <v>2284.97</v>
+        <v>2213.88</v>
       </c>
       <c r="J78" t="n">
-        <v>2320.14</v>
+        <v>2381.16</v>
       </c>
       <c r="K78" t="n">
-        <v>2355.89</v>
+        <v>2429.75</v>
       </c>
       <c r="L78" t="n">
-        <v>2391.65</v>
+        <v>2478.35</v>
       </c>
       <c r="M78" t="n">
-        <v>2427.11</v>
+        <v>2586.29</v>
       </c>
       <c r="N78" t="n">
-        <v>2462.57</v>
+        <v>2694.22</v>
       </c>
       <c r="O78" t="n">
-        <v>2498.61</v>
+        <v>2683.48</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -7015,78 +7017,76 @@
       </c>
       <c r="S78" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T78" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U78" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V78" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U78" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V78" s="8" t="n">
+        <v/>
       </c>
       <c r="W78" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr"/>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2508.02</v>
+        <v>2455.99</v>
       </c>
       <c r="C79" t="n">
-        <v>2545.62</v>
+        <v>2492.01</v>
       </c>
       <c r="D79" t="n">
-        <v>2432.35</v>
+        <v>2445.69</v>
       </c>
       <c r="E79" t="n">
-        <v>2456.08</v>
+        <v>2480.74</v>
       </c>
       <c r="F79" t="n">
-        <v>-51.94</v>
+        <v>24.66</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0207</v>
+        <v>0.01</v>
       </c>
       <c r="H79" t="n">
-        <v>113.27</v>
+        <v>46.32</v>
       </c>
       <c r="I79" t="n">
-        <v>2213.88</v>
+        <v>2319.08</v>
       </c>
       <c r="J79" t="n">
-        <v>2381.16</v>
+        <v>2326.35</v>
       </c>
       <c r="K79" t="n">
-        <v>2429.75</v>
+        <v>2399.44</v>
       </c>
       <c r="L79" t="n">
-        <v>2478.35</v>
+        <v>2472.53</v>
       </c>
       <c r="M79" t="n">
-        <v>2586.29</v>
+        <v>2512.71</v>
       </c>
       <c r="N79" t="n">
-        <v>2694.22</v>
+        <v>2552.89</v>
       </c>
       <c r="O79" t="n">
-        <v>2683.48</v>
+        <v>2658.89</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T79" s="8" t="n">
@@ -7125,50 +7125,50 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2455.99</v>
+        <v>2480.82</v>
       </c>
       <c r="C80" t="n">
-        <v>2492.01</v>
+        <v>2525.32</v>
       </c>
       <c r="D80" t="n">
-        <v>2445.69</v>
+        <v>2468.19</v>
       </c>
       <c r="E80" t="n">
-        <v>2480.74</v>
+        <v>2514.55</v>
       </c>
       <c r="F80" t="n">
-        <v>24.66</v>
+        <v>33.81</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0136</v>
       </c>
       <c r="H80" t="n">
-        <v>46.32</v>
+        <v>57.13</v>
       </c>
       <c r="I80" t="n">
-        <v>2319.08</v>
+        <v>2399.37</v>
       </c>
       <c r="J80" t="n">
-        <v>2326.35</v>
+        <v>2440.36</v>
       </c>
       <c r="K80" t="n">
-        <v>2399.44</v>
+        <v>2457.58</v>
       </c>
       <c r="L80" t="n">
-        <v>2472.53</v>
+        <v>2474.79</v>
       </c>
       <c r="M80" t="n">
-        <v>2512.71</v>
+        <v>2503.9</v>
       </c>
       <c r="N80" t="n">
-        <v>2552.89</v>
+        <v>2533</v>
       </c>
       <c r="O80" t="n">
-        <v>2658.89</v>
+        <v>2538.33</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7179,13 +7179,15 @@
       <c r="R80" s="6" t="n">
         <v/>
       </c>
-      <c r="S80" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="n">
-        <v/>
+      <c r="S80" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U80" s="8" t="n">
         <v/>
@@ -7198,59 +7200,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2480.82</v>
+        <v>2514.58</v>
       </c>
       <c r="C81" t="n">
-        <v>2525.32</v>
+        <v>2534.86</v>
       </c>
       <c r="D81" t="n">
-        <v>2468.19</v>
+        <v>2466.91</v>
       </c>
       <c r="E81" t="n">
-        <v>2514.55</v>
+        <v>2490.96</v>
       </c>
       <c r="F81" t="n">
-        <v>33.81</v>
+        <v>-23.59</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0094</v>
       </c>
       <c r="H81" t="n">
-        <v>57.13</v>
+        <v>67.95</v>
       </c>
       <c r="I81" t="n">
-        <v>2399.37</v>
+        <v>2411.07</v>
       </c>
       <c r="J81" t="n">
-        <v>2440.36</v>
+        <v>2466.32</v>
       </c>
       <c r="K81" t="n">
-        <v>2457.58</v>
+        <v>2485.99</v>
       </c>
       <c r="L81" t="n">
-        <v>2474.79</v>
+        <v>2505.65</v>
       </c>
       <c r="M81" t="n">
-        <v>2503.9</v>
+        <v>2543.11</v>
       </c>
       <c r="N81" t="n">
-        <v>2533</v>
+        <v>2580.57</v>
       </c>
       <c r="O81" t="n">
-        <v>2538.33</v>
+        <v>2582.45</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7258,18 +7256,18 @@
       <c r="Q81" s="6" t="n">
         <v/>
       </c>
-      <c r="R81" s="6" t="n">
-        <v/>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S81" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="n">
+        <v/>
       </c>
       <c r="U81" s="8" t="n">
         <v/>
@@ -7282,55 +7280,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr"/>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2514.58</v>
+        <v>2490.92</v>
       </c>
       <c r="C82" t="n">
-        <v>2534.86</v>
+        <v>2506.75</v>
       </c>
       <c r="D82" t="n">
-        <v>2466.91</v>
+        <v>2441.33</v>
       </c>
       <c r="E82" t="n">
-        <v>2490.96</v>
+        <v>2484.94</v>
       </c>
       <c r="F82" t="n">
-        <v>-23.59</v>
+        <v>-6.02</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0024</v>
       </c>
       <c r="H82" t="n">
-        <v>67.95</v>
+        <v>65.42</v>
       </c>
       <c r="I82" t="n">
-        <v>2411.07</v>
+        <v>2398.96</v>
       </c>
       <c r="J82" t="n">
-        <v>2466.32</v>
+        <v>2418.04</v>
       </c>
       <c r="K82" t="n">
-        <v>2485.99</v>
+        <v>2456.98</v>
       </c>
       <c r="L82" t="n">
-        <v>2505.65</v>
+        <v>2495.92</v>
       </c>
       <c r="M82" t="n">
-        <v>2543.11</v>
+        <v>2524.93</v>
       </c>
       <c r="N82" t="n">
-        <v>2580.57</v>
+        <v>2553.94</v>
       </c>
       <c r="O82" t="n">
-        <v>2582.45</v>
+        <v>2602.81</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7340,12 +7342,12 @@
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S82" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S82" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T82" s="8" t="n">
@@ -7364,57 +7366,57 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2490.92</v>
+        <v>2484.89</v>
       </c>
       <c r="C83" t="n">
-        <v>2506.75</v>
+        <v>2522.37</v>
       </c>
       <c r="D83" t="n">
-        <v>2441.33</v>
+        <v>2443.7</v>
       </c>
       <c r="E83" t="n">
-        <v>2484.94</v>
+        <v>2466.91</v>
       </c>
       <c r="F83" t="n">
-        <v>-6.02</v>
+        <v>-18.03</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0073</v>
       </c>
       <c r="H83" t="n">
-        <v>65.42</v>
+        <v>78.67</v>
       </c>
       <c r="I83" t="n">
-        <v>2398.96</v>
+        <v>2375.9</v>
       </c>
       <c r="J83" t="n">
-        <v>2418.04</v>
+        <v>2424.97</v>
       </c>
       <c r="K83" t="n">
-        <v>2456.98</v>
+        <v>2452.23</v>
       </c>
       <c r="L83" t="n">
-        <v>2495.92</v>
+        <v>2479.49</v>
       </c>
       <c r="M83" t="n">
-        <v>2524.93</v>
+        <v>2517.65</v>
       </c>
       <c r="N83" t="n">
-        <v>2553.94</v>
+        <v>2555.82</v>
       </c>
       <c r="O83" t="n">
-        <v>2602.81</v>
+        <v>2572.18</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
@@ -7427,13 +7429,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S83" s="7" t="inlineStr">
+      <c r="S83" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T83" s="8" t="n">
-        <v/>
+      <c r="T83" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U83" s="8" t="n">
         <v/>
@@ -7448,57 +7452,57 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2484.89</v>
+        <v>2466.91</v>
       </c>
       <c r="C84" t="n">
-        <v>2522.37</v>
+        <v>2483.72</v>
       </c>
       <c r="D84" t="n">
-        <v>2443.7</v>
+        <v>2406.91</v>
       </c>
       <c r="E84" t="n">
-        <v>2466.91</v>
+        <v>2437.1</v>
       </c>
       <c r="F84" t="n">
-        <v>-18.03</v>
+        <v>-29.82</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0121</v>
       </c>
       <c r="H84" t="n">
-        <v>78.67</v>
+        <v>76.81</v>
       </c>
       <c r="I84" t="n">
-        <v>2375.9</v>
+        <v>2365.04</v>
       </c>
       <c r="J84" t="n">
-        <v>2424.97</v>
+        <v>2380.19</v>
       </c>
       <c r="K84" t="n">
-        <v>2452.23</v>
+        <v>2427.58</v>
       </c>
       <c r="L84" t="n">
-        <v>2479.49</v>
+        <v>2474.97</v>
       </c>
       <c r="M84" t="n">
-        <v>2517.65</v>
+        <v>2506.25</v>
       </c>
       <c r="N84" t="n">
-        <v>2555.82</v>
+        <v>2537.52</v>
       </c>
       <c r="O84" t="n">
-        <v>2572.18</v>
+        <v>2601.04</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
@@ -7508,18 +7512,16 @@
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S84" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S84" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="n">
+        <v/>
       </c>
       <c r="U84" s="8" t="n">
         <v/>
@@ -7534,57 +7536,57 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2466.91</v>
+        <v>2437.14</v>
       </c>
       <c r="C85" t="n">
-        <v>2483.72</v>
+        <v>2663.05</v>
       </c>
       <c r="D85" t="n">
-        <v>2406.91</v>
+        <v>2435.29</v>
       </c>
       <c r="E85" t="n">
-        <v>2437.1</v>
+        <v>2514.73</v>
       </c>
       <c r="F85" t="n">
-        <v>-29.82</v>
+        <v>77.64</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.0121</v>
+        <v>0.0319</v>
       </c>
       <c r="H85" t="n">
-        <v>76.81</v>
+        <v>227.76</v>
       </c>
       <c r="I85" t="n">
-        <v>2365.04</v>
+        <v>2330.09</v>
       </c>
       <c r="J85" t="n">
-        <v>2380.19</v>
+        <v>2356.18</v>
       </c>
       <c r="K85" t="n">
-        <v>2427.58</v>
+        <v>2398.69</v>
       </c>
       <c r="L85" t="n">
-        <v>2474.97</v>
+        <v>2441.21</v>
       </c>
       <c r="M85" t="n">
-        <v>2506.25</v>
+        <v>2475.51</v>
       </c>
       <c r="N85" t="n">
-        <v>2537.52</v>
+        <v>2509.8</v>
       </c>
       <c r="O85" t="n">
-        <v>2601.04</v>
+        <v>2560.53</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7592,83 +7594,83 @@
       <c r="Q85" s="6" t="n">
         <v/>
       </c>
-      <c r="R85" s="6" t="inlineStr">
+      <c r="R85" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S85" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U85" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S85" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U85" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V85" s="8" t="n">
-        <v/>
+      <c r="V85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W85" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2437.14</v>
+        <v>2514.77</v>
       </c>
       <c r="C86" t="n">
-        <v>2663.05</v>
+        <v>2544.47</v>
       </c>
       <c r="D86" t="n">
-        <v>2435.29</v>
+        <v>2508.8</v>
       </c>
       <c r="E86" t="n">
-        <v>2514.73</v>
+        <v>2525.94</v>
       </c>
       <c r="F86" t="n">
-        <v>77.64</v>
+        <v>11.21</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.0319</v>
+        <v>0.0045</v>
       </c>
       <c r="H86" t="n">
-        <v>227.76</v>
+        <v>35.67</v>
       </c>
       <c r="I86" t="n">
-        <v>2330.09</v>
+        <v>2207.52</v>
       </c>
       <c r="J86" t="n">
-        <v>2356.18</v>
+        <v>2269.75</v>
       </c>
       <c r="K86" t="n">
-        <v>2398.69</v>
+        <v>2400.85</v>
       </c>
       <c r="L86" t="n">
-        <v>2441.21</v>
+        <v>2531.95</v>
       </c>
       <c r="M86" t="n">
-        <v>2475.51</v>
+        <v>2628.62</v>
       </c>
       <c r="N86" t="n">
-        <v>2509.8</v>
+        <v>2725.28</v>
       </c>
       <c r="O86" t="n">
-        <v>2560.53</v>
+        <v>2890.82</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7681,91 +7683,95 @@
       </c>
       <c r="S86" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U86" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U86" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V86" s="8" t="n">
+        <v/>
       </c>
       <c r="W86" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr"/>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2514.77</v>
+        <v>2525.94</v>
       </c>
       <c r="C87" t="n">
-        <v>2544.47</v>
+        <v>2526.85</v>
       </c>
       <c r="D87" t="n">
-        <v>2508.8</v>
+        <v>2462.84</v>
       </c>
       <c r="E87" t="n">
-        <v>2525.94</v>
+        <v>2477.02</v>
       </c>
       <c r="F87" t="n">
-        <v>11.21</v>
+        <v>-48.92</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0194</v>
       </c>
       <c r="H87" t="n">
-        <v>35.67</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>2207.52</v>
+        <v>2473.13</v>
       </c>
       <c r="J87" t="n">
-        <v>2269.75</v>
+        <v>2489.93</v>
       </c>
       <c r="K87" t="n">
-        <v>2400.85</v>
+        <v>2508.11</v>
       </c>
       <c r="L87" t="n">
-        <v>2531.95</v>
+        <v>2526.29</v>
       </c>
       <c r="M87" t="n">
-        <v>2628.62</v>
+        <v>2543.78</v>
       </c>
       <c r="N87" t="n">
-        <v>2725.28</v>
+        <v>2561.27</v>
       </c>
       <c r="O87" t="n">
-        <v>2890.82</v>
-      </c>
-      <c r="P87" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q87" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R87" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S87" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>2580.14</v>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S87" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T87" s="8" t="n">
@@ -7777,148 +7783,148 @@
       <c r="V87" s="8" t="n">
         <v/>
       </c>
-      <c r="W87" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W87" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2525.94</v>
+        <v>2476.6</v>
       </c>
       <c r="C88" t="n">
-        <v>2526.85</v>
+        <v>2612.4</v>
       </c>
       <c r="D88" t="n">
-        <v>2462.84</v>
+        <v>2465.43</v>
       </c>
       <c r="E88" t="n">
-        <v>2477.02</v>
+        <v>2514.41</v>
       </c>
       <c r="F88" t="n">
-        <v>-48.92</v>
+        <v>37.39</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-0.0194</v>
+        <v>0.0151</v>
       </c>
       <c r="H88" t="n">
-        <v>64.01000000000001</v>
+        <v>146.98</v>
       </c>
       <c r="I88" t="n">
-        <v>2473.13</v>
+        <v>2398.83</v>
       </c>
       <c r="J88" t="n">
-        <v>2489.93</v>
+        <v>2404.09</v>
       </c>
       <c r="K88" t="n">
-        <v>2508.11</v>
+        <v>2445.01</v>
       </c>
       <c r="L88" t="n">
-        <v>2526.29</v>
+        <v>2485.93</v>
       </c>
       <c r="M88" t="n">
-        <v>2543.78</v>
+        <v>2509.03</v>
       </c>
       <c r="N88" t="n">
-        <v>2561.27</v>
+        <v>2532.12</v>
       </c>
       <c r="O88" t="n">
-        <v>2580.14</v>
-      </c>
-      <c r="P88" s="6" t="inlineStr">
+        <v>2590.87</v>
+      </c>
+      <c r="P88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S88" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q88" s="6" t="inlineStr">
+      <c r="U88" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R88" s="6" t="inlineStr">
+      <c r="V88" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S88" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V88" s="8" t="n">
-        <v/>
-      </c>
       <c r="W88" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr"/>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2476.6</v>
+        <v>2514.36</v>
       </c>
       <c r="C89" t="n">
-        <v>2612.4</v>
+        <v>2519.32</v>
       </c>
       <c r="D89" t="n">
-        <v>2465.43</v>
+        <v>2357.96</v>
       </c>
       <c r="E89" t="n">
-        <v>2514.41</v>
+        <v>2399.09</v>
       </c>
       <c r="F89" t="n">
-        <v>37.39</v>
+        <v>-115.32</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.0459</v>
       </c>
       <c r="H89" t="n">
-        <v>146.98</v>
+        <v>161.36</v>
       </c>
       <c r="I89" t="n">
-        <v>2398.83</v>
+        <v>2318.45</v>
       </c>
       <c r="J89" t="n">
-        <v>2404.09</v>
+        <v>2355.18</v>
       </c>
       <c r="K89" t="n">
-        <v>2445.01</v>
+        <v>2440.92</v>
       </c>
       <c r="L89" t="n">
-        <v>2485.93</v>
+        <v>2526.66</v>
       </c>
       <c r="M89" t="n">
-        <v>2509.03</v>
+        <v>2587.9</v>
       </c>
       <c r="N89" t="n">
-        <v>2532.12</v>
+        <v>2649.13</v>
       </c>
       <c r="O89" t="n">
-        <v>2590.87</v>
+        <v>2759.38</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7926,87 +7932,79 @@
       <c r="Q89" s="6" t="n">
         <v/>
       </c>
-      <c r="R89" s="6" t="n">
-        <v/>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S89" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V89" s="8" t="n">
+        <v/>
       </c>
       <c r="W89" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2514.36</v>
+        <v>2416.14</v>
       </c>
       <c r="C90" t="n">
-        <v>2519.32</v>
+        <v>2424.06</v>
       </c>
       <c r="D90" t="n">
-        <v>2357.96</v>
+        <v>2416.13</v>
       </c>
       <c r="E90" t="n">
-        <v>2399.09</v>
+        <v>2412.42</v>
       </c>
       <c r="F90" t="n">
-        <v>-115.32</v>
+        <v>13.33</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0459</v>
+        <v>0.0056</v>
       </c>
       <c r="H90" t="n">
-        <v>161.36</v>
+        <v>7.93</v>
       </c>
       <c r="I90" t="n">
-        <v>2318.45</v>
+        <v>2196.6</v>
       </c>
       <c r="J90" t="n">
-        <v>2355.18</v>
+        <v>2217.95</v>
       </c>
       <c r="K90" t="n">
-        <v>2440.92</v>
+        <v>2318.41</v>
       </c>
       <c r="L90" t="n">
-        <v>2526.66</v>
+        <v>2418.86</v>
       </c>
       <c r="M90" t="n">
-        <v>2587.9</v>
+        <v>2479.77</v>
       </c>
       <c r="N90" t="n">
-        <v>2649.13</v>
+        <v>2540.67</v>
       </c>
       <c r="O90" t="n">
-        <v>2759.38</v>
+        <v>2680.68</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
@@ -8014,14 +8012,12 @@
       <c r="Q90" s="6" t="n">
         <v/>
       </c>
-      <c r="R90" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S90" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S90" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T90" s="8" t="n">
@@ -8038,116 +8034,38 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr"/>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>2397.64</v>
-      </c>
-      <c r="C91" t="n">
-        <v>2424.1</v>
-      </c>
-      <c r="D91" t="n">
-        <v>2370.11</v>
-      </c>
-      <c r="E91" t="n">
-        <v>2396.95</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-2.14</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>-0.0009</v>
-      </c>
-      <c r="H91" t="n">
-        <v>53.99</v>
-      </c>
-      <c r="I91" t="n">
-        <v>2196.6</v>
-      </c>
-      <c r="J91" t="n">
-        <v>2217.95</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2318.41</v>
-      </c>
-      <c r="L91" t="n">
-        <v>2418.86</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2479.77</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2540.67</v>
-      </c>
-      <c r="O91" t="n">
-        <v>2680.68</v>
-      </c>
-      <c r="P91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S91" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W91" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
+      <c r="A91" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I92" s="13" t="n">
-        <v>2316.12</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>2342.88</v>
-      </c>
-      <c r="K92" s="13" t="n">
-        <v>2369.95</v>
-      </c>
-      <c r="L92" s="13" t="n">
-        <v>2397.03</v>
-      </c>
-      <c r="M92" s="13" t="n">
-        <v>2423.95</v>
-      </c>
-      <c r="N92" s="13" t="n">
-        <v>2450.86</v>
-      </c>
-      <c r="O92" s="13" t="n">
-        <v>2478.09</v>
+      <c r="I91" s="13" t="n">
+        <v>2408.2</v>
+      </c>
+      <c r="J91" s="13" t="n">
+        <v>2400.66</v>
+      </c>
+      <c r="K91" s="13" t="n">
+        <v>2408.46</v>
+      </c>
+      <c r="L91" s="13" t="n">
+        <v>2416.26</v>
+      </c>
+      <c r="M91" s="13" t="n">
+        <v>2416.38</v>
+      </c>
+      <c r="N91" s="13" t="n">
+        <v>2416.51</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>2431.98</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X91"/>
+  <dimension ref="A1:X92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7961,29 +7961,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2416.14</v>
+        <v>2399.06</v>
       </c>
       <c r="C90" t="n">
-        <v>2424.06</v>
+        <v>2426.93</v>
       </c>
       <c r="D90" t="n">
-        <v>2416.13</v>
+        <v>2368.74</v>
       </c>
       <c r="E90" t="n">
-        <v>2412.42</v>
+        <v>2416.12</v>
       </c>
       <c r="F90" t="n">
-        <v>13.33</v>
+        <v>17.03</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0056</v>
+        <v>0.0071</v>
       </c>
       <c r="H90" t="n">
-        <v>7.93</v>
+        <v>58.19</v>
       </c>
       <c r="I90" t="n">
         <v>2196.6</v>
@@ -8041,31 +8041,115 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="12" t="inlineStr">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2416.14</v>
+      </c>
+      <c r="C91" t="n">
+        <v>2477.4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2413.96</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2441.68</v>
+      </c>
+      <c r="F91" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="H91" t="n">
+        <v>63.44</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2310.54</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2367.07</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2387.02</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2406.98</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2445.22</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2483.46</v>
+      </c>
+      <c r="O91" t="n">
+        <v>2485.12</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W91" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I91" s="13" t="n">
-        <v>2408.2</v>
-      </c>
-      <c r="J91" s="13" t="n">
-        <v>2400.66</v>
-      </c>
-      <c r="K91" s="13" t="n">
-        <v>2408.46</v>
-      </c>
-      <c r="L91" s="13" t="n">
-        <v>2416.26</v>
-      </c>
-      <c r="M91" s="13" t="n">
-        <v>2416.38</v>
-      </c>
-      <c r="N91" s="13" t="n">
-        <v>2416.51</v>
-      </c>
-      <c r="O91" s="13" t="n">
-        <v>2431.98</v>
+      <c r="I92" s="13" t="n">
+        <v>2350.51</v>
+      </c>
+      <c r="J92" s="13" t="n">
+        <v>2376.24</v>
+      </c>
+      <c r="K92" s="13" t="n">
+        <v>2409.96</v>
+      </c>
+      <c r="L92" s="13" t="n">
+        <v>2443.68</v>
+      </c>
+      <c r="M92" s="13" t="n">
+        <v>2473.4</v>
+      </c>
+      <c r="N92" s="13" t="n">
+        <v>2503.12</v>
+      </c>
+      <c r="O92" s="13" t="n">
+        <v>2540.85</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -8056,13 +8056,13 @@
         <v>2413.96</v>
       </c>
       <c r="E91" t="n">
-        <v>2441.68</v>
+        <v>2445.47</v>
       </c>
       <c r="F91" t="n">
-        <v>25.56</v>
+        <v>29.35</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0121</v>
       </c>
       <c r="H91" t="n">
         <v>63.44</v>
@@ -8134,19 +8134,19 @@
         <v>2350.51</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>2376.24</v>
+        <v>2381.92</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>2409.96</v>
+        <v>2413.75</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>2443.68</v>
+        <v>2445.57</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>2473.4</v>
+        <v>2477.19</v>
       </c>
       <c r="N92" s="13" t="n">
-        <v>2503.12</v>
+        <v>2508.81</v>
       </c>
       <c r="O92" s="13" t="n">
         <v>2540.85</v>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,19 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X92"/>
+  <dimension ref="A1:X90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,69 +634,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1710.98</v>
+        <v>1739.34</v>
       </c>
       <c r="C2" t="n">
-        <v>1747.26</v>
+        <v>1739.49</v>
       </c>
       <c r="D2" t="n">
-        <v>1702.8</v>
+        <v>1701.94</v>
       </c>
       <c r="E2" t="n">
-        <v>1739.3</v>
+        <v>1704.58</v>
       </c>
       <c r="F2" t="n">
-        <v>28.32</v>
+        <v>-34.72</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0166</v>
+        <v>-0.02</v>
       </c>
       <c r="H2" t="n">
-        <v>44.46</v>
+        <v>37.55</v>
       </c>
       <c r="I2" t="n">
-        <v>1639.2</v>
+        <v>1658.34</v>
       </c>
       <c r="J2" t="n">
-        <v>1678.63</v>
+        <v>1701.98</v>
       </c>
       <c r="K2" t="n">
-        <v>1691.48</v>
+        <v>1717.07</v>
       </c>
       <c r="L2" t="n">
-        <v>1704.34</v>
+        <v>1732.17</v>
       </c>
       <c r="M2" t="n">
-        <v>1730.48</v>
+        <v>1761.53</v>
       </c>
       <c r="N2" t="n">
-        <v>1756.62</v>
+        <v>1790.89</v>
       </c>
       <c r="O2" t="n">
-        <v>1756.19</v>
+        <v>1791.72</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -716,80 +711,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1739.34</v>
+        <v>1704.63</v>
       </c>
       <c r="C3" t="n">
-        <v>1739.49</v>
+        <v>1776.83</v>
       </c>
       <c r="D3" t="n">
-        <v>1701.94</v>
+        <v>1704.52</v>
       </c>
       <c r="E3" t="n">
-        <v>1704.58</v>
+        <v>1726.51</v>
       </c>
       <c r="F3" t="n">
-        <v>-34.72</v>
+        <v>21.93</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.02</v>
+        <v>0.0129</v>
       </c>
       <c r="H3" t="n">
-        <v>37.55</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>1658.34</v>
+        <v>1664.39</v>
       </c>
       <c r="J3" t="n">
-        <v>1701.98</v>
+        <v>1658.97</v>
       </c>
       <c r="K3" t="n">
-        <v>1717.07</v>
+        <v>1685.81</v>
       </c>
       <c r="L3" t="n">
-        <v>1732.17</v>
+        <v>1712.65</v>
       </c>
       <c r="M3" t="n">
-        <v>1761.53</v>
+        <v>1723.36</v>
       </c>
       <c r="N3" t="n">
-        <v>1790.89</v>
+        <v>1734.06</v>
       </c>
       <c r="O3" t="n">
-        <v>1791.72</v>
+        <v>1777.04</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
@@ -798,83 +797,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1704.63</v>
+        <v>1726.52</v>
       </c>
       <c r="C4" t="n">
-        <v>1776.83</v>
+        <v>1733.61</v>
       </c>
       <c r="D4" t="n">
-        <v>1704.52</v>
+        <v>1638.25</v>
       </c>
       <c r="E4" t="n">
-        <v>1726.51</v>
+        <v>1665.44</v>
       </c>
       <c r="F4" t="n">
-        <v>21.93</v>
+        <v>-61.07</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0354</v>
       </c>
       <c r="H4" t="n">
-        <v>72.31999999999999</v>
+        <v>95.36</v>
       </c>
       <c r="I4" t="n">
-        <v>1664.39</v>
+        <v>1632.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1658.97</v>
+        <v>1647.11</v>
       </c>
       <c r="K4" t="n">
-        <v>1685.81</v>
+        <v>1690.35</v>
       </c>
       <c r="L4" t="n">
-        <v>1712.65</v>
+        <v>1733.59</v>
       </c>
       <c r="M4" t="n">
-        <v>1723.36</v>
+        <v>1762.67</v>
       </c>
       <c r="N4" t="n">
-        <v>1734.06</v>
+        <v>1791.74</v>
       </c>
       <c r="O4" t="n">
-        <v>1777.04</v>
+        <v>1849.15</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -884,70 +879,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1726.52</v>
+        <v>1665.31</v>
       </c>
       <c r="C5" t="n">
-        <v>1733.61</v>
+        <v>1687.49</v>
       </c>
       <c r="D5" t="n">
-        <v>1638.25</v>
+        <v>1551.48</v>
       </c>
       <c r="E5" t="n">
-        <v>1665.44</v>
+        <v>1619.92</v>
       </c>
       <c r="F5" t="n">
-        <v>-61.07</v>
+        <v>-45.51</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0354</v>
+        <v>-0.0273</v>
       </c>
       <c r="H5" t="n">
-        <v>95.36</v>
+        <v>136.01</v>
       </c>
       <c r="I5" t="n">
-        <v>1632.2</v>
+        <v>1542.89</v>
       </c>
       <c r="J5" t="n">
-        <v>1647.11</v>
+        <v>1559.83</v>
       </c>
       <c r="K5" t="n">
-        <v>1690.35</v>
+        <v>1617.76</v>
       </c>
       <c r="L5" t="n">
-        <v>1733.59</v>
+        <v>1675.68</v>
       </c>
       <c r="M5" t="n">
-        <v>1762.67</v>
+        <v>1713.12</v>
       </c>
       <c r="N5" t="n">
-        <v>1791.74</v>
+        <v>1750.55</v>
       </c>
       <c r="O5" t="n">
-        <v>1849.15</v>
+        <v>1828.97</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -975,65 +974,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1665.31</v>
+        <v>1619.89</v>
       </c>
       <c r="C6" t="n">
-        <v>1687.49</v>
+        <v>1656.65</v>
       </c>
       <c r="D6" t="n">
-        <v>1551.48</v>
+        <v>1531.78</v>
       </c>
       <c r="E6" t="n">
-        <v>1619.92</v>
+        <v>1564.82</v>
       </c>
       <c r="F6" t="n">
-        <v>-45.51</v>
+        <v>-55.11</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.034</v>
       </c>
       <c r="H6" t="n">
-        <v>136.01</v>
+        <v>124.87</v>
       </c>
       <c r="I6" t="n">
-        <v>1542.89</v>
+        <v>1415.48</v>
       </c>
       <c r="J6" t="n">
-        <v>1559.83</v>
+        <v>1484.14</v>
       </c>
       <c r="K6" t="n">
-        <v>1617.76</v>
+        <v>1551.92</v>
       </c>
       <c r="L6" t="n">
-        <v>1675.68</v>
+        <v>1619.71</v>
       </c>
       <c r="M6" t="n">
-        <v>1713.12</v>
+        <v>1687.93</v>
       </c>
       <c r="N6" t="n">
-        <v>1750.55</v>
+        <v>1756.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1828.97</v>
+        <v>1823.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q6" s="6" t="n">
+        <v/>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1061,50 +1058,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1619.89</v>
+        <v>1564.61</v>
       </c>
       <c r="C7" t="n">
-        <v>1656.65</v>
+        <v>1590.2</v>
       </c>
       <c r="D7" t="n">
-        <v>1531.78</v>
+        <v>1510.51</v>
       </c>
       <c r="E7" t="n">
-        <v>1564.82</v>
+        <v>1576.62</v>
       </c>
       <c r="F7" t="n">
-        <v>-55.11</v>
+        <v>11.8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.034</v>
+        <v>0.0075</v>
       </c>
       <c r="H7" t="n">
-        <v>124.87</v>
+        <v>79.69</v>
       </c>
       <c r="I7" t="n">
-        <v>1415.48</v>
+        <v>1406.91</v>
       </c>
       <c r="J7" t="n">
-        <v>1484.14</v>
+        <v>1425.25</v>
       </c>
       <c r="K7" t="n">
-        <v>1551.92</v>
+        <v>1502.38</v>
       </c>
       <c r="L7" t="n">
-        <v>1619.71</v>
+        <v>1579.52</v>
       </c>
       <c r="M7" t="n">
-        <v>1687.93</v>
+        <v>1627.25</v>
       </c>
       <c r="N7" t="n">
-        <v>1756.15</v>
+        <v>1674.98</v>
       </c>
       <c r="O7" t="n">
-        <v>1823.5</v>
+        <v>1781.51</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1112,14 +1109,12 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1138,57 +1133,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1564.61</v>
+        <v>1576.59</v>
       </c>
       <c r="C8" t="n">
-        <v>1590.2</v>
+        <v>1607.87</v>
       </c>
       <c r="D8" t="n">
-        <v>1510.51</v>
+        <v>1561.97</v>
       </c>
       <c r="E8" t="n">
-        <v>1576.62</v>
+        <v>1571.59</v>
       </c>
       <c r="F8" t="n">
-        <v>11.8</v>
+        <v>-5.03</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0032</v>
       </c>
       <c r="H8" t="n">
-        <v>79.69</v>
+        <v>45.89</v>
       </c>
       <c r="I8" t="n">
-        <v>1406.91</v>
+        <v>1430.81</v>
       </c>
       <c r="J8" t="n">
-        <v>1425.25</v>
+        <v>1510.05</v>
       </c>
       <c r="K8" t="n">
-        <v>1502.38</v>
+        <v>1536.77</v>
       </c>
       <c r="L8" t="n">
-        <v>1579.52</v>
+        <v>1563.48</v>
       </c>
       <c r="M8" t="n">
-        <v>1627.25</v>
+        <v>1616.46</v>
       </c>
       <c r="N8" t="n">
-        <v>1674.98</v>
+        <v>1669.44</v>
       </c>
       <c r="O8" t="n">
-        <v>1781.51</v>
+        <v>1669.89</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1201,7 +1196,7 @@
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1220,57 +1215,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1576.59</v>
+        <v>1571.56</v>
       </c>
       <c r="C9" t="n">
-        <v>1607.87</v>
+        <v>1585.22</v>
       </c>
       <c r="D9" t="n">
-        <v>1561.97</v>
+        <v>1548.76</v>
       </c>
       <c r="E9" t="n">
-        <v>1571.59</v>
+        <v>1570.36</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.03</v>
+        <v>-1.23</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.0008</v>
       </c>
       <c r="H9" t="n">
-        <v>45.89</v>
+        <v>36.46</v>
       </c>
       <c r="I9" t="n">
-        <v>1430.81</v>
+        <v>1516.08</v>
       </c>
       <c r="J9" t="n">
-        <v>1510.05</v>
+        <v>1519.03</v>
       </c>
       <c r="K9" t="n">
-        <v>1536.77</v>
+        <v>1548.64</v>
       </c>
       <c r="L9" t="n">
-        <v>1563.48</v>
+        <v>1578.25</v>
       </c>
       <c r="M9" t="n">
-        <v>1616.46</v>
+        <v>1594.53</v>
       </c>
       <c r="N9" t="n">
-        <v>1669.44</v>
+        <v>1610.82</v>
       </c>
       <c r="O9" t="n">
-        <v>1669.89</v>
+        <v>1653.76</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1283,7 +1278,7 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1302,57 +1297,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1571.56</v>
+        <v>1569.99</v>
       </c>
       <c r="C10" t="n">
-        <v>1585.22</v>
+        <v>1633.65</v>
       </c>
       <c r="D10" t="n">
-        <v>1548.76</v>
+        <v>1550.04</v>
       </c>
       <c r="E10" t="n">
-        <v>1570.36</v>
+        <v>1610.21</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.23</v>
+        <v>39.84</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0254</v>
       </c>
       <c r="H10" t="n">
-        <v>36.46</v>
+        <v>83.61</v>
       </c>
       <c r="I10" t="n">
-        <v>1516.08</v>
+        <v>1512.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1519.03</v>
+        <v>1535.59</v>
       </c>
       <c r="K10" t="n">
-        <v>1548.64</v>
+        <v>1552.13</v>
       </c>
       <c r="L10" t="n">
-        <v>1578.25</v>
+        <v>1568.68</v>
       </c>
       <c r="M10" t="n">
-        <v>1594.53</v>
+        <v>1588.59</v>
       </c>
       <c r="N10" t="n">
-        <v>1610.82</v>
+        <v>1608.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1653.76</v>
+        <v>1621.68</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1360,81 +1355,85 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1569.99</v>
+        <v>1610.16</v>
       </c>
       <c r="C11" t="n">
-        <v>1633.65</v>
+        <v>1611.35</v>
       </c>
       <c r="D11" t="n">
-        <v>1550.04</v>
+        <v>1549.25</v>
       </c>
       <c r="E11" t="n">
-        <v>1610.21</v>
+        <v>1569.58</v>
       </c>
       <c r="F11" t="n">
-        <v>39.84</v>
+        <v>-40.62</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0254</v>
+        <v>-0.0252</v>
       </c>
       <c r="H11" t="n">
-        <v>83.61</v>
+        <v>62.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1512.3</v>
+        <v>1466.43</v>
       </c>
       <c r="J11" t="n">
-        <v>1535.59</v>
+        <v>1535.78</v>
       </c>
       <c r="K11" t="n">
-        <v>1552.13</v>
+        <v>1568.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1568.68</v>
+        <v>1601.02</v>
       </c>
       <c r="M11" t="n">
-        <v>1588.59</v>
+        <v>1652.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1608.5</v>
+        <v>1703</v>
       </c>
       <c r="O11" t="n">
-        <v>1621.68</v>
+        <v>1717.25</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1444,83 +1443,81 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1610.16</v>
+        <v>1569.91</v>
       </c>
       <c r="C12" t="n">
-        <v>1611.35</v>
+        <v>1642.45</v>
       </c>
       <c r="D12" t="n">
-        <v>1549.25</v>
+        <v>1551.14</v>
       </c>
       <c r="E12" t="n">
-        <v>1569.58</v>
+        <v>1608.96</v>
       </c>
       <c r="F12" t="n">
-        <v>-40.62</v>
+        <v>39.38</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0252</v>
+        <v>0.0251</v>
       </c>
       <c r="H12" t="n">
-        <v>62.1</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1466.43</v>
+        <v>1487.16</v>
       </c>
       <c r="J12" t="n">
-        <v>1535.78</v>
+        <v>1502.13</v>
       </c>
       <c r="K12" t="n">
-        <v>1568.4</v>
+        <v>1538.54</v>
       </c>
       <c r="L12" t="n">
-        <v>1601.02</v>
+        <v>1574.94</v>
       </c>
       <c r="M12" t="n">
-        <v>1652.01</v>
+        <v>1600.63</v>
       </c>
       <c r="N12" t="n">
-        <v>1703</v>
+        <v>1626.32</v>
       </c>
       <c r="O12" t="n">
-        <v>1717.25</v>
+        <v>1673.44</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1528,21 +1525,23 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1552,59 +1551,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1569.91</v>
+        <v>1609.01</v>
       </c>
       <c r="C13" t="n">
-        <v>1642.45</v>
+        <v>1720.34</v>
       </c>
       <c r="D13" t="n">
-        <v>1551.14</v>
+        <v>1595.94</v>
       </c>
       <c r="E13" t="n">
-        <v>1608.96</v>
+        <v>1698.17</v>
       </c>
       <c r="F13" t="n">
-        <v>39.38</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0554</v>
       </c>
       <c r="H13" t="n">
-        <v>91.31999999999999</v>
+        <v>124.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1487.16</v>
+        <v>1459.82</v>
       </c>
       <c r="J13" t="n">
-        <v>1502.13</v>
+        <v>1523.73</v>
       </c>
       <c r="K13" t="n">
-        <v>1538.54</v>
+        <v>1563.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1574.94</v>
+        <v>1602.88</v>
       </c>
       <c r="M13" t="n">
-        <v>1600.63</v>
+        <v>1654.62</v>
       </c>
       <c r="N13" t="n">
-        <v>1626.32</v>
+        <v>1706.36</v>
       </c>
       <c r="O13" t="n">
-        <v>1673.44</v>
+        <v>1733.77</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1615,19 +1610,19 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V13" s="8" t="n">
@@ -1643,50 +1638,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1609.01</v>
+        <v>1698.42</v>
       </c>
       <c r="C14" t="n">
-        <v>1720.34</v>
+        <v>1772.54</v>
       </c>
       <c r="D14" t="n">
-        <v>1595.94</v>
+        <v>1693.04</v>
       </c>
       <c r="E14" t="n">
-        <v>1698.17</v>
+        <v>1756.52</v>
       </c>
       <c r="F14" t="n">
-        <v>89.20999999999999</v>
+        <v>58.35</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0344</v>
       </c>
       <c r="H14" t="n">
-        <v>124.4</v>
+        <v>79.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1459.82</v>
+        <v>1471.54</v>
       </c>
       <c r="J14" t="n">
-        <v>1523.73</v>
+        <v>1593.78</v>
       </c>
       <c r="K14" t="n">
-        <v>1563.3</v>
+        <v>1635.97</v>
       </c>
       <c r="L14" t="n">
-        <v>1602.88</v>
+        <v>1678.16</v>
       </c>
       <c r="M14" t="n">
-        <v>1654.62</v>
+        <v>1760.37</v>
       </c>
       <c r="N14" t="n">
-        <v>1706.36</v>
+        <v>1842.59</v>
       </c>
       <c r="O14" t="n">
-        <v>1733.77</v>
+        <v>1844.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1697,20 +1692,18 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1725,50 +1718,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1698.42</v>
+        <v>1756.58</v>
       </c>
       <c r="C15" t="n">
-        <v>1772.54</v>
+        <v>1804.59</v>
       </c>
       <c r="D15" t="n">
-        <v>1693.04</v>
+        <v>1743.56</v>
       </c>
       <c r="E15" t="n">
-        <v>1756.52</v>
+        <v>1779.03</v>
       </c>
       <c r="F15" t="n">
-        <v>58.35</v>
+        <v>22.51</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0128</v>
       </c>
       <c r="H15" t="n">
-        <v>79.5</v>
+        <v>61.02</v>
       </c>
       <c r="I15" t="n">
-        <v>1471.54</v>
+        <v>1613.53</v>
       </c>
       <c r="J15" t="n">
-        <v>1593.78</v>
+        <v>1688.88</v>
       </c>
       <c r="K15" t="n">
-        <v>1635.97</v>
+        <v>1716.77</v>
       </c>
       <c r="L15" t="n">
-        <v>1678.16</v>
+        <v>1744.65</v>
       </c>
       <c r="M15" t="n">
-        <v>1760.37</v>
+        <v>1796.27</v>
       </c>
       <c r="N15" t="n">
-        <v>1842.59</v>
+        <v>1847.89</v>
       </c>
       <c r="O15" t="n">
-        <v>1844.75</v>
+        <v>1852.05</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1779,7 +1772,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1805,50 +1798,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1756.58</v>
+        <v>1779.04</v>
       </c>
       <c r="C16" t="n">
-        <v>1804.59</v>
+        <v>1805.91</v>
       </c>
       <c r="D16" t="n">
-        <v>1743.56</v>
+        <v>1749.14</v>
       </c>
       <c r="E16" t="n">
-        <v>1779.03</v>
+        <v>1783.01</v>
       </c>
       <c r="F16" t="n">
-        <v>22.51</v>
+        <v>3.97</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0022</v>
       </c>
       <c r="H16" t="n">
-        <v>61.02</v>
+        <v>56.78</v>
       </c>
       <c r="I16" t="n">
-        <v>1613.53</v>
+        <v>1682.54</v>
       </c>
       <c r="J16" t="n">
-        <v>1688.88</v>
+        <v>1720.49</v>
       </c>
       <c r="K16" t="n">
-        <v>1716.77</v>
+        <v>1748.52</v>
       </c>
       <c r="L16" t="n">
-        <v>1744.65</v>
+        <v>1776.55</v>
       </c>
       <c r="M16" t="n">
-        <v>1796.27</v>
+        <v>1809.55</v>
       </c>
       <c r="N16" t="n">
-        <v>1847.89</v>
+        <v>1842.54</v>
       </c>
       <c r="O16" t="n">
-        <v>1852.05</v>
+        <v>1865.61</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1859,15 +1852,13 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1885,67 +1876,73 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779.04</v>
+        <v>1783</v>
       </c>
       <c r="C17" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D17" t="n">
-        <v>1749.14</v>
+        <v>1728.97</v>
       </c>
       <c r="E17" t="n">
-        <v>1783.01</v>
+        <v>1797.57</v>
       </c>
       <c r="F17" t="n">
-        <v>3.97</v>
+        <v>14.57</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>56.78</v>
+        <v>100.55</v>
       </c>
       <c r="I17" t="n">
-        <v>1682.54</v>
+        <v>1692.36</v>
       </c>
       <c r="J17" t="n">
-        <v>1720.49</v>
+        <v>1728.97</v>
       </c>
       <c r="K17" t="n">
-        <v>1748.52</v>
+        <v>1754.62</v>
       </c>
       <c r="L17" t="n">
-        <v>1776.55</v>
+        <v>1780.27</v>
       </c>
       <c r="M17" t="n">
-        <v>1809.55</v>
+        <v>1811.39</v>
       </c>
       <c r="N17" t="n">
-        <v>1842.54</v>
+        <v>1842.52</v>
       </c>
       <c r="O17" t="n">
-        <v>1865.61</v>
+        <v>1862.69</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1958,78 +1955,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1783</v>
+        <v>1797.56</v>
       </c>
       <c r="C18" t="n">
-        <v>1829.51</v>
+        <v>1810.33</v>
       </c>
       <c r="D18" t="n">
-        <v>1728.97</v>
+        <v>1756.71</v>
       </c>
       <c r="E18" t="n">
-        <v>1797.57</v>
+        <v>1768.51</v>
       </c>
       <c r="F18" t="n">
-        <v>14.57</v>
+        <v>-29.06</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0162</v>
       </c>
       <c r="H18" t="n">
-        <v>100.55</v>
+        <v>53.62</v>
       </c>
       <c r="I18" t="n">
-        <v>1692.36</v>
+        <v>1628.42</v>
       </c>
       <c r="J18" t="n">
-        <v>1728.97</v>
+        <v>1706.19</v>
       </c>
       <c r="K18" t="n">
-        <v>1754.62</v>
+        <v>1747.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1780.27</v>
+        <v>1788.41</v>
       </c>
       <c r="M18" t="n">
-        <v>1811.39</v>
+        <v>1847.85</v>
       </c>
       <c r="N18" t="n">
-        <v>1842.52</v>
+        <v>1907.29</v>
       </c>
       <c r="O18" t="n">
-        <v>1862.69</v>
+        <v>1930.06</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2044,57 +2039,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1797.56</v>
+        <v>1768.39</v>
       </c>
       <c r="C19" t="n">
-        <v>1810.33</v>
+        <v>1782.86</v>
       </c>
       <c r="D19" t="n">
-        <v>1756.71</v>
+        <v>1711.9</v>
       </c>
       <c r="E19" t="n">
-        <v>1768.51</v>
+        <v>1742.68</v>
       </c>
       <c r="F19" t="n">
-        <v>-29.06</v>
+        <v>-25.83</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0146</v>
       </c>
       <c r="H19" t="n">
-        <v>53.62</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>1628.42</v>
+        <v>1703.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1706.19</v>
+        <v>1707.39</v>
       </c>
       <c r="K19" t="n">
-        <v>1747.3</v>
+        <v>1741.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1788.41</v>
+        <v>1776.02</v>
       </c>
       <c r="M19" t="n">
-        <v>1847.85</v>
+        <v>1795.32</v>
       </c>
       <c r="N19" t="n">
-        <v>1907.29</v>
+        <v>1814.62</v>
       </c>
       <c r="O19" t="n">
-        <v>1930.06</v>
+        <v>1863.95</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2102,12 +2097,14 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2126,57 +2123,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1768.39</v>
+        <v>1742.66</v>
       </c>
       <c r="C20" t="n">
-        <v>1782.86</v>
+        <v>1760.21</v>
       </c>
       <c r="D20" t="n">
-        <v>1711.9</v>
+        <v>1721.3</v>
       </c>
       <c r="E20" t="n">
-        <v>1742.68</v>
+        <v>1744.48</v>
       </c>
       <c r="F20" t="n">
-        <v>-25.83</v>
+        <v>1.81</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>70.95999999999999</v>
+        <v>38.91</v>
       </c>
       <c r="I20" t="n">
-        <v>1703.1</v>
+        <v>1640.94</v>
       </c>
       <c r="J20" t="n">
-        <v>1707.39</v>
+        <v>1669.37</v>
       </c>
       <c r="K20" t="n">
-        <v>1741.7</v>
+        <v>1707.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1776.02</v>
+        <v>1745.03</v>
       </c>
       <c r="M20" t="n">
-        <v>1795.32</v>
+        <v>1778.16</v>
       </c>
       <c r="N20" t="n">
-        <v>1814.62</v>
+        <v>1811.29</v>
       </c>
       <c r="O20" t="n">
-        <v>1863.95</v>
+        <v>1853.82</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2184,14 +2181,12 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2210,57 +2205,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1742.66</v>
+        <v>1744.47</v>
       </c>
       <c r="C21" t="n">
-        <v>1760.21</v>
+        <v>1809.76</v>
       </c>
       <c r="D21" t="n">
-        <v>1721.3</v>
+        <v>1736.72</v>
       </c>
       <c r="E21" t="n">
-        <v>1744.48</v>
+        <v>1795.69</v>
       </c>
       <c r="F21" t="n">
-        <v>1.81</v>
+        <v>51.21</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0294</v>
       </c>
       <c r="H21" t="n">
-        <v>38.91</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>1640.94</v>
+        <v>1682.39</v>
       </c>
       <c r="J21" t="n">
-        <v>1669.37</v>
+        <v>1707.44</v>
       </c>
       <c r="K21" t="n">
-        <v>1707.2</v>
+        <v>1725.03</v>
       </c>
       <c r="L21" t="n">
-        <v>1745.03</v>
+        <v>1742.62</v>
       </c>
       <c r="M21" t="n">
-        <v>1778.16</v>
+        <v>1763.94</v>
       </c>
       <c r="N21" t="n">
-        <v>1811.29</v>
+        <v>1785.26</v>
       </c>
       <c r="O21" t="n">
-        <v>1853.82</v>
+        <v>1799.11</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,76 +2268,78 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1744.47</v>
+        <v>1795.82</v>
       </c>
       <c r="C22" t="n">
-        <v>1809.76</v>
+        <v>1827.83</v>
       </c>
       <c r="D22" t="n">
-        <v>1736.72</v>
+        <v>1786.3</v>
       </c>
       <c r="E22" t="n">
-        <v>1795.69</v>
+        <v>1788.1</v>
       </c>
       <c r="F22" t="n">
-        <v>51.21</v>
+        <v>-7.59</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0294</v>
+        <v>-0.0042</v>
       </c>
       <c r="H22" t="n">
-        <v>73.04000000000001</v>
+        <v>41.54</v>
       </c>
       <c r="I22" t="n">
-        <v>1682.39</v>
+        <v>1663.69</v>
       </c>
       <c r="J22" t="n">
-        <v>1707.44</v>
+        <v>1733.88</v>
       </c>
       <c r="K22" t="n">
-        <v>1725.03</v>
+        <v>1759.18</v>
       </c>
       <c r="L22" t="n">
-        <v>1742.62</v>
+        <v>1784.47</v>
       </c>
       <c r="M22" t="n">
-        <v>1763.94</v>
+        <v>1832.21</v>
       </c>
       <c r="N22" t="n">
-        <v>1785.26</v>
+        <v>1879.95</v>
       </c>
       <c r="O22" t="n">
-        <v>1799.11</v>
+        <v>1882.79</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,80 +2350,78 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1795.82</v>
+        <v>1787.57</v>
       </c>
       <c r="C23" t="n">
-        <v>1827.83</v>
+        <v>1824.98</v>
       </c>
       <c r="D23" t="n">
-        <v>1786.3</v>
+        <v>1779.64</v>
       </c>
       <c r="E23" t="n">
-        <v>1788.1</v>
+        <v>1805.79</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.59</v>
+        <v>17.69</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>41.54</v>
+        <v>45.34</v>
       </c>
       <c r="I23" t="n">
-        <v>1663.69</v>
+        <v>1744.76</v>
       </c>
       <c r="J23" t="n">
-        <v>1733.88</v>
+        <v>1737.08</v>
       </c>
       <c r="K23" t="n">
-        <v>1759.18</v>
+        <v>1767.33</v>
       </c>
       <c r="L23" t="n">
-        <v>1784.47</v>
+        <v>1797.58</v>
       </c>
       <c r="M23" t="n">
-        <v>1832.21</v>
+        <v>1808.87</v>
       </c>
       <c r="N23" t="n">
-        <v>1879.95</v>
+        <v>1820.15</v>
       </c>
       <c r="O23" t="n">
-        <v>1882.79</v>
+        <v>1869.37</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2437,16 +2432,20 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2458,81 +2457,83 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1787.57</v>
+        <v>1805.76</v>
       </c>
       <c r="C24" t="n">
-        <v>1824.98</v>
+        <v>1842.46</v>
       </c>
       <c r="D24" t="n">
-        <v>1779.64</v>
+        <v>1749.35</v>
       </c>
       <c r="E24" t="n">
-        <v>1805.79</v>
+        <v>1773.5</v>
       </c>
       <c r="F24" t="n">
-        <v>17.69</v>
+        <v>-32.29</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.0179</v>
       </c>
       <c r="H24" t="n">
-        <v>45.34</v>
+        <v>93.11</v>
       </c>
       <c r="I24" t="n">
-        <v>1744.76</v>
+        <v>1734.29</v>
       </c>
       <c r="J24" t="n">
-        <v>1737.08</v>
+        <v>1762.18</v>
       </c>
       <c r="K24" t="n">
-        <v>1767.33</v>
+        <v>1783.12</v>
       </c>
       <c r="L24" t="n">
-        <v>1797.58</v>
+        <v>1804.05</v>
       </c>
       <c r="M24" t="n">
-        <v>1808.87</v>
+        <v>1828.46</v>
       </c>
       <c r="N24" t="n">
-        <v>1820.15</v>
+        <v>1852.87</v>
       </c>
       <c r="O24" t="n">
-        <v>1869.37</v>
+        <v>1870.32</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2551,77 +2552,75 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1805.76</v>
+        <v>1773.47</v>
       </c>
       <c r="C25" t="n">
-        <v>1842.46</v>
+        <v>1894.06</v>
       </c>
       <c r="D25" t="n">
-        <v>1749.35</v>
+        <v>1772.02</v>
       </c>
       <c r="E25" t="n">
-        <v>1773.5</v>
+        <v>1889.48</v>
       </c>
       <c r="F25" t="n">
-        <v>-32.29</v>
+        <v>115.98</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0654</v>
       </c>
       <c r="H25" t="n">
-        <v>93.11</v>
+        <v>122.04</v>
       </c>
       <c r="I25" t="n">
-        <v>1734.29</v>
+        <v>1656.24</v>
       </c>
       <c r="J25" t="n">
-        <v>1762.18</v>
+        <v>1669.19</v>
       </c>
       <c r="K25" t="n">
-        <v>1783.12</v>
+        <v>1726.95</v>
       </c>
       <c r="L25" t="n">
-        <v>1804.05</v>
+        <v>1784.7</v>
       </c>
       <c r="M25" t="n">
-        <v>1828.46</v>
+        <v>1820.05</v>
       </c>
       <c r="N25" t="n">
-        <v>1852.87</v>
+        <v>1855.41</v>
       </c>
       <c r="O25" t="n">
-        <v>1870.32</v>
+        <v>1935.56</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2630,59 +2629,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1773.47</v>
+        <v>1889.5</v>
       </c>
       <c r="C26" t="n">
-        <v>1894.06</v>
+        <v>1944.16</v>
       </c>
       <c r="D26" t="n">
-        <v>1772.02</v>
+        <v>1863.64</v>
       </c>
       <c r="E26" t="n">
-        <v>1889.48</v>
+        <v>1916.94</v>
       </c>
       <c r="F26" t="n">
-        <v>115.98</v>
+        <v>27.46</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0654</v>
+        <v>0.0145</v>
       </c>
       <c r="H26" t="n">
-        <v>122.04</v>
+        <v>80.53</v>
       </c>
       <c r="I26" t="n">
-        <v>1656.24</v>
+        <v>1649.97</v>
       </c>
       <c r="J26" t="n">
-        <v>1669.19</v>
+        <v>1795.66</v>
       </c>
       <c r="K26" t="n">
-        <v>1726.95</v>
+        <v>1828.46</v>
       </c>
       <c r="L26" t="n">
-        <v>1784.7</v>
+        <v>1861.26</v>
       </c>
       <c r="M26" t="n">
-        <v>1820.05</v>
+        <v>1950.5</v>
       </c>
       <c r="N26" t="n">
-        <v>1855.41</v>
+        <v>2039.74</v>
       </c>
       <c r="O26" t="n">
-        <v>1935.56</v>
+        <v>2016.11</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2693,20 +2688,18 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2721,50 +2714,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1889.5</v>
+        <v>1916.98</v>
       </c>
       <c r="C27" t="n">
-        <v>1944.16</v>
+        <v>1927.09</v>
       </c>
       <c r="D27" t="n">
-        <v>1863.64</v>
+        <v>1856.78</v>
       </c>
       <c r="E27" t="n">
-        <v>1916.94</v>
+        <v>1863.19</v>
       </c>
       <c r="F27" t="n">
-        <v>27.46</v>
+        <v>-53.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0145</v>
+        <v>-0.028</v>
       </c>
       <c r="H27" t="n">
-        <v>80.53</v>
+        <v>70.31</v>
       </c>
       <c r="I27" t="n">
-        <v>1649.97</v>
+        <v>1783.11</v>
       </c>
       <c r="J27" t="n">
-        <v>1795.66</v>
+        <v>1842.94</v>
       </c>
       <c r="K27" t="n">
-        <v>1828.46</v>
+        <v>1876.68</v>
       </c>
       <c r="L27" t="n">
-        <v>1861.26</v>
+        <v>1910.42</v>
       </c>
       <c r="M27" t="n">
-        <v>1950.5</v>
+        <v>1957.21</v>
       </c>
       <c r="N27" t="n">
-        <v>2039.74</v>
+        <v>2003.99</v>
       </c>
       <c r="O27" t="n">
-        <v>2016.11</v>
+        <v>2024.69</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2772,18 +2765,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2796,55 +2789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1916.98</v>
+        <v>1863.22</v>
       </c>
       <c r="C28" t="n">
-        <v>1927.09</v>
+        <v>1869.07</v>
       </c>
       <c r="D28" t="n">
-        <v>1856.78</v>
+        <v>1803.05</v>
       </c>
       <c r="E28" t="n">
-        <v>1863.19</v>
+        <v>1840.99</v>
       </c>
       <c r="F28" t="n">
-        <v>-53.75</v>
+        <v>-22.21</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.0119</v>
       </c>
       <c r="H28" t="n">
-        <v>70.31</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>1783.11</v>
+        <v>1786.47</v>
       </c>
       <c r="J28" t="n">
-        <v>1842.94</v>
+        <v>1778.51</v>
       </c>
       <c r="K28" t="n">
-        <v>1876.68</v>
+        <v>1828.04</v>
       </c>
       <c r="L28" t="n">
-        <v>1910.42</v>
+        <v>1877.56</v>
       </c>
       <c r="M28" t="n">
-        <v>1957.21</v>
+        <v>1898.35</v>
       </c>
       <c r="N28" t="n">
-        <v>2003.99</v>
+        <v>1919.13</v>
       </c>
       <c r="O28" t="n">
-        <v>2024.69</v>
+        <v>1997.4</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2857,7 +2854,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2885,50 +2882,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1863.22</v>
+        <v>1841.1</v>
       </c>
       <c r="C29" t="n">
-        <v>1869.07</v>
+        <v>1864.13</v>
       </c>
       <c r="D29" t="n">
-        <v>1803.05</v>
+        <v>1836.61</v>
       </c>
       <c r="E29" t="n">
-        <v>1840.99</v>
+        <v>1861.39</v>
       </c>
       <c r="F29" t="n">
-        <v>-22.21</v>
+        <v>20.4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0111</v>
       </c>
       <c r="H29" t="n">
-        <v>66.01000000000001</v>
+        <v>27.52</v>
       </c>
       <c r="I29" t="n">
-        <v>1786.47</v>
+        <v>1737.04</v>
       </c>
       <c r="J29" t="n">
-        <v>1778.51</v>
+        <v>1777.44</v>
       </c>
       <c r="K29" t="n">
-        <v>1828.04</v>
+        <v>1807.98</v>
       </c>
       <c r="L29" t="n">
-        <v>1877.56</v>
+        <v>1838.52</v>
       </c>
       <c r="M29" t="n">
-        <v>1898.35</v>
+        <v>1873.99</v>
       </c>
       <c r="N29" t="n">
-        <v>1919.13</v>
+        <v>1909.47</v>
       </c>
       <c r="O29" t="n">
-        <v>1997.4</v>
+        <v>1935.08</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2936,19 +2933,19 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2962,57 +2959,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1841.1</v>
+        <v>1861.42</v>
       </c>
       <c r="C30" t="n">
-        <v>1864.13</v>
+        <v>1877.03</v>
       </c>
       <c r="D30" t="n">
-        <v>1836.61</v>
+        <v>1852.73</v>
       </c>
       <c r="E30" t="n">
-        <v>1861.39</v>
+        <v>1871.51</v>
       </c>
       <c r="F30" t="n">
-        <v>20.4</v>
+        <v>10.12</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0054</v>
       </c>
       <c r="H30" t="n">
-        <v>27.52</v>
+        <v>24.3</v>
       </c>
       <c r="I30" t="n">
-        <v>1737.04</v>
+        <v>1809.09</v>
       </c>
       <c r="J30" t="n">
-        <v>1777.44</v>
+        <v>1839.38</v>
       </c>
       <c r="K30" t="n">
-        <v>1807.98</v>
+        <v>1847.63</v>
       </c>
       <c r="L30" t="n">
-        <v>1838.52</v>
+        <v>1855.88</v>
       </c>
       <c r="M30" t="n">
-        <v>1873.99</v>
+        <v>1875.15</v>
       </c>
       <c r="N30" t="n">
-        <v>1909.47</v>
+        <v>1894.43</v>
       </c>
       <c r="O30" t="n">
-        <v>1935.08</v>
+        <v>1891.66</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,7 +3020,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3044,231 +3041,227 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1861.42</v>
+        <v>1871.28</v>
       </c>
       <c r="C31" t="n">
-        <v>1877.03</v>
+        <v>1916.24</v>
       </c>
       <c r="D31" t="n">
-        <v>1852.73</v>
+        <v>1842.82</v>
       </c>
       <c r="E31" t="n">
-        <v>1871.51</v>
+        <v>1903.76</v>
       </c>
       <c r="F31" t="n">
-        <v>10.12</v>
+        <v>32.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0172</v>
       </c>
       <c r="H31" t="n">
-        <v>24.3</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>1809.09</v>
+        <v>1828.42</v>
       </c>
       <c r="J31" t="n">
-        <v>1839.38</v>
+        <v>1850.52</v>
       </c>
       <c r="K31" t="n">
-        <v>1847.63</v>
+        <v>1859.36</v>
       </c>
       <c r="L31" t="n">
-        <v>1855.88</v>
+        <v>1868.19</v>
       </c>
       <c r="M31" t="n">
-        <v>1875.15</v>
+        <v>1883.66</v>
       </c>
       <c r="N31" t="n">
-        <v>1894.43</v>
+        <v>1899.13</v>
       </c>
       <c r="O31" t="n">
-        <v>1891.66</v>
+        <v>1901.34</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1871.28</v>
+        <v>1903.69</v>
       </c>
       <c r="C32" t="n">
-        <v>1916.24</v>
+        <v>1949.55</v>
       </c>
       <c r="D32" t="n">
-        <v>1842.82</v>
+        <v>1900.07</v>
       </c>
       <c r="E32" t="n">
-        <v>1903.76</v>
+        <v>1928.38</v>
       </c>
       <c r="F32" t="n">
-        <v>32.25</v>
+        <v>24.62</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0129</v>
       </c>
       <c r="H32" t="n">
-        <v>73.43000000000001</v>
+        <v>49.48</v>
       </c>
       <c r="I32" t="n">
-        <v>1828.42</v>
+        <v>1769.39</v>
       </c>
       <c r="J32" t="n">
-        <v>1850.52</v>
+        <v>1842.45</v>
       </c>
       <c r="K32" t="n">
-        <v>1859.36</v>
+        <v>1867.05</v>
       </c>
       <c r="L32" t="n">
-        <v>1868.19</v>
+        <v>1891.64</v>
       </c>
       <c r="M32" t="n">
-        <v>1883.66</v>
+        <v>1940.47</v>
       </c>
       <c r="N32" t="n">
-        <v>1899.13</v>
+        <v>1989.3</v>
       </c>
       <c r="O32" t="n">
-        <v>1901.34</v>
+        <v>1989.67</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1903.69</v>
+        <v>1928.2</v>
       </c>
       <c r="C33" t="n">
-        <v>1949.55</v>
+        <v>1955.15</v>
       </c>
       <c r="D33" t="n">
-        <v>1900.07</v>
+        <v>1909.61</v>
       </c>
       <c r="E33" t="n">
-        <v>1928.38</v>
+        <v>1933.49</v>
       </c>
       <c r="F33" t="n">
-        <v>24.62</v>
+        <v>5.11</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0026</v>
       </c>
       <c r="H33" t="n">
-        <v>49.48</v>
+        <v>45.54</v>
       </c>
       <c r="I33" t="n">
-        <v>1769.39</v>
+        <v>1850.58</v>
       </c>
       <c r="J33" t="n">
-        <v>1842.45</v>
+        <v>1880.69</v>
       </c>
       <c r="K33" t="n">
-        <v>1867.05</v>
+        <v>1903.64</v>
       </c>
       <c r="L33" t="n">
-        <v>1891.64</v>
+        <v>1926.6</v>
       </c>
       <c r="M33" t="n">
-        <v>1940.47</v>
+        <v>1953.12</v>
       </c>
       <c r="N33" t="n">
-        <v>1989.3</v>
+        <v>1979.65</v>
       </c>
       <c r="O33" t="n">
-        <v>1989.67</v>
+        <v>1999.03</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3279,14 +3272,14 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
@@ -3305,69 +3298,71 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1928.2</v>
+        <v>1933.47</v>
       </c>
       <c r="C34" t="n">
-        <v>1955.15</v>
+        <v>1940.28</v>
       </c>
       <c r="D34" t="n">
-        <v>1909.61</v>
+        <v>1868.52</v>
       </c>
       <c r="E34" t="n">
-        <v>1933.49</v>
+        <v>1877.1</v>
       </c>
       <c r="F34" t="n">
-        <v>5.11</v>
+        <v>-56.39</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0292</v>
       </c>
       <c r="H34" t="n">
-        <v>45.54</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>1850.58</v>
+        <v>1864.07</v>
       </c>
       <c r="J34" t="n">
-        <v>1880.69</v>
+        <v>1888.51</v>
       </c>
       <c r="K34" t="n">
-        <v>1903.64</v>
+        <v>1910.72</v>
       </c>
       <c r="L34" t="n">
-        <v>1926.6</v>
+        <v>1932.93</v>
       </c>
       <c r="M34" t="n">
-        <v>1953.12</v>
+        <v>1956.26</v>
       </c>
       <c r="N34" t="n">
-        <v>1979.65</v>
+        <v>1979.58</v>
       </c>
       <c r="O34" t="n">
-        <v>1999.03</v>
+        <v>2000.68</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3375,9 +3370,9 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3385,65 +3380,63 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1933.47</v>
+        <v>1877.1</v>
       </c>
       <c r="C35" t="n">
-        <v>1940.28</v>
+        <v>1907.54</v>
       </c>
       <c r="D35" t="n">
-        <v>1868.52</v>
+        <v>1846.82</v>
       </c>
       <c r="E35" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="F35" t="n">
-        <v>-56.39</v>
+        <v>-16.92</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0292</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>71.76000000000001</v>
+        <v>60.72</v>
       </c>
       <c r="I35" t="n">
-        <v>1864.07</v>
+        <v>1796.76</v>
       </c>
       <c r="J35" t="n">
-        <v>1888.51</v>
+        <v>1791.69</v>
       </c>
       <c r="K35" t="n">
-        <v>1910.72</v>
+        <v>1841.22</v>
       </c>
       <c r="L35" t="n">
-        <v>1932.93</v>
+        <v>1890.75</v>
       </c>
       <c r="M35" t="n">
-        <v>1956.26</v>
+        <v>1912.98</v>
       </c>
       <c r="N35" t="n">
-        <v>1979.58</v>
+        <v>1935.21</v>
       </c>
       <c r="O35" t="n">
-        <v>2000.68</v>
+        <v>2012.05</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3467,50 +3460,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="C36" t="n">
-        <v>1907.54</v>
+        <v>1875.14</v>
       </c>
       <c r="D36" t="n">
-        <v>1846.82</v>
+        <v>1849.83</v>
       </c>
       <c r="E36" t="n">
-        <v>1860.18</v>
+        <v>1873.22</v>
       </c>
       <c r="F36" t="n">
-        <v>-16.92</v>
+        <v>13.05</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H36" t="n">
-        <v>60.72</v>
+        <v>25.32</v>
       </c>
       <c r="I36" t="n">
-        <v>1796.76</v>
+        <v>1786.1</v>
       </c>
       <c r="J36" t="n">
-        <v>1791.69</v>
+        <v>1790.95</v>
       </c>
       <c r="K36" t="n">
-        <v>1841.22</v>
+        <v>1829.82</v>
       </c>
       <c r="L36" t="n">
-        <v>1890.75</v>
+        <v>1868.68</v>
       </c>
       <c r="M36" t="n">
-        <v>1912.98</v>
+        <v>1890.54</v>
       </c>
       <c r="N36" t="n">
-        <v>1935.21</v>
+        <v>1912.39</v>
       </c>
       <c r="O36" t="n">
-        <v>2012.05</v>
+        <v>1968.26</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3518,14 +3511,12 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3542,55 +3533,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1860.18</v>
+        <v>1873.24</v>
       </c>
       <c r="C37" t="n">
-        <v>1875.14</v>
+        <v>1963.25</v>
       </c>
       <c r="D37" t="n">
-        <v>1849.83</v>
+        <v>1872.38</v>
       </c>
       <c r="E37" t="n">
-        <v>1873.22</v>
+        <v>1953.41</v>
       </c>
       <c r="F37" t="n">
-        <v>13.05</v>
+        <v>80.19</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0428</v>
       </c>
       <c r="H37" t="n">
-        <v>25.32</v>
+        <v>90.86</v>
       </c>
       <c r="I37" t="n">
-        <v>1786.1</v>
+        <v>1824.51</v>
       </c>
       <c r="J37" t="n">
-        <v>1790.95</v>
+        <v>1853.27</v>
       </c>
       <c r="K37" t="n">
-        <v>1829.82</v>
+        <v>1860.56</v>
       </c>
       <c r="L37" t="n">
-        <v>1868.68</v>
+        <v>1867.85</v>
       </c>
       <c r="M37" t="n">
-        <v>1890.54</v>
+        <v>1885.88</v>
       </c>
       <c r="N37" t="n">
-        <v>1912.39</v>
+        <v>1903.91</v>
       </c>
       <c r="O37" t="n">
-        <v>1968.26</v>
+        <v>1900.46</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3601,179 +3596,179 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1873.24</v>
+        <v>1953.41</v>
       </c>
       <c r="C38" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D38" t="n">
-        <v>1872.38</v>
+        <v>1882.42</v>
       </c>
       <c r="E38" t="n">
-        <v>1953.41</v>
+        <v>1890.61</v>
       </c>
       <c r="F38" t="n">
-        <v>80.19</v>
+        <v>-62.8</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0428</v>
+        <v>-0.0321</v>
       </c>
       <c r="H38" t="n">
-        <v>90.86</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>1824.51</v>
+        <v>1781.52</v>
       </c>
       <c r="J38" t="n">
-        <v>1853.27</v>
+        <v>1880.35</v>
       </c>
       <c r="K38" t="n">
-        <v>1860.56</v>
+        <v>1907.98</v>
       </c>
       <c r="L38" t="n">
-        <v>1867.85</v>
+        <v>1935.61</v>
       </c>
       <c r="M38" t="n">
-        <v>1885.88</v>
+        <v>1998.84</v>
       </c>
       <c r="N38" t="n">
-        <v>1903.91</v>
+        <v>2062.07</v>
       </c>
       <c r="O38" t="n">
-        <v>1900.46</v>
+        <v>2054.11</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1953.41</v>
+        <v>1890.63</v>
       </c>
       <c r="C39" t="n">
-        <v>1976.46</v>
+        <v>1926.5</v>
       </c>
       <c r="D39" t="n">
-        <v>1882.42</v>
+        <v>1856.34</v>
       </c>
       <c r="E39" t="n">
-        <v>1890.61</v>
+        <v>1919.95</v>
       </c>
       <c r="F39" t="n">
-        <v>-62.8</v>
+        <v>29.33</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0321</v>
+        <v>0.0155</v>
       </c>
       <c r="H39" t="n">
-        <v>94.04000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="I39" t="n">
-        <v>1781.52</v>
+        <v>1788.38</v>
       </c>
       <c r="J39" t="n">
-        <v>1880.35</v>
+        <v>1777.16</v>
       </c>
       <c r="K39" t="n">
-        <v>1907.98</v>
+        <v>1843.59</v>
       </c>
       <c r="L39" t="n">
-        <v>1935.61</v>
+        <v>1910.03</v>
       </c>
       <c r="M39" t="n">
-        <v>1998.84</v>
+        <v>1937.63</v>
       </c>
       <c r="N39" t="n">
-        <v>2062.07</v>
+        <v>1965.24</v>
       </c>
       <c r="O39" t="n">
-        <v>2054.11</v>
+        <v>2070.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3792,57 +3787,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1890.63</v>
+        <v>1919.99</v>
       </c>
       <c r="C40" t="n">
-        <v>1926.5</v>
+        <v>1929.9</v>
       </c>
       <c r="D40" t="n">
-        <v>1856.34</v>
+        <v>1873.62</v>
       </c>
       <c r="E40" t="n">
-        <v>1919.95</v>
+        <v>1908.52</v>
       </c>
       <c r="F40" t="n">
-        <v>29.33</v>
+        <v>-11.43</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.006</v>
       </c>
       <c r="H40" t="n">
-        <v>70.16</v>
+        <v>56.28</v>
       </c>
       <c r="I40" t="n">
-        <v>1788.38</v>
+        <v>1786.18</v>
       </c>
       <c r="J40" t="n">
-        <v>1777.16</v>
+        <v>1864.05</v>
       </c>
       <c r="K40" t="n">
-        <v>1843.59</v>
+        <v>1884.87</v>
       </c>
       <c r="L40" t="n">
-        <v>1910.03</v>
+        <v>1905.69</v>
       </c>
       <c r="M40" t="n">
-        <v>1937.63</v>
+        <v>1955.03</v>
       </c>
       <c r="N40" t="n">
-        <v>1965.24</v>
+        <v>2004.37</v>
       </c>
       <c r="O40" t="n">
-        <v>2070.5</v>
+        <v>1996.67</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3850,10 +3845,12 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3874,57 +3871,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1919.99</v>
+        <v>1908.59</v>
       </c>
       <c r="C41" t="n">
-        <v>1929.9</v>
+        <v>1934.58</v>
       </c>
       <c r="D41" t="n">
-        <v>1873.62</v>
+        <v>1892.2</v>
       </c>
       <c r="E41" t="n">
-        <v>1908.52</v>
+        <v>1917.37</v>
       </c>
       <c r="F41" t="n">
-        <v>-11.43</v>
+        <v>8.85</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0046</v>
       </c>
       <c r="H41" t="n">
-        <v>56.28</v>
+        <v>42.38</v>
       </c>
       <c r="I41" t="n">
-        <v>1786.18</v>
+        <v>1817.34</v>
       </c>
       <c r="J41" t="n">
-        <v>1864.05</v>
+        <v>1855.62</v>
       </c>
       <c r="K41" t="n">
-        <v>1884.87</v>
+        <v>1880.38</v>
       </c>
       <c r="L41" t="n">
-        <v>1905.69</v>
+        <v>1905.14</v>
       </c>
       <c r="M41" t="n">
-        <v>1955.03</v>
+        <v>1936.66</v>
       </c>
       <c r="N41" t="n">
-        <v>2004.37</v>
+        <v>1968.18</v>
       </c>
       <c r="O41" t="n">
-        <v>1996.67</v>
+        <v>1986.18</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3932,12 +3929,10 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3956,72 +3951,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1908.59</v>
+        <v>1917.14</v>
       </c>
       <c r="C42" t="n">
-        <v>1934.58</v>
+        <v>1933.78</v>
       </c>
       <c r="D42" t="n">
-        <v>1892.2</v>
+        <v>1847.47</v>
       </c>
       <c r="E42" t="n">
-        <v>1917.37</v>
+        <v>1860.35</v>
       </c>
       <c r="F42" t="n">
-        <v>8.85</v>
+        <v>-57.03</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0297</v>
       </c>
       <c r="H42" t="n">
-        <v>42.38</v>
+        <v>86.31</v>
       </c>
       <c r="I42" t="n">
-        <v>1817.34</v>
+        <v>1849.82</v>
       </c>
       <c r="J42" t="n">
-        <v>1855.62</v>
+        <v>1876.99</v>
       </c>
       <c r="K42" t="n">
-        <v>1880.38</v>
+        <v>1896.18</v>
       </c>
       <c r="L42" t="n">
-        <v>1905.14</v>
+        <v>1915.38</v>
       </c>
       <c r="M42" t="n">
-        <v>1936.66</v>
+        <v>1938.56</v>
       </c>
       <c r="N42" t="n">
-        <v>1968.18</v>
+        <v>1961.75</v>
       </c>
       <c r="O42" t="n">
-        <v>1986.18</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+        <v>1976.96</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4033,9 +4030,9 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr"/>
@@ -4043,67 +4040,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1917.14</v>
+        <v>1860.37</v>
       </c>
       <c r="C43" t="n">
-        <v>1933.78</v>
+        <v>1873.17</v>
       </c>
       <c r="D43" t="n">
-        <v>1847.47</v>
+        <v>1821.49</v>
       </c>
       <c r="E43" t="n">
-        <v>1860.35</v>
+        <v>1843.42</v>
       </c>
       <c r="F43" t="n">
-        <v>-57.03</v>
+        <v>-16.93</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0297</v>
+        <v>-0.0091</v>
       </c>
       <c r="H43" t="n">
-        <v>86.31</v>
+        <v>51.69</v>
       </c>
       <c r="I43" t="n">
-        <v>1849.82</v>
+        <v>1761.16</v>
       </c>
       <c r="J43" t="n">
-        <v>1876.99</v>
+        <v>1758.9</v>
       </c>
       <c r="K43" t="n">
-        <v>1896.18</v>
+        <v>1817.19</v>
       </c>
       <c r="L43" t="n">
-        <v>1915.38</v>
+        <v>1875.48</v>
       </c>
       <c r="M43" t="n">
-        <v>1938.56</v>
+        <v>1903.5</v>
       </c>
       <c r="N43" t="n">
-        <v>1961.75</v>
+        <v>1931.52</v>
       </c>
       <c r="O43" t="n">
-        <v>1976.96</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
+        <v>2020.09</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4127,50 +4120,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1860.37</v>
+        <v>1843.42</v>
       </c>
       <c r="C44" t="n">
-        <v>1873.17</v>
+        <v>1895.77</v>
       </c>
       <c r="D44" t="n">
-        <v>1821.49</v>
+        <v>1842.15</v>
       </c>
       <c r="E44" t="n">
-        <v>1843.42</v>
+        <v>1882.52</v>
       </c>
       <c r="F44" t="n">
-        <v>-16.93</v>
+        <v>39.1</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0212</v>
       </c>
       <c r="H44" t="n">
-        <v>51.69</v>
+        <v>53.61</v>
       </c>
       <c r="I44" t="n">
-        <v>1761.16</v>
+        <v>1769.8</v>
       </c>
       <c r="J44" t="n">
-        <v>1758.9</v>
+        <v>1789.78</v>
       </c>
       <c r="K44" t="n">
-        <v>1817.19</v>
+        <v>1817.57</v>
       </c>
       <c r="L44" t="n">
-        <v>1875.48</v>
+        <v>1845.37</v>
       </c>
       <c r="M44" t="n">
-        <v>1903.5</v>
+        <v>1869.26</v>
       </c>
       <c r="N44" t="n">
-        <v>1931.52</v>
+        <v>1893.15</v>
       </c>
       <c r="O44" t="n">
-        <v>2020.09</v>
+        <v>1924.86</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4178,22 +4171,24 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4202,79 +4197,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1843.42</v>
+        <v>1882.78</v>
       </c>
       <c r="C45" t="n">
-        <v>1895.77</v>
+        <v>1883.44</v>
       </c>
       <c r="D45" t="n">
-        <v>1842.15</v>
+        <v>1827.7</v>
       </c>
       <c r="E45" t="n">
-        <v>1882.52</v>
+        <v>1858.26</v>
       </c>
       <c r="F45" t="n">
-        <v>39.1</v>
+        <v>-24.27</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0129</v>
       </c>
       <c r="H45" t="n">
-        <v>53.61</v>
+        <v>55.74</v>
       </c>
       <c r="I45" t="n">
-        <v>1769.8</v>
+        <v>1788.54</v>
       </c>
       <c r="J45" t="n">
-        <v>1789.78</v>
+        <v>1835.69</v>
       </c>
       <c r="K45" t="n">
-        <v>1817.57</v>
+        <v>1855.72</v>
       </c>
       <c r="L45" t="n">
-        <v>1845.37</v>
+        <v>1875.74</v>
       </c>
       <c r="M45" t="n">
-        <v>1869.26</v>
+        <v>1909.33</v>
       </c>
       <c r="N45" t="n">
-        <v>1893.15</v>
+        <v>1942.91</v>
       </c>
       <c r="O45" t="n">
-        <v>1924.86</v>
+        <v>1949.38</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4284,76 +4283,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1882.78</v>
+        <v>1858.22</v>
       </c>
       <c r="C46" t="n">
-        <v>1883.44</v>
+        <v>1879.54</v>
       </c>
       <c r="D46" t="n">
-        <v>1827.7</v>
+        <v>1847.17</v>
       </c>
       <c r="E46" t="n">
-        <v>1858.26</v>
+        <v>1868.39</v>
       </c>
       <c r="F46" t="n">
-        <v>-24.27</v>
+        <v>10.13</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0055</v>
       </c>
       <c r="H46" t="n">
-        <v>55.74</v>
+        <v>32.36</v>
       </c>
       <c r="I46" t="n">
-        <v>1788.54</v>
+        <v>1771.96</v>
       </c>
       <c r="J46" t="n">
-        <v>1835.69</v>
+        <v>1803.86</v>
       </c>
       <c r="K46" t="n">
-        <v>1855.72</v>
+        <v>1830.39</v>
       </c>
       <c r="L46" t="n">
-        <v>1875.74</v>
+        <v>1856.91</v>
       </c>
       <c r="M46" t="n">
-        <v>1909.33</v>
+        <v>1886.13</v>
       </c>
       <c r="N46" t="n">
-        <v>1942.91</v>
+        <v>1915.34</v>
       </c>
       <c r="O46" t="n">
-        <v>1949.38</v>
+        <v>1939.18</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4370,55 +4361,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1858.22</v>
+        <v>1868.49</v>
       </c>
       <c r="C47" t="n">
-        <v>1879.54</v>
+        <v>1922.64</v>
       </c>
       <c r="D47" t="n">
-        <v>1847.17</v>
+        <v>1854.34</v>
       </c>
       <c r="E47" t="n">
-        <v>1868.39</v>
+        <v>1906.53</v>
       </c>
       <c r="F47" t="n">
-        <v>10.13</v>
+        <v>38.14</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0204</v>
       </c>
       <c r="H47" t="n">
-        <v>32.36</v>
+        <v>68.3</v>
       </c>
       <c r="I47" t="n">
-        <v>1771.96</v>
+        <v>1814.81</v>
       </c>
       <c r="J47" t="n">
-        <v>1803.86</v>
+        <v>1838.54</v>
       </c>
       <c r="K47" t="n">
-        <v>1830.39</v>
+        <v>1852.2</v>
       </c>
       <c r="L47" t="n">
-        <v>1856.91</v>
+        <v>1865.87</v>
       </c>
       <c r="M47" t="n">
-        <v>1886.13</v>
+        <v>1884.57</v>
       </c>
       <c r="N47" t="n">
-        <v>1915.34</v>
+        <v>1903.26</v>
       </c>
       <c r="O47" t="n">
-        <v>1939.18</v>
+        <v>1911.9</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4429,78 +4424,80 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1868.49</v>
+        <v>1906.44</v>
       </c>
       <c r="C48" t="n">
-        <v>1922.64</v>
+        <v>1917.7</v>
       </c>
       <c r="D48" t="n">
-        <v>1854.34</v>
+        <v>1890.96</v>
       </c>
       <c r="E48" t="n">
-        <v>1906.53</v>
+        <v>1902.06</v>
       </c>
       <c r="F48" t="n">
-        <v>38.14</v>
+        <v>-4.47</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.0023</v>
       </c>
       <c r="H48" t="n">
-        <v>68.3</v>
+        <v>26.74</v>
       </c>
       <c r="I48" t="n">
-        <v>1814.81</v>
+        <v>1786.04</v>
       </c>
       <c r="J48" t="n">
-        <v>1838.54</v>
+        <v>1847.24</v>
       </c>
       <c r="K48" t="n">
-        <v>1852.2</v>
+        <v>1872.38</v>
       </c>
       <c r="L48" t="n">
-        <v>1865.87</v>
+        <v>1897.51</v>
       </c>
       <c r="M48" t="n">
-        <v>1884.57</v>
+        <v>1940.68</v>
       </c>
       <c r="N48" t="n">
-        <v>1903.26</v>
+        <v>1983.84</v>
       </c>
       <c r="O48" t="n">
-        <v>1911.9</v>
+        <v>1990.94</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4511,80 +4508,78 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1906.44</v>
+        <v>1902.14</v>
       </c>
       <c r="C49" t="n">
-        <v>1917.7</v>
+        <v>1937.17</v>
       </c>
       <c r="D49" t="n">
-        <v>1890.96</v>
+        <v>1893.08</v>
       </c>
       <c r="E49" t="n">
-        <v>1902.06</v>
+        <v>1913.28</v>
       </c>
       <c r="F49" t="n">
-        <v>-4.47</v>
+        <v>11.22</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0059</v>
       </c>
       <c r="H49" t="n">
-        <v>26.74</v>
+        <v>44.08</v>
       </c>
       <c r="I49" t="n">
-        <v>1786.04</v>
+        <v>1864.23</v>
       </c>
       <c r="J49" t="n">
-        <v>1847.24</v>
+        <v>1874.18</v>
       </c>
       <c r="K49" t="n">
-        <v>1872.38</v>
+        <v>1888.69</v>
       </c>
       <c r="L49" t="n">
-        <v>1897.51</v>
+        <v>1903.19</v>
       </c>
       <c r="M49" t="n">
-        <v>1940.68</v>
+        <v>1915.43</v>
       </c>
       <c r="N49" t="n">
-        <v>1983.84</v>
+        <v>1927.66</v>
       </c>
       <c r="O49" t="n">
-        <v>1990.94</v>
+        <v>1944.44</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4595,16 +4590,20 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4614,59 +4613,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1902.14</v>
+        <v>1913.32</v>
       </c>
       <c r="C50" t="n">
-        <v>1937.17</v>
+        <v>1924.62</v>
       </c>
       <c r="D50" t="n">
-        <v>1893.08</v>
+        <v>1911.48</v>
       </c>
       <c r="E50" t="n">
-        <v>1913.28</v>
+        <v>1915.53</v>
       </c>
       <c r="F50" t="n">
-        <v>11.22</v>
+        <v>2.25</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0012</v>
       </c>
       <c r="H50" t="n">
-        <v>44.08</v>
+        <v>13.13</v>
       </c>
       <c r="I50" t="n">
-        <v>1864.23</v>
+        <v>1849</v>
       </c>
       <c r="J50" t="n">
-        <v>1874.18</v>
+        <v>1868.27</v>
       </c>
       <c r="K50" t="n">
-        <v>1888.69</v>
+        <v>1891.24</v>
       </c>
       <c r="L50" t="n">
-        <v>1903.19</v>
+        <v>1914.2</v>
       </c>
       <c r="M50" t="n">
-        <v>1915.43</v>
+        <v>1935.32</v>
       </c>
       <c r="N50" t="n">
-        <v>1927.66</v>
+        <v>1956.44</v>
       </c>
       <c r="O50" t="n">
-        <v>1944.44</v>
+        <v>1981.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4677,20 +4672,16 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4700,55 +4691,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1913.32</v>
+        <v>1915.46</v>
       </c>
       <c r="C51" t="n">
-        <v>1924.62</v>
+        <v>1935.53</v>
       </c>
       <c r="D51" t="n">
-        <v>1911.48</v>
+        <v>1907.03</v>
       </c>
       <c r="E51" t="n">
-        <v>1915.53</v>
+        <v>1908.68</v>
       </c>
       <c r="F51" t="n">
-        <v>2.25</v>
+        <v>-6.85</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0036</v>
       </c>
       <c r="H51" t="n">
-        <v>13.13</v>
+        <v>28.5</v>
       </c>
       <c r="I51" t="n">
-        <v>1849</v>
+        <v>1898.35</v>
       </c>
       <c r="J51" t="n">
-        <v>1868.27</v>
+        <v>1901.14</v>
       </c>
       <c r="K51" t="n">
-        <v>1891.24</v>
+        <v>1908.97</v>
       </c>
       <c r="L51" t="n">
-        <v>1914.2</v>
+        <v>1916.79</v>
       </c>
       <c r="M51" t="n">
-        <v>1935.32</v>
+        <v>1922.1</v>
       </c>
       <c r="N51" t="n">
-        <v>1956.44</v>
+        <v>1927.4</v>
       </c>
       <c r="O51" t="n">
-        <v>1981.25</v>
+        <v>1937.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4756,19 +4751,25 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4780,70 +4781,74 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1915.46</v>
+        <v>1908.72</v>
       </c>
       <c r="C52" t="n">
-        <v>1935.53</v>
+        <v>1928.99</v>
       </c>
       <c r="D52" t="n">
-        <v>1907.03</v>
+        <v>1866.79</v>
       </c>
       <c r="E52" t="n">
-        <v>1908.68</v>
+        <v>1871.28</v>
       </c>
       <c r="F52" t="n">
-        <v>-6.85</v>
+        <v>-37.4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0196</v>
       </c>
       <c r="H52" t="n">
-        <v>28.5</v>
+        <v>62.2</v>
       </c>
       <c r="I52" t="n">
-        <v>1898.35</v>
+        <v>1878.52</v>
       </c>
       <c r="J52" t="n">
-        <v>1901.14</v>
+        <v>1873.88</v>
       </c>
       <c r="K52" t="n">
-        <v>1908.97</v>
+        <v>1894.43</v>
       </c>
       <c r="L52" t="n">
-        <v>1916.79</v>
+        <v>1914.98</v>
       </c>
       <c r="M52" t="n">
-        <v>1922.1</v>
+        <v>1922.93</v>
       </c>
       <c r="N52" t="n">
-        <v>1927.4</v>
+        <v>1930.89</v>
       </c>
       <c r="O52" t="n">
-        <v>1937.75</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+        <v>1964.03</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4853,97 +4858,83 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1908.72</v>
+        <v>1871.26</v>
       </c>
       <c r="C53" t="n">
-        <v>1928.99</v>
+        <v>1895.75</v>
       </c>
       <c r="D53" t="n">
-        <v>1866.79</v>
+        <v>1852.84</v>
       </c>
       <c r="E53" t="n">
-        <v>1871.28</v>
+        <v>1881.37</v>
       </c>
       <c r="F53" t="n">
-        <v>-37.4</v>
+        <v>10.09</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0196</v>
+        <v>0.0054</v>
       </c>
       <c r="H53" t="n">
-        <v>62.2</v>
+        <v>42.91</v>
       </c>
       <c r="I53" t="n">
-        <v>1878.52</v>
+        <v>1804.59</v>
       </c>
       <c r="J53" t="n">
-        <v>1873.88</v>
+        <v>1795.77</v>
       </c>
       <c r="K53" t="n">
-        <v>1894.43</v>
+        <v>1840.18</v>
       </c>
       <c r="L53" t="n">
-        <v>1914.98</v>
+        <v>1884.59</v>
       </c>
       <c r="M53" t="n">
-        <v>1922.93</v>
+        <v>1902.38</v>
       </c>
       <c r="N53" t="n">
-        <v>1930.89</v>
+        <v>1920.18</v>
       </c>
       <c r="O53" t="n">
-        <v>1964.03</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>1991.2</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4956,55 +4947,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1871.26</v>
+        <v>1881.37</v>
       </c>
       <c r="C54" t="n">
-        <v>1895.75</v>
+        <v>1921.78</v>
       </c>
       <c r="D54" t="n">
-        <v>1852.84</v>
+        <v>1873.35</v>
       </c>
       <c r="E54" t="n">
-        <v>1881.37</v>
+        <v>1878.14</v>
       </c>
       <c r="F54" t="n">
-        <v>10.09</v>
+        <v>-3.24</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0017</v>
       </c>
       <c r="H54" t="n">
-        <v>42.91</v>
+        <v>48.43</v>
       </c>
       <c r="I54" t="n">
-        <v>1804.59</v>
+        <v>1809.93</v>
       </c>
       <c r="J54" t="n">
-        <v>1795.77</v>
+        <v>1842</v>
       </c>
       <c r="K54" t="n">
-        <v>1840.18</v>
+        <v>1859.92</v>
       </c>
       <c r="L54" t="n">
-        <v>1884.59</v>
+        <v>1877.83</v>
       </c>
       <c r="M54" t="n">
-        <v>1902.38</v>
+        <v>1902.83</v>
       </c>
       <c r="N54" t="n">
-        <v>1920.18</v>
+        <v>1927.82</v>
       </c>
       <c r="O54" t="n">
-        <v>1991.2</v>
+        <v>1938.66</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5017,11 +5012,13 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5036,57 +5033,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1881.37</v>
+        <v>1878.19</v>
       </c>
       <c r="C55" t="n">
-        <v>1921.78</v>
+        <v>1898.23</v>
       </c>
       <c r="D55" t="n">
-        <v>1873.35</v>
+        <v>1861.92</v>
       </c>
       <c r="E55" t="n">
-        <v>1878.14</v>
+        <v>1883.99</v>
       </c>
       <c r="F55" t="n">
-        <v>-3.24</v>
+        <v>5.86</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="H55" t="n">
-        <v>48.43</v>
+        <v>36.3</v>
       </c>
       <c r="I55" t="n">
-        <v>1809.93</v>
+        <v>1824.92</v>
       </c>
       <c r="J55" t="n">
-        <v>1842</v>
+        <v>1819.99</v>
       </c>
       <c r="K55" t="n">
-        <v>1859.92</v>
+        <v>1853.92</v>
       </c>
       <c r="L55" t="n">
-        <v>1877.83</v>
+        <v>1887.85</v>
       </c>
       <c r="M55" t="n">
-        <v>1902.83</v>
+        <v>1902.35</v>
       </c>
       <c r="N55" t="n">
-        <v>1927.82</v>
+        <v>1916.85</v>
       </c>
       <c r="O55" t="n">
-        <v>1938.66</v>
+        <v>1970.2</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5099,13 +5096,11 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5120,57 +5115,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1878.19</v>
+        <v>1884.02</v>
       </c>
       <c r="C56" t="n">
-        <v>1898.23</v>
+        <v>1889.27</v>
       </c>
       <c r="D56" t="n">
-        <v>1861.92</v>
+        <v>1862.56</v>
       </c>
       <c r="E56" t="n">
-        <v>1883.99</v>
+        <v>1880.65</v>
       </c>
       <c r="F56" t="n">
-        <v>5.86</v>
+        <v>-3.34</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0018</v>
       </c>
       <c r="H56" t="n">
-        <v>36.3</v>
+        <v>26.71</v>
       </c>
       <c r="I56" t="n">
-        <v>1824.92</v>
+        <v>1825.62</v>
       </c>
       <c r="J56" t="n">
-        <v>1819.99</v>
+        <v>1849.65</v>
       </c>
       <c r="K56" t="n">
-        <v>1853.92</v>
+        <v>1865.84</v>
       </c>
       <c r="L56" t="n">
-        <v>1887.85</v>
+        <v>1882.03</v>
       </c>
       <c r="M56" t="n">
-        <v>1902.35</v>
+        <v>1902.14</v>
       </c>
       <c r="N56" t="n">
-        <v>1916.85</v>
+        <v>1922.26</v>
       </c>
       <c r="O56" t="n">
-        <v>1970.2</v>
+        <v>1934.53</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5178,10 +5173,12 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5209,50 +5206,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1884.02</v>
+        <v>1880.61</v>
       </c>
       <c r="C57" t="n">
-        <v>1889.27</v>
+        <v>1884.72</v>
       </c>
       <c r="D57" t="n">
-        <v>1862.56</v>
+        <v>1874.33</v>
       </c>
       <c r="E57" t="n">
-        <v>1880.65</v>
+        <v>1880.91</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.34</v>
+        <v>0.26</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0001</v>
       </c>
       <c r="H57" t="n">
-        <v>26.71</v>
+        <v>10.39</v>
       </c>
       <c r="I57" t="n">
-        <v>1825.62</v>
+        <v>1835.86</v>
       </c>
       <c r="J57" t="n">
-        <v>1849.65</v>
+        <v>1856.31</v>
       </c>
       <c r="K57" t="n">
-        <v>1865.84</v>
+        <v>1867.3</v>
       </c>
       <c r="L57" t="n">
-        <v>1882.03</v>
+        <v>1878.28</v>
       </c>
       <c r="M57" t="n">
-        <v>1902.14</v>
+        <v>1894</v>
       </c>
       <c r="N57" t="n">
-        <v>1922.26</v>
+        <v>1909.72</v>
       </c>
       <c r="O57" t="n">
-        <v>1934.53</v>
+        <v>1915.98</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5260,14 +5257,12 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5286,74 +5281,80 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1880.61</v>
+        <v>1880.89</v>
       </c>
       <c r="C58" t="n">
-        <v>1884.72</v>
+        <v>1889.61</v>
       </c>
       <c r="D58" t="n">
-        <v>1874.33</v>
+        <v>1867.89</v>
       </c>
       <c r="E58" t="n">
-        <v>1880.91</v>
+        <v>1873.94</v>
       </c>
       <c r="F58" t="n">
-        <v>0.26</v>
+        <v>-6.97</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0037</v>
       </c>
       <c r="H58" t="n">
-        <v>10.39</v>
+        <v>21.71</v>
       </c>
       <c r="I58" t="n">
-        <v>1835.86</v>
+        <v>1863.94</v>
       </c>
       <c r="J58" t="n">
-        <v>1856.31</v>
+        <v>1871.21</v>
       </c>
       <c r="K58" t="n">
-        <v>1867.3</v>
+        <v>1875.71</v>
       </c>
       <c r="L58" t="n">
-        <v>1878.28</v>
+        <v>1880.22</v>
       </c>
       <c r="M58" t="n">
-        <v>1894</v>
+        <v>1886.1</v>
       </c>
       <c r="N58" t="n">
-        <v>1909.72</v>
+        <v>1891.99</v>
       </c>
       <c r="O58" t="n">
-        <v>1915.98</v>
+        <v>1895.11</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5368,145 +5369,141 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1880.89</v>
+        <v>1873.97</v>
       </c>
       <c r="C59" t="n">
-        <v>1889.61</v>
+        <v>1916.66</v>
       </c>
       <c r="D59" t="n">
-        <v>1867.89</v>
+        <v>1870.75</v>
       </c>
       <c r="E59" t="n">
-        <v>1873.94</v>
+        <v>1912.2</v>
       </c>
       <c r="F59" t="n">
-        <v>-6.97</v>
+        <v>38.26</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0204</v>
       </c>
       <c r="H59" t="n">
-        <v>21.71</v>
+        <v>45.91</v>
       </c>
       <c r="I59" t="n">
-        <v>1863.94</v>
+        <v>1846.18</v>
       </c>
       <c r="J59" t="n">
-        <v>1871.21</v>
+        <v>1849.83</v>
       </c>
       <c r="K59" t="n">
-        <v>1875.71</v>
+        <v>1863.09</v>
       </c>
       <c r="L59" t="n">
-        <v>1880.22</v>
+        <v>1876.35</v>
       </c>
       <c r="M59" t="n">
-        <v>1886.1</v>
+        <v>1884.8</v>
       </c>
       <c r="N59" t="n">
-        <v>1891.99</v>
+        <v>1893.25</v>
       </c>
       <c r="O59" t="n">
-        <v>1895.11</v>
+        <v>1911.32</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W59" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W59" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1873.97</v>
+        <v>1912.21</v>
       </c>
       <c r="C60" t="n">
-        <v>1916.66</v>
+        <v>1920.52</v>
       </c>
       <c r="D60" t="n">
-        <v>1870.75</v>
+        <v>1884.48</v>
       </c>
       <c r="E60" t="n">
-        <v>1912.2</v>
+        <v>1916.46</v>
       </c>
       <c r="F60" t="n">
-        <v>38.26</v>
+        <v>4.26</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.0022</v>
       </c>
       <c r="H60" t="n">
-        <v>45.91</v>
+        <v>36.05</v>
       </c>
       <c r="I60" t="n">
-        <v>1846.18</v>
+        <v>1824.84</v>
       </c>
       <c r="J60" t="n">
-        <v>1849.83</v>
+        <v>1875.54</v>
       </c>
       <c r="K60" t="n">
-        <v>1863.09</v>
+        <v>1889.25</v>
       </c>
       <c r="L60" t="n">
-        <v>1876.35</v>
+        <v>1902.95</v>
       </c>
       <c r="M60" t="n">
-        <v>1884.8</v>
+        <v>1935.16</v>
       </c>
       <c r="N60" t="n">
-        <v>1893.25</v>
+        <v>1967.36</v>
       </c>
       <c r="O60" t="n">
-        <v>1911.32</v>
+        <v>1962.57</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5514,28 +5511,24 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
@@ -5547,50 +5540,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1912.21</v>
+        <v>1916.43</v>
       </c>
       <c r="C61" t="n">
-        <v>1920.52</v>
+        <v>2327.7</v>
       </c>
       <c r="D61" t="n">
-        <v>1884.48</v>
+        <v>1905.08</v>
       </c>
       <c r="E61" t="n">
-        <v>1916.46</v>
+        <v>2251.46</v>
       </c>
       <c r="F61" t="n">
-        <v>4.26</v>
+        <v>335</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.1748</v>
       </c>
       <c r="H61" t="n">
-        <v>36.05</v>
+        <v>422.62</v>
       </c>
       <c r="I61" t="n">
-        <v>1824.84</v>
+        <v>1848.43</v>
       </c>
       <c r="J61" t="n">
-        <v>1875.54</v>
+        <v>1887.39</v>
       </c>
       <c r="K61" t="n">
-        <v>1889.25</v>
+        <v>1898.44</v>
       </c>
       <c r="L61" t="n">
-        <v>1902.95</v>
+        <v>1909.48</v>
       </c>
       <c r="M61" t="n">
-        <v>1935.16</v>
+        <v>1934.48</v>
       </c>
       <c r="N61" t="n">
-        <v>1967.36</v>
+        <v>1959.48</v>
       </c>
       <c r="O61" t="n">
-        <v>1962.57</v>
+        <v>1956.57</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5598,24 +5591,28 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
@@ -5627,50 +5624,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1916.43</v>
+        <v>2251.44</v>
       </c>
       <c r="C62" t="n">
-        <v>2327.7</v>
+        <v>2357.23</v>
       </c>
       <c r="D62" t="n">
-        <v>1905.08</v>
+        <v>2222.57</v>
       </c>
       <c r="E62" t="n">
-        <v>2251.46</v>
+        <v>2326.38</v>
       </c>
       <c r="F62" t="n">
-        <v>335</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.1748</v>
+        <v>0.0333</v>
       </c>
       <c r="H62" t="n">
-        <v>422.62</v>
+        <v>134.65</v>
       </c>
       <c r="I62" t="n">
-        <v>1848.43</v>
+        <v>1482.46</v>
       </c>
       <c r="J62" t="n">
-        <v>1887.39</v>
+        <v>1896.37</v>
       </c>
       <c r="K62" t="n">
-        <v>1898.44</v>
+        <v>2040.15</v>
       </c>
       <c r="L62" t="n">
-        <v>1909.48</v>
+        <v>2183.92</v>
       </c>
       <c r="M62" t="n">
-        <v>1934.48</v>
+        <v>2462.77</v>
       </c>
       <c r="N62" t="n">
-        <v>1959.48</v>
+        <v>2741.61</v>
       </c>
       <c r="O62" t="n">
-        <v>1956.57</v>
+        <v>2750.32</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5681,25 +5678,21 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
@@ -5711,50 +5704,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2251.44</v>
+        <v>2326.38</v>
       </c>
       <c r="C63" t="n">
-        <v>2357.23</v>
+        <v>2545.88</v>
       </c>
       <c r="D63" t="n">
-        <v>2222.57</v>
+        <v>2324.71</v>
       </c>
       <c r="E63" t="n">
-        <v>2326.38</v>
+        <v>2515.28</v>
       </c>
       <c r="F63" t="n">
-        <v>74.93000000000001</v>
+        <v>188.9</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0333</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>134.65</v>
+        <v>221.17</v>
       </c>
       <c r="I63" t="n">
-        <v>1482.46</v>
+        <v>2087.92</v>
       </c>
       <c r="J63" t="n">
-        <v>1896.37</v>
+        <v>2209.97</v>
       </c>
       <c r="K63" t="n">
-        <v>2040.15</v>
+        <v>2259.06</v>
       </c>
       <c r="L63" t="n">
-        <v>2183.92</v>
+        <v>2308.14</v>
       </c>
       <c r="M63" t="n">
-        <v>2462.77</v>
+        <v>2393.71</v>
       </c>
       <c r="N63" t="n">
-        <v>2741.61</v>
+        <v>2479.28</v>
       </c>
       <c r="O63" t="n">
-        <v>2750.32</v>
+        <v>2491.88</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5765,21 +5758,25 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
+      <c r="S63" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
       </c>
       <c r="W63" s="9" t="inlineStr">
         <is>
@@ -5791,50 +5788,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2326.38</v>
+        <v>2515.39</v>
       </c>
       <c r="C64" t="n">
-        <v>2545.88</v>
+        <v>2528.9</v>
       </c>
       <c r="D64" t="n">
-        <v>2324.71</v>
+        <v>2389.9</v>
       </c>
       <c r="E64" t="n">
-        <v>2515.28</v>
+        <v>2424.25</v>
       </c>
       <c r="F64" t="n">
-        <v>188.9</v>
+        <v>-91.03</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0362</v>
       </c>
       <c r="H64" t="n">
-        <v>221.17</v>
+        <v>138.99</v>
       </c>
       <c r="I64" t="n">
-        <v>2087.92</v>
+        <v>2103.54</v>
       </c>
       <c r="J64" t="n">
-        <v>2209.97</v>
+        <v>2334.1</v>
       </c>
       <c r="K64" t="n">
-        <v>2259.06</v>
+        <v>2404.7</v>
       </c>
       <c r="L64" t="n">
-        <v>2308.14</v>
+        <v>2475.29</v>
       </c>
       <c r="M64" t="n">
-        <v>2393.71</v>
+        <v>2625.87</v>
       </c>
       <c r="N64" t="n">
-        <v>2479.28</v>
+        <v>2776.45</v>
       </c>
       <c r="O64" t="n">
-        <v>2491.88</v>
+        <v>2767.05</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5842,83 +5839,83 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="n">
-        <v/>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
       </c>
       <c r="W64" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2515.39</v>
+        <v>2424.22</v>
       </c>
       <c r="C65" t="n">
-        <v>2528.9</v>
+        <v>2483.93</v>
       </c>
       <c r="D65" t="n">
-        <v>2389.9</v>
+        <v>2357.14</v>
       </c>
       <c r="E65" t="n">
-        <v>2424.25</v>
+        <v>2463.82</v>
       </c>
       <c r="F65" t="n">
-        <v>-91.03</v>
+        <v>39.56</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.0362</v>
+        <v>0.0163</v>
       </c>
       <c r="H65" t="n">
-        <v>138.99</v>
+        <v>126.79</v>
       </c>
       <c r="I65" t="n">
-        <v>2103.54</v>
+        <v>2250.91</v>
       </c>
       <c r="J65" t="n">
-        <v>2334.1</v>
+        <v>2267.68</v>
       </c>
       <c r="K65" t="n">
-        <v>2404.7</v>
+        <v>2354.75</v>
       </c>
       <c r="L65" t="n">
-        <v>2475.29</v>
+        <v>2441.83</v>
       </c>
       <c r="M65" t="n">
-        <v>2625.87</v>
+        <v>2493.75</v>
       </c>
       <c r="N65" t="n">
-        <v>2776.45</v>
+        <v>2545.67</v>
       </c>
       <c r="O65" t="n">
-        <v>2767.05</v>
+        <v>2667.89</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5926,14 +5923,12 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R65" s="6" t="n">
+        <v/>
       </c>
       <c r="S65" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">
@@ -5959,50 +5954,50 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2424.22</v>
+        <v>2463.64</v>
       </c>
       <c r="C66" t="n">
-        <v>2483.93</v>
+        <v>2531.74</v>
       </c>
       <c r="D66" t="n">
-        <v>2357.14</v>
+        <v>2425.39</v>
       </c>
       <c r="E66" t="n">
-        <v>2463.82</v>
+        <v>2481.83</v>
       </c>
       <c r="F66" t="n">
-        <v>39.56</v>
+        <v>18.02</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0073</v>
       </c>
       <c r="H66" t="n">
-        <v>126.79</v>
+        <v>106.36</v>
       </c>
       <c r="I66" t="n">
-        <v>2250.91</v>
+        <v>2230.35</v>
       </c>
       <c r="J66" t="n">
-        <v>2267.68</v>
+        <v>2358.67</v>
       </c>
       <c r="K66" t="n">
-        <v>2354.75</v>
+        <v>2400.42</v>
       </c>
       <c r="L66" t="n">
-        <v>2441.83</v>
+        <v>2442.18</v>
       </c>
       <c r="M66" t="n">
-        <v>2493.75</v>
+        <v>2527.21</v>
       </c>
       <c r="N66" t="n">
-        <v>2545.67</v>
+        <v>2612.25</v>
       </c>
       <c r="O66" t="n">
-        <v>2667.89</v>
+        <v>2610.72</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6013,13 +6008,15 @@
       <c r="R66" s="6" t="n">
         <v/>
       </c>
-      <c r="S66" s="7" t="inlineStr">
+      <c r="S66" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T66" s="8" t="n">
-        <v/>
+      <c r="T66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U66" s="8" t="n">
         <v/>
@@ -6032,59 +6029,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2463.64</v>
+        <v>2481.78</v>
       </c>
       <c r="C67" t="n">
-        <v>2531.74</v>
+        <v>2531.08</v>
       </c>
       <c r="D67" t="n">
-        <v>2425.39</v>
+        <v>2416.6</v>
       </c>
       <c r="E67" t="n">
-        <v>2481.83</v>
+        <v>2443.16</v>
       </c>
       <c r="F67" t="n">
-        <v>18.02</v>
+        <v>-38.67</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0156</v>
       </c>
       <c r="H67" t="n">
-        <v>106.36</v>
+        <v>114.48</v>
       </c>
       <c r="I67" t="n">
-        <v>2230.35</v>
+        <v>2319.03</v>
       </c>
       <c r="J67" t="n">
-        <v>2358.67</v>
+        <v>2377.11</v>
       </c>
       <c r="K67" t="n">
-        <v>2400.42</v>
+        <v>2428.65</v>
       </c>
       <c r="L67" t="n">
-        <v>2442.18</v>
+        <v>2480.2</v>
       </c>
       <c r="M67" t="n">
-        <v>2527.21</v>
+        <v>2535.01</v>
       </c>
       <c r="N67" t="n">
-        <v>2612.25</v>
+        <v>2589.82</v>
       </c>
       <c r="O67" t="n">
-        <v>2610.72</v>
+        <v>2638.1</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6092,18 +6085,18 @@
       <c r="Q67" s="6" t="n">
         <v/>
       </c>
-      <c r="R67" s="6" t="n">
-        <v/>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S67" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="n">
+        <v/>
       </c>
       <c r="U67" s="8" t="n">
         <v/>
@@ -6116,55 +6109,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr"/>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2481.78</v>
+        <v>2442.49</v>
       </c>
       <c r="C68" t="n">
-        <v>2531.08</v>
+        <v>2514.67</v>
       </c>
       <c r="D68" t="n">
-        <v>2416.6</v>
+        <v>2432.51</v>
       </c>
       <c r="E68" t="n">
-        <v>2443.16</v>
+        <v>2506.26</v>
       </c>
       <c r="F68" t="n">
-        <v>-38.67</v>
+        <v>63.1</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0258</v>
       </c>
       <c r="H68" t="n">
-        <v>114.48</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>2319.03</v>
+        <v>2302.12</v>
       </c>
       <c r="J68" t="n">
-        <v>2377.11</v>
+        <v>2313.34</v>
       </c>
       <c r="K68" t="n">
-        <v>2428.65</v>
+        <v>2385.92</v>
       </c>
       <c r="L68" t="n">
-        <v>2480.2</v>
+        <v>2458.5</v>
       </c>
       <c r="M68" t="n">
-        <v>2535.01</v>
+        <v>2500.4</v>
       </c>
       <c r="N68" t="n">
-        <v>2589.82</v>
+        <v>2542.3</v>
       </c>
       <c r="O68" t="n">
-        <v>2638.1</v>
+        <v>2645.57</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
@@ -6172,19 +6169,19 @@
       <c r="Q68" s="6" t="n">
         <v/>
       </c>
-      <c r="R68" s="6" t="inlineStr">
+      <c r="R68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S68" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S68" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="n">
-        <v/>
-      </c>
       <c r="U68" s="8" t="n">
         <v/>
       </c>
@@ -6198,57 +6195,57 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2442.49</v>
+        <v>2506.24</v>
       </c>
       <c r="C69" t="n">
-        <v>2514.67</v>
+        <v>2564.27</v>
       </c>
       <c r="D69" t="n">
-        <v>2432.51</v>
+        <v>2481.94</v>
       </c>
       <c r="E69" t="n">
-        <v>2506.26</v>
+        <v>2510.41</v>
       </c>
       <c r="F69" t="n">
-        <v>63.1</v>
+        <v>4.15</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0258</v>
+        <v>0.0017</v>
       </c>
       <c r="H69" t="n">
-        <v>82.15000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="I69" t="n">
-        <v>2302.12</v>
+        <v>2350.36</v>
       </c>
       <c r="J69" t="n">
-        <v>2313.34</v>
+        <v>2440.44</v>
       </c>
       <c r="K69" t="n">
-        <v>2385.92</v>
+        <v>2465.18</v>
       </c>
       <c r="L69" t="n">
-        <v>2458.5</v>
+        <v>2489.93</v>
       </c>
       <c r="M69" t="n">
-        <v>2500.4</v>
+        <v>2547.34</v>
       </c>
       <c r="N69" t="n">
-        <v>2542.3</v>
+        <v>2604.75</v>
       </c>
       <c r="O69" t="n">
-        <v>2645.57</v>
+        <v>2596.82</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6259,14 +6256,14 @@
       <c r="R69" s="6" t="n">
         <v/>
       </c>
-      <c r="S69" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S69" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T69" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U69" s="8" t="n">
@@ -6280,78 +6277,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2506.24</v>
+        <v>2510.67</v>
       </c>
       <c r="C70" t="n">
-        <v>2564.27</v>
+        <v>2534.01</v>
       </c>
       <c r="D70" t="n">
-        <v>2481.94</v>
+        <v>2408.72</v>
       </c>
       <c r="E70" t="n">
-        <v>2510.41</v>
+        <v>2442.54</v>
       </c>
       <c r="F70" t="n">
-        <v>4.15</v>
+        <v>-67.87</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.027</v>
       </c>
       <c r="H70" t="n">
-        <v>82.33</v>
+        <v>125.29</v>
       </c>
       <c r="I70" t="n">
-        <v>2350.36</v>
+        <v>2399.62</v>
       </c>
       <c r="J70" t="n">
-        <v>2440.44</v>
+        <v>2421.73</v>
       </c>
       <c r="K70" t="n">
-        <v>2465.18</v>
+        <v>2469.25</v>
       </c>
       <c r="L70" t="n">
-        <v>2489.93</v>
+        <v>2516.76</v>
       </c>
       <c r="M70" t="n">
-        <v>2547.34</v>
+        <v>2551.57</v>
       </c>
       <c r="N70" t="n">
-        <v>2604.75</v>
+        <v>2586.39</v>
       </c>
       <c r="O70" t="n">
-        <v>2596.82</v>
+        <v>2646.6</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
       </c>
-      <c r="Q70" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R70" s="6" t="n">
-        <v/>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S70" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="n">
+        <v/>
       </c>
       <c r="U70" s="8" t="n">
         <v/>
@@ -6364,72 +6359,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr"/>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2510.67</v>
+        <v>2442.56</v>
       </c>
       <c r="C71" t="n">
-        <v>2534.01</v>
+        <v>2459.63</v>
       </c>
       <c r="D71" t="n">
-        <v>2408.72</v>
+        <v>2430.81</v>
       </c>
       <c r="E71" t="n">
-        <v>2442.54</v>
+        <v>2457.69</v>
       </c>
       <c r="F71" t="n">
-        <v>-67.87</v>
+        <v>15.15</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.027</v>
+        <v>0.0062</v>
       </c>
       <c r="H71" t="n">
-        <v>125.29</v>
+        <v>28.82</v>
       </c>
       <c r="I71" t="n">
-        <v>2399.62</v>
+        <v>2283.43</v>
       </c>
       <c r="J71" t="n">
-        <v>2421.73</v>
+        <v>2302.83</v>
       </c>
       <c r="K71" t="n">
-        <v>2469.25</v>
+        <v>2379.89</v>
       </c>
       <c r="L71" t="n">
-        <v>2516.76</v>
+        <v>2456.95</v>
       </c>
       <c r="M71" t="n">
-        <v>2551.57</v>
+        <v>2505.18</v>
       </c>
       <c r="N71" t="n">
-        <v>2586.39</v>
+        <v>2553.41</v>
       </c>
       <c r="O71" t="n">
-        <v>2646.6</v>
+        <v>2659.3</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
       </c>
-      <c r="Q71" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R71" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q71" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R71" s="6" t="n">
+        <v/>
       </c>
       <c r="S71" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T71" s="8" t="n">
@@ -6448,84 +6443,96 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2442.56</v>
+        <v>2457.69</v>
       </c>
       <c r="C72" t="n">
-        <v>2459.63</v>
+        <v>2532.96</v>
       </c>
       <c r="D72" t="n">
-        <v>2430.81</v>
+        <v>2389.47</v>
       </c>
       <c r="E72" t="n">
-        <v>2457.69</v>
+        <v>2417.94</v>
       </c>
       <c r="F72" t="n">
-        <v>15.15</v>
+        <v>-39.75</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H72" t="n">
-        <v>28.82</v>
+        <v>143.49</v>
       </c>
       <c r="I72" t="n">
-        <v>2283.43</v>
+        <v>2401.99</v>
       </c>
       <c r="J72" t="n">
-        <v>2302.83</v>
+        <v>2435.1</v>
       </c>
       <c r="K72" t="n">
-        <v>2379.89</v>
+        <v>2443.28</v>
       </c>
       <c r="L72" t="n">
-        <v>2456.95</v>
+        <v>2451.45</v>
       </c>
       <c r="M72" t="n">
-        <v>2505.18</v>
+        <v>2472.1</v>
       </c>
       <c r="N72" t="n">
-        <v>2553.41</v>
+        <v>2492.74</v>
       </c>
       <c r="O72" t="n">
-        <v>2659.3</v>
-      </c>
-      <c r="P72" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q72" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R72" s="6" t="n">
-        <v/>
+        <v>2488.45</v>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T72" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U72" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V72" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W72" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W72" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -6537,85 +6544,75 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2457.69</v>
+        <v>2417.9</v>
       </c>
       <c r="C73" t="n">
-        <v>2532.96</v>
+        <v>2488.92</v>
       </c>
       <c r="D73" t="n">
-        <v>2389.47</v>
+        <v>2401.81</v>
       </c>
       <c r="E73" t="n">
-        <v>2417.94</v>
+        <v>2466.82</v>
       </c>
       <c r="F73" t="n">
-        <v>-39.75</v>
+        <v>48.88</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.0202</v>
       </c>
       <c r="H73" t="n">
-        <v>143.49</v>
+        <v>87.11</v>
       </c>
       <c r="I73" t="n">
-        <v>2401.99</v>
+        <v>2245.98</v>
       </c>
       <c r="J73" t="n">
-        <v>2435.1</v>
+        <v>2252.81</v>
       </c>
       <c r="K73" t="n">
-        <v>2443.28</v>
+        <v>2346.19</v>
       </c>
       <c r="L73" t="n">
-        <v>2451.45</v>
+        <v>2439.58</v>
       </c>
       <c r="M73" t="n">
-        <v>2472.1</v>
+        <v>2489.68</v>
       </c>
       <c r="N73" t="n">
-        <v>2492.74</v>
+        <v>2539.79</v>
       </c>
       <c r="O73" t="n">
-        <v>2488.45</v>
-      </c>
-      <c r="P73" s="6" t="inlineStr">
+        <v>2676.45</v>
+      </c>
+      <c r="P73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q73" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R73" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S73" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U73" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V73" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U73" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V73" s="8" t="n">
+        <v/>
       </c>
       <c r="W73" s="11" t="inlineStr">
         <is>
@@ -6624,76 +6621,78 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2417.9</v>
+        <v>2466.58</v>
       </c>
       <c r="C74" t="n">
-        <v>2488.92</v>
+        <v>2484.4</v>
       </c>
       <c r="D74" t="n">
-        <v>2401.81</v>
+        <v>2383.8</v>
       </c>
       <c r="E74" t="n">
-        <v>2466.82</v>
+        <v>2417.84</v>
       </c>
       <c r="F74" t="n">
-        <v>48.88</v>
+        <v>-48.98</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.0202</v>
+        <v>-0.0199</v>
       </c>
       <c r="H74" t="n">
-        <v>87.11</v>
+        <v>100.6</v>
       </c>
       <c r="I74" t="n">
-        <v>2245.98</v>
+        <v>2314.69</v>
       </c>
       <c r="J74" t="n">
-        <v>2252.81</v>
+        <v>2390.43</v>
       </c>
       <c r="K74" t="n">
-        <v>2346.19</v>
+        <v>2423.26</v>
       </c>
       <c r="L74" t="n">
-        <v>2439.58</v>
+        <v>2456.09</v>
       </c>
       <c r="M74" t="n">
-        <v>2489.68</v>
+        <v>2510.38</v>
       </c>
       <c r="N74" t="n">
-        <v>2539.79</v>
+        <v>2564.66</v>
       </c>
       <c r="O74" t="n">
-        <v>2676.45</v>
+        <v>2576.04</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
       </c>
-      <c r="Q74" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R74" s="6" t="n">
-        <v/>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="n">
+        <v/>
       </c>
       <c r="U74" s="8" t="n">
         <v/>
@@ -6706,74 +6705,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2466.58</v>
+        <v>2417.83</v>
       </c>
       <c r="C75" t="n">
-        <v>2484.4</v>
+        <v>2427.4</v>
       </c>
       <c r="D75" t="n">
-        <v>2383.8</v>
+        <v>2356.19</v>
       </c>
       <c r="E75" t="n">
-        <v>2417.84</v>
+        <v>2391.5</v>
       </c>
       <c r="F75" t="n">
-        <v>-48.98</v>
+        <v>-26.34</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.0109</v>
       </c>
       <c r="H75" t="n">
-        <v>100.6</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>2314.69</v>
+        <v>2283.21</v>
       </c>
       <c r="J75" t="n">
-        <v>2390.43</v>
+        <v>2309.12</v>
       </c>
       <c r="K75" t="n">
-        <v>2423.26</v>
+        <v>2367.54</v>
       </c>
       <c r="L75" t="n">
-        <v>2456.09</v>
+        <v>2425.97</v>
       </c>
       <c r="M75" t="n">
-        <v>2510.38</v>
+        <v>2468.14</v>
       </c>
       <c r="N75" t="n">
-        <v>2564.66</v>
+        <v>2510.31</v>
       </c>
       <c r="O75" t="n">
-        <v>2576.04</v>
+        <v>2584.99</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
       </c>
-      <c r="Q75" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q75" s="6" t="n">
+        <v/>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S75" s="10" t="inlineStr">
+      <c r="S75" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -6797,50 +6790,50 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2417.83</v>
+        <v>2391.6</v>
       </c>
       <c r="C76" t="n">
-        <v>2427.4</v>
+        <v>2526.95</v>
       </c>
       <c r="D76" t="n">
-        <v>2356.19</v>
+        <v>2370.42</v>
       </c>
       <c r="E76" t="n">
-        <v>2391.5</v>
+        <v>2508.02</v>
       </c>
       <c r="F76" t="n">
-        <v>-26.34</v>
+        <v>116.52</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.0109</v>
+        <v>0.0487</v>
       </c>
       <c r="H76" t="n">
-        <v>71.20999999999999</v>
+        <v>156.53</v>
       </c>
       <c r="I76" t="n">
-        <v>2283.21</v>
+        <v>2284.97</v>
       </c>
       <c r="J76" t="n">
-        <v>2309.12</v>
+        <v>2320.14</v>
       </c>
       <c r="K76" t="n">
-        <v>2367.54</v>
+        <v>2355.89</v>
       </c>
       <c r="L76" t="n">
-        <v>2425.97</v>
+        <v>2391.65</v>
       </c>
       <c r="M76" t="n">
-        <v>2468.14</v>
+        <v>2427.11</v>
       </c>
       <c r="N76" t="n">
-        <v>2510.31</v>
+        <v>2462.57</v>
       </c>
       <c r="O76" t="n">
-        <v>2584.99</v>
+        <v>2498.61</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
@@ -6848,28 +6841,32 @@
       <c r="Q76" s="6" t="n">
         <v/>
       </c>
-      <c r="R76" s="6" t="inlineStr">
+      <c r="R76" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S76" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V76" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S76" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U76" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V76" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W76" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W76" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X76" t="inlineStr"/>
@@ -6877,50 +6874,50 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2391.6</v>
+        <v>2508.02</v>
       </c>
       <c r="C77" t="n">
-        <v>2526.95</v>
+        <v>2545.62</v>
       </c>
       <c r="D77" t="n">
-        <v>2370.42</v>
+        <v>2432.35</v>
       </c>
       <c r="E77" t="n">
-        <v>2508.02</v>
+        <v>2456.08</v>
       </c>
       <c r="F77" t="n">
-        <v>116.52</v>
+        <v>-51.94</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.0487</v>
+        <v>-0.0207</v>
       </c>
       <c r="H77" t="n">
-        <v>156.53</v>
+        <v>113.27</v>
       </c>
       <c r="I77" t="n">
-        <v>2284.97</v>
+        <v>2213.88</v>
       </c>
       <c r="J77" t="n">
-        <v>2320.14</v>
+        <v>2381.16</v>
       </c>
       <c r="K77" t="n">
-        <v>2355.89</v>
+        <v>2429.75</v>
       </c>
       <c r="L77" t="n">
-        <v>2391.65</v>
+        <v>2478.35</v>
       </c>
       <c r="M77" t="n">
-        <v>2427.11</v>
+        <v>2586.29</v>
       </c>
       <c r="N77" t="n">
-        <v>2462.57</v>
+        <v>2694.22</v>
       </c>
       <c r="O77" t="n">
-        <v>2498.61</v>
+        <v>2683.48</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
@@ -6933,78 +6930,76 @@
       </c>
       <c r="S77" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U77" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V77" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U77" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V77" s="8" t="n">
+        <v/>
       </c>
       <c r="W77" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr"/>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2508.02</v>
+        <v>2455.99</v>
       </c>
       <c r="C78" t="n">
-        <v>2545.62</v>
+        <v>2492.01</v>
       </c>
       <c r="D78" t="n">
-        <v>2432.35</v>
+        <v>2445.69</v>
       </c>
       <c r="E78" t="n">
-        <v>2456.08</v>
+        <v>2480.74</v>
       </c>
       <c r="F78" t="n">
-        <v>-51.94</v>
+        <v>24.66</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0207</v>
+        <v>0.01</v>
       </c>
       <c r="H78" t="n">
-        <v>113.27</v>
+        <v>46.32</v>
       </c>
       <c r="I78" t="n">
-        <v>2213.88</v>
+        <v>2319.08</v>
       </c>
       <c r="J78" t="n">
-        <v>2381.16</v>
+        <v>2326.35</v>
       </c>
       <c r="K78" t="n">
-        <v>2429.75</v>
+        <v>2399.44</v>
       </c>
       <c r="L78" t="n">
-        <v>2478.35</v>
+        <v>2472.53</v>
       </c>
       <c r="M78" t="n">
-        <v>2586.29</v>
+        <v>2512.71</v>
       </c>
       <c r="N78" t="n">
-        <v>2694.22</v>
+        <v>2552.89</v>
       </c>
       <c r="O78" t="n">
-        <v>2683.48</v>
+        <v>2658.89</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -7017,7 +7012,7 @@
       </c>
       <c r="S78" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T78" s="8" t="n">
@@ -7043,50 +7038,50 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2455.99</v>
+        <v>2480.82</v>
       </c>
       <c r="C79" t="n">
-        <v>2492.01</v>
+        <v>2525.32</v>
       </c>
       <c r="D79" t="n">
-        <v>2445.69</v>
+        <v>2468.19</v>
       </c>
       <c r="E79" t="n">
-        <v>2480.74</v>
+        <v>2514.55</v>
       </c>
       <c r="F79" t="n">
-        <v>24.66</v>
+        <v>33.81</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0136</v>
       </c>
       <c r="H79" t="n">
-        <v>46.32</v>
+        <v>57.13</v>
       </c>
       <c r="I79" t="n">
-        <v>2319.08</v>
+        <v>2399.37</v>
       </c>
       <c r="J79" t="n">
-        <v>2326.35</v>
+        <v>2440.36</v>
       </c>
       <c r="K79" t="n">
-        <v>2399.44</v>
+        <v>2457.58</v>
       </c>
       <c r="L79" t="n">
-        <v>2472.53</v>
+        <v>2474.79</v>
       </c>
       <c r="M79" t="n">
-        <v>2512.71</v>
+        <v>2503.9</v>
       </c>
       <c r="N79" t="n">
-        <v>2552.89</v>
+        <v>2533</v>
       </c>
       <c r="O79" t="n">
-        <v>2658.89</v>
+        <v>2538.33</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7097,13 +7092,15 @@
       <c r="R79" s="6" t="n">
         <v/>
       </c>
-      <c r="S79" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="n">
-        <v/>
+      <c r="S79" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U79" s="8" t="n">
         <v/>
@@ -7116,59 +7113,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2480.82</v>
+        <v>2514.58</v>
       </c>
       <c r="C80" t="n">
-        <v>2525.32</v>
+        <v>2534.86</v>
       </c>
       <c r="D80" t="n">
-        <v>2468.19</v>
+        <v>2466.91</v>
       </c>
       <c r="E80" t="n">
-        <v>2514.55</v>
+        <v>2490.96</v>
       </c>
       <c r="F80" t="n">
-        <v>33.81</v>
+        <v>-23.59</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0094</v>
       </c>
       <c r="H80" t="n">
-        <v>57.13</v>
+        <v>67.95</v>
       </c>
       <c r="I80" t="n">
-        <v>2399.37</v>
+        <v>2411.07</v>
       </c>
       <c r="J80" t="n">
-        <v>2440.36</v>
+        <v>2466.32</v>
       </c>
       <c r="K80" t="n">
-        <v>2457.58</v>
+        <v>2485.99</v>
       </c>
       <c r="L80" t="n">
-        <v>2474.79</v>
+        <v>2505.65</v>
       </c>
       <c r="M80" t="n">
-        <v>2503.9</v>
+        <v>2543.11</v>
       </c>
       <c r="N80" t="n">
-        <v>2533</v>
+        <v>2580.57</v>
       </c>
       <c r="O80" t="n">
-        <v>2538.33</v>
+        <v>2582.45</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7176,18 +7169,18 @@
       <c r="Q80" s="6" t="n">
         <v/>
       </c>
-      <c r="R80" s="6" t="n">
-        <v/>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="n">
+        <v/>
       </c>
       <c r="U80" s="8" t="n">
         <v/>
@@ -7200,55 +7193,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr"/>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2514.58</v>
+        <v>2490.92</v>
       </c>
       <c r="C81" t="n">
-        <v>2534.86</v>
+        <v>2506.75</v>
       </c>
       <c r="D81" t="n">
-        <v>2466.91</v>
+        <v>2441.33</v>
       </c>
       <c r="E81" t="n">
-        <v>2490.96</v>
+        <v>2484.94</v>
       </c>
       <c r="F81" t="n">
-        <v>-23.59</v>
+        <v>-6.02</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0024</v>
       </c>
       <c r="H81" t="n">
-        <v>67.95</v>
+        <v>65.42</v>
       </c>
       <c r="I81" t="n">
-        <v>2411.07</v>
+        <v>2398.96</v>
       </c>
       <c r="J81" t="n">
-        <v>2466.32</v>
+        <v>2418.04</v>
       </c>
       <c r="K81" t="n">
-        <v>2485.99</v>
+        <v>2456.98</v>
       </c>
       <c r="L81" t="n">
-        <v>2505.65</v>
+        <v>2495.92</v>
       </c>
       <c r="M81" t="n">
-        <v>2543.11</v>
+        <v>2524.93</v>
       </c>
       <c r="N81" t="n">
-        <v>2580.57</v>
+        <v>2553.94</v>
       </c>
       <c r="O81" t="n">
-        <v>2582.45</v>
+        <v>2602.81</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7258,12 +7255,12 @@
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S81" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S81" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T81" s="8" t="n">
@@ -7282,57 +7279,57 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2490.92</v>
+        <v>2484.89</v>
       </c>
       <c r="C82" t="n">
-        <v>2506.75</v>
+        <v>2522.37</v>
       </c>
       <c r="D82" t="n">
-        <v>2441.33</v>
+        <v>2443.7</v>
       </c>
       <c r="E82" t="n">
-        <v>2484.94</v>
+        <v>2466.91</v>
       </c>
       <c r="F82" t="n">
-        <v>-6.02</v>
+        <v>-18.03</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0073</v>
       </c>
       <c r="H82" t="n">
-        <v>65.42</v>
+        <v>78.67</v>
       </c>
       <c r="I82" t="n">
-        <v>2398.96</v>
+        <v>2375.9</v>
       </c>
       <c r="J82" t="n">
-        <v>2418.04</v>
+        <v>2424.97</v>
       </c>
       <c r="K82" t="n">
-        <v>2456.98</v>
+        <v>2452.23</v>
       </c>
       <c r="L82" t="n">
-        <v>2495.92</v>
+        <v>2479.49</v>
       </c>
       <c r="M82" t="n">
-        <v>2524.93</v>
+        <v>2517.65</v>
       </c>
       <c r="N82" t="n">
-        <v>2553.94</v>
+        <v>2555.82</v>
       </c>
       <c r="O82" t="n">
-        <v>2602.81</v>
+        <v>2572.18</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7345,13 +7342,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S82" s="10" t="inlineStr">
+      <c r="S82" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T82" s="8" t="n">
-        <v/>
+      <c r="T82" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U82" s="8" t="n">
         <v/>
@@ -7366,57 +7365,57 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2484.89</v>
+        <v>2466.91</v>
       </c>
       <c r="C83" t="n">
-        <v>2522.37</v>
+        <v>2483.72</v>
       </c>
       <c r="D83" t="n">
-        <v>2443.7</v>
+        <v>2406.91</v>
       </c>
       <c r="E83" t="n">
-        <v>2466.91</v>
+        <v>2437.1</v>
       </c>
       <c r="F83" t="n">
-        <v>-18.03</v>
+        <v>-29.82</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0121</v>
       </c>
       <c r="H83" t="n">
-        <v>78.67</v>
+        <v>76.81</v>
       </c>
       <c r="I83" t="n">
-        <v>2375.9</v>
+        <v>2365.04</v>
       </c>
       <c r="J83" t="n">
-        <v>2424.97</v>
+        <v>2380.19</v>
       </c>
       <c r="K83" t="n">
-        <v>2452.23</v>
+        <v>2427.58</v>
       </c>
       <c r="L83" t="n">
-        <v>2479.49</v>
+        <v>2474.97</v>
       </c>
       <c r="M83" t="n">
-        <v>2517.65</v>
+        <v>2506.25</v>
       </c>
       <c r="N83" t="n">
-        <v>2555.82</v>
+        <v>2537.52</v>
       </c>
       <c r="O83" t="n">
-        <v>2572.18</v>
+        <v>2601.04</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
@@ -7426,18 +7425,16 @@
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S83" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S83" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="n">
+        <v/>
       </c>
       <c r="U83" s="8" t="n">
         <v/>
@@ -7452,57 +7449,57 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2466.91</v>
+        <v>2437.14</v>
       </c>
       <c r="C84" t="n">
-        <v>2483.72</v>
+        <v>2663.05</v>
       </c>
       <c r="D84" t="n">
-        <v>2406.91</v>
+        <v>2435.29</v>
       </c>
       <c r="E84" t="n">
-        <v>2437.1</v>
+        <v>2514.73</v>
       </c>
       <c r="F84" t="n">
-        <v>-29.82</v>
+        <v>77.64</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0121</v>
+        <v>0.0319</v>
       </c>
       <c r="H84" t="n">
-        <v>76.81</v>
+        <v>227.76</v>
       </c>
       <c r="I84" t="n">
-        <v>2365.04</v>
+        <v>2330.09</v>
       </c>
       <c r="J84" t="n">
-        <v>2380.19</v>
+        <v>2356.18</v>
       </c>
       <c r="K84" t="n">
-        <v>2427.58</v>
+        <v>2398.69</v>
       </c>
       <c r="L84" t="n">
-        <v>2474.97</v>
+        <v>2441.21</v>
       </c>
       <c r="M84" t="n">
-        <v>2506.25</v>
+        <v>2475.51</v>
       </c>
       <c r="N84" t="n">
-        <v>2537.52</v>
+        <v>2509.8</v>
       </c>
       <c r="O84" t="n">
-        <v>2601.04</v>
+        <v>2560.53</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
@@ -7510,83 +7507,83 @@
       <c r="Q84" s="6" t="n">
         <v/>
       </c>
-      <c r="R84" s="6" t="inlineStr">
+      <c r="R84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S84" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U84" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S84" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U84" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V84" s="8" t="n">
-        <v/>
+      <c r="V84" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W84" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2437.14</v>
+        <v>2514.77</v>
       </c>
       <c r="C85" t="n">
-        <v>2663.05</v>
+        <v>2544.47</v>
       </c>
       <c r="D85" t="n">
-        <v>2435.29</v>
+        <v>2508.8</v>
       </c>
       <c r="E85" t="n">
-        <v>2514.73</v>
+        <v>2525.94</v>
       </c>
       <c r="F85" t="n">
-        <v>77.64</v>
+        <v>11.21</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.0319</v>
+        <v>0.0045</v>
       </c>
       <c r="H85" t="n">
-        <v>227.76</v>
+        <v>35.67</v>
       </c>
       <c r="I85" t="n">
-        <v>2330.09</v>
+        <v>2207.52</v>
       </c>
       <c r="J85" t="n">
-        <v>2356.18</v>
+        <v>2269.75</v>
       </c>
       <c r="K85" t="n">
-        <v>2398.69</v>
+        <v>2400.85</v>
       </c>
       <c r="L85" t="n">
-        <v>2441.21</v>
+        <v>2531.95</v>
       </c>
       <c r="M85" t="n">
-        <v>2475.51</v>
+        <v>2628.62</v>
       </c>
       <c r="N85" t="n">
-        <v>2509.8</v>
+        <v>2725.28</v>
       </c>
       <c r="O85" t="n">
-        <v>2560.53</v>
+        <v>2890.82</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7599,91 +7596,95 @@
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U85" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U85" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V85" s="8" t="n">
+        <v/>
       </c>
       <c r="W85" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr"/>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2514.77</v>
+        <v>2525.94</v>
       </c>
       <c r="C86" t="n">
-        <v>2544.47</v>
+        <v>2526.85</v>
       </c>
       <c r="D86" t="n">
-        <v>2508.8</v>
+        <v>2462.84</v>
       </c>
       <c r="E86" t="n">
-        <v>2525.94</v>
+        <v>2477.02</v>
       </c>
       <c r="F86" t="n">
-        <v>11.21</v>
+        <v>-48.92</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0194</v>
       </c>
       <c r="H86" t="n">
-        <v>35.67</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>2207.52</v>
+        <v>2473.13</v>
       </c>
       <c r="J86" t="n">
-        <v>2269.75</v>
+        <v>2489.93</v>
       </c>
       <c r="K86" t="n">
-        <v>2400.85</v>
+        <v>2508.11</v>
       </c>
       <c r="L86" t="n">
-        <v>2531.95</v>
+        <v>2526.29</v>
       </c>
       <c r="M86" t="n">
-        <v>2628.62</v>
+        <v>2543.78</v>
       </c>
       <c r="N86" t="n">
-        <v>2725.28</v>
+        <v>2561.27</v>
       </c>
       <c r="O86" t="n">
-        <v>2890.82</v>
-      </c>
-      <c r="P86" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q86" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R86" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S86" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>2580.14</v>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S86" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T86" s="8" t="n">
@@ -7695,148 +7696,148 @@
       <c r="V86" s="8" t="n">
         <v/>
       </c>
-      <c r="W86" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W86" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2525.94</v>
+        <v>2476.6</v>
       </c>
       <c r="C87" t="n">
-        <v>2526.85</v>
+        <v>2612.4</v>
       </c>
       <c r="D87" t="n">
-        <v>2462.84</v>
+        <v>2465.43</v>
       </c>
       <c r="E87" t="n">
-        <v>2477.02</v>
+        <v>2514.41</v>
       </c>
       <c r="F87" t="n">
-        <v>-48.92</v>
+        <v>37.39</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>-0.0194</v>
+        <v>0.0151</v>
       </c>
       <c r="H87" t="n">
-        <v>64.01000000000001</v>
+        <v>146.98</v>
       </c>
       <c r="I87" t="n">
-        <v>2473.13</v>
+        <v>2398.83</v>
       </c>
       <c r="J87" t="n">
-        <v>2489.93</v>
+        <v>2404.09</v>
       </c>
       <c r="K87" t="n">
-        <v>2508.11</v>
+        <v>2445.01</v>
       </c>
       <c r="L87" t="n">
-        <v>2526.29</v>
+        <v>2485.93</v>
       </c>
       <c r="M87" t="n">
-        <v>2543.78</v>
+        <v>2509.03</v>
       </c>
       <c r="N87" t="n">
-        <v>2561.27</v>
+        <v>2532.12</v>
       </c>
       <c r="O87" t="n">
-        <v>2580.14</v>
-      </c>
-      <c r="P87" s="6" t="inlineStr">
+        <v>2590.87</v>
+      </c>
+      <c r="P87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R87" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S87" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q87" s="6" t="inlineStr">
+      <c r="U87" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R87" s="6" t="inlineStr">
+      <c r="V87" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S87" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V87" s="8" t="n">
-        <v/>
-      </c>
       <c r="W87" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr"/>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2476.6</v>
+        <v>2514.36</v>
       </c>
       <c r="C88" t="n">
-        <v>2612.4</v>
+        <v>2519.32</v>
       </c>
       <c r="D88" t="n">
-        <v>2465.43</v>
+        <v>2357.96</v>
       </c>
       <c r="E88" t="n">
-        <v>2514.41</v>
+        <v>2399.09</v>
       </c>
       <c r="F88" t="n">
-        <v>37.39</v>
+        <v>-115.32</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.0459</v>
       </c>
       <c r="H88" t="n">
-        <v>146.98</v>
+        <v>161.36</v>
       </c>
       <c r="I88" t="n">
-        <v>2398.83</v>
+        <v>2318.45</v>
       </c>
       <c r="J88" t="n">
-        <v>2404.09</v>
+        <v>2355.18</v>
       </c>
       <c r="K88" t="n">
-        <v>2445.01</v>
+        <v>2440.92</v>
       </c>
       <c r="L88" t="n">
-        <v>2485.93</v>
+        <v>2526.66</v>
       </c>
       <c r="M88" t="n">
-        <v>2509.03</v>
+        <v>2587.9</v>
       </c>
       <c r="N88" t="n">
-        <v>2532.12</v>
+        <v>2649.13</v>
       </c>
       <c r="O88" t="n">
-        <v>2590.87</v>
+        <v>2759.38</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
@@ -7844,87 +7845,79 @@
       <c r="Q88" s="6" t="n">
         <v/>
       </c>
-      <c r="R88" s="6" t="n">
-        <v/>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V88" s="8" t="n">
+        <v/>
       </c>
       <c r="W88" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2514.36</v>
+        <v>2399.06</v>
       </c>
       <c r="C89" t="n">
-        <v>2519.32</v>
+        <v>2426.93</v>
       </c>
       <c r="D89" t="n">
-        <v>2357.96</v>
+        <v>2368.74</v>
       </c>
       <c r="E89" t="n">
-        <v>2399.09</v>
+        <v>2416.12</v>
       </c>
       <c r="F89" t="n">
-        <v>-115.32</v>
+        <v>17.03</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-0.0459</v>
+        <v>0.0071</v>
       </c>
       <c r="H89" t="n">
-        <v>161.36</v>
+        <v>58.19</v>
       </c>
       <c r="I89" t="n">
-        <v>2318.45</v>
+        <v>2196.6</v>
       </c>
       <c r="J89" t="n">
-        <v>2355.18</v>
+        <v>2217.95</v>
       </c>
       <c r="K89" t="n">
-        <v>2440.92</v>
+        <v>2318.41</v>
       </c>
       <c r="L89" t="n">
-        <v>2526.66</v>
+        <v>2418.86</v>
       </c>
       <c r="M89" t="n">
-        <v>2587.9</v>
+        <v>2479.77</v>
       </c>
       <c r="N89" t="n">
-        <v>2649.13</v>
+        <v>2540.67</v>
       </c>
       <c r="O89" t="n">
-        <v>2759.38</v>
+        <v>2680.68</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7932,14 +7925,12 @@
       <c r="Q89" s="6" t="n">
         <v/>
       </c>
-      <c r="R89" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S89" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S89" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T89" s="8" t="n">
@@ -7956,55 +7947,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr"/>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2399.06</v>
+        <v>2445.49</v>
       </c>
       <c r="C90" t="n">
-        <v>2426.93</v>
+        <v>2445.49</v>
       </c>
       <c r="D90" t="n">
-        <v>2368.74</v>
+        <v>2438.16</v>
       </c>
       <c r="E90" t="n">
-        <v>2416.12</v>
+        <v>2438.11</v>
       </c>
       <c r="F90" t="n">
-        <v>17.03</v>
+        <v>21.99</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0091</v>
       </c>
       <c r="H90" t="n">
-        <v>58.19</v>
+        <v>7.32</v>
       </c>
       <c r="I90" t="n">
-        <v>2196.6</v>
+        <v>2310.54</v>
       </c>
       <c r="J90" t="n">
-        <v>2217.95</v>
+        <v>2367.07</v>
       </c>
       <c r="K90" t="n">
-        <v>2318.41</v>
+        <v>2387.02</v>
       </c>
       <c r="L90" t="n">
-        <v>2418.86</v>
+        <v>2406.98</v>
       </c>
       <c r="M90" t="n">
-        <v>2479.77</v>
+        <v>2445.22</v>
       </c>
       <c r="N90" t="n">
-        <v>2540.67</v>
+        <v>2483.46</v>
       </c>
       <c r="O90" t="n">
-        <v>2680.68</v>
+        <v>2485.12</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
@@ -8017,11 +8012,13 @@
       </c>
       <c r="S90" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U90" s="8" t="n">
         <v/>
@@ -8036,120 +8033,8 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>2416.14</v>
-      </c>
-      <c r="C91" t="n">
-        <v>2477.4</v>
-      </c>
-      <c r="D91" t="n">
-        <v>2413.96</v>
-      </c>
-      <c r="E91" t="n">
-        <v>2445.47</v>
-      </c>
-      <c r="F91" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="H91" t="n">
-        <v>63.44</v>
-      </c>
-      <c r="I91" t="n">
-        <v>2310.54</v>
-      </c>
-      <c r="J91" t="n">
-        <v>2367.07</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2387.02</v>
-      </c>
-      <c r="L91" t="n">
-        <v>2406.98</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2445.22</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2483.46</v>
-      </c>
-      <c r="O91" t="n">
-        <v>2485.12</v>
-      </c>
-      <c r="P91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S91" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W91" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
           <t>強警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I92" s="13" t="n">
-        <v>2350.51</v>
-      </c>
-      <c r="J92" s="13" t="n">
-        <v>2381.92</v>
-      </c>
-      <c r="K92" s="13" t="n">
-        <v>2413.75</v>
-      </c>
-      <c r="L92" s="13" t="n">
-        <v>2445.57</v>
-      </c>
-      <c r="M92" s="13" t="n">
-        <v>2477.19</v>
-      </c>
-      <c r="N92" s="13" t="n">
-        <v>2508.81</v>
-      </c>
-      <c r="O92" s="13" t="n">
-        <v>2540.85</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -7969,13 +7969,13 @@
         <v>2438.16</v>
       </c>
       <c r="E90" t="n">
-        <v>2438.11</v>
+        <v>2445.52</v>
       </c>
       <c r="F90" t="n">
-        <v>21.99</v>
+        <v>29.4</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0122</v>
       </c>
       <c r="H90" t="n">
         <v>7.32</v>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X90"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1739.34</v>
+        <v>1726.52</v>
       </c>
       <c r="C2" t="n">
-        <v>1739.49</v>
+        <v>1733.61</v>
       </c>
       <c r="D2" t="n">
-        <v>1701.94</v>
+        <v>1638.25</v>
       </c>
       <c r="E2" t="n">
-        <v>1704.58</v>
+        <v>1665.44</v>
       </c>
       <c r="F2" t="n">
-        <v>-34.72</v>
+        <v>-61.07</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.02</v>
+        <v>-0.0354</v>
       </c>
       <c r="H2" t="n">
-        <v>37.55</v>
+        <v>95.36</v>
       </c>
       <c r="I2" t="n">
-        <v>1658.34</v>
+        <v>1632.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1701.98</v>
+        <v>1647.11</v>
       </c>
       <c r="K2" t="n">
-        <v>1717.07</v>
+        <v>1690.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1732.17</v>
+        <v>1733.59</v>
       </c>
       <c r="M2" t="n">
-        <v>1761.53</v>
+        <v>1762.67</v>
       </c>
       <c r="N2" t="n">
-        <v>1790.89</v>
+        <v>1791.74</v>
       </c>
       <c r="O2" t="n">
-        <v>1791.72</v>
+        <v>1849.15</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -720,74 +720,74 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1704.63</v>
+        <v>1665.31</v>
       </c>
       <c r="C3" t="n">
-        <v>1776.83</v>
+        <v>1687.49</v>
       </c>
       <c r="D3" t="n">
-        <v>1704.52</v>
+        <v>1551.48</v>
       </c>
       <c r="E3" t="n">
-        <v>1726.51</v>
+        <v>1619.92</v>
       </c>
       <c r="F3" t="n">
-        <v>21.93</v>
+        <v>-45.51</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0273</v>
       </c>
       <c r="H3" t="n">
-        <v>72.31999999999999</v>
+        <v>136.01</v>
       </c>
       <c r="I3" t="n">
-        <v>1664.39</v>
+        <v>1542.89</v>
       </c>
       <c r="J3" t="n">
-        <v>1658.97</v>
+        <v>1559.83</v>
       </c>
       <c r="K3" t="n">
-        <v>1685.81</v>
+        <v>1617.76</v>
       </c>
       <c r="L3" t="n">
-        <v>1712.65</v>
+        <v>1675.68</v>
       </c>
       <c r="M3" t="n">
-        <v>1723.36</v>
+        <v>1713.12</v>
       </c>
       <c r="N3" t="n">
-        <v>1734.06</v>
+        <v>1750.55</v>
       </c>
       <c r="O3" t="n">
-        <v>1777.04</v>
+        <v>1828.97</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -797,67 +797,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1726.52</v>
+        <v>1619.89</v>
       </c>
       <c r="C4" t="n">
-        <v>1733.61</v>
+        <v>1656.65</v>
       </c>
       <c r="D4" t="n">
-        <v>1638.25</v>
+        <v>1531.78</v>
       </c>
       <c r="E4" t="n">
-        <v>1665.44</v>
+        <v>1564.82</v>
       </c>
       <c r="F4" t="n">
-        <v>-61.07</v>
+        <v>-55.11</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0354</v>
+        <v>-0.034</v>
       </c>
       <c r="H4" t="n">
-        <v>95.36</v>
+        <v>124.87</v>
       </c>
       <c r="I4" t="n">
-        <v>1632.2</v>
+        <v>1415.48</v>
       </c>
       <c r="J4" t="n">
-        <v>1647.11</v>
+        <v>1484.14</v>
       </c>
       <c r="K4" t="n">
-        <v>1690.35</v>
+        <v>1551.92</v>
       </c>
       <c r="L4" t="n">
-        <v>1733.59</v>
+        <v>1619.71</v>
       </c>
       <c r="M4" t="n">
-        <v>1762.67</v>
+        <v>1687.93</v>
       </c>
       <c r="N4" t="n">
-        <v>1791.74</v>
+        <v>1756.15</v>
       </c>
       <c r="O4" t="n">
-        <v>1849.15</v>
+        <v>1823.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
@@ -888,67 +890,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1665.31</v>
+        <v>1564.61</v>
       </c>
       <c r="C5" t="n">
-        <v>1687.49</v>
+        <v>1590.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1551.48</v>
+        <v>1510.51</v>
       </c>
       <c r="E5" t="n">
-        <v>1619.92</v>
+        <v>1576.62</v>
       </c>
       <c r="F5" t="n">
-        <v>-45.51</v>
+        <v>11.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0273</v>
+        <v>0.0075</v>
       </c>
       <c r="H5" t="n">
-        <v>136.01</v>
+        <v>79.69</v>
       </c>
       <c r="I5" t="n">
-        <v>1542.89</v>
+        <v>1406.91</v>
       </c>
       <c r="J5" t="n">
-        <v>1559.83</v>
+        <v>1425.25</v>
       </c>
       <c r="K5" t="n">
-        <v>1617.76</v>
+        <v>1502.38</v>
       </c>
       <c r="L5" t="n">
-        <v>1675.68</v>
+        <v>1579.52</v>
       </c>
       <c r="M5" t="n">
-        <v>1713.12</v>
+        <v>1627.25</v>
       </c>
       <c r="N5" t="n">
-        <v>1750.55</v>
+        <v>1674.98</v>
       </c>
       <c r="O5" t="n">
-        <v>1828.97</v>
+        <v>1781.51</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -967,57 +965,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1619.89</v>
+        <v>1576.59</v>
       </c>
       <c r="C6" t="n">
-        <v>1656.65</v>
+        <v>1607.87</v>
       </c>
       <c r="D6" t="n">
-        <v>1531.78</v>
+        <v>1561.97</v>
       </c>
       <c r="E6" t="n">
-        <v>1564.82</v>
+        <v>1571.59</v>
       </c>
       <c r="F6" t="n">
-        <v>-55.11</v>
+        <v>-5.03</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.034</v>
+        <v>-0.0032</v>
       </c>
       <c r="H6" t="n">
-        <v>124.87</v>
+        <v>45.89</v>
       </c>
       <c r="I6" t="n">
-        <v>1415.48</v>
+        <v>1430.81</v>
       </c>
       <c r="J6" t="n">
-        <v>1484.14</v>
+        <v>1510.05</v>
       </c>
       <c r="K6" t="n">
-        <v>1551.92</v>
+        <v>1536.77</v>
       </c>
       <c r="L6" t="n">
-        <v>1619.71</v>
+        <v>1563.48</v>
       </c>
       <c r="M6" t="n">
-        <v>1687.93</v>
+        <v>1616.46</v>
       </c>
       <c r="N6" t="n">
-        <v>1756.15</v>
+        <v>1669.44</v>
       </c>
       <c r="O6" t="n">
-        <v>1823.5</v>
+        <v>1669.89</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,14 +1023,12 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1051,57 +1047,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1564.61</v>
+        <v>1571.56</v>
       </c>
       <c r="C7" t="n">
-        <v>1590.2</v>
+        <v>1585.22</v>
       </c>
       <c r="D7" t="n">
-        <v>1510.51</v>
+        <v>1548.76</v>
       </c>
       <c r="E7" t="n">
-        <v>1576.62</v>
+        <v>1570.36</v>
       </c>
       <c r="F7" t="n">
-        <v>11.8</v>
+        <v>-1.23</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0008</v>
       </c>
       <c r="H7" t="n">
-        <v>79.69</v>
+        <v>36.46</v>
       </c>
       <c r="I7" t="n">
-        <v>1406.91</v>
+        <v>1516.08</v>
       </c>
       <c r="J7" t="n">
-        <v>1425.25</v>
+        <v>1519.03</v>
       </c>
       <c r="K7" t="n">
-        <v>1502.38</v>
+        <v>1548.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1579.52</v>
+        <v>1578.25</v>
       </c>
       <c r="M7" t="n">
-        <v>1627.25</v>
+        <v>1594.53</v>
       </c>
       <c r="N7" t="n">
-        <v>1674.98</v>
+        <v>1610.82</v>
       </c>
       <c r="O7" t="n">
-        <v>1781.51</v>
+        <v>1653.76</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1133,57 +1129,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1576.59</v>
+        <v>1569.99</v>
       </c>
       <c r="C8" t="n">
-        <v>1607.87</v>
+        <v>1633.65</v>
       </c>
       <c r="D8" t="n">
-        <v>1561.97</v>
+        <v>1550.04</v>
       </c>
       <c r="E8" t="n">
-        <v>1571.59</v>
+        <v>1610.21</v>
       </c>
       <c r="F8" t="n">
-        <v>-5.03</v>
+        <v>39.84</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0032</v>
+        <v>0.0254</v>
       </c>
       <c r="H8" t="n">
-        <v>45.89</v>
+        <v>83.61</v>
       </c>
       <c r="I8" t="n">
-        <v>1430.81</v>
+        <v>1512.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1510.05</v>
+        <v>1535.59</v>
       </c>
       <c r="K8" t="n">
-        <v>1536.77</v>
+        <v>1552.13</v>
       </c>
       <c r="L8" t="n">
-        <v>1563.48</v>
+        <v>1568.68</v>
       </c>
       <c r="M8" t="n">
-        <v>1616.46</v>
+        <v>1588.59</v>
       </c>
       <c r="N8" t="n">
-        <v>1669.44</v>
+        <v>1608.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1669.89</v>
+        <v>1621.68</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,81 +1187,85 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1571.56</v>
+        <v>1610.16</v>
       </c>
       <c r="C9" t="n">
-        <v>1585.22</v>
+        <v>1611.35</v>
       </c>
       <c r="D9" t="n">
-        <v>1548.76</v>
+        <v>1549.25</v>
       </c>
       <c r="E9" t="n">
-        <v>1570.36</v>
+        <v>1569.58</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.23</v>
+        <v>-40.62</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0008</v>
+        <v>-0.0252</v>
       </c>
       <c r="H9" t="n">
-        <v>36.46</v>
+        <v>62.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1516.08</v>
+        <v>1466.43</v>
       </c>
       <c r="J9" t="n">
-        <v>1519.03</v>
+        <v>1535.78</v>
       </c>
       <c r="K9" t="n">
-        <v>1548.64</v>
+        <v>1568.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1578.25</v>
+        <v>1601.02</v>
       </c>
       <c r="M9" t="n">
-        <v>1594.53</v>
+        <v>1652.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1610.82</v>
+        <v>1703</v>
       </c>
       <c r="O9" t="n">
-        <v>1653.76</v>
+        <v>1717.25</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,12 +1273,14 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1304,50 +1306,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1569.99</v>
+        <v>1569.91</v>
       </c>
       <c r="C10" t="n">
-        <v>1633.65</v>
+        <v>1642.45</v>
       </c>
       <c r="D10" t="n">
-        <v>1550.04</v>
+        <v>1551.14</v>
       </c>
       <c r="E10" t="n">
-        <v>1610.21</v>
+        <v>1608.96</v>
       </c>
       <c r="F10" t="n">
-        <v>39.84</v>
+        <v>39.38</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0254</v>
+        <v>0.0251</v>
       </c>
       <c r="H10" t="n">
-        <v>83.61</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1512.3</v>
+        <v>1487.16</v>
       </c>
       <c r="J10" t="n">
-        <v>1535.59</v>
+        <v>1502.13</v>
       </c>
       <c r="K10" t="n">
-        <v>1552.13</v>
+        <v>1538.54</v>
       </c>
       <c r="L10" t="n">
-        <v>1568.68</v>
+        <v>1574.94</v>
       </c>
       <c r="M10" t="n">
-        <v>1588.59</v>
+        <v>1600.63</v>
       </c>
       <c r="N10" t="n">
-        <v>1608.5</v>
+        <v>1626.32</v>
       </c>
       <c r="O10" t="n">
-        <v>1621.68</v>
+        <v>1673.44</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,30 +1357,26 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1390,50 +1388,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1610.16</v>
+        <v>1609.01</v>
       </c>
       <c r="C11" t="n">
-        <v>1611.35</v>
+        <v>1720.34</v>
       </c>
       <c r="D11" t="n">
-        <v>1549.25</v>
+        <v>1595.94</v>
       </c>
       <c r="E11" t="n">
-        <v>1569.58</v>
+        <v>1698.17</v>
       </c>
       <c r="F11" t="n">
-        <v>-40.62</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0252</v>
+        <v>0.0554</v>
       </c>
       <c r="H11" t="n">
-        <v>62.1</v>
+        <v>124.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1466.43</v>
+        <v>1459.82</v>
       </c>
       <c r="J11" t="n">
-        <v>1535.78</v>
+        <v>1523.73</v>
       </c>
       <c r="K11" t="n">
-        <v>1568.4</v>
+        <v>1563.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1601.02</v>
+        <v>1602.88</v>
       </c>
       <c r="M11" t="n">
-        <v>1652.01</v>
+        <v>1654.62</v>
       </c>
       <c r="N11" t="n">
-        <v>1703</v>
+        <v>1706.36</v>
       </c>
       <c r="O11" t="n">
-        <v>1717.25</v>
+        <v>1733.77</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1441,22 +1439,24 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1465,59 +1465,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1569.91</v>
+        <v>1698.42</v>
       </c>
       <c r="C12" t="n">
-        <v>1642.45</v>
+        <v>1772.54</v>
       </c>
       <c r="D12" t="n">
-        <v>1551.14</v>
+        <v>1693.04</v>
       </c>
       <c r="E12" t="n">
-        <v>1608.96</v>
+        <v>1756.52</v>
       </c>
       <c r="F12" t="n">
-        <v>39.38</v>
+        <v>58.35</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0344</v>
       </c>
       <c r="H12" t="n">
-        <v>91.31999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1487.16</v>
+        <v>1471.54</v>
       </c>
       <c r="J12" t="n">
-        <v>1502.13</v>
+        <v>1593.78</v>
       </c>
       <c r="K12" t="n">
-        <v>1538.54</v>
+        <v>1635.97</v>
       </c>
       <c r="L12" t="n">
-        <v>1574.94</v>
+        <v>1678.16</v>
       </c>
       <c r="M12" t="n">
-        <v>1600.63</v>
+        <v>1760.37</v>
       </c>
       <c r="N12" t="n">
-        <v>1626.32</v>
+        <v>1842.59</v>
       </c>
       <c r="O12" t="n">
-        <v>1673.44</v>
+        <v>1844.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1538,10 +1534,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1556,50 +1550,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1609.01</v>
+        <v>1756.58</v>
       </c>
       <c r="C13" t="n">
-        <v>1720.34</v>
+        <v>1804.59</v>
       </c>
       <c r="D13" t="n">
-        <v>1595.94</v>
+        <v>1743.56</v>
       </c>
       <c r="E13" t="n">
-        <v>1698.17</v>
+        <v>1779.03</v>
       </c>
       <c r="F13" t="n">
-        <v>89.20999999999999</v>
+        <v>22.51</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0128</v>
       </c>
       <c r="H13" t="n">
-        <v>124.4</v>
+        <v>61.02</v>
       </c>
       <c r="I13" t="n">
-        <v>1459.82</v>
+        <v>1613.53</v>
       </c>
       <c r="J13" t="n">
-        <v>1523.73</v>
+        <v>1688.88</v>
       </c>
       <c r="K13" t="n">
-        <v>1563.3</v>
+        <v>1716.77</v>
       </c>
       <c r="L13" t="n">
-        <v>1602.88</v>
+        <v>1744.65</v>
       </c>
       <c r="M13" t="n">
-        <v>1654.62</v>
+        <v>1796.27</v>
       </c>
       <c r="N13" t="n">
-        <v>1706.36</v>
+        <v>1847.89</v>
       </c>
       <c r="O13" t="n">
-        <v>1733.77</v>
+        <v>1852.05</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1617,13 +1611,11 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1638,50 +1630,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1698.42</v>
+        <v>1779.04</v>
       </c>
       <c r="C14" t="n">
-        <v>1772.54</v>
+        <v>1805.91</v>
       </c>
       <c r="D14" t="n">
-        <v>1693.04</v>
+        <v>1749.14</v>
       </c>
       <c r="E14" t="n">
-        <v>1756.52</v>
+        <v>1783.01</v>
       </c>
       <c r="F14" t="n">
-        <v>58.35</v>
+        <v>3.97</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0022</v>
       </c>
       <c r="H14" t="n">
-        <v>79.5</v>
+        <v>56.78</v>
       </c>
       <c r="I14" t="n">
-        <v>1471.54</v>
+        <v>1682.54</v>
       </c>
       <c r="J14" t="n">
-        <v>1593.78</v>
+        <v>1720.49</v>
       </c>
       <c r="K14" t="n">
-        <v>1635.97</v>
+        <v>1748.52</v>
       </c>
       <c r="L14" t="n">
-        <v>1678.16</v>
+        <v>1776.55</v>
       </c>
       <c r="M14" t="n">
-        <v>1760.37</v>
+        <v>1809.55</v>
       </c>
       <c r="N14" t="n">
-        <v>1842.59</v>
+        <v>1842.54</v>
       </c>
       <c r="O14" t="n">
-        <v>1844.75</v>
+        <v>1865.61</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,13 +1686,11 @@
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1718,59 +1708,63 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1756.58</v>
+        <v>1783</v>
       </c>
       <c r="C15" t="n">
-        <v>1804.59</v>
+        <v>1829.51</v>
       </c>
       <c r="D15" t="n">
-        <v>1743.56</v>
+        <v>1728.97</v>
       </c>
       <c r="E15" t="n">
-        <v>1779.03</v>
+        <v>1797.57</v>
       </c>
       <c r="F15" t="n">
-        <v>22.51</v>
+        <v>14.57</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>61.02</v>
+        <v>100.55</v>
       </c>
       <c r="I15" t="n">
-        <v>1613.53</v>
+        <v>1692.36</v>
       </c>
       <c r="J15" t="n">
-        <v>1688.88</v>
+        <v>1728.97</v>
       </c>
       <c r="K15" t="n">
-        <v>1716.77</v>
+        <v>1754.62</v>
       </c>
       <c r="L15" t="n">
-        <v>1744.65</v>
+        <v>1780.27</v>
       </c>
       <c r="M15" t="n">
-        <v>1796.27</v>
+        <v>1811.39</v>
       </c>
       <c r="N15" t="n">
-        <v>1847.89</v>
+        <v>1842.52</v>
       </c>
       <c r="O15" t="n">
-        <v>1852.05</v>
+        <v>1862.69</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
@@ -1793,55 +1787,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779.04</v>
+        <v>1797.56</v>
       </c>
       <c r="C16" t="n">
-        <v>1805.91</v>
+        <v>1810.33</v>
       </c>
       <c r="D16" t="n">
-        <v>1749.14</v>
+        <v>1756.71</v>
       </c>
       <c r="E16" t="n">
-        <v>1783.01</v>
+        <v>1768.51</v>
       </c>
       <c r="F16" t="n">
-        <v>3.97</v>
+        <v>-29.06</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0162</v>
       </c>
       <c r="H16" t="n">
-        <v>56.78</v>
+        <v>53.62</v>
       </c>
       <c r="I16" t="n">
-        <v>1682.54</v>
+        <v>1628.42</v>
       </c>
       <c r="J16" t="n">
-        <v>1720.49</v>
+        <v>1706.19</v>
       </c>
       <c r="K16" t="n">
-        <v>1748.52</v>
+        <v>1747.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1776.55</v>
+        <v>1788.41</v>
       </c>
       <c r="M16" t="n">
-        <v>1809.55</v>
+        <v>1847.85</v>
       </c>
       <c r="N16" t="n">
-        <v>1842.54</v>
+        <v>1907.29</v>
       </c>
       <c r="O16" t="n">
-        <v>1865.61</v>
+        <v>1930.06</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1852,9 +1850,9 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1871,79 +1869,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1783</v>
+        <v>1768.39</v>
       </c>
       <c r="C17" t="n">
-        <v>1829.51</v>
+        <v>1782.86</v>
       </c>
       <c r="D17" t="n">
-        <v>1728.97</v>
+        <v>1711.9</v>
       </c>
       <c r="E17" t="n">
-        <v>1797.57</v>
+        <v>1742.68</v>
       </c>
       <c r="F17" t="n">
-        <v>14.57</v>
+        <v>-25.83</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0146</v>
       </c>
       <c r="H17" t="n">
-        <v>100.55</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1692.36</v>
+        <v>1703.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1728.97</v>
+        <v>1707.39</v>
       </c>
       <c r="K17" t="n">
-        <v>1754.62</v>
+        <v>1741.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1780.27</v>
+        <v>1776.02</v>
       </c>
       <c r="M17" t="n">
-        <v>1811.39</v>
+        <v>1795.32</v>
       </c>
       <c r="N17" t="n">
-        <v>1842.52</v>
+        <v>1814.62</v>
       </c>
       <c r="O17" t="n">
-        <v>1862.69</v>
+        <v>1863.95</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q17" s="6" t="n">
+        <v/>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1957,57 +1955,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1797.56</v>
+        <v>1742.66</v>
       </c>
       <c r="C18" t="n">
-        <v>1810.33</v>
+        <v>1760.21</v>
       </c>
       <c r="D18" t="n">
-        <v>1756.71</v>
+        <v>1721.3</v>
       </c>
       <c r="E18" t="n">
-        <v>1768.51</v>
+        <v>1744.48</v>
       </c>
       <c r="F18" t="n">
-        <v>-29.06</v>
+        <v>1.81</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>53.62</v>
+        <v>38.91</v>
       </c>
       <c r="I18" t="n">
-        <v>1628.42</v>
+        <v>1640.94</v>
       </c>
       <c r="J18" t="n">
-        <v>1706.19</v>
+        <v>1669.37</v>
       </c>
       <c r="K18" t="n">
-        <v>1747.3</v>
+        <v>1707.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1788.41</v>
+        <v>1745.03</v>
       </c>
       <c r="M18" t="n">
-        <v>1847.85</v>
+        <v>1778.16</v>
       </c>
       <c r="N18" t="n">
-        <v>1907.29</v>
+        <v>1811.29</v>
       </c>
       <c r="O18" t="n">
-        <v>1930.06</v>
+        <v>1853.82</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2039,57 +2037,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1768.39</v>
+        <v>1744.47</v>
       </c>
       <c r="C19" t="n">
-        <v>1782.86</v>
+        <v>1809.76</v>
       </c>
       <c r="D19" t="n">
-        <v>1711.9</v>
+        <v>1736.72</v>
       </c>
       <c r="E19" t="n">
-        <v>1742.68</v>
+        <v>1795.69</v>
       </c>
       <c r="F19" t="n">
-        <v>-25.83</v>
+        <v>51.21</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.0294</v>
       </c>
       <c r="H19" t="n">
-        <v>70.95999999999999</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1703.1</v>
+        <v>1682.39</v>
       </c>
       <c r="J19" t="n">
-        <v>1707.39</v>
+        <v>1707.44</v>
       </c>
       <c r="K19" t="n">
-        <v>1741.7</v>
+        <v>1725.03</v>
       </c>
       <c r="L19" t="n">
-        <v>1776.02</v>
+        <v>1742.62</v>
       </c>
       <c r="M19" t="n">
-        <v>1795.32</v>
+        <v>1763.94</v>
       </c>
       <c r="N19" t="n">
-        <v>1814.62</v>
+        <v>1785.26</v>
       </c>
       <c r="O19" t="n">
-        <v>1863.95</v>
+        <v>1799.11</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2097,83 +2095,83 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1742.66</v>
+        <v>1795.82</v>
       </c>
       <c r="C20" t="n">
-        <v>1760.21</v>
+        <v>1827.83</v>
       </c>
       <c r="D20" t="n">
-        <v>1721.3</v>
+        <v>1786.3</v>
       </c>
       <c r="E20" t="n">
-        <v>1744.48</v>
+        <v>1788.1</v>
       </c>
       <c r="F20" t="n">
-        <v>1.81</v>
+        <v>-7.59</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.001</v>
+        <v>-0.0042</v>
       </c>
       <c r="H20" t="n">
-        <v>38.91</v>
+        <v>41.54</v>
       </c>
       <c r="I20" t="n">
-        <v>1640.94</v>
+        <v>1663.69</v>
       </c>
       <c r="J20" t="n">
-        <v>1669.37</v>
+        <v>1733.88</v>
       </c>
       <c r="K20" t="n">
-        <v>1707.2</v>
+        <v>1759.18</v>
       </c>
       <c r="L20" t="n">
-        <v>1745.03</v>
+        <v>1784.47</v>
       </c>
       <c r="M20" t="n">
-        <v>1778.16</v>
+        <v>1832.21</v>
       </c>
       <c r="N20" t="n">
-        <v>1811.29</v>
+        <v>1879.95</v>
       </c>
       <c r="O20" t="n">
-        <v>1853.82</v>
+        <v>1882.79</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2184,9 +2182,9 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2212,50 +2210,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1744.47</v>
+        <v>1787.57</v>
       </c>
       <c r="C21" t="n">
-        <v>1809.76</v>
+        <v>1824.98</v>
       </c>
       <c r="D21" t="n">
-        <v>1736.72</v>
+        <v>1779.64</v>
       </c>
       <c r="E21" t="n">
-        <v>1795.69</v>
+        <v>1805.79</v>
       </c>
       <c r="F21" t="n">
-        <v>51.21</v>
+        <v>17.69</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0294</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>73.04000000000001</v>
+        <v>45.34</v>
       </c>
       <c r="I21" t="n">
-        <v>1682.39</v>
+        <v>1744.76</v>
       </c>
       <c r="J21" t="n">
-        <v>1707.44</v>
+        <v>1737.08</v>
       </c>
       <c r="K21" t="n">
-        <v>1725.03</v>
+        <v>1767.33</v>
       </c>
       <c r="L21" t="n">
-        <v>1742.62</v>
+        <v>1797.58</v>
       </c>
       <c r="M21" t="n">
-        <v>1763.94</v>
+        <v>1808.87</v>
       </c>
       <c r="N21" t="n">
-        <v>1785.26</v>
+        <v>1820.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1799.11</v>
+        <v>1869.37</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,90 +2271,98 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1795.82</v>
+        <v>1805.76</v>
       </c>
       <c r="C22" t="n">
-        <v>1827.83</v>
+        <v>1842.46</v>
       </c>
       <c r="D22" t="n">
-        <v>1786.3</v>
+        <v>1749.35</v>
       </c>
       <c r="E22" t="n">
-        <v>1788.1</v>
+        <v>1773.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.59</v>
+        <v>-32.29</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0179</v>
       </c>
       <c r="H22" t="n">
-        <v>41.54</v>
+        <v>93.11</v>
       </c>
       <c r="I22" t="n">
-        <v>1663.69</v>
+        <v>1734.29</v>
       </c>
       <c r="J22" t="n">
-        <v>1733.88</v>
+        <v>1762.18</v>
       </c>
       <c r="K22" t="n">
-        <v>1759.18</v>
+        <v>1783.12</v>
       </c>
       <c r="L22" t="n">
-        <v>1784.47</v>
+        <v>1804.05</v>
       </c>
       <c r="M22" t="n">
-        <v>1832.21</v>
+        <v>1828.46</v>
       </c>
       <c r="N22" t="n">
-        <v>1879.95</v>
+        <v>1852.87</v>
       </c>
       <c r="O22" t="n">
-        <v>1882.79</v>
+        <v>1870.32</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2371,57 +2377,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1787.57</v>
+        <v>1773.47</v>
       </c>
       <c r="C23" t="n">
-        <v>1824.98</v>
+        <v>1894.06</v>
       </c>
       <c r="D23" t="n">
-        <v>1779.64</v>
+        <v>1772.02</v>
       </c>
       <c r="E23" t="n">
-        <v>1805.79</v>
+        <v>1889.48</v>
       </c>
       <c r="F23" t="n">
-        <v>17.69</v>
+        <v>115.98</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0654</v>
       </c>
       <c r="H23" t="n">
-        <v>45.34</v>
+        <v>122.04</v>
       </c>
       <c r="I23" t="n">
-        <v>1744.76</v>
+        <v>1656.24</v>
       </c>
       <c r="J23" t="n">
-        <v>1737.08</v>
+        <v>1669.19</v>
       </c>
       <c r="K23" t="n">
-        <v>1767.33</v>
+        <v>1726.95</v>
       </c>
       <c r="L23" t="n">
-        <v>1797.58</v>
+        <v>1784.7</v>
       </c>
       <c r="M23" t="n">
-        <v>1808.87</v>
+        <v>1820.05</v>
       </c>
       <c r="N23" t="n">
-        <v>1820.15</v>
+        <v>1855.41</v>
       </c>
       <c r="O23" t="n">
-        <v>1869.37</v>
+        <v>1935.56</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2439,14 +2445,14 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2455,83 +2461,75 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1805.76</v>
+        <v>1889.5</v>
       </c>
       <c r="C24" t="n">
-        <v>1842.46</v>
+        <v>1944.16</v>
       </c>
       <c r="D24" t="n">
-        <v>1749.35</v>
+        <v>1863.64</v>
       </c>
       <c r="E24" t="n">
-        <v>1773.5</v>
+        <v>1916.94</v>
       </c>
       <c r="F24" t="n">
-        <v>-32.29</v>
+        <v>27.46</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0145</v>
       </c>
       <c r="H24" t="n">
-        <v>93.11</v>
+        <v>80.53</v>
       </c>
       <c r="I24" t="n">
-        <v>1734.29</v>
+        <v>1649.97</v>
       </c>
       <c r="J24" t="n">
-        <v>1762.18</v>
+        <v>1795.66</v>
       </c>
       <c r="K24" t="n">
-        <v>1783.12</v>
+        <v>1828.46</v>
       </c>
       <c r="L24" t="n">
-        <v>1804.05</v>
+        <v>1861.26</v>
       </c>
       <c r="M24" t="n">
-        <v>1828.46</v>
+        <v>1950.5</v>
       </c>
       <c r="N24" t="n">
-        <v>1852.87</v>
+        <v>2039.74</v>
       </c>
       <c r="O24" t="n">
-        <v>1870.32</v>
+        <v>2016.11</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2543,59 +2541,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1773.47</v>
+        <v>1916.98</v>
       </c>
       <c r="C25" t="n">
-        <v>1894.06</v>
+        <v>1927.09</v>
       </c>
       <c r="D25" t="n">
-        <v>1772.02</v>
+        <v>1856.78</v>
       </c>
       <c r="E25" t="n">
-        <v>1889.48</v>
+        <v>1863.19</v>
       </c>
       <c r="F25" t="n">
-        <v>115.98</v>
+        <v>-53.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0654</v>
+        <v>-0.028</v>
       </c>
       <c r="H25" t="n">
-        <v>122.04</v>
+        <v>70.31</v>
       </c>
       <c r="I25" t="n">
-        <v>1656.24</v>
+        <v>1783.11</v>
       </c>
       <c r="J25" t="n">
-        <v>1669.19</v>
+        <v>1842.94</v>
       </c>
       <c r="K25" t="n">
-        <v>1726.95</v>
+        <v>1876.68</v>
       </c>
       <c r="L25" t="n">
-        <v>1784.7</v>
+        <v>1910.42</v>
       </c>
       <c r="M25" t="n">
-        <v>1820.05</v>
+        <v>1957.21</v>
       </c>
       <c r="N25" t="n">
-        <v>1855.41</v>
+        <v>2003.99</v>
       </c>
       <c r="O25" t="n">
-        <v>1935.56</v>
+        <v>2024.69</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2603,24 +2597,22 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2629,55 +2621,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1889.5</v>
+        <v>1863.22</v>
       </c>
       <c r="C26" t="n">
-        <v>1944.16</v>
+        <v>1869.07</v>
       </c>
       <c r="D26" t="n">
-        <v>1863.64</v>
+        <v>1803.05</v>
       </c>
       <c r="E26" t="n">
-        <v>1916.94</v>
+        <v>1840.99</v>
       </c>
       <c r="F26" t="n">
-        <v>27.46</v>
+        <v>-22.21</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0145</v>
+        <v>-0.0119</v>
       </c>
       <c r="H26" t="n">
-        <v>80.53</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>1649.97</v>
+        <v>1786.47</v>
       </c>
       <c r="J26" t="n">
-        <v>1795.66</v>
+        <v>1778.51</v>
       </c>
       <c r="K26" t="n">
-        <v>1828.46</v>
+        <v>1828.04</v>
       </c>
       <c r="L26" t="n">
-        <v>1861.26</v>
+        <v>1877.56</v>
       </c>
       <c r="M26" t="n">
-        <v>1950.5</v>
+        <v>1898.35</v>
       </c>
       <c r="N26" t="n">
-        <v>2039.74</v>
+        <v>1919.13</v>
       </c>
       <c r="O26" t="n">
-        <v>2016.11</v>
+        <v>1997.4</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2685,19 +2681,19 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2709,55 +2705,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1916.98</v>
+        <v>1841.1</v>
       </c>
       <c r="C27" t="n">
-        <v>1927.09</v>
+        <v>1864.13</v>
       </c>
       <c r="D27" t="n">
-        <v>1856.78</v>
+        <v>1836.61</v>
       </c>
       <c r="E27" t="n">
-        <v>1863.19</v>
+        <v>1861.39</v>
       </c>
       <c r="F27" t="n">
-        <v>-53.75</v>
+        <v>20.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.028</v>
+        <v>0.0111</v>
       </c>
       <c r="H27" t="n">
-        <v>70.31</v>
+        <v>27.52</v>
       </c>
       <c r="I27" t="n">
-        <v>1783.11</v>
+        <v>1737.04</v>
       </c>
       <c r="J27" t="n">
-        <v>1842.94</v>
+        <v>1777.44</v>
       </c>
       <c r="K27" t="n">
-        <v>1876.68</v>
+        <v>1807.98</v>
       </c>
       <c r="L27" t="n">
-        <v>1910.42</v>
+        <v>1838.52</v>
       </c>
       <c r="M27" t="n">
-        <v>1957.21</v>
+        <v>1873.99</v>
       </c>
       <c r="N27" t="n">
-        <v>2003.99</v>
+        <v>1909.47</v>
       </c>
       <c r="O27" t="n">
-        <v>2024.69</v>
+        <v>1935.08</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2765,19 +2765,19 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2791,57 +2791,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1863.22</v>
+        <v>1861.42</v>
       </c>
       <c r="C28" t="n">
-        <v>1869.07</v>
+        <v>1877.03</v>
       </c>
       <c r="D28" t="n">
-        <v>1803.05</v>
+        <v>1852.73</v>
       </c>
       <c r="E28" t="n">
-        <v>1840.99</v>
+        <v>1871.51</v>
       </c>
       <c r="F28" t="n">
-        <v>-22.21</v>
+        <v>10.12</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0054</v>
       </c>
       <c r="H28" t="n">
-        <v>66.01000000000001</v>
+        <v>24.3</v>
       </c>
       <c r="I28" t="n">
-        <v>1786.47</v>
+        <v>1809.09</v>
       </c>
       <c r="J28" t="n">
-        <v>1778.51</v>
+        <v>1839.38</v>
       </c>
       <c r="K28" t="n">
-        <v>1828.04</v>
+        <v>1847.63</v>
       </c>
       <c r="L28" t="n">
-        <v>1877.56</v>
+        <v>1855.88</v>
       </c>
       <c r="M28" t="n">
-        <v>1898.35</v>
+        <v>1875.15</v>
       </c>
       <c r="N28" t="n">
-        <v>1919.13</v>
+        <v>1894.43</v>
       </c>
       <c r="O28" t="n">
-        <v>1997.4</v>
+        <v>1891.66</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2849,19 +2849,19 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2873,68 +2873,68 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1841.1</v>
+        <v>1871.28</v>
       </c>
       <c r="C29" t="n">
-        <v>1864.13</v>
+        <v>1916.24</v>
       </c>
       <c r="D29" t="n">
-        <v>1836.61</v>
+        <v>1842.82</v>
       </c>
       <c r="E29" t="n">
-        <v>1861.39</v>
+        <v>1903.76</v>
       </c>
       <c r="F29" t="n">
-        <v>20.4</v>
+        <v>32.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0172</v>
       </c>
       <c r="H29" t="n">
-        <v>27.52</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>1737.04</v>
+        <v>1828.42</v>
       </c>
       <c r="J29" t="n">
-        <v>1777.44</v>
+        <v>1850.52</v>
       </c>
       <c r="K29" t="n">
-        <v>1807.98</v>
+        <v>1859.36</v>
       </c>
       <c r="L29" t="n">
-        <v>1838.52</v>
+        <v>1868.19</v>
       </c>
       <c r="M29" t="n">
-        <v>1873.99</v>
+        <v>1883.66</v>
       </c>
       <c r="N29" t="n">
-        <v>1909.47</v>
+        <v>1899.13</v>
       </c>
       <c r="O29" t="n">
-        <v>1935.08</v>
+        <v>1901.34</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
@@ -2943,14 +2943,18 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
@@ -2966,50 +2970,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1861.42</v>
+        <v>1903.69</v>
       </c>
       <c r="C30" t="n">
-        <v>1877.03</v>
+        <v>1949.55</v>
       </c>
       <c r="D30" t="n">
-        <v>1852.73</v>
+        <v>1900.07</v>
       </c>
       <c r="E30" t="n">
-        <v>1871.51</v>
+        <v>1928.38</v>
       </c>
       <c r="F30" t="n">
-        <v>10.12</v>
+        <v>24.62</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0129</v>
       </c>
       <c r="H30" t="n">
-        <v>24.3</v>
+        <v>49.48</v>
       </c>
       <c r="I30" t="n">
-        <v>1809.09</v>
+        <v>1769.39</v>
       </c>
       <c r="J30" t="n">
-        <v>1839.38</v>
+        <v>1842.45</v>
       </c>
       <c r="K30" t="n">
-        <v>1847.63</v>
+        <v>1867.05</v>
       </c>
       <c r="L30" t="n">
-        <v>1855.88</v>
+        <v>1891.64</v>
       </c>
       <c r="M30" t="n">
-        <v>1875.15</v>
+        <v>1940.47</v>
       </c>
       <c r="N30" t="n">
-        <v>1894.43</v>
+        <v>1989.3</v>
       </c>
       <c r="O30" t="n">
-        <v>1891.66</v>
+        <v>1989.67</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3046,171 +3050,161 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1871.28</v>
+        <v>1928.2</v>
       </c>
       <c r="C31" t="n">
-        <v>1916.24</v>
+        <v>1955.15</v>
       </c>
       <c r="D31" t="n">
-        <v>1842.82</v>
+        <v>1909.61</v>
       </c>
       <c r="E31" t="n">
-        <v>1903.76</v>
+        <v>1933.49</v>
       </c>
       <c r="F31" t="n">
-        <v>32.25</v>
+        <v>5.11</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0026</v>
       </c>
       <c r="H31" t="n">
-        <v>73.43000000000001</v>
+        <v>45.54</v>
       </c>
       <c r="I31" t="n">
-        <v>1828.42</v>
+        <v>1850.58</v>
       </c>
       <c r="J31" t="n">
-        <v>1850.52</v>
+        <v>1880.69</v>
       </c>
       <c r="K31" t="n">
-        <v>1859.36</v>
+        <v>1903.64</v>
       </c>
       <c r="L31" t="n">
-        <v>1868.19</v>
+        <v>1926.6</v>
       </c>
       <c r="M31" t="n">
-        <v>1883.66</v>
+        <v>1953.12</v>
       </c>
       <c r="N31" t="n">
-        <v>1899.13</v>
+        <v>1979.65</v>
       </c>
       <c r="O31" t="n">
-        <v>1901.34</v>
+        <v>1999.03</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1903.69</v>
+        <v>1933.47</v>
       </c>
       <c r="C32" t="n">
-        <v>1949.55</v>
+        <v>1940.28</v>
       </c>
       <c r="D32" t="n">
-        <v>1900.07</v>
+        <v>1868.52</v>
       </c>
       <c r="E32" t="n">
-        <v>1928.38</v>
+        <v>1877.1</v>
       </c>
       <c r="F32" t="n">
-        <v>24.62</v>
+        <v>-56.39</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0292</v>
       </c>
       <c r="H32" t="n">
-        <v>49.48</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>1769.39</v>
+        <v>1864.07</v>
       </c>
       <c r="J32" t="n">
-        <v>1842.45</v>
+        <v>1888.51</v>
       </c>
       <c r="K32" t="n">
-        <v>1867.05</v>
+        <v>1910.72</v>
       </c>
       <c r="L32" t="n">
-        <v>1891.64</v>
+        <v>1932.93</v>
       </c>
       <c r="M32" t="n">
-        <v>1940.47</v>
+        <v>1956.26</v>
       </c>
       <c r="N32" t="n">
-        <v>1989.3</v>
+        <v>1979.58</v>
       </c>
       <c r="O32" t="n">
-        <v>1989.67</v>
+        <v>2000.68</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -3218,50 +3212,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1928.2</v>
+        <v>1877.1</v>
       </c>
       <c r="C33" t="n">
-        <v>1955.15</v>
+        <v>1907.54</v>
       </c>
       <c r="D33" t="n">
-        <v>1909.61</v>
+        <v>1846.82</v>
       </c>
       <c r="E33" t="n">
-        <v>1933.49</v>
+        <v>1860.18</v>
       </c>
       <c r="F33" t="n">
-        <v>5.11</v>
+        <v>-16.92</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>45.54</v>
+        <v>60.72</v>
       </c>
       <c r="I33" t="n">
-        <v>1850.58</v>
+        <v>1796.76</v>
       </c>
       <c r="J33" t="n">
-        <v>1880.69</v>
+        <v>1791.69</v>
       </c>
       <c r="K33" t="n">
-        <v>1903.64</v>
+        <v>1841.22</v>
       </c>
       <c r="L33" t="n">
-        <v>1926.6</v>
+        <v>1890.75</v>
       </c>
       <c r="M33" t="n">
-        <v>1953.12</v>
+        <v>1912.98</v>
       </c>
       <c r="N33" t="n">
-        <v>1979.65</v>
+        <v>1935.21</v>
       </c>
       <c r="O33" t="n">
-        <v>1999.03</v>
+        <v>2012.05</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3269,18 +3263,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3288,9 +3282,9 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3298,67 +3292,63 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1933.47</v>
+        <v>1860.18</v>
       </c>
       <c r="C34" t="n">
-        <v>1940.28</v>
+        <v>1875.14</v>
       </c>
       <c r="D34" t="n">
-        <v>1868.52</v>
+        <v>1849.83</v>
       </c>
       <c r="E34" t="n">
-        <v>1877.1</v>
+        <v>1873.22</v>
       </c>
       <c r="F34" t="n">
-        <v>-56.39</v>
+        <v>13.05</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0292</v>
+        <v>0.007</v>
       </c>
       <c r="H34" t="n">
-        <v>71.76000000000001</v>
+        <v>25.32</v>
       </c>
       <c r="I34" t="n">
-        <v>1864.07</v>
+        <v>1786.1</v>
       </c>
       <c r="J34" t="n">
-        <v>1888.51</v>
+        <v>1790.95</v>
       </c>
       <c r="K34" t="n">
-        <v>1910.72</v>
+        <v>1829.82</v>
       </c>
       <c r="L34" t="n">
-        <v>1932.93</v>
+        <v>1868.68</v>
       </c>
       <c r="M34" t="n">
-        <v>1956.26</v>
+        <v>1890.54</v>
       </c>
       <c r="N34" t="n">
-        <v>1979.58</v>
+        <v>1912.39</v>
       </c>
       <c r="O34" t="n">
-        <v>2000.68</v>
+        <v>1968.26</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3375,55 +3365,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1877.1</v>
+        <v>1873.24</v>
       </c>
       <c r="C35" t="n">
-        <v>1907.54</v>
+        <v>1963.25</v>
       </c>
       <c r="D35" t="n">
-        <v>1846.82</v>
+        <v>1872.38</v>
       </c>
       <c r="E35" t="n">
-        <v>1860.18</v>
+        <v>1953.41</v>
       </c>
       <c r="F35" t="n">
-        <v>-16.92</v>
+        <v>80.19</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.0428</v>
       </c>
       <c r="H35" t="n">
-        <v>60.72</v>
+        <v>90.86</v>
       </c>
       <c r="I35" t="n">
-        <v>1796.76</v>
+        <v>1824.51</v>
       </c>
       <c r="J35" t="n">
-        <v>1791.69</v>
+        <v>1853.27</v>
       </c>
       <c r="K35" t="n">
-        <v>1841.22</v>
+        <v>1860.56</v>
       </c>
       <c r="L35" t="n">
-        <v>1890.75</v>
+        <v>1867.85</v>
       </c>
       <c r="M35" t="n">
-        <v>1912.98</v>
+        <v>1885.88</v>
       </c>
       <c r="N35" t="n">
-        <v>1935.21</v>
+        <v>1903.91</v>
       </c>
       <c r="O35" t="n">
-        <v>2012.05</v>
+        <v>1900.46</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3431,28 +3425,32 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3460,63 +3458,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1860.18</v>
+        <v>1953.41</v>
       </c>
       <c r="C36" t="n">
-        <v>1875.14</v>
+        <v>1976.46</v>
       </c>
       <c r="D36" t="n">
-        <v>1849.83</v>
+        <v>1882.42</v>
       </c>
       <c r="E36" t="n">
-        <v>1873.22</v>
+        <v>1890.61</v>
       </c>
       <c r="F36" t="n">
-        <v>13.05</v>
+        <v>-62.8</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.007</v>
+        <v>-0.0321</v>
       </c>
       <c r="H36" t="n">
-        <v>25.32</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>1786.1</v>
+        <v>1781.52</v>
       </c>
       <c r="J36" t="n">
-        <v>1790.95</v>
+        <v>1880.35</v>
       </c>
       <c r="K36" t="n">
-        <v>1829.82</v>
+        <v>1907.98</v>
       </c>
       <c r="L36" t="n">
-        <v>1868.68</v>
+        <v>1935.61</v>
       </c>
       <c r="M36" t="n">
-        <v>1890.54</v>
+        <v>1998.84</v>
       </c>
       <c r="N36" t="n">
-        <v>1912.39</v>
+        <v>2062.07</v>
       </c>
       <c r="O36" t="n">
-        <v>1968.26</v>
+        <v>2054.11</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3528,64 +3530,64 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1873.24</v>
+        <v>1890.63</v>
       </c>
       <c r="C37" t="n">
-        <v>1963.25</v>
+        <v>1926.5</v>
       </c>
       <c r="D37" t="n">
-        <v>1872.38</v>
+        <v>1856.34</v>
       </c>
       <c r="E37" t="n">
-        <v>1953.41</v>
+        <v>1919.95</v>
       </c>
       <c r="F37" t="n">
-        <v>80.19</v>
+        <v>29.33</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0428</v>
+        <v>0.0155</v>
       </c>
       <c r="H37" t="n">
-        <v>90.86</v>
+        <v>70.16</v>
       </c>
       <c r="I37" t="n">
-        <v>1824.51</v>
+        <v>1788.38</v>
       </c>
       <c r="J37" t="n">
-        <v>1853.27</v>
+        <v>1777.16</v>
       </c>
       <c r="K37" t="n">
-        <v>1860.56</v>
+        <v>1843.59</v>
       </c>
       <c r="L37" t="n">
-        <v>1867.85</v>
+        <v>1910.03</v>
       </c>
       <c r="M37" t="n">
-        <v>1885.88</v>
+        <v>1937.63</v>
       </c>
       <c r="N37" t="n">
-        <v>1903.91</v>
+        <v>1965.24</v>
       </c>
       <c r="O37" t="n">
-        <v>1900.46</v>
+        <v>2070.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3598,95 +3600,91 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1953.41</v>
+        <v>1919.99</v>
       </c>
       <c r="C38" t="n">
-        <v>1976.46</v>
+        <v>1929.9</v>
       </c>
       <c r="D38" t="n">
-        <v>1882.42</v>
+        <v>1873.62</v>
       </c>
       <c r="E38" t="n">
-        <v>1890.61</v>
+        <v>1908.52</v>
       </c>
       <c r="F38" t="n">
-        <v>-62.8</v>
+        <v>-11.43</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.006</v>
       </c>
       <c r="H38" t="n">
-        <v>94.04000000000001</v>
+        <v>56.28</v>
       </c>
       <c r="I38" t="n">
-        <v>1781.52</v>
+        <v>1786.18</v>
       </c>
       <c r="J38" t="n">
-        <v>1880.35</v>
+        <v>1864.05</v>
       </c>
       <c r="K38" t="n">
-        <v>1907.98</v>
+        <v>1884.87</v>
       </c>
       <c r="L38" t="n">
-        <v>1935.61</v>
+        <v>1905.69</v>
       </c>
       <c r="M38" t="n">
-        <v>1998.84</v>
+        <v>1955.03</v>
       </c>
       <c r="N38" t="n">
-        <v>2062.07</v>
+        <v>2004.37</v>
       </c>
       <c r="O38" t="n">
-        <v>2054.11</v>
+        <v>1996.67</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q38" s="6" t="n">
+        <v/>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3712,50 +3710,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1890.63</v>
+        <v>1908.59</v>
       </c>
       <c r="C39" t="n">
-        <v>1926.5</v>
+        <v>1934.58</v>
       </c>
       <c r="D39" t="n">
-        <v>1856.34</v>
+        <v>1892.2</v>
       </c>
       <c r="E39" t="n">
-        <v>1919.95</v>
+        <v>1917.37</v>
       </c>
       <c r="F39" t="n">
-        <v>29.33</v>
+        <v>8.85</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0155</v>
+        <v>0.0046</v>
       </c>
       <c r="H39" t="n">
-        <v>70.16</v>
+        <v>42.38</v>
       </c>
       <c r="I39" t="n">
-        <v>1788.38</v>
+        <v>1817.34</v>
       </c>
       <c r="J39" t="n">
-        <v>1777.16</v>
+        <v>1855.62</v>
       </c>
       <c r="K39" t="n">
-        <v>1843.59</v>
+        <v>1880.38</v>
       </c>
       <c r="L39" t="n">
-        <v>1910.03</v>
+        <v>1905.14</v>
       </c>
       <c r="M39" t="n">
-        <v>1937.63</v>
+        <v>1936.66</v>
       </c>
       <c r="N39" t="n">
-        <v>1965.24</v>
+        <v>1968.18</v>
       </c>
       <c r="O39" t="n">
-        <v>2070.5</v>
+        <v>1986.18</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3785,74 +3783,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1919.99</v>
+        <v>1917.14</v>
       </c>
       <c r="C40" t="n">
-        <v>1929.9</v>
+        <v>1933.78</v>
       </c>
       <c r="D40" t="n">
-        <v>1873.62</v>
+        <v>1847.47</v>
       </c>
       <c r="E40" t="n">
-        <v>1908.52</v>
+        <v>1860.35</v>
       </c>
       <c r="F40" t="n">
-        <v>-11.43</v>
+        <v>-57.03</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.006</v>
+        <v>-0.0297</v>
       </c>
       <c r="H40" t="n">
-        <v>56.28</v>
+        <v>86.31</v>
       </c>
       <c r="I40" t="n">
-        <v>1786.18</v>
+        <v>1849.82</v>
       </c>
       <c r="J40" t="n">
-        <v>1864.05</v>
+        <v>1876.99</v>
       </c>
       <c r="K40" t="n">
-        <v>1884.87</v>
+        <v>1896.18</v>
       </c>
       <c r="L40" t="n">
-        <v>1905.69</v>
+        <v>1915.38</v>
       </c>
       <c r="M40" t="n">
-        <v>1955.03</v>
+        <v>1938.56</v>
       </c>
       <c r="N40" t="n">
-        <v>2004.37</v>
+        <v>1961.75</v>
       </c>
       <c r="O40" t="n">
-        <v>1996.67</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>1976.96</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3864,64 +3862,60 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1908.59</v>
+        <v>1860.37</v>
       </c>
       <c r="C41" t="n">
-        <v>1934.58</v>
+        <v>1873.17</v>
       </c>
       <c r="D41" t="n">
-        <v>1892.2</v>
+        <v>1821.49</v>
       </c>
       <c r="E41" t="n">
-        <v>1917.37</v>
+        <v>1843.42</v>
       </c>
       <c r="F41" t="n">
-        <v>8.85</v>
+        <v>-16.93</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0091</v>
       </c>
       <c r="H41" t="n">
-        <v>42.38</v>
+        <v>51.69</v>
       </c>
       <c r="I41" t="n">
-        <v>1817.34</v>
+        <v>1761.16</v>
       </c>
       <c r="J41" t="n">
-        <v>1855.62</v>
+        <v>1758.9</v>
       </c>
       <c r="K41" t="n">
-        <v>1880.38</v>
+        <v>1817.19</v>
       </c>
       <c r="L41" t="n">
-        <v>1905.14</v>
+        <v>1875.48</v>
       </c>
       <c r="M41" t="n">
-        <v>1936.66</v>
+        <v>1903.5</v>
       </c>
       <c r="N41" t="n">
-        <v>1968.18</v>
+        <v>1931.52</v>
       </c>
       <c r="O41" t="n">
-        <v>1986.18</v>
+        <v>2020.09</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3929,12 +3923,14 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3946,9 +3942,9 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
@@ -3956,77 +3952,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1917.14</v>
+        <v>1843.42</v>
       </c>
       <c r="C42" t="n">
-        <v>1933.78</v>
+        <v>1895.77</v>
       </c>
       <c r="D42" t="n">
-        <v>1847.47</v>
+        <v>1842.15</v>
       </c>
       <c r="E42" t="n">
-        <v>1860.35</v>
+        <v>1882.52</v>
       </c>
       <c r="F42" t="n">
-        <v>-57.03</v>
+        <v>39.1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0297</v>
+        <v>0.0212</v>
       </c>
       <c r="H42" t="n">
-        <v>86.31</v>
+        <v>53.61</v>
       </c>
       <c r="I42" t="n">
-        <v>1849.82</v>
+        <v>1769.8</v>
       </c>
       <c r="J42" t="n">
-        <v>1876.99</v>
+        <v>1789.78</v>
       </c>
       <c r="K42" t="n">
-        <v>1896.18</v>
+        <v>1817.57</v>
       </c>
       <c r="L42" t="n">
-        <v>1915.38</v>
+        <v>1845.37</v>
       </c>
       <c r="M42" t="n">
-        <v>1938.56</v>
+        <v>1869.26</v>
       </c>
       <c r="N42" t="n">
-        <v>1961.75</v>
+        <v>1893.15</v>
       </c>
       <c r="O42" t="n">
-        <v>1976.96</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
+        <v>1924.86</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4035,61 +4029,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1860.37</v>
+        <v>1882.78</v>
       </c>
       <c r="C43" t="n">
-        <v>1873.17</v>
+        <v>1883.44</v>
       </c>
       <c r="D43" t="n">
-        <v>1821.49</v>
+        <v>1827.7</v>
       </c>
       <c r="E43" t="n">
-        <v>1843.42</v>
+        <v>1858.26</v>
       </c>
       <c r="F43" t="n">
-        <v>-16.93</v>
+        <v>-24.27</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0091</v>
+        <v>-0.0129</v>
       </c>
       <c r="H43" t="n">
-        <v>51.69</v>
+        <v>55.74</v>
       </c>
       <c r="I43" t="n">
-        <v>1761.16</v>
+        <v>1788.54</v>
       </c>
       <c r="J43" t="n">
-        <v>1758.9</v>
+        <v>1835.69</v>
       </c>
       <c r="K43" t="n">
-        <v>1817.19</v>
+        <v>1855.72</v>
       </c>
       <c r="L43" t="n">
-        <v>1875.48</v>
+        <v>1875.74</v>
       </c>
       <c r="M43" t="n">
-        <v>1903.5</v>
+        <v>1909.33</v>
       </c>
       <c r="N43" t="n">
-        <v>1931.52</v>
+        <v>1942.91</v>
       </c>
       <c r="O43" t="n">
-        <v>2020.09</v>
+        <v>1949.38</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
@@ -4120,50 +4120,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1843.42</v>
+        <v>1858.22</v>
       </c>
       <c r="C44" t="n">
-        <v>1895.77</v>
+        <v>1879.54</v>
       </c>
       <c r="D44" t="n">
-        <v>1842.15</v>
+        <v>1847.17</v>
       </c>
       <c r="E44" t="n">
-        <v>1882.52</v>
+        <v>1868.39</v>
       </c>
       <c r="F44" t="n">
-        <v>39.1</v>
+        <v>10.13</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0212</v>
+        <v>0.0055</v>
       </c>
       <c r="H44" t="n">
-        <v>53.61</v>
+        <v>32.36</v>
       </c>
       <c r="I44" t="n">
-        <v>1769.8</v>
+        <v>1771.96</v>
       </c>
       <c r="J44" t="n">
-        <v>1789.78</v>
+        <v>1803.86</v>
       </c>
       <c r="K44" t="n">
-        <v>1817.57</v>
+        <v>1830.39</v>
       </c>
       <c r="L44" t="n">
-        <v>1845.37</v>
+        <v>1856.91</v>
       </c>
       <c r="M44" t="n">
-        <v>1869.26</v>
+        <v>1886.13</v>
       </c>
       <c r="N44" t="n">
-        <v>1893.15</v>
+        <v>1915.34</v>
       </c>
       <c r="O44" t="n">
-        <v>1924.86</v>
+        <v>1939.18</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4176,18 +4176,14 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4199,88 +4195,90 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1882.78</v>
+        <v>1868.49</v>
       </c>
       <c r="C45" t="n">
-        <v>1883.44</v>
+        <v>1922.64</v>
       </c>
       <c r="D45" t="n">
-        <v>1827.7</v>
+        <v>1854.34</v>
       </c>
       <c r="E45" t="n">
-        <v>1858.26</v>
+        <v>1906.53</v>
       </c>
       <c r="F45" t="n">
-        <v>-24.27</v>
+        <v>38.14</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0204</v>
       </c>
       <c r="H45" t="n">
-        <v>55.74</v>
+        <v>68.3</v>
       </c>
       <c r="I45" t="n">
-        <v>1788.54</v>
+        <v>1814.81</v>
       </c>
       <c r="J45" t="n">
-        <v>1835.69</v>
+        <v>1838.54</v>
       </c>
       <c r="K45" t="n">
-        <v>1855.72</v>
+        <v>1852.2</v>
       </c>
       <c r="L45" t="n">
-        <v>1875.74</v>
+        <v>1865.87</v>
       </c>
       <c r="M45" t="n">
-        <v>1909.33</v>
+        <v>1884.57</v>
       </c>
       <c r="N45" t="n">
-        <v>1942.91</v>
+        <v>1903.26</v>
       </c>
       <c r="O45" t="n">
-        <v>1949.38</v>
+        <v>1911.9</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr"/>
@@ -4288,50 +4286,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1858.22</v>
+        <v>1906.44</v>
       </c>
       <c r="C46" t="n">
-        <v>1879.54</v>
+        <v>1917.7</v>
       </c>
       <c r="D46" t="n">
-        <v>1847.17</v>
+        <v>1890.96</v>
       </c>
       <c r="E46" t="n">
-        <v>1868.39</v>
+        <v>1902.06</v>
       </c>
       <c r="F46" t="n">
-        <v>10.13</v>
+        <v>-4.47</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.0023</v>
       </c>
       <c r="H46" t="n">
-        <v>32.36</v>
+        <v>26.74</v>
       </c>
       <c r="I46" t="n">
-        <v>1771.96</v>
+        <v>1786.04</v>
       </c>
       <c r="J46" t="n">
-        <v>1803.86</v>
+        <v>1847.24</v>
       </c>
       <c r="K46" t="n">
-        <v>1830.39</v>
+        <v>1872.38</v>
       </c>
       <c r="L46" t="n">
-        <v>1856.91</v>
+        <v>1897.51</v>
       </c>
       <c r="M46" t="n">
-        <v>1886.13</v>
+        <v>1940.68</v>
       </c>
       <c r="N46" t="n">
-        <v>1915.34</v>
+        <v>1983.84</v>
       </c>
       <c r="O46" t="n">
-        <v>1939.18</v>
+        <v>1990.94</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4356,9 +4354,9 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -4370,50 +4368,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1868.49</v>
+        <v>1902.14</v>
       </c>
       <c r="C47" t="n">
-        <v>1922.64</v>
+        <v>1937.17</v>
       </c>
       <c r="D47" t="n">
-        <v>1854.34</v>
+        <v>1893.08</v>
       </c>
       <c r="E47" t="n">
-        <v>1906.53</v>
+        <v>1913.28</v>
       </c>
       <c r="F47" t="n">
-        <v>38.14</v>
+        <v>11.22</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.0059</v>
       </c>
       <c r="H47" t="n">
-        <v>68.3</v>
+        <v>44.08</v>
       </c>
       <c r="I47" t="n">
-        <v>1814.81</v>
+        <v>1864.23</v>
       </c>
       <c r="J47" t="n">
-        <v>1838.54</v>
+        <v>1874.18</v>
       </c>
       <c r="K47" t="n">
-        <v>1852.2</v>
+        <v>1888.69</v>
       </c>
       <c r="L47" t="n">
-        <v>1865.87</v>
+        <v>1903.19</v>
       </c>
       <c r="M47" t="n">
-        <v>1884.57</v>
+        <v>1915.43</v>
       </c>
       <c r="N47" t="n">
-        <v>1903.26</v>
+        <v>1927.66</v>
       </c>
       <c r="O47" t="n">
-        <v>1911.9</v>
+        <v>1944.44</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4431,18 +4429,16 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4454,50 +4450,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1906.44</v>
+        <v>1913.32</v>
       </c>
       <c r="C48" t="n">
-        <v>1917.7</v>
+        <v>1924.62</v>
       </c>
       <c r="D48" t="n">
-        <v>1890.96</v>
+        <v>1911.48</v>
       </c>
       <c r="E48" t="n">
-        <v>1902.06</v>
+        <v>1915.53</v>
       </c>
       <c r="F48" t="n">
-        <v>-4.47</v>
+        <v>2.25</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0012</v>
       </c>
       <c r="H48" t="n">
-        <v>26.74</v>
+        <v>13.13</v>
       </c>
       <c r="I48" t="n">
-        <v>1786.04</v>
+        <v>1849</v>
       </c>
       <c r="J48" t="n">
-        <v>1847.24</v>
+        <v>1868.27</v>
       </c>
       <c r="K48" t="n">
-        <v>1872.38</v>
+        <v>1891.24</v>
       </c>
       <c r="L48" t="n">
-        <v>1897.51</v>
+        <v>1914.2</v>
       </c>
       <c r="M48" t="n">
-        <v>1940.68</v>
+        <v>1935.32</v>
       </c>
       <c r="N48" t="n">
-        <v>1983.84</v>
+        <v>1956.44</v>
       </c>
       <c r="O48" t="n">
-        <v>1990.94</v>
+        <v>1981.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4529,57 +4525,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1902.14</v>
+        <v>1915.46</v>
       </c>
       <c r="C49" t="n">
-        <v>1937.17</v>
+        <v>1935.53</v>
       </c>
       <c r="D49" t="n">
-        <v>1893.08</v>
+        <v>1907.03</v>
       </c>
       <c r="E49" t="n">
-        <v>1913.28</v>
+        <v>1908.68</v>
       </c>
       <c r="F49" t="n">
-        <v>11.22</v>
+        <v>-6.85</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0036</v>
       </c>
       <c r="H49" t="n">
-        <v>44.08</v>
+        <v>28.5</v>
       </c>
       <c r="I49" t="n">
-        <v>1864.23</v>
+        <v>1898.35</v>
       </c>
       <c r="J49" t="n">
-        <v>1874.18</v>
+        <v>1901.14</v>
       </c>
       <c r="K49" t="n">
-        <v>1888.69</v>
+        <v>1908.97</v>
       </c>
       <c r="L49" t="n">
-        <v>1903.19</v>
+        <v>1916.79</v>
       </c>
       <c r="M49" t="n">
-        <v>1915.43</v>
+        <v>1922.1</v>
       </c>
       <c r="N49" t="n">
-        <v>1927.66</v>
+        <v>1927.4</v>
       </c>
       <c r="O49" t="n">
-        <v>1944.44</v>
+        <v>1937.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4587,17 +4583,19 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U49" s="8" t="inlineStr">
@@ -4613,72 +4611,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1913.32</v>
+        <v>1908.72</v>
       </c>
       <c r="C50" t="n">
-        <v>1924.62</v>
+        <v>1928.99</v>
       </c>
       <c r="D50" t="n">
-        <v>1911.48</v>
+        <v>1866.79</v>
       </c>
       <c r="E50" t="n">
-        <v>1915.53</v>
+        <v>1871.28</v>
       </c>
       <c r="F50" t="n">
-        <v>2.25</v>
+        <v>-37.4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0196</v>
       </c>
       <c r="H50" t="n">
-        <v>13.13</v>
+        <v>62.2</v>
       </c>
       <c r="I50" t="n">
-        <v>1849</v>
+        <v>1878.52</v>
       </c>
       <c r="J50" t="n">
-        <v>1868.27</v>
+        <v>1873.88</v>
       </c>
       <c r="K50" t="n">
-        <v>1891.24</v>
+        <v>1894.43</v>
       </c>
       <c r="L50" t="n">
-        <v>1914.2</v>
+        <v>1914.98</v>
       </c>
       <c r="M50" t="n">
-        <v>1935.32</v>
+        <v>1922.93</v>
       </c>
       <c r="N50" t="n">
-        <v>1956.44</v>
+        <v>1930.89</v>
       </c>
       <c r="O50" t="n">
-        <v>1981.25</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+        <v>1964.03</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4686,64 +4696,60 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1915.46</v>
+        <v>1871.26</v>
       </c>
       <c r="C51" t="n">
-        <v>1935.53</v>
+        <v>1895.75</v>
       </c>
       <c r="D51" t="n">
-        <v>1907.03</v>
+        <v>1852.84</v>
       </c>
       <c r="E51" t="n">
-        <v>1908.68</v>
+        <v>1881.37</v>
       </c>
       <c r="F51" t="n">
-        <v>-6.85</v>
+        <v>10.09</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.0054</v>
       </c>
       <c r="H51" t="n">
-        <v>28.5</v>
+        <v>42.91</v>
       </c>
       <c r="I51" t="n">
-        <v>1898.35</v>
+        <v>1804.59</v>
       </c>
       <c r="J51" t="n">
-        <v>1901.14</v>
+        <v>1795.77</v>
       </c>
       <c r="K51" t="n">
-        <v>1908.97</v>
+        <v>1840.18</v>
       </c>
       <c r="L51" t="n">
-        <v>1916.79</v>
+        <v>1884.59</v>
       </c>
       <c r="M51" t="n">
-        <v>1922.1</v>
+        <v>1902.38</v>
       </c>
       <c r="N51" t="n">
-        <v>1927.4</v>
+        <v>1920.18</v>
       </c>
       <c r="O51" t="n">
-        <v>1937.75</v>
+        <v>1991.2</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4751,113 +4757,101 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1908.72</v>
+        <v>1881.37</v>
       </c>
       <c r="C52" t="n">
-        <v>1928.99</v>
+        <v>1921.78</v>
       </c>
       <c r="D52" t="n">
-        <v>1866.79</v>
+        <v>1873.35</v>
       </c>
       <c r="E52" t="n">
-        <v>1871.28</v>
+        <v>1878.14</v>
       </c>
       <c r="F52" t="n">
-        <v>-37.4</v>
+        <v>-3.24</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.0017</v>
       </c>
       <c r="H52" t="n">
-        <v>62.2</v>
+        <v>48.43</v>
       </c>
       <c r="I52" t="n">
-        <v>1878.52</v>
+        <v>1809.93</v>
       </c>
       <c r="J52" t="n">
-        <v>1873.88</v>
+        <v>1842</v>
       </c>
       <c r="K52" t="n">
-        <v>1894.43</v>
+        <v>1859.92</v>
       </c>
       <c r="L52" t="n">
-        <v>1914.98</v>
+        <v>1877.83</v>
       </c>
       <c r="M52" t="n">
-        <v>1922.93</v>
+        <v>1902.83</v>
       </c>
       <c r="N52" t="n">
-        <v>1930.89</v>
+        <v>1927.82</v>
       </c>
       <c r="O52" t="n">
-        <v>1964.03</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
+        <v>1938.66</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4869,55 +4863,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1871.26</v>
+        <v>1878.19</v>
       </c>
       <c r="C53" t="n">
-        <v>1895.75</v>
+        <v>1898.23</v>
       </c>
       <c r="D53" t="n">
-        <v>1852.84</v>
+        <v>1861.92</v>
       </c>
       <c r="E53" t="n">
-        <v>1881.37</v>
+        <v>1883.99</v>
       </c>
       <c r="F53" t="n">
-        <v>10.09</v>
+        <v>5.86</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0031</v>
       </c>
       <c r="H53" t="n">
-        <v>42.91</v>
+        <v>36.3</v>
       </c>
       <c r="I53" t="n">
-        <v>1804.59</v>
+        <v>1824.92</v>
       </c>
       <c r="J53" t="n">
-        <v>1795.77</v>
+        <v>1819.99</v>
       </c>
       <c r="K53" t="n">
-        <v>1840.18</v>
+        <v>1853.92</v>
       </c>
       <c r="L53" t="n">
-        <v>1884.59</v>
+        <v>1887.85</v>
       </c>
       <c r="M53" t="n">
-        <v>1902.38</v>
+        <v>1902.35</v>
       </c>
       <c r="N53" t="n">
-        <v>1920.18</v>
+        <v>1916.85</v>
       </c>
       <c r="O53" t="n">
-        <v>1991.2</v>
+        <v>1970.2</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4956,50 +4954,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1881.37</v>
+        <v>1884.02</v>
       </c>
       <c r="C54" t="n">
-        <v>1921.78</v>
+        <v>1889.27</v>
       </c>
       <c r="D54" t="n">
-        <v>1873.35</v>
+        <v>1862.56</v>
       </c>
       <c r="E54" t="n">
-        <v>1878.14</v>
+        <v>1880.65</v>
       </c>
       <c r="F54" t="n">
-        <v>-3.24</v>
+        <v>-3.34</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0018</v>
       </c>
       <c r="H54" t="n">
-        <v>48.43</v>
+        <v>26.71</v>
       </c>
       <c r="I54" t="n">
-        <v>1809.93</v>
+        <v>1825.62</v>
       </c>
       <c r="J54" t="n">
-        <v>1842</v>
+        <v>1849.65</v>
       </c>
       <c r="K54" t="n">
-        <v>1859.92</v>
+        <v>1865.84</v>
       </c>
       <c r="L54" t="n">
-        <v>1877.83</v>
+        <v>1882.03</v>
       </c>
       <c r="M54" t="n">
-        <v>1902.83</v>
+        <v>1902.14</v>
       </c>
       <c r="N54" t="n">
-        <v>1927.82</v>
+        <v>1922.26</v>
       </c>
       <c r="O54" t="n">
-        <v>1938.66</v>
+        <v>1934.53</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5007,19 +5005,19 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5033,57 +5031,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1878.19</v>
+        <v>1880.61</v>
       </c>
       <c r="C55" t="n">
-        <v>1898.23</v>
+        <v>1884.72</v>
       </c>
       <c r="D55" t="n">
-        <v>1861.92</v>
+        <v>1874.33</v>
       </c>
       <c r="E55" t="n">
-        <v>1883.99</v>
+        <v>1880.91</v>
       </c>
       <c r="F55" t="n">
-        <v>5.86</v>
+        <v>0.26</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0031</v>
+        <v>0.0001</v>
       </c>
       <c r="H55" t="n">
-        <v>36.3</v>
+        <v>10.39</v>
       </c>
       <c r="I55" t="n">
-        <v>1824.92</v>
+        <v>1835.86</v>
       </c>
       <c r="J55" t="n">
-        <v>1819.99</v>
+        <v>1856.31</v>
       </c>
       <c r="K55" t="n">
-        <v>1853.92</v>
+        <v>1867.3</v>
       </c>
       <c r="L55" t="n">
-        <v>1887.85</v>
+        <v>1878.28</v>
       </c>
       <c r="M55" t="n">
-        <v>1902.35</v>
+        <v>1894</v>
       </c>
       <c r="N55" t="n">
-        <v>1916.85</v>
+        <v>1909.72</v>
       </c>
       <c r="O55" t="n">
-        <v>1970.2</v>
+        <v>1915.98</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5094,9 +5092,9 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5115,76 +5113,80 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1884.02</v>
+        <v>1880.89</v>
       </c>
       <c r="C56" t="n">
-        <v>1889.27</v>
+        <v>1889.61</v>
       </c>
       <c r="D56" t="n">
-        <v>1862.56</v>
+        <v>1867.89</v>
       </c>
       <c r="E56" t="n">
-        <v>1880.65</v>
+        <v>1873.94</v>
       </c>
       <c r="F56" t="n">
-        <v>-3.34</v>
+        <v>-6.97</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0018</v>
+        <v>-0.0037</v>
       </c>
       <c r="H56" t="n">
-        <v>26.71</v>
+        <v>21.71</v>
       </c>
       <c r="I56" t="n">
-        <v>1825.62</v>
+        <v>1863.94</v>
       </c>
       <c r="J56" t="n">
-        <v>1849.65</v>
+        <v>1871.21</v>
       </c>
       <c r="K56" t="n">
-        <v>1865.84</v>
+        <v>1875.71</v>
       </c>
       <c r="L56" t="n">
-        <v>1882.03</v>
+        <v>1880.22</v>
       </c>
       <c r="M56" t="n">
-        <v>1902.14</v>
+        <v>1886.1</v>
       </c>
       <c r="N56" t="n">
-        <v>1922.26</v>
+        <v>1891.99</v>
       </c>
       <c r="O56" t="n">
-        <v>1934.53</v>
+        <v>1895.11</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5206,50 +5208,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1880.61</v>
+        <v>1873.97</v>
       </c>
       <c r="C57" t="n">
-        <v>1884.72</v>
+        <v>1916.66</v>
       </c>
       <c r="D57" t="n">
-        <v>1874.33</v>
+        <v>1870.75</v>
       </c>
       <c r="E57" t="n">
-        <v>1880.91</v>
+        <v>1912.2</v>
       </c>
       <c r="F57" t="n">
-        <v>0.26</v>
+        <v>38.26</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0204</v>
       </c>
       <c r="H57" t="n">
-        <v>10.39</v>
+        <v>45.91</v>
       </c>
       <c r="I57" t="n">
-        <v>1835.86</v>
+        <v>1846.18</v>
       </c>
       <c r="J57" t="n">
-        <v>1856.31</v>
+        <v>1849.83</v>
       </c>
       <c r="K57" t="n">
-        <v>1867.3</v>
+        <v>1863.09</v>
       </c>
       <c r="L57" t="n">
-        <v>1878.28</v>
+        <v>1876.35</v>
       </c>
       <c r="M57" t="n">
-        <v>1894</v>
+        <v>1884.8</v>
       </c>
       <c r="N57" t="n">
-        <v>1909.72</v>
+        <v>1893.25</v>
       </c>
       <c r="O57" t="n">
-        <v>1915.98</v>
+        <v>1911.32</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5262,99 +5264,97 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1880.89</v>
+        <v>1912.21</v>
       </c>
       <c r="C58" t="n">
-        <v>1889.61</v>
+        <v>1920.52</v>
       </c>
       <c r="D58" t="n">
-        <v>1867.89</v>
+        <v>1884.48</v>
       </c>
       <c r="E58" t="n">
-        <v>1873.94</v>
+        <v>1916.46</v>
       </c>
       <c r="F58" t="n">
-        <v>-6.97</v>
+        <v>4.26</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0022</v>
       </c>
       <c r="H58" t="n">
-        <v>21.71</v>
+        <v>36.05</v>
       </c>
       <c r="I58" t="n">
-        <v>1863.94</v>
+        <v>1824.84</v>
       </c>
       <c r="J58" t="n">
-        <v>1871.21</v>
+        <v>1875.54</v>
       </c>
       <c r="K58" t="n">
-        <v>1875.71</v>
+        <v>1889.25</v>
       </c>
       <c r="L58" t="n">
-        <v>1880.22</v>
+        <v>1902.95</v>
       </c>
       <c r="M58" t="n">
-        <v>1886.1</v>
+        <v>1935.16</v>
       </c>
       <c r="N58" t="n">
-        <v>1891.99</v>
+        <v>1967.36</v>
       </c>
       <c r="O58" t="n">
-        <v>1895.11</v>
+        <v>1962.57</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5362,64 +5362,60 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1873.97</v>
+        <v>1916.43</v>
       </c>
       <c r="C59" t="n">
-        <v>1916.66</v>
+        <v>2327.7</v>
       </c>
       <c r="D59" t="n">
-        <v>1870.75</v>
+        <v>1905.08</v>
       </c>
       <c r="E59" t="n">
-        <v>1912.2</v>
+        <v>2251.46</v>
       </c>
       <c r="F59" t="n">
-        <v>38.26</v>
+        <v>335</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.1748</v>
       </c>
       <c r="H59" t="n">
-        <v>45.91</v>
+        <v>422.62</v>
       </c>
       <c r="I59" t="n">
-        <v>1846.18</v>
+        <v>1848.43</v>
       </c>
       <c r="J59" t="n">
-        <v>1849.83</v>
+        <v>1887.39</v>
       </c>
       <c r="K59" t="n">
-        <v>1863.09</v>
+        <v>1898.44</v>
       </c>
       <c r="L59" t="n">
-        <v>1876.35</v>
+        <v>1909.48</v>
       </c>
       <c r="M59" t="n">
-        <v>1884.8</v>
+        <v>1934.48</v>
       </c>
       <c r="N59" t="n">
-        <v>1893.25</v>
+        <v>1959.48</v>
       </c>
       <c r="O59" t="n">
-        <v>1911.32</v>
+        <v>1956.57</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5442,12 +5438,12 @@
       </c>
       <c r="U59" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W59" s="9" t="inlineStr">
@@ -5460,50 +5456,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1912.21</v>
+        <v>2251.44</v>
       </c>
       <c r="C60" t="n">
-        <v>1920.52</v>
+        <v>2357.23</v>
       </c>
       <c r="D60" t="n">
-        <v>1884.48</v>
+        <v>2222.57</v>
       </c>
       <c r="E60" t="n">
-        <v>1916.46</v>
+        <v>2326.38</v>
       </c>
       <c r="F60" t="n">
-        <v>4.26</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.0333</v>
       </c>
       <c r="H60" t="n">
-        <v>36.05</v>
+        <v>134.65</v>
       </c>
       <c r="I60" t="n">
-        <v>1824.84</v>
+        <v>1482.46</v>
       </c>
       <c r="J60" t="n">
-        <v>1875.54</v>
+        <v>1896.37</v>
       </c>
       <c r="K60" t="n">
-        <v>1889.25</v>
+        <v>2040.15</v>
       </c>
       <c r="L60" t="n">
-        <v>1902.95</v>
+        <v>2183.92</v>
       </c>
       <c r="M60" t="n">
-        <v>1935.16</v>
+        <v>2462.77</v>
       </c>
       <c r="N60" t="n">
-        <v>1967.36</v>
+        <v>2741.61</v>
       </c>
       <c r="O60" t="n">
-        <v>1962.57</v>
+        <v>2750.32</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5511,18 +5507,18 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5540,50 +5536,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1916.43</v>
+        <v>2326.38</v>
       </c>
       <c r="C61" t="n">
-        <v>2327.7</v>
+        <v>2545.88</v>
       </c>
       <c r="D61" t="n">
-        <v>1905.08</v>
+        <v>2324.71</v>
       </c>
       <c r="E61" t="n">
-        <v>2251.46</v>
+        <v>2515.28</v>
       </c>
       <c r="F61" t="n">
-        <v>335</v>
+        <v>188.9</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.1748</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>422.62</v>
+        <v>221.17</v>
       </c>
       <c r="I61" t="n">
-        <v>1848.43</v>
+        <v>2087.92</v>
       </c>
       <c r="J61" t="n">
-        <v>1887.39</v>
+        <v>2209.97</v>
       </c>
       <c r="K61" t="n">
-        <v>1898.44</v>
+        <v>2259.06</v>
       </c>
       <c r="L61" t="n">
-        <v>1909.48</v>
+        <v>2308.14</v>
       </c>
       <c r="M61" t="n">
-        <v>1934.48</v>
+        <v>2393.71</v>
       </c>
       <c r="N61" t="n">
-        <v>1959.48</v>
+        <v>2479.28</v>
       </c>
       <c r="O61" t="n">
-        <v>1956.57</v>
+        <v>2491.88</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5606,12 +5602,12 @@
       </c>
       <c r="U61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W61" s="9" t="inlineStr">
@@ -5624,50 +5620,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2251.44</v>
+        <v>2515.39</v>
       </c>
       <c r="C62" t="n">
-        <v>2357.23</v>
+        <v>2528.9</v>
       </c>
       <c r="D62" t="n">
-        <v>2222.57</v>
+        <v>2389.9</v>
       </c>
       <c r="E62" t="n">
-        <v>2326.38</v>
+        <v>2424.25</v>
       </c>
       <c r="F62" t="n">
-        <v>74.93000000000001</v>
+        <v>-91.03</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0333</v>
+        <v>-0.0362</v>
       </c>
       <c r="H62" t="n">
-        <v>134.65</v>
+        <v>138.99</v>
       </c>
       <c r="I62" t="n">
-        <v>1482.46</v>
+        <v>2103.54</v>
       </c>
       <c r="J62" t="n">
-        <v>1896.37</v>
+        <v>2334.1</v>
       </c>
       <c r="K62" t="n">
-        <v>2040.15</v>
+        <v>2404.7</v>
       </c>
       <c r="L62" t="n">
-        <v>2183.92</v>
+        <v>2475.29</v>
       </c>
       <c r="M62" t="n">
-        <v>2462.77</v>
+        <v>2625.87</v>
       </c>
       <c r="N62" t="n">
-        <v>2741.61</v>
+        <v>2776.45</v>
       </c>
       <c r="O62" t="n">
-        <v>2750.32</v>
+        <v>2767.05</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5675,19 +5671,19 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
@@ -5699,55 +5695,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2326.38</v>
+        <v>2424.22</v>
       </c>
       <c r="C63" t="n">
-        <v>2545.88</v>
+        <v>2483.93</v>
       </c>
       <c r="D63" t="n">
-        <v>2324.71</v>
+        <v>2357.14</v>
       </c>
       <c r="E63" t="n">
-        <v>2515.28</v>
+        <v>2463.82</v>
       </c>
       <c r="F63" t="n">
-        <v>188.9</v>
+        <v>39.56</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0163</v>
       </c>
       <c r="H63" t="n">
-        <v>221.17</v>
+        <v>126.79</v>
       </c>
       <c r="I63" t="n">
-        <v>2087.92</v>
+        <v>2250.91</v>
       </c>
       <c r="J63" t="n">
-        <v>2209.97</v>
+        <v>2267.68</v>
       </c>
       <c r="K63" t="n">
-        <v>2259.06</v>
+        <v>2354.75</v>
       </c>
       <c r="L63" t="n">
-        <v>2308.14</v>
+        <v>2441.83</v>
       </c>
       <c r="M63" t="n">
-        <v>2393.71</v>
+        <v>2493.75</v>
       </c>
       <c r="N63" t="n">
-        <v>2479.28</v>
+        <v>2545.67</v>
       </c>
       <c r="O63" t="n">
-        <v>2491.88</v>
+        <v>2667.89</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5760,78 +5760,76 @@
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
       </c>
       <c r="W63" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2515.39</v>
+        <v>2463.64</v>
       </c>
       <c r="C64" t="n">
-        <v>2528.9</v>
+        <v>2531.74</v>
       </c>
       <c r="D64" t="n">
-        <v>2389.9</v>
+        <v>2425.39</v>
       </c>
       <c r="E64" t="n">
-        <v>2424.25</v>
+        <v>2481.83</v>
       </c>
       <c r="F64" t="n">
-        <v>-91.03</v>
+        <v>18.02</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0362</v>
+        <v>0.0073</v>
       </c>
       <c r="H64" t="n">
-        <v>138.99</v>
+        <v>106.36</v>
       </c>
       <c r="I64" t="n">
-        <v>2103.54</v>
+        <v>2230.35</v>
       </c>
       <c r="J64" t="n">
-        <v>2334.1</v>
+        <v>2358.67</v>
       </c>
       <c r="K64" t="n">
-        <v>2404.7</v>
+        <v>2400.42</v>
       </c>
       <c r="L64" t="n">
-        <v>2475.29</v>
+        <v>2442.18</v>
       </c>
       <c r="M64" t="n">
-        <v>2625.87</v>
+        <v>2527.21</v>
       </c>
       <c r="N64" t="n">
-        <v>2776.45</v>
+        <v>2612.25</v>
       </c>
       <c r="O64" t="n">
-        <v>2767.05</v>
+        <v>2610.72</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5839,18 +5837,18 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5863,59 +5861,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2424.22</v>
+        <v>2481.78</v>
       </c>
       <c r="C65" t="n">
-        <v>2483.93</v>
+        <v>2531.08</v>
       </c>
       <c r="D65" t="n">
-        <v>2357.14</v>
+        <v>2416.6</v>
       </c>
       <c r="E65" t="n">
-        <v>2463.82</v>
+        <v>2443.16</v>
       </c>
       <c r="F65" t="n">
-        <v>39.56</v>
+        <v>-38.67</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0163</v>
+        <v>-0.0156</v>
       </c>
       <c r="H65" t="n">
-        <v>126.79</v>
+        <v>114.48</v>
       </c>
       <c r="I65" t="n">
-        <v>2250.91</v>
+        <v>2319.03</v>
       </c>
       <c r="J65" t="n">
-        <v>2267.68</v>
+        <v>2377.11</v>
       </c>
       <c r="K65" t="n">
-        <v>2354.75</v>
+        <v>2428.65</v>
       </c>
       <c r="L65" t="n">
-        <v>2441.83</v>
+        <v>2480.2</v>
       </c>
       <c r="M65" t="n">
-        <v>2493.75</v>
+        <v>2535.01</v>
       </c>
       <c r="N65" t="n">
-        <v>2545.67</v>
+        <v>2589.82</v>
       </c>
       <c r="O65" t="n">
-        <v>2667.89</v>
+        <v>2638.1</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5923,12 +5917,14 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S65" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">
@@ -5947,57 +5943,57 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2463.64</v>
+        <v>2442.49</v>
       </c>
       <c r="C66" t="n">
-        <v>2531.74</v>
+        <v>2514.67</v>
       </c>
       <c r="D66" t="n">
-        <v>2425.39</v>
+        <v>2432.51</v>
       </c>
       <c r="E66" t="n">
-        <v>2481.83</v>
+        <v>2506.26</v>
       </c>
       <c r="F66" t="n">
-        <v>18.02</v>
+        <v>63.1</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0073</v>
+        <v>0.0258</v>
       </c>
       <c r="H66" t="n">
-        <v>106.36</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>2230.35</v>
+        <v>2302.12</v>
       </c>
       <c r="J66" t="n">
-        <v>2358.67</v>
+        <v>2313.34</v>
       </c>
       <c r="K66" t="n">
-        <v>2400.42</v>
+        <v>2385.92</v>
       </c>
       <c r="L66" t="n">
-        <v>2442.18</v>
+        <v>2458.5</v>
       </c>
       <c r="M66" t="n">
-        <v>2527.21</v>
+        <v>2500.4</v>
       </c>
       <c r="N66" t="n">
-        <v>2612.25</v>
+        <v>2542.3</v>
       </c>
       <c r="O66" t="n">
-        <v>2610.72</v>
+        <v>2645.57</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6010,12 +6006,12 @@
       </c>
       <c r="S66" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T66" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U66" s="8" t="n">
@@ -6029,55 +6025,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2481.78</v>
+        <v>2506.24</v>
       </c>
       <c r="C67" t="n">
-        <v>2531.08</v>
+        <v>2564.27</v>
       </c>
       <c r="D67" t="n">
-        <v>2416.6</v>
+        <v>2481.94</v>
       </c>
       <c r="E67" t="n">
-        <v>2443.16</v>
+        <v>2510.41</v>
       </c>
       <c r="F67" t="n">
-        <v>-38.67</v>
+        <v>4.15</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0017</v>
       </c>
       <c r="H67" t="n">
-        <v>114.48</v>
+        <v>82.33</v>
       </c>
       <c r="I67" t="n">
-        <v>2319.03</v>
+        <v>2350.36</v>
       </c>
       <c r="J67" t="n">
-        <v>2377.11</v>
+        <v>2440.44</v>
       </c>
       <c r="K67" t="n">
-        <v>2428.65</v>
+        <v>2465.18</v>
       </c>
       <c r="L67" t="n">
-        <v>2480.2</v>
+        <v>2489.93</v>
       </c>
       <c r="M67" t="n">
-        <v>2535.01</v>
+        <v>2547.34</v>
       </c>
       <c r="N67" t="n">
-        <v>2589.82</v>
+        <v>2604.75</v>
       </c>
       <c r="O67" t="n">
-        <v>2638.1</v>
+        <v>2596.82</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
@@ -6085,18 +6085,18 @@
       <c r="Q67" s="6" t="n">
         <v/>
       </c>
-      <c r="R67" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S67" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T67" s="8" t="n">
-        <v/>
+      <c r="R67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S67" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U67" s="8" t="n">
         <v/>
@@ -6109,79 +6109,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2442.49</v>
+        <v>2510.67</v>
       </c>
       <c r="C68" t="n">
-        <v>2514.67</v>
+        <v>2534.01</v>
       </c>
       <c r="D68" t="n">
-        <v>2432.51</v>
+        <v>2408.72</v>
       </c>
       <c r="E68" t="n">
-        <v>2506.26</v>
+        <v>2442.54</v>
       </c>
       <c r="F68" t="n">
-        <v>63.1</v>
+        <v>-67.87</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.0258</v>
+        <v>-0.027</v>
       </c>
       <c r="H68" t="n">
-        <v>82.15000000000001</v>
+        <v>125.29</v>
       </c>
       <c r="I68" t="n">
-        <v>2302.12</v>
+        <v>2399.62</v>
       </c>
       <c r="J68" t="n">
-        <v>2313.34</v>
+        <v>2421.73</v>
       </c>
       <c r="K68" t="n">
-        <v>2385.92</v>
+        <v>2469.25</v>
       </c>
       <c r="L68" t="n">
-        <v>2458.5</v>
+        <v>2516.76</v>
       </c>
       <c r="M68" t="n">
-        <v>2500.4</v>
+        <v>2551.57</v>
       </c>
       <c r="N68" t="n">
-        <v>2542.3</v>
+        <v>2586.39</v>
       </c>
       <c r="O68" t="n">
-        <v>2645.57</v>
+        <v>2646.6</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
       </c>
-      <c r="Q68" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R68" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S68" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="inlineStr">
+      <c r="Q68" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="n">
+        <v/>
+      </c>
       <c r="U68" s="8" t="n">
         <v/>
       </c>
@@ -6195,57 +6193,57 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2506.24</v>
+        <v>2442.56</v>
       </c>
       <c r="C69" t="n">
-        <v>2564.27</v>
+        <v>2459.63</v>
       </c>
       <c r="D69" t="n">
-        <v>2481.94</v>
+        <v>2430.81</v>
       </c>
       <c r="E69" t="n">
-        <v>2510.41</v>
+        <v>2457.69</v>
       </c>
       <c r="F69" t="n">
-        <v>4.15</v>
+        <v>15.15</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0062</v>
       </c>
       <c r="H69" t="n">
-        <v>82.33</v>
+        <v>28.82</v>
       </c>
       <c r="I69" t="n">
-        <v>2350.36</v>
+        <v>2283.43</v>
       </c>
       <c r="J69" t="n">
-        <v>2440.44</v>
+        <v>2302.83</v>
       </c>
       <c r="K69" t="n">
-        <v>2465.18</v>
+        <v>2379.89</v>
       </c>
       <c r="L69" t="n">
-        <v>2489.93</v>
+        <v>2456.95</v>
       </c>
       <c r="M69" t="n">
-        <v>2547.34</v>
+        <v>2505.18</v>
       </c>
       <c r="N69" t="n">
-        <v>2604.75</v>
+        <v>2553.41</v>
       </c>
       <c r="O69" t="n">
-        <v>2596.82</v>
+        <v>2659.3</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
@@ -6261,10 +6259,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T69" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T69" s="8" t="n">
+        <v/>
       </c>
       <c r="U69" s="8" t="n">
         <v/>
@@ -6277,62 +6273,68 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr"/>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2510.67</v>
+        <v>2457.69</v>
       </c>
       <c r="C70" t="n">
-        <v>2534.01</v>
+        <v>2532.96</v>
       </c>
       <c r="D70" t="n">
-        <v>2408.72</v>
+        <v>2389.47</v>
       </c>
       <c r="E70" t="n">
-        <v>2442.54</v>
+        <v>2417.94</v>
       </c>
       <c r="F70" t="n">
-        <v>-67.87</v>
+        <v>-39.75</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.027</v>
+        <v>-0.0162</v>
       </c>
       <c r="H70" t="n">
-        <v>125.29</v>
+        <v>143.49</v>
       </c>
       <c r="I70" t="n">
-        <v>2399.62</v>
+        <v>2401.99</v>
       </c>
       <c r="J70" t="n">
-        <v>2421.73</v>
+        <v>2435.1</v>
       </c>
       <c r="K70" t="n">
-        <v>2469.25</v>
+        <v>2443.28</v>
       </c>
       <c r="L70" t="n">
-        <v>2516.76</v>
+        <v>2451.45</v>
       </c>
       <c r="M70" t="n">
-        <v>2551.57</v>
+        <v>2472.1</v>
       </c>
       <c r="N70" t="n">
-        <v>2586.39</v>
+        <v>2492.74</v>
       </c>
       <c r="O70" t="n">
-        <v>2646.6</v>
-      </c>
-      <c r="P70" s="6" t="n">
-        <v/>
+        <v>2488.45</v>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
@@ -6345,73 +6347,79 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T70" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U70" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V70" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W70" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="T70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W70" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2442.56</v>
+        <v>2417.9</v>
       </c>
       <c r="C71" t="n">
-        <v>2459.63</v>
+        <v>2488.92</v>
       </c>
       <c r="D71" t="n">
-        <v>2430.81</v>
+        <v>2401.81</v>
       </c>
       <c r="E71" t="n">
-        <v>2457.69</v>
+        <v>2466.82</v>
       </c>
       <c r="F71" t="n">
-        <v>15.15</v>
+        <v>48.88</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0062</v>
+        <v>0.0202</v>
       </c>
       <c r="H71" t="n">
-        <v>28.82</v>
+        <v>87.11</v>
       </c>
       <c r="I71" t="n">
-        <v>2283.43</v>
+        <v>2245.98</v>
       </c>
       <c r="J71" t="n">
-        <v>2302.83</v>
+        <v>2252.81</v>
       </c>
       <c r="K71" t="n">
-        <v>2379.89</v>
+        <v>2346.19</v>
       </c>
       <c r="L71" t="n">
-        <v>2456.95</v>
+        <v>2439.58</v>
       </c>
       <c r="M71" t="n">
-        <v>2505.18</v>
+        <v>2489.68</v>
       </c>
       <c r="N71" t="n">
-        <v>2553.41</v>
+        <v>2539.79</v>
       </c>
       <c r="O71" t="n">
-        <v>2659.3</v>
+        <v>2676.45</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6424,11 +6432,13 @@
       </c>
       <c r="S71" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U71" s="8" t="n">
         <v/>
@@ -6436,158 +6446,146 @@
       <c r="V71" s="8" t="n">
         <v/>
       </c>
-      <c r="W71" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W71" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2457.69</v>
+        <v>2466.58</v>
       </c>
       <c r="C72" t="n">
-        <v>2532.96</v>
+        <v>2484.4</v>
       </c>
       <c r="D72" t="n">
-        <v>2389.47</v>
+        <v>2383.8</v>
       </c>
       <c r="E72" t="n">
-        <v>2417.94</v>
+        <v>2417.84</v>
       </c>
       <c r="F72" t="n">
-        <v>-39.75</v>
+        <v>-48.98</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0199</v>
       </c>
       <c r="H72" t="n">
-        <v>143.49</v>
+        <v>100.6</v>
       </c>
       <c r="I72" t="n">
-        <v>2401.99</v>
+        <v>2314.69</v>
       </c>
       <c r="J72" t="n">
-        <v>2435.1</v>
+        <v>2390.43</v>
       </c>
       <c r="K72" t="n">
-        <v>2443.28</v>
+        <v>2423.26</v>
       </c>
       <c r="L72" t="n">
-        <v>2451.45</v>
+        <v>2456.09</v>
       </c>
       <c r="M72" t="n">
-        <v>2472.1</v>
+        <v>2510.38</v>
       </c>
       <c r="N72" t="n">
-        <v>2492.74</v>
+        <v>2564.66</v>
       </c>
       <c r="O72" t="n">
-        <v>2488.45</v>
-      </c>
-      <c r="P72" s="6" t="inlineStr">
+        <v>2576.04</v>
+      </c>
+      <c r="P72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R72" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q72" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R72" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T72" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U72" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V72" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T72" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U72" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V72" s="8" t="n">
+        <v/>
       </c>
       <c r="W72" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2417.9</v>
+        <v>2417.83</v>
       </c>
       <c r="C73" t="n">
-        <v>2488.92</v>
+        <v>2427.4</v>
       </c>
       <c r="D73" t="n">
-        <v>2401.81</v>
+        <v>2356.19</v>
       </c>
       <c r="E73" t="n">
-        <v>2466.82</v>
+        <v>2391.5</v>
       </c>
       <c r="F73" t="n">
-        <v>48.88</v>
+        <v>-26.34</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0202</v>
+        <v>-0.0109</v>
       </c>
       <c r="H73" t="n">
-        <v>87.11</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>2245.98</v>
+        <v>2283.21</v>
       </c>
       <c r="J73" t="n">
-        <v>2252.81</v>
+        <v>2309.12</v>
       </c>
       <c r="K73" t="n">
-        <v>2346.19</v>
+        <v>2367.54</v>
       </c>
       <c r="L73" t="n">
-        <v>2439.58</v>
+        <v>2425.97</v>
       </c>
       <c r="M73" t="n">
-        <v>2489.68</v>
+        <v>2468.14</v>
       </c>
       <c r="N73" t="n">
-        <v>2539.79</v>
+        <v>2510.31</v>
       </c>
       <c r="O73" t="n">
-        <v>2676.45</v>
+        <v>2584.99</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6595,19 +6593,19 @@
       <c r="Q73" s="6" t="n">
         <v/>
       </c>
-      <c r="R73" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S73" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="inlineStr">
+      <c r="R73" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S73" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="n">
+        <v/>
+      </c>
       <c r="U73" s="8" t="n">
         <v/>
       </c>
@@ -6619,90 +6617,88 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2466.58</v>
+        <v>2391.6</v>
       </c>
       <c r="C74" t="n">
-        <v>2484.4</v>
+        <v>2526.95</v>
       </c>
       <c r="D74" t="n">
-        <v>2383.8</v>
+        <v>2370.42</v>
       </c>
       <c r="E74" t="n">
-        <v>2417.84</v>
+        <v>2508.02</v>
       </c>
       <c r="F74" t="n">
-        <v>-48.98</v>
+        <v>116.52</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.0199</v>
+        <v>0.0487</v>
       </c>
       <c r="H74" t="n">
-        <v>100.6</v>
+        <v>156.53</v>
       </c>
       <c r="I74" t="n">
-        <v>2314.69</v>
+        <v>2284.97</v>
       </c>
       <c r="J74" t="n">
-        <v>2390.43</v>
+        <v>2320.14</v>
       </c>
       <c r="K74" t="n">
-        <v>2423.26</v>
+        <v>2355.89</v>
       </c>
       <c r="L74" t="n">
-        <v>2456.09</v>
+        <v>2391.65</v>
       </c>
       <c r="M74" t="n">
-        <v>2510.38</v>
+        <v>2427.11</v>
       </c>
       <c r="N74" t="n">
-        <v>2564.66</v>
+        <v>2462.57</v>
       </c>
       <c r="O74" t="n">
-        <v>2576.04</v>
+        <v>2498.61</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
       </c>
-      <c r="Q74" s="6" t="inlineStr">
+      <c r="Q74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R74" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S74" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R74" s="6" t="inlineStr">
+      <c r="U74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V74" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S74" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U74" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V74" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W74" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W74" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X74" t="inlineStr"/>
@@ -6710,50 +6706,50 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2417.83</v>
+        <v>2508.02</v>
       </c>
       <c r="C75" t="n">
-        <v>2427.4</v>
+        <v>2545.62</v>
       </c>
       <c r="D75" t="n">
-        <v>2356.19</v>
+        <v>2432.35</v>
       </c>
       <c r="E75" t="n">
-        <v>2391.5</v>
+        <v>2456.08</v>
       </c>
       <c r="F75" t="n">
-        <v>-26.34</v>
+        <v>-51.94</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0207</v>
       </c>
       <c r="H75" t="n">
-        <v>71.20999999999999</v>
+        <v>113.27</v>
       </c>
       <c r="I75" t="n">
-        <v>2283.21</v>
+        <v>2213.88</v>
       </c>
       <c r="J75" t="n">
-        <v>2309.12</v>
+        <v>2381.16</v>
       </c>
       <c r="K75" t="n">
-        <v>2367.54</v>
+        <v>2429.75</v>
       </c>
       <c r="L75" t="n">
-        <v>2425.97</v>
+        <v>2478.35</v>
       </c>
       <c r="M75" t="n">
-        <v>2468.14</v>
+        <v>2586.29</v>
       </c>
       <c r="N75" t="n">
-        <v>2510.31</v>
+        <v>2694.22</v>
       </c>
       <c r="O75" t="n">
-        <v>2584.99</v>
+        <v>2683.48</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
@@ -6761,14 +6757,12 @@
       <c r="Q75" s="6" t="n">
         <v/>
       </c>
-      <c r="R75" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R75" s="6" t="n">
+        <v/>
       </c>
       <c r="S75" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T75" s="8" t="n">
@@ -6780,60 +6774,64 @@
       <c r="V75" s="8" t="n">
         <v/>
       </c>
-      <c r="W75" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr"/>
+      <c r="W75" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2391.6</v>
+        <v>2455.99</v>
       </c>
       <c r="C76" t="n">
-        <v>2526.95</v>
+        <v>2492.01</v>
       </c>
       <c r="D76" t="n">
-        <v>2370.42</v>
+        <v>2445.69</v>
       </c>
       <c r="E76" t="n">
-        <v>2508.02</v>
+        <v>2480.74</v>
       </c>
       <c r="F76" t="n">
-        <v>116.52</v>
+        <v>24.66</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.0487</v>
+        <v>0.01</v>
       </c>
       <c r="H76" t="n">
-        <v>156.53</v>
+        <v>46.32</v>
       </c>
       <c r="I76" t="n">
-        <v>2284.97</v>
+        <v>2319.08</v>
       </c>
       <c r="J76" t="n">
-        <v>2320.14</v>
+        <v>2326.35</v>
       </c>
       <c r="K76" t="n">
-        <v>2355.89</v>
+        <v>2399.44</v>
       </c>
       <c r="L76" t="n">
-        <v>2391.65</v>
+        <v>2472.53</v>
       </c>
       <c r="M76" t="n">
-        <v>2427.11</v>
+        <v>2512.71</v>
       </c>
       <c r="N76" t="n">
-        <v>2462.57</v>
+        <v>2552.89</v>
       </c>
       <c r="O76" t="n">
-        <v>2498.61</v>
+        <v>2658.89</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
@@ -6846,78 +6844,76 @@
       </c>
       <c r="S76" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U76" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V76" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U76" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V76" s="8" t="n">
+        <v/>
       </c>
       <c r="W76" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr"/>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2508.02</v>
+        <v>2480.82</v>
       </c>
       <c r="C77" t="n">
-        <v>2545.62</v>
+        <v>2525.32</v>
       </c>
       <c r="D77" t="n">
-        <v>2432.35</v>
+        <v>2468.19</v>
       </c>
       <c r="E77" t="n">
-        <v>2456.08</v>
+        <v>2514.55</v>
       </c>
       <c r="F77" t="n">
-        <v>-51.94</v>
+        <v>33.81</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0207</v>
+        <v>0.0136</v>
       </c>
       <c r="H77" t="n">
-        <v>113.27</v>
+        <v>57.13</v>
       </c>
       <c r="I77" t="n">
-        <v>2213.88</v>
+        <v>2399.37</v>
       </c>
       <c r="J77" t="n">
-        <v>2381.16</v>
+        <v>2440.36</v>
       </c>
       <c r="K77" t="n">
-        <v>2429.75</v>
+        <v>2457.58</v>
       </c>
       <c r="L77" t="n">
-        <v>2478.35</v>
+        <v>2474.79</v>
       </c>
       <c r="M77" t="n">
-        <v>2586.29</v>
+        <v>2503.9</v>
       </c>
       <c r="N77" t="n">
-        <v>2694.22</v>
+        <v>2533</v>
       </c>
       <c r="O77" t="n">
-        <v>2683.48</v>
+        <v>2538.33</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
@@ -6928,13 +6924,15 @@
       <c r="R77" s="6" t="n">
         <v/>
       </c>
-      <c r="S77" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="n">
-        <v/>
+      <c r="S77" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U77" s="8" t="n">
         <v/>
@@ -6947,59 +6945,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2455.99</v>
+        <v>2514.58</v>
       </c>
       <c r="C78" t="n">
-        <v>2492.01</v>
+        <v>2534.86</v>
       </c>
       <c r="D78" t="n">
-        <v>2445.69</v>
+        <v>2466.91</v>
       </c>
       <c r="E78" t="n">
-        <v>2480.74</v>
+        <v>2490.96</v>
       </c>
       <c r="F78" t="n">
-        <v>24.66</v>
+        <v>-23.59</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.01</v>
+        <v>-0.0094</v>
       </c>
       <c r="H78" t="n">
-        <v>46.32</v>
+        <v>67.95</v>
       </c>
       <c r="I78" t="n">
-        <v>2319.08</v>
+        <v>2411.07</v>
       </c>
       <c r="J78" t="n">
-        <v>2326.35</v>
+        <v>2466.32</v>
       </c>
       <c r="K78" t="n">
-        <v>2399.44</v>
+        <v>2485.99</v>
       </c>
       <c r="L78" t="n">
-        <v>2472.53</v>
+        <v>2505.65</v>
       </c>
       <c r="M78" t="n">
-        <v>2512.71</v>
+        <v>2543.11</v>
       </c>
       <c r="N78" t="n">
-        <v>2552.89</v>
+        <v>2580.57</v>
       </c>
       <c r="O78" t="n">
-        <v>2658.89</v>
+        <v>2582.45</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -7007,12 +7001,14 @@
       <c r="Q78" s="6" t="n">
         <v/>
       </c>
-      <c r="R78" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S78" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S78" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T78" s="8" t="n">
@@ -7031,57 +7027,57 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2480.82</v>
+        <v>2490.92</v>
       </c>
       <c r="C79" t="n">
-        <v>2525.32</v>
+        <v>2506.75</v>
       </c>
       <c r="D79" t="n">
-        <v>2468.19</v>
+        <v>2441.33</v>
       </c>
       <c r="E79" t="n">
-        <v>2514.55</v>
+        <v>2484.94</v>
       </c>
       <c r="F79" t="n">
-        <v>33.81</v>
+        <v>-6.02</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0024</v>
       </c>
       <c r="H79" t="n">
-        <v>57.13</v>
+        <v>65.42</v>
       </c>
       <c r="I79" t="n">
-        <v>2399.37</v>
+        <v>2398.96</v>
       </c>
       <c r="J79" t="n">
-        <v>2440.36</v>
+        <v>2418.04</v>
       </c>
       <c r="K79" t="n">
-        <v>2457.58</v>
+        <v>2456.98</v>
       </c>
       <c r="L79" t="n">
-        <v>2474.79</v>
+        <v>2495.92</v>
       </c>
       <c r="M79" t="n">
-        <v>2503.9</v>
+        <v>2524.93</v>
       </c>
       <c r="N79" t="n">
-        <v>2533</v>
+        <v>2553.94</v>
       </c>
       <c r="O79" t="n">
-        <v>2538.33</v>
+        <v>2602.81</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7089,18 +7085,18 @@
       <c r="Q79" s="6" t="n">
         <v/>
       </c>
-      <c r="R79" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S79" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S79" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="n">
+        <v/>
       </c>
       <c r="U79" s="8" t="n">
         <v/>
@@ -7113,55 +7109,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr"/>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2514.58</v>
+        <v>2484.89</v>
       </c>
       <c r="C80" t="n">
-        <v>2534.86</v>
+        <v>2522.37</v>
       </c>
       <c r="D80" t="n">
+        <v>2443.7</v>
+      </c>
+      <c r="E80" t="n">
         <v>2466.91</v>
       </c>
-      <c r="E80" t="n">
-        <v>2490.96</v>
-      </c>
       <c r="F80" t="n">
-        <v>-23.59</v>
+        <v>-18.03</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0073</v>
       </c>
       <c r="H80" t="n">
-        <v>67.95</v>
+        <v>78.67</v>
       </c>
       <c r="I80" t="n">
-        <v>2411.07</v>
+        <v>2375.9</v>
       </c>
       <c r="J80" t="n">
-        <v>2466.32</v>
+        <v>2424.97</v>
       </c>
       <c r="K80" t="n">
-        <v>2485.99</v>
+        <v>2452.23</v>
       </c>
       <c r="L80" t="n">
-        <v>2505.65</v>
+        <v>2479.49</v>
       </c>
       <c r="M80" t="n">
-        <v>2543.11</v>
+        <v>2517.65</v>
       </c>
       <c r="N80" t="n">
-        <v>2580.57</v>
+        <v>2555.82</v>
       </c>
       <c r="O80" t="n">
-        <v>2582.45</v>
+        <v>2572.18</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7171,16 +7171,18 @@
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U80" s="8" t="n">
         <v/>
@@ -7195,57 +7197,57 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2490.92</v>
+        <v>2466.91</v>
       </c>
       <c r="C81" t="n">
-        <v>2506.75</v>
+        <v>2483.72</v>
       </c>
       <c r="D81" t="n">
-        <v>2441.33</v>
+        <v>2406.91</v>
       </c>
       <c r="E81" t="n">
-        <v>2484.94</v>
+        <v>2437.1</v>
       </c>
       <c r="F81" t="n">
-        <v>-6.02</v>
+        <v>-29.82</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0121</v>
       </c>
       <c r="H81" t="n">
-        <v>65.42</v>
+        <v>76.81</v>
       </c>
       <c r="I81" t="n">
-        <v>2398.96</v>
+        <v>2365.04</v>
       </c>
       <c r="J81" t="n">
-        <v>2418.04</v>
+        <v>2380.19</v>
       </c>
       <c r="K81" t="n">
-        <v>2456.98</v>
+        <v>2427.58</v>
       </c>
       <c r="L81" t="n">
-        <v>2495.92</v>
+        <v>2474.97</v>
       </c>
       <c r="M81" t="n">
-        <v>2524.93</v>
+        <v>2506.25</v>
       </c>
       <c r="N81" t="n">
-        <v>2553.94</v>
+        <v>2537.52</v>
       </c>
       <c r="O81" t="n">
-        <v>2602.81</v>
+        <v>2601.04</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7255,12 +7257,12 @@
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T81" s="8" t="n">
@@ -7286,50 +7288,50 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2484.89</v>
+        <v>2437.14</v>
       </c>
       <c r="C82" t="n">
-        <v>2522.37</v>
+        <v>2663.05</v>
       </c>
       <c r="D82" t="n">
-        <v>2443.7</v>
+        <v>2435.29</v>
       </c>
       <c r="E82" t="n">
-        <v>2466.91</v>
+        <v>2514.73</v>
       </c>
       <c r="F82" t="n">
-        <v>-18.03</v>
+        <v>77.64</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0319</v>
       </c>
       <c r="H82" t="n">
-        <v>78.67</v>
+        <v>227.76</v>
       </c>
       <c r="I82" t="n">
-        <v>2375.9</v>
+        <v>2330.09</v>
       </c>
       <c r="J82" t="n">
-        <v>2424.97</v>
+        <v>2356.18</v>
       </c>
       <c r="K82" t="n">
-        <v>2452.23</v>
+        <v>2398.69</v>
       </c>
       <c r="L82" t="n">
-        <v>2479.49</v>
+        <v>2441.21</v>
       </c>
       <c r="M82" t="n">
-        <v>2517.65</v>
+        <v>2475.51</v>
       </c>
       <c r="N82" t="n">
-        <v>2555.82</v>
+        <v>2509.8</v>
       </c>
       <c r="O82" t="n">
-        <v>2572.18</v>
+        <v>2560.53</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7337,85 +7339,83 @@
       <c r="Q82" s="6" t="n">
         <v/>
       </c>
-      <c r="R82" s="6" t="inlineStr">
+      <c r="R82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S82" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S82" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="inlineStr">
+      <c r="U82" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V82" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U82" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V82" s="8" t="n">
-        <v/>
-      </c>
       <c r="W82" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2466.91</v>
+        <v>2514.77</v>
       </c>
       <c r="C83" t="n">
-        <v>2483.72</v>
+        <v>2544.47</v>
       </c>
       <c r="D83" t="n">
-        <v>2406.91</v>
+        <v>2508.8</v>
       </c>
       <c r="E83" t="n">
-        <v>2437.1</v>
+        <v>2525.94</v>
       </c>
       <c r="F83" t="n">
-        <v>-29.82</v>
+        <v>11.21</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.0121</v>
+        <v>0.0045</v>
       </c>
       <c r="H83" t="n">
-        <v>76.81</v>
+        <v>35.67</v>
       </c>
       <c r="I83" t="n">
-        <v>2365.04</v>
+        <v>2207.52</v>
       </c>
       <c r="J83" t="n">
-        <v>2380.19</v>
+        <v>2269.75</v>
       </c>
       <c r="K83" t="n">
-        <v>2427.58</v>
+        <v>2400.85</v>
       </c>
       <c r="L83" t="n">
-        <v>2474.97</v>
+        <v>2531.95</v>
       </c>
       <c r="M83" t="n">
-        <v>2506.25</v>
+        <v>2628.62</v>
       </c>
       <c r="N83" t="n">
-        <v>2537.52</v>
+        <v>2725.28</v>
       </c>
       <c r="O83" t="n">
-        <v>2601.04</v>
+        <v>2890.82</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
@@ -7423,14 +7423,12 @@
       <c r="Q83" s="6" t="n">
         <v/>
       </c>
-      <c r="R83" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R83" s="6" t="n">
+        <v/>
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T83" s="8" t="n">
@@ -7449,90 +7447,90 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2437.14</v>
+        <v>2525.94</v>
       </c>
       <c r="C84" t="n">
-        <v>2663.05</v>
+        <v>2526.85</v>
       </c>
       <c r="D84" t="n">
-        <v>2435.29</v>
+        <v>2462.84</v>
       </c>
       <c r="E84" t="n">
-        <v>2514.73</v>
+        <v>2477.02</v>
       </c>
       <c r="F84" t="n">
-        <v>77.64</v>
+        <v>-48.92</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.0319</v>
+        <v>-0.0194</v>
       </c>
       <c r="H84" t="n">
-        <v>227.76</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>2330.09</v>
+        <v>2473.13</v>
       </c>
       <c r="J84" t="n">
-        <v>2356.18</v>
+        <v>2489.93</v>
       </c>
       <c r="K84" t="n">
-        <v>2398.69</v>
+        <v>2508.11</v>
       </c>
       <c r="L84" t="n">
-        <v>2441.21</v>
+        <v>2526.29</v>
       </c>
       <c r="M84" t="n">
-        <v>2475.51</v>
+        <v>2543.78</v>
       </c>
       <c r="N84" t="n">
-        <v>2509.8</v>
+        <v>2561.27</v>
       </c>
       <c r="O84" t="n">
-        <v>2560.53</v>
-      </c>
-      <c r="P84" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q84" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R84" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S84" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="inlineStr">
+        <v>2580.14</v>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q84" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U84" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V84" s="8" t="inlineStr">
+      <c r="R84" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W84" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S84" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U84" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V84" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W84" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X84" t="inlineStr"/>
@@ -7540,50 +7538,50 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2514.77</v>
+        <v>2476.6</v>
       </c>
       <c r="C85" t="n">
-        <v>2544.47</v>
+        <v>2612.4</v>
       </c>
       <c r="D85" t="n">
-        <v>2508.8</v>
+        <v>2465.43</v>
       </c>
       <c r="E85" t="n">
-        <v>2525.94</v>
+        <v>2514.41</v>
       </c>
       <c r="F85" t="n">
-        <v>11.21</v>
+        <v>37.39</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0151</v>
       </c>
       <c r="H85" t="n">
-        <v>35.67</v>
+        <v>146.98</v>
       </c>
       <c r="I85" t="n">
-        <v>2207.52</v>
+        <v>2398.83</v>
       </c>
       <c r="J85" t="n">
-        <v>2269.75</v>
+        <v>2404.09</v>
       </c>
       <c r="K85" t="n">
-        <v>2400.85</v>
+        <v>2445.01</v>
       </c>
       <c r="L85" t="n">
-        <v>2531.95</v>
+        <v>2485.93</v>
       </c>
       <c r="M85" t="n">
-        <v>2628.62</v>
+        <v>2509.03</v>
       </c>
       <c r="N85" t="n">
-        <v>2725.28</v>
+        <v>2532.12</v>
       </c>
       <c r="O85" t="n">
-        <v>2890.82</v>
+        <v>2590.87</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7594,92 +7592,94 @@
       <c r="R85" s="6" t="n">
         <v/>
       </c>
-      <c r="S85" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U85" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V85" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W85" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S85" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W85" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2525.94</v>
+        <v>2514.36</v>
       </c>
       <c r="C86" t="n">
-        <v>2526.85</v>
+        <v>2519.32</v>
       </c>
       <c r="D86" t="n">
-        <v>2462.84</v>
+        <v>2357.96</v>
       </c>
       <c r="E86" t="n">
-        <v>2477.02</v>
+        <v>2399.09</v>
       </c>
       <c r="F86" t="n">
-        <v>-48.92</v>
+        <v>-115.32</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.0194</v>
+        <v>-0.0459</v>
       </c>
       <c r="H86" t="n">
-        <v>64.01000000000001</v>
+        <v>161.36</v>
       </c>
       <c r="I86" t="n">
-        <v>2473.13</v>
+        <v>2318.45</v>
       </c>
       <c r="J86" t="n">
-        <v>2489.93</v>
+        <v>2355.18</v>
       </c>
       <c r="K86" t="n">
-        <v>2508.11</v>
+        <v>2440.92</v>
       </c>
       <c r="L86" t="n">
-        <v>2526.29</v>
+        <v>2526.66</v>
       </c>
       <c r="M86" t="n">
-        <v>2543.78</v>
+        <v>2587.9</v>
       </c>
       <c r="N86" t="n">
-        <v>2561.27</v>
+        <v>2649.13</v>
       </c>
       <c r="O86" t="n">
-        <v>2580.14</v>
-      </c>
-      <c r="P86" s="6" t="inlineStr">
+        <v>2759.38</v>
+      </c>
+      <c r="P86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q86" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q86" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R86" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S86" s="7" t="inlineStr">
@@ -7706,50 +7706,50 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2476.6</v>
+        <v>2399.06</v>
       </c>
       <c r="C87" t="n">
-        <v>2612.4</v>
+        <v>2426.93</v>
       </c>
       <c r="D87" t="n">
-        <v>2465.43</v>
+        <v>2368.74</v>
       </c>
       <c r="E87" t="n">
-        <v>2514.41</v>
+        <v>2416.12</v>
       </c>
       <c r="F87" t="n">
-        <v>37.39</v>
+        <v>17.03</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0071</v>
       </c>
       <c r="H87" t="n">
-        <v>146.98</v>
+        <v>58.19</v>
       </c>
       <c r="I87" t="n">
-        <v>2398.83</v>
+        <v>2196.6</v>
       </c>
       <c r="J87" t="n">
-        <v>2404.09</v>
+        <v>2217.95</v>
       </c>
       <c r="K87" t="n">
-        <v>2445.01</v>
+        <v>2318.41</v>
       </c>
       <c r="L87" t="n">
-        <v>2485.93</v>
+        <v>2418.86</v>
       </c>
       <c r="M87" t="n">
-        <v>2509.03</v>
+        <v>2479.77</v>
       </c>
       <c r="N87" t="n">
-        <v>2532.12</v>
+        <v>2540.67</v>
       </c>
       <c r="O87" t="n">
-        <v>2590.87</v>
+        <v>2680.68</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7760,25 +7760,19 @@
       <c r="R87" s="6" t="n">
         <v/>
       </c>
-      <c r="S87" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S87" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V87" s="8" t="n">
+        <v/>
       </c>
       <c r="W87" s="11" t="inlineStr">
         <is>
@@ -7787,57 +7781,57 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2514.36</v>
+        <v>2416.17</v>
       </c>
       <c r="C88" t="n">
-        <v>2519.32</v>
+        <v>2480.74</v>
       </c>
       <c r="D88" t="n">
-        <v>2357.96</v>
+        <v>2412.19</v>
       </c>
       <c r="E88" t="n">
-        <v>2399.09</v>
+        <v>2447.11</v>
       </c>
       <c r="F88" t="n">
-        <v>-115.32</v>
+        <v>30.99</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-0.0459</v>
+        <v>0.0128</v>
       </c>
       <c r="H88" t="n">
-        <v>161.36</v>
+        <v>68.55</v>
       </c>
       <c r="I88" t="n">
-        <v>2318.45</v>
+        <v>2310.54</v>
       </c>
       <c r="J88" t="n">
-        <v>2355.18</v>
+        <v>2367.07</v>
       </c>
       <c r="K88" t="n">
-        <v>2440.92</v>
+        <v>2387.02</v>
       </c>
       <c r="L88" t="n">
-        <v>2526.66</v>
+        <v>2406.98</v>
       </c>
       <c r="M88" t="n">
-        <v>2587.9</v>
+        <v>2445.22</v>
       </c>
       <c r="N88" t="n">
-        <v>2649.13</v>
+        <v>2483.46</v>
       </c>
       <c r="O88" t="n">
-        <v>2759.38</v>
+        <v>2485.12</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
@@ -7845,19 +7839,19 @@
       <c r="Q88" s="6" t="n">
         <v/>
       </c>
-      <c r="R88" s="6" t="inlineStr">
+      <c r="R88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S88" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S88" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="n">
-        <v/>
-      </c>
       <c r="U88" s="8" t="n">
         <v/>
       </c>
@@ -7869,55 +7863,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr"/>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2399.06</v>
+        <v>2447.11</v>
       </c>
       <c r="C89" t="n">
-        <v>2426.93</v>
+        <v>2643.96</v>
       </c>
       <c r="D89" t="n">
-        <v>2368.74</v>
+        <v>2435.15</v>
       </c>
       <c r="E89" t="n">
-        <v>2416.12</v>
+        <v>2611.35</v>
       </c>
       <c r="F89" t="n">
-        <v>17.03</v>
+        <v>164.24</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H89" t="n">
-        <v>58.19</v>
+        <v>208.81</v>
       </c>
       <c r="I89" t="n">
-        <v>2196.6</v>
+        <v>2343.64</v>
       </c>
       <c r="J89" t="n">
-        <v>2217.95</v>
+        <v>2378.88</v>
       </c>
       <c r="K89" t="n">
-        <v>2318.41</v>
+        <v>2412.83</v>
       </c>
       <c r="L89" t="n">
-        <v>2418.86</v>
+        <v>2446.78</v>
       </c>
       <c r="M89" t="n">
-        <v>2479.77</v>
+        <v>2481.38</v>
       </c>
       <c r="N89" t="n">
-        <v>2540.67</v>
+        <v>2515.98</v>
       </c>
       <c r="O89" t="n">
-        <v>2680.68</v>
+        <v>2549.29</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7928,78 +7926,80 @@
       <c r="R89" s="6" t="n">
         <v/>
       </c>
-      <c r="S89" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W89" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S89" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U89" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V89" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W89" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2445.49</v>
+        <v>2611.46</v>
       </c>
       <c r="C90" t="n">
-        <v>2445.49</v>
+        <v>2659.72</v>
       </c>
       <c r="D90" t="n">
-        <v>2438.16</v>
+        <v>2602.74</v>
       </c>
       <c r="E90" t="n">
-        <v>2445.52</v>
+        <v>2631.96</v>
       </c>
       <c r="F90" t="n">
-        <v>29.4</v>
+        <v>20.62</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0122</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H90" t="n">
-        <v>7.32</v>
+        <v>56.98</v>
       </c>
       <c r="I90" t="n">
-        <v>2310.54</v>
+        <v>2226.33</v>
       </c>
       <c r="J90" t="n">
-        <v>2367.07</v>
+        <v>2438.43</v>
       </c>
       <c r="K90" t="n">
-        <v>2387.02</v>
+        <v>2506.94</v>
       </c>
       <c r="L90" t="n">
-        <v>2406.98</v>
+        <v>2575.45</v>
       </c>
       <c r="M90" t="n">
-        <v>2445.22</v>
+        <v>2715.75</v>
       </c>
       <c r="N90" t="n">
-        <v>2483.46</v>
+        <v>2856.06</v>
       </c>
       <c r="O90" t="n">
-        <v>2485.12</v>
+        <v>2852.78</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
@@ -8012,13 +8012,11 @@
       </c>
       <c r="S90" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="n">
+        <v/>
       </c>
       <c r="U90" s="8" t="n">
         <v/>
@@ -8026,14 +8024,96 @@
       <c r="V90" s="8" t="n">
         <v/>
       </c>
-      <c r="W90" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>強警訊</t>
+      <c r="W90" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2631.78</v>
+      </c>
+      <c r="C91" t="n">
+        <v>2645.33</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2569.74</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2644.05</v>
+      </c>
+      <c r="F91" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="H91" t="n">
+        <v>75.59</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2545.76</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2575.35</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2603.47</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2631.6</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2660.45</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2689.31</v>
+      </c>
+      <c r="O91" t="n">
+        <v>2716.7</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S91" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W91" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -634,62 +634,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1726.52</v>
+        <v>1665.31</v>
       </c>
       <c r="C2" t="n">
-        <v>1733.61</v>
+        <v>1687.49</v>
       </c>
       <c r="D2" t="n">
-        <v>1638.25</v>
+        <v>1551.48</v>
       </c>
       <c r="E2" t="n">
-        <v>1665.44</v>
+        <v>1619.92</v>
       </c>
       <c r="F2" t="n">
-        <v>-61.07</v>
+        <v>-45.51</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0354</v>
+        <v>-0.0273</v>
       </c>
       <c r="H2" t="n">
-        <v>95.36</v>
+        <v>136.01</v>
       </c>
       <c r="I2" t="n">
-        <v>1632.2</v>
+        <v>1542.89</v>
       </c>
       <c r="J2" t="n">
-        <v>1647.11</v>
+        <v>1559.83</v>
       </c>
       <c r="K2" t="n">
-        <v>1690.35</v>
+        <v>1617.76</v>
       </c>
       <c r="L2" t="n">
-        <v>1733.59</v>
+        <v>1675.68</v>
       </c>
       <c r="M2" t="n">
-        <v>1762.67</v>
+        <v>1713.12</v>
       </c>
       <c r="N2" t="n">
-        <v>1791.74</v>
+        <v>1750.55</v>
       </c>
       <c r="O2" t="n">
-        <v>1849.15</v>
+        <v>1828.97</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -720,58 +720,56 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1665.31</v>
+        <v>1619.89</v>
       </c>
       <c r="C3" t="n">
-        <v>1687.49</v>
+        <v>1656.65</v>
       </c>
       <c r="D3" t="n">
-        <v>1551.48</v>
+        <v>1531.78</v>
       </c>
       <c r="E3" t="n">
-        <v>1619.92</v>
+        <v>1564.82</v>
       </c>
       <c r="F3" t="n">
-        <v>-45.51</v>
+        <v>-55.11</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.034</v>
       </c>
       <c r="H3" t="n">
-        <v>136.01</v>
+        <v>124.87</v>
       </c>
       <c r="I3" t="n">
-        <v>1542.89</v>
+        <v>1415.48</v>
       </c>
       <c r="J3" t="n">
-        <v>1559.83</v>
+        <v>1484.14</v>
       </c>
       <c r="K3" t="n">
-        <v>1617.76</v>
+        <v>1551.92</v>
       </c>
       <c r="L3" t="n">
-        <v>1675.68</v>
+        <v>1619.71</v>
       </c>
       <c r="M3" t="n">
-        <v>1713.12</v>
+        <v>1687.93</v>
       </c>
       <c r="N3" t="n">
-        <v>1750.55</v>
+        <v>1756.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1828.97</v>
+        <v>1823.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q3" s="6" t="n">
+        <v/>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
@@ -806,50 +804,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1619.89</v>
+        <v>1564.61</v>
       </c>
       <c r="C4" t="n">
-        <v>1656.65</v>
+        <v>1590.2</v>
       </c>
       <c r="D4" t="n">
-        <v>1531.78</v>
+        <v>1510.51</v>
       </c>
       <c r="E4" t="n">
-        <v>1564.82</v>
+        <v>1576.62</v>
       </c>
       <c r="F4" t="n">
-        <v>-55.11</v>
+        <v>11.8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.034</v>
+        <v>0.0075</v>
       </c>
       <c r="H4" t="n">
-        <v>124.87</v>
+        <v>79.69</v>
       </c>
       <c r="I4" t="n">
-        <v>1415.48</v>
+        <v>1406.91</v>
       </c>
       <c r="J4" t="n">
-        <v>1484.14</v>
+        <v>1425.25</v>
       </c>
       <c r="K4" t="n">
-        <v>1551.92</v>
+        <v>1502.38</v>
       </c>
       <c r="L4" t="n">
-        <v>1619.71</v>
+        <v>1579.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1687.93</v>
+        <v>1627.25</v>
       </c>
       <c r="N4" t="n">
-        <v>1756.15</v>
+        <v>1674.98</v>
       </c>
       <c r="O4" t="n">
-        <v>1823.5</v>
+        <v>1781.51</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -857,14 +855,12 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -883,57 +879,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1564.61</v>
+        <v>1576.59</v>
       </c>
       <c r="C5" t="n">
-        <v>1590.2</v>
+        <v>1607.87</v>
       </c>
       <c r="D5" t="n">
-        <v>1510.51</v>
+        <v>1561.97</v>
       </c>
       <c r="E5" t="n">
-        <v>1576.62</v>
+        <v>1571.59</v>
       </c>
       <c r="F5" t="n">
-        <v>11.8</v>
+        <v>-5.03</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0032</v>
       </c>
       <c r="H5" t="n">
-        <v>79.69</v>
+        <v>45.89</v>
       </c>
       <c r="I5" t="n">
-        <v>1406.91</v>
+        <v>1430.81</v>
       </c>
       <c r="J5" t="n">
-        <v>1425.25</v>
+        <v>1510.05</v>
       </c>
       <c r="K5" t="n">
-        <v>1502.38</v>
+        <v>1536.77</v>
       </c>
       <c r="L5" t="n">
-        <v>1579.52</v>
+        <v>1563.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1627.25</v>
+        <v>1616.46</v>
       </c>
       <c r="N5" t="n">
-        <v>1674.98</v>
+        <v>1669.44</v>
       </c>
       <c r="O5" t="n">
-        <v>1781.51</v>
+        <v>1669.89</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -944,9 +940,9 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -965,57 +961,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1576.59</v>
+        <v>1571.56</v>
       </c>
       <c r="C6" t="n">
-        <v>1607.87</v>
+        <v>1585.22</v>
       </c>
       <c r="D6" t="n">
-        <v>1561.97</v>
+        <v>1548.76</v>
       </c>
       <c r="E6" t="n">
-        <v>1571.59</v>
+        <v>1570.36</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.03</v>
+        <v>-1.23</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.0008</v>
       </c>
       <c r="H6" t="n">
-        <v>45.89</v>
+        <v>36.46</v>
       </c>
       <c r="I6" t="n">
-        <v>1430.81</v>
+        <v>1516.08</v>
       </c>
       <c r="J6" t="n">
-        <v>1510.05</v>
+        <v>1519.03</v>
       </c>
       <c r="K6" t="n">
-        <v>1536.77</v>
+        <v>1548.64</v>
       </c>
       <c r="L6" t="n">
-        <v>1563.48</v>
+        <v>1578.25</v>
       </c>
       <c r="M6" t="n">
-        <v>1616.46</v>
+        <v>1594.53</v>
       </c>
       <c r="N6" t="n">
-        <v>1669.44</v>
+        <v>1610.82</v>
       </c>
       <c r="O6" t="n">
-        <v>1669.89</v>
+        <v>1653.76</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1026,9 +1022,9 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1047,57 +1043,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1571.56</v>
+        <v>1569.99</v>
       </c>
       <c r="C7" t="n">
-        <v>1585.22</v>
+        <v>1633.65</v>
       </c>
       <c r="D7" t="n">
-        <v>1548.76</v>
+        <v>1550.04</v>
       </c>
       <c r="E7" t="n">
-        <v>1570.36</v>
+        <v>1610.21</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.23</v>
+        <v>39.84</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0254</v>
       </c>
       <c r="H7" t="n">
-        <v>36.46</v>
+        <v>83.61</v>
       </c>
       <c r="I7" t="n">
-        <v>1516.08</v>
+        <v>1512.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1519.03</v>
+        <v>1535.59</v>
       </c>
       <c r="K7" t="n">
-        <v>1548.64</v>
+        <v>1552.13</v>
       </c>
       <c r="L7" t="n">
-        <v>1578.25</v>
+        <v>1568.68</v>
       </c>
       <c r="M7" t="n">
-        <v>1594.53</v>
+        <v>1588.59</v>
       </c>
       <c r="N7" t="n">
-        <v>1610.82</v>
+        <v>1608.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1653.76</v>
+        <v>1621.68</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,81 +1101,85 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1569.99</v>
+        <v>1610.16</v>
       </c>
       <c r="C8" t="n">
-        <v>1633.65</v>
+        <v>1611.35</v>
       </c>
       <c r="D8" t="n">
-        <v>1550.04</v>
+        <v>1549.25</v>
       </c>
       <c r="E8" t="n">
-        <v>1610.21</v>
+        <v>1569.58</v>
       </c>
       <c r="F8" t="n">
-        <v>39.84</v>
+        <v>-40.62</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0254</v>
+        <v>-0.0252</v>
       </c>
       <c r="H8" t="n">
-        <v>83.61</v>
+        <v>62.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1512.3</v>
+        <v>1466.43</v>
       </c>
       <c r="J8" t="n">
-        <v>1535.59</v>
+        <v>1535.78</v>
       </c>
       <c r="K8" t="n">
-        <v>1552.13</v>
+        <v>1568.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1568.68</v>
+        <v>1601.02</v>
       </c>
       <c r="M8" t="n">
-        <v>1588.59</v>
+        <v>1652.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1608.5</v>
+        <v>1703</v>
       </c>
       <c r="O8" t="n">
-        <v>1621.68</v>
+        <v>1717.25</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1189,83 +1189,81 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1610.16</v>
+        <v>1569.91</v>
       </c>
       <c r="C9" t="n">
-        <v>1611.35</v>
+        <v>1642.45</v>
       </c>
       <c r="D9" t="n">
-        <v>1549.25</v>
+        <v>1551.14</v>
       </c>
       <c r="E9" t="n">
-        <v>1569.58</v>
+        <v>1608.96</v>
       </c>
       <c r="F9" t="n">
-        <v>-40.62</v>
+        <v>39.38</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0252</v>
+        <v>0.0251</v>
       </c>
       <c r="H9" t="n">
-        <v>62.1</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>1466.43</v>
+        <v>1487.16</v>
       </c>
       <c r="J9" t="n">
-        <v>1535.78</v>
+        <v>1502.13</v>
       </c>
       <c r="K9" t="n">
-        <v>1568.4</v>
+        <v>1538.54</v>
       </c>
       <c r="L9" t="n">
-        <v>1601.02</v>
+        <v>1574.94</v>
       </c>
       <c r="M9" t="n">
-        <v>1652.01</v>
+        <v>1600.63</v>
       </c>
       <c r="N9" t="n">
-        <v>1703</v>
+        <v>1626.32</v>
       </c>
       <c r="O9" t="n">
-        <v>1717.25</v>
+        <v>1673.44</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,21 +1271,23 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1297,59 +1297,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1569.91</v>
+        <v>1609.01</v>
       </c>
       <c r="C10" t="n">
-        <v>1642.45</v>
+        <v>1720.34</v>
       </c>
       <c r="D10" t="n">
-        <v>1551.14</v>
+        <v>1595.94</v>
       </c>
       <c r="E10" t="n">
-        <v>1608.96</v>
+        <v>1698.17</v>
       </c>
       <c r="F10" t="n">
-        <v>39.38</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0554</v>
       </c>
       <c r="H10" t="n">
-        <v>91.31999999999999</v>
+        <v>124.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1487.16</v>
+        <v>1459.82</v>
       </c>
       <c r="J10" t="n">
-        <v>1502.13</v>
+        <v>1523.73</v>
       </c>
       <c r="K10" t="n">
-        <v>1538.54</v>
+        <v>1563.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1574.94</v>
+        <v>1602.88</v>
       </c>
       <c r="M10" t="n">
-        <v>1600.63</v>
+        <v>1654.62</v>
       </c>
       <c r="N10" t="n">
-        <v>1626.32</v>
+        <v>1706.36</v>
       </c>
       <c r="O10" t="n">
-        <v>1673.44</v>
+        <v>1733.77</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1367,12 +1363,12 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V10" s="8" t="n">
@@ -1388,50 +1384,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1609.01</v>
+        <v>1698.42</v>
       </c>
       <c r="C11" t="n">
-        <v>1720.34</v>
+        <v>1772.54</v>
       </c>
       <c r="D11" t="n">
-        <v>1595.94</v>
+        <v>1693.04</v>
       </c>
       <c r="E11" t="n">
-        <v>1698.17</v>
+        <v>1756.52</v>
       </c>
       <c r="F11" t="n">
-        <v>89.20999999999999</v>
+        <v>58.35</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0344</v>
       </c>
       <c r="H11" t="n">
-        <v>124.4</v>
+        <v>79.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1459.82</v>
+        <v>1471.54</v>
       </c>
       <c r="J11" t="n">
-        <v>1523.73</v>
+        <v>1593.78</v>
       </c>
       <c r="K11" t="n">
-        <v>1563.3</v>
+        <v>1635.97</v>
       </c>
       <c r="L11" t="n">
-        <v>1602.88</v>
+        <v>1678.16</v>
       </c>
       <c r="M11" t="n">
-        <v>1654.62</v>
+        <v>1760.37</v>
       </c>
       <c r="N11" t="n">
-        <v>1706.36</v>
+        <v>1842.59</v>
       </c>
       <c r="O11" t="n">
-        <v>1733.77</v>
+        <v>1844.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1449,13 +1445,11 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1470,50 +1464,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1698.42</v>
+        <v>1756.58</v>
       </c>
       <c r="C12" t="n">
-        <v>1772.54</v>
+        <v>1804.59</v>
       </c>
       <c r="D12" t="n">
-        <v>1693.04</v>
+        <v>1743.56</v>
       </c>
       <c r="E12" t="n">
-        <v>1756.52</v>
+        <v>1779.03</v>
       </c>
       <c r="F12" t="n">
-        <v>58.35</v>
+        <v>22.51</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0128</v>
       </c>
       <c r="H12" t="n">
-        <v>79.5</v>
+        <v>61.02</v>
       </c>
       <c r="I12" t="n">
-        <v>1471.54</v>
+        <v>1613.53</v>
       </c>
       <c r="J12" t="n">
-        <v>1593.78</v>
+        <v>1688.88</v>
       </c>
       <c r="K12" t="n">
-        <v>1635.97</v>
+        <v>1716.77</v>
       </c>
       <c r="L12" t="n">
-        <v>1678.16</v>
+        <v>1744.65</v>
       </c>
       <c r="M12" t="n">
-        <v>1760.37</v>
+        <v>1796.27</v>
       </c>
       <c r="N12" t="n">
-        <v>1842.59</v>
+        <v>1847.89</v>
       </c>
       <c r="O12" t="n">
-        <v>1844.75</v>
+        <v>1852.05</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1550,50 +1544,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1756.58</v>
+        <v>1779.04</v>
       </c>
       <c r="C13" t="n">
-        <v>1804.59</v>
+        <v>1805.91</v>
       </c>
       <c r="D13" t="n">
-        <v>1743.56</v>
+        <v>1749.14</v>
       </c>
       <c r="E13" t="n">
-        <v>1779.03</v>
+        <v>1783.01</v>
       </c>
       <c r="F13" t="n">
-        <v>22.51</v>
+        <v>3.97</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0022</v>
       </c>
       <c r="H13" t="n">
-        <v>61.02</v>
+        <v>56.78</v>
       </c>
       <c r="I13" t="n">
-        <v>1613.53</v>
+        <v>1682.54</v>
       </c>
       <c r="J13" t="n">
-        <v>1688.88</v>
+        <v>1720.49</v>
       </c>
       <c r="K13" t="n">
-        <v>1716.77</v>
+        <v>1748.52</v>
       </c>
       <c r="L13" t="n">
-        <v>1744.65</v>
+        <v>1776.55</v>
       </c>
       <c r="M13" t="n">
-        <v>1796.27</v>
+        <v>1809.55</v>
       </c>
       <c r="N13" t="n">
-        <v>1847.89</v>
+        <v>1842.54</v>
       </c>
       <c r="O13" t="n">
-        <v>1852.05</v>
+        <v>1865.61</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1606,13 +1600,11 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1630,67 +1622,73 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779.04</v>
+        <v>1783</v>
       </c>
       <c r="C14" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D14" t="n">
-        <v>1749.14</v>
+        <v>1728.97</v>
       </c>
       <c r="E14" t="n">
-        <v>1783.01</v>
+        <v>1797.57</v>
       </c>
       <c r="F14" t="n">
-        <v>3.97</v>
+        <v>14.57</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>56.78</v>
+        <v>100.55</v>
       </c>
       <c r="I14" t="n">
-        <v>1682.54</v>
+        <v>1692.36</v>
       </c>
       <c r="J14" t="n">
-        <v>1720.49</v>
+        <v>1728.97</v>
       </c>
       <c r="K14" t="n">
-        <v>1748.52</v>
+        <v>1754.62</v>
       </c>
       <c r="L14" t="n">
-        <v>1776.55</v>
+        <v>1780.27</v>
       </c>
       <c r="M14" t="n">
-        <v>1809.55</v>
+        <v>1811.39</v>
       </c>
       <c r="N14" t="n">
-        <v>1842.54</v>
+        <v>1842.52</v>
       </c>
       <c r="O14" t="n">
-        <v>1865.61</v>
+        <v>1862.69</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1703,78 +1701,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1783</v>
+        <v>1797.56</v>
       </c>
       <c r="C15" t="n">
-        <v>1829.51</v>
+        <v>1810.33</v>
       </c>
       <c r="D15" t="n">
-        <v>1728.97</v>
+        <v>1756.71</v>
       </c>
       <c r="E15" t="n">
-        <v>1797.57</v>
+        <v>1768.51</v>
       </c>
       <c r="F15" t="n">
-        <v>14.57</v>
+        <v>-29.06</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0162</v>
       </c>
       <c r="H15" t="n">
-        <v>100.55</v>
+        <v>53.62</v>
       </c>
       <c r="I15" t="n">
-        <v>1692.36</v>
+        <v>1628.42</v>
       </c>
       <c r="J15" t="n">
-        <v>1728.97</v>
+        <v>1706.19</v>
       </c>
       <c r="K15" t="n">
-        <v>1754.62</v>
+        <v>1747.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1780.27</v>
+        <v>1788.41</v>
       </c>
       <c r="M15" t="n">
-        <v>1811.39</v>
+        <v>1847.85</v>
       </c>
       <c r="N15" t="n">
-        <v>1842.52</v>
+        <v>1907.29</v>
       </c>
       <c r="O15" t="n">
-        <v>1862.69</v>
+        <v>1930.06</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1789,57 +1785,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1797.56</v>
+        <v>1768.39</v>
       </c>
       <c r="C16" t="n">
-        <v>1810.33</v>
+        <v>1782.86</v>
       </c>
       <c r="D16" t="n">
-        <v>1756.71</v>
+        <v>1711.9</v>
       </c>
       <c r="E16" t="n">
-        <v>1768.51</v>
+        <v>1742.68</v>
       </c>
       <c r="F16" t="n">
-        <v>-29.06</v>
+        <v>-25.83</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0146</v>
       </c>
       <c r="H16" t="n">
-        <v>53.62</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>1628.42</v>
+        <v>1703.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1706.19</v>
+        <v>1707.39</v>
       </c>
       <c r="K16" t="n">
-        <v>1747.3</v>
+        <v>1741.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1788.41</v>
+        <v>1776.02</v>
       </c>
       <c r="M16" t="n">
-        <v>1847.85</v>
+        <v>1795.32</v>
       </c>
       <c r="N16" t="n">
-        <v>1907.29</v>
+        <v>1814.62</v>
       </c>
       <c r="O16" t="n">
-        <v>1930.06</v>
+        <v>1863.95</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1847,12 +1843,14 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1871,57 +1869,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1768.39</v>
+        <v>1742.66</v>
       </c>
       <c r="C17" t="n">
-        <v>1782.86</v>
+        <v>1760.21</v>
       </c>
       <c r="D17" t="n">
-        <v>1711.9</v>
+        <v>1721.3</v>
       </c>
       <c r="E17" t="n">
-        <v>1742.68</v>
+        <v>1744.48</v>
       </c>
       <c r="F17" t="n">
-        <v>-25.83</v>
+        <v>1.81</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>70.95999999999999</v>
+        <v>38.91</v>
       </c>
       <c r="I17" t="n">
-        <v>1703.1</v>
+        <v>1640.94</v>
       </c>
       <c r="J17" t="n">
-        <v>1707.39</v>
+        <v>1669.37</v>
       </c>
       <c r="K17" t="n">
-        <v>1741.7</v>
+        <v>1707.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1776.02</v>
+        <v>1745.03</v>
       </c>
       <c r="M17" t="n">
-        <v>1795.32</v>
+        <v>1778.16</v>
       </c>
       <c r="N17" t="n">
-        <v>1814.62</v>
+        <v>1811.29</v>
       </c>
       <c r="O17" t="n">
-        <v>1863.95</v>
+        <v>1853.82</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1929,14 +1927,12 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1955,57 +1951,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1742.66</v>
+        <v>1744.47</v>
       </c>
       <c r="C18" t="n">
-        <v>1760.21</v>
+        <v>1809.76</v>
       </c>
       <c r="D18" t="n">
-        <v>1721.3</v>
+        <v>1736.72</v>
       </c>
       <c r="E18" t="n">
-        <v>1744.48</v>
+        <v>1795.69</v>
       </c>
       <c r="F18" t="n">
-        <v>1.81</v>
+        <v>51.21</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0294</v>
       </c>
       <c r="H18" t="n">
-        <v>38.91</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>1640.94</v>
+        <v>1682.39</v>
       </c>
       <c r="J18" t="n">
-        <v>1669.37</v>
+        <v>1707.44</v>
       </c>
       <c r="K18" t="n">
-        <v>1707.2</v>
+        <v>1725.03</v>
       </c>
       <c r="L18" t="n">
-        <v>1745.03</v>
+        <v>1742.62</v>
       </c>
       <c r="M18" t="n">
-        <v>1778.16</v>
+        <v>1763.94</v>
       </c>
       <c r="N18" t="n">
-        <v>1811.29</v>
+        <v>1785.26</v>
       </c>
       <c r="O18" t="n">
-        <v>1853.82</v>
+        <v>1799.11</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2016,78 +2012,80 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1744.47</v>
+        <v>1795.82</v>
       </c>
       <c r="C19" t="n">
-        <v>1809.76</v>
+        <v>1827.83</v>
       </c>
       <c r="D19" t="n">
-        <v>1736.72</v>
+        <v>1786.3</v>
       </c>
       <c r="E19" t="n">
-        <v>1795.69</v>
+        <v>1788.1</v>
       </c>
       <c r="F19" t="n">
-        <v>51.21</v>
+        <v>-7.59</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0294</v>
+        <v>-0.0042</v>
       </c>
       <c r="H19" t="n">
-        <v>73.04000000000001</v>
+        <v>41.54</v>
       </c>
       <c r="I19" t="n">
-        <v>1682.39</v>
+        <v>1663.69</v>
       </c>
       <c r="J19" t="n">
-        <v>1707.44</v>
+        <v>1733.88</v>
       </c>
       <c r="K19" t="n">
-        <v>1725.03</v>
+        <v>1759.18</v>
       </c>
       <c r="L19" t="n">
-        <v>1742.62</v>
+        <v>1784.47</v>
       </c>
       <c r="M19" t="n">
-        <v>1763.94</v>
+        <v>1832.21</v>
       </c>
       <c r="N19" t="n">
-        <v>1785.26</v>
+        <v>1879.95</v>
       </c>
       <c r="O19" t="n">
-        <v>1799.11</v>
+        <v>1882.79</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2100,78 +2098,76 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1795.82</v>
+        <v>1787.57</v>
       </c>
       <c r="C20" t="n">
-        <v>1827.83</v>
+        <v>1824.98</v>
       </c>
       <c r="D20" t="n">
-        <v>1786.3</v>
+        <v>1779.64</v>
       </c>
       <c r="E20" t="n">
-        <v>1788.1</v>
+        <v>1805.79</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.59</v>
+        <v>17.69</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>41.54</v>
+        <v>45.34</v>
       </c>
       <c r="I20" t="n">
-        <v>1663.69</v>
+        <v>1744.76</v>
       </c>
       <c r="J20" t="n">
-        <v>1733.88</v>
+        <v>1737.08</v>
       </c>
       <c r="K20" t="n">
-        <v>1759.18</v>
+        <v>1767.33</v>
       </c>
       <c r="L20" t="n">
-        <v>1784.47</v>
+        <v>1797.58</v>
       </c>
       <c r="M20" t="n">
-        <v>1832.21</v>
+        <v>1808.87</v>
       </c>
       <c r="N20" t="n">
-        <v>1879.95</v>
+        <v>1820.15</v>
       </c>
       <c r="O20" t="n">
-        <v>1882.79</v>
+        <v>1869.37</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2184,14 +2180,18 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2203,81 +2203,83 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1787.57</v>
+        <v>1805.76</v>
       </c>
       <c r="C21" t="n">
-        <v>1824.98</v>
+        <v>1842.46</v>
       </c>
       <c r="D21" t="n">
-        <v>1779.64</v>
+        <v>1749.35</v>
       </c>
       <c r="E21" t="n">
-        <v>1805.79</v>
+        <v>1773.5</v>
       </c>
       <c r="F21" t="n">
-        <v>17.69</v>
+        <v>-32.29</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.0179</v>
       </c>
       <c r="H21" t="n">
-        <v>45.34</v>
+        <v>93.11</v>
       </c>
       <c r="I21" t="n">
-        <v>1744.76</v>
+        <v>1734.29</v>
       </c>
       <c r="J21" t="n">
-        <v>1737.08</v>
+        <v>1762.18</v>
       </c>
       <c r="K21" t="n">
-        <v>1767.33</v>
+        <v>1783.12</v>
       </c>
       <c r="L21" t="n">
-        <v>1797.58</v>
+        <v>1804.05</v>
       </c>
       <c r="M21" t="n">
-        <v>1808.87</v>
+        <v>1828.46</v>
       </c>
       <c r="N21" t="n">
-        <v>1820.15</v>
+        <v>1852.87</v>
       </c>
       <c r="O21" t="n">
-        <v>1869.37</v>
+        <v>1870.32</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2296,77 +2298,75 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1805.76</v>
+        <v>1773.47</v>
       </c>
       <c r="C22" t="n">
-        <v>1842.46</v>
+        <v>1894.06</v>
       </c>
       <c r="D22" t="n">
-        <v>1749.35</v>
+        <v>1772.02</v>
       </c>
       <c r="E22" t="n">
-        <v>1773.5</v>
+        <v>1889.48</v>
       </c>
       <c r="F22" t="n">
-        <v>-32.29</v>
+        <v>115.98</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0654</v>
       </c>
       <c r="H22" t="n">
-        <v>93.11</v>
+        <v>122.04</v>
       </c>
       <c r="I22" t="n">
-        <v>1734.29</v>
+        <v>1656.24</v>
       </c>
       <c r="J22" t="n">
-        <v>1762.18</v>
+        <v>1669.19</v>
       </c>
       <c r="K22" t="n">
-        <v>1783.12</v>
+        <v>1726.95</v>
       </c>
       <c r="L22" t="n">
-        <v>1804.05</v>
+        <v>1784.7</v>
       </c>
       <c r="M22" t="n">
-        <v>1828.46</v>
+        <v>1820.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1852.87</v>
+        <v>1855.41</v>
       </c>
       <c r="O22" t="n">
-        <v>1870.32</v>
+        <v>1935.56</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2375,59 +2375,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1773.47</v>
+        <v>1889.5</v>
       </c>
       <c r="C23" t="n">
-        <v>1894.06</v>
+        <v>1944.16</v>
       </c>
       <c r="D23" t="n">
-        <v>1772.02</v>
+        <v>1863.64</v>
       </c>
       <c r="E23" t="n">
-        <v>1889.48</v>
+        <v>1916.94</v>
       </c>
       <c r="F23" t="n">
-        <v>115.98</v>
+        <v>27.46</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0654</v>
+        <v>0.0145</v>
       </c>
       <c r="H23" t="n">
-        <v>122.04</v>
+        <v>80.53</v>
       </c>
       <c r="I23" t="n">
-        <v>1656.24</v>
+        <v>1649.97</v>
       </c>
       <c r="J23" t="n">
-        <v>1669.19</v>
+        <v>1795.66</v>
       </c>
       <c r="K23" t="n">
-        <v>1726.95</v>
+        <v>1828.46</v>
       </c>
       <c r="L23" t="n">
-        <v>1784.7</v>
+        <v>1861.26</v>
       </c>
       <c r="M23" t="n">
-        <v>1820.05</v>
+        <v>1950.5</v>
       </c>
       <c r="N23" t="n">
-        <v>1855.41</v>
+        <v>2039.74</v>
       </c>
       <c r="O23" t="n">
-        <v>1935.56</v>
+        <v>2016.11</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2445,13 +2441,11 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2466,50 +2460,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1889.5</v>
+        <v>1916.98</v>
       </c>
       <c r="C24" t="n">
-        <v>1944.16</v>
+        <v>1927.09</v>
       </c>
       <c r="D24" t="n">
-        <v>1863.64</v>
+        <v>1856.78</v>
       </c>
       <c r="E24" t="n">
-        <v>1916.94</v>
+        <v>1863.19</v>
       </c>
       <c r="F24" t="n">
-        <v>27.46</v>
+        <v>-53.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0145</v>
+        <v>-0.028</v>
       </c>
       <c r="H24" t="n">
-        <v>80.53</v>
+        <v>70.31</v>
       </c>
       <c r="I24" t="n">
-        <v>1649.97</v>
+        <v>1783.11</v>
       </c>
       <c r="J24" t="n">
-        <v>1795.66</v>
+        <v>1842.94</v>
       </c>
       <c r="K24" t="n">
-        <v>1828.46</v>
+        <v>1876.68</v>
       </c>
       <c r="L24" t="n">
-        <v>1861.26</v>
+        <v>1910.42</v>
       </c>
       <c r="M24" t="n">
-        <v>1950.5</v>
+        <v>1957.21</v>
       </c>
       <c r="N24" t="n">
-        <v>2039.74</v>
+        <v>2003.99</v>
       </c>
       <c r="O24" t="n">
-        <v>2016.11</v>
+        <v>2024.69</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2517,19 +2511,19 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2541,55 +2535,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1916.98</v>
+        <v>1863.22</v>
       </c>
       <c r="C25" t="n">
-        <v>1927.09</v>
+        <v>1869.07</v>
       </c>
       <c r="D25" t="n">
-        <v>1856.78</v>
+        <v>1803.05</v>
       </c>
       <c r="E25" t="n">
-        <v>1863.19</v>
+        <v>1840.99</v>
       </c>
       <c r="F25" t="n">
-        <v>-53.75</v>
+        <v>-22.21</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.0119</v>
       </c>
       <c r="H25" t="n">
-        <v>70.31</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>1783.11</v>
+        <v>1786.47</v>
       </c>
       <c r="J25" t="n">
-        <v>1842.94</v>
+        <v>1778.51</v>
       </c>
       <c r="K25" t="n">
-        <v>1876.68</v>
+        <v>1828.04</v>
       </c>
       <c r="L25" t="n">
-        <v>1910.42</v>
+        <v>1877.56</v>
       </c>
       <c r="M25" t="n">
-        <v>1957.21</v>
+        <v>1898.35</v>
       </c>
       <c r="N25" t="n">
-        <v>2003.99</v>
+        <v>1919.13</v>
       </c>
       <c r="O25" t="n">
-        <v>2024.69</v>
+        <v>1997.4</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2630,50 +2628,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1863.22</v>
+        <v>1841.1</v>
       </c>
       <c r="C26" t="n">
-        <v>1869.07</v>
+        <v>1864.13</v>
       </c>
       <c r="D26" t="n">
-        <v>1803.05</v>
+        <v>1836.61</v>
       </c>
       <c r="E26" t="n">
-        <v>1840.99</v>
+        <v>1861.39</v>
       </c>
       <c r="F26" t="n">
-        <v>-22.21</v>
+        <v>20.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0111</v>
       </c>
       <c r="H26" t="n">
-        <v>66.01000000000001</v>
+        <v>27.52</v>
       </c>
       <c r="I26" t="n">
-        <v>1786.47</v>
+        <v>1737.04</v>
       </c>
       <c r="J26" t="n">
-        <v>1778.51</v>
+        <v>1777.44</v>
       </c>
       <c r="K26" t="n">
-        <v>1828.04</v>
+        <v>1807.98</v>
       </c>
       <c r="L26" t="n">
-        <v>1877.56</v>
+        <v>1838.52</v>
       </c>
       <c r="M26" t="n">
-        <v>1898.35</v>
+        <v>1873.99</v>
       </c>
       <c r="N26" t="n">
-        <v>1919.13</v>
+        <v>1909.47</v>
       </c>
       <c r="O26" t="n">
-        <v>1997.4</v>
+        <v>1935.08</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2681,19 +2679,19 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2707,57 +2705,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1841.1</v>
+        <v>1861.42</v>
       </c>
       <c r="C27" t="n">
-        <v>1864.13</v>
+        <v>1877.03</v>
       </c>
       <c r="D27" t="n">
-        <v>1836.61</v>
+        <v>1852.73</v>
       </c>
       <c r="E27" t="n">
-        <v>1861.39</v>
+        <v>1871.51</v>
       </c>
       <c r="F27" t="n">
-        <v>20.4</v>
+        <v>10.12</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0054</v>
       </c>
       <c r="H27" t="n">
-        <v>27.52</v>
+        <v>24.3</v>
       </c>
       <c r="I27" t="n">
-        <v>1737.04</v>
+        <v>1809.09</v>
       </c>
       <c r="J27" t="n">
-        <v>1777.44</v>
+        <v>1839.38</v>
       </c>
       <c r="K27" t="n">
-        <v>1807.98</v>
+        <v>1847.63</v>
       </c>
       <c r="L27" t="n">
-        <v>1838.52</v>
+        <v>1855.88</v>
       </c>
       <c r="M27" t="n">
-        <v>1873.99</v>
+        <v>1875.15</v>
       </c>
       <c r="N27" t="n">
-        <v>1909.47</v>
+        <v>1894.43</v>
       </c>
       <c r="O27" t="n">
-        <v>1935.08</v>
+        <v>1891.66</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2789,68 +2787,68 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1861.42</v>
+        <v>1871.28</v>
       </c>
       <c r="C28" t="n">
-        <v>1877.03</v>
+        <v>1916.24</v>
       </c>
       <c r="D28" t="n">
-        <v>1852.73</v>
+        <v>1842.82</v>
       </c>
       <c r="E28" t="n">
-        <v>1871.51</v>
+        <v>1903.76</v>
       </c>
       <c r="F28" t="n">
-        <v>10.12</v>
+        <v>32.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0172</v>
       </c>
       <c r="H28" t="n">
-        <v>24.3</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>1809.09</v>
+        <v>1828.42</v>
       </c>
       <c r="J28" t="n">
-        <v>1839.38</v>
+        <v>1850.52</v>
       </c>
       <c r="K28" t="n">
-        <v>1847.63</v>
+        <v>1859.36</v>
       </c>
       <c r="L28" t="n">
-        <v>1855.88</v>
+        <v>1868.19</v>
       </c>
       <c r="M28" t="n">
-        <v>1875.15</v>
+        <v>1883.66</v>
       </c>
       <c r="N28" t="n">
-        <v>1894.43</v>
+        <v>1899.13</v>
       </c>
       <c r="O28" t="n">
-        <v>1891.66</v>
+        <v>1901.34</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
@@ -2859,82 +2857,86 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1871.28</v>
+        <v>1903.69</v>
       </c>
       <c r="C29" t="n">
-        <v>1916.24</v>
+        <v>1949.55</v>
       </c>
       <c r="D29" t="n">
-        <v>1842.82</v>
+        <v>1900.07</v>
       </c>
       <c r="E29" t="n">
-        <v>1903.76</v>
+        <v>1928.38</v>
       </c>
       <c r="F29" t="n">
-        <v>32.25</v>
+        <v>24.62</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0129</v>
       </c>
       <c r="H29" t="n">
-        <v>73.43000000000001</v>
+        <v>49.48</v>
       </c>
       <c r="I29" t="n">
-        <v>1828.42</v>
+        <v>1769.39</v>
       </c>
       <c r="J29" t="n">
-        <v>1850.52</v>
+        <v>1842.45</v>
       </c>
       <c r="K29" t="n">
-        <v>1859.36</v>
+        <v>1867.05</v>
       </c>
       <c r="L29" t="n">
-        <v>1868.19</v>
+        <v>1891.64</v>
       </c>
       <c r="M29" t="n">
-        <v>1883.66</v>
+        <v>1940.47</v>
       </c>
       <c r="N29" t="n">
-        <v>1899.13</v>
+        <v>1989.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1901.34</v>
+        <v>1989.67</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
@@ -2943,77 +2945,69 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1903.69</v>
+        <v>1928.2</v>
       </c>
       <c r="C30" t="n">
-        <v>1949.55</v>
+        <v>1955.15</v>
       </c>
       <c r="D30" t="n">
-        <v>1900.07</v>
+        <v>1909.61</v>
       </c>
       <c r="E30" t="n">
-        <v>1928.38</v>
+        <v>1933.49</v>
       </c>
       <c r="F30" t="n">
-        <v>24.62</v>
+        <v>5.11</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0026</v>
       </c>
       <c r="H30" t="n">
-        <v>49.48</v>
+        <v>45.54</v>
       </c>
       <c r="I30" t="n">
-        <v>1769.39</v>
+        <v>1850.58</v>
       </c>
       <c r="J30" t="n">
-        <v>1842.45</v>
+        <v>1880.69</v>
       </c>
       <c r="K30" t="n">
-        <v>1867.05</v>
+        <v>1903.64</v>
       </c>
       <c r="L30" t="n">
-        <v>1891.64</v>
+        <v>1926.6</v>
       </c>
       <c r="M30" t="n">
-        <v>1940.47</v>
+        <v>1953.12</v>
       </c>
       <c r="N30" t="n">
-        <v>1989.3</v>
+        <v>1979.65</v>
       </c>
       <c r="O30" t="n">
-        <v>1989.67</v>
+        <v>1999.03</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3026,12 +3020,12 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U30" s="8" t="n">
@@ -3050,79 +3044,81 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1928.2</v>
+        <v>1933.47</v>
       </c>
       <c r="C31" t="n">
-        <v>1955.15</v>
+        <v>1940.28</v>
       </c>
       <c r="D31" t="n">
-        <v>1909.61</v>
+        <v>1868.52</v>
       </c>
       <c r="E31" t="n">
-        <v>1933.49</v>
+        <v>1877.1</v>
       </c>
       <c r="F31" t="n">
-        <v>5.11</v>
+        <v>-56.39</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0292</v>
       </c>
       <c r="H31" t="n">
-        <v>45.54</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>1850.58</v>
+        <v>1864.07</v>
       </c>
       <c r="J31" t="n">
-        <v>1880.69</v>
+        <v>1888.51</v>
       </c>
       <c r="K31" t="n">
-        <v>1903.64</v>
+        <v>1910.72</v>
       </c>
       <c r="L31" t="n">
-        <v>1926.6</v>
+        <v>1932.93</v>
       </c>
       <c r="M31" t="n">
-        <v>1953.12</v>
+        <v>1956.26</v>
       </c>
       <c r="N31" t="n">
-        <v>1979.65</v>
+        <v>1979.58</v>
       </c>
       <c r="O31" t="n">
-        <v>1999.03</v>
+        <v>2000.68</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
@@ -3130,62 +3126,60 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1933.47</v>
+        <v>1877.1</v>
       </c>
       <c r="C32" t="n">
-        <v>1940.28</v>
+        <v>1907.54</v>
       </c>
       <c r="D32" t="n">
-        <v>1868.52</v>
+        <v>1846.82</v>
       </c>
       <c r="E32" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="F32" t="n">
-        <v>-56.39</v>
+        <v>-16.92</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0292</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>71.76000000000001</v>
+        <v>60.72</v>
       </c>
       <c r="I32" t="n">
-        <v>1864.07</v>
+        <v>1796.76</v>
       </c>
       <c r="J32" t="n">
-        <v>1888.51</v>
+        <v>1791.69</v>
       </c>
       <c r="K32" t="n">
-        <v>1910.72</v>
+        <v>1841.22</v>
       </c>
       <c r="L32" t="n">
-        <v>1932.93</v>
+        <v>1890.75</v>
       </c>
       <c r="M32" t="n">
-        <v>1956.26</v>
+        <v>1912.98</v>
       </c>
       <c r="N32" t="n">
-        <v>1979.58</v>
+        <v>1935.21</v>
       </c>
       <c r="O32" t="n">
-        <v>2000.68</v>
+        <v>2012.05</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
@@ -3212,50 +3206,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="C33" t="n">
-        <v>1907.54</v>
+        <v>1875.14</v>
       </c>
       <c r="D33" t="n">
-        <v>1846.82</v>
+        <v>1849.83</v>
       </c>
       <c r="E33" t="n">
-        <v>1860.18</v>
+        <v>1873.22</v>
       </c>
       <c r="F33" t="n">
-        <v>-16.92</v>
+        <v>13.05</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H33" t="n">
-        <v>60.72</v>
+        <v>25.32</v>
       </c>
       <c r="I33" t="n">
-        <v>1796.76</v>
+        <v>1786.1</v>
       </c>
       <c r="J33" t="n">
-        <v>1791.69</v>
+        <v>1790.95</v>
       </c>
       <c r="K33" t="n">
-        <v>1841.22</v>
+        <v>1829.82</v>
       </c>
       <c r="L33" t="n">
-        <v>1890.75</v>
+        <v>1868.68</v>
       </c>
       <c r="M33" t="n">
-        <v>1912.98</v>
+        <v>1890.54</v>
       </c>
       <c r="N33" t="n">
-        <v>1935.21</v>
+        <v>1912.39</v>
       </c>
       <c r="O33" t="n">
-        <v>2012.05</v>
+        <v>1968.26</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3263,14 +3257,12 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3287,55 +3279,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1860.18</v>
+        <v>1873.24</v>
       </c>
       <c r="C34" t="n">
-        <v>1875.14</v>
+        <v>1963.25</v>
       </c>
       <c r="D34" t="n">
-        <v>1849.83</v>
+        <v>1872.38</v>
       </c>
       <c r="E34" t="n">
-        <v>1873.22</v>
+        <v>1953.41</v>
       </c>
       <c r="F34" t="n">
-        <v>13.05</v>
+        <v>80.19</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0428</v>
       </c>
       <c r="H34" t="n">
-        <v>25.32</v>
+        <v>90.86</v>
       </c>
       <c r="I34" t="n">
-        <v>1786.1</v>
+        <v>1824.51</v>
       </c>
       <c r="J34" t="n">
-        <v>1790.95</v>
+        <v>1853.27</v>
       </c>
       <c r="K34" t="n">
-        <v>1829.82</v>
+        <v>1860.56</v>
       </c>
       <c r="L34" t="n">
-        <v>1868.68</v>
+        <v>1867.85</v>
       </c>
       <c r="M34" t="n">
-        <v>1890.54</v>
+        <v>1885.88</v>
       </c>
       <c r="N34" t="n">
-        <v>1912.39</v>
+        <v>1903.91</v>
       </c>
       <c r="O34" t="n">
-        <v>1968.26</v>
+        <v>1900.46</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3348,177 +3344,177 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1873.24</v>
+        <v>1953.41</v>
       </c>
       <c r="C35" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D35" t="n">
-        <v>1872.38</v>
+        <v>1882.42</v>
       </c>
       <c r="E35" t="n">
-        <v>1953.41</v>
+        <v>1890.61</v>
       </c>
       <c r="F35" t="n">
-        <v>80.19</v>
+        <v>-62.8</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0428</v>
+        <v>-0.0321</v>
       </c>
       <c r="H35" t="n">
-        <v>90.86</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>1824.51</v>
+        <v>1781.52</v>
       </c>
       <c r="J35" t="n">
-        <v>1853.27</v>
+        <v>1880.35</v>
       </c>
       <c r="K35" t="n">
-        <v>1860.56</v>
+        <v>1907.98</v>
       </c>
       <c r="L35" t="n">
-        <v>1867.85</v>
+        <v>1935.61</v>
       </c>
       <c r="M35" t="n">
-        <v>1885.88</v>
+        <v>1998.84</v>
       </c>
       <c r="N35" t="n">
-        <v>1903.91</v>
+        <v>2062.07</v>
       </c>
       <c r="O35" t="n">
-        <v>1900.46</v>
+        <v>2054.11</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1953.41</v>
+        <v>1890.63</v>
       </c>
       <c r="C36" t="n">
-        <v>1976.46</v>
+        <v>1926.5</v>
       </c>
       <c r="D36" t="n">
-        <v>1882.42</v>
+        <v>1856.34</v>
       </c>
       <c r="E36" t="n">
-        <v>1890.61</v>
+        <v>1919.95</v>
       </c>
       <c r="F36" t="n">
-        <v>-62.8</v>
+        <v>29.33</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0321</v>
+        <v>0.0155</v>
       </c>
       <c r="H36" t="n">
-        <v>94.04000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="I36" t="n">
-        <v>1781.52</v>
+        <v>1788.38</v>
       </c>
       <c r="J36" t="n">
-        <v>1880.35</v>
+        <v>1777.16</v>
       </c>
       <c r="K36" t="n">
-        <v>1907.98</v>
+        <v>1843.59</v>
       </c>
       <c r="L36" t="n">
-        <v>1935.61</v>
+        <v>1910.03</v>
       </c>
       <c r="M36" t="n">
-        <v>1998.84</v>
+        <v>1937.63</v>
       </c>
       <c r="N36" t="n">
-        <v>2062.07</v>
+        <v>1965.24</v>
       </c>
       <c r="O36" t="n">
-        <v>2054.11</v>
+        <v>2070.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3537,57 +3533,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1890.63</v>
+        <v>1919.99</v>
       </c>
       <c r="C37" t="n">
-        <v>1926.5</v>
+        <v>1929.9</v>
       </c>
       <c r="D37" t="n">
-        <v>1856.34</v>
+        <v>1873.62</v>
       </c>
       <c r="E37" t="n">
-        <v>1919.95</v>
+        <v>1908.52</v>
       </c>
       <c r="F37" t="n">
-        <v>29.33</v>
+        <v>-11.43</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.006</v>
       </c>
       <c r="H37" t="n">
-        <v>70.16</v>
+        <v>56.28</v>
       </c>
       <c r="I37" t="n">
-        <v>1788.38</v>
+        <v>1786.18</v>
       </c>
       <c r="J37" t="n">
-        <v>1777.16</v>
+        <v>1864.05</v>
       </c>
       <c r="K37" t="n">
-        <v>1843.59</v>
+        <v>1884.87</v>
       </c>
       <c r="L37" t="n">
-        <v>1910.03</v>
+        <v>1905.69</v>
       </c>
       <c r="M37" t="n">
-        <v>1937.63</v>
+        <v>1955.03</v>
       </c>
       <c r="N37" t="n">
-        <v>1965.24</v>
+        <v>2004.37</v>
       </c>
       <c r="O37" t="n">
-        <v>2070.5</v>
+        <v>1996.67</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3595,8 +3591,10 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
@@ -3619,57 +3617,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1919.99</v>
+        <v>1908.59</v>
       </c>
       <c r="C38" t="n">
-        <v>1929.9</v>
+        <v>1934.58</v>
       </c>
       <c r="D38" t="n">
-        <v>1873.62</v>
+        <v>1892.2</v>
       </c>
       <c r="E38" t="n">
-        <v>1908.52</v>
+        <v>1917.37</v>
       </c>
       <c r="F38" t="n">
-        <v>-11.43</v>
+        <v>8.85</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0046</v>
       </c>
       <c r="H38" t="n">
-        <v>56.28</v>
+        <v>42.38</v>
       </c>
       <c r="I38" t="n">
-        <v>1786.18</v>
+        <v>1817.34</v>
       </c>
       <c r="J38" t="n">
-        <v>1864.05</v>
+        <v>1855.62</v>
       </c>
       <c r="K38" t="n">
-        <v>1884.87</v>
+        <v>1880.38</v>
       </c>
       <c r="L38" t="n">
-        <v>1905.69</v>
+        <v>1905.14</v>
       </c>
       <c r="M38" t="n">
-        <v>1955.03</v>
+        <v>1936.66</v>
       </c>
       <c r="N38" t="n">
-        <v>2004.37</v>
+        <v>1968.18</v>
       </c>
       <c r="O38" t="n">
-        <v>1996.67</v>
+        <v>1986.18</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3677,10 +3675,8 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
@@ -3701,72 +3697,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1908.59</v>
+        <v>1917.14</v>
       </c>
       <c r="C39" t="n">
-        <v>1934.58</v>
+        <v>1933.78</v>
       </c>
       <c r="D39" t="n">
-        <v>1892.2</v>
+        <v>1847.47</v>
       </c>
       <c r="E39" t="n">
-        <v>1917.37</v>
+        <v>1860.35</v>
       </c>
       <c r="F39" t="n">
-        <v>8.85</v>
+        <v>-57.03</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0297</v>
       </c>
       <c r="H39" t="n">
-        <v>42.38</v>
+        <v>86.31</v>
       </c>
       <c r="I39" t="n">
-        <v>1817.34</v>
+        <v>1849.82</v>
       </c>
       <c r="J39" t="n">
-        <v>1855.62</v>
+        <v>1876.99</v>
       </c>
       <c r="K39" t="n">
-        <v>1880.38</v>
+        <v>1896.18</v>
       </c>
       <c r="L39" t="n">
-        <v>1905.14</v>
+        <v>1915.38</v>
       </c>
       <c r="M39" t="n">
-        <v>1936.66</v>
+        <v>1938.56</v>
       </c>
       <c r="N39" t="n">
-        <v>1968.18</v>
+        <v>1961.75</v>
       </c>
       <c r="O39" t="n">
-        <v>1986.18</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>1976.96</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3778,9 +3776,9 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
@@ -3788,64 +3786,60 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1917.14</v>
+        <v>1860.37</v>
       </c>
       <c r="C40" t="n">
-        <v>1933.78</v>
+        <v>1873.17</v>
       </c>
       <c r="D40" t="n">
-        <v>1847.47</v>
+        <v>1821.49</v>
       </c>
       <c r="E40" t="n">
-        <v>1860.35</v>
+        <v>1843.42</v>
       </c>
       <c r="F40" t="n">
-        <v>-57.03</v>
+        <v>-16.93</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0297</v>
+        <v>-0.0091</v>
       </c>
       <c r="H40" t="n">
-        <v>86.31</v>
+        <v>51.69</v>
       </c>
       <c r="I40" t="n">
-        <v>1849.82</v>
+        <v>1761.16</v>
       </c>
       <c r="J40" t="n">
-        <v>1876.99</v>
+        <v>1758.9</v>
       </c>
       <c r="K40" t="n">
-        <v>1896.18</v>
+        <v>1817.19</v>
       </c>
       <c r="L40" t="n">
-        <v>1915.38</v>
+        <v>1875.48</v>
       </c>
       <c r="M40" t="n">
-        <v>1938.56</v>
+        <v>1903.5</v>
       </c>
       <c r="N40" t="n">
-        <v>1961.75</v>
+        <v>1931.52</v>
       </c>
       <c r="O40" t="n">
-        <v>1976.96</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
+        <v>2020.09</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
@@ -3872,50 +3866,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1860.37</v>
+        <v>1843.42</v>
       </c>
       <c r="C41" t="n">
-        <v>1873.17</v>
+        <v>1895.77</v>
       </c>
       <c r="D41" t="n">
-        <v>1821.49</v>
+        <v>1842.15</v>
       </c>
       <c r="E41" t="n">
-        <v>1843.42</v>
+        <v>1882.52</v>
       </c>
       <c r="F41" t="n">
-        <v>-16.93</v>
+        <v>39.1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0212</v>
       </c>
       <c r="H41" t="n">
-        <v>51.69</v>
+        <v>53.61</v>
       </c>
       <c r="I41" t="n">
-        <v>1761.16</v>
+        <v>1769.8</v>
       </c>
       <c r="J41" t="n">
-        <v>1758.9</v>
+        <v>1789.78</v>
       </c>
       <c r="K41" t="n">
-        <v>1817.19</v>
+        <v>1817.57</v>
       </c>
       <c r="L41" t="n">
-        <v>1875.48</v>
+        <v>1845.37</v>
       </c>
       <c r="M41" t="n">
-        <v>1903.5</v>
+        <v>1869.26</v>
       </c>
       <c r="N41" t="n">
-        <v>1931.52</v>
+        <v>1893.15</v>
       </c>
       <c r="O41" t="n">
-        <v>2020.09</v>
+        <v>1924.86</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3923,22 +3917,24 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3947,80 +3943,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1843.42</v>
+        <v>1882.78</v>
       </c>
       <c r="C42" t="n">
-        <v>1895.77</v>
+        <v>1883.44</v>
       </c>
       <c r="D42" t="n">
-        <v>1842.15</v>
+        <v>1827.7</v>
       </c>
       <c r="E42" t="n">
-        <v>1882.52</v>
+        <v>1858.26</v>
       </c>
       <c r="F42" t="n">
-        <v>39.1</v>
+        <v>-24.27</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0129</v>
       </c>
       <c r="H42" t="n">
-        <v>53.61</v>
+        <v>55.74</v>
       </c>
       <c r="I42" t="n">
-        <v>1769.8</v>
+        <v>1788.54</v>
       </c>
       <c r="J42" t="n">
-        <v>1789.78</v>
+        <v>1835.69</v>
       </c>
       <c r="K42" t="n">
-        <v>1817.57</v>
+        <v>1855.72</v>
       </c>
       <c r="L42" t="n">
-        <v>1845.37</v>
+        <v>1875.74</v>
       </c>
       <c r="M42" t="n">
-        <v>1869.26</v>
+        <v>1909.33</v>
       </c>
       <c r="N42" t="n">
-        <v>1893.15</v>
+        <v>1942.91</v>
       </c>
       <c r="O42" t="n">
-        <v>1924.86</v>
+        <v>1949.38</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4029,76 +4029,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1882.78</v>
+        <v>1858.22</v>
       </c>
       <c r="C43" t="n">
-        <v>1883.44</v>
+        <v>1879.54</v>
       </c>
       <c r="D43" t="n">
-        <v>1827.7</v>
+        <v>1847.17</v>
       </c>
       <c r="E43" t="n">
-        <v>1858.26</v>
+        <v>1868.39</v>
       </c>
       <c r="F43" t="n">
-        <v>-24.27</v>
+        <v>10.13</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0055</v>
       </c>
       <c r="H43" t="n">
-        <v>55.74</v>
+        <v>32.36</v>
       </c>
       <c r="I43" t="n">
-        <v>1788.54</v>
+        <v>1771.96</v>
       </c>
       <c r="J43" t="n">
-        <v>1835.69</v>
+        <v>1803.86</v>
       </c>
       <c r="K43" t="n">
-        <v>1855.72</v>
+        <v>1830.39</v>
       </c>
       <c r="L43" t="n">
-        <v>1875.74</v>
+        <v>1856.91</v>
       </c>
       <c r="M43" t="n">
-        <v>1909.33</v>
+        <v>1886.13</v>
       </c>
       <c r="N43" t="n">
-        <v>1942.91</v>
+        <v>1915.34</v>
       </c>
       <c r="O43" t="n">
-        <v>1949.38</v>
+        <v>1939.18</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4115,55 +4107,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1858.22</v>
+        <v>1868.49</v>
       </c>
       <c r="C44" t="n">
-        <v>1879.54</v>
+        <v>1922.64</v>
       </c>
       <c r="D44" t="n">
-        <v>1847.17</v>
+        <v>1854.34</v>
       </c>
       <c r="E44" t="n">
-        <v>1868.39</v>
+        <v>1906.53</v>
       </c>
       <c r="F44" t="n">
-        <v>10.13</v>
+        <v>38.14</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0204</v>
       </c>
       <c r="H44" t="n">
-        <v>32.36</v>
+        <v>68.3</v>
       </c>
       <c r="I44" t="n">
-        <v>1771.96</v>
+        <v>1814.81</v>
       </c>
       <c r="J44" t="n">
-        <v>1803.86</v>
+        <v>1838.54</v>
       </c>
       <c r="K44" t="n">
-        <v>1830.39</v>
+        <v>1852.2</v>
       </c>
       <c r="L44" t="n">
-        <v>1856.91</v>
+        <v>1865.87</v>
       </c>
       <c r="M44" t="n">
-        <v>1886.13</v>
+        <v>1884.57</v>
       </c>
       <c r="N44" t="n">
-        <v>1915.34</v>
+        <v>1903.26</v>
       </c>
       <c r="O44" t="n">
-        <v>1939.18</v>
+        <v>1911.9</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4176,76 +4172,78 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1868.49</v>
+        <v>1906.44</v>
       </c>
       <c r="C45" t="n">
-        <v>1922.64</v>
+        <v>1917.7</v>
       </c>
       <c r="D45" t="n">
-        <v>1854.34</v>
+        <v>1890.96</v>
       </c>
       <c r="E45" t="n">
-        <v>1906.53</v>
+        <v>1902.06</v>
       </c>
       <c r="F45" t="n">
-        <v>38.14</v>
+        <v>-4.47</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.0023</v>
       </c>
       <c r="H45" t="n">
-        <v>68.3</v>
+        <v>26.74</v>
       </c>
       <c r="I45" t="n">
-        <v>1814.81</v>
+        <v>1786.04</v>
       </c>
       <c r="J45" t="n">
-        <v>1838.54</v>
+        <v>1847.24</v>
       </c>
       <c r="K45" t="n">
-        <v>1852.2</v>
+        <v>1872.38</v>
       </c>
       <c r="L45" t="n">
-        <v>1865.87</v>
+        <v>1897.51</v>
       </c>
       <c r="M45" t="n">
-        <v>1884.57</v>
+        <v>1940.68</v>
       </c>
       <c r="N45" t="n">
-        <v>1903.26</v>
+        <v>1983.84</v>
       </c>
       <c r="O45" t="n">
-        <v>1911.9</v>
+        <v>1990.94</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4258,78 +4256,76 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1906.44</v>
+        <v>1902.14</v>
       </c>
       <c r="C46" t="n">
-        <v>1917.7</v>
+        <v>1937.17</v>
       </c>
       <c r="D46" t="n">
-        <v>1890.96</v>
+        <v>1893.08</v>
       </c>
       <c r="E46" t="n">
-        <v>1902.06</v>
+        <v>1913.28</v>
       </c>
       <c r="F46" t="n">
-        <v>-4.47</v>
+        <v>11.22</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0059</v>
       </c>
       <c r="H46" t="n">
-        <v>26.74</v>
+        <v>44.08</v>
       </c>
       <c r="I46" t="n">
-        <v>1786.04</v>
+        <v>1864.23</v>
       </c>
       <c r="J46" t="n">
-        <v>1847.24</v>
+        <v>1874.18</v>
       </c>
       <c r="K46" t="n">
-        <v>1872.38</v>
+        <v>1888.69</v>
       </c>
       <c r="L46" t="n">
-        <v>1897.51</v>
+        <v>1903.19</v>
       </c>
       <c r="M46" t="n">
-        <v>1940.68</v>
+        <v>1915.43</v>
       </c>
       <c r="N46" t="n">
-        <v>1983.84</v>
+        <v>1927.66</v>
       </c>
       <c r="O46" t="n">
-        <v>1990.94</v>
+        <v>1944.44</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4342,14 +4338,18 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4359,59 +4359,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1902.14</v>
+        <v>1913.32</v>
       </c>
       <c r="C47" t="n">
-        <v>1937.17</v>
+        <v>1924.62</v>
       </c>
       <c r="D47" t="n">
-        <v>1893.08</v>
+        <v>1911.48</v>
       </c>
       <c r="E47" t="n">
-        <v>1913.28</v>
+        <v>1915.53</v>
       </c>
       <c r="F47" t="n">
-        <v>11.22</v>
+        <v>2.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0012</v>
       </c>
       <c r="H47" t="n">
-        <v>44.08</v>
+        <v>13.13</v>
       </c>
       <c r="I47" t="n">
-        <v>1864.23</v>
+        <v>1849</v>
       </c>
       <c r="J47" t="n">
-        <v>1874.18</v>
+        <v>1868.27</v>
       </c>
       <c r="K47" t="n">
-        <v>1888.69</v>
+        <v>1891.24</v>
       </c>
       <c r="L47" t="n">
-        <v>1903.19</v>
+        <v>1914.2</v>
       </c>
       <c r="M47" t="n">
-        <v>1915.43</v>
+        <v>1935.32</v>
       </c>
       <c r="N47" t="n">
-        <v>1927.66</v>
+        <v>1956.44</v>
       </c>
       <c r="O47" t="n">
-        <v>1944.44</v>
+        <v>1981.25</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4424,18 +4420,14 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4445,55 +4437,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1913.32</v>
+        <v>1915.46</v>
       </c>
       <c r="C48" t="n">
-        <v>1924.62</v>
+        <v>1935.53</v>
       </c>
       <c r="D48" t="n">
-        <v>1911.48</v>
+        <v>1907.03</v>
       </c>
       <c r="E48" t="n">
-        <v>1915.53</v>
+        <v>1908.68</v>
       </c>
       <c r="F48" t="n">
-        <v>2.25</v>
+        <v>-6.85</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0036</v>
       </c>
       <c r="H48" t="n">
-        <v>13.13</v>
+        <v>28.5</v>
       </c>
       <c r="I48" t="n">
-        <v>1849</v>
+        <v>1898.35</v>
       </c>
       <c r="J48" t="n">
-        <v>1868.27</v>
+        <v>1901.14</v>
       </c>
       <c r="K48" t="n">
-        <v>1891.24</v>
+        <v>1908.97</v>
       </c>
       <c r="L48" t="n">
-        <v>1914.2</v>
+        <v>1916.79</v>
       </c>
       <c r="M48" t="n">
-        <v>1935.32</v>
+        <v>1922.1</v>
       </c>
       <c r="N48" t="n">
-        <v>1956.44</v>
+        <v>1927.4</v>
       </c>
       <c r="O48" t="n">
-        <v>1981.25</v>
+        <v>1937.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4501,19 +4497,25 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4525,67 +4527,71 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1915.46</v>
+        <v>1908.72</v>
       </c>
       <c r="C49" t="n">
-        <v>1935.53</v>
+        <v>1928.99</v>
       </c>
       <c r="D49" t="n">
-        <v>1907.03</v>
+        <v>1866.79</v>
       </c>
       <c r="E49" t="n">
-        <v>1908.68</v>
+        <v>1871.28</v>
       </c>
       <c r="F49" t="n">
-        <v>-6.85</v>
+        <v>-37.4</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0196</v>
       </c>
       <c r="H49" t="n">
-        <v>28.5</v>
+        <v>62.2</v>
       </c>
       <c r="I49" t="n">
-        <v>1898.35</v>
+        <v>1878.52</v>
       </c>
       <c r="J49" t="n">
-        <v>1901.14</v>
+        <v>1873.88</v>
       </c>
       <c r="K49" t="n">
-        <v>1908.97</v>
+        <v>1894.43</v>
       </c>
       <c r="L49" t="n">
-        <v>1916.79</v>
+        <v>1914.98</v>
       </c>
       <c r="M49" t="n">
-        <v>1922.1</v>
+        <v>1922.93</v>
       </c>
       <c r="N49" t="n">
-        <v>1927.4</v>
+        <v>1930.89</v>
       </c>
       <c r="O49" t="n">
-        <v>1937.75</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+        <v>1964.03</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
@@ -4598,97 +4604,83 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1908.72</v>
+        <v>1871.26</v>
       </c>
       <c r="C50" t="n">
-        <v>1928.99</v>
+        <v>1895.75</v>
       </c>
       <c r="D50" t="n">
-        <v>1866.79</v>
+        <v>1852.84</v>
       </c>
       <c r="E50" t="n">
-        <v>1871.28</v>
+        <v>1881.37</v>
       </c>
       <c r="F50" t="n">
-        <v>-37.4</v>
+        <v>10.09</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0196</v>
+        <v>0.0054</v>
       </c>
       <c r="H50" t="n">
-        <v>62.2</v>
+        <v>42.91</v>
       </c>
       <c r="I50" t="n">
-        <v>1878.52</v>
+        <v>1804.59</v>
       </c>
       <c r="J50" t="n">
-        <v>1873.88</v>
+        <v>1795.77</v>
       </c>
       <c r="K50" t="n">
-        <v>1894.43</v>
+        <v>1840.18</v>
       </c>
       <c r="L50" t="n">
-        <v>1914.98</v>
+        <v>1884.59</v>
       </c>
       <c r="M50" t="n">
-        <v>1922.93</v>
+        <v>1902.38</v>
       </c>
       <c r="N50" t="n">
-        <v>1930.89</v>
+        <v>1920.18</v>
       </c>
       <c r="O50" t="n">
-        <v>1964.03</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>1991.2</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4701,55 +4693,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1871.26</v>
+        <v>1881.37</v>
       </c>
       <c r="C51" t="n">
-        <v>1895.75</v>
+        <v>1921.78</v>
       </c>
       <c r="D51" t="n">
-        <v>1852.84</v>
+        <v>1873.35</v>
       </c>
       <c r="E51" t="n">
-        <v>1881.37</v>
+        <v>1878.14</v>
       </c>
       <c r="F51" t="n">
-        <v>10.09</v>
+        <v>-3.24</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0017</v>
       </c>
       <c r="H51" t="n">
-        <v>42.91</v>
+        <v>48.43</v>
       </c>
       <c r="I51" t="n">
-        <v>1804.59</v>
+        <v>1809.93</v>
       </c>
       <c r="J51" t="n">
-        <v>1795.77</v>
+        <v>1842</v>
       </c>
       <c r="K51" t="n">
-        <v>1840.18</v>
+        <v>1859.92</v>
       </c>
       <c r="L51" t="n">
-        <v>1884.59</v>
+        <v>1877.83</v>
       </c>
       <c r="M51" t="n">
-        <v>1902.38</v>
+        <v>1902.83</v>
       </c>
       <c r="N51" t="n">
-        <v>1920.18</v>
+        <v>1927.82</v>
       </c>
       <c r="O51" t="n">
-        <v>1991.2</v>
+        <v>1938.66</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4760,13 +4756,15 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4781,57 +4779,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1881.37</v>
+        <v>1878.19</v>
       </c>
       <c r="C52" t="n">
-        <v>1921.78</v>
+        <v>1898.23</v>
       </c>
       <c r="D52" t="n">
-        <v>1873.35</v>
+        <v>1861.92</v>
       </c>
       <c r="E52" t="n">
-        <v>1878.14</v>
+        <v>1883.99</v>
       </c>
       <c r="F52" t="n">
-        <v>-3.24</v>
+        <v>5.86</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="H52" t="n">
-        <v>48.43</v>
+        <v>36.3</v>
       </c>
       <c r="I52" t="n">
-        <v>1809.93</v>
+        <v>1824.92</v>
       </c>
       <c r="J52" t="n">
-        <v>1842</v>
+        <v>1819.99</v>
       </c>
       <c r="K52" t="n">
-        <v>1859.92</v>
+        <v>1853.92</v>
       </c>
       <c r="L52" t="n">
-        <v>1877.83</v>
+        <v>1887.85</v>
       </c>
       <c r="M52" t="n">
-        <v>1902.83</v>
+        <v>1902.35</v>
       </c>
       <c r="N52" t="n">
-        <v>1927.82</v>
+        <v>1916.85</v>
       </c>
       <c r="O52" t="n">
-        <v>1938.66</v>
+        <v>1970.2</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4842,15 +4840,13 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4865,57 +4861,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1878.19</v>
+        <v>1884.02</v>
       </c>
       <c r="C53" t="n">
-        <v>1898.23</v>
+        <v>1889.27</v>
       </c>
       <c r="D53" t="n">
-        <v>1861.92</v>
+        <v>1862.56</v>
       </c>
       <c r="E53" t="n">
-        <v>1883.99</v>
+        <v>1880.65</v>
       </c>
       <c r="F53" t="n">
-        <v>5.86</v>
+        <v>-3.34</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0018</v>
       </c>
       <c r="H53" t="n">
-        <v>36.3</v>
+        <v>26.71</v>
       </c>
       <c r="I53" t="n">
-        <v>1824.92</v>
+        <v>1825.62</v>
       </c>
       <c r="J53" t="n">
-        <v>1819.99</v>
+        <v>1849.65</v>
       </c>
       <c r="K53" t="n">
-        <v>1853.92</v>
+        <v>1865.84</v>
       </c>
       <c r="L53" t="n">
-        <v>1887.85</v>
+        <v>1882.03</v>
       </c>
       <c r="M53" t="n">
-        <v>1902.35</v>
+        <v>1902.14</v>
       </c>
       <c r="N53" t="n">
-        <v>1916.85</v>
+        <v>1922.26</v>
       </c>
       <c r="O53" t="n">
-        <v>1970.2</v>
+        <v>1934.53</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4923,8 +4919,10 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
@@ -4954,50 +4952,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1884.02</v>
+        <v>1880.61</v>
       </c>
       <c r="C54" t="n">
-        <v>1889.27</v>
+        <v>1884.72</v>
       </c>
       <c r="D54" t="n">
-        <v>1862.56</v>
+        <v>1874.33</v>
       </c>
       <c r="E54" t="n">
-        <v>1880.65</v>
+        <v>1880.91</v>
       </c>
       <c r="F54" t="n">
-        <v>-3.34</v>
+        <v>0.26</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0001</v>
       </c>
       <c r="H54" t="n">
-        <v>26.71</v>
+        <v>10.39</v>
       </c>
       <c r="I54" t="n">
-        <v>1825.62</v>
+        <v>1835.86</v>
       </c>
       <c r="J54" t="n">
-        <v>1849.65</v>
+        <v>1856.31</v>
       </c>
       <c r="K54" t="n">
-        <v>1865.84</v>
+        <v>1867.3</v>
       </c>
       <c r="L54" t="n">
-        <v>1882.03</v>
+        <v>1878.28</v>
       </c>
       <c r="M54" t="n">
-        <v>1902.14</v>
+        <v>1894</v>
       </c>
       <c r="N54" t="n">
-        <v>1922.26</v>
+        <v>1909.72</v>
       </c>
       <c r="O54" t="n">
-        <v>1934.53</v>
+        <v>1915.98</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5005,14 +5003,12 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5031,74 +5027,80 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1880.61</v>
+        <v>1880.89</v>
       </c>
       <c r="C55" t="n">
-        <v>1884.72</v>
+        <v>1889.61</v>
       </c>
       <c r="D55" t="n">
-        <v>1874.33</v>
+        <v>1867.89</v>
       </c>
       <c r="E55" t="n">
-        <v>1880.91</v>
+        <v>1873.94</v>
       </c>
       <c r="F55" t="n">
-        <v>0.26</v>
+        <v>-6.97</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0037</v>
       </c>
       <c r="H55" t="n">
-        <v>10.39</v>
+        <v>21.71</v>
       </c>
       <c r="I55" t="n">
-        <v>1835.86</v>
+        <v>1863.94</v>
       </c>
       <c r="J55" t="n">
-        <v>1856.31</v>
+        <v>1871.21</v>
       </c>
       <c r="K55" t="n">
-        <v>1867.3</v>
+        <v>1875.71</v>
       </c>
       <c r="L55" t="n">
-        <v>1878.28</v>
+        <v>1880.22</v>
       </c>
       <c r="M55" t="n">
-        <v>1894</v>
+        <v>1886.1</v>
       </c>
       <c r="N55" t="n">
-        <v>1909.72</v>
+        <v>1891.99</v>
       </c>
       <c r="O55" t="n">
-        <v>1915.98</v>
+        <v>1895.11</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5113,145 +5115,141 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1880.89</v>
+        <v>1873.97</v>
       </c>
       <c r="C56" t="n">
-        <v>1889.61</v>
+        <v>1916.66</v>
       </c>
       <c r="D56" t="n">
-        <v>1867.89</v>
+        <v>1870.75</v>
       </c>
       <c r="E56" t="n">
-        <v>1873.94</v>
+        <v>1912.2</v>
       </c>
       <c r="F56" t="n">
-        <v>-6.97</v>
+        <v>38.26</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0204</v>
       </c>
       <c r="H56" t="n">
-        <v>21.71</v>
+        <v>45.91</v>
       </c>
       <c r="I56" t="n">
-        <v>1863.94</v>
+        <v>1846.18</v>
       </c>
       <c r="J56" t="n">
-        <v>1871.21</v>
+        <v>1849.83</v>
       </c>
       <c r="K56" t="n">
-        <v>1875.71</v>
+        <v>1863.09</v>
       </c>
       <c r="L56" t="n">
-        <v>1880.22</v>
+        <v>1876.35</v>
       </c>
       <c r="M56" t="n">
-        <v>1886.1</v>
+        <v>1884.8</v>
       </c>
       <c r="N56" t="n">
-        <v>1891.99</v>
+        <v>1893.25</v>
       </c>
       <c r="O56" t="n">
-        <v>1895.11</v>
+        <v>1911.32</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1873.97</v>
+        <v>1912.21</v>
       </c>
       <c r="C57" t="n">
-        <v>1916.66</v>
+        <v>1920.52</v>
       </c>
       <c r="D57" t="n">
-        <v>1870.75</v>
+        <v>1884.48</v>
       </c>
       <c r="E57" t="n">
-        <v>1912.2</v>
+        <v>1916.46</v>
       </c>
       <c r="F57" t="n">
-        <v>38.26</v>
+        <v>4.26</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.0022</v>
       </c>
       <c r="H57" t="n">
-        <v>45.91</v>
+        <v>36.05</v>
       </c>
       <c r="I57" t="n">
-        <v>1846.18</v>
+        <v>1824.84</v>
       </c>
       <c r="J57" t="n">
-        <v>1849.83</v>
+        <v>1875.54</v>
       </c>
       <c r="K57" t="n">
-        <v>1863.09</v>
+        <v>1889.25</v>
       </c>
       <c r="L57" t="n">
-        <v>1876.35</v>
+        <v>1902.95</v>
       </c>
       <c r="M57" t="n">
-        <v>1884.8</v>
+        <v>1935.16</v>
       </c>
       <c r="N57" t="n">
-        <v>1893.25</v>
+        <v>1967.36</v>
       </c>
       <c r="O57" t="n">
-        <v>1911.32</v>
+        <v>1962.57</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5259,28 +5257,24 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5292,50 +5286,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1912.21</v>
+        <v>1916.43</v>
       </c>
       <c r="C58" t="n">
-        <v>1920.52</v>
+        <v>2327.7</v>
       </c>
       <c r="D58" t="n">
-        <v>1884.48</v>
+        <v>1905.08</v>
       </c>
       <c r="E58" t="n">
-        <v>1916.46</v>
+        <v>2251.46</v>
       </c>
       <c r="F58" t="n">
-        <v>4.26</v>
+        <v>335</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.1748</v>
       </c>
       <c r="H58" t="n">
-        <v>36.05</v>
+        <v>422.62</v>
       </c>
       <c r="I58" t="n">
-        <v>1824.84</v>
+        <v>1848.43</v>
       </c>
       <c r="J58" t="n">
-        <v>1875.54</v>
+        <v>1887.39</v>
       </c>
       <c r="K58" t="n">
-        <v>1889.25</v>
+        <v>1898.44</v>
       </c>
       <c r="L58" t="n">
-        <v>1902.95</v>
+        <v>1909.48</v>
       </c>
       <c r="M58" t="n">
-        <v>1935.16</v>
+        <v>1934.48</v>
       </c>
       <c r="N58" t="n">
-        <v>1967.36</v>
+        <v>1959.48</v>
       </c>
       <c r="O58" t="n">
-        <v>1962.57</v>
+        <v>1956.57</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5343,24 +5337,28 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5372,50 +5370,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1916.43</v>
+        <v>2251.44</v>
       </c>
       <c r="C59" t="n">
-        <v>2327.7</v>
+        <v>2357.23</v>
       </c>
       <c r="D59" t="n">
-        <v>1905.08</v>
+        <v>2222.57</v>
       </c>
       <c r="E59" t="n">
-        <v>2251.46</v>
+        <v>2326.38</v>
       </c>
       <c r="F59" t="n">
-        <v>335</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.1748</v>
+        <v>0.0333</v>
       </c>
       <c r="H59" t="n">
-        <v>422.62</v>
+        <v>134.65</v>
       </c>
       <c r="I59" t="n">
-        <v>1848.43</v>
+        <v>1482.46</v>
       </c>
       <c r="J59" t="n">
-        <v>1887.39</v>
+        <v>1896.37</v>
       </c>
       <c r="K59" t="n">
-        <v>1898.44</v>
+        <v>2040.15</v>
       </c>
       <c r="L59" t="n">
-        <v>1909.48</v>
+        <v>2183.92</v>
       </c>
       <c r="M59" t="n">
-        <v>1934.48</v>
+        <v>2462.77</v>
       </c>
       <c r="N59" t="n">
-        <v>1959.48</v>
+        <v>2741.61</v>
       </c>
       <c r="O59" t="n">
-        <v>1956.57</v>
+        <v>2750.32</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5433,18 +5431,14 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
@@ -5456,50 +5450,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2251.44</v>
+        <v>2326.38</v>
       </c>
       <c r="C60" t="n">
-        <v>2357.23</v>
+        <v>2545.88</v>
       </c>
       <c r="D60" t="n">
-        <v>2222.57</v>
+        <v>2324.71</v>
       </c>
       <c r="E60" t="n">
-        <v>2326.38</v>
+        <v>2515.28</v>
       </c>
       <c r="F60" t="n">
-        <v>74.93000000000001</v>
+        <v>188.9</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0333</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>134.65</v>
+        <v>221.17</v>
       </c>
       <c r="I60" t="n">
-        <v>1482.46</v>
+        <v>2087.92</v>
       </c>
       <c r="J60" t="n">
-        <v>1896.37</v>
+        <v>2209.97</v>
       </c>
       <c r="K60" t="n">
-        <v>2040.15</v>
+        <v>2259.06</v>
       </c>
       <c r="L60" t="n">
-        <v>2183.92</v>
+        <v>2308.14</v>
       </c>
       <c r="M60" t="n">
-        <v>2462.77</v>
+        <v>2393.71</v>
       </c>
       <c r="N60" t="n">
-        <v>2741.61</v>
+        <v>2479.28</v>
       </c>
       <c r="O60" t="n">
-        <v>2750.32</v>
+        <v>2491.88</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5517,14 +5511,18 @@
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
@@ -5536,50 +5534,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2326.38</v>
+        <v>2515.39</v>
       </c>
       <c r="C61" t="n">
-        <v>2545.88</v>
+        <v>2528.9</v>
       </c>
       <c r="D61" t="n">
-        <v>2324.71</v>
+        <v>2389.9</v>
       </c>
       <c r="E61" t="n">
-        <v>2515.28</v>
+        <v>2424.25</v>
       </c>
       <c r="F61" t="n">
-        <v>188.9</v>
+        <v>-91.03</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0362</v>
       </c>
       <c r="H61" t="n">
-        <v>221.17</v>
+        <v>138.99</v>
       </c>
       <c r="I61" t="n">
-        <v>2087.92</v>
+        <v>2103.54</v>
       </c>
       <c r="J61" t="n">
-        <v>2209.97</v>
+        <v>2334.1</v>
       </c>
       <c r="K61" t="n">
-        <v>2259.06</v>
+        <v>2404.7</v>
       </c>
       <c r="L61" t="n">
-        <v>2308.14</v>
+        <v>2475.29</v>
       </c>
       <c r="M61" t="n">
-        <v>2393.71</v>
+        <v>2625.87</v>
       </c>
       <c r="N61" t="n">
-        <v>2479.28</v>
+        <v>2776.45</v>
       </c>
       <c r="O61" t="n">
-        <v>2491.88</v>
+        <v>2767.05</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5587,83 +5585,83 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2515.39</v>
+        <v>2424.22</v>
       </c>
       <c r="C62" t="n">
-        <v>2528.9</v>
+        <v>2483.93</v>
       </c>
       <c r="D62" t="n">
-        <v>2389.9</v>
+        <v>2357.14</v>
       </c>
       <c r="E62" t="n">
-        <v>2424.25</v>
+        <v>2463.82</v>
       </c>
       <c r="F62" t="n">
-        <v>-91.03</v>
+        <v>39.56</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0362</v>
+        <v>0.0163</v>
       </c>
       <c r="H62" t="n">
-        <v>138.99</v>
+        <v>126.79</v>
       </c>
       <c r="I62" t="n">
-        <v>2103.54</v>
+        <v>2250.91</v>
       </c>
       <c r="J62" t="n">
-        <v>2334.1</v>
+        <v>2267.68</v>
       </c>
       <c r="K62" t="n">
-        <v>2404.7</v>
+        <v>2354.75</v>
       </c>
       <c r="L62" t="n">
-        <v>2475.29</v>
+        <v>2441.83</v>
       </c>
       <c r="M62" t="n">
-        <v>2625.87</v>
+        <v>2493.75</v>
       </c>
       <c r="N62" t="n">
-        <v>2776.45</v>
+        <v>2545.67</v>
       </c>
       <c r="O62" t="n">
-        <v>2767.05</v>
+        <v>2667.89</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5671,14 +5669,12 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5704,50 +5700,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2424.22</v>
+        <v>2463.64</v>
       </c>
       <c r="C63" t="n">
-        <v>2483.93</v>
+        <v>2531.74</v>
       </c>
       <c r="D63" t="n">
-        <v>2357.14</v>
+        <v>2425.39</v>
       </c>
       <c r="E63" t="n">
-        <v>2463.82</v>
+        <v>2481.83</v>
       </c>
       <c r="F63" t="n">
-        <v>39.56</v>
+        <v>18.02</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0073</v>
       </c>
       <c r="H63" t="n">
-        <v>126.79</v>
+        <v>106.36</v>
       </c>
       <c r="I63" t="n">
-        <v>2250.91</v>
+        <v>2230.35</v>
       </c>
       <c r="J63" t="n">
-        <v>2267.68</v>
+        <v>2358.67</v>
       </c>
       <c r="K63" t="n">
-        <v>2354.75</v>
+        <v>2400.42</v>
       </c>
       <c r="L63" t="n">
-        <v>2441.83</v>
+        <v>2442.18</v>
       </c>
       <c r="M63" t="n">
-        <v>2493.75</v>
+        <v>2527.21</v>
       </c>
       <c r="N63" t="n">
-        <v>2545.67</v>
+        <v>2612.25</v>
       </c>
       <c r="O63" t="n">
-        <v>2667.89</v>
+        <v>2610.72</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5763,8 +5759,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T63" s="8" t="n">
-        <v/>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5777,59 +5775,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2463.64</v>
+        <v>2481.78</v>
       </c>
       <c r="C64" t="n">
-        <v>2531.74</v>
+        <v>2531.08</v>
       </c>
       <c r="D64" t="n">
-        <v>2425.39</v>
+        <v>2416.6</v>
       </c>
       <c r="E64" t="n">
-        <v>2481.83</v>
+        <v>2443.16</v>
       </c>
       <c r="F64" t="n">
-        <v>18.02</v>
+        <v>-38.67</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0156</v>
       </c>
       <c r="H64" t="n">
-        <v>106.36</v>
+        <v>114.48</v>
       </c>
       <c r="I64" t="n">
-        <v>2230.35</v>
+        <v>2319.03</v>
       </c>
       <c r="J64" t="n">
-        <v>2358.67</v>
+        <v>2377.11</v>
       </c>
       <c r="K64" t="n">
-        <v>2400.42</v>
+        <v>2428.65</v>
       </c>
       <c r="L64" t="n">
-        <v>2442.18</v>
+        <v>2480.2</v>
       </c>
       <c r="M64" t="n">
-        <v>2527.21</v>
+        <v>2535.01</v>
       </c>
       <c r="N64" t="n">
-        <v>2612.25</v>
+        <v>2589.82</v>
       </c>
       <c r="O64" t="n">
-        <v>2610.72</v>
+        <v>2638.1</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5837,18 +5831,18 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5861,55 +5855,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2481.78</v>
+        <v>2442.49</v>
       </c>
       <c r="C65" t="n">
-        <v>2531.08</v>
+        <v>2514.67</v>
       </c>
       <c r="D65" t="n">
-        <v>2416.6</v>
+        <v>2432.51</v>
       </c>
       <c r="E65" t="n">
-        <v>2443.16</v>
+        <v>2506.26</v>
       </c>
       <c r="F65" t="n">
-        <v>-38.67</v>
+        <v>63.1</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0258</v>
       </c>
       <c r="H65" t="n">
-        <v>114.48</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>2319.03</v>
+        <v>2302.12</v>
       </c>
       <c r="J65" t="n">
-        <v>2377.11</v>
+        <v>2313.34</v>
       </c>
       <c r="K65" t="n">
-        <v>2428.65</v>
+        <v>2385.92</v>
       </c>
       <c r="L65" t="n">
-        <v>2480.2</v>
+        <v>2458.5</v>
       </c>
       <c r="M65" t="n">
-        <v>2535.01</v>
+        <v>2500.4</v>
       </c>
       <c r="N65" t="n">
-        <v>2589.82</v>
+        <v>2542.3</v>
       </c>
       <c r="O65" t="n">
-        <v>2638.1</v>
+        <v>2645.57</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5917,19 +5915,19 @@
       <c r="Q65" s="6" t="n">
         <v/>
       </c>
-      <c r="R65" s="6" t="inlineStr">
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="n">
-        <v/>
-      </c>
       <c r="U65" s="8" t="n">
         <v/>
       </c>
@@ -5943,57 +5941,57 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2442.49</v>
+        <v>2506.24</v>
       </c>
       <c r="C66" t="n">
-        <v>2514.67</v>
+        <v>2564.27</v>
       </c>
       <c r="D66" t="n">
-        <v>2432.51</v>
+        <v>2481.94</v>
       </c>
       <c r="E66" t="n">
-        <v>2506.26</v>
+        <v>2510.41</v>
       </c>
       <c r="F66" t="n">
-        <v>63.1</v>
+        <v>4.15</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0258</v>
+        <v>0.0017</v>
       </c>
       <c r="H66" t="n">
-        <v>82.15000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="I66" t="n">
-        <v>2302.12</v>
+        <v>2350.36</v>
       </c>
       <c r="J66" t="n">
-        <v>2313.34</v>
+        <v>2440.44</v>
       </c>
       <c r="K66" t="n">
-        <v>2385.92</v>
+        <v>2465.18</v>
       </c>
       <c r="L66" t="n">
-        <v>2458.5</v>
+        <v>2489.93</v>
       </c>
       <c r="M66" t="n">
-        <v>2500.4</v>
+        <v>2547.34</v>
       </c>
       <c r="N66" t="n">
-        <v>2542.3</v>
+        <v>2604.75</v>
       </c>
       <c r="O66" t="n">
-        <v>2645.57</v>
+        <v>2596.82</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
@@ -6006,12 +6004,12 @@
       </c>
       <c r="S66" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T66" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U66" s="8" t="n">
@@ -6025,79 +6023,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2506.24</v>
+        <v>2510.67</v>
       </c>
       <c r="C67" t="n">
-        <v>2564.27</v>
+        <v>2534.01</v>
       </c>
       <c r="D67" t="n">
-        <v>2481.94</v>
+        <v>2408.72</v>
       </c>
       <c r="E67" t="n">
-        <v>2510.41</v>
+        <v>2442.54</v>
       </c>
       <c r="F67" t="n">
-        <v>4.15</v>
+        <v>-67.87</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.027</v>
       </c>
       <c r="H67" t="n">
-        <v>82.33</v>
+        <v>125.29</v>
       </c>
       <c r="I67" t="n">
-        <v>2350.36</v>
+        <v>2399.62</v>
       </c>
       <c r="J67" t="n">
-        <v>2440.44</v>
+        <v>2421.73</v>
       </c>
       <c r="K67" t="n">
-        <v>2465.18</v>
+        <v>2469.25</v>
       </c>
       <c r="L67" t="n">
-        <v>2489.93</v>
+        <v>2516.76</v>
       </c>
       <c r="M67" t="n">
-        <v>2547.34</v>
+        <v>2551.57</v>
       </c>
       <c r="N67" t="n">
-        <v>2604.75</v>
+        <v>2586.39</v>
       </c>
       <c r="O67" t="n">
-        <v>2596.82</v>
+        <v>2646.6</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
       </c>
-      <c r="Q67" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R67" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S67" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T67" s="8" t="inlineStr">
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="n">
+        <v/>
+      </c>
       <c r="U67" s="8" t="n">
         <v/>
       </c>
@@ -6109,72 +6105,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr"/>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2510.67</v>
+        <v>2442.56</v>
       </c>
       <c r="C68" t="n">
-        <v>2534.01</v>
+        <v>2459.63</v>
       </c>
       <c r="D68" t="n">
-        <v>2408.72</v>
+        <v>2430.81</v>
       </c>
       <c r="E68" t="n">
-        <v>2442.54</v>
+        <v>2457.69</v>
       </c>
       <c r="F68" t="n">
-        <v>-67.87</v>
+        <v>15.15</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.027</v>
+        <v>0.0062</v>
       </c>
       <c r="H68" t="n">
-        <v>125.29</v>
+        <v>28.82</v>
       </c>
       <c r="I68" t="n">
-        <v>2399.62</v>
+        <v>2283.43</v>
       </c>
       <c r="J68" t="n">
-        <v>2421.73</v>
+        <v>2302.83</v>
       </c>
       <c r="K68" t="n">
-        <v>2469.25</v>
+        <v>2379.89</v>
       </c>
       <c r="L68" t="n">
-        <v>2516.76</v>
+        <v>2456.95</v>
       </c>
       <c r="M68" t="n">
-        <v>2551.57</v>
+        <v>2505.18</v>
       </c>
       <c r="N68" t="n">
-        <v>2586.39</v>
+        <v>2553.41</v>
       </c>
       <c r="O68" t="n">
-        <v>2646.6</v>
+        <v>2659.3</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
       </c>
-      <c r="Q68" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R68" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S68" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S68" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T68" s="8" t="n">
@@ -6193,84 +6189,96 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2442.56</v>
+        <v>2457.69</v>
       </c>
       <c r="C69" t="n">
-        <v>2459.63</v>
+        <v>2532.96</v>
       </c>
       <c r="D69" t="n">
-        <v>2430.81</v>
+        <v>2389.47</v>
       </c>
       <c r="E69" t="n">
-        <v>2457.69</v>
+        <v>2417.94</v>
       </c>
       <c r="F69" t="n">
-        <v>15.15</v>
+        <v>-39.75</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H69" t="n">
-        <v>28.82</v>
+        <v>143.49</v>
       </c>
       <c r="I69" t="n">
-        <v>2283.43</v>
+        <v>2401.99</v>
       </c>
       <c r="J69" t="n">
-        <v>2302.83</v>
+        <v>2435.1</v>
       </c>
       <c r="K69" t="n">
-        <v>2379.89</v>
+        <v>2443.28</v>
       </c>
       <c r="L69" t="n">
-        <v>2456.95</v>
+        <v>2451.45</v>
       </c>
       <c r="M69" t="n">
-        <v>2505.18</v>
+        <v>2472.1</v>
       </c>
       <c r="N69" t="n">
-        <v>2553.41</v>
+        <v>2492.74</v>
       </c>
       <c r="O69" t="n">
-        <v>2659.3</v>
-      </c>
-      <c r="P69" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q69" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R69" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S69" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T69" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U69" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V69" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W69" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+        <v>2488.45</v>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S69" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W69" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -6282,85 +6290,75 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2457.69</v>
+        <v>2417.9</v>
       </c>
       <c r="C70" t="n">
-        <v>2532.96</v>
+        <v>2488.92</v>
       </c>
       <c r="D70" t="n">
-        <v>2389.47</v>
+        <v>2401.81</v>
       </c>
       <c r="E70" t="n">
-        <v>2417.94</v>
+        <v>2466.82</v>
       </c>
       <c r="F70" t="n">
-        <v>-39.75</v>
+        <v>48.88</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.0202</v>
       </c>
       <c r="H70" t="n">
-        <v>143.49</v>
+        <v>87.11</v>
       </c>
       <c r="I70" t="n">
-        <v>2401.99</v>
+        <v>2245.98</v>
       </c>
       <c r="J70" t="n">
-        <v>2435.1</v>
+        <v>2252.81</v>
       </c>
       <c r="K70" t="n">
-        <v>2443.28</v>
+        <v>2346.19</v>
       </c>
       <c r="L70" t="n">
-        <v>2451.45</v>
+        <v>2439.58</v>
       </c>
       <c r="M70" t="n">
-        <v>2472.1</v>
+        <v>2489.68</v>
       </c>
       <c r="N70" t="n">
-        <v>2492.74</v>
+        <v>2539.79</v>
       </c>
       <c r="O70" t="n">
-        <v>2488.45</v>
-      </c>
-      <c r="P70" s="6" t="inlineStr">
+        <v>2676.45</v>
+      </c>
+      <c r="P70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S70" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q70" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R70" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S70" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U70" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V70" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U70" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V70" s="8" t="n">
+        <v/>
       </c>
       <c r="W70" s="11" t="inlineStr">
         <is>
@@ -6369,77 +6367,79 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2417.9</v>
+        <v>2466.58</v>
       </c>
       <c r="C71" t="n">
-        <v>2488.92</v>
+        <v>2484.4</v>
       </c>
       <c r="D71" t="n">
-        <v>2401.81</v>
+        <v>2383.8</v>
       </c>
       <c r="E71" t="n">
-        <v>2466.82</v>
+        <v>2417.84</v>
       </c>
       <c r="F71" t="n">
-        <v>48.88</v>
+        <v>-48.98</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0202</v>
+        <v>-0.0199</v>
       </c>
       <c r="H71" t="n">
-        <v>87.11</v>
+        <v>100.6</v>
       </c>
       <c r="I71" t="n">
-        <v>2245.98</v>
+        <v>2314.69</v>
       </c>
       <c r="J71" t="n">
-        <v>2252.81</v>
+        <v>2390.43</v>
       </c>
       <c r="K71" t="n">
-        <v>2346.19</v>
+        <v>2423.26</v>
       </c>
       <c r="L71" t="n">
-        <v>2439.58</v>
+        <v>2456.09</v>
       </c>
       <c r="M71" t="n">
-        <v>2489.68</v>
+        <v>2510.38</v>
       </c>
       <c r="N71" t="n">
-        <v>2539.79</v>
+        <v>2564.66</v>
       </c>
       <c r="O71" t="n">
-        <v>2676.45</v>
+        <v>2576.04</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
       </c>
-      <c r="Q71" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R71" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S71" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="inlineStr">
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R71" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S71" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="n">
+        <v/>
+      </c>
       <c r="U71" s="8" t="n">
         <v/>
       </c>
@@ -6451,67 +6451,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2466.58</v>
+        <v>2417.83</v>
       </c>
       <c r="C72" t="n">
-        <v>2484.4</v>
+        <v>2427.4</v>
       </c>
       <c r="D72" t="n">
-        <v>2383.8</v>
+        <v>2356.19</v>
       </c>
       <c r="E72" t="n">
-        <v>2417.84</v>
+        <v>2391.5</v>
       </c>
       <c r="F72" t="n">
-        <v>-48.98</v>
+        <v>-26.34</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.0109</v>
       </c>
       <c r="H72" t="n">
-        <v>100.6</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>2314.69</v>
+        <v>2283.21</v>
       </c>
       <c r="J72" t="n">
-        <v>2390.43</v>
+        <v>2309.12</v>
       </c>
       <c r="K72" t="n">
-        <v>2423.26</v>
+        <v>2367.54</v>
       </c>
       <c r="L72" t="n">
-        <v>2456.09</v>
+        <v>2425.97</v>
       </c>
       <c r="M72" t="n">
-        <v>2510.38</v>
+        <v>2468.14</v>
       </c>
       <c r="N72" t="n">
-        <v>2564.66</v>
+        <v>2510.31</v>
       </c>
       <c r="O72" t="n">
-        <v>2576.04</v>
+        <v>2584.99</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
       </c>
-      <c r="Q72" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q72" s="6" t="n">
+        <v/>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
@@ -6542,50 +6536,50 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2417.83</v>
+        <v>2391.6</v>
       </c>
       <c r="C73" t="n">
-        <v>2427.4</v>
+        <v>2526.95</v>
       </c>
       <c r="D73" t="n">
-        <v>2356.19</v>
+        <v>2370.42</v>
       </c>
       <c r="E73" t="n">
-        <v>2391.5</v>
+        <v>2508.02</v>
       </c>
       <c r="F73" t="n">
-        <v>-26.34</v>
+        <v>116.52</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.0109</v>
+        <v>0.0487</v>
       </c>
       <c r="H73" t="n">
-        <v>71.20999999999999</v>
+        <v>156.53</v>
       </c>
       <c r="I73" t="n">
-        <v>2283.21</v>
+        <v>2284.97</v>
       </c>
       <c r="J73" t="n">
-        <v>2309.12</v>
+        <v>2320.14</v>
       </c>
       <c r="K73" t="n">
-        <v>2367.54</v>
+        <v>2355.89</v>
       </c>
       <c r="L73" t="n">
-        <v>2425.97</v>
+        <v>2391.65</v>
       </c>
       <c r="M73" t="n">
-        <v>2468.14</v>
+        <v>2427.11</v>
       </c>
       <c r="N73" t="n">
-        <v>2510.31</v>
+        <v>2462.57</v>
       </c>
       <c r="O73" t="n">
-        <v>2584.99</v>
+        <v>2498.61</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6593,28 +6587,32 @@
       <c r="Q73" s="6" t="n">
         <v/>
       </c>
-      <c r="R73" s="6" t="inlineStr">
+      <c r="R73" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V73" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S73" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U73" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V73" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W73" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W73" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X73" t="inlineStr"/>
@@ -6622,50 +6620,50 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2391.6</v>
+        <v>2508.02</v>
       </c>
       <c r="C74" t="n">
-        <v>2526.95</v>
+        <v>2545.62</v>
       </c>
       <c r="D74" t="n">
-        <v>2370.42</v>
+        <v>2432.35</v>
       </c>
       <c r="E74" t="n">
-        <v>2508.02</v>
+        <v>2456.08</v>
       </c>
       <c r="F74" t="n">
-        <v>116.52</v>
+        <v>-51.94</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.0487</v>
+        <v>-0.0207</v>
       </c>
       <c r="H74" t="n">
-        <v>156.53</v>
+        <v>113.27</v>
       </c>
       <c r="I74" t="n">
-        <v>2284.97</v>
+        <v>2213.88</v>
       </c>
       <c r="J74" t="n">
-        <v>2320.14</v>
+        <v>2381.16</v>
       </c>
       <c r="K74" t="n">
-        <v>2355.89</v>
+        <v>2429.75</v>
       </c>
       <c r="L74" t="n">
-        <v>2391.65</v>
+        <v>2478.35</v>
       </c>
       <c r="M74" t="n">
-        <v>2427.11</v>
+        <v>2586.29</v>
       </c>
       <c r="N74" t="n">
-        <v>2462.57</v>
+        <v>2694.22</v>
       </c>
       <c r="O74" t="n">
-        <v>2498.61</v>
+        <v>2683.48</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
@@ -6676,80 +6674,78 @@
       <c r="R74" s="6" t="n">
         <v/>
       </c>
-      <c r="S74" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U74" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V74" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S74" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U74" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V74" s="8" t="n">
+        <v/>
       </c>
       <c r="W74" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr"/>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2508.02</v>
+        <v>2455.99</v>
       </c>
       <c r="C75" t="n">
-        <v>2545.62</v>
+        <v>2492.01</v>
       </c>
       <c r="D75" t="n">
-        <v>2432.35</v>
+        <v>2445.69</v>
       </c>
       <c r="E75" t="n">
-        <v>2456.08</v>
+        <v>2480.74</v>
       </c>
       <c r="F75" t="n">
-        <v>-51.94</v>
+        <v>24.66</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0207</v>
+        <v>0.01</v>
       </c>
       <c r="H75" t="n">
-        <v>113.27</v>
+        <v>46.32</v>
       </c>
       <c r="I75" t="n">
-        <v>2213.88</v>
+        <v>2319.08</v>
       </c>
       <c r="J75" t="n">
-        <v>2381.16</v>
+        <v>2326.35</v>
       </c>
       <c r="K75" t="n">
-        <v>2429.75</v>
+        <v>2399.44</v>
       </c>
       <c r="L75" t="n">
-        <v>2478.35</v>
+        <v>2472.53</v>
       </c>
       <c r="M75" t="n">
-        <v>2586.29</v>
+        <v>2512.71</v>
       </c>
       <c r="N75" t="n">
-        <v>2694.22</v>
+        <v>2552.89</v>
       </c>
       <c r="O75" t="n">
-        <v>2683.48</v>
+        <v>2658.89</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
@@ -6760,9 +6756,9 @@
       <c r="R75" s="6" t="n">
         <v/>
       </c>
-      <c r="S75" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S75" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T75" s="8" t="n">
@@ -6788,50 +6784,50 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2455.99</v>
+        <v>2480.82</v>
       </c>
       <c r="C76" t="n">
-        <v>2492.01</v>
+        <v>2525.32</v>
       </c>
       <c r="D76" t="n">
-        <v>2445.69</v>
+        <v>2468.19</v>
       </c>
       <c r="E76" t="n">
-        <v>2480.74</v>
+        <v>2514.55</v>
       </c>
       <c r="F76" t="n">
-        <v>24.66</v>
+        <v>33.81</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0136</v>
       </c>
       <c r="H76" t="n">
-        <v>46.32</v>
+        <v>57.13</v>
       </c>
       <c r="I76" t="n">
-        <v>2319.08</v>
+        <v>2399.37</v>
       </c>
       <c r="J76" t="n">
-        <v>2326.35</v>
+        <v>2440.36</v>
       </c>
       <c r="K76" t="n">
-        <v>2399.44</v>
+        <v>2457.58</v>
       </c>
       <c r="L76" t="n">
-        <v>2472.53</v>
+        <v>2474.79</v>
       </c>
       <c r="M76" t="n">
-        <v>2512.71</v>
+        <v>2503.9</v>
       </c>
       <c r="N76" t="n">
-        <v>2552.89</v>
+        <v>2533</v>
       </c>
       <c r="O76" t="n">
-        <v>2658.89</v>
+        <v>2538.33</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
@@ -6844,11 +6840,13 @@
       </c>
       <c r="S76" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U76" s="8" t="n">
         <v/>
@@ -6861,59 +6859,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2480.82</v>
+        <v>2514.58</v>
       </c>
       <c r="C77" t="n">
-        <v>2525.32</v>
+        <v>2534.86</v>
       </c>
       <c r="D77" t="n">
-        <v>2468.19</v>
+        <v>2466.91</v>
       </c>
       <c r="E77" t="n">
-        <v>2514.55</v>
+        <v>2490.96</v>
       </c>
       <c r="F77" t="n">
-        <v>33.81</v>
+        <v>-23.59</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0094</v>
       </c>
       <c r="H77" t="n">
-        <v>57.13</v>
+        <v>67.95</v>
       </c>
       <c r="I77" t="n">
-        <v>2399.37</v>
+        <v>2411.07</v>
       </c>
       <c r="J77" t="n">
-        <v>2440.36</v>
+        <v>2466.32</v>
       </c>
       <c r="K77" t="n">
-        <v>2457.58</v>
+        <v>2485.99</v>
       </c>
       <c r="L77" t="n">
-        <v>2474.79</v>
+        <v>2505.65</v>
       </c>
       <c r="M77" t="n">
-        <v>2503.9</v>
+        <v>2543.11</v>
       </c>
       <c r="N77" t="n">
-        <v>2533</v>
+        <v>2580.57</v>
       </c>
       <c r="O77" t="n">
-        <v>2538.33</v>
+        <v>2582.45</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
@@ -6921,19 +6915,19 @@
       <c r="Q77" s="6" t="n">
         <v/>
       </c>
-      <c r="R77" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S77" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="inlineStr">
+      <c r="R77" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S77" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="n">
+        <v/>
+      </c>
       <c r="U77" s="8" t="n">
         <v/>
       </c>
@@ -6945,55 +6939,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr"/>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2514.58</v>
+        <v>2490.92</v>
       </c>
       <c r="C78" t="n">
-        <v>2534.86</v>
+        <v>2506.75</v>
       </c>
       <c r="D78" t="n">
-        <v>2466.91</v>
+        <v>2441.33</v>
       </c>
       <c r="E78" t="n">
-        <v>2490.96</v>
+        <v>2484.94</v>
       </c>
       <c r="F78" t="n">
-        <v>-23.59</v>
+        <v>-6.02</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0024</v>
       </c>
       <c r="H78" t="n">
-        <v>67.95</v>
+        <v>65.42</v>
       </c>
       <c r="I78" t="n">
-        <v>2411.07</v>
+        <v>2398.96</v>
       </c>
       <c r="J78" t="n">
-        <v>2466.32</v>
+        <v>2418.04</v>
       </c>
       <c r="K78" t="n">
-        <v>2485.99</v>
+        <v>2456.98</v>
       </c>
       <c r="L78" t="n">
-        <v>2505.65</v>
+        <v>2495.92</v>
       </c>
       <c r="M78" t="n">
-        <v>2543.11</v>
+        <v>2524.93</v>
       </c>
       <c r="N78" t="n">
-        <v>2580.57</v>
+        <v>2553.94</v>
       </c>
       <c r="O78" t="n">
-        <v>2582.45</v>
+        <v>2602.81</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -7003,12 +7001,12 @@
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T78" s="8" t="n">
@@ -7027,57 +7025,57 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2490.92</v>
+        <v>2484.89</v>
       </c>
       <c r="C79" t="n">
-        <v>2506.75</v>
+        <v>2522.37</v>
       </c>
       <c r="D79" t="n">
-        <v>2441.33</v>
+        <v>2443.7</v>
       </c>
       <c r="E79" t="n">
-        <v>2484.94</v>
+        <v>2466.91</v>
       </c>
       <c r="F79" t="n">
-        <v>-6.02</v>
+        <v>-18.03</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0073</v>
       </c>
       <c r="H79" t="n">
-        <v>65.42</v>
+        <v>78.67</v>
       </c>
       <c r="I79" t="n">
-        <v>2398.96</v>
+        <v>2375.9</v>
       </c>
       <c r="J79" t="n">
-        <v>2418.04</v>
+        <v>2424.97</v>
       </c>
       <c r="K79" t="n">
-        <v>2456.98</v>
+        <v>2452.23</v>
       </c>
       <c r="L79" t="n">
-        <v>2495.92</v>
+        <v>2479.49</v>
       </c>
       <c r="M79" t="n">
-        <v>2524.93</v>
+        <v>2517.65</v>
       </c>
       <c r="N79" t="n">
-        <v>2553.94</v>
+        <v>2555.82</v>
       </c>
       <c r="O79" t="n">
-        <v>2602.81</v>
+        <v>2572.18</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7095,8 +7093,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T79" s="8" t="n">
-        <v/>
+      <c r="T79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U79" s="8" t="n">
         <v/>
@@ -7111,57 +7111,57 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2484.89</v>
+        <v>2466.91</v>
       </c>
       <c r="C80" t="n">
-        <v>2522.37</v>
+        <v>2483.72</v>
       </c>
       <c r="D80" t="n">
-        <v>2443.7</v>
+        <v>2406.91</v>
       </c>
       <c r="E80" t="n">
-        <v>2466.91</v>
+        <v>2437.1</v>
       </c>
       <c r="F80" t="n">
-        <v>-18.03</v>
+        <v>-29.82</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0121</v>
       </c>
       <c r="H80" t="n">
-        <v>78.67</v>
+        <v>76.81</v>
       </c>
       <c r="I80" t="n">
-        <v>2375.9</v>
+        <v>2365.04</v>
       </c>
       <c r="J80" t="n">
-        <v>2424.97</v>
+        <v>2380.19</v>
       </c>
       <c r="K80" t="n">
-        <v>2452.23</v>
+        <v>2427.58</v>
       </c>
       <c r="L80" t="n">
-        <v>2479.49</v>
+        <v>2474.97</v>
       </c>
       <c r="M80" t="n">
-        <v>2517.65</v>
+        <v>2506.25</v>
       </c>
       <c r="N80" t="n">
-        <v>2555.82</v>
+        <v>2537.52</v>
       </c>
       <c r="O80" t="n">
-        <v>2572.18</v>
+        <v>2601.04</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7171,18 +7171,16 @@
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="n">
+        <v/>
       </c>
       <c r="U80" s="8" t="n">
         <v/>
@@ -7197,57 +7195,57 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2466.91</v>
+        <v>2437.14</v>
       </c>
       <c r="C81" t="n">
-        <v>2483.72</v>
+        <v>2663.05</v>
       </c>
       <c r="D81" t="n">
-        <v>2406.91</v>
+        <v>2435.29</v>
       </c>
       <c r="E81" t="n">
-        <v>2437.1</v>
+        <v>2514.73</v>
       </c>
       <c r="F81" t="n">
-        <v>-29.82</v>
+        <v>77.64</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0121</v>
+        <v>0.0319</v>
       </c>
       <c r="H81" t="n">
-        <v>76.81</v>
+        <v>227.76</v>
       </c>
       <c r="I81" t="n">
-        <v>2365.04</v>
+        <v>2330.09</v>
       </c>
       <c r="J81" t="n">
-        <v>2380.19</v>
+        <v>2356.18</v>
       </c>
       <c r="K81" t="n">
-        <v>2427.58</v>
+        <v>2398.69</v>
       </c>
       <c r="L81" t="n">
-        <v>2474.97</v>
+        <v>2441.21</v>
       </c>
       <c r="M81" t="n">
-        <v>2506.25</v>
+        <v>2475.51</v>
       </c>
       <c r="N81" t="n">
-        <v>2537.52</v>
+        <v>2509.8</v>
       </c>
       <c r="O81" t="n">
-        <v>2601.04</v>
+        <v>2560.53</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7255,83 +7253,83 @@
       <c r="Q81" s="6" t="n">
         <v/>
       </c>
-      <c r="R81" s="6" t="inlineStr">
+      <c r="R81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S81" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U81" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S81" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U81" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V81" s="8" t="n">
-        <v/>
+      <c r="V81" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W81" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2437.14</v>
+        <v>2514.77</v>
       </c>
       <c r="C82" t="n">
-        <v>2663.05</v>
+        <v>2544.47</v>
       </c>
       <c r="D82" t="n">
-        <v>2435.29</v>
+        <v>2508.8</v>
       </c>
       <c r="E82" t="n">
-        <v>2514.73</v>
+        <v>2525.94</v>
       </c>
       <c r="F82" t="n">
-        <v>77.64</v>
+        <v>11.21</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.0319</v>
+        <v>0.0045</v>
       </c>
       <c r="H82" t="n">
-        <v>227.76</v>
+        <v>35.67</v>
       </c>
       <c r="I82" t="n">
-        <v>2330.09</v>
+        <v>2207.52</v>
       </c>
       <c r="J82" t="n">
-        <v>2356.18</v>
+        <v>2269.75</v>
       </c>
       <c r="K82" t="n">
-        <v>2398.69</v>
+        <v>2400.85</v>
       </c>
       <c r="L82" t="n">
-        <v>2441.21</v>
+        <v>2531.95</v>
       </c>
       <c r="M82" t="n">
-        <v>2475.51</v>
+        <v>2628.62</v>
       </c>
       <c r="N82" t="n">
-        <v>2509.8</v>
+        <v>2725.28</v>
       </c>
       <c r="O82" t="n">
-        <v>2560.53</v>
+        <v>2890.82</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7342,93 +7340,97 @@
       <c r="R82" s="6" t="n">
         <v/>
       </c>
-      <c r="S82" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U82" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S82" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U82" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V82" s="8" t="n">
+        <v/>
       </c>
       <c r="W82" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr"/>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2514.77</v>
+        <v>2525.94</v>
       </c>
       <c r="C83" t="n">
-        <v>2544.47</v>
+        <v>2526.85</v>
       </c>
       <c r="D83" t="n">
-        <v>2508.8</v>
+        <v>2462.84</v>
       </c>
       <c r="E83" t="n">
-        <v>2525.94</v>
+        <v>2477.02</v>
       </c>
       <c r="F83" t="n">
-        <v>11.21</v>
+        <v>-48.92</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0194</v>
       </c>
       <c r="H83" t="n">
-        <v>35.67</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>2207.52</v>
+        <v>2473.13</v>
       </c>
       <c r="J83" t="n">
-        <v>2269.75</v>
+        <v>2489.93</v>
       </c>
       <c r="K83" t="n">
-        <v>2400.85</v>
+        <v>2508.11</v>
       </c>
       <c r="L83" t="n">
-        <v>2531.95</v>
+        <v>2526.29</v>
       </c>
       <c r="M83" t="n">
-        <v>2628.62</v>
+        <v>2543.78</v>
       </c>
       <c r="N83" t="n">
-        <v>2725.28</v>
+        <v>2561.27</v>
       </c>
       <c r="O83" t="n">
-        <v>2890.82</v>
-      </c>
-      <c r="P83" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q83" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R83" s="6" t="n">
-        <v/>
+        <v>2580.14</v>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R83" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T83" s="8" t="n">
@@ -7440,148 +7442,148 @@
       <c r="V83" s="8" t="n">
         <v/>
       </c>
-      <c r="W83" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W83" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2525.94</v>
+        <v>2476.6</v>
       </c>
       <c r="C84" t="n">
-        <v>2526.85</v>
+        <v>2612.4</v>
       </c>
       <c r="D84" t="n">
-        <v>2462.84</v>
+        <v>2465.43</v>
       </c>
       <c r="E84" t="n">
-        <v>2477.02</v>
+        <v>2514.41</v>
       </c>
       <c r="F84" t="n">
-        <v>-48.92</v>
+        <v>37.39</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0194</v>
+        <v>0.0151</v>
       </c>
       <c r="H84" t="n">
-        <v>64.01000000000001</v>
+        <v>146.98</v>
       </c>
       <c r="I84" t="n">
-        <v>2473.13</v>
+        <v>2398.83</v>
       </c>
       <c r="J84" t="n">
-        <v>2489.93</v>
+        <v>2404.09</v>
       </c>
       <c r="K84" t="n">
-        <v>2508.11</v>
+        <v>2445.01</v>
       </c>
       <c r="L84" t="n">
-        <v>2526.29</v>
+        <v>2485.93</v>
       </c>
       <c r="M84" t="n">
-        <v>2543.78</v>
+        <v>2509.03</v>
       </c>
       <c r="N84" t="n">
-        <v>2561.27</v>
+        <v>2532.12</v>
       </c>
       <c r="O84" t="n">
-        <v>2580.14</v>
-      </c>
-      <c r="P84" s="6" t="inlineStr">
+        <v>2590.87</v>
+      </c>
+      <c r="P84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R84" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S84" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q84" s="6" t="inlineStr">
+      <c r="U84" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R84" s="6" t="inlineStr">
+      <c r="V84" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S84" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U84" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V84" s="8" t="n">
-        <v/>
-      </c>
       <c r="W84" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr"/>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2476.6</v>
+        <v>2514.36</v>
       </c>
       <c r="C85" t="n">
-        <v>2612.4</v>
+        <v>2519.32</v>
       </c>
       <c r="D85" t="n">
-        <v>2465.43</v>
+        <v>2357.96</v>
       </c>
       <c r="E85" t="n">
-        <v>2514.41</v>
+        <v>2399.09</v>
       </c>
       <c r="F85" t="n">
-        <v>37.39</v>
+        <v>-115.32</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.0459</v>
       </c>
       <c r="H85" t="n">
-        <v>146.98</v>
+        <v>161.36</v>
       </c>
       <c r="I85" t="n">
-        <v>2398.83</v>
+        <v>2318.45</v>
       </c>
       <c r="J85" t="n">
-        <v>2404.09</v>
+        <v>2355.18</v>
       </c>
       <c r="K85" t="n">
-        <v>2445.01</v>
+        <v>2440.92</v>
       </c>
       <c r="L85" t="n">
-        <v>2485.93</v>
+        <v>2526.66</v>
       </c>
       <c r="M85" t="n">
-        <v>2509.03</v>
+        <v>2587.9</v>
       </c>
       <c r="N85" t="n">
-        <v>2532.12</v>
+        <v>2649.13</v>
       </c>
       <c r="O85" t="n">
-        <v>2590.87</v>
+        <v>2759.38</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7589,87 +7591,79 @@
       <c r="Q85" s="6" t="n">
         <v/>
       </c>
-      <c r="R85" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S85" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="inlineStr">
+      <c r="R85" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S85" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U85" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V85" s="8" t="n">
+        <v/>
       </c>
       <c r="W85" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2514.36</v>
+        <v>2399.06</v>
       </c>
       <c r="C86" t="n">
-        <v>2519.32</v>
+        <v>2426.93</v>
       </c>
       <c r="D86" t="n">
-        <v>2357.96</v>
+        <v>2368.74</v>
       </c>
       <c r="E86" t="n">
-        <v>2399.09</v>
+        <v>2416.12</v>
       </c>
       <c r="F86" t="n">
-        <v>-115.32</v>
+        <v>17.03</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.0459</v>
+        <v>0.0071</v>
       </c>
       <c r="H86" t="n">
-        <v>161.36</v>
+        <v>58.19</v>
       </c>
       <c r="I86" t="n">
-        <v>2318.45</v>
+        <v>2196.6</v>
       </c>
       <c r="J86" t="n">
-        <v>2355.18</v>
+        <v>2217.95</v>
       </c>
       <c r="K86" t="n">
-        <v>2440.92</v>
+        <v>2318.41</v>
       </c>
       <c r="L86" t="n">
-        <v>2526.66</v>
+        <v>2418.86</v>
       </c>
       <c r="M86" t="n">
-        <v>2587.9</v>
+        <v>2479.77</v>
       </c>
       <c r="N86" t="n">
-        <v>2649.13</v>
+        <v>2540.67</v>
       </c>
       <c r="O86" t="n">
-        <v>2759.38</v>
+        <v>2680.68</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7677,14 +7671,12 @@
       <c r="Q86" s="6" t="n">
         <v/>
       </c>
-      <c r="R86" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R86" s="6" t="n">
+        <v/>
       </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T86" s="8" t="n">
@@ -7701,55 +7693,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr"/>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2399.06</v>
+        <v>2416.17</v>
       </c>
       <c r="C87" t="n">
-        <v>2426.93</v>
+        <v>2480.74</v>
       </c>
       <c r="D87" t="n">
-        <v>2368.74</v>
+        <v>2412.19</v>
       </c>
       <c r="E87" t="n">
-        <v>2416.12</v>
+        <v>2447.11</v>
       </c>
       <c r="F87" t="n">
-        <v>17.03</v>
+        <v>30.99</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0128</v>
       </c>
       <c r="H87" t="n">
-        <v>58.19</v>
+        <v>68.55</v>
       </c>
       <c r="I87" t="n">
-        <v>2196.6</v>
+        <v>2310.54</v>
       </c>
       <c r="J87" t="n">
-        <v>2217.95</v>
+        <v>2367.07</v>
       </c>
       <c r="K87" t="n">
-        <v>2318.41</v>
+        <v>2387.02</v>
       </c>
       <c r="L87" t="n">
-        <v>2418.86</v>
+        <v>2406.98</v>
       </c>
       <c r="M87" t="n">
-        <v>2479.77</v>
+        <v>2445.22</v>
       </c>
       <c r="N87" t="n">
-        <v>2540.67</v>
+        <v>2483.46</v>
       </c>
       <c r="O87" t="n">
-        <v>2680.68</v>
+        <v>2485.12</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7760,13 +7756,15 @@
       <c r="R87" s="6" t="n">
         <v/>
       </c>
-      <c r="S87" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="n">
-        <v/>
+      <c r="S87" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U87" s="8" t="n">
         <v/>
@@ -7781,57 +7779,57 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2416.17</v>
+        <v>2447.11</v>
       </c>
       <c r="C88" t="n">
-        <v>2480.74</v>
+        <v>2643.96</v>
       </c>
       <c r="D88" t="n">
-        <v>2412.19</v>
+        <v>2435.15</v>
       </c>
       <c r="E88" t="n">
-        <v>2447.11</v>
+        <v>2611.35</v>
       </c>
       <c r="F88" t="n">
-        <v>30.99</v>
+        <v>164.24</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>68.55</v>
+        <v>208.81</v>
       </c>
       <c r="I88" t="n">
-        <v>2310.54</v>
+        <v>2343.64</v>
       </c>
       <c r="J88" t="n">
-        <v>2367.07</v>
+        <v>2378.88</v>
       </c>
       <c r="K88" t="n">
-        <v>2387.02</v>
+        <v>2412.83</v>
       </c>
       <c r="L88" t="n">
-        <v>2406.98</v>
+        <v>2446.78</v>
       </c>
       <c r="M88" t="n">
-        <v>2445.22</v>
+        <v>2481.38</v>
       </c>
       <c r="N88" t="n">
-        <v>2483.46</v>
+        <v>2515.98</v>
       </c>
       <c r="O88" t="n">
-        <v>2485.12</v>
+        <v>2549.29</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
@@ -7849,73 +7847,73 @@
       </c>
       <c r="T88" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U88" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V88" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W88" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W88" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2447.11</v>
+        <v>2611.46</v>
       </c>
       <c r="C89" t="n">
-        <v>2643.96</v>
+        <v>2659.72</v>
       </c>
       <c r="D89" t="n">
-        <v>2435.15</v>
+        <v>2602.74</v>
       </c>
       <c r="E89" t="n">
-        <v>2611.35</v>
+        <v>2631.96</v>
       </c>
       <c r="F89" t="n">
-        <v>164.24</v>
+        <v>20.62</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H89" t="n">
-        <v>208.81</v>
+        <v>56.98</v>
       </c>
       <c r="I89" t="n">
-        <v>2343.64</v>
+        <v>2226.33</v>
       </c>
       <c r="J89" t="n">
-        <v>2378.88</v>
+        <v>2438.43</v>
       </c>
       <c r="K89" t="n">
-        <v>2412.83</v>
+        <v>2506.94</v>
       </c>
       <c r="L89" t="n">
-        <v>2446.78</v>
+        <v>2575.45</v>
       </c>
       <c r="M89" t="n">
-        <v>2481.38</v>
+        <v>2715.75</v>
       </c>
       <c r="N89" t="n">
-        <v>2515.98</v>
+        <v>2856.06</v>
       </c>
       <c r="O89" t="n">
-        <v>2549.29</v>
+        <v>2852.78</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7928,23 +7926,17 @@
       </c>
       <c r="S89" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V89" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V89" s="8" t="n">
+        <v/>
       </c>
       <c r="W89" s="9" t="inlineStr">
         <is>
@@ -7956,59 +7948,63 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2611.46</v>
+        <v>2632.01</v>
       </c>
       <c r="C90" t="n">
-        <v>2659.72</v>
+        <v>2647.87</v>
       </c>
       <c r="D90" t="n">
-        <v>2602.74</v>
+        <v>2564.43</v>
       </c>
       <c r="E90" t="n">
-        <v>2631.96</v>
+        <v>2643</v>
       </c>
       <c r="F90" t="n">
-        <v>20.62</v>
+        <v>11.03</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0042</v>
       </c>
       <c r="H90" t="n">
-        <v>56.98</v>
+        <v>83.44</v>
       </c>
       <c r="I90" t="n">
-        <v>2226.33</v>
+        <v>2545.76</v>
       </c>
       <c r="J90" t="n">
-        <v>2438.43</v>
+        <v>2575.35</v>
       </c>
       <c r="K90" t="n">
-        <v>2506.94</v>
+        <v>2603.47</v>
       </c>
       <c r="L90" t="n">
-        <v>2575.45</v>
+        <v>2631.6</v>
       </c>
       <c r="M90" t="n">
-        <v>2715.75</v>
+        <v>2660.45</v>
       </c>
       <c r="N90" t="n">
-        <v>2856.06</v>
+        <v>2689.31</v>
       </c>
       <c r="O90" t="n">
-        <v>2852.78</v>
+        <v>2716.7</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
       </c>
-      <c r="Q90" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R90" s="6" t="n">
-        <v/>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S90" s="10" t="inlineStr">
         <is>
@@ -8029,93 +8025,95 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr"/>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2631.78</v>
+        <v>2644.8</v>
       </c>
       <c r="C91" t="n">
-        <v>2645.33</v>
+        <v>2804.96</v>
       </c>
       <c r="D91" t="n">
-        <v>2569.74</v>
+        <v>2644.8</v>
       </c>
       <c r="E91" t="n">
-        <v>2644.05</v>
+        <v>2770.86</v>
       </c>
       <c r="F91" t="n">
-        <v>12.09</v>
+        <v>127.86</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.0484</v>
       </c>
       <c r="H91" t="n">
-        <v>75.59</v>
+        <v>160.17</v>
       </c>
       <c r="I91" t="n">
-        <v>2545.76</v>
+        <v>2480.99</v>
       </c>
       <c r="J91" t="n">
-        <v>2575.35</v>
+        <v>2577.98</v>
       </c>
       <c r="K91" t="n">
-        <v>2603.47</v>
+        <v>2601.28</v>
       </c>
       <c r="L91" t="n">
-        <v>2631.6</v>
+        <v>2624.58</v>
       </c>
       <c r="M91" t="n">
-        <v>2660.45</v>
+        <v>2684.72</v>
       </c>
       <c r="N91" t="n">
-        <v>2689.31</v>
+        <v>2744.86</v>
       </c>
       <c r="O91" t="n">
-        <v>2716.7</v>
+        <v>2731.31</v>
       </c>
       <c r="P91" s="6" t="n">
         <v/>
       </c>
-      <c r="Q91" s="6" t="inlineStr">
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S91" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R91" s="6" t="inlineStr">
+      <c r="U91" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V91" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S91" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
-      </c>
       <c r="W91" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -634,58 +634,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1665.31</v>
+        <v>1619.89</v>
       </c>
       <c r="C2" t="n">
-        <v>1687.49</v>
+        <v>1656.65</v>
       </c>
       <c r="D2" t="n">
-        <v>1551.48</v>
+        <v>1531.78</v>
       </c>
       <c r="E2" t="n">
-        <v>1619.92</v>
+        <v>1564.82</v>
       </c>
       <c r="F2" t="n">
-        <v>-45.51</v>
+        <v>-55.11</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0273</v>
+        <v>-0.034</v>
       </c>
       <c r="H2" t="n">
-        <v>136.01</v>
+        <v>124.87</v>
       </c>
       <c r="I2" t="n">
-        <v>1542.89</v>
+        <v>1415.48</v>
       </c>
       <c r="J2" t="n">
-        <v>1559.83</v>
+        <v>1484.14</v>
       </c>
       <c r="K2" t="n">
-        <v>1617.76</v>
+        <v>1551.92</v>
       </c>
       <c r="L2" t="n">
-        <v>1675.68</v>
+        <v>1619.71</v>
       </c>
       <c r="M2" t="n">
-        <v>1713.12</v>
+        <v>1687.93</v>
       </c>
       <c r="N2" t="n">
-        <v>1750.55</v>
+        <v>1756.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1828.97</v>
+        <v>1823.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -720,50 +718,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1619.89</v>
+        <v>1564.61</v>
       </c>
       <c r="C3" t="n">
-        <v>1656.65</v>
+        <v>1590.2</v>
       </c>
       <c r="D3" t="n">
-        <v>1531.78</v>
+        <v>1510.51</v>
       </c>
       <c r="E3" t="n">
-        <v>1564.82</v>
+        <v>1576.62</v>
       </c>
       <c r="F3" t="n">
-        <v>-55.11</v>
+        <v>11.8</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.034</v>
+        <v>0.0075</v>
       </c>
       <c r="H3" t="n">
-        <v>124.87</v>
+        <v>79.69</v>
       </c>
       <c r="I3" t="n">
-        <v>1415.48</v>
+        <v>1406.91</v>
       </c>
       <c r="J3" t="n">
-        <v>1484.14</v>
+        <v>1425.25</v>
       </c>
       <c r="K3" t="n">
-        <v>1551.92</v>
+        <v>1502.38</v>
       </c>
       <c r="L3" t="n">
-        <v>1619.71</v>
+        <v>1579.52</v>
       </c>
       <c r="M3" t="n">
-        <v>1687.93</v>
+        <v>1627.25</v>
       </c>
       <c r="N3" t="n">
-        <v>1756.15</v>
+        <v>1674.98</v>
       </c>
       <c r="O3" t="n">
-        <v>1823.5</v>
+        <v>1781.51</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -771,14 +769,12 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -797,57 +793,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1564.61</v>
+        <v>1576.59</v>
       </c>
       <c r="C4" t="n">
-        <v>1590.2</v>
+        <v>1607.87</v>
       </c>
       <c r="D4" t="n">
-        <v>1510.51</v>
+        <v>1561.97</v>
       </c>
       <c r="E4" t="n">
-        <v>1576.62</v>
+        <v>1571.59</v>
       </c>
       <c r="F4" t="n">
-        <v>11.8</v>
+        <v>-5.03</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0032</v>
       </c>
       <c r="H4" t="n">
-        <v>79.69</v>
+        <v>45.89</v>
       </c>
       <c r="I4" t="n">
-        <v>1406.91</v>
+        <v>1430.81</v>
       </c>
       <c r="J4" t="n">
-        <v>1425.25</v>
+        <v>1510.05</v>
       </c>
       <c r="K4" t="n">
-        <v>1502.38</v>
+        <v>1536.77</v>
       </c>
       <c r="L4" t="n">
-        <v>1579.52</v>
+        <v>1563.48</v>
       </c>
       <c r="M4" t="n">
-        <v>1627.25</v>
+        <v>1616.46</v>
       </c>
       <c r="N4" t="n">
-        <v>1674.98</v>
+        <v>1669.44</v>
       </c>
       <c r="O4" t="n">
-        <v>1781.51</v>
+        <v>1669.89</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,9 +854,9 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -879,57 +875,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1576.59</v>
+        <v>1571.56</v>
       </c>
       <c r="C5" t="n">
-        <v>1607.87</v>
+        <v>1585.22</v>
       </c>
       <c r="D5" t="n">
-        <v>1561.97</v>
+        <v>1548.76</v>
       </c>
       <c r="E5" t="n">
-        <v>1571.59</v>
+        <v>1570.36</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.03</v>
+        <v>-1.23</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.0008</v>
       </c>
       <c r="H5" t="n">
-        <v>45.89</v>
+        <v>36.46</v>
       </c>
       <c r="I5" t="n">
-        <v>1430.81</v>
+        <v>1516.08</v>
       </c>
       <c r="J5" t="n">
-        <v>1510.05</v>
+        <v>1519.03</v>
       </c>
       <c r="K5" t="n">
-        <v>1536.77</v>
+        <v>1548.64</v>
       </c>
       <c r="L5" t="n">
-        <v>1563.48</v>
+        <v>1578.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1616.46</v>
+        <v>1594.53</v>
       </c>
       <c r="N5" t="n">
-        <v>1669.44</v>
+        <v>1610.82</v>
       </c>
       <c r="O5" t="n">
-        <v>1669.89</v>
+        <v>1653.76</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,9 +936,9 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -961,57 +957,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1571.56</v>
+        <v>1569.99</v>
       </c>
       <c r="C6" t="n">
-        <v>1585.22</v>
+        <v>1633.65</v>
       </c>
       <c r="D6" t="n">
-        <v>1548.76</v>
+        <v>1550.04</v>
       </c>
       <c r="E6" t="n">
-        <v>1570.36</v>
+        <v>1610.21</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.23</v>
+        <v>39.84</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0254</v>
       </c>
       <c r="H6" t="n">
-        <v>36.46</v>
+        <v>83.61</v>
       </c>
       <c r="I6" t="n">
-        <v>1516.08</v>
+        <v>1512.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1519.03</v>
+        <v>1535.59</v>
       </c>
       <c r="K6" t="n">
-        <v>1548.64</v>
+        <v>1552.13</v>
       </c>
       <c r="L6" t="n">
-        <v>1578.25</v>
+        <v>1568.68</v>
       </c>
       <c r="M6" t="n">
-        <v>1594.53</v>
+        <v>1588.59</v>
       </c>
       <c r="N6" t="n">
-        <v>1610.82</v>
+        <v>1608.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1653.76</v>
+        <v>1621.68</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,81 +1015,85 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1569.99</v>
+        <v>1610.16</v>
       </c>
       <c r="C7" t="n">
-        <v>1633.65</v>
+        <v>1611.35</v>
       </c>
       <c r="D7" t="n">
-        <v>1550.04</v>
+        <v>1549.25</v>
       </c>
       <c r="E7" t="n">
-        <v>1610.21</v>
+        <v>1569.58</v>
       </c>
       <c r="F7" t="n">
-        <v>39.84</v>
+        <v>-40.62</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0254</v>
+        <v>-0.0252</v>
       </c>
       <c r="H7" t="n">
-        <v>83.61</v>
+        <v>62.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1512.3</v>
+        <v>1466.43</v>
       </c>
       <c r="J7" t="n">
-        <v>1535.59</v>
+        <v>1535.78</v>
       </c>
       <c r="K7" t="n">
-        <v>1552.13</v>
+        <v>1568.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1568.68</v>
+        <v>1601.02</v>
       </c>
       <c r="M7" t="n">
-        <v>1588.59</v>
+        <v>1652.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1608.5</v>
+        <v>1703</v>
       </c>
       <c r="O7" t="n">
-        <v>1621.68</v>
+        <v>1717.25</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1103,83 +1103,81 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1610.16</v>
+        <v>1569.91</v>
       </c>
       <c r="C8" t="n">
-        <v>1611.35</v>
+        <v>1642.45</v>
       </c>
       <c r="D8" t="n">
-        <v>1549.25</v>
+        <v>1551.14</v>
       </c>
       <c r="E8" t="n">
-        <v>1569.58</v>
+        <v>1608.96</v>
       </c>
       <c r="F8" t="n">
-        <v>-40.62</v>
+        <v>39.38</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0252</v>
+        <v>0.0251</v>
       </c>
       <c r="H8" t="n">
-        <v>62.1</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1466.43</v>
+        <v>1487.16</v>
       </c>
       <c r="J8" t="n">
-        <v>1535.78</v>
+        <v>1502.13</v>
       </c>
       <c r="K8" t="n">
-        <v>1568.4</v>
+        <v>1538.54</v>
       </c>
       <c r="L8" t="n">
-        <v>1601.02</v>
+        <v>1574.94</v>
       </c>
       <c r="M8" t="n">
-        <v>1652.01</v>
+        <v>1600.63</v>
       </c>
       <c r="N8" t="n">
-        <v>1703</v>
+        <v>1626.32</v>
       </c>
       <c r="O8" t="n">
-        <v>1717.25</v>
+        <v>1673.44</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,21 +1185,23 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1211,59 +1211,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1569.91</v>
+        <v>1609.01</v>
       </c>
       <c r="C9" t="n">
-        <v>1642.45</v>
+        <v>1720.34</v>
       </c>
       <c r="D9" t="n">
-        <v>1551.14</v>
+        <v>1595.94</v>
       </c>
       <c r="E9" t="n">
-        <v>1608.96</v>
+        <v>1698.17</v>
       </c>
       <c r="F9" t="n">
-        <v>39.38</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0554</v>
       </c>
       <c r="H9" t="n">
-        <v>91.31999999999999</v>
+        <v>124.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1487.16</v>
+        <v>1459.82</v>
       </c>
       <c r="J9" t="n">
-        <v>1502.13</v>
+        <v>1523.73</v>
       </c>
       <c r="K9" t="n">
-        <v>1538.54</v>
+        <v>1563.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1574.94</v>
+        <v>1602.88</v>
       </c>
       <c r="M9" t="n">
-        <v>1600.63</v>
+        <v>1654.62</v>
       </c>
       <c r="N9" t="n">
-        <v>1626.32</v>
+        <v>1706.36</v>
       </c>
       <c r="O9" t="n">
-        <v>1673.44</v>
+        <v>1733.77</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1281,12 +1277,12 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V9" s="8" t="n">
@@ -1302,50 +1298,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1609.01</v>
+        <v>1698.42</v>
       </c>
       <c r="C10" t="n">
-        <v>1720.34</v>
+        <v>1772.54</v>
       </c>
       <c r="D10" t="n">
-        <v>1595.94</v>
+        <v>1693.04</v>
       </c>
       <c r="E10" t="n">
-        <v>1698.17</v>
+        <v>1756.52</v>
       </c>
       <c r="F10" t="n">
-        <v>89.20999999999999</v>
+        <v>58.35</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0344</v>
       </c>
       <c r="H10" t="n">
-        <v>124.4</v>
+        <v>79.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1459.82</v>
+        <v>1471.54</v>
       </c>
       <c r="J10" t="n">
-        <v>1523.73</v>
+        <v>1593.78</v>
       </c>
       <c r="K10" t="n">
-        <v>1563.3</v>
+        <v>1635.97</v>
       </c>
       <c r="L10" t="n">
-        <v>1602.88</v>
+        <v>1678.16</v>
       </c>
       <c r="M10" t="n">
-        <v>1654.62</v>
+        <v>1760.37</v>
       </c>
       <c r="N10" t="n">
-        <v>1706.36</v>
+        <v>1842.59</v>
       </c>
       <c r="O10" t="n">
-        <v>1733.77</v>
+        <v>1844.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1363,13 +1359,11 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1384,50 +1378,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1698.42</v>
+        <v>1756.58</v>
       </c>
       <c r="C11" t="n">
-        <v>1772.54</v>
+        <v>1804.59</v>
       </c>
       <c r="D11" t="n">
-        <v>1693.04</v>
+        <v>1743.56</v>
       </c>
       <c r="E11" t="n">
-        <v>1756.52</v>
+        <v>1779.03</v>
       </c>
       <c r="F11" t="n">
-        <v>58.35</v>
+        <v>22.51</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0128</v>
       </c>
       <c r="H11" t="n">
-        <v>79.5</v>
+        <v>61.02</v>
       </c>
       <c r="I11" t="n">
-        <v>1471.54</v>
+        <v>1613.53</v>
       </c>
       <c r="J11" t="n">
-        <v>1593.78</v>
+        <v>1688.88</v>
       </c>
       <c r="K11" t="n">
-        <v>1635.97</v>
+        <v>1716.77</v>
       </c>
       <c r="L11" t="n">
-        <v>1678.16</v>
+        <v>1744.65</v>
       </c>
       <c r="M11" t="n">
-        <v>1760.37</v>
+        <v>1796.27</v>
       </c>
       <c r="N11" t="n">
-        <v>1842.59</v>
+        <v>1847.89</v>
       </c>
       <c r="O11" t="n">
-        <v>1844.75</v>
+        <v>1852.05</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1464,50 +1458,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1756.58</v>
+        <v>1779.04</v>
       </c>
       <c r="C12" t="n">
-        <v>1804.59</v>
+        <v>1805.91</v>
       </c>
       <c r="D12" t="n">
-        <v>1743.56</v>
+        <v>1749.14</v>
       </c>
       <c r="E12" t="n">
-        <v>1779.03</v>
+        <v>1783.01</v>
       </c>
       <c r="F12" t="n">
-        <v>22.51</v>
+        <v>3.97</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0022</v>
       </c>
       <c r="H12" t="n">
-        <v>61.02</v>
+        <v>56.78</v>
       </c>
       <c r="I12" t="n">
-        <v>1613.53</v>
+        <v>1682.54</v>
       </c>
       <c r="J12" t="n">
-        <v>1688.88</v>
+        <v>1720.49</v>
       </c>
       <c r="K12" t="n">
-        <v>1716.77</v>
+        <v>1748.52</v>
       </c>
       <c r="L12" t="n">
-        <v>1744.65</v>
+        <v>1776.55</v>
       </c>
       <c r="M12" t="n">
-        <v>1796.27</v>
+        <v>1809.55</v>
       </c>
       <c r="N12" t="n">
-        <v>1847.89</v>
+        <v>1842.54</v>
       </c>
       <c r="O12" t="n">
-        <v>1852.05</v>
+        <v>1865.61</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1520,13 +1514,11 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1544,67 +1536,73 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779.04</v>
+        <v>1783</v>
       </c>
       <c r="C13" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D13" t="n">
-        <v>1749.14</v>
+        <v>1728.97</v>
       </c>
       <c r="E13" t="n">
-        <v>1783.01</v>
+        <v>1797.57</v>
       </c>
       <c r="F13" t="n">
-        <v>3.97</v>
+        <v>14.57</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>56.78</v>
+        <v>100.55</v>
       </c>
       <c r="I13" t="n">
-        <v>1682.54</v>
+        <v>1692.36</v>
       </c>
       <c r="J13" t="n">
-        <v>1720.49</v>
+        <v>1728.97</v>
       </c>
       <c r="K13" t="n">
-        <v>1748.52</v>
+        <v>1754.62</v>
       </c>
       <c r="L13" t="n">
-        <v>1776.55</v>
+        <v>1780.27</v>
       </c>
       <c r="M13" t="n">
-        <v>1809.55</v>
+        <v>1811.39</v>
       </c>
       <c r="N13" t="n">
-        <v>1842.54</v>
+        <v>1842.52</v>
       </c>
       <c r="O13" t="n">
-        <v>1865.61</v>
+        <v>1862.69</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1617,78 +1615,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1783</v>
+        <v>1797.56</v>
       </c>
       <c r="C14" t="n">
-        <v>1829.51</v>
+        <v>1810.33</v>
       </c>
       <c r="D14" t="n">
-        <v>1728.97</v>
+        <v>1756.71</v>
       </c>
       <c r="E14" t="n">
-        <v>1797.57</v>
+        <v>1768.51</v>
       </c>
       <c r="F14" t="n">
-        <v>14.57</v>
+        <v>-29.06</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0162</v>
       </c>
       <c r="H14" t="n">
-        <v>100.55</v>
+        <v>53.62</v>
       </c>
       <c r="I14" t="n">
-        <v>1692.36</v>
+        <v>1628.42</v>
       </c>
       <c r="J14" t="n">
-        <v>1728.97</v>
+        <v>1706.19</v>
       </c>
       <c r="K14" t="n">
-        <v>1754.62</v>
+        <v>1747.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1780.27</v>
+        <v>1788.41</v>
       </c>
       <c r="M14" t="n">
-        <v>1811.39</v>
+        <v>1847.85</v>
       </c>
       <c r="N14" t="n">
-        <v>1842.52</v>
+        <v>1907.29</v>
       </c>
       <c r="O14" t="n">
-        <v>1862.69</v>
+        <v>1930.06</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1703,57 +1699,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1797.56</v>
+        <v>1768.39</v>
       </c>
       <c r="C15" t="n">
-        <v>1810.33</v>
+        <v>1782.86</v>
       </c>
       <c r="D15" t="n">
-        <v>1756.71</v>
+        <v>1711.9</v>
       </c>
       <c r="E15" t="n">
-        <v>1768.51</v>
+        <v>1742.68</v>
       </c>
       <c r="F15" t="n">
-        <v>-29.06</v>
+        <v>-25.83</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0146</v>
       </c>
       <c r="H15" t="n">
-        <v>53.62</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>1628.42</v>
+        <v>1703.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1706.19</v>
+        <v>1707.39</v>
       </c>
       <c r="K15" t="n">
-        <v>1747.3</v>
+        <v>1741.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1788.41</v>
+        <v>1776.02</v>
       </c>
       <c r="M15" t="n">
-        <v>1847.85</v>
+        <v>1795.32</v>
       </c>
       <c r="N15" t="n">
-        <v>1907.29</v>
+        <v>1814.62</v>
       </c>
       <c r="O15" t="n">
-        <v>1930.06</v>
+        <v>1863.95</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1761,12 +1757,14 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1785,57 +1783,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1768.39</v>
+        <v>1742.66</v>
       </c>
       <c r="C16" t="n">
-        <v>1782.86</v>
+        <v>1760.21</v>
       </c>
       <c r="D16" t="n">
-        <v>1711.9</v>
+        <v>1721.3</v>
       </c>
       <c r="E16" t="n">
-        <v>1742.68</v>
+        <v>1744.48</v>
       </c>
       <c r="F16" t="n">
-        <v>-25.83</v>
+        <v>1.81</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>70.95999999999999</v>
+        <v>38.91</v>
       </c>
       <c r="I16" t="n">
-        <v>1703.1</v>
+        <v>1640.94</v>
       </c>
       <c r="J16" t="n">
-        <v>1707.39</v>
+        <v>1669.37</v>
       </c>
       <c r="K16" t="n">
-        <v>1741.7</v>
+        <v>1707.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1776.02</v>
+        <v>1745.03</v>
       </c>
       <c r="M16" t="n">
-        <v>1795.32</v>
+        <v>1778.16</v>
       </c>
       <c r="N16" t="n">
-        <v>1814.62</v>
+        <v>1811.29</v>
       </c>
       <c r="O16" t="n">
-        <v>1863.95</v>
+        <v>1853.82</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1843,14 +1841,12 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1869,57 +1865,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1742.66</v>
+        <v>1744.47</v>
       </c>
       <c r="C17" t="n">
-        <v>1760.21</v>
+        <v>1809.76</v>
       </c>
       <c r="D17" t="n">
-        <v>1721.3</v>
+        <v>1736.72</v>
       </c>
       <c r="E17" t="n">
-        <v>1744.48</v>
+        <v>1795.69</v>
       </c>
       <c r="F17" t="n">
-        <v>1.81</v>
+        <v>51.21</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0294</v>
       </c>
       <c r="H17" t="n">
-        <v>38.91</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>1640.94</v>
+        <v>1682.39</v>
       </c>
       <c r="J17" t="n">
-        <v>1669.37</v>
+        <v>1707.44</v>
       </c>
       <c r="K17" t="n">
-        <v>1707.2</v>
+        <v>1725.03</v>
       </c>
       <c r="L17" t="n">
-        <v>1745.03</v>
+        <v>1742.62</v>
       </c>
       <c r="M17" t="n">
-        <v>1778.16</v>
+        <v>1763.94</v>
       </c>
       <c r="N17" t="n">
-        <v>1811.29</v>
+        <v>1785.26</v>
       </c>
       <c r="O17" t="n">
-        <v>1853.82</v>
+        <v>1799.11</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1930,78 +1926,80 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1744.47</v>
+        <v>1795.82</v>
       </c>
       <c r="C18" t="n">
-        <v>1809.76</v>
+        <v>1827.83</v>
       </c>
       <c r="D18" t="n">
-        <v>1736.72</v>
+        <v>1786.3</v>
       </c>
       <c r="E18" t="n">
-        <v>1795.69</v>
+        <v>1788.1</v>
       </c>
       <c r="F18" t="n">
-        <v>51.21</v>
+        <v>-7.59</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0294</v>
+        <v>-0.0042</v>
       </c>
       <c r="H18" t="n">
-        <v>73.04000000000001</v>
+        <v>41.54</v>
       </c>
       <c r="I18" t="n">
-        <v>1682.39</v>
+        <v>1663.69</v>
       </c>
       <c r="J18" t="n">
-        <v>1707.44</v>
+        <v>1733.88</v>
       </c>
       <c r="K18" t="n">
-        <v>1725.03</v>
+        <v>1759.18</v>
       </c>
       <c r="L18" t="n">
-        <v>1742.62</v>
+        <v>1784.47</v>
       </c>
       <c r="M18" t="n">
-        <v>1763.94</v>
+        <v>1832.21</v>
       </c>
       <c r="N18" t="n">
-        <v>1785.26</v>
+        <v>1879.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1799.11</v>
+        <v>1882.79</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2014,78 +2012,76 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1795.82</v>
+        <v>1787.57</v>
       </c>
       <c r="C19" t="n">
-        <v>1827.83</v>
+        <v>1824.98</v>
       </c>
       <c r="D19" t="n">
-        <v>1786.3</v>
+        <v>1779.64</v>
       </c>
       <c r="E19" t="n">
-        <v>1788.1</v>
+        <v>1805.79</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.59</v>
+        <v>17.69</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>41.54</v>
+        <v>45.34</v>
       </c>
       <c r="I19" t="n">
-        <v>1663.69</v>
+        <v>1744.76</v>
       </c>
       <c r="J19" t="n">
-        <v>1733.88</v>
+        <v>1737.08</v>
       </c>
       <c r="K19" t="n">
-        <v>1759.18</v>
+        <v>1767.33</v>
       </c>
       <c r="L19" t="n">
-        <v>1784.47</v>
+        <v>1797.58</v>
       </c>
       <c r="M19" t="n">
-        <v>1832.21</v>
+        <v>1808.87</v>
       </c>
       <c r="N19" t="n">
-        <v>1879.95</v>
+        <v>1820.15</v>
       </c>
       <c r="O19" t="n">
-        <v>1882.79</v>
+        <v>1869.37</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2098,14 +2094,18 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2117,81 +2117,83 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1787.57</v>
+        <v>1805.76</v>
       </c>
       <c r="C20" t="n">
-        <v>1824.98</v>
+        <v>1842.46</v>
       </c>
       <c r="D20" t="n">
-        <v>1779.64</v>
+        <v>1749.35</v>
       </c>
       <c r="E20" t="n">
-        <v>1805.79</v>
+        <v>1773.5</v>
       </c>
       <c r="F20" t="n">
-        <v>17.69</v>
+        <v>-32.29</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.0179</v>
       </c>
       <c r="H20" t="n">
-        <v>45.34</v>
+        <v>93.11</v>
       </c>
       <c r="I20" t="n">
-        <v>1744.76</v>
+        <v>1734.29</v>
       </c>
       <c r="J20" t="n">
-        <v>1737.08</v>
+        <v>1762.18</v>
       </c>
       <c r="K20" t="n">
-        <v>1767.33</v>
+        <v>1783.12</v>
       </c>
       <c r="L20" t="n">
-        <v>1797.58</v>
+        <v>1804.05</v>
       </c>
       <c r="M20" t="n">
-        <v>1808.87</v>
+        <v>1828.46</v>
       </c>
       <c r="N20" t="n">
-        <v>1820.15</v>
+        <v>1852.87</v>
       </c>
       <c r="O20" t="n">
-        <v>1869.37</v>
+        <v>1870.32</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2210,77 +2212,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1805.76</v>
+        <v>1773.47</v>
       </c>
       <c r="C21" t="n">
-        <v>1842.46</v>
+        <v>1894.06</v>
       </c>
       <c r="D21" t="n">
-        <v>1749.35</v>
+        <v>1772.02</v>
       </c>
       <c r="E21" t="n">
-        <v>1773.5</v>
+        <v>1889.48</v>
       </c>
       <c r="F21" t="n">
-        <v>-32.29</v>
+        <v>115.98</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0654</v>
       </c>
       <c r="H21" t="n">
-        <v>93.11</v>
+        <v>122.04</v>
       </c>
       <c r="I21" t="n">
-        <v>1734.29</v>
+        <v>1656.24</v>
       </c>
       <c r="J21" t="n">
-        <v>1762.18</v>
+        <v>1669.19</v>
       </c>
       <c r="K21" t="n">
-        <v>1783.12</v>
+        <v>1726.95</v>
       </c>
       <c r="L21" t="n">
-        <v>1804.05</v>
+        <v>1784.7</v>
       </c>
       <c r="M21" t="n">
-        <v>1828.46</v>
+        <v>1820.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1852.87</v>
+        <v>1855.41</v>
       </c>
       <c r="O21" t="n">
-        <v>1870.32</v>
+        <v>1935.56</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2289,59 +2289,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1773.47</v>
+        <v>1889.5</v>
       </c>
       <c r="C22" t="n">
-        <v>1894.06</v>
+        <v>1944.16</v>
       </c>
       <c r="D22" t="n">
-        <v>1772.02</v>
+        <v>1863.64</v>
       </c>
       <c r="E22" t="n">
-        <v>1889.48</v>
+        <v>1916.94</v>
       </c>
       <c r="F22" t="n">
-        <v>115.98</v>
+        <v>27.46</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0654</v>
+        <v>0.0145</v>
       </c>
       <c r="H22" t="n">
-        <v>122.04</v>
+        <v>80.53</v>
       </c>
       <c r="I22" t="n">
-        <v>1656.24</v>
+        <v>1649.97</v>
       </c>
       <c r="J22" t="n">
-        <v>1669.19</v>
+        <v>1795.66</v>
       </c>
       <c r="K22" t="n">
-        <v>1726.95</v>
+        <v>1828.46</v>
       </c>
       <c r="L22" t="n">
-        <v>1784.7</v>
+        <v>1861.26</v>
       </c>
       <c r="M22" t="n">
-        <v>1820.05</v>
+        <v>1950.5</v>
       </c>
       <c r="N22" t="n">
-        <v>1855.41</v>
+        <v>2039.74</v>
       </c>
       <c r="O22" t="n">
-        <v>1935.56</v>
+        <v>2016.11</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2359,13 +2355,11 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2380,50 +2374,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1889.5</v>
+        <v>1916.98</v>
       </c>
       <c r="C23" t="n">
-        <v>1944.16</v>
+        <v>1927.09</v>
       </c>
       <c r="D23" t="n">
-        <v>1863.64</v>
+        <v>1856.78</v>
       </c>
       <c r="E23" t="n">
-        <v>1916.94</v>
+        <v>1863.19</v>
       </c>
       <c r="F23" t="n">
-        <v>27.46</v>
+        <v>-53.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0145</v>
+        <v>-0.028</v>
       </c>
       <c r="H23" t="n">
-        <v>80.53</v>
+        <v>70.31</v>
       </c>
       <c r="I23" t="n">
-        <v>1649.97</v>
+        <v>1783.11</v>
       </c>
       <c r="J23" t="n">
-        <v>1795.66</v>
+        <v>1842.94</v>
       </c>
       <c r="K23" t="n">
-        <v>1828.46</v>
+        <v>1876.68</v>
       </c>
       <c r="L23" t="n">
-        <v>1861.26</v>
+        <v>1910.42</v>
       </c>
       <c r="M23" t="n">
-        <v>1950.5</v>
+        <v>1957.21</v>
       </c>
       <c r="N23" t="n">
-        <v>2039.74</v>
+        <v>2003.99</v>
       </c>
       <c r="O23" t="n">
-        <v>2016.11</v>
+        <v>2024.69</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2431,19 +2425,19 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2455,55 +2449,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1916.98</v>
+        <v>1863.22</v>
       </c>
       <c r="C24" t="n">
-        <v>1927.09</v>
+        <v>1869.07</v>
       </c>
       <c r="D24" t="n">
-        <v>1856.78</v>
+        <v>1803.05</v>
       </c>
       <c r="E24" t="n">
-        <v>1863.19</v>
+        <v>1840.99</v>
       </c>
       <c r="F24" t="n">
-        <v>-53.75</v>
+        <v>-22.21</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.0119</v>
       </c>
       <c r="H24" t="n">
-        <v>70.31</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>1783.11</v>
+        <v>1786.47</v>
       </c>
       <c r="J24" t="n">
-        <v>1842.94</v>
+        <v>1778.51</v>
       </c>
       <c r="K24" t="n">
-        <v>1876.68</v>
+        <v>1828.04</v>
       </c>
       <c r="L24" t="n">
-        <v>1910.42</v>
+        <v>1877.56</v>
       </c>
       <c r="M24" t="n">
-        <v>1957.21</v>
+        <v>1898.35</v>
       </c>
       <c r="N24" t="n">
-        <v>2003.99</v>
+        <v>1919.13</v>
       </c>
       <c r="O24" t="n">
-        <v>2024.69</v>
+        <v>1997.4</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2544,50 +2542,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1863.22</v>
+        <v>1841.1</v>
       </c>
       <c r="C25" t="n">
-        <v>1869.07</v>
+        <v>1864.13</v>
       </c>
       <c r="D25" t="n">
-        <v>1803.05</v>
+        <v>1836.61</v>
       </c>
       <c r="E25" t="n">
-        <v>1840.99</v>
+        <v>1861.39</v>
       </c>
       <c r="F25" t="n">
-        <v>-22.21</v>
+        <v>20.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0111</v>
       </c>
       <c r="H25" t="n">
-        <v>66.01000000000001</v>
+        <v>27.52</v>
       </c>
       <c r="I25" t="n">
-        <v>1786.47</v>
+        <v>1737.04</v>
       </c>
       <c r="J25" t="n">
-        <v>1778.51</v>
+        <v>1777.44</v>
       </c>
       <c r="K25" t="n">
-        <v>1828.04</v>
+        <v>1807.98</v>
       </c>
       <c r="L25" t="n">
-        <v>1877.56</v>
+        <v>1838.52</v>
       </c>
       <c r="M25" t="n">
-        <v>1898.35</v>
+        <v>1873.99</v>
       </c>
       <c r="N25" t="n">
-        <v>1919.13</v>
+        <v>1909.47</v>
       </c>
       <c r="O25" t="n">
-        <v>1997.4</v>
+        <v>1935.08</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2595,19 +2593,19 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2621,57 +2619,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1841.1</v>
+        <v>1861.42</v>
       </c>
       <c r="C26" t="n">
-        <v>1864.13</v>
+        <v>1877.03</v>
       </c>
       <c r="D26" t="n">
-        <v>1836.61</v>
+        <v>1852.73</v>
       </c>
       <c r="E26" t="n">
-        <v>1861.39</v>
+        <v>1871.51</v>
       </c>
       <c r="F26" t="n">
-        <v>20.4</v>
+        <v>10.12</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0054</v>
       </c>
       <c r="H26" t="n">
-        <v>27.52</v>
+        <v>24.3</v>
       </c>
       <c r="I26" t="n">
-        <v>1737.04</v>
+        <v>1809.09</v>
       </c>
       <c r="J26" t="n">
-        <v>1777.44</v>
+        <v>1839.38</v>
       </c>
       <c r="K26" t="n">
-        <v>1807.98</v>
+        <v>1847.63</v>
       </c>
       <c r="L26" t="n">
-        <v>1838.52</v>
+        <v>1855.88</v>
       </c>
       <c r="M26" t="n">
-        <v>1873.99</v>
+        <v>1875.15</v>
       </c>
       <c r="N26" t="n">
-        <v>1909.47</v>
+        <v>1894.43</v>
       </c>
       <c r="O26" t="n">
-        <v>1935.08</v>
+        <v>1891.66</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2703,68 +2701,68 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1861.42</v>
+        <v>1871.28</v>
       </c>
       <c r="C27" t="n">
-        <v>1877.03</v>
+        <v>1916.24</v>
       </c>
       <c r="D27" t="n">
-        <v>1852.73</v>
+        <v>1842.82</v>
       </c>
       <c r="E27" t="n">
-        <v>1871.51</v>
+        <v>1903.76</v>
       </c>
       <c r="F27" t="n">
-        <v>10.12</v>
+        <v>32.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0172</v>
       </c>
       <c r="H27" t="n">
-        <v>24.3</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>1809.09</v>
+        <v>1828.42</v>
       </c>
       <c r="J27" t="n">
-        <v>1839.38</v>
+        <v>1850.52</v>
       </c>
       <c r="K27" t="n">
-        <v>1847.63</v>
+        <v>1859.36</v>
       </c>
       <c r="L27" t="n">
-        <v>1855.88</v>
+        <v>1868.19</v>
       </c>
       <c r="M27" t="n">
-        <v>1875.15</v>
+        <v>1883.66</v>
       </c>
       <c r="N27" t="n">
-        <v>1894.43</v>
+        <v>1899.13</v>
       </c>
       <c r="O27" t="n">
-        <v>1891.66</v>
+        <v>1901.34</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
@@ -2773,82 +2771,86 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1871.28</v>
+        <v>1903.69</v>
       </c>
       <c r="C28" t="n">
-        <v>1916.24</v>
+        <v>1949.55</v>
       </c>
       <c r="D28" t="n">
-        <v>1842.82</v>
+        <v>1900.07</v>
       </c>
       <c r="E28" t="n">
-        <v>1903.76</v>
+        <v>1928.38</v>
       </c>
       <c r="F28" t="n">
-        <v>32.25</v>
+        <v>24.62</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0129</v>
       </c>
       <c r="H28" t="n">
-        <v>73.43000000000001</v>
+        <v>49.48</v>
       </c>
       <c r="I28" t="n">
-        <v>1828.42</v>
+        <v>1769.39</v>
       </c>
       <c r="J28" t="n">
-        <v>1850.52</v>
+        <v>1842.45</v>
       </c>
       <c r="K28" t="n">
-        <v>1859.36</v>
+        <v>1867.05</v>
       </c>
       <c r="L28" t="n">
-        <v>1868.19</v>
+        <v>1891.64</v>
       </c>
       <c r="M28" t="n">
-        <v>1883.66</v>
+        <v>1940.47</v>
       </c>
       <c r="N28" t="n">
-        <v>1899.13</v>
+        <v>1989.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1901.34</v>
+        <v>1989.67</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
@@ -2857,77 +2859,69 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1903.69</v>
+        <v>1928.2</v>
       </c>
       <c r="C29" t="n">
-        <v>1949.55</v>
+        <v>1955.15</v>
       </c>
       <c r="D29" t="n">
-        <v>1900.07</v>
+        <v>1909.61</v>
       </c>
       <c r="E29" t="n">
-        <v>1928.38</v>
+        <v>1933.49</v>
       </c>
       <c r="F29" t="n">
-        <v>24.62</v>
+        <v>5.11</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0026</v>
       </c>
       <c r="H29" t="n">
-        <v>49.48</v>
+        <v>45.54</v>
       </c>
       <c r="I29" t="n">
-        <v>1769.39</v>
+        <v>1850.58</v>
       </c>
       <c r="J29" t="n">
-        <v>1842.45</v>
+        <v>1880.69</v>
       </c>
       <c r="K29" t="n">
-        <v>1867.05</v>
+        <v>1903.64</v>
       </c>
       <c r="L29" t="n">
-        <v>1891.64</v>
+        <v>1926.6</v>
       </c>
       <c r="M29" t="n">
-        <v>1940.47</v>
+        <v>1953.12</v>
       </c>
       <c r="N29" t="n">
-        <v>1989.3</v>
+        <v>1979.65</v>
       </c>
       <c r="O29" t="n">
-        <v>1989.67</v>
+        <v>1999.03</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2940,12 +2934,12 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U29" s="8" t="n">
@@ -2964,79 +2958,81 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1928.2</v>
+        <v>1933.47</v>
       </c>
       <c r="C30" t="n">
-        <v>1955.15</v>
+        <v>1940.28</v>
       </c>
       <c r="D30" t="n">
-        <v>1909.61</v>
+        <v>1868.52</v>
       </c>
       <c r="E30" t="n">
-        <v>1933.49</v>
+        <v>1877.1</v>
       </c>
       <c r="F30" t="n">
-        <v>5.11</v>
+        <v>-56.39</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0292</v>
       </c>
       <c r="H30" t="n">
-        <v>45.54</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>1850.58</v>
+        <v>1864.07</v>
       </c>
       <c r="J30" t="n">
-        <v>1880.69</v>
+        <v>1888.51</v>
       </c>
       <c r="K30" t="n">
-        <v>1903.64</v>
+        <v>1910.72</v>
       </c>
       <c r="L30" t="n">
-        <v>1926.6</v>
+        <v>1932.93</v>
       </c>
       <c r="M30" t="n">
-        <v>1953.12</v>
+        <v>1956.26</v>
       </c>
       <c r="N30" t="n">
-        <v>1979.65</v>
+        <v>1979.58</v>
       </c>
       <c r="O30" t="n">
-        <v>1999.03</v>
+        <v>2000.68</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -3044,62 +3040,60 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1933.47</v>
+        <v>1877.1</v>
       </c>
       <c r="C31" t="n">
-        <v>1940.28</v>
+        <v>1907.54</v>
       </c>
       <c r="D31" t="n">
-        <v>1868.52</v>
+        <v>1846.82</v>
       </c>
       <c r="E31" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="F31" t="n">
-        <v>-56.39</v>
+        <v>-16.92</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0292</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>71.76000000000001</v>
+        <v>60.72</v>
       </c>
       <c r="I31" t="n">
-        <v>1864.07</v>
+        <v>1796.76</v>
       </c>
       <c r="J31" t="n">
-        <v>1888.51</v>
+        <v>1791.69</v>
       </c>
       <c r="K31" t="n">
-        <v>1910.72</v>
+        <v>1841.22</v>
       </c>
       <c r="L31" t="n">
-        <v>1932.93</v>
+        <v>1890.75</v>
       </c>
       <c r="M31" t="n">
-        <v>1956.26</v>
+        <v>1912.98</v>
       </c>
       <c r="N31" t="n">
-        <v>1979.58</v>
+        <v>1935.21</v>
       </c>
       <c r="O31" t="n">
-        <v>2000.68</v>
+        <v>2012.05</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
@@ -3126,50 +3120,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="C32" t="n">
-        <v>1907.54</v>
+        <v>1875.14</v>
       </c>
       <c r="D32" t="n">
-        <v>1846.82</v>
+        <v>1849.83</v>
       </c>
       <c r="E32" t="n">
-        <v>1860.18</v>
+        <v>1873.22</v>
       </c>
       <c r="F32" t="n">
-        <v>-16.92</v>
+        <v>13.05</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H32" t="n">
-        <v>60.72</v>
+        <v>25.32</v>
       </c>
       <c r="I32" t="n">
-        <v>1796.76</v>
+        <v>1786.1</v>
       </c>
       <c r="J32" t="n">
-        <v>1791.69</v>
+        <v>1790.95</v>
       </c>
       <c r="K32" t="n">
-        <v>1841.22</v>
+        <v>1829.82</v>
       </c>
       <c r="L32" t="n">
-        <v>1890.75</v>
+        <v>1868.68</v>
       </c>
       <c r="M32" t="n">
-        <v>1912.98</v>
+        <v>1890.54</v>
       </c>
       <c r="N32" t="n">
-        <v>1935.21</v>
+        <v>1912.39</v>
       </c>
       <c r="O32" t="n">
-        <v>2012.05</v>
+        <v>1968.26</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3177,14 +3171,12 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3201,55 +3193,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1860.18</v>
+        <v>1873.24</v>
       </c>
       <c r="C33" t="n">
-        <v>1875.14</v>
+        <v>1963.25</v>
       </c>
       <c r="D33" t="n">
-        <v>1849.83</v>
+        <v>1872.38</v>
       </c>
       <c r="E33" t="n">
-        <v>1873.22</v>
+        <v>1953.41</v>
       </c>
       <c r="F33" t="n">
-        <v>13.05</v>
+        <v>80.19</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0428</v>
       </c>
       <c r="H33" t="n">
-        <v>25.32</v>
+        <v>90.86</v>
       </c>
       <c r="I33" t="n">
-        <v>1786.1</v>
+        <v>1824.51</v>
       </c>
       <c r="J33" t="n">
-        <v>1790.95</v>
+        <v>1853.27</v>
       </c>
       <c r="K33" t="n">
-        <v>1829.82</v>
+        <v>1860.56</v>
       </c>
       <c r="L33" t="n">
-        <v>1868.68</v>
+        <v>1867.85</v>
       </c>
       <c r="M33" t="n">
-        <v>1890.54</v>
+        <v>1885.88</v>
       </c>
       <c r="N33" t="n">
-        <v>1912.39</v>
+        <v>1903.91</v>
       </c>
       <c r="O33" t="n">
-        <v>1968.26</v>
+        <v>1900.46</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3262,177 +3258,177 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1873.24</v>
+        <v>1953.41</v>
       </c>
       <c r="C34" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D34" t="n">
-        <v>1872.38</v>
+        <v>1882.42</v>
       </c>
       <c r="E34" t="n">
-        <v>1953.41</v>
+        <v>1890.61</v>
       </c>
       <c r="F34" t="n">
-        <v>80.19</v>
+        <v>-62.8</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0428</v>
+        <v>-0.0321</v>
       </c>
       <c r="H34" t="n">
-        <v>90.86</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>1824.51</v>
+        <v>1781.52</v>
       </c>
       <c r="J34" t="n">
-        <v>1853.27</v>
+        <v>1880.35</v>
       </c>
       <c r="K34" t="n">
-        <v>1860.56</v>
+        <v>1907.98</v>
       </c>
       <c r="L34" t="n">
-        <v>1867.85</v>
+        <v>1935.61</v>
       </c>
       <c r="M34" t="n">
-        <v>1885.88</v>
+        <v>1998.84</v>
       </c>
       <c r="N34" t="n">
-        <v>1903.91</v>
+        <v>2062.07</v>
       </c>
       <c r="O34" t="n">
-        <v>1900.46</v>
+        <v>2054.11</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1953.41</v>
+        <v>1890.63</v>
       </c>
       <c r="C35" t="n">
-        <v>1976.46</v>
+        <v>1926.5</v>
       </c>
       <c r="D35" t="n">
-        <v>1882.42</v>
+        <v>1856.34</v>
       </c>
       <c r="E35" t="n">
-        <v>1890.61</v>
+        <v>1919.95</v>
       </c>
       <c r="F35" t="n">
-        <v>-62.8</v>
+        <v>29.33</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0321</v>
+        <v>0.0155</v>
       </c>
       <c r="H35" t="n">
-        <v>94.04000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="I35" t="n">
-        <v>1781.52</v>
+        <v>1788.38</v>
       </c>
       <c r="J35" t="n">
-        <v>1880.35</v>
+        <v>1777.16</v>
       </c>
       <c r="K35" t="n">
-        <v>1907.98</v>
+        <v>1843.59</v>
       </c>
       <c r="L35" t="n">
-        <v>1935.61</v>
+        <v>1910.03</v>
       </c>
       <c r="M35" t="n">
-        <v>1998.84</v>
+        <v>1937.63</v>
       </c>
       <c r="N35" t="n">
-        <v>2062.07</v>
+        <v>1965.24</v>
       </c>
       <c r="O35" t="n">
-        <v>2054.11</v>
+        <v>2070.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3451,57 +3447,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1890.63</v>
+        <v>1919.99</v>
       </c>
       <c r="C36" t="n">
-        <v>1926.5</v>
+        <v>1929.9</v>
       </c>
       <c r="D36" t="n">
-        <v>1856.34</v>
+        <v>1873.62</v>
       </c>
       <c r="E36" t="n">
-        <v>1919.95</v>
+        <v>1908.52</v>
       </c>
       <c r="F36" t="n">
-        <v>29.33</v>
+        <v>-11.43</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.006</v>
       </c>
       <c r="H36" t="n">
-        <v>70.16</v>
+        <v>56.28</v>
       </c>
       <c r="I36" t="n">
-        <v>1788.38</v>
+        <v>1786.18</v>
       </c>
       <c r="J36" t="n">
-        <v>1777.16</v>
+        <v>1864.05</v>
       </c>
       <c r="K36" t="n">
-        <v>1843.59</v>
+        <v>1884.87</v>
       </c>
       <c r="L36" t="n">
-        <v>1910.03</v>
+        <v>1905.69</v>
       </c>
       <c r="M36" t="n">
-        <v>1937.63</v>
+        <v>1955.03</v>
       </c>
       <c r="N36" t="n">
-        <v>1965.24</v>
+        <v>2004.37</v>
       </c>
       <c r="O36" t="n">
-        <v>2070.5</v>
+        <v>1996.67</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3509,8 +3505,10 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
@@ -3533,57 +3531,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1919.99</v>
+        <v>1908.59</v>
       </c>
       <c r="C37" t="n">
-        <v>1929.9</v>
+        <v>1934.58</v>
       </c>
       <c r="D37" t="n">
-        <v>1873.62</v>
+        <v>1892.2</v>
       </c>
       <c r="E37" t="n">
-        <v>1908.52</v>
+        <v>1917.37</v>
       </c>
       <c r="F37" t="n">
-        <v>-11.43</v>
+        <v>8.85</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0046</v>
       </c>
       <c r="H37" t="n">
-        <v>56.28</v>
+        <v>42.38</v>
       </c>
       <c r="I37" t="n">
-        <v>1786.18</v>
+        <v>1817.34</v>
       </c>
       <c r="J37" t="n">
-        <v>1864.05</v>
+        <v>1855.62</v>
       </c>
       <c r="K37" t="n">
-        <v>1884.87</v>
+        <v>1880.38</v>
       </c>
       <c r="L37" t="n">
-        <v>1905.69</v>
+        <v>1905.14</v>
       </c>
       <c r="M37" t="n">
-        <v>1955.03</v>
+        <v>1936.66</v>
       </c>
       <c r="N37" t="n">
-        <v>2004.37</v>
+        <v>1968.18</v>
       </c>
       <c r="O37" t="n">
-        <v>1996.67</v>
+        <v>1986.18</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3591,10 +3589,8 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
@@ -3615,72 +3611,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1908.59</v>
+        <v>1917.14</v>
       </c>
       <c r="C38" t="n">
-        <v>1934.58</v>
+        <v>1933.78</v>
       </c>
       <c r="D38" t="n">
-        <v>1892.2</v>
+        <v>1847.47</v>
       </c>
       <c r="E38" t="n">
-        <v>1917.37</v>
+        <v>1860.35</v>
       </c>
       <c r="F38" t="n">
-        <v>8.85</v>
+        <v>-57.03</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0297</v>
       </c>
       <c r="H38" t="n">
-        <v>42.38</v>
+        <v>86.31</v>
       </c>
       <c r="I38" t="n">
-        <v>1817.34</v>
+        <v>1849.82</v>
       </c>
       <c r="J38" t="n">
-        <v>1855.62</v>
+        <v>1876.99</v>
       </c>
       <c r="K38" t="n">
-        <v>1880.38</v>
+        <v>1896.18</v>
       </c>
       <c r="L38" t="n">
-        <v>1905.14</v>
+        <v>1915.38</v>
       </c>
       <c r="M38" t="n">
-        <v>1936.66</v>
+        <v>1938.56</v>
       </c>
       <c r="N38" t="n">
-        <v>1968.18</v>
+        <v>1961.75</v>
       </c>
       <c r="O38" t="n">
-        <v>1986.18</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>1976.96</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3692,9 +3690,9 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3702,64 +3700,60 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1917.14</v>
+        <v>1860.37</v>
       </c>
       <c r="C39" t="n">
-        <v>1933.78</v>
+        <v>1873.17</v>
       </c>
       <c r="D39" t="n">
-        <v>1847.47</v>
+        <v>1821.49</v>
       </c>
       <c r="E39" t="n">
-        <v>1860.35</v>
+        <v>1843.42</v>
       </c>
       <c r="F39" t="n">
-        <v>-57.03</v>
+        <v>-16.93</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0297</v>
+        <v>-0.0091</v>
       </c>
       <c r="H39" t="n">
-        <v>86.31</v>
+        <v>51.69</v>
       </c>
       <c r="I39" t="n">
-        <v>1849.82</v>
+        <v>1761.16</v>
       </c>
       <c r="J39" t="n">
-        <v>1876.99</v>
+        <v>1758.9</v>
       </c>
       <c r="K39" t="n">
-        <v>1896.18</v>
+        <v>1817.19</v>
       </c>
       <c r="L39" t="n">
-        <v>1915.38</v>
+        <v>1875.48</v>
       </c>
       <c r="M39" t="n">
-        <v>1938.56</v>
+        <v>1903.5</v>
       </c>
       <c r="N39" t="n">
-        <v>1961.75</v>
+        <v>1931.52</v>
       </c>
       <c r="O39" t="n">
-        <v>1976.96</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
+        <v>2020.09</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
@@ -3786,50 +3780,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1860.37</v>
+        <v>1843.42</v>
       </c>
       <c r="C40" t="n">
-        <v>1873.17</v>
+        <v>1895.77</v>
       </c>
       <c r="D40" t="n">
-        <v>1821.49</v>
+        <v>1842.15</v>
       </c>
       <c r="E40" t="n">
-        <v>1843.42</v>
+        <v>1882.52</v>
       </c>
       <c r="F40" t="n">
-        <v>-16.93</v>
+        <v>39.1</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0212</v>
       </c>
       <c r="H40" t="n">
-        <v>51.69</v>
+        <v>53.61</v>
       </c>
       <c r="I40" t="n">
-        <v>1761.16</v>
+        <v>1769.8</v>
       </c>
       <c r="J40" t="n">
-        <v>1758.9</v>
+        <v>1789.78</v>
       </c>
       <c r="K40" t="n">
-        <v>1817.19</v>
+        <v>1817.57</v>
       </c>
       <c r="L40" t="n">
-        <v>1875.48</v>
+        <v>1845.37</v>
       </c>
       <c r="M40" t="n">
-        <v>1903.5</v>
+        <v>1869.26</v>
       </c>
       <c r="N40" t="n">
-        <v>1931.52</v>
+        <v>1893.15</v>
       </c>
       <c r="O40" t="n">
-        <v>2020.09</v>
+        <v>1924.86</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3837,22 +3831,24 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3861,80 +3857,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1843.42</v>
+        <v>1882.78</v>
       </c>
       <c r="C41" t="n">
-        <v>1895.77</v>
+        <v>1883.44</v>
       </c>
       <c r="D41" t="n">
-        <v>1842.15</v>
+        <v>1827.7</v>
       </c>
       <c r="E41" t="n">
-        <v>1882.52</v>
+        <v>1858.26</v>
       </c>
       <c r="F41" t="n">
-        <v>39.1</v>
+        <v>-24.27</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0129</v>
       </c>
       <c r="H41" t="n">
-        <v>53.61</v>
+        <v>55.74</v>
       </c>
       <c r="I41" t="n">
-        <v>1769.8</v>
+        <v>1788.54</v>
       </c>
       <c r="J41" t="n">
-        <v>1789.78</v>
+        <v>1835.69</v>
       </c>
       <c r="K41" t="n">
-        <v>1817.57</v>
+        <v>1855.72</v>
       </c>
       <c r="L41" t="n">
-        <v>1845.37</v>
+        <v>1875.74</v>
       </c>
       <c r="M41" t="n">
-        <v>1869.26</v>
+        <v>1909.33</v>
       </c>
       <c r="N41" t="n">
-        <v>1893.15</v>
+        <v>1942.91</v>
       </c>
       <c r="O41" t="n">
-        <v>1924.86</v>
+        <v>1949.38</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="Q41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3943,76 +3943,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1882.78</v>
+        <v>1858.22</v>
       </c>
       <c r="C42" t="n">
-        <v>1883.44</v>
+        <v>1879.54</v>
       </c>
       <c r="D42" t="n">
-        <v>1827.7</v>
+        <v>1847.17</v>
       </c>
       <c r="E42" t="n">
-        <v>1858.26</v>
+        <v>1868.39</v>
       </c>
       <c r="F42" t="n">
-        <v>-24.27</v>
+        <v>10.13</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0055</v>
       </c>
       <c r="H42" t="n">
-        <v>55.74</v>
+        <v>32.36</v>
       </c>
       <c r="I42" t="n">
-        <v>1788.54</v>
+        <v>1771.96</v>
       </c>
       <c r="J42" t="n">
-        <v>1835.69</v>
+        <v>1803.86</v>
       </c>
       <c r="K42" t="n">
-        <v>1855.72</v>
+        <v>1830.39</v>
       </c>
       <c r="L42" t="n">
-        <v>1875.74</v>
+        <v>1856.91</v>
       </c>
       <c r="M42" t="n">
-        <v>1909.33</v>
+        <v>1886.13</v>
       </c>
       <c r="N42" t="n">
-        <v>1942.91</v>
+        <v>1915.34</v>
       </c>
       <c r="O42" t="n">
-        <v>1949.38</v>
+        <v>1939.18</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4029,55 +4021,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1858.22</v>
+        <v>1868.49</v>
       </c>
       <c r="C43" t="n">
-        <v>1879.54</v>
+        <v>1922.64</v>
       </c>
       <c r="D43" t="n">
-        <v>1847.17</v>
+        <v>1854.34</v>
       </c>
       <c r="E43" t="n">
-        <v>1868.39</v>
+        <v>1906.53</v>
       </c>
       <c r="F43" t="n">
-        <v>10.13</v>
+        <v>38.14</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0204</v>
       </c>
       <c r="H43" t="n">
-        <v>32.36</v>
+        <v>68.3</v>
       </c>
       <c r="I43" t="n">
-        <v>1771.96</v>
+        <v>1814.81</v>
       </c>
       <c r="J43" t="n">
-        <v>1803.86</v>
+        <v>1838.54</v>
       </c>
       <c r="K43" t="n">
-        <v>1830.39</v>
+        <v>1852.2</v>
       </c>
       <c r="L43" t="n">
-        <v>1856.91</v>
+        <v>1865.87</v>
       </c>
       <c r="M43" t="n">
-        <v>1886.13</v>
+        <v>1884.57</v>
       </c>
       <c r="N43" t="n">
-        <v>1915.34</v>
+        <v>1903.26</v>
       </c>
       <c r="O43" t="n">
-        <v>1939.18</v>
+        <v>1911.9</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4090,76 +4086,78 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1868.49</v>
+        <v>1906.44</v>
       </c>
       <c r="C44" t="n">
-        <v>1922.64</v>
+        <v>1917.7</v>
       </c>
       <c r="D44" t="n">
-        <v>1854.34</v>
+        <v>1890.96</v>
       </c>
       <c r="E44" t="n">
-        <v>1906.53</v>
+        <v>1902.06</v>
       </c>
       <c r="F44" t="n">
-        <v>38.14</v>
+        <v>-4.47</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.0023</v>
       </c>
       <c r="H44" t="n">
-        <v>68.3</v>
+        <v>26.74</v>
       </c>
       <c r="I44" t="n">
-        <v>1814.81</v>
+        <v>1786.04</v>
       </c>
       <c r="J44" t="n">
-        <v>1838.54</v>
+        <v>1847.24</v>
       </c>
       <c r="K44" t="n">
-        <v>1852.2</v>
+        <v>1872.38</v>
       </c>
       <c r="L44" t="n">
-        <v>1865.87</v>
+        <v>1897.51</v>
       </c>
       <c r="M44" t="n">
-        <v>1884.57</v>
+        <v>1940.68</v>
       </c>
       <c r="N44" t="n">
-        <v>1903.26</v>
+        <v>1983.84</v>
       </c>
       <c r="O44" t="n">
-        <v>1911.9</v>
+        <v>1990.94</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4172,78 +4170,76 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1906.44</v>
+        <v>1902.14</v>
       </c>
       <c r="C45" t="n">
-        <v>1917.7</v>
+        <v>1937.17</v>
       </c>
       <c r="D45" t="n">
-        <v>1890.96</v>
+        <v>1893.08</v>
       </c>
       <c r="E45" t="n">
-        <v>1902.06</v>
+        <v>1913.28</v>
       </c>
       <c r="F45" t="n">
-        <v>-4.47</v>
+        <v>11.22</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0059</v>
       </c>
       <c r="H45" t="n">
-        <v>26.74</v>
+        <v>44.08</v>
       </c>
       <c r="I45" t="n">
-        <v>1786.04</v>
+        <v>1864.23</v>
       </c>
       <c r="J45" t="n">
-        <v>1847.24</v>
+        <v>1874.18</v>
       </c>
       <c r="K45" t="n">
-        <v>1872.38</v>
+        <v>1888.69</v>
       </c>
       <c r="L45" t="n">
-        <v>1897.51</v>
+        <v>1903.19</v>
       </c>
       <c r="M45" t="n">
-        <v>1940.68</v>
+        <v>1915.43</v>
       </c>
       <c r="N45" t="n">
-        <v>1983.84</v>
+        <v>1927.66</v>
       </c>
       <c r="O45" t="n">
-        <v>1990.94</v>
+        <v>1944.44</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4256,14 +4252,18 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4273,59 +4273,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1902.14</v>
+        <v>1913.32</v>
       </c>
       <c r="C46" t="n">
-        <v>1937.17</v>
+        <v>1924.62</v>
       </c>
       <c r="D46" t="n">
-        <v>1893.08</v>
+        <v>1911.48</v>
       </c>
       <c r="E46" t="n">
-        <v>1913.28</v>
+        <v>1915.53</v>
       </c>
       <c r="F46" t="n">
-        <v>11.22</v>
+        <v>2.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0012</v>
       </c>
       <c r="H46" t="n">
-        <v>44.08</v>
+        <v>13.13</v>
       </c>
       <c r="I46" t="n">
-        <v>1864.23</v>
+        <v>1849</v>
       </c>
       <c r="J46" t="n">
-        <v>1874.18</v>
+        <v>1868.27</v>
       </c>
       <c r="K46" t="n">
-        <v>1888.69</v>
+        <v>1891.24</v>
       </c>
       <c r="L46" t="n">
-        <v>1903.19</v>
+        <v>1914.2</v>
       </c>
       <c r="M46" t="n">
-        <v>1915.43</v>
+        <v>1935.32</v>
       </c>
       <c r="N46" t="n">
-        <v>1927.66</v>
+        <v>1956.44</v>
       </c>
       <c r="O46" t="n">
-        <v>1944.44</v>
+        <v>1981.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4338,18 +4334,14 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4359,55 +4351,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1913.32</v>
+        <v>1915.46</v>
       </c>
       <c r="C47" t="n">
-        <v>1924.62</v>
+        <v>1935.53</v>
       </c>
       <c r="D47" t="n">
-        <v>1911.48</v>
+        <v>1907.03</v>
       </c>
       <c r="E47" t="n">
-        <v>1915.53</v>
+        <v>1908.68</v>
       </c>
       <c r="F47" t="n">
-        <v>2.25</v>
+        <v>-6.85</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0036</v>
       </c>
       <c r="H47" t="n">
-        <v>13.13</v>
+        <v>28.5</v>
       </c>
       <c r="I47" t="n">
-        <v>1849</v>
+        <v>1898.35</v>
       </c>
       <c r="J47" t="n">
-        <v>1868.27</v>
+        <v>1901.14</v>
       </c>
       <c r="K47" t="n">
-        <v>1891.24</v>
+        <v>1908.97</v>
       </c>
       <c r="L47" t="n">
-        <v>1914.2</v>
+        <v>1916.79</v>
       </c>
       <c r="M47" t="n">
-        <v>1935.32</v>
+        <v>1922.1</v>
       </c>
       <c r="N47" t="n">
-        <v>1956.44</v>
+        <v>1927.4</v>
       </c>
       <c r="O47" t="n">
-        <v>1981.25</v>
+        <v>1937.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4415,19 +4411,25 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4439,67 +4441,71 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1915.46</v>
+        <v>1908.72</v>
       </c>
       <c r="C48" t="n">
-        <v>1935.53</v>
+        <v>1928.99</v>
       </c>
       <c r="D48" t="n">
-        <v>1907.03</v>
+        <v>1866.79</v>
       </c>
       <c r="E48" t="n">
-        <v>1908.68</v>
+        <v>1871.28</v>
       </c>
       <c r="F48" t="n">
-        <v>-6.85</v>
+        <v>-37.4</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0196</v>
       </c>
       <c r="H48" t="n">
-        <v>28.5</v>
+        <v>62.2</v>
       </c>
       <c r="I48" t="n">
-        <v>1898.35</v>
+        <v>1878.52</v>
       </c>
       <c r="J48" t="n">
-        <v>1901.14</v>
+        <v>1873.88</v>
       </c>
       <c r="K48" t="n">
-        <v>1908.97</v>
+        <v>1894.43</v>
       </c>
       <c r="L48" t="n">
-        <v>1916.79</v>
+        <v>1914.98</v>
       </c>
       <c r="M48" t="n">
-        <v>1922.1</v>
+        <v>1922.93</v>
       </c>
       <c r="N48" t="n">
-        <v>1927.4</v>
+        <v>1930.89</v>
       </c>
       <c r="O48" t="n">
-        <v>1937.75</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>1964.03</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
@@ -4512,97 +4518,83 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1908.72</v>
+        <v>1871.26</v>
       </c>
       <c r="C49" t="n">
-        <v>1928.99</v>
+        <v>1895.75</v>
       </c>
       <c r="D49" t="n">
-        <v>1866.79</v>
+        <v>1852.84</v>
       </c>
       <c r="E49" t="n">
-        <v>1871.28</v>
+        <v>1881.37</v>
       </c>
       <c r="F49" t="n">
-        <v>-37.4</v>
+        <v>10.09</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0196</v>
+        <v>0.0054</v>
       </c>
       <c r="H49" t="n">
-        <v>62.2</v>
+        <v>42.91</v>
       </c>
       <c r="I49" t="n">
-        <v>1878.52</v>
+        <v>1804.59</v>
       </c>
       <c r="J49" t="n">
-        <v>1873.88</v>
+        <v>1795.77</v>
       </c>
       <c r="K49" t="n">
-        <v>1894.43</v>
+        <v>1840.18</v>
       </c>
       <c r="L49" t="n">
-        <v>1914.98</v>
+        <v>1884.59</v>
       </c>
       <c r="M49" t="n">
-        <v>1922.93</v>
+        <v>1902.38</v>
       </c>
       <c r="N49" t="n">
-        <v>1930.89</v>
+        <v>1920.18</v>
       </c>
       <c r="O49" t="n">
-        <v>1964.03</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>1991.2</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4615,55 +4607,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1871.26</v>
+        <v>1881.37</v>
       </c>
       <c r="C50" t="n">
-        <v>1895.75</v>
+        <v>1921.78</v>
       </c>
       <c r="D50" t="n">
-        <v>1852.84</v>
+        <v>1873.35</v>
       </c>
       <c r="E50" t="n">
-        <v>1881.37</v>
+        <v>1878.14</v>
       </c>
       <c r="F50" t="n">
-        <v>10.09</v>
+        <v>-3.24</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0017</v>
       </c>
       <c r="H50" t="n">
-        <v>42.91</v>
+        <v>48.43</v>
       </c>
       <c r="I50" t="n">
-        <v>1804.59</v>
+        <v>1809.93</v>
       </c>
       <c r="J50" t="n">
-        <v>1795.77</v>
+        <v>1842</v>
       </c>
       <c r="K50" t="n">
-        <v>1840.18</v>
+        <v>1859.92</v>
       </c>
       <c r="L50" t="n">
-        <v>1884.59</v>
+        <v>1877.83</v>
       </c>
       <c r="M50" t="n">
-        <v>1902.38</v>
+        <v>1902.83</v>
       </c>
       <c r="N50" t="n">
-        <v>1920.18</v>
+        <v>1927.82</v>
       </c>
       <c r="O50" t="n">
-        <v>1991.2</v>
+        <v>1938.66</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4674,13 +4670,15 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4695,57 +4693,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1881.37</v>
+        <v>1878.19</v>
       </c>
       <c r="C51" t="n">
-        <v>1921.78</v>
+        <v>1898.23</v>
       </c>
       <c r="D51" t="n">
-        <v>1873.35</v>
+        <v>1861.92</v>
       </c>
       <c r="E51" t="n">
-        <v>1878.14</v>
+        <v>1883.99</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.24</v>
+        <v>5.86</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="H51" t="n">
-        <v>48.43</v>
+        <v>36.3</v>
       </c>
       <c r="I51" t="n">
-        <v>1809.93</v>
+        <v>1824.92</v>
       </c>
       <c r="J51" t="n">
-        <v>1842</v>
+        <v>1819.99</v>
       </c>
       <c r="K51" t="n">
-        <v>1859.92</v>
+        <v>1853.92</v>
       </c>
       <c r="L51" t="n">
-        <v>1877.83</v>
+        <v>1887.85</v>
       </c>
       <c r="M51" t="n">
-        <v>1902.83</v>
+        <v>1902.35</v>
       </c>
       <c r="N51" t="n">
-        <v>1927.82</v>
+        <v>1916.85</v>
       </c>
       <c r="O51" t="n">
-        <v>1938.66</v>
+        <v>1970.2</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4756,15 +4754,13 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4779,57 +4775,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1878.19</v>
+        <v>1884.02</v>
       </c>
       <c r="C52" t="n">
-        <v>1898.23</v>
+        <v>1889.27</v>
       </c>
       <c r="D52" t="n">
-        <v>1861.92</v>
+        <v>1862.56</v>
       </c>
       <c r="E52" t="n">
-        <v>1883.99</v>
+        <v>1880.65</v>
       </c>
       <c r="F52" t="n">
-        <v>5.86</v>
+        <v>-3.34</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0018</v>
       </c>
       <c r="H52" t="n">
-        <v>36.3</v>
+        <v>26.71</v>
       </c>
       <c r="I52" t="n">
-        <v>1824.92</v>
+        <v>1825.62</v>
       </c>
       <c r="J52" t="n">
-        <v>1819.99</v>
+        <v>1849.65</v>
       </c>
       <c r="K52" t="n">
-        <v>1853.92</v>
+        <v>1865.84</v>
       </c>
       <c r="L52" t="n">
-        <v>1887.85</v>
+        <v>1882.03</v>
       </c>
       <c r="M52" t="n">
-        <v>1902.35</v>
+        <v>1902.14</v>
       </c>
       <c r="N52" t="n">
-        <v>1916.85</v>
+        <v>1922.26</v>
       </c>
       <c r="O52" t="n">
-        <v>1970.2</v>
+        <v>1934.53</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4837,8 +4833,10 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
@@ -4868,50 +4866,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1884.02</v>
+        <v>1880.61</v>
       </c>
       <c r="C53" t="n">
-        <v>1889.27</v>
+        <v>1884.72</v>
       </c>
       <c r="D53" t="n">
-        <v>1862.56</v>
+        <v>1874.33</v>
       </c>
       <c r="E53" t="n">
-        <v>1880.65</v>
+        <v>1880.91</v>
       </c>
       <c r="F53" t="n">
-        <v>-3.34</v>
+        <v>0.26</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0001</v>
       </c>
       <c r="H53" t="n">
-        <v>26.71</v>
+        <v>10.39</v>
       </c>
       <c r="I53" t="n">
-        <v>1825.62</v>
+        <v>1835.86</v>
       </c>
       <c r="J53" t="n">
-        <v>1849.65</v>
+        <v>1856.31</v>
       </c>
       <c r="K53" t="n">
-        <v>1865.84</v>
+        <v>1867.3</v>
       </c>
       <c r="L53" t="n">
-        <v>1882.03</v>
+        <v>1878.28</v>
       </c>
       <c r="M53" t="n">
-        <v>1902.14</v>
+        <v>1894</v>
       </c>
       <c r="N53" t="n">
-        <v>1922.26</v>
+        <v>1909.72</v>
       </c>
       <c r="O53" t="n">
-        <v>1934.53</v>
+        <v>1915.98</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4919,14 +4917,12 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4945,74 +4941,80 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1880.61</v>
+        <v>1880.89</v>
       </c>
       <c r="C54" t="n">
-        <v>1884.72</v>
+        <v>1889.61</v>
       </c>
       <c r="D54" t="n">
-        <v>1874.33</v>
+        <v>1867.89</v>
       </c>
       <c r="E54" t="n">
-        <v>1880.91</v>
+        <v>1873.94</v>
       </c>
       <c r="F54" t="n">
-        <v>0.26</v>
+        <v>-6.97</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0037</v>
       </c>
       <c r="H54" t="n">
-        <v>10.39</v>
+        <v>21.71</v>
       </c>
       <c r="I54" t="n">
-        <v>1835.86</v>
+        <v>1863.94</v>
       </c>
       <c r="J54" t="n">
-        <v>1856.31</v>
+        <v>1871.21</v>
       </c>
       <c r="K54" t="n">
-        <v>1867.3</v>
+        <v>1875.71</v>
       </c>
       <c r="L54" t="n">
-        <v>1878.28</v>
+        <v>1880.22</v>
       </c>
       <c r="M54" t="n">
-        <v>1894</v>
+        <v>1886.1</v>
       </c>
       <c r="N54" t="n">
-        <v>1909.72</v>
+        <v>1891.99</v>
       </c>
       <c r="O54" t="n">
-        <v>1915.98</v>
+        <v>1895.11</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5027,145 +5029,141 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1880.89</v>
+        <v>1873.97</v>
       </c>
       <c r="C55" t="n">
-        <v>1889.61</v>
+        <v>1916.66</v>
       </c>
       <c r="D55" t="n">
-        <v>1867.89</v>
+        <v>1870.75</v>
       </c>
       <c r="E55" t="n">
-        <v>1873.94</v>
+        <v>1912.2</v>
       </c>
       <c r="F55" t="n">
-        <v>-6.97</v>
+        <v>38.26</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0204</v>
       </c>
       <c r="H55" t="n">
-        <v>21.71</v>
+        <v>45.91</v>
       </c>
       <c r="I55" t="n">
-        <v>1863.94</v>
+        <v>1846.18</v>
       </c>
       <c r="J55" t="n">
-        <v>1871.21</v>
+        <v>1849.83</v>
       </c>
       <c r="K55" t="n">
-        <v>1875.71</v>
+        <v>1863.09</v>
       </c>
       <c r="L55" t="n">
-        <v>1880.22</v>
+        <v>1876.35</v>
       </c>
       <c r="M55" t="n">
-        <v>1886.1</v>
+        <v>1884.8</v>
       </c>
       <c r="N55" t="n">
-        <v>1891.99</v>
+        <v>1893.25</v>
       </c>
       <c r="O55" t="n">
-        <v>1895.11</v>
+        <v>1911.32</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1873.97</v>
+        <v>1912.21</v>
       </c>
       <c r="C56" t="n">
-        <v>1916.66</v>
+        <v>1920.52</v>
       </c>
       <c r="D56" t="n">
-        <v>1870.75</v>
+        <v>1884.48</v>
       </c>
       <c r="E56" t="n">
-        <v>1912.2</v>
+        <v>1916.46</v>
       </c>
       <c r="F56" t="n">
-        <v>38.26</v>
+        <v>4.26</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.0022</v>
       </c>
       <c r="H56" t="n">
-        <v>45.91</v>
+        <v>36.05</v>
       </c>
       <c r="I56" t="n">
-        <v>1846.18</v>
+        <v>1824.84</v>
       </c>
       <c r="J56" t="n">
-        <v>1849.83</v>
+        <v>1875.54</v>
       </c>
       <c r="K56" t="n">
-        <v>1863.09</v>
+        <v>1889.25</v>
       </c>
       <c r="L56" t="n">
-        <v>1876.35</v>
+        <v>1902.95</v>
       </c>
       <c r="M56" t="n">
-        <v>1884.8</v>
+        <v>1935.16</v>
       </c>
       <c r="N56" t="n">
-        <v>1893.25</v>
+        <v>1967.36</v>
       </c>
       <c r="O56" t="n">
-        <v>1911.32</v>
+        <v>1962.57</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5173,28 +5171,24 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
@@ -5206,50 +5200,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1912.21</v>
+        <v>1916.43</v>
       </c>
       <c r="C57" t="n">
-        <v>1920.52</v>
+        <v>2327.7</v>
       </c>
       <c r="D57" t="n">
-        <v>1884.48</v>
+        <v>1905.08</v>
       </c>
       <c r="E57" t="n">
-        <v>1916.46</v>
+        <v>2251.46</v>
       </c>
       <c r="F57" t="n">
-        <v>4.26</v>
+        <v>335</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.1748</v>
       </c>
       <c r="H57" t="n">
-        <v>36.05</v>
+        <v>422.62</v>
       </c>
       <c r="I57" t="n">
-        <v>1824.84</v>
+        <v>1848.43</v>
       </c>
       <c r="J57" t="n">
-        <v>1875.54</v>
+        <v>1887.39</v>
       </c>
       <c r="K57" t="n">
-        <v>1889.25</v>
+        <v>1898.44</v>
       </c>
       <c r="L57" t="n">
-        <v>1902.95</v>
+        <v>1909.48</v>
       </c>
       <c r="M57" t="n">
-        <v>1935.16</v>
+        <v>1934.48</v>
       </c>
       <c r="N57" t="n">
-        <v>1967.36</v>
+        <v>1959.48</v>
       </c>
       <c r="O57" t="n">
-        <v>1962.57</v>
+        <v>1956.57</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5257,24 +5251,28 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5286,50 +5284,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1916.43</v>
+        <v>2251.44</v>
       </c>
       <c r="C58" t="n">
-        <v>2327.7</v>
+        <v>2357.23</v>
       </c>
       <c r="D58" t="n">
-        <v>1905.08</v>
+        <v>2222.57</v>
       </c>
       <c r="E58" t="n">
-        <v>2251.46</v>
+        <v>2326.38</v>
       </c>
       <c r="F58" t="n">
-        <v>335</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.1748</v>
+        <v>0.0333</v>
       </c>
       <c r="H58" t="n">
-        <v>422.62</v>
+        <v>134.65</v>
       </c>
       <c r="I58" t="n">
-        <v>1848.43</v>
+        <v>1482.46</v>
       </c>
       <c r="J58" t="n">
-        <v>1887.39</v>
+        <v>1896.37</v>
       </c>
       <c r="K58" t="n">
-        <v>1898.44</v>
+        <v>2040.15</v>
       </c>
       <c r="L58" t="n">
-        <v>1909.48</v>
+        <v>2183.92</v>
       </c>
       <c r="M58" t="n">
-        <v>1934.48</v>
+        <v>2462.77</v>
       </c>
       <c r="N58" t="n">
-        <v>1959.48</v>
+        <v>2741.61</v>
       </c>
       <c r="O58" t="n">
-        <v>1956.57</v>
+        <v>2750.32</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5347,18 +5345,14 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5370,50 +5364,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2251.44</v>
+        <v>2326.38</v>
       </c>
       <c r="C59" t="n">
-        <v>2357.23</v>
+        <v>2545.88</v>
       </c>
       <c r="D59" t="n">
-        <v>2222.57</v>
+        <v>2324.71</v>
       </c>
       <c r="E59" t="n">
-        <v>2326.38</v>
+        <v>2515.28</v>
       </c>
       <c r="F59" t="n">
-        <v>74.93000000000001</v>
+        <v>188.9</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0333</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>134.65</v>
+        <v>221.17</v>
       </c>
       <c r="I59" t="n">
-        <v>1482.46</v>
+        <v>2087.92</v>
       </c>
       <c r="J59" t="n">
-        <v>1896.37</v>
+        <v>2209.97</v>
       </c>
       <c r="K59" t="n">
-        <v>2040.15</v>
+        <v>2259.06</v>
       </c>
       <c r="L59" t="n">
-        <v>2183.92</v>
+        <v>2308.14</v>
       </c>
       <c r="M59" t="n">
-        <v>2462.77</v>
+        <v>2393.71</v>
       </c>
       <c r="N59" t="n">
-        <v>2741.61</v>
+        <v>2479.28</v>
       </c>
       <c r="O59" t="n">
-        <v>2750.32</v>
+        <v>2491.88</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5431,14 +5425,18 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
@@ -5450,50 +5448,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2326.38</v>
+        <v>2515.39</v>
       </c>
       <c r="C60" t="n">
-        <v>2545.88</v>
+        <v>2528.9</v>
       </c>
       <c r="D60" t="n">
-        <v>2324.71</v>
+        <v>2389.9</v>
       </c>
       <c r="E60" t="n">
-        <v>2515.28</v>
+        <v>2424.25</v>
       </c>
       <c r="F60" t="n">
-        <v>188.9</v>
+        <v>-91.03</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0362</v>
       </c>
       <c r="H60" t="n">
-        <v>221.17</v>
+        <v>138.99</v>
       </c>
       <c r="I60" t="n">
-        <v>2087.92</v>
+        <v>2103.54</v>
       </c>
       <c r="J60" t="n">
-        <v>2209.97</v>
+        <v>2334.1</v>
       </c>
       <c r="K60" t="n">
-        <v>2259.06</v>
+        <v>2404.7</v>
       </c>
       <c r="L60" t="n">
-        <v>2308.14</v>
+        <v>2475.29</v>
       </c>
       <c r="M60" t="n">
-        <v>2393.71</v>
+        <v>2625.87</v>
       </c>
       <c r="N60" t="n">
-        <v>2479.28</v>
+        <v>2776.45</v>
       </c>
       <c r="O60" t="n">
-        <v>2491.88</v>
+        <v>2767.05</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5501,83 +5499,83 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
+      </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2515.39</v>
+        <v>2424.22</v>
       </c>
       <c r="C61" t="n">
-        <v>2528.9</v>
+        <v>2483.93</v>
       </c>
       <c r="D61" t="n">
-        <v>2389.9</v>
+        <v>2357.14</v>
       </c>
       <c r="E61" t="n">
-        <v>2424.25</v>
+        <v>2463.82</v>
       </c>
       <c r="F61" t="n">
-        <v>-91.03</v>
+        <v>39.56</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0362</v>
+        <v>0.0163</v>
       </c>
       <c r="H61" t="n">
-        <v>138.99</v>
+        <v>126.79</v>
       </c>
       <c r="I61" t="n">
-        <v>2103.54</v>
+        <v>2250.91</v>
       </c>
       <c r="J61" t="n">
-        <v>2334.1</v>
+        <v>2267.68</v>
       </c>
       <c r="K61" t="n">
-        <v>2404.7</v>
+        <v>2354.75</v>
       </c>
       <c r="L61" t="n">
-        <v>2475.29</v>
+        <v>2441.83</v>
       </c>
       <c r="M61" t="n">
-        <v>2625.87</v>
+        <v>2493.75</v>
       </c>
       <c r="N61" t="n">
-        <v>2776.45</v>
+        <v>2545.67</v>
       </c>
       <c r="O61" t="n">
-        <v>2767.05</v>
+        <v>2667.89</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5585,14 +5583,12 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5618,50 +5614,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2424.22</v>
+        <v>2463.64</v>
       </c>
       <c r="C62" t="n">
-        <v>2483.93</v>
+        <v>2531.74</v>
       </c>
       <c r="D62" t="n">
-        <v>2357.14</v>
+        <v>2425.39</v>
       </c>
       <c r="E62" t="n">
-        <v>2463.82</v>
+        <v>2481.83</v>
       </c>
       <c r="F62" t="n">
-        <v>39.56</v>
+        <v>18.02</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0073</v>
       </c>
       <c r="H62" t="n">
-        <v>126.79</v>
+        <v>106.36</v>
       </c>
       <c r="I62" t="n">
-        <v>2250.91</v>
+        <v>2230.35</v>
       </c>
       <c r="J62" t="n">
-        <v>2267.68</v>
+        <v>2358.67</v>
       </c>
       <c r="K62" t="n">
-        <v>2354.75</v>
+        <v>2400.42</v>
       </c>
       <c r="L62" t="n">
-        <v>2441.83</v>
+        <v>2442.18</v>
       </c>
       <c r="M62" t="n">
-        <v>2493.75</v>
+        <v>2527.21</v>
       </c>
       <c r="N62" t="n">
-        <v>2545.67</v>
+        <v>2612.25</v>
       </c>
       <c r="O62" t="n">
-        <v>2667.89</v>
+        <v>2610.72</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5677,8 +5673,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5691,59 +5689,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2463.64</v>
+        <v>2481.78</v>
       </c>
       <c r="C63" t="n">
-        <v>2531.74</v>
+        <v>2531.08</v>
       </c>
       <c r="D63" t="n">
-        <v>2425.39</v>
+        <v>2416.6</v>
       </c>
       <c r="E63" t="n">
-        <v>2481.83</v>
+        <v>2443.16</v>
       </c>
       <c r="F63" t="n">
-        <v>18.02</v>
+        <v>-38.67</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0156</v>
       </c>
       <c r="H63" t="n">
-        <v>106.36</v>
+        <v>114.48</v>
       </c>
       <c r="I63" t="n">
-        <v>2230.35</v>
+        <v>2319.03</v>
       </c>
       <c r="J63" t="n">
-        <v>2358.67</v>
+        <v>2377.11</v>
       </c>
       <c r="K63" t="n">
-        <v>2400.42</v>
+        <v>2428.65</v>
       </c>
       <c r="L63" t="n">
-        <v>2442.18</v>
+        <v>2480.2</v>
       </c>
       <c r="M63" t="n">
-        <v>2527.21</v>
+        <v>2535.01</v>
       </c>
       <c r="N63" t="n">
-        <v>2612.25</v>
+        <v>2589.82</v>
       </c>
       <c r="O63" t="n">
-        <v>2610.72</v>
+        <v>2638.1</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5751,18 +5745,18 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5775,55 +5769,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2481.78</v>
+        <v>2442.49</v>
       </c>
       <c r="C64" t="n">
-        <v>2531.08</v>
+        <v>2514.67</v>
       </c>
       <c r="D64" t="n">
-        <v>2416.6</v>
+        <v>2432.51</v>
       </c>
       <c r="E64" t="n">
-        <v>2443.16</v>
+        <v>2506.26</v>
       </c>
       <c r="F64" t="n">
-        <v>-38.67</v>
+        <v>63.1</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0258</v>
       </c>
       <c r="H64" t="n">
-        <v>114.48</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>2319.03</v>
+        <v>2302.12</v>
       </c>
       <c r="J64" t="n">
-        <v>2377.11</v>
+        <v>2313.34</v>
       </c>
       <c r="K64" t="n">
-        <v>2428.65</v>
+        <v>2385.92</v>
       </c>
       <c r="L64" t="n">
-        <v>2480.2</v>
+        <v>2458.5</v>
       </c>
       <c r="M64" t="n">
-        <v>2535.01</v>
+        <v>2500.4</v>
       </c>
       <c r="N64" t="n">
-        <v>2589.82</v>
+        <v>2542.3</v>
       </c>
       <c r="O64" t="n">
-        <v>2638.1</v>
+        <v>2645.57</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5831,19 +5829,19 @@
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="inlineStr">
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
       <c r="U64" s="8" t="n">
         <v/>
       </c>
@@ -5857,57 +5855,57 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2442.49</v>
+        <v>2506.24</v>
       </c>
       <c r="C65" t="n">
-        <v>2514.67</v>
+        <v>2564.27</v>
       </c>
       <c r="D65" t="n">
-        <v>2432.51</v>
+        <v>2481.94</v>
       </c>
       <c r="E65" t="n">
-        <v>2506.26</v>
+        <v>2510.41</v>
       </c>
       <c r="F65" t="n">
-        <v>63.1</v>
+        <v>4.15</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0258</v>
+        <v>0.0017</v>
       </c>
       <c r="H65" t="n">
-        <v>82.15000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="I65" t="n">
-        <v>2302.12</v>
+        <v>2350.36</v>
       </c>
       <c r="J65" t="n">
-        <v>2313.34</v>
+        <v>2440.44</v>
       </c>
       <c r="K65" t="n">
-        <v>2385.92</v>
+        <v>2465.18</v>
       </c>
       <c r="L65" t="n">
-        <v>2458.5</v>
+        <v>2489.93</v>
       </c>
       <c r="M65" t="n">
-        <v>2500.4</v>
+        <v>2547.34</v>
       </c>
       <c r="N65" t="n">
-        <v>2542.3</v>
+        <v>2604.75</v>
       </c>
       <c r="O65" t="n">
-        <v>2645.57</v>
+        <v>2596.82</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
@@ -5920,12 +5918,12 @@
       </c>
       <c r="S65" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U65" s="8" t="n">
@@ -5939,79 +5937,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2506.24</v>
+        <v>2510.67</v>
       </c>
       <c r="C66" t="n">
-        <v>2564.27</v>
+        <v>2534.01</v>
       </c>
       <c r="D66" t="n">
-        <v>2481.94</v>
+        <v>2408.72</v>
       </c>
       <c r="E66" t="n">
-        <v>2510.41</v>
+        <v>2442.54</v>
       </c>
       <c r="F66" t="n">
-        <v>4.15</v>
+        <v>-67.87</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.027</v>
       </c>
       <c r="H66" t="n">
-        <v>82.33</v>
+        <v>125.29</v>
       </c>
       <c r="I66" t="n">
-        <v>2350.36</v>
+        <v>2399.62</v>
       </c>
       <c r="J66" t="n">
-        <v>2440.44</v>
+        <v>2421.73</v>
       </c>
       <c r="K66" t="n">
-        <v>2465.18</v>
+        <v>2469.25</v>
       </c>
       <c r="L66" t="n">
-        <v>2489.93</v>
+        <v>2516.76</v>
       </c>
       <c r="M66" t="n">
-        <v>2547.34</v>
+        <v>2551.57</v>
       </c>
       <c r="N66" t="n">
-        <v>2604.75</v>
+        <v>2586.39</v>
       </c>
       <c r="O66" t="n">
-        <v>2596.82</v>
+        <v>2646.6</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
       </c>
-      <c r="Q66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S66" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T66" s="8" t="inlineStr">
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="n">
+        <v/>
+      </c>
       <c r="U66" s="8" t="n">
         <v/>
       </c>
@@ -6023,72 +6019,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr"/>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2510.67</v>
+        <v>2442.56</v>
       </c>
       <c r="C67" t="n">
-        <v>2534.01</v>
+        <v>2459.63</v>
       </c>
       <c r="D67" t="n">
-        <v>2408.72</v>
+        <v>2430.81</v>
       </c>
       <c r="E67" t="n">
-        <v>2442.54</v>
+        <v>2457.69</v>
       </c>
       <c r="F67" t="n">
-        <v>-67.87</v>
+        <v>15.15</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.027</v>
+        <v>0.0062</v>
       </c>
       <c r="H67" t="n">
-        <v>125.29</v>
+        <v>28.82</v>
       </c>
       <c r="I67" t="n">
-        <v>2399.62</v>
+        <v>2283.43</v>
       </c>
       <c r="J67" t="n">
-        <v>2421.73</v>
+        <v>2302.83</v>
       </c>
       <c r="K67" t="n">
-        <v>2469.25</v>
+        <v>2379.89</v>
       </c>
       <c r="L67" t="n">
-        <v>2516.76</v>
+        <v>2456.95</v>
       </c>
       <c r="M67" t="n">
-        <v>2551.57</v>
+        <v>2505.18</v>
       </c>
       <c r="N67" t="n">
-        <v>2586.39</v>
+        <v>2553.41</v>
       </c>
       <c r="O67" t="n">
-        <v>2646.6</v>
+        <v>2659.3</v>
       </c>
       <c r="P67" s="6" t="n">
         <v/>
       </c>
-      <c r="Q67" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R67" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S67" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S67" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T67" s="8" t="n">
@@ -6107,84 +6103,96 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2442.56</v>
+        <v>2457.69</v>
       </c>
       <c r="C68" t="n">
-        <v>2459.63</v>
+        <v>2532.96</v>
       </c>
       <c r="D68" t="n">
-        <v>2430.81</v>
+        <v>2389.47</v>
       </c>
       <c r="E68" t="n">
-        <v>2457.69</v>
+        <v>2417.94</v>
       </c>
       <c r="F68" t="n">
-        <v>15.15</v>
+        <v>-39.75</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H68" t="n">
-        <v>28.82</v>
+        <v>143.49</v>
       </c>
       <c r="I68" t="n">
-        <v>2283.43</v>
+        <v>2401.99</v>
       </c>
       <c r="J68" t="n">
-        <v>2302.83</v>
+        <v>2435.1</v>
       </c>
       <c r="K68" t="n">
-        <v>2379.89</v>
+        <v>2443.28</v>
       </c>
       <c r="L68" t="n">
-        <v>2456.95</v>
+        <v>2451.45</v>
       </c>
       <c r="M68" t="n">
-        <v>2505.18</v>
+        <v>2472.1</v>
       </c>
       <c r="N68" t="n">
-        <v>2553.41</v>
+        <v>2492.74</v>
       </c>
       <c r="O68" t="n">
-        <v>2659.3</v>
-      </c>
-      <c r="P68" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q68" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R68" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S68" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U68" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V68" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W68" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+        <v>2488.45</v>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W68" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -6196,85 +6204,75 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2457.69</v>
+        <v>2417.9</v>
       </c>
       <c r="C69" t="n">
-        <v>2532.96</v>
+        <v>2488.92</v>
       </c>
       <c r="D69" t="n">
-        <v>2389.47</v>
+        <v>2401.81</v>
       </c>
       <c r="E69" t="n">
-        <v>2417.94</v>
+        <v>2466.82</v>
       </c>
       <c r="F69" t="n">
-        <v>-39.75</v>
+        <v>48.88</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.0202</v>
       </c>
       <c r="H69" t="n">
-        <v>143.49</v>
+        <v>87.11</v>
       </c>
       <c r="I69" t="n">
-        <v>2401.99</v>
+        <v>2245.98</v>
       </c>
       <c r="J69" t="n">
-        <v>2435.1</v>
+        <v>2252.81</v>
       </c>
       <c r="K69" t="n">
-        <v>2443.28</v>
+        <v>2346.19</v>
       </c>
       <c r="L69" t="n">
-        <v>2451.45</v>
+        <v>2439.58</v>
       </c>
       <c r="M69" t="n">
-        <v>2472.1</v>
+        <v>2489.68</v>
       </c>
       <c r="N69" t="n">
-        <v>2492.74</v>
+        <v>2539.79</v>
       </c>
       <c r="O69" t="n">
-        <v>2488.45</v>
-      </c>
-      <c r="P69" s="6" t="inlineStr">
+        <v>2676.45</v>
+      </c>
+      <c r="P69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R69" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S69" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q69" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R69" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S69" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T69" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U69" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V69" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U69" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V69" s="8" t="n">
+        <v/>
       </c>
       <c r="W69" s="11" t="inlineStr">
         <is>
@@ -6283,77 +6281,79 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2417.9</v>
+        <v>2466.58</v>
       </c>
       <c r="C70" t="n">
-        <v>2488.92</v>
+        <v>2484.4</v>
       </c>
       <c r="D70" t="n">
-        <v>2401.81</v>
+        <v>2383.8</v>
       </c>
       <c r="E70" t="n">
-        <v>2466.82</v>
+        <v>2417.84</v>
       </c>
       <c r="F70" t="n">
-        <v>48.88</v>
+        <v>-48.98</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.0202</v>
+        <v>-0.0199</v>
       </c>
       <c r="H70" t="n">
-        <v>87.11</v>
+        <v>100.6</v>
       </c>
       <c r="I70" t="n">
-        <v>2245.98</v>
+        <v>2314.69</v>
       </c>
       <c r="J70" t="n">
-        <v>2252.81</v>
+        <v>2390.43</v>
       </c>
       <c r="K70" t="n">
-        <v>2346.19</v>
+        <v>2423.26</v>
       </c>
       <c r="L70" t="n">
-        <v>2439.58</v>
+        <v>2456.09</v>
       </c>
       <c r="M70" t="n">
-        <v>2489.68</v>
+        <v>2510.38</v>
       </c>
       <c r="N70" t="n">
-        <v>2539.79</v>
+        <v>2564.66</v>
       </c>
       <c r="O70" t="n">
-        <v>2676.45</v>
+        <v>2576.04</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
       </c>
-      <c r="Q70" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R70" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S70" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="inlineStr">
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R70" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="n">
+        <v/>
+      </c>
       <c r="U70" s="8" t="n">
         <v/>
       </c>
@@ -6365,67 +6365,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2466.58</v>
+        <v>2417.83</v>
       </c>
       <c r="C71" t="n">
-        <v>2484.4</v>
+        <v>2427.4</v>
       </c>
       <c r="D71" t="n">
-        <v>2383.8</v>
+        <v>2356.19</v>
       </c>
       <c r="E71" t="n">
-        <v>2417.84</v>
+        <v>2391.5</v>
       </c>
       <c r="F71" t="n">
-        <v>-48.98</v>
+        <v>-26.34</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.0109</v>
       </c>
       <c r="H71" t="n">
-        <v>100.6</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>2314.69</v>
+        <v>2283.21</v>
       </c>
       <c r="J71" t="n">
-        <v>2390.43</v>
+        <v>2309.12</v>
       </c>
       <c r="K71" t="n">
-        <v>2423.26</v>
+        <v>2367.54</v>
       </c>
       <c r="L71" t="n">
-        <v>2456.09</v>
+        <v>2425.97</v>
       </c>
       <c r="M71" t="n">
-        <v>2510.38</v>
+        <v>2468.14</v>
       </c>
       <c r="N71" t="n">
-        <v>2564.66</v>
+        <v>2510.31</v>
       </c>
       <c r="O71" t="n">
-        <v>2576.04</v>
+        <v>2584.99</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
       </c>
-      <c r="Q71" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q71" s="6" t="n">
+        <v/>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
@@ -6456,50 +6450,50 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2417.83</v>
+        <v>2391.6</v>
       </c>
       <c r="C72" t="n">
-        <v>2427.4</v>
+        <v>2526.95</v>
       </c>
       <c r="D72" t="n">
-        <v>2356.19</v>
+        <v>2370.42</v>
       </c>
       <c r="E72" t="n">
-        <v>2391.5</v>
+        <v>2508.02</v>
       </c>
       <c r="F72" t="n">
-        <v>-26.34</v>
+        <v>116.52</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0109</v>
+        <v>0.0487</v>
       </c>
       <c r="H72" t="n">
-        <v>71.20999999999999</v>
+        <v>156.53</v>
       </c>
       <c r="I72" t="n">
-        <v>2283.21</v>
+        <v>2284.97</v>
       </c>
       <c r="J72" t="n">
-        <v>2309.12</v>
+        <v>2320.14</v>
       </c>
       <c r="K72" t="n">
-        <v>2367.54</v>
+        <v>2355.89</v>
       </c>
       <c r="L72" t="n">
-        <v>2425.97</v>
+        <v>2391.65</v>
       </c>
       <c r="M72" t="n">
-        <v>2468.14</v>
+        <v>2427.11</v>
       </c>
       <c r="N72" t="n">
-        <v>2510.31</v>
+        <v>2462.57</v>
       </c>
       <c r="O72" t="n">
-        <v>2584.99</v>
+        <v>2498.61</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
@@ -6507,28 +6501,32 @@
       <c r="Q72" s="6" t="n">
         <v/>
       </c>
-      <c r="R72" s="6" t="inlineStr">
+      <c r="R72" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S72" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V72" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S72" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T72" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U72" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V72" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W72" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W72" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X72" t="inlineStr"/>
@@ -6536,50 +6534,50 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2391.6</v>
+        <v>2508.02</v>
       </c>
       <c r="C73" t="n">
-        <v>2526.95</v>
+        <v>2545.62</v>
       </c>
       <c r="D73" t="n">
-        <v>2370.42</v>
+        <v>2432.35</v>
       </c>
       <c r="E73" t="n">
-        <v>2508.02</v>
+        <v>2456.08</v>
       </c>
       <c r="F73" t="n">
-        <v>116.52</v>
+        <v>-51.94</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0487</v>
+        <v>-0.0207</v>
       </c>
       <c r="H73" t="n">
-        <v>156.53</v>
+        <v>113.27</v>
       </c>
       <c r="I73" t="n">
-        <v>2284.97</v>
+        <v>2213.88</v>
       </c>
       <c r="J73" t="n">
-        <v>2320.14</v>
+        <v>2381.16</v>
       </c>
       <c r="K73" t="n">
-        <v>2355.89</v>
+        <v>2429.75</v>
       </c>
       <c r="L73" t="n">
-        <v>2391.65</v>
+        <v>2478.35</v>
       </c>
       <c r="M73" t="n">
-        <v>2427.11</v>
+        <v>2586.29</v>
       </c>
       <c r="N73" t="n">
-        <v>2462.57</v>
+        <v>2694.22</v>
       </c>
       <c r="O73" t="n">
-        <v>2498.61</v>
+        <v>2683.48</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6590,80 +6588,78 @@
       <c r="R73" s="6" t="n">
         <v/>
       </c>
-      <c r="S73" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U73" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V73" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S73" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U73" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V73" s="8" t="n">
+        <v/>
       </c>
       <c r="W73" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr"/>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2508.02</v>
+        <v>2455.99</v>
       </c>
       <c r="C74" t="n">
-        <v>2545.62</v>
+        <v>2492.01</v>
       </c>
       <c r="D74" t="n">
-        <v>2432.35</v>
+        <v>2445.69</v>
       </c>
       <c r="E74" t="n">
-        <v>2456.08</v>
+        <v>2480.74</v>
       </c>
       <c r="F74" t="n">
-        <v>-51.94</v>
+        <v>24.66</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>-0.0207</v>
+        <v>0.01</v>
       </c>
       <c r="H74" t="n">
-        <v>113.27</v>
+        <v>46.32</v>
       </c>
       <c r="I74" t="n">
-        <v>2213.88</v>
+        <v>2319.08</v>
       </c>
       <c r="J74" t="n">
-        <v>2381.16</v>
+        <v>2326.35</v>
       </c>
       <c r="K74" t="n">
-        <v>2429.75</v>
+        <v>2399.44</v>
       </c>
       <c r="L74" t="n">
-        <v>2478.35</v>
+        <v>2472.53</v>
       </c>
       <c r="M74" t="n">
-        <v>2586.29</v>
+        <v>2512.71</v>
       </c>
       <c r="N74" t="n">
-        <v>2694.22</v>
+        <v>2552.89</v>
       </c>
       <c r="O74" t="n">
-        <v>2683.48</v>
+        <v>2658.89</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
@@ -6674,9 +6670,9 @@
       <c r="R74" s="6" t="n">
         <v/>
       </c>
-      <c r="S74" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S74" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T74" s="8" t="n">
@@ -6702,50 +6698,50 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2455.99</v>
+        <v>2480.82</v>
       </c>
       <c r="C75" t="n">
-        <v>2492.01</v>
+        <v>2525.32</v>
       </c>
       <c r="D75" t="n">
-        <v>2445.69</v>
+        <v>2468.19</v>
       </c>
       <c r="E75" t="n">
-        <v>2480.74</v>
+        <v>2514.55</v>
       </c>
       <c r="F75" t="n">
-        <v>24.66</v>
+        <v>33.81</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0136</v>
       </c>
       <c r="H75" t="n">
-        <v>46.32</v>
+        <v>57.13</v>
       </c>
       <c r="I75" t="n">
-        <v>2319.08</v>
+        <v>2399.37</v>
       </c>
       <c r="J75" t="n">
-        <v>2326.35</v>
+        <v>2440.36</v>
       </c>
       <c r="K75" t="n">
-        <v>2399.44</v>
+        <v>2457.58</v>
       </c>
       <c r="L75" t="n">
-        <v>2472.53</v>
+        <v>2474.79</v>
       </c>
       <c r="M75" t="n">
-        <v>2512.71</v>
+        <v>2503.9</v>
       </c>
       <c r="N75" t="n">
-        <v>2552.89</v>
+        <v>2533</v>
       </c>
       <c r="O75" t="n">
-        <v>2658.89</v>
+        <v>2538.33</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
@@ -6758,11 +6754,13 @@
       </c>
       <c r="S75" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T75" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U75" s="8" t="n">
         <v/>
@@ -6775,59 +6773,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2480.82</v>
+        <v>2514.58</v>
       </c>
       <c r="C76" t="n">
-        <v>2525.32</v>
+        <v>2534.86</v>
       </c>
       <c r="D76" t="n">
-        <v>2468.19</v>
+        <v>2466.91</v>
       </c>
       <c r="E76" t="n">
-        <v>2514.55</v>
+        <v>2490.96</v>
       </c>
       <c r="F76" t="n">
-        <v>33.81</v>
+        <v>-23.59</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0094</v>
       </c>
       <c r="H76" t="n">
-        <v>57.13</v>
+        <v>67.95</v>
       </c>
       <c r="I76" t="n">
-        <v>2399.37</v>
+        <v>2411.07</v>
       </c>
       <c r="J76" t="n">
-        <v>2440.36</v>
+        <v>2466.32</v>
       </c>
       <c r="K76" t="n">
-        <v>2457.58</v>
+        <v>2485.99</v>
       </c>
       <c r="L76" t="n">
-        <v>2474.79</v>
+        <v>2505.65</v>
       </c>
       <c r="M76" t="n">
-        <v>2503.9</v>
+        <v>2543.11</v>
       </c>
       <c r="N76" t="n">
-        <v>2533</v>
+        <v>2580.57</v>
       </c>
       <c r="O76" t="n">
-        <v>2538.33</v>
+        <v>2582.45</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
@@ -6835,19 +6829,19 @@
       <c r="Q76" s="6" t="n">
         <v/>
       </c>
-      <c r="R76" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S76" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T76" s="8" t="inlineStr">
+      <c r="R76" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S76" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T76" s="8" t="n">
+        <v/>
+      </c>
       <c r="U76" s="8" t="n">
         <v/>
       </c>
@@ -6859,55 +6853,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr"/>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2514.58</v>
+        <v>2490.92</v>
       </c>
       <c r="C77" t="n">
-        <v>2534.86</v>
+        <v>2506.75</v>
       </c>
       <c r="D77" t="n">
-        <v>2466.91</v>
+        <v>2441.33</v>
       </c>
       <c r="E77" t="n">
-        <v>2490.96</v>
+        <v>2484.94</v>
       </c>
       <c r="F77" t="n">
-        <v>-23.59</v>
+        <v>-6.02</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0024</v>
       </c>
       <c r="H77" t="n">
-        <v>67.95</v>
+        <v>65.42</v>
       </c>
       <c r="I77" t="n">
-        <v>2411.07</v>
+        <v>2398.96</v>
       </c>
       <c r="J77" t="n">
-        <v>2466.32</v>
+        <v>2418.04</v>
       </c>
       <c r="K77" t="n">
-        <v>2485.99</v>
+        <v>2456.98</v>
       </c>
       <c r="L77" t="n">
-        <v>2505.65</v>
+        <v>2495.92</v>
       </c>
       <c r="M77" t="n">
-        <v>2543.11</v>
+        <v>2524.93</v>
       </c>
       <c r="N77" t="n">
-        <v>2580.57</v>
+        <v>2553.94</v>
       </c>
       <c r="O77" t="n">
-        <v>2582.45</v>
+        <v>2602.81</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
@@ -6917,12 +6915,12 @@
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S77" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T77" s="8" t="n">
@@ -6941,57 +6939,57 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2490.92</v>
+        <v>2484.89</v>
       </c>
       <c r="C78" t="n">
-        <v>2506.75</v>
+        <v>2522.37</v>
       </c>
       <c r="D78" t="n">
-        <v>2441.33</v>
+        <v>2443.7</v>
       </c>
       <c r="E78" t="n">
-        <v>2484.94</v>
+        <v>2466.91</v>
       </c>
       <c r="F78" t="n">
-        <v>-6.02</v>
+        <v>-18.03</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0073</v>
       </c>
       <c r="H78" t="n">
-        <v>65.42</v>
+        <v>78.67</v>
       </c>
       <c r="I78" t="n">
-        <v>2398.96</v>
+        <v>2375.9</v>
       </c>
       <c r="J78" t="n">
-        <v>2418.04</v>
+        <v>2424.97</v>
       </c>
       <c r="K78" t="n">
-        <v>2456.98</v>
+        <v>2452.23</v>
       </c>
       <c r="L78" t="n">
-        <v>2495.92</v>
+        <v>2479.49</v>
       </c>
       <c r="M78" t="n">
-        <v>2524.93</v>
+        <v>2517.65</v>
       </c>
       <c r="N78" t="n">
-        <v>2553.94</v>
+        <v>2555.82</v>
       </c>
       <c r="O78" t="n">
-        <v>2602.81</v>
+        <v>2572.18</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -7009,8 +7007,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T78" s="8" t="n">
-        <v/>
+      <c r="T78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U78" s="8" t="n">
         <v/>
@@ -7025,57 +7025,57 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2484.89</v>
+        <v>2466.91</v>
       </c>
       <c r="C79" t="n">
-        <v>2522.37</v>
+        <v>2483.72</v>
       </c>
       <c r="D79" t="n">
-        <v>2443.7</v>
+        <v>2406.91</v>
       </c>
       <c r="E79" t="n">
-        <v>2466.91</v>
+        <v>2437.1</v>
       </c>
       <c r="F79" t="n">
-        <v>-18.03</v>
+        <v>-29.82</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0121</v>
       </c>
       <c r="H79" t="n">
-        <v>78.67</v>
+        <v>76.81</v>
       </c>
       <c r="I79" t="n">
-        <v>2375.9</v>
+        <v>2365.04</v>
       </c>
       <c r="J79" t="n">
-        <v>2424.97</v>
+        <v>2380.19</v>
       </c>
       <c r="K79" t="n">
-        <v>2452.23</v>
+        <v>2427.58</v>
       </c>
       <c r="L79" t="n">
-        <v>2479.49</v>
+        <v>2474.97</v>
       </c>
       <c r="M79" t="n">
-        <v>2517.65</v>
+        <v>2506.25</v>
       </c>
       <c r="N79" t="n">
-        <v>2555.82</v>
+        <v>2537.52</v>
       </c>
       <c r="O79" t="n">
-        <v>2572.18</v>
+        <v>2601.04</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7085,18 +7085,16 @@
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="n">
+        <v/>
       </c>
       <c r="U79" s="8" t="n">
         <v/>
@@ -7111,57 +7109,57 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2466.91</v>
+        <v>2437.14</v>
       </c>
       <c r="C80" t="n">
-        <v>2483.72</v>
+        <v>2663.05</v>
       </c>
       <c r="D80" t="n">
-        <v>2406.91</v>
+        <v>2435.29</v>
       </c>
       <c r="E80" t="n">
-        <v>2437.1</v>
+        <v>2514.73</v>
       </c>
       <c r="F80" t="n">
-        <v>-29.82</v>
+        <v>77.64</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-0.0121</v>
+        <v>0.0319</v>
       </c>
       <c r="H80" t="n">
-        <v>76.81</v>
+        <v>227.76</v>
       </c>
       <c r="I80" t="n">
-        <v>2365.04</v>
+        <v>2330.09</v>
       </c>
       <c r="J80" t="n">
-        <v>2380.19</v>
+        <v>2356.18</v>
       </c>
       <c r="K80" t="n">
-        <v>2427.58</v>
+        <v>2398.69</v>
       </c>
       <c r="L80" t="n">
-        <v>2474.97</v>
+        <v>2441.21</v>
       </c>
       <c r="M80" t="n">
-        <v>2506.25</v>
+        <v>2475.51</v>
       </c>
       <c r="N80" t="n">
-        <v>2537.52</v>
+        <v>2509.8</v>
       </c>
       <c r="O80" t="n">
-        <v>2601.04</v>
+        <v>2560.53</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7169,83 +7167,83 @@
       <c r="Q80" s="6" t="n">
         <v/>
       </c>
-      <c r="R80" s="6" t="inlineStr">
+      <c r="R80" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S80" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U80" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S80" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U80" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V80" s="8" t="n">
-        <v/>
+      <c r="V80" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W80" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2437.14</v>
+        <v>2514.77</v>
       </c>
       <c r="C81" t="n">
-        <v>2663.05</v>
+        <v>2544.47</v>
       </c>
       <c r="D81" t="n">
-        <v>2435.29</v>
+        <v>2508.8</v>
       </c>
       <c r="E81" t="n">
-        <v>2514.73</v>
+        <v>2525.94</v>
       </c>
       <c r="F81" t="n">
-        <v>77.64</v>
+        <v>11.21</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.0319</v>
+        <v>0.0045</v>
       </c>
       <c r="H81" t="n">
-        <v>227.76</v>
+        <v>35.67</v>
       </c>
       <c r="I81" t="n">
-        <v>2330.09</v>
+        <v>2207.52</v>
       </c>
       <c r="J81" t="n">
-        <v>2356.18</v>
+        <v>2269.75</v>
       </c>
       <c r="K81" t="n">
-        <v>2398.69</v>
+        <v>2400.85</v>
       </c>
       <c r="L81" t="n">
-        <v>2441.21</v>
+        <v>2531.95</v>
       </c>
       <c r="M81" t="n">
-        <v>2475.51</v>
+        <v>2628.62</v>
       </c>
       <c r="N81" t="n">
-        <v>2509.8</v>
+        <v>2725.28</v>
       </c>
       <c r="O81" t="n">
-        <v>2560.53</v>
+        <v>2890.82</v>
       </c>
       <c r="P81" s="6" t="n">
         <v/>
@@ -7256,93 +7254,97 @@
       <c r="R81" s="6" t="n">
         <v/>
       </c>
-      <c r="S81" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U81" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V81" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S81" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U81" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V81" s="8" t="n">
+        <v/>
       </c>
       <c r="W81" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr"/>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2514.77</v>
+        <v>2525.94</v>
       </c>
       <c r="C82" t="n">
-        <v>2544.47</v>
+        <v>2526.85</v>
       </c>
       <c r="D82" t="n">
-        <v>2508.8</v>
+        <v>2462.84</v>
       </c>
       <c r="E82" t="n">
-        <v>2525.94</v>
+        <v>2477.02</v>
       </c>
       <c r="F82" t="n">
-        <v>11.21</v>
+        <v>-48.92</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0194</v>
       </c>
       <c r="H82" t="n">
-        <v>35.67</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>2207.52</v>
+        <v>2473.13</v>
       </c>
       <c r="J82" t="n">
-        <v>2269.75</v>
+        <v>2489.93</v>
       </c>
       <c r="K82" t="n">
-        <v>2400.85</v>
+        <v>2508.11</v>
       </c>
       <c r="L82" t="n">
-        <v>2531.95</v>
+        <v>2526.29</v>
       </c>
       <c r="M82" t="n">
-        <v>2628.62</v>
+        <v>2543.78</v>
       </c>
       <c r="N82" t="n">
-        <v>2725.28</v>
+        <v>2561.27</v>
       </c>
       <c r="O82" t="n">
-        <v>2890.82</v>
-      </c>
-      <c r="P82" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q82" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R82" s="6" t="n">
-        <v/>
+        <v>2580.14</v>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S82" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T82" s="8" t="n">
@@ -7354,148 +7356,148 @@
       <c r="V82" s="8" t="n">
         <v/>
       </c>
-      <c r="W82" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W82" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2525.94</v>
+        <v>2476.6</v>
       </c>
       <c r="C83" t="n">
-        <v>2526.85</v>
+        <v>2612.4</v>
       </c>
       <c r="D83" t="n">
-        <v>2462.84</v>
+        <v>2465.43</v>
       </c>
       <c r="E83" t="n">
-        <v>2477.02</v>
+        <v>2514.41</v>
       </c>
       <c r="F83" t="n">
-        <v>-48.92</v>
+        <v>37.39</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.0194</v>
+        <v>0.0151</v>
       </c>
       <c r="H83" t="n">
-        <v>64.01000000000001</v>
+        <v>146.98</v>
       </c>
       <c r="I83" t="n">
-        <v>2473.13</v>
+        <v>2398.83</v>
       </c>
       <c r="J83" t="n">
-        <v>2489.93</v>
+        <v>2404.09</v>
       </c>
       <c r="K83" t="n">
-        <v>2508.11</v>
+        <v>2445.01</v>
       </c>
       <c r="L83" t="n">
-        <v>2526.29</v>
+        <v>2485.93</v>
       </c>
       <c r="M83" t="n">
-        <v>2543.78</v>
+        <v>2509.03</v>
       </c>
       <c r="N83" t="n">
-        <v>2561.27</v>
+        <v>2532.12</v>
       </c>
       <c r="O83" t="n">
-        <v>2580.14</v>
-      </c>
-      <c r="P83" s="6" t="inlineStr">
+        <v>2590.87</v>
+      </c>
+      <c r="P83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S83" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q83" s="6" t="inlineStr">
+      <c r="U83" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R83" s="6" t="inlineStr">
+      <c r="V83" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S83" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U83" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V83" s="8" t="n">
-        <v/>
-      </c>
       <c r="W83" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr"/>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2476.6</v>
+        <v>2514.36</v>
       </c>
       <c r="C84" t="n">
-        <v>2612.4</v>
+        <v>2519.32</v>
       </c>
       <c r="D84" t="n">
-        <v>2465.43</v>
+        <v>2357.96</v>
       </c>
       <c r="E84" t="n">
-        <v>2514.41</v>
+        <v>2399.09</v>
       </c>
       <c r="F84" t="n">
-        <v>37.39</v>
+        <v>-115.32</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.0459</v>
       </c>
       <c r="H84" t="n">
-        <v>146.98</v>
+        <v>161.36</v>
       </c>
       <c r="I84" t="n">
-        <v>2398.83</v>
+        <v>2318.45</v>
       </c>
       <c r="J84" t="n">
-        <v>2404.09</v>
+        <v>2355.18</v>
       </c>
       <c r="K84" t="n">
-        <v>2445.01</v>
+        <v>2440.92</v>
       </c>
       <c r="L84" t="n">
-        <v>2485.93</v>
+        <v>2526.66</v>
       </c>
       <c r="M84" t="n">
-        <v>2509.03</v>
+        <v>2587.9</v>
       </c>
       <c r="N84" t="n">
-        <v>2532.12</v>
+        <v>2649.13</v>
       </c>
       <c r="O84" t="n">
-        <v>2590.87</v>
+        <v>2759.38</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
@@ -7503,87 +7505,79 @@
       <c r="Q84" s="6" t="n">
         <v/>
       </c>
-      <c r="R84" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S84" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="inlineStr">
+      <c r="R84" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U84" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V84" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S84" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U84" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V84" s="8" t="n">
+        <v/>
       </c>
       <c r="W84" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2514.36</v>
+        <v>2399.06</v>
       </c>
       <c r="C85" t="n">
-        <v>2519.32</v>
+        <v>2426.93</v>
       </c>
       <c r="D85" t="n">
-        <v>2357.96</v>
+        <v>2368.74</v>
       </c>
       <c r="E85" t="n">
-        <v>2399.09</v>
+        <v>2416.12</v>
       </c>
       <c r="F85" t="n">
-        <v>-115.32</v>
+        <v>17.03</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.0459</v>
+        <v>0.0071</v>
       </c>
       <c r="H85" t="n">
-        <v>161.36</v>
+        <v>58.19</v>
       </c>
       <c r="I85" t="n">
-        <v>2318.45</v>
+        <v>2196.6</v>
       </c>
       <c r="J85" t="n">
-        <v>2355.18</v>
+        <v>2217.95</v>
       </c>
       <c r="K85" t="n">
-        <v>2440.92</v>
+        <v>2318.41</v>
       </c>
       <c r="L85" t="n">
-        <v>2526.66</v>
+        <v>2418.86</v>
       </c>
       <c r="M85" t="n">
-        <v>2587.9</v>
+        <v>2479.77</v>
       </c>
       <c r="N85" t="n">
-        <v>2649.13</v>
+        <v>2540.67</v>
       </c>
       <c r="O85" t="n">
-        <v>2759.38</v>
+        <v>2680.68</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7591,14 +7585,12 @@
       <c r="Q85" s="6" t="n">
         <v/>
       </c>
-      <c r="R85" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R85" s="6" t="n">
+        <v/>
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T85" s="8" t="n">
@@ -7615,55 +7607,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr"/>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2399.06</v>
+        <v>2416.17</v>
       </c>
       <c r="C86" t="n">
-        <v>2426.93</v>
+        <v>2480.74</v>
       </c>
       <c r="D86" t="n">
-        <v>2368.74</v>
+        <v>2412.19</v>
       </c>
       <c r="E86" t="n">
-        <v>2416.12</v>
+        <v>2447.11</v>
       </c>
       <c r="F86" t="n">
-        <v>17.03</v>
+        <v>30.99</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0128</v>
       </c>
       <c r="H86" t="n">
-        <v>58.19</v>
+        <v>68.55</v>
       </c>
       <c r="I86" t="n">
-        <v>2196.6</v>
+        <v>2310.54</v>
       </c>
       <c r="J86" t="n">
-        <v>2217.95</v>
+        <v>2367.07</v>
       </c>
       <c r="K86" t="n">
-        <v>2318.41</v>
+        <v>2387.02</v>
       </c>
       <c r="L86" t="n">
-        <v>2418.86</v>
+        <v>2406.98</v>
       </c>
       <c r="M86" t="n">
-        <v>2479.77</v>
+        <v>2445.22</v>
       </c>
       <c r="N86" t="n">
-        <v>2540.67</v>
+        <v>2483.46</v>
       </c>
       <c r="O86" t="n">
-        <v>2680.68</v>
+        <v>2485.12</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7674,13 +7670,15 @@
       <c r="R86" s="6" t="n">
         <v/>
       </c>
-      <c r="S86" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T86" s="8" t="n">
-        <v/>
+      <c r="S86" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U86" s="8" t="n">
         <v/>
@@ -7695,57 +7693,57 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2416.17</v>
+        <v>2447.11</v>
       </c>
       <c r="C87" t="n">
-        <v>2480.74</v>
+        <v>2643.96</v>
       </c>
       <c r="D87" t="n">
-        <v>2412.19</v>
+        <v>2435.15</v>
       </c>
       <c r="E87" t="n">
-        <v>2447.11</v>
+        <v>2611.35</v>
       </c>
       <c r="F87" t="n">
-        <v>30.99</v>
+        <v>164.24</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>68.55</v>
+        <v>208.81</v>
       </c>
       <c r="I87" t="n">
-        <v>2310.54</v>
+        <v>2343.64</v>
       </c>
       <c r="J87" t="n">
-        <v>2367.07</v>
+        <v>2378.88</v>
       </c>
       <c r="K87" t="n">
-        <v>2387.02</v>
+        <v>2412.83</v>
       </c>
       <c r="L87" t="n">
-        <v>2406.98</v>
+        <v>2446.78</v>
       </c>
       <c r="M87" t="n">
-        <v>2445.22</v>
+        <v>2481.38</v>
       </c>
       <c r="N87" t="n">
-        <v>2483.46</v>
+        <v>2515.98</v>
       </c>
       <c r="O87" t="n">
-        <v>2485.12</v>
+        <v>2549.29</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7763,73 +7761,73 @@
       </c>
       <c r="T87" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U87" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V87" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V87" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W87" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W87" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2447.11</v>
+        <v>2611.46</v>
       </c>
       <c r="C88" t="n">
-        <v>2643.96</v>
+        <v>2659.72</v>
       </c>
       <c r="D88" t="n">
-        <v>2435.15</v>
+        <v>2602.74</v>
       </c>
       <c r="E88" t="n">
-        <v>2611.35</v>
+        <v>2631.96</v>
       </c>
       <c r="F88" t="n">
-        <v>164.24</v>
+        <v>20.62</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>208.81</v>
+        <v>56.98</v>
       </c>
       <c r="I88" t="n">
-        <v>2343.64</v>
+        <v>2226.33</v>
       </c>
       <c r="J88" t="n">
-        <v>2378.88</v>
+        <v>2438.43</v>
       </c>
       <c r="K88" t="n">
-        <v>2412.83</v>
+        <v>2506.94</v>
       </c>
       <c r="L88" t="n">
-        <v>2446.78</v>
+        <v>2575.45</v>
       </c>
       <c r="M88" t="n">
-        <v>2481.38</v>
+        <v>2715.75</v>
       </c>
       <c r="N88" t="n">
-        <v>2515.98</v>
+        <v>2856.06</v>
       </c>
       <c r="O88" t="n">
-        <v>2549.29</v>
+        <v>2852.78</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
@@ -7842,23 +7840,17 @@
       </c>
       <c r="S88" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V88" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U88" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V88" s="8" t="n">
+        <v/>
       </c>
       <c r="W88" s="9" t="inlineStr">
         <is>
@@ -7870,59 +7862,63 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2611.46</v>
+        <v>2632.01</v>
       </c>
       <c r="C89" t="n">
-        <v>2659.72</v>
+        <v>2647.87</v>
       </c>
       <c r="D89" t="n">
-        <v>2602.74</v>
+        <v>2564.43</v>
       </c>
       <c r="E89" t="n">
-        <v>2631.96</v>
+        <v>2643</v>
       </c>
       <c r="F89" t="n">
-        <v>20.62</v>
+        <v>11.03</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0042</v>
       </c>
       <c r="H89" t="n">
-        <v>56.98</v>
+        <v>83.44</v>
       </c>
       <c r="I89" t="n">
-        <v>2226.33</v>
+        <v>2545.76</v>
       </c>
       <c r="J89" t="n">
-        <v>2438.43</v>
+        <v>2575.35</v>
       </c>
       <c r="K89" t="n">
-        <v>2506.94</v>
+        <v>2603.47</v>
       </c>
       <c r="L89" t="n">
-        <v>2575.45</v>
+        <v>2631.6</v>
       </c>
       <c r="M89" t="n">
-        <v>2715.75</v>
+        <v>2660.45</v>
       </c>
       <c r="N89" t="n">
-        <v>2856.06</v>
+        <v>2689.31</v>
       </c>
       <c r="O89" t="n">
-        <v>2852.78</v>
+        <v>2716.7</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
       </c>
-      <c r="Q89" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R89" s="6" t="n">
-        <v/>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S89" s="10" t="inlineStr">
         <is>
@@ -7943,141 +7939,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr"/>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2632.01</v>
+        <v>2642.78</v>
       </c>
       <c r="C90" t="n">
-        <v>2647.87</v>
+        <v>2805.5</v>
       </c>
       <c r="D90" t="n">
-        <v>2564.43</v>
+        <v>2642.78</v>
       </c>
       <c r="E90" t="n">
-        <v>2643</v>
+        <v>2776.47</v>
       </c>
       <c r="F90" t="n">
-        <v>11.03</v>
+        <v>133.47</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0505</v>
       </c>
       <c r="H90" t="n">
-        <v>83.44</v>
+        <v>162.72</v>
       </c>
       <c r="I90" t="n">
-        <v>2545.76</v>
+        <v>2480.99</v>
       </c>
       <c r="J90" t="n">
-        <v>2575.35</v>
+        <v>2577.98</v>
       </c>
       <c r="K90" t="n">
-        <v>2603.47</v>
+        <v>2601.28</v>
       </c>
       <c r="L90" t="n">
-        <v>2631.6</v>
+        <v>2624.58</v>
       </c>
       <c r="M90" t="n">
-        <v>2660.45</v>
+        <v>2684.72</v>
       </c>
       <c r="N90" t="n">
-        <v>2689.31</v>
+        <v>2744.86</v>
       </c>
       <c r="O90" t="n">
-        <v>2716.7</v>
+        <v>2731.31</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
       </c>
-      <c r="Q90" s="6" t="inlineStr">
+      <c r="Q90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R90" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S90" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R90" s="6" t="inlineStr">
+      <c r="U90" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V90" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S90" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U90" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V90" s="8" t="n">
-        <v/>
-      </c>
       <c r="W90" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2644.8</v>
+        <v>2775.96</v>
       </c>
       <c r="C91" t="n">
-        <v>2804.96</v>
+        <v>2776.61</v>
       </c>
       <c r="D91" t="n">
-        <v>2644.8</v>
+        <v>2718.93</v>
       </c>
       <c r="E91" t="n">
-        <v>2770.86</v>
+        <v>2752.99</v>
       </c>
       <c r="F91" t="n">
-        <v>127.86</v>
+        <v>-23.48</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.0484</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>160.17</v>
+        <v>57.68</v>
       </c>
       <c r="I91" t="n">
-        <v>2480.99</v>
+        <v>2480.07</v>
       </c>
       <c r="J91" t="n">
-        <v>2577.98</v>
+        <v>2639.92</v>
       </c>
       <c r="K91" t="n">
-        <v>2601.28</v>
+        <v>2695.11</v>
       </c>
       <c r="L91" t="n">
-        <v>2624.58</v>
+        <v>2750.3</v>
       </c>
       <c r="M91" t="n">
-        <v>2684.72</v>
+        <v>2857.83</v>
       </c>
       <c r="N91" t="n">
-        <v>2744.86</v>
+        <v>2965.35</v>
       </c>
       <c r="O91" t="n">
-        <v>2731.31</v>
+        <v>2968.22</v>
       </c>
       <c r="P91" s="6" t="n">
         <v/>
@@ -8090,30 +8088,28 @@
       </c>
       <c r="S91" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U91" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
       </c>
       <c r="W91" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr"/>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -8045,13 +8045,13 @@
         <v>2718.93</v>
       </c>
       <c r="E91" t="n">
-        <v>2752.99</v>
+        <v>2739.44</v>
       </c>
       <c r="F91" t="n">
-        <v>-23.48</v>
+        <v>-37.03</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0133</v>
       </c>
       <c r="H91" t="n">
         <v>57.68</v>
@@ -8086,9 +8086,9 @@
       <c r="R91" s="6" t="n">
         <v/>
       </c>
-      <c r="S91" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T91" s="8" t="n">

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X91"/>
+  <dimension ref="A1:X90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1619.89</v>
+        <v>1564.61</v>
       </c>
       <c r="C2" t="n">
-        <v>1656.65</v>
+        <v>1590.2</v>
       </c>
       <c r="D2" t="n">
-        <v>1531.78</v>
+        <v>1510.51</v>
       </c>
       <c r="E2" t="n">
-        <v>1564.82</v>
+        <v>1576.62</v>
       </c>
       <c r="F2" t="n">
-        <v>-55.11</v>
+        <v>11.8</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.034</v>
+        <v>0.0075</v>
       </c>
       <c r="H2" t="n">
-        <v>124.87</v>
+        <v>79.69</v>
       </c>
       <c r="I2" t="n">
-        <v>1415.48</v>
+        <v>1406.91</v>
       </c>
       <c r="J2" t="n">
-        <v>1484.14</v>
+        <v>1425.25</v>
       </c>
       <c r="K2" t="n">
-        <v>1551.92</v>
+        <v>1502.38</v>
       </c>
       <c r="L2" t="n">
-        <v>1619.71</v>
+        <v>1579.52</v>
       </c>
       <c r="M2" t="n">
-        <v>1687.93</v>
+        <v>1627.25</v>
       </c>
       <c r="N2" t="n">
-        <v>1756.15</v>
+        <v>1674.98</v>
       </c>
       <c r="O2" t="n">
-        <v>1823.5</v>
+        <v>1781.51</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,14 +685,12 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -711,57 +709,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1564.61</v>
+        <v>1576.59</v>
       </c>
       <c r="C3" t="n">
-        <v>1590.2</v>
+        <v>1607.87</v>
       </c>
       <c r="D3" t="n">
-        <v>1510.51</v>
+        <v>1561.97</v>
       </c>
       <c r="E3" t="n">
-        <v>1576.62</v>
+        <v>1571.59</v>
       </c>
       <c r="F3" t="n">
-        <v>11.8</v>
+        <v>-5.03</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0032</v>
       </c>
       <c r="H3" t="n">
-        <v>79.69</v>
+        <v>45.89</v>
       </c>
       <c r="I3" t="n">
-        <v>1406.91</v>
+        <v>1430.81</v>
       </c>
       <c r="J3" t="n">
-        <v>1425.25</v>
+        <v>1510.05</v>
       </c>
       <c r="K3" t="n">
-        <v>1502.38</v>
+        <v>1536.77</v>
       </c>
       <c r="L3" t="n">
-        <v>1579.52</v>
+        <v>1563.48</v>
       </c>
       <c r="M3" t="n">
-        <v>1627.25</v>
+        <v>1616.46</v>
       </c>
       <c r="N3" t="n">
-        <v>1674.98</v>
+        <v>1669.44</v>
       </c>
       <c r="O3" t="n">
-        <v>1781.51</v>
+        <v>1669.89</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,9 +770,9 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -793,57 +791,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1576.59</v>
+        <v>1571.56</v>
       </c>
       <c r="C4" t="n">
-        <v>1607.87</v>
+        <v>1585.22</v>
       </c>
       <c r="D4" t="n">
-        <v>1561.97</v>
+        <v>1548.76</v>
       </c>
       <c r="E4" t="n">
-        <v>1571.59</v>
+        <v>1570.36</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.03</v>
+        <v>-1.23</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.0008</v>
       </c>
       <c r="H4" t="n">
-        <v>45.89</v>
+        <v>36.46</v>
       </c>
       <c r="I4" t="n">
-        <v>1430.81</v>
+        <v>1516.08</v>
       </c>
       <c r="J4" t="n">
-        <v>1510.05</v>
+        <v>1519.03</v>
       </c>
       <c r="K4" t="n">
-        <v>1536.77</v>
+        <v>1548.64</v>
       </c>
       <c r="L4" t="n">
-        <v>1563.48</v>
+        <v>1578.25</v>
       </c>
       <c r="M4" t="n">
-        <v>1616.46</v>
+        <v>1594.53</v>
       </c>
       <c r="N4" t="n">
-        <v>1669.44</v>
+        <v>1610.82</v>
       </c>
       <c r="O4" t="n">
-        <v>1669.89</v>
+        <v>1653.76</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,9 +852,9 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -875,57 +873,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1571.56</v>
+        <v>1569.99</v>
       </c>
       <c r="C5" t="n">
-        <v>1585.22</v>
+        <v>1633.65</v>
       </c>
       <c r="D5" t="n">
-        <v>1548.76</v>
+        <v>1550.04</v>
       </c>
       <c r="E5" t="n">
-        <v>1570.36</v>
+        <v>1610.21</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.23</v>
+        <v>39.84</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0254</v>
       </c>
       <c r="H5" t="n">
-        <v>36.46</v>
+        <v>83.61</v>
       </c>
       <c r="I5" t="n">
-        <v>1516.08</v>
+        <v>1512.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1519.03</v>
+        <v>1535.59</v>
       </c>
       <c r="K5" t="n">
-        <v>1548.64</v>
+        <v>1552.13</v>
       </c>
       <c r="L5" t="n">
-        <v>1578.25</v>
+        <v>1568.68</v>
       </c>
       <c r="M5" t="n">
-        <v>1594.53</v>
+        <v>1588.59</v>
       </c>
       <c r="N5" t="n">
-        <v>1610.82</v>
+        <v>1608.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1653.76</v>
+        <v>1621.68</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,81 +931,85 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1569.99</v>
+        <v>1610.16</v>
       </c>
       <c r="C6" t="n">
-        <v>1633.65</v>
+        <v>1611.35</v>
       </c>
       <c r="D6" t="n">
-        <v>1550.04</v>
+        <v>1549.25</v>
       </c>
       <c r="E6" t="n">
-        <v>1610.21</v>
+        <v>1569.58</v>
       </c>
       <c r="F6" t="n">
-        <v>39.84</v>
+        <v>-40.62</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0254</v>
+        <v>-0.0252</v>
       </c>
       <c r="H6" t="n">
-        <v>83.61</v>
+        <v>62.1</v>
       </c>
       <c r="I6" t="n">
-        <v>1512.3</v>
+        <v>1466.43</v>
       </c>
       <c r="J6" t="n">
-        <v>1535.59</v>
+        <v>1535.78</v>
       </c>
       <c r="K6" t="n">
-        <v>1552.13</v>
+        <v>1568.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1568.68</v>
+        <v>1601.02</v>
       </c>
       <c r="M6" t="n">
-        <v>1588.59</v>
+        <v>1652.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1608.5</v>
+        <v>1703</v>
       </c>
       <c r="O6" t="n">
-        <v>1621.68</v>
+        <v>1717.25</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,83 +1019,81 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1610.16</v>
+        <v>1569.91</v>
       </c>
       <c r="C7" t="n">
-        <v>1611.35</v>
+        <v>1642.45</v>
       </c>
       <c r="D7" t="n">
-        <v>1549.25</v>
+        <v>1551.14</v>
       </c>
       <c r="E7" t="n">
-        <v>1569.58</v>
+        <v>1608.96</v>
       </c>
       <c r="F7" t="n">
-        <v>-40.62</v>
+        <v>39.38</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0252</v>
+        <v>0.0251</v>
       </c>
       <c r="H7" t="n">
-        <v>62.1</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1466.43</v>
+        <v>1487.16</v>
       </c>
       <c r="J7" t="n">
-        <v>1535.78</v>
+        <v>1502.13</v>
       </c>
       <c r="K7" t="n">
-        <v>1568.4</v>
+        <v>1538.54</v>
       </c>
       <c r="L7" t="n">
-        <v>1601.02</v>
+        <v>1574.94</v>
       </c>
       <c r="M7" t="n">
-        <v>1652.01</v>
+        <v>1600.63</v>
       </c>
       <c r="N7" t="n">
-        <v>1703</v>
+        <v>1626.32</v>
       </c>
       <c r="O7" t="n">
-        <v>1717.25</v>
+        <v>1673.44</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1101,21 +1101,23 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1125,59 +1127,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1569.91</v>
+        <v>1609.01</v>
       </c>
       <c r="C8" t="n">
-        <v>1642.45</v>
+        <v>1720.34</v>
       </c>
       <c r="D8" t="n">
-        <v>1551.14</v>
+        <v>1595.94</v>
       </c>
       <c r="E8" t="n">
-        <v>1608.96</v>
+        <v>1698.17</v>
       </c>
       <c r="F8" t="n">
-        <v>39.38</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0554</v>
       </c>
       <c r="H8" t="n">
-        <v>91.31999999999999</v>
+        <v>124.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1487.16</v>
+        <v>1459.82</v>
       </c>
       <c r="J8" t="n">
-        <v>1502.13</v>
+        <v>1523.73</v>
       </c>
       <c r="K8" t="n">
-        <v>1538.54</v>
+        <v>1563.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1574.94</v>
+        <v>1602.88</v>
       </c>
       <c r="M8" t="n">
-        <v>1600.63</v>
+        <v>1654.62</v>
       </c>
       <c r="N8" t="n">
-        <v>1626.32</v>
+        <v>1706.36</v>
       </c>
       <c r="O8" t="n">
-        <v>1673.44</v>
+        <v>1733.77</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1195,12 +1193,12 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V8" s="8" t="n">
@@ -1216,50 +1214,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1609.01</v>
+        <v>1698.42</v>
       </c>
       <c r="C9" t="n">
-        <v>1720.34</v>
+        <v>1772.54</v>
       </c>
       <c r="D9" t="n">
-        <v>1595.94</v>
+        <v>1693.04</v>
       </c>
       <c r="E9" t="n">
-        <v>1698.17</v>
+        <v>1756.52</v>
       </c>
       <c r="F9" t="n">
-        <v>89.20999999999999</v>
+        <v>58.35</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0344</v>
       </c>
       <c r="H9" t="n">
-        <v>124.4</v>
+        <v>79.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1459.82</v>
+        <v>1471.54</v>
       </c>
       <c r="J9" t="n">
-        <v>1523.73</v>
+        <v>1593.78</v>
       </c>
       <c r="K9" t="n">
-        <v>1563.3</v>
+        <v>1635.97</v>
       </c>
       <c r="L9" t="n">
-        <v>1602.88</v>
+        <v>1678.16</v>
       </c>
       <c r="M9" t="n">
-        <v>1654.62</v>
+        <v>1760.37</v>
       </c>
       <c r="N9" t="n">
-        <v>1706.36</v>
+        <v>1842.59</v>
       </c>
       <c r="O9" t="n">
-        <v>1733.77</v>
+        <v>1844.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1277,13 +1275,11 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1298,50 +1294,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1698.42</v>
+        <v>1756.58</v>
       </c>
       <c r="C10" t="n">
-        <v>1772.54</v>
+        <v>1804.59</v>
       </c>
       <c r="D10" t="n">
-        <v>1693.04</v>
+        <v>1743.56</v>
       </c>
       <c r="E10" t="n">
-        <v>1756.52</v>
+        <v>1779.03</v>
       </c>
       <c r="F10" t="n">
-        <v>58.35</v>
+        <v>22.51</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0128</v>
       </c>
       <c r="H10" t="n">
-        <v>79.5</v>
+        <v>61.02</v>
       </c>
       <c r="I10" t="n">
-        <v>1471.54</v>
+        <v>1613.53</v>
       </c>
       <c r="J10" t="n">
-        <v>1593.78</v>
+        <v>1688.88</v>
       </c>
       <c r="K10" t="n">
-        <v>1635.97</v>
+        <v>1716.77</v>
       </c>
       <c r="L10" t="n">
-        <v>1678.16</v>
+        <v>1744.65</v>
       </c>
       <c r="M10" t="n">
-        <v>1760.37</v>
+        <v>1796.27</v>
       </c>
       <c r="N10" t="n">
-        <v>1842.59</v>
+        <v>1847.89</v>
       </c>
       <c r="O10" t="n">
-        <v>1844.75</v>
+        <v>1852.05</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1378,50 +1374,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1756.58</v>
+        <v>1779.04</v>
       </c>
       <c r="C11" t="n">
-        <v>1804.59</v>
+        <v>1805.91</v>
       </c>
       <c r="D11" t="n">
-        <v>1743.56</v>
+        <v>1749.14</v>
       </c>
       <c r="E11" t="n">
-        <v>1779.03</v>
+        <v>1783.01</v>
       </c>
       <c r="F11" t="n">
-        <v>22.51</v>
+        <v>3.97</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0022</v>
       </c>
       <c r="H11" t="n">
-        <v>61.02</v>
+        <v>56.78</v>
       </c>
       <c r="I11" t="n">
-        <v>1613.53</v>
+        <v>1682.54</v>
       </c>
       <c r="J11" t="n">
-        <v>1688.88</v>
+        <v>1720.49</v>
       </c>
       <c r="K11" t="n">
-        <v>1716.77</v>
+        <v>1748.52</v>
       </c>
       <c r="L11" t="n">
-        <v>1744.65</v>
+        <v>1776.55</v>
       </c>
       <c r="M11" t="n">
-        <v>1796.27</v>
+        <v>1809.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1847.89</v>
+        <v>1842.54</v>
       </c>
       <c r="O11" t="n">
-        <v>1852.05</v>
+        <v>1865.61</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1434,13 +1430,11 @@
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1458,67 +1452,73 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779.04</v>
+        <v>1783</v>
       </c>
       <c r="C12" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D12" t="n">
-        <v>1749.14</v>
+        <v>1728.97</v>
       </c>
       <c r="E12" t="n">
-        <v>1783.01</v>
+        <v>1797.57</v>
       </c>
       <c r="F12" t="n">
-        <v>3.97</v>
+        <v>14.57</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>56.78</v>
+        <v>100.55</v>
       </c>
       <c r="I12" t="n">
-        <v>1682.54</v>
+        <v>1692.36</v>
       </c>
       <c r="J12" t="n">
-        <v>1720.49</v>
+        <v>1728.97</v>
       </c>
       <c r="K12" t="n">
-        <v>1748.52</v>
+        <v>1754.62</v>
       </c>
       <c r="L12" t="n">
-        <v>1776.55</v>
+        <v>1780.27</v>
       </c>
       <c r="M12" t="n">
-        <v>1809.55</v>
+        <v>1811.39</v>
       </c>
       <c r="N12" t="n">
-        <v>1842.54</v>
+        <v>1842.52</v>
       </c>
       <c r="O12" t="n">
-        <v>1865.61</v>
+        <v>1862.69</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1531,78 +1531,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1783</v>
+        <v>1797.56</v>
       </c>
       <c r="C13" t="n">
-        <v>1829.51</v>
+        <v>1810.33</v>
       </c>
       <c r="D13" t="n">
-        <v>1728.97</v>
+        <v>1756.71</v>
       </c>
       <c r="E13" t="n">
-        <v>1797.57</v>
+        <v>1768.51</v>
       </c>
       <c r="F13" t="n">
-        <v>14.57</v>
+        <v>-29.06</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0162</v>
       </c>
       <c r="H13" t="n">
-        <v>100.55</v>
+        <v>53.62</v>
       </c>
       <c r="I13" t="n">
-        <v>1692.36</v>
+        <v>1628.42</v>
       </c>
       <c r="J13" t="n">
-        <v>1728.97</v>
+        <v>1706.19</v>
       </c>
       <c r="K13" t="n">
-        <v>1754.62</v>
+        <v>1747.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1780.27</v>
+        <v>1788.41</v>
       </c>
       <c r="M13" t="n">
-        <v>1811.39</v>
+        <v>1847.85</v>
       </c>
       <c r="N13" t="n">
-        <v>1842.52</v>
+        <v>1907.29</v>
       </c>
       <c r="O13" t="n">
-        <v>1862.69</v>
+        <v>1930.06</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1617,57 +1615,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1797.56</v>
+        <v>1768.39</v>
       </c>
       <c r="C14" t="n">
-        <v>1810.33</v>
+        <v>1782.86</v>
       </c>
       <c r="D14" t="n">
-        <v>1756.71</v>
+        <v>1711.9</v>
       </c>
       <c r="E14" t="n">
-        <v>1768.51</v>
+        <v>1742.68</v>
       </c>
       <c r="F14" t="n">
-        <v>-29.06</v>
+        <v>-25.83</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0146</v>
       </c>
       <c r="H14" t="n">
-        <v>53.62</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1628.42</v>
+        <v>1703.1</v>
       </c>
       <c r="J14" t="n">
-        <v>1706.19</v>
+        <v>1707.39</v>
       </c>
       <c r="K14" t="n">
-        <v>1747.3</v>
+        <v>1741.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1788.41</v>
+        <v>1776.02</v>
       </c>
       <c r="M14" t="n">
-        <v>1847.85</v>
+        <v>1795.32</v>
       </c>
       <c r="N14" t="n">
-        <v>1907.29</v>
+        <v>1814.62</v>
       </c>
       <c r="O14" t="n">
-        <v>1930.06</v>
+        <v>1863.95</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1675,12 +1673,14 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1699,57 +1699,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1768.39</v>
+        <v>1742.66</v>
       </c>
       <c r="C15" t="n">
-        <v>1782.86</v>
+        <v>1760.21</v>
       </c>
       <c r="D15" t="n">
-        <v>1711.9</v>
+        <v>1721.3</v>
       </c>
       <c r="E15" t="n">
-        <v>1742.68</v>
+        <v>1744.48</v>
       </c>
       <c r="F15" t="n">
-        <v>-25.83</v>
+        <v>1.81</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>70.95999999999999</v>
+        <v>38.91</v>
       </c>
       <c r="I15" t="n">
-        <v>1703.1</v>
+        <v>1640.94</v>
       </c>
       <c r="J15" t="n">
-        <v>1707.39</v>
+        <v>1669.37</v>
       </c>
       <c r="K15" t="n">
-        <v>1741.7</v>
+        <v>1707.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1776.02</v>
+        <v>1745.03</v>
       </c>
       <c r="M15" t="n">
-        <v>1795.32</v>
+        <v>1778.16</v>
       </c>
       <c r="N15" t="n">
-        <v>1814.62</v>
+        <v>1811.29</v>
       </c>
       <c r="O15" t="n">
-        <v>1863.95</v>
+        <v>1853.82</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1757,14 +1757,12 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1783,57 +1781,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1742.66</v>
+        <v>1744.47</v>
       </c>
       <c r="C16" t="n">
-        <v>1760.21</v>
+        <v>1809.76</v>
       </c>
       <c r="D16" t="n">
-        <v>1721.3</v>
+        <v>1736.72</v>
       </c>
       <c r="E16" t="n">
-        <v>1744.48</v>
+        <v>1795.69</v>
       </c>
       <c r="F16" t="n">
-        <v>1.81</v>
+        <v>51.21</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0294</v>
       </c>
       <c r="H16" t="n">
-        <v>38.91</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1640.94</v>
+        <v>1682.39</v>
       </c>
       <c r="J16" t="n">
-        <v>1669.37</v>
+        <v>1707.44</v>
       </c>
       <c r="K16" t="n">
-        <v>1707.2</v>
+        <v>1725.03</v>
       </c>
       <c r="L16" t="n">
-        <v>1745.03</v>
+        <v>1742.62</v>
       </c>
       <c r="M16" t="n">
-        <v>1778.16</v>
+        <v>1763.94</v>
       </c>
       <c r="N16" t="n">
-        <v>1811.29</v>
+        <v>1785.26</v>
       </c>
       <c r="O16" t="n">
-        <v>1853.82</v>
+        <v>1799.11</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1844,78 +1842,80 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1744.47</v>
+        <v>1795.82</v>
       </c>
       <c r="C17" t="n">
-        <v>1809.76</v>
+        <v>1827.83</v>
       </c>
       <c r="D17" t="n">
-        <v>1736.72</v>
+        <v>1786.3</v>
       </c>
       <c r="E17" t="n">
-        <v>1795.69</v>
+        <v>1788.1</v>
       </c>
       <c r="F17" t="n">
-        <v>51.21</v>
+        <v>-7.59</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0294</v>
+        <v>-0.0042</v>
       </c>
       <c r="H17" t="n">
-        <v>73.04000000000001</v>
+        <v>41.54</v>
       </c>
       <c r="I17" t="n">
-        <v>1682.39</v>
+        <v>1663.69</v>
       </c>
       <c r="J17" t="n">
-        <v>1707.44</v>
+        <v>1733.88</v>
       </c>
       <c r="K17" t="n">
-        <v>1725.03</v>
+        <v>1759.18</v>
       </c>
       <c r="L17" t="n">
-        <v>1742.62</v>
+        <v>1784.47</v>
       </c>
       <c r="M17" t="n">
-        <v>1763.94</v>
+        <v>1832.21</v>
       </c>
       <c r="N17" t="n">
-        <v>1785.26</v>
+        <v>1879.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1799.11</v>
+        <v>1882.79</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1928,78 +1928,76 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1795.82</v>
+        <v>1787.57</v>
       </c>
       <c r="C18" t="n">
-        <v>1827.83</v>
+        <v>1824.98</v>
       </c>
       <c r="D18" t="n">
-        <v>1786.3</v>
+        <v>1779.64</v>
       </c>
       <c r="E18" t="n">
-        <v>1788.1</v>
+        <v>1805.79</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.59</v>
+        <v>17.69</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>41.54</v>
+        <v>45.34</v>
       </c>
       <c r="I18" t="n">
-        <v>1663.69</v>
+        <v>1744.76</v>
       </c>
       <c r="J18" t="n">
-        <v>1733.88</v>
+        <v>1737.08</v>
       </c>
       <c r="K18" t="n">
-        <v>1759.18</v>
+        <v>1767.33</v>
       </c>
       <c r="L18" t="n">
-        <v>1784.47</v>
+        <v>1797.58</v>
       </c>
       <c r="M18" t="n">
-        <v>1832.21</v>
+        <v>1808.87</v>
       </c>
       <c r="N18" t="n">
-        <v>1879.95</v>
+        <v>1820.15</v>
       </c>
       <c r="O18" t="n">
-        <v>1882.79</v>
+        <v>1869.37</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2012,14 +2010,18 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2031,81 +2033,83 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1787.57</v>
+        <v>1805.76</v>
       </c>
       <c r="C19" t="n">
-        <v>1824.98</v>
+        <v>1842.46</v>
       </c>
       <c r="D19" t="n">
-        <v>1779.64</v>
+        <v>1749.35</v>
       </c>
       <c r="E19" t="n">
-        <v>1805.79</v>
+        <v>1773.5</v>
       </c>
       <c r="F19" t="n">
-        <v>17.69</v>
+        <v>-32.29</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.0179</v>
       </c>
       <c r="H19" t="n">
-        <v>45.34</v>
+        <v>93.11</v>
       </c>
       <c r="I19" t="n">
-        <v>1744.76</v>
+        <v>1734.29</v>
       </c>
       <c r="J19" t="n">
-        <v>1737.08</v>
+        <v>1762.18</v>
       </c>
       <c r="K19" t="n">
-        <v>1767.33</v>
+        <v>1783.12</v>
       </c>
       <c r="L19" t="n">
-        <v>1797.58</v>
+        <v>1804.05</v>
       </c>
       <c r="M19" t="n">
-        <v>1808.87</v>
+        <v>1828.46</v>
       </c>
       <c r="N19" t="n">
-        <v>1820.15</v>
+        <v>1852.87</v>
       </c>
       <c r="O19" t="n">
-        <v>1869.37</v>
+        <v>1870.32</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2124,77 +2128,75 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1805.76</v>
+        <v>1773.47</v>
       </c>
       <c r="C20" t="n">
-        <v>1842.46</v>
+        <v>1894.06</v>
       </c>
       <c r="D20" t="n">
-        <v>1749.35</v>
+        <v>1772.02</v>
       </c>
       <c r="E20" t="n">
-        <v>1773.5</v>
+        <v>1889.48</v>
       </c>
       <c r="F20" t="n">
-        <v>-32.29</v>
+        <v>115.98</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0654</v>
       </c>
       <c r="H20" t="n">
-        <v>93.11</v>
+        <v>122.04</v>
       </c>
       <c r="I20" t="n">
-        <v>1734.29</v>
+        <v>1656.24</v>
       </c>
       <c r="J20" t="n">
-        <v>1762.18</v>
+        <v>1669.19</v>
       </c>
       <c r="K20" t="n">
-        <v>1783.12</v>
+        <v>1726.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1804.05</v>
+        <v>1784.7</v>
       </c>
       <c r="M20" t="n">
-        <v>1828.46</v>
+        <v>1820.05</v>
       </c>
       <c r="N20" t="n">
-        <v>1852.87</v>
+        <v>1855.41</v>
       </c>
       <c r="O20" t="n">
-        <v>1870.32</v>
+        <v>1935.56</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2203,59 +2205,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1773.47</v>
+        <v>1889.5</v>
       </c>
       <c r="C21" t="n">
-        <v>1894.06</v>
+        <v>1944.16</v>
       </c>
       <c r="D21" t="n">
-        <v>1772.02</v>
+        <v>1863.64</v>
       </c>
       <c r="E21" t="n">
-        <v>1889.48</v>
+        <v>1916.94</v>
       </c>
       <c r="F21" t="n">
-        <v>115.98</v>
+        <v>27.46</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0654</v>
+        <v>0.0145</v>
       </c>
       <c r="H21" t="n">
-        <v>122.04</v>
+        <v>80.53</v>
       </c>
       <c r="I21" t="n">
-        <v>1656.24</v>
+        <v>1649.97</v>
       </c>
       <c r="J21" t="n">
-        <v>1669.19</v>
+        <v>1795.66</v>
       </c>
       <c r="K21" t="n">
-        <v>1726.95</v>
+        <v>1828.46</v>
       </c>
       <c r="L21" t="n">
-        <v>1784.7</v>
+        <v>1861.26</v>
       </c>
       <c r="M21" t="n">
-        <v>1820.05</v>
+        <v>1950.5</v>
       </c>
       <c r="N21" t="n">
-        <v>1855.41</v>
+        <v>2039.74</v>
       </c>
       <c r="O21" t="n">
-        <v>1935.56</v>
+        <v>2016.11</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,13 +2271,11 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2294,50 +2290,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1889.5</v>
+        <v>1916.98</v>
       </c>
       <c r="C22" t="n">
-        <v>1944.16</v>
+        <v>1927.09</v>
       </c>
       <c r="D22" t="n">
-        <v>1863.64</v>
+        <v>1856.78</v>
       </c>
       <c r="E22" t="n">
-        <v>1916.94</v>
+        <v>1863.19</v>
       </c>
       <c r="F22" t="n">
-        <v>27.46</v>
+        <v>-53.75</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0145</v>
+        <v>-0.028</v>
       </c>
       <c r="H22" t="n">
-        <v>80.53</v>
+        <v>70.31</v>
       </c>
       <c r="I22" t="n">
-        <v>1649.97</v>
+        <v>1783.11</v>
       </c>
       <c r="J22" t="n">
-        <v>1795.66</v>
+        <v>1842.94</v>
       </c>
       <c r="K22" t="n">
-        <v>1828.46</v>
+        <v>1876.68</v>
       </c>
       <c r="L22" t="n">
-        <v>1861.26</v>
+        <v>1910.42</v>
       </c>
       <c r="M22" t="n">
-        <v>1950.5</v>
+        <v>1957.21</v>
       </c>
       <c r="N22" t="n">
-        <v>2039.74</v>
+        <v>2003.99</v>
       </c>
       <c r="O22" t="n">
-        <v>2016.11</v>
+        <v>2024.69</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2345,19 +2341,19 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2369,55 +2365,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1916.98</v>
+        <v>1863.22</v>
       </c>
       <c r="C23" t="n">
-        <v>1927.09</v>
+        <v>1869.07</v>
       </c>
       <c r="D23" t="n">
-        <v>1856.78</v>
+        <v>1803.05</v>
       </c>
       <c r="E23" t="n">
-        <v>1863.19</v>
+        <v>1840.99</v>
       </c>
       <c r="F23" t="n">
-        <v>-53.75</v>
+        <v>-22.21</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.0119</v>
       </c>
       <c r="H23" t="n">
-        <v>70.31</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1783.11</v>
+        <v>1786.47</v>
       </c>
       <c r="J23" t="n">
-        <v>1842.94</v>
+        <v>1778.51</v>
       </c>
       <c r="K23" t="n">
-        <v>1876.68</v>
+        <v>1828.04</v>
       </c>
       <c r="L23" t="n">
-        <v>1910.42</v>
+        <v>1877.56</v>
       </c>
       <c r="M23" t="n">
-        <v>1957.21</v>
+        <v>1898.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2003.99</v>
+        <v>1919.13</v>
       </c>
       <c r="O23" t="n">
-        <v>2024.69</v>
+        <v>1997.4</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2458,50 +2458,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1863.22</v>
+        <v>1841.1</v>
       </c>
       <c r="C24" t="n">
-        <v>1869.07</v>
+        <v>1864.13</v>
       </c>
       <c r="D24" t="n">
-        <v>1803.05</v>
+        <v>1836.61</v>
       </c>
       <c r="E24" t="n">
-        <v>1840.99</v>
+        <v>1861.39</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.21</v>
+        <v>20.4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0111</v>
       </c>
       <c r="H24" t="n">
-        <v>66.01000000000001</v>
+        <v>27.52</v>
       </c>
       <c r="I24" t="n">
-        <v>1786.47</v>
+        <v>1737.04</v>
       </c>
       <c r="J24" t="n">
-        <v>1778.51</v>
+        <v>1777.44</v>
       </c>
       <c r="K24" t="n">
-        <v>1828.04</v>
+        <v>1807.98</v>
       </c>
       <c r="L24" t="n">
-        <v>1877.56</v>
+        <v>1838.52</v>
       </c>
       <c r="M24" t="n">
-        <v>1898.35</v>
+        <v>1873.99</v>
       </c>
       <c r="N24" t="n">
-        <v>1919.13</v>
+        <v>1909.47</v>
       </c>
       <c r="O24" t="n">
-        <v>1997.4</v>
+        <v>1935.08</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2509,19 +2509,19 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2535,57 +2535,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1841.1</v>
+        <v>1861.42</v>
       </c>
       <c r="C25" t="n">
-        <v>1864.13</v>
+        <v>1877.03</v>
       </c>
       <c r="D25" t="n">
-        <v>1836.61</v>
+        <v>1852.73</v>
       </c>
       <c r="E25" t="n">
-        <v>1861.39</v>
+        <v>1871.51</v>
       </c>
       <c r="F25" t="n">
-        <v>20.4</v>
+        <v>10.12</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0054</v>
       </c>
       <c r="H25" t="n">
-        <v>27.52</v>
+        <v>24.3</v>
       </c>
       <c r="I25" t="n">
-        <v>1737.04</v>
+        <v>1809.09</v>
       </c>
       <c r="J25" t="n">
-        <v>1777.44</v>
+        <v>1839.38</v>
       </c>
       <c r="K25" t="n">
-        <v>1807.98</v>
+        <v>1847.63</v>
       </c>
       <c r="L25" t="n">
-        <v>1838.52</v>
+        <v>1855.88</v>
       </c>
       <c r="M25" t="n">
-        <v>1873.99</v>
+        <v>1875.15</v>
       </c>
       <c r="N25" t="n">
-        <v>1909.47</v>
+        <v>1894.43</v>
       </c>
       <c r="O25" t="n">
-        <v>1935.08</v>
+        <v>1891.66</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2617,68 +2617,68 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1861.42</v>
+        <v>1871.28</v>
       </c>
       <c r="C26" t="n">
-        <v>1877.03</v>
+        <v>1916.24</v>
       </c>
       <c r="D26" t="n">
-        <v>1852.73</v>
+        <v>1842.82</v>
       </c>
       <c r="E26" t="n">
-        <v>1871.51</v>
+        <v>1903.76</v>
       </c>
       <c r="F26" t="n">
-        <v>10.12</v>
+        <v>32.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0172</v>
       </c>
       <c r="H26" t="n">
-        <v>24.3</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>1809.09</v>
+        <v>1828.42</v>
       </c>
       <c r="J26" t="n">
-        <v>1839.38</v>
+        <v>1850.52</v>
       </c>
       <c r="K26" t="n">
-        <v>1847.63</v>
+        <v>1859.36</v>
       </c>
       <c r="L26" t="n">
-        <v>1855.88</v>
+        <v>1868.19</v>
       </c>
       <c r="M26" t="n">
-        <v>1875.15</v>
+        <v>1883.66</v>
       </c>
       <c r="N26" t="n">
-        <v>1894.43</v>
+        <v>1899.13</v>
       </c>
       <c r="O26" t="n">
-        <v>1891.66</v>
+        <v>1901.34</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
@@ -2687,82 +2687,86 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1871.28</v>
+        <v>1903.69</v>
       </c>
       <c r="C27" t="n">
-        <v>1916.24</v>
+        <v>1949.55</v>
       </c>
       <c r="D27" t="n">
-        <v>1842.82</v>
+        <v>1900.07</v>
       </c>
       <c r="E27" t="n">
-        <v>1903.76</v>
+        <v>1928.38</v>
       </c>
       <c r="F27" t="n">
-        <v>32.25</v>
+        <v>24.62</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0129</v>
       </c>
       <c r="H27" t="n">
-        <v>73.43000000000001</v>
+        <v>49.48</v>
       </c>
       <c r="I27" t="n">
-        <v>1828.42</v>
+        <v>1769.39</v>
       </c>
       <c r="J27" t="n">
-        <v>1850.52</v>
+        <v>1842.45</v>
       </c>
       <c r="K27" t="n">
-        <v>1859.36</v>
+        <v>1867.05</v>
       </c>
       <c r="L27" t="n">
-        <v>1868.19</v>
+        <v>1891.64</v>
       </c>
       <c r="M27" t="n">
-        <v>1883.66</v>
+        <v>1940.47</v>
       </c>
       <c r="N27" t="n">
-        <v>1899.13</v>
+        <v>1989.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1901.34</v>
+        <v>1989.67</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
@@ -2771,77 +2775,69 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1903.69</v>
+        <v>1928.2</v>
       </c>
       <c r="C28" t="n">
-        <v>1949.55</v>
+        <v>1955.15</v>
       </c>
       <c r="D28" t="n">
-        <v>1900.07</v>
+        <v>1909.61</v>
       </c>
       <c r="E28" t="n">
-        <v>1928.38</v>
+        <v>1933.49</v>
       </c>
       <c r="F28" t="n">
-        <v>24.62</v>
+        <v>5.11</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0026</v>
       </c>
       <c r="H28" t="n">
-        <v>49.48</v>
+        <v>45.54</v>
       </c>
       <c r="I28" t="n">
-        <v>1769.39</v>
+        <v>1850.58</v>
       </c>
       <c r="J28" t="n">
-        <v>1842.45</v>
+        <v>1880.69</v>
       </c>
       <c r="K28" t="n">
-        <v>1867.05</v>
+        <v>1903.64</v>
       </c>
       <c r="L28" t="n">
-        <v>1891.64</v>
+        <v>1926.6</v>
       </c>
       <c r="M28" t="n">
-        <v>1940.47</v>
+        <v>1953.12</v>
       </c>
       <c r="N28" t="n">
-        <v>1989.3</v>
+        <v>1979.65</v>
       </c>
       <c r="O28" t="n">
-        <v>1989.67</v>
+        <v>1999.03</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2854,12 +2850,12 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U28" s="8" t="n">
@@ -2878,79 +2874,81 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1928.2</v>
+        <v>1933.47</v>
       </c>
       <c r="C29" t="n">
-        <v>1955.15</v>
+        <v>1940.28</v>
       </c>
       <c r="D29" t="n">
-        <v>1909.61</v>
+        <v>1868.52</v>
       </c>
       <c r="E29" t="n">
-        <v>1933.49</v>
+        <v>1877.1</v>
       </c>
       <c r="F29" t="n">
-        <v>5.11</v>
+        <v>-56.39</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0292</v>
       </c>
       <c r="H29" t="n">
-        <v>45.54</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>1850.58</v>
+        <v>1864.07</v>
       </c>
       <c r="J29" t="n">
-        <v>1880.69</v>
+        <v>1888.51</v>
       </c>
       <c r="K29" t="n">
-        <v>1903.64</v>
+        <v>1910.72</v>
       </c>
       <c r="L29" t="n">
-        <v>1926.6</v>
+        <v>1932.93</v>
       </c>
       <c r="M29" t="n">
-        <v>1953.12</v>
+        <v>1956.26</v>
       </c>
       <c r="N29" t="n">
-        <v>1979.65</v>
+        <v>1979.58</v>
       </c>
       <c r="O29" t="n">
-        <v>1999.03</v>
+        <v>2000.68</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -2958,62 +2956,60 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1933.47</v>
+        <v>1877.1</v>
       </c>
       <c r="C30" t="n">
-        <v>1940.28</v>
+        <v>1907.54</v>
       </c>
       <c r="D30" t="n">
-        <v>1868.52</v>
+        <v>1846.82</v>
       </c>
       <c r="E30" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="F30" t="n">
-        <v>-56.39</v>
+        <v>-16.92</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0292</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>71.76000000000001</v>
+        <v>60.72</v>
       </c>
       <c r="I30" t="n">
-        <v>1864.07</v>
+        <v>1796.76</v>
       </c>
       <c r="J30" t="n">
-        <v>1888.51</v>
+        <v>1791.69</v>
       </c>
       <c r="K30" t="n">
-        <v>1910.72</v>
+        <v>1841.22</v>
       </c>
       <c r="L30" t="n">
-        <v>1932.93</v>
+        <v>1890.75</v>
       </c>
       <c r="M30" t="n">
-        <v>1956.26</v>
+        <v>1912.98</v>
       </c>
       <c r="N30" t="n">
-        <v>1979.58</v>
+        <v>1935.21</v>
       </c>
       <c r="O30" t="n">
-        <v>2000.68</v>
+        <v>2012.05</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
@@ -3040,50 +3036,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="C31" t="n">
-        <v>1907.54</v>
+        <v>1875.14</v>
       </c>
       <c r="D31" t="n">
-        <v>1846.82</v>
+        <v>1849.83</v>
       </c>
       <c r="E31" t="n">
-        <v>1860.18</v>
+        <v>1873.22</v>
       </c>
       <c r="F31" t="n">
-        <v>-16.92</v>
+        <v>13.05</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H31" t="n">
-        <v>60.72</v>
+        <v>25.32</v>
       </c>
       <c r="I31" t="n">
-        <v>1796.76</v>
+        <v>1786.1</v>
       </c>
       <c r="J31" t="n">
-        <v>1791.69</v>
+        <v>1790.95</v>
       </c>
       <c r="K31" t="n">
-        <v>1841.22</v>
+        <v>1829.82</v>
       </c>
       <c r="L31" t="n">
-        <v>1890.75</v>
+        <v>1868.68</v>
       </c>
       <c r="M31" t="n">
-        <v>1912.98</v>
+        <v>1890.54</v>
       </c>
       <c r="N31" t="n">
-        <v>1935.21</v>
+        <v>1912.39</v>
       </c>
       <c r="O31" t="n">
-        <v>2012.05</v>
+        <v>1968.26</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3091,14 +3087,12 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3115,55 +3109,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1860.18</v>
+        <v>1873.24</v>
       </c>
       <c r="C32" t="n">
-        <v>1875.14</v>
+        <v>1963.25</v>
       </c>
       <c r="D32" t="n">
-        <v>1849.83</v>
+        <v>1872.38</v>
       </c>
       <c r="E32" t="n">
-        <v>1873.22</v>
+        <v>1953.41</v>
       </c>
       <c r="F32" t="n">
-        <v>13.05</v>
+        <v>80.19</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0428</v>
       </c>
       <c r="H32" t="n">
-        <v>25.32</v>
+        <v>90.86</v>
       </c>
       <c r="I32" t="n">
-        <v>1786.1</v>
+        <v>1824.51</v>
       </c>
       <c r="J32" t="n">
-        <v>1790.95</v>
+        <v>1853.27</v>
       </c>
       <c r="K32" t="n">
-        <v>1829.82</v>
+        <v>1860.56</v>
       </c>
       <c r="L32" t="n">
-        <v>1868.68</v>
+        <v>1867.85</v>
       </c>
       <c r="M32" t="n">
-        <v>1890.54</v>
+        <v>1885.88</v>
       </c>
       <c r="N32" t="n">
-        <v>1912.39</v>
+        <v>1903.91</v>
       </c>
       <c r="O32" t="n">
-        <v>1968.26</v>
+        <v>1900.46</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3176,177 +3174,177 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1873.24</v>
+        <v>1953.41</v>
       </c>
       <c r="C33" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D33" t="n">
-        <v>1872.38</v>
+        <v>1882.42</v>
       </c>
       <c r="E33" t="n">
-        <v>1953.41</v>
+        <v>1890.61</v>
       </c>
       <c r="F33" t="n">
-        <v>80.19</v>
+        <v>-62.8</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0428</v>
+        <v>-0.0321</v>
       </c>
       <c r="H33" t="n">
-        <v>90.86</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>1824.51</v>
+        <v>1781.52</v>
       </c>
       <c r="J33" t="n">
-        <v>1853.27</v>
+        <v>1880.35</v>
       </c>
       <c r="K33" t="n">
-        <v>1860.56</v>
+        <v>1907.98</v>
       </c>
       <c r="L33" t="n">
-        <v>1867.85</v>
+        <v>1935.61</v>
       </c>
       <c r="M33" t="n">
-        <v>1885.88</v>
+        <v>1998.84</v>
       </c>
       <c r="N33" t="n">
-        <v>1903.91</v>
+        <v>2062.07</v>
       </c>
       <c r="O33" t="n">
-        <v>1900.46</v>
+        <v>2054.11</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1953.41</v>
+        <v>1890.63</v>
       </c>
       <c r="C34" t="n">
-        <v>1976.46</v>
+        <v>1926.5</v>
       </c>
       <c r="D34" t="n">
-        <v>1882.42</v>
+        <v>1856.34</v>
       </c>
       <c r="E34" t="n">
-        <v>1890.61</v>
+        <v>1919.95</v>
       </c>
       <c r="F34" t="n">
-        <v>-62.8</v>
+        <v>29.33</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0321</v>
+        <v>0.0155</v>
       </c>
       <c r="H34" t="n">
-        <v>94.04000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="I34" t="n">
-        <v>1781.52</v>
+        <v>1788.38</v>
       </c>
       <c r="J34" t="n">
-        <v>1880.35</v>
+        <v>1777.16</v>
       </c>
       <c r="K34" t="n">
-        <v>1907.98</v>
+        <v>1843.59</v>
       </c>
       <c r="L34" t="n">
-        <v>1935.61</v>
+        <v>1910.03</v>
       </c>
       <c r="M34" t="n">
-        <v>1998.84</v>
+        <v>1937.63</v>
       </c>
       <c r="N34" t="n">
-        <v>2062.07</v>
+        <v>1965.24</v>
       </c>
       <c r="O34" t="n">
-        <v>2054.11</v>
+        <v>2070.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3365,57 +3363,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1890.63</v>
+        <v>1919.99</v>
       </c>
       <c r="C35" t="n">
-        <v>1926.5</v>
+        <v>1929.9</v>
       </c>
       <c r="D35" t="n">
-        <v>1856.34</v>
+        <v>1873.62</v>
       </c>
       <c r="E35" t="n">
-        <v>1919.95</v>
+        <v>1908.52</v>
       </c>
       <c r="F35" t="n">
-        <v>29.33</v>
+        <v>-11.43</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.006</v>
       </c>
       <c r="H35" t="n">
-        <v>70.16</v>
+        <v>56.28</v>
       </c>
       <c r="I35" t="n">
-        <v>1788.38</v>
+        <v>1786.18</v>
       </c>
       <c r="J35" t="n">
-        <v>1777.16</v>
+        <v>1864.05</v>
       </c>
       <c r="K35" t="n">
-        <v>1843.59</v>
+        <v>1884.87</v>
       </c>
       <c r="L35" t="n">
-        <v>1910.03</v>
+        <v>1905.69</v>
       </c>
       <c r="M35" t="n">
-        <v>1937.63</v>
+        <v>1955.03</v>
       </c>
       <c r="N35" t="n">
-        <v>1965.24</v>
+        <v>2004.37</v>
       </c>
       <c r="O35" t="n">
-        <v>2070.5</v>
+        <v>1996.67</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3423,8 +3421,10 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
@@ -3447,57 +3447,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1919.99</v>
+        <v>1908.59</v>
       </c>
       <c r="C36" t="n">
-        <v>1929.9</v>
+        <v>1934.58</v>
       </c>
       <c r="D36" t="n">
-        <v>1873.62</v>
+        <v>1892.2</v>
       </c>
       <c r="E36" t="n">
-        <v>1908.52</v>
+        <v>1917.37</v>
       </c>
       <c r="F36" t="n">
-        <v>-11.43</v>
+        <v>8.85</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0046</v>
       </c>
       <c r="H36" t="n">
-        <v>56.28</v>
+        <v>42.38</v>
       </c>
       <c r="I36" t="n">
-        <v>1786.18</v>
+        <v>1817.34</v>
       </c>
       <c r="J36" t="n">
-        <v>1864.05</v>
+        <v>1855.62</v>
       </c>
       <c r="K36" t="n">
-        <v>1884.87</v>
+        <v>1880.38</v>
       </c>
       <c r="L36" t="n">
-        <v>1905.69</v>
+        <v>1905.14</v>
       </c>
       <c r="M36" t="n">
-        <v>1955.03</v>
+        <v>1936.66</v>
       </c>
       <c r="N36" t="n">
-        <v>2004.37</v>
+        <v>1968.18</v>
       </c>
       <c r="O36" t="n">
-        <v>1996.67</v>
+        <v>1986.18</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3505,10 +3505,8 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
@@ -3529,72 +3527,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1908.59</v>
+        <v>1917.14</v>
       </c>
       <c r="C37" t="n">
-        <v>1934.58</v>
+        <v>1933.78</v>
       </c>
       <c r="D37" t="n">
-        <v>1892.2</v>
+        <v>1847.47</v>
       </c>
       <c r="E37" t="n">
-        <v>1917.37</v>
+        <v>1860.35</v>
       </c>
       <c r="F37" t="n">
-        <v>8.85</v>
+        <v>-57.03</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0297</v>
       </c>
       <c r="H37" t="n">
-        <v>42.38</v>
+        <v>86.31</v>
       </c>
       <c r="I37" t="n">
-        <v>1817.34</v>
+        <v>1849.82</v>
       </c>
       <c r="J37" t="n">
-        <v>1855.62</v>
+        <v>1876.99</v>
       </c>
       <c r="K37" t="n">
-        <v>1880.38</v>
+        <v>1896.18</v>
       </c>
       <c r="L37" t="n">
-        <v>1905.14</v>
+        <v>1915.38</v>
       </c>
       <c r="M37" t="n">
-        <v>1936.66</v>
+        <v>1938.56</v>
       </c>
       <c r="N37" t="n">
-        <v>1968.18</v>
+        <v>1961.75</v>
       </c>
       <c r="O37" t="n">
-        <v>1986.18</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>1976.96</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3606,9 +3606,9 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3616,64 +3616,60 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1917.14</v>
+        <v>1860.37</v>
       </c>
       <c r="C38" t="n">
-        <v>1933.78</v>
+        <v>1873.17</v>
       </c>
       <c r="D38" t="n">
-        <v>1847.47</v>
+        <v>1821.49</v>
       </c>
       <c r="E38" t="n">
-        <v>1860.35</v>
+        <v>1843.42</v>
       </c>
       <c r="F38" t="n">
-        <v>-57.03</v>
+        <v>-16.93</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0297</v>
+        <v>-0.0091</v>
       </c>
       <c r="H38" t="n">
-        <v>86.31</v>
+        <v>51.69</v>
       </c>
       <c r="I38" t="n">
-        <v>1849.82</v>
+        <v>1761.16</v>
       </c>
       <c r="J38" t="n">
-        <v>1876.99</v>
+        <v>1758.9</v>
       </c>
       <c r="K38" t="n">
-        <v>1896.18</v>
+        <v>1817.19</v>
       </c>
       <c r="L38" t="n">
-        <v>1915.38</v>
+        <v>1875.48</v>
       </c>
       <c r="M38" t="n">
-        <v>1938.56</v>
+        <v>1903.5</v>
       </c>
       <c r="N38" t="n">
-        <v>1961.75</v>
+        <v>1931.52</v>
       </c>
       <c r="O38" t="n">
-        <v>1976.96</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
+        <v>2020.09</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
@@ -3700,50 +3696,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1860.37</v>
+        <v>1843.42</v>
       </c>
       <c r="C39" t="n">
-        <v>1873.17</v>
+        <v>1895.77</v>
       </c>
       <c r="D39" t="n">
-        <v>1821.49</v>
+        <v>1842.15</v>
       </c>
       <c r="E39" t="n">
-        <v>1843.42</v>
+        <v>1882.52</v>
       </c>
       <c r="F39" t="n">
-        <v>-16.93</v>
+        <v>39.1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0212</v>
       </c>
       <c r="H39" t="n">
-        <v>51.69</v>
+        <v>53.61</v>
       </c>
       <c r="I39" t="n">
-        <v>1761.16</v>
+        <v>1769.8</v>
       </c>
       <c r="J39" t="n">
-        <v>1758.9</v>
+        <v>1789.78</v>
       </c>
       <c r="K39" t="n">
-        <v>1817.19</v>
+        <v>1817.57</v>
       </c>
       <c r="L39" t="n">
-        <v>1875.48</v>
+        <v>1845.37</v>
       </c>
       <c r="M39" t="n">
-        <v>1903.5</v>
+        <v>1869.26</v>
       </c>
       <c r="N39" t="n">
-        <v>1931.52</v>
+        <v>1893.15</v>
       </c>
       <c r="O39" t="n">
-        <v>2020.09</v>
+        <v>1924.86</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3751,22 +3747,24 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3775,80 +3773,84 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1843.42</v>
+        <v>1882.78</v>
       </c>
       <c r="C40" t="n">
-        <v>1895.77</v>
+        <v>1883.44</v>
       </c>
       <c r="D40" t="n">
-        <v>1842.15</v>
+        <v>1827.7</v>
       </c>
       <c r="E40" t="n">
-        <v>1882.52</v>
+        <v>1858.26</v>
       </c>
       <c r="F40" t="n">
-        <v>39.1</v>
+        <v>-24.27</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0129</v>
       </c>
       <c r="H40" t="n">
-        <v>53.61</v>
+        <v>55.74</v>
       </c>
       <c r="I40" t="n">
-        <v>1769.8</v>
+        <v>1788.54</v>
       </c>
       <c r="J40" t="n">
-        <v>1789.78</v>
+        <v>1835.69</v>
       </c>
       <c r="K40" t="n">
-        <v>1817.57</v>
+        <v>1855.72</v>
       </c>
       <c r="L40" t="n">
-        <v>1845.37</v>
+        <v>1875.74</v>
       </c>
       <c r="M40" t="n">
-        <v>1869.26</v>
+        <v>1909.33</v>
       </c>
       <c r="N40" t="n">
-        <v>1893.15</v>
+        <v>1942.91</v>
       </c>
       <c r="O40" t="n">
-        <v>1924.86</v>
+        <v>1949.38</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="inlineStr">
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3857,76 +3859,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1882.78</v>
+        <v>1858.22</v>
       </c>
       <c r="C41" t="n">
-        <v>1883.44</v>
+        <v>1879.54</v>
       </c>
       <c r="D41" t="n">
-        <v>1827.7</v>
+        <v>1847.17</v>
       </c>
       <c r="E41" t="n">
-        <v>1858.26</v>
+        <v>1868.39</v>
       </c>
       <c r="F41" t="n">
-        <v>-24.27</v>
+        <v>10.13</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0055</v>
       </c>
       <c r="H41" t="n">
-        <v>55.74</v>
+        <v>32.36</v>
       </c>
       <c r="I41" t="n">
-        <v>1788.54</v>
+        <v>1771.96</v>
       </c>
       <c r="J41" t="n">
-        <v>1835.69</v>
+        <v>1803.86</v>
       </c>
       <c r="K41" t="n">
-        <v>1855.72</v>
+        <v>1830.39</v>
       </c>
       <c r="L41" t="n">
-        <v>1875.74</v>
+        <v>1856.91</v>
       </c>
       <c r="M41" t="n">
-        <v>1909.33</v>
+        <v>1886.13</v>
       </c>
       <c r="N41" t="n">
-        <v>1942.91</v>
+        <v>1915.34</v>
       </c>
       <c r="O41" t="n">
-        <v>1949.38</v>
+        <v>1939.18</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3943,55 +3937,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1858.22</v>
+        <v>1868.49</v>
       </c>
       <c r="C42" t="n">
-        <v>1879.54</v>
+        <v>1922.64</v>
       </c>
       <c r="D42" t="n">
-        <v>1847.17</v>
+        <v>1854.34</v>
       </c>
       <c r="E42" t="n">
-        <v>1868.39</v>
+        <v>1906.53</v>
       </c>
       <c r="F42" t="n">
-        <v>10.13</v>
+        <v>38.14</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0204</v>
       </c>
       <c r="H42" t="n">
-        <v>32.36</v>
+        <v>68.3</v>
       </c>
       <c r="I42" t="n">
-        <v>1771.96</v>
+        <v>1814.81</v>
       </c>
       <c r="J42" t="n">
-        <v>1803.86</v>
+        <v>1838.54</v>
       </c>
       <c r="K42" t="n">
-        <v>1830.39</v>
+        <v>1852.2</v>
       </c>
       <c r="L42" t="n">
-        <v>1856.91</v>
+        <v>1865.87</v>
       </c>
       <c r="M42" t="n">
-        <v>1886.13</v>
+        <v>1884.57</v>
       </c>
       <c r="N42" t="n">
-        <v>1915.34</v>
+        <v>1903.26</v>
       </c>
       <c r="O42" t="n">
-        <v>1939.18</v>
+        <v>1911.9</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4004,76 +4002,78 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1868.49</v>
+        <v>1906.44</v>
       </c>
       <c r="C43" t="n">
-        <v>1922.64</v>
+        <v>1917.7</v>
       </c>
       <c r="D43" t="n">
-        <v>1854.34</v>
+        <v>1890.96</v>
       </c>
       <c r="E43" t="n">
-        <v>1906.53</v>
+        <v>1902.06</v>
       </c>
       <c r="F43" t="n">
-        <v>38.14</v>
+        <v>-4.47</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.0023</v>
       </c>
       <c r="H43" t="n">
-        <v>68.3</v>
+        <v>26.74</v>
       </c>
       <c r="I43" t="n">
-        <v>1814.81</v>
+        <v>1786.04</v>
       </c>
       <c r="J43" t="n">
-        <v>1838.54</v>
+        <v>1847.24</v>
       </c>
       <c r="K43" t="n">
-        <v>1852.2</v>
+        <v>1872.38</v>
       </c>
       <c r="L43" t="n">
-        <v>1865.87</v>
+        <v>1897.51</v>
       </c>
       <c r="M43" t="n">
-        <v>1884.57</v>
+        <v>1940.68</v>
       </c>
       <c r="N43" t="n">
-        <v>1903.26</v>
+        <v>1983.84</v>
       </c>
       <c r="O43" t="n">
-        <v>1911.9</v>
+        <v>1990.94</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4086,78 +4086,76 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1906.44</v>
+        <v>1902.14</v>
       </c>
       <c r="C44" t="n">
-        <v>1917.7</v>
+        <v>1937.17</v>
       </c>
       <c r="D44" t="n">
-        <v>1890.96</v>
+        <v>1893.08</v>
       </c>
       <c r="E44" t="n">
-        <v>1902.06</v>
+        <v>1913.28</v>
       </c>
       <c r="F44" t="n">
-        <v>-4.47</v>
+        <v>11.22</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0059</v>
       </c>
       <c r="H44" t="n">
-        <v>26.74</v>
+        <v>44.08</v>
       </c>
       <c r="I44" t="n">
-        <v>1786.04</v>
+        <v>1864.23</v>
       </c>
       <c r="J44" t="n">
-        <v>1847.24</v>
+        <v>1874.18</v>
       </c>
       <c r="K44" t="n">
-        <v>1872.38</v>
+        <v>1888.69</v>
       </c>
       <c r="L44" t="n">
-        <v>1897.51</v>
+        <v>1903.19</v>
       </c>
       <c r="M44" t="n">
-        <v>1940.68</v>
+        <v>1915.43</v>
       </c>
       <c r="N44" t="n">
-        <v>1983.84</v>
+        <v>1927.66</v>
       </c>
       <c r="O44" t="n">
-        <v>1990.94</v>
+        <v>1944.44</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4170,14 +4168,18 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4187,59 +4189,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1902.14</v>
+        <v>1913.32</v>
       </c>
       <c r="C45" t="n">
-        <v>1937.17</v>
+        <v>1924.62</v>
       </c>
       <c r="D45" t="n">
-        <v>1893.08</v>
+        <v>1911.48</v>
       </c>
       <c r="E45" t="n">
-        <v>1913.28</v>
+        <v>1915.53</v>
       </c>
       <c r="F45" t="n">
-        <v>11.22</v>
+        <v>2.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0012</v>
       </c>
       <c r="H45" t="n">
-        <v>44.08</v>
+        <v>13.13</v>
       </c>
       <c r="I45" t="n">
-        <v>1864.23</v>
+        <v>1849</v>
       </c>
       <c r="J45" t="n">
-        <v>1874.18</v>
+        <v>1868.27</v>
       </c>
       <c r="K45" t="n">
-        <v>1888.69</v>
+        <v>1891.24</v>
       </c>
       <c r="L45" t="n">
-        <v>1903.19</v>
+        <v>1914.2</v>
       </c>
       <c r="M45" t="n">
-        <v>1915.43</v>
+        <v>1935.32</v>
       </c>
       <c r="N45" t="n">
-        <v>1927.66</v>
+        <v>1956.44</v>
       </c>
       <c r="O45" t="n">
-        <v>1944.44</v>
+        <v>1981.25</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4252,18 +4250,14 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4273,55 +4267,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1913.32</v>
+        <v>1915.46</v>
       </c>
       <c r="C46" t="n">
-        <v>1924.62</v>
+        <v>1935.53</v>
       </c>
       <c r="D46" t="n">
-        <v>1911.48</v>
+        <v>1907.03</v>
       </c>
       <c r="E46" t="n">
-        <v>1915.53</v>
+        <v>1908.68</v>
       </c>
       <c r="F46" t="n">
-        <v>2.25</v>
+        <v>-6.85</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0036</v>
       </c>
       <c r="H46" t="n">
-        <v>13.13</v>
+        <v>28.5</v>
       </c>
       <c r="I46" t="n">
-        <v>1849</v>
+        <v>1898.35</v>
       </c>
       <c r="J46" t="n">
-        <v>1868.27</v>
+        <v>1901.14</v>
       </c>
       <c r="K46" t="n">
-        <v>1891.24</v>
+        <v>1908.97</v>
       </c>
       <c r="L46" t="n">
-        <v>1914.2</v>
+        <v>1916.79</v>
       </c>
       <c r="M46" t="n">
-        <v>1935.32</v>
+        <v>1922.1</v>
       </c>
       <c r="N46" t="n">
-        <v>1956.44</v>
+        <v>1927.4</v>
       </c>
       <c r="O46" t="n">
-        <v>1981.25</v>
+        <v>1937.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4329,19 +4327,25 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4353,67 +4357,71 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1915.46</v>
+        <v>1908.72</v>
       </c>
       <c r="C47" t="n">
-        <v>1935.53</v>
+        <v>1928.99</v>
       </c>
       <c r="D47" t="n">
-        <v>1907.03</v>
+        <v>1866.79</v>
       </c>
       <c r="E47" t="n">
-        <v>1908.68</v>
+        <v>1871.28</v>
       </c>
       <c r="F47" t="n">
-        <v>-6.85</v>
+        <v>-37.4</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0196</v>
       </c>
       <c r="H47" t="n">
-        <v>28.5</v>
+        <v>62.2</v>
       </c>
       <c r="I47" t="n">
-        <v>1898.35</v>
+        <v>1878.52</v>
       </c>
       <c r="J47" t="n">
-        <v>1901.14</v>
+        <v>1873.88</v>
       </c>
       <c r="K47" t="n">
-        <v>1908.97</v>
+        <v>1894.43</v>
       </c>
       <c r="L47" t="n">
-        <v>1916.79</v>
+        <v>1914.98</v>
       </c>
       <c r="M47" t="n">
-        <v>1922.1</v>
+        <v>1922.93</v>
       </c>
       <c r="N47" t="n">
-        <v>1927.4</v>
+        <v>1930.89</v>
       </c>
       <c r="O47" t="n">
-        <v>1937.75</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>1964.03</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
@@ -4426,97 +4434,83 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1908.72</v>
+        <v>1871.26</v>
       </c>
       <c r="C48" t="n">
-        <v>1928.99</v>
+        <v>1895.75</v>
       </c>
       <c r="D48" t="n">
-        <v>1866.79</v>
+        <v>1852.84</v>
       </c>
       <c r="E48" t="n">
-        <v>1871.28</v>
+        <v>1881.37</v>
       </c>
       <c r="F48" t="n">
-        <v>-37.4</v>
+        <v>10.09</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0196</v>
+        <v>0.0054</v>
       </c>
       <c r="H48" t="n">
-        <v>62.2</v>
+        <v>42.91</v>
       </c>
       <c r="I48" t="n">
-        <v>1878.52</v>
+        <v>1804.59</v>
       </c>
       <c r="J48" t="n">
-        <v>1873.88</v>
+        <v>1795.77</v>
       </c>
       <c r="K48" t="n">
-        <v>1894.43</v>
+        <v>1840.18</v>
       </c>
       <c r="L48" t="n">
-        <v>1914.98</v>
+        <v>1884.59</v>
       </c>
       <c r="M48" t="n">
-        <v>1922.93</v>
+        <v>1902.38</v>
       </c>
       <c r="N48" t="n">
-        <v>1930.89</v>
+        <v>1920.18</v>
       </c>
       <c r="O48" t="n">
-        <v>1964.03</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>1991.2</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4529,55 +4523,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1871.26</v>
+        <v>1881.37</v>
       </c>
       <c r="C49" t="n">
-        <v>1895.75</v>
+        <v>1921.78</v>
       </c>
       <c r="D49" t="n">
-        <v>1852.84</v>
+        <v>1873.35</v>
       </c>
       <c r="E49" t="n">
-        <v>1881.37</v>
+        <v>1878.14</v>
       </c>
       <c r="F49" t="n">
-        <v>10.09</v>
+        <v>-3.24</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0017</v>
       </c>
       <c r="H49" t="n">
-        <v>42.91</v>
+        <v>48.43</v>
       </c>
       <c r="I49" t="n">
-        <v>1804.59</v>
+        <v>1809.93</v>
       </c>
       <c r="J49" t="n">
-        <v>1795.77</v>
+        <v>1842</v>
       </c>
       <c r="K49" t="n">
-        <v>1840.18</v>
+        <v>1859.92</v>
       </c>
       <c r="L49" t="n">
-        <v>1884.59</v>
+        <v>1877.83</v>
       </c>
       <c r="M49" t="n">
-        <v>1902.38</v>
+        <v>1902.83</v>
       </c>
       <c r="N49" t="n">
-        <v>1920.18</v>
+        <v>1927.82</v>
       </c>
       <c r="O49" t="n">
-        <v>1991.2</v>
+        <v>1938.66</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4588,13 +4586,15 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4609,57 +4609,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1881.37</v>
+        <v>1878.19</v>
       </c>
       <c r="C50" t="n">
-        <v>1921.78</v>
+        <v>1898.23</v>
       </c>
       <c r="D50" t="n">
-        <v>1873.35</v>
+        <v>1861.92</v>
       </c>
       <c r="E50" t="n">
-        <v>1878.14</v>
+        <v>1883.99</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.24</v>
+        <v>5.86</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="H50" t="n">
-        <v>48.43</v>
+        <v>36.3</v>
       </c>
       <c r="I50" t="n">
-        <v>1809.93</v>
+        <v>1824.92</v>
       </c>
       <c r="J50" t="n">
-        <v>1842</v>
+        <v>1819.99</v>
       </c>
       <c r="K50" t="n">
-        <v>1859.92</v>
+        <v>1853.92</v>
       </c>
       <c r="L50" t="n">
-        <v>1877.83</v>
+        <v>1887.85</v>
       </c>
       <c r="M50" t="n">
-        <v>1902.83</v>
+        <v>1902.35</v>
       </c>
       <c r="N50" t="n">
-        <v>1927.82</v>
+        <v>1916.85</v>
       </c>
       <c r="O50" t="n">
-        <v>1938.66</v>
+        <v>1970.2</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4670,15 +4670,13 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4693,57 +4691,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1878.19</v>
+        <v>1884.02</v>
       </c>
       <c r="C51" t="n">
-        <v>1898.23</v>
+        <v>1889.27</v>
       </c>
       <c r="D51" t="n">
-        <v>1861.92</v>
+        <v>1862.56</v>
       </c>
       <c r="E51" t="n">
-        <v>1883.99</v>
+        <v>1880.65</v>
       </c>
       <c r="F51" t="n">
-        <v>5.86</v>
+        <v>-3.34</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0018</v>
       </c>
       <c r="H51" t="n">
-        <v>36.3</v>
+        <v>26.71</v>
       </c>
       <c r="I51" t="n">
-        <v>1824.92</v>
+        <v>1825.62</v>
       </c>
       <c r="J51" t="n">
-        <v>1819.99</v>
+        <v>1849.65</v>
       </c>
       <c r="K51" t="n">
-        <v>1853.92</v>
+        <v>1865.84</v>
       </c>
       <c r="L51" t="n">
-        <v>1887.85</v>
+        <v>1882.03</v>
       </c>
       <c r="M51" t="n">
-        <v>1902.35</v>
+        <v>1902.14</v>
       </c>
       <c r="N51" t="n">
-        <v>1916.85</v>
+        <v>1922.26</v>
       </c>
       <c r="O51" t="n">
-        <v>1970.2</v>
+        <v>1934.53</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4751,8 +4749,10 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
@@ -4782,50 +4782,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1884.02</v>
+        <v>1880.61</v>
       </c>
       <c r="C52" t="n">
-        <v>1889.27</v>
+        <v>1884.72</v>
       </c>
       <c r="D52" t="n">
-        <v>1862.56</v>
+        <v>1874.33</v>
       </c>
       <c r="E52" t="n">
-        <v>1880.65</v>
+        <v>1880.91</v>
       </c>
       <c r="F52" t="n">
-        <v>-3.34</v>
+        <v>0.26</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0001</v>
       </c>
       <c r="H52" t="n">
-        <v>26.71</v>
+        <v>10.39</v>
       </c>
       <c r="I52" t="n">
-        <v>1825.62</v>
+        <v>1835.86</v>
       </c>
       <c r="J52" t="n">
-        <v>1849.65</v>
+        <v>1856.31</v>
       </c>
       <c r="K52" t="n">
-        <v>1865.84</v>
+        <v>1867.3</v>
       </c>
       <c r="L52" t="n">
-        <v>1882.03</v>
+        <v>1878.28</v>
       </c>
       <c r="M52" t="n">
-        <v>1902.14</v>
+        <v>1894</v>
       </c>
       <c r="N52" t="n">
-        <v>1922.26</v>
+        <v>1909.72</v>
       </c>
       <c r="O52" t="n">
-        <v>1934.53</v>
+        <v>1915.98</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4833,14 +4833,12 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4859,74 +4857,80 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1880.61</v>
+        <v>1880.89</v>
       </c>
       <c r="C53" t="n">
-        <v>1884.72</v>
+        <v>1889.61</v>
       </c>
       <c r="D53" t="n">
-        <v>1874.33</v>
+        <v>1867.89</v>
       </c>
       <c r="E53" t="n">
-        <v>1880.91</v>
+        <v>1873.94</v>
       </c>
       <c r="F53" t="n">
-        <v>0.26</v>
+        <v>-6.97</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0037</v>
       </c>
       <c r="H53" t="n">
-        <v>10.39</v>
+        <v>21.71</v>
       </c>
       <c r="I53" t="n">
-        <v>1835.86</v>
+        <v>1863.94</v>
       </c>
       <c r="J53" t="n">
-        <v>1856.31</v>
+        <v>1871.21</v>
       </c>
       <c r="K53" t="n">
-        <v>1867.3</v>
+        <v>1875.71</v>
       </c>
       <c r="L53" t="n">
-        <v>1878.28</v>
+        <v>1880.22</v>
       </c>
       <c r="M53" t="n">
-        <v>1894</v>
+        <v>1886.1</v>
       </c>
       <c r="N53" t="n">
-        <v>1909.72</v>
+        <v>1891.99</v>
       </c>
       <c r="O53" t="n">
-        <v>1915.98</v>
+        <v>1895.11</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4941,145 +4945,141 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1880.89</v>
+        <v>1873.97</v>
       </c>
       <c r="C54" t="n">
-        <v>1889.61</v>
+        <v>1916.66</v>
       </c>
       <c r="D54" t="n">
-        <v>1867.89</v>
+        <v>1870.75</v>
       </c>
       <c r="E54" t="n">
-        <v>1873.94</v>
+        <v>1912.2</v>
       </c>
       <c r="F54" t="n">
-        <v>-6.97</v>
+        <v>38.26</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0204</v>
       </c>
       <c r="H54" t="n">
-        <v>21.71</v>
+        <v>45.91</v>
       </c>
       <c r="I54" t="n">
-        <v>1863.94</v>
+        <v>1846.18</v>
       </c>
       <c r="J54" t="n">
-        <v>1871.21</v>
+        <v>1849.83</v>
       </c>
       <c r="K54" t="n">
-        <v>1875.71</v>
+        <v>1863.09</v>
       </c>
       <c r="L54" t="n">
-        <v>1880.22</v>
+        <v>1876.35</v>
       </c>
       <c r="M54" t="n">
-        <v>1886.1</v>
+        <v>1884.8</v>
       </c>
       <c r="N54" t="n">
-        <v>1891.99</v>
+        <v>1893.25</v>
       </c>
       <c r="O54" t="n">
-        <v>1895.11</v>
+        <v>1911.32</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1873.97</v>
+        <v>1912.21</v>
       </c>
       <c r="C55" t="n">
-        <v>1916.66</v>
+        <v>1920.52</v>
       </c>
       <c r="D55" t="n">
-        <v>1870.75</v>
+        <v>1884.48</v>
       </c>
       <c r="E55" t="n">
-        <v>1912.2</v>
+        <v>1916.46</v>
       </c>
       <c r="F55" t="n">
-        <v>38.26</v>
+        <v>4.26</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.0022</v>
       </c>
       <c r="H55" t="n">
-        <v>45.91</v>
+        <v>36.05</v>
       </c>
       <c r="I55" t="n">
-        <v>1846.18</v>
+        <v>1824.84</v>
       </c>
       <c r="J55" t="n">
-        <v>1849.83</v>
+        <v>1875.54</v>
       </c>
       <c r="K55" t="n">
-        <v>1863.09</v>
+        <v>1889.25</v>
       </c>
       <c r="L55" t="n">
-        <v>1876.35</v>
+        <v>1902.95</v>
       </c>
       <c r="M55" t="n">
-        <v>1884.8</v>
+        <v>1935.16</v>
       </c>
       <c r="N55" t="n">
-        <v>1893.25</v>
+        <v>1967.36</v>
       </c>
       <c r="O55" t="n">
-        <v>1911.32</v>
+        <v>1962.57</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5087,28 +5087,24 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
@@ -5120,50 +5116,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1912.21</v>
+        <v>1916.43</v>
       </c>
       <c r="C56" t="n">
-        <v>1920.52</v>
+        <v>2327.7</v>
       </c>
       <c r="D56" t="n">
-        <v>1884.48</v>
+        <v>1905.08</v>
       </c>
       <c r="E56" t="n">
-        <v>1916.46</v>
+        <v>2251.46</v>
       </c>
       <c r="F56" t="n">
-        <v>4.26</v>
+        <v>335</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.1748</v>
       </c>
       <c r="H56" t="n">
-        <v>36.05</v>
+        <v>422.62</v>
       </c>
       <c r="I56" t="n">
-        <v>1824.84</v>
+        <v>1848.43</v>
       </c>
       <c r="J56" t="n">
-        <v>1875.54</v>
+        <v>1887.39</v>
       </c>
       <c r="K56" t="n">
-        <v>1889.25</v>
+        <v>1898.44</v>
       </c>
       <c r="L56" t="n">
-        <v>1902.95</v>
+        <v>1909.48</v>
       </c>
       <c r="M56" t="n">
-        <v>1935.16</v>
+        <v>1934.48</v>
       </c>
       <c r="N56" t="n">
-        <v>1967.36</v>
+        <v>1959.48</v>
       </c>
       <c r="O56" t="n">
-        <v>1962.57</v>
+        <v>1956.57</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5171,24 +5167,28 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
@@ -5200,50 +5200,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1916.43</v>
+        <v>2251.44</v>
       </c>
       <c r="C57" t="n">
-        <v>2327.7</v>
+        <v>2357.23</v>
       </c>
       <c r="D57" t="n">
-        <v>1905.08</v>
+        <v>2222.57</v>
       </c>
       <c r="E57" t="n">
-        <v>2251.46</v>
+        <v>2326.38</v>
       </c>
       <c r="F57" t="n">
-        <v>335</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.1748</v>
+        <v>0.0333</v>
       </c>
       <c r="H57" t="n">
-        <v>422.62</v>
+        <v>134.65</v>
       </c>
       <c r="I57" t="n">
-        <v>1848.43</v>
+        <v>1482.46</v>
       </c>
       <c r="J57" t="n">
-        <v>1887.39</v>
+        <v>1896.37</v>
       </c>
       <c r="K57" t="n">
-        <v>1898.44</v>
+        <v>2040.15</v>
       </c>
       <c r="L57" t="n">
-        <v>1909.48</v>
+        <v>2183.92</v>
       </c>
       <c r="M57" t="n">
-        <v>1934.48</v>
+        <v>2462.77</v>
       </c>
       <c r="N57" t="n">
-        <v>1959.48</v>
+        <v>2741.61</v>
       </c>
       <c r="O57" t="n">
-        <v>1956.57</v>
+        <v>2750.32</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5261,18 +5261,14 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5284,50 +5280,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2251.44</v>
+        <v>2326.38</v>
       </c>
       <c r="C58" t="n">
-        <v>2357.23</v>
+        <v>2545.88</v>
       </c>
       <c r="D58" t="n">
-        <v>2222.57</v>
+        <v>2324.71</v>
       </c>
       <c r="E58" t="n">
-        <v>2326.38</v>
+        <v>2515.28</v>
       </c>
       <c r="F58" t="n">
-        <v>74.93000000000001</v>
+        <v>188.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0333</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>134.65</v>
+        <v>221.17</v>
       </c>
       <c r="I58" t="n">
-        <v>1482.46</v>
+        <v>2087.92</v>
       </c>
       <c r="J58" t="n">
-        <v>1896.37</v>
+        <v>2209.97</v>
       </c>
       <c r="K58" t="n">
-        <v>2040.15</v>
+        <v>2259.06</v>
       </c>
       <c r="L58" t="n">
-        <v>2183.92</v>
+        <v>2308.14</v>
       </c>
       <c r="M58" t="n">
-        <v>2462.77</v>
+        <v>2393.71</v>
       </c>
       <c r="N58" t="n">
-        <v>2741.61</v>
+        <v>2479.28</v>
       </c>
       <c r="O58" t="n">
-        <v>2750.32</v>
+        <v>2491.88</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5345,14 +5341,18 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5364,50 +5364,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2326.38</v>
+        <v>2515.39</v>
       </c>
       <c r="C59" t="n">
-        <v>2545.88</v>
+        <v>2528.9</v>
       </c>
       <c r="D59" t="n">
-        <v>2324.71</v>
+        <v>2389.9</v>
       </c>
       <c r="E59" t="n">
-        <v>2515.28</v>
+        <v>2424.25</v>
       </c>
       <c r="F59" t="n">
-        <v>188.9</v>
+        <v>-91.03</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0362</v>
       </c>
       <c r="H59" t="n">
-        <v>221.17</v>
+        <v>138.99</v>
       </c>
       <c r="I59" t="n">
-        <v>2087.92</v>
+        <v>2103.54</v>
       </c>
       <c r="J59" t="n">
-        <v>2209.97</v>
+        <v>2334.1</v>
       </c>
       <c r="K59" t="n">
-        <v>2259.06</v>
+        <v>2404.7</v>
       </c>
       <c r="L59" t="n">
-        <v>2308.14</v>
+        <v>2475.29</v>
       </c>
       <c r="M59" t="n">
-        <v>2393.71</v>
+        <v>2625.87</v>
       </c>
       <c r="N59" t="n">
-        <v>2479.28</v>
+        <v>2776.45</v>
       </c>
       <c r="O59" t="n">
-        <v>2491.88</v>
+        <v>2767.05</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5415,83 +5415,83 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
+      </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2515.39</v>
+        <v>2424.22</v>
       </c>
       <c r="C60" t="n">
-        <v>2528.9</v>
+        <v>2483.93</v>
       </c>
       <c r="D60" t="n">
-        <v>2389.9</v>
+        <v>2357.14</v>
       </c>
       <c r="E60" t="n">
-        <v>2424.25</v>
+        <v>2463.82</v>
       </c>
       <c r="F60" t="n">
-        <v>-91.03</v>
+        <v>39.56</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0362</v>
+        <v>0.0163</v>
       </c>
       <c r="H60" t="n">
-        <v>138.99</v>
+        <v>126.79</v>
       </c>
       <c r="I60" t="n">
-        <v>2103.54</v>
+        <v>2250.91</v>
       </c>
       <c r="J60" t="n">
-        <v>2334.1</v>
+        <v>2267.68</v>
       </c>
       <c r="K60" t="n">
-        <v>2404.7</v>
+        <v>2354.75</v>
       </c>
       <c r="L60" t="n">
-        <v>2475.29</v>
+        <v>2441.83</v>
       </c>
       <c r="M60" t="n">
-        <v>2625.87</v>
+        <v>2493.75</v>
       </c>
       <c r="N60" t="n">
-        <v>2776.45</v>
+        <v>2545.67</v>
       </c>
       <c r="O60" t="n">
-        <v>2767.05</v>
+        <v>2667.89</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5499,14 +5499,12 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5532,50 +5530,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2424.22</v>
+        <v>2463.64</v>
       </c>
       <c r="C61" t="n">
-        <v>2483.93</v>
+        <v>2531.74</v>
       </c>
       <c r="D61" t="n">
-        <v>2357.14</v>
+        <v>2425.39</v>
       </c>
       <c r="E61" t="n">
-        <v>2463.82</v>
+        <v>2481.83</v>
       </c>
       <c r="F61" t="n">
-        <v>39.56</v>
+        <v>18.02</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0073</v>
       </c>
       <c r="H61" t="n">
-        <v>126.79</v>
+        <v>106.36</v>
       </c>
       <c r="I61" t="n">
-        <v>2250.91</v>
+        <v>2230.35</v>
       </c>
       <c r="J61" t="n">
-        <v>2267.68</v>
+        <v>2358.67</v>
       </c>
       <c r="K61" t="n">
-        <v>2354.75</v>
+        <v>2400.42</v>
       </c>
       <c r="L61" t="n">
-        <v>2441.83</v>
+        <v>2442.18</v>
       </c>
       <c r="M61" t="n">
-        <v>2493.75</v>
+        <v>2527.21</v>
       </c>
       <c r="N61" t="n">
-        <v>2545.67</v>
+        <v>2612.25</v>
       </c>
       <c r="O61" t="n">
-        <v>2667.89</v>
+        <v>2610.72</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5591,8 +5589,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5605,59 +5605,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2463.64</v>
+        <v>2481.78</v>
       </c>
       <c r="C62" t="n">
-        <v>2531.74</v>
+        <v>2531.08</v>
       </c>
       <c r="D62" t="n">
-        <v>2425.39</v>
+        <v>2416.6</v>
       </c>
       <c r="E62" t="n">
-        <v>2481.83</v>
+        <v>2443.16</v>
       </c>
       <c r="F62" t="n">
-        <v>18.02</v>
+        <v>-38.67</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0156</v>
       </c>
       <c r="H62" t="n">
-        <v>106.36</v>
+        <v>114.48</v>
       </c>
       <c r="I62" t="n">
-        <v>2230.35</v>
+        <v>2319.03</v>
       </c>
       <c r="J62" t="n">
-        <v>2358.67</v>
+        <v>2377.11</v>
       </c>
       <c r="K62" t="n">
-        <v>2400.42</v>
+        <v>2428.65</v>
       </c>
       <c r="L62" t="n">
-        <v>2442.18</v>
+        <v>2480.2</v>
       </c>
       <c r="M62" t="n">
-        <v>2527.21</v>
+        <v>2535.01</v>
       </c>
       <c r="N62" t="n">
-        <v>2612.25</v>
+        <v>2589.82</v>
       </c>
       <c r="O62" t="n">
-        <v>2610.72</v>
+        <v>2638.1</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5665,18 +5661,18 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5689,55 +5685,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2481.78</v>
+        <v>2442.49</v>
       </c>
       <c r="C63" t="n">
-        <v>2531.08</v>
+        <v>2514.67</v>
       </c>
       <c r="D63" t="n">
-        <v>2416.6</v>
+        <v>2432.51</v>
       </c>
       <c r="E63" t="n">
-        <v>2443.16</v>
+        <v>2506.26</v>
       </c>
       <c r="F63" t="n">
-        <v>-38.67</v>
+        <v>63.1</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0258</v>
       </c>
       <c r="H63" t="n">
-        <v>114.48</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>2319.03</v>
+        <v>2302.12</v>
       </c>
       <c r="J63" t="n">
-        <v>2377.11</v>
+        <v>2313.34</v>
       </c>
       <c r="K63" t="n">
-        <v>2428.65</v>
+        <v>2385.92</v>
       </c>
       <c r="L63" t="n">
-        <v>2480.2</v>
+        <v>2458.5</v>
       </c>
       <c r="M63" t="n">
-        <v>2535.01</v>
+        <v>2500.4</v>
       </c>
       <c r="N63" t="n">
-        <v>2589.82</v>
+        <v>2542.3</v>
       </c>
       <c r="O63" t="n">
-        <v>2638.1</v>
+        <v>2645.57</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5745,19 +5745,19 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
       <c r="U63" s="8" t="n">
         <v/>
       </c>
@@ -5771,57 +5771,57 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2442.49</v>
+        <v>2506.24</v>
       </c>
       <c r="C64" t="n">
-        <v>2514.67</v>
+        <v>2564.27</v>
       </c>
       <c r="D64" t="n">
-        <v>2432.51</v>
+        <v>2481.94</v>
       </c>
       <c r="E64" t="n">
-        <v>2506.26</v>
+        <v>2510.41</v>
       </c>
       <c r="F64" t="n">
-        <v>63.1</v>
+        <v>4.15</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0258</v>
+        <v>0.0017</v>
       </c>
       <c r="H64" t="n">
-        <v>82.15000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="I64" t="n">
-        <v>2302.12</v>
+        <v>2350.36</v>
       </c>
       <c r="J64" t="n">
-        <v>2313.34</v>
+        <v>2440.44</v>
       </c>
       <c r="K64" t="n">
-        <v>2385.92</v>
+        <v>2465.18</v>
       </c>
       <c r="L64" t="n">
-        <v>2458.5</v>
+        <v>2489.93</v>
       </c>
       <c r="M64" t="n">
-        <v>2500.4</v>
+        <v>2547.34</v>
       </c>
       <c r="N64" t="n">
-        <v>2542.3</v>
+        <v>2604.75</v>
       </c>
       <c r="O64" t="n">
-        <v>2645.57</v>
+        <v>2596.82</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5834,12 +5834,12 @@
       </c>
       <c r="S64" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U64" s="8" t="n">
@@ -5853,79 +5853,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2506.24</v>
+        <v>2510.67</v>
       </c>
       <c r="C65" t="n">
-        <v>2564.27</v>
+        <v>2534.01</v>
       </c>
       <c r="D65" t="n">
-        <v>2481.94</v>
+        <v>2408.72</v>
       </c>
       <c r="E65" t="n">
-        <v>2510.41</v>
+        <v>2442.54</v>
       </c>
       <c r="F65" t="n">
-        <v>4.15</v>
+        <v>-67.87</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.027</v>
       </c>
       <c r="H65" t="n">
-        <v>82.33</v>
+        <v>125.29</v>
       </c>
       <c r="I65" t="n">
-        <v>2350.36</v>
+        <v>2399.62</v>
       </c>
       <c r="J65" t="n">
-        <v>2440.44</v>
+        <v>2421.73</v>
       </c>
       <c r="K65" t="n">
-        <v>2465.18</v>
+        <v>2469.25</v>
       </c>
       <c r="L65" t="n">
-        <v>2489.93</v>
+        <v>2516.76</v>
       </c>
       <c r="M65" t="n">
-        <v>2547.34</v>
+        <v>2551.57</v>
       </c>
       <c r="N65" t="n">
-        <v>2604.75</v>
+        <v>2586.39</v>
       </c>
       <c r="O65" t="n">
-        <v>2596.82</v>
+        <v>2646.6</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
       </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S65" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R65" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="n">
+        <v/>
+      </c>
       <c r="U65" s="8" t="n">
         <v/>
       </c>
@@ -5937,72 +5935,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr"/>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2510.67</v>
+        <v>2442.56</v>
       </c>
       <c r="C66" t="n">
-        <v>2534.01</v>
+        <v>2459.63</v>
       </c>
       <c r="D66" t="n">
-        <v>2408.72</v>
+        <v>2430.81</v>
       </c>
       <c r="E66" t="n">
-        <v>2442.54</v>
+        <v>2457.69</v>
       </c>
       <c r="F66" t="n">
-        <v>-67.87</v>
+        <v>15.15</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>-0.027</v>
+        <v>0.0062</v>
       </c>
       <c r="H66" t="n">
-        <v>125.29</v>
+        <v>28.82</v>
       </c>
       <c r="I66" t="n">
-        <v>2399.62</v>
+        <v>2283.43</v>
       </c>
       <c r="J66" t="n">
-        <v>2421.73</v>
+        <v>2302.83</v>
       </c>
       <c r="K66" t="n">
-        <v>2469.25</v>
+        <v>2379.89</v>
       </c>
       <c r="L66" t="n">
-        <v>2516.76</v>
+        <v>2456.95</v>
       </c>
       <c r="M66" t="n">
-        <v>2551.57</v>
+        <v>2505.18</v>
       </c>
       <c r="N66" t="n">
-        <v>2586.39</v>
+        <v>2553.41</v>
       </c>
       <c r="O66" t="n">
-        <v>2646.6</v>
+        <v>2659.3</v>
       </c>
       <c r="P66" s="6" t="n">
         <v/>
       </c>
-      <c r="Q66" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R66" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S66" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q66" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R66" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S66" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T66" s="8" t="n">
@@ -6021,84 +6019,96 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2442.56</v>
+        <v>2457.69</v>
       </c>
       <c r="C67" t="n">
-        <v>2459.63</v>
+        <v>2532.96</v>
       </c>
       <c r="D67" t="n">
-        <v>2430.81</v>
+        <v>2389.47</v>
       </c>
       <c r="E67" t="n">
-        <v>2457.69</v>
+        <v>2417.94</v>
       </c>
       <c r="F67" t="n">
-        <v>15.15</v>
+        <v>-39.75</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H67" t="n">
-        <v>28.82</v>
+        <v>143.49</v>
       </c>
       <c r="I67" t="n">
-        <v>2283.43</v>
+        <v>2401.99</v>
       </c>
       <c r="J67" t="n">
-        <v>2302.83</v>
+        <v>2435.1</v>
       </c>
       <c r="K67" t="n">
-        <v>2379.89</v>
+        <v>2443.28</v>
       </c>
       <c r="L67" t="n">
-        <v>2456.95</v>
+        <v>2451.45</v>
       </c>
       <c r="M67" t="n">
-        <v>2505.18</v>
+        <v>2472.1</v>
       </c>
       <c r="N67" t="n">
-        <v>2553.41</v>
+        <v>2492.74</v>
       </c>
       <c r="O67" t="n">
-        <v>2659.3</v>
-      </c>
-      <c r="P67" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q67" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R67" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S67" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T67" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U67" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V67" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W67" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+        <v>2488.45</v>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R67" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V67" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W67" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
@@ -6110,85 +6120,75 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2457.69</v>
+        <v>2417.9</v>
       </c>
       <c r="C68" t="n">
-        <v>2532.96</v>
+        <v>2488.92</v>
       </c>
       <c r="D68" t="n">
-        <v>2389.47</v>
+        <v>2401.81</v>
       </c>
       <c r="E68" t="n">
-        <v>2417.94</v>
+        <v>2466.82</v>
       </c>
       <c r="F68" t="n">
-        <v>-39.75</v>
+        <v>48.88</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.0202</v>
       </c>
       <c r="H68" t="n">
-        <v>143.49</v>
+        <v>87.11</v>
       </c>
       <c r="I68" t="n">
-        <v>2401.99</v>
+        <v>2245.98</v>
       </c>
       <c r="J68" t="n">
-        <v>2435.1</v>
+        <v>2252.81</v>
       </c>
       <c r="K68" t="n">
-        <v>2443.28</v>
+        <v>2346.19</v>
       </c>
       <c r="L68" t="n">
-        <v>2451.45</v>
+        <v>2439.58</v>
       </c>
       <c r="M68" t="n">
-        <v>2472.1</v>
+        <v>2489.68</v>
       </c>
       <c r="N68" t="n">
-        <v>2492.74</v>
+        <v>2539.79</v>
       </c>
       <c r="O68" t="n">
-        <v>2488.45</v>
-      </c>
-      <c r="P68" s="6" t="inlineStr">
+        <v>2676.45</v>
+      </c>
+      <c r="P68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R68" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S68" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q68" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R68" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S68" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U68" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V68" s="8" t="n">
+        <v/>
       </c>
       <c r="W68" s="11" t="inlineStr">
         <is>
@@ -6197,77 +6197,79 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2417.9</v>
+        <v>2466.58</v>
       </c>
       <c r="C69" t="n">
-        <v>2488.92</v>
+        <v>2484.4</v>
       </c>
       <c r="D69" t="n">
-        <v>2401.81</v>
+        <v>2383.8</v>
       </c>
       <c r="E69" t="n">
-        <v>2466.82</v>
+        <v>2417.84</v>
       </c>
       <c r="F69" t="n">
-        <v>48.88</v>
+        <v>-48.98</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0202</v>
+        <v>-0.0199</v>
       </c>
       <c r="H69" t="n">
-        <v>87.11</v>
+        <v>100.6</v>
       </c>
       <c r="I69" t="n">
-        <v>2245.98</v>
+        <v>2314.69</v>
       </c>
       <c r="J69" t="n">
-        <v>2252.81</v>
+        <v>2390.43</v>
       </c>
       <c r="K69" t="n">
-        <v>2346.19</v>
+        <v>2423.26</v>
       </c>
       <c r="L69" t="n">
-        <v>2439.58</v>
+        <v>2456.09</v>
       </c>
       <c r="M69" t="n">
-        <v>2489.68</v>
+        <v>2510.38</v>
       </c>
       <c r="N69" t="n">
-        <v>2539.79</v>
+        <v>2564.66</v>
       </c>
       <c r="O69" t="n">
-        <v>2676.45</v>
+        <v>2576.04</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
       </c>
-      <c r="Q69" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R69" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S69" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T69" s="8" t="inlineStr">
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R69" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S69" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T69" s="8" t="n">
+        <v/>
+      </c>
       <c r="U69" s="8" t="n">
         <v/>
       </c>
@@ -6279,67 +6281,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2466.58</v>
+        <v>2417.83</v>
       </c>
       <c r="C70" t="n">
-        <v>2484.4</v>
+        <v>2427.4</v>
       </c>
       <c r="D70" t="n">
-        <v>2383.8</v>
+        <v>2356.19</v>
       </c>
       <c r="E70" t="n">
-        <v>2417.84</v>
+        <v>2391.5</v>
       </c>
       <c r="F70" t="n">
-        <v>-48.98</v>
+        <v>-26.34</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.0109</v>
       </c>
       <c r="H70" t="n">
-        <v>100.6</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>2314.69</v>
+        <v>2283.21</v>
       </c>
       <c r="J70" t="n">
-        <v>2390.43</v>
+        <v>2309.12</v>
       </c>
       <c r="K70" t="n">
-        <v>2423.26</v>
+        <v>2367.54</v>
       </c>
       <c r="L70" t="n">
-        <v>2456.09</v>
+        <v>2425.97</v>
       </c>
       <c r="M70" t="n">
-        <v>2510.38</v>
+        <v>2468.14</v>
       </c>
       <c r="N70" t="n">
-        <v>2564.66</v>
+        <v>2510.31</v>
       </c>
       <c r="O70" t="n">
-        <v>2576.04</v>
+        <v>2584.99</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
       </c>
-      <c r="Q70" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q70" s="6" t="n">
+        <v/>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
@@ -6370,50 +6366,50 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2417.83</v>
+        <v>2391.6</v>
       </c>
       <c r="C71" t="n">
-        <v>2427.4</v>
+        <v>2526.95</v>
       </c>
       <c r="D71" t="n">
-        <v>2356.19</v>
+        <v>2370.42</v>
       </c>
       <c r="E71" t="n">
-        <v>2391.5</v>
+        <v>2508.02</v>
       </c>
       <c r="F71" t="n">
-        <v>-26.34</v>
+        <v>116.52</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.0109</v>
+        <v>0.0487</v>
       </c>
       <c r="H71" t="n">
-        <v>71.20999999999999</v>
+        <v>156.53</v>
       </c>
       <c r="I71" t="n">
-        <v>2283.21</v>
+        <v>2284.97</v>
       </c>
       <c r="J71" t="n">
-        <v>2309.12</v>
+        <v>2320.14</v>
       </c>
       <c r="K71" t="n">
-        <v>2367.54</v>
+        <v>2355.89</v>
       </c>
       <c r="L71" t="n">
-        <v>2425.97</v>
+        <v>2391.65</v>
       </c>
       <c r="M71" t="n">
-        <v>2468.14</v>
+        <v>2427.11</v>
       </c>
       <c r="N71" t="n">
-        <v>2510.31</v>
+        <v>2462.57</v>
       </c>
       <c r="O71" t="n">
-        <v>2584.99</v>
+        <v>2498.61</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6421,28 +6417,32 @@
       <c r="Q71" s="6" t="n">
         <v/>
       </c>
-      <c r="R71" s="6" t="inlineStr">
+      <c r="R71" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S71" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V71" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S71" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U71" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V71" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W71" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W71" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X71" t="inlineStr"/>
@@ -6450,50 +6450,50 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2391.6</v>
+        <v>2508.02</v>
       </c>
       <c r="C72" t="n">
-        <v>2526.95</v>
+        <v>2545.62</v>
       </c>
       <c r="D72" t="n">
-        <v>2370.42</v>
+        <v>2432.35</v>
       </c>
       <c r="E72" t="n">
-        <v>2508.02</v>
+        <v>2456.08</v>
       </c>
       <c r="F72" t="n">
-        <v>116.52</v>
+        <v>-51.94</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.0487</v>
+        <v>-0.0207</v>
       </c>
       <c r="H72" t="n">
-        <v>156.53</v>
+        <v>113.27</v>
       </c>
       <c r="I72" t="n">
-        <v>2284.97</v>
+        <v>2213.88</v>
       </c>
       <c r="J72" t="n">
-        <v>2320.14</v>
+        <v>2381.16</v>
       </c>
       <c r="K72" t="n">
-        <v>2355.89</v>
+        <v>2429.75</v>
       </c>
       <c r="L72" t="n">
-        <v>2391.65</v>
+        <v>2478.35</v>
       </c>
       <c r="M72" t="n">
-        <v>2427.11</v>
+        <v>2586.29</v>
       </c>
       <c r="N72" t="n">
-        <v>2462.57</v>
+        <v>2694.22</v>
       </c>
       <c r="O72" t="n">
-        <v>2498.61</v>
+        <v>2683.48</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
@@ -6504,80 +6504,78 @@
       <c r="R72" s="6" t="n">
         <v/>
       </c>
-      <c r="S72" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T72" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U72" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V72" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S72" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T72" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U72" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V72" s="8" t="n">
+        <v/>
       </c>
       <c r="W72" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr"/>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2508.02</v>
+        <v>2455.99</v>
       </c>
       <c r="C73" t="n">
-        <v>2545.62</v>
+        <v>2492.01</v>
       </c>
       <c r="D73" t="n">
-        <v>2432.35</v>
+        <v>2445.69</v>
       </c>
       <c r="E73" t="n">
-        <v>2456.08</v>
+        <v>2480.74</v>
       </c>
       <c r="F73" t="n">
-        <v>-51.94</v>
+        <v>24.66</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-0.0207</v>
+        <v>0.01</v>
       </c>
       <c r="H73" t="n">
-        <v>113.27</v>
+        <v>46.32</v>
       </c>
       <c r="I73" t="n">
-        <v>2213.88</v>
+        <v>2319.08</v>
       </c>
       <c r="J73" t="n">
-        <v>2381.16</v>
+        <v>2326.35</v>
       </c>
       <c r="K73" t="n">
-        <v>2429.75</v>
+        <v>2399.44</v>
       </c>
       <c r="L73" t="n">
-        <v>2478.35</v>
+        <v>2472.53</v>
       </c>
       <c r="M73" t="n">
-        <v>2586.29</v>
+        <v>2512.71</v>
       </c>
       <c r="N73" t="n">
-        <v>2694.22</v>
+        <v>2552.89</v>
       </c>
       <c r="O73" t="n">
-        <v>2683.48</v>
+        <v>2658.89</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6588,9 +6586,9 @@
       <c r="R73" s="6" t="n">
         <v/>
       </c>
-      <c r="S73" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S73" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T73" s="8" t="n">
@@ -6616,50 +6614,50 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2455.99</v>
+        <v>2480.82</v>
       </c>
       <c r="C74" t="n">
-        <v>2492.01</v>
+        <v>2525.32</v>
       </c>
       <c r="D74" t="n">
-        <v>2445.69</v>
+        <v>2468.19</v>
       </c>
       <c r="E74" t="n">
-        <v>2480.74</v>
+        <v>2514.55</v>
       </c>
       <c r="F74" t="n">
-        <v>24.66</v>
+        <v>33.81</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0136</v>
       </c>
       <c r="H74" t="n">
-        <v>46.32</v>
+        <v>57.13</v>
       </c>
       <c r="I74" t="n">
-        <v>2319.08</v>
+        <v>2399.37</v>
       </c>
       <c r="J74" t="n">
-        <v>2326.35</v>
+        <v>2440.36</v>
       </c>
       <c r="K74" t="n">
-        <v>2399.44</v>
+        <v>2457.58</v>
       </c>
       <c r="L74" t="n">
-        <v>2472.53</v>
+        <v>2474.79</v>
       </c>
       <c r="M74" t="n">
-        <v>2512.71</v>
+        <v>2503.9</v>
       </c>
       <c r="N74" t="n">
-        <v>2552.89</v>
+        <v>2533</v>
       </c>
       <c r="O74" t="n">
-        <v>2658.89</v>
+        <v>2538.33</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
@@ -6672,11 +6670,13 @@
       </c>
       <c r="S74" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U74" s="8" t="n">
         <v/>
@@ -6689,59 +6689,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2480.82</v>
+        <v>2514.58</v>
       </c>
       <c r="C75" t="n">
-        <v>2525.32</v>
+        <v>2534.86</v>
       </c>
       <c r="D75" t="n">
-        <v>2468.19</v>
+        <v>2466.91</v>
       </c>
       <c r="E75" t="n">
-        <v>2514.55</v>
+        <v>2490.96</v>
       </c>
       <c r="F75" t="n">
-        <v>33.81</v>
+        <v>-23.59</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0094</v>
       </c>
       <c r="H75" t="n">
-        <v>57.13</v>
+        <v>67.95</v>
       </c>
       <c r="I75" t="n">
-        <v>2399.37</v>
+        <v>2411.07</v>
       </c>
       <c r="J75" t="n">
-        <v>2440.36</v>
+        <v>2466.32</v>
       </c>
       <c r="K75" t="n">
-        <v>2457.58</v>
+        <v>2485.99</v>
       </c>
       <c r="L75" t="n">
-        <v>2474.79</v>
+        <v>2505.65</v>
       </c>
       <c r="M75" t="n">
-        <v>2503.9</v>
+        <v>2543.11</v>
       </c>
       <c r="N75" t="n">
-        <v>2533</v>
+        <v>2580.57</v>
       </c>
       <c r="O75" t="n">
-        <v>2538.33</v>
+        <v>2582.45</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
@@ -6749,19 +6745,19 @@
       <c r="Q75" s="6" t="n">
         <v/>
       </c>
-      <c r="R75" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S75" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T75" s="8" t="inlineStr">
+      <c r="R75" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S75" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T75" s="8" t="n">
+        <v/>
+      </c>
       <c r="U75" s="8" t="n">
         <v/>
       </c>
@@ -6773,55 +6769,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr"/>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2514.58</v>
+        <v>2490.92</v>
       </c>
       <c r="C76" t="n">
-        <v>2534.86</v>
+        <v>2506.75</v>
       </c>
       <c r="D76" t="n">
-        <v>2466.91</v>
+        <v>2441.33</v>
       </c>
       <c r="E76" t="n">
-        <v>2490.96</v>
+        <v>2484.94</v>
       </c>
       <c r="F76" t="n">
-        <v>-23.59</v>
+        <v>-6.02</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0024</v>
       </c>
       <c r="H76" t="n">
-        <v>67.95</v>
+        <v>65.42</v>
       </c>
       <c r="I76" t="n">
-        <v>2411.07</v>
+        <v>2398.96</v>
       </c>
       <c r="J76" t="n">
-        <v>2466.32</v>
+        <v>2418.04</v>
       </c>
       <c r="K76" t="n">
-        <v>2485.99</v>
+        <v>2456.98</v>
       </c>
       <c r="L76" t="n">
-        <v>2505.65</v>
+        <v>2495.92</v>
       </c>
       <c r="M76" t="n">
-        <v>2543.11</v>
+        <v>2524.93</v>
       </c>
       <c r="N76" t="n">
-        <v>2580.57</v>
+        <v>2553.94</v>
       </c>
       <c r="O76" t="n">
-        <v>2582.45</v>
+        <v>2602.81</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
@@ -6831,12 +6831,12 @@
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T76" s="8" t="n">
@@ -6855,57 +6855,57 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2490.92</v>
+        <v>2484.89</v>
       </c>
       <c r="C77" t="n">
-        <v>2506.75</v>
+        <v>2522.37</v>
       </c>
       <c r="D77" t="n">
-        <v>2441.33</v>
+        <v>2443.7</v>
       </c>
       <c r="E77" t="n">
-        <v>2484.94</v>
+        <v>2466.91</v>
       </c>
       <c r="F77" t="n">
-        <v>-6.02</v>
+        <v>-18.03</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0073</v>
       </c>
       <c r="H77" t="n">
-        <v>65.42</v>
+        <v>78.67</v>
       </c>
       <c r="I77" t="n">
-        <v>2398.96</v>
+        <v>2375.9</v>
       </c>
       <c r="J77" t="n">
-        <v>2418.04</v>
+        <v>2424.97</v>
       </c>
       <c r="K77" t="n">
-        <v>2456.98</v>
+        <v>2452.23</v>
       </c>
       <c r="L77" t="n">
-        <v>2495.92</v>
+        <v>2479.49</v>
       </c>
       <c r="M77" t="n">
-        <v>2524.93</v>
+        <v>2517.65</v>
       </c>
       <c r="N77" t="n">
-        <v>2553.94</v>
+        <v>2555.82</v>
       </c>
       <c r="O77" t="n">
-        <v>2602.81</v>
+        <v>2572.18</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
@@ -6923,8 +6923,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T77" s="8" t="n">
-        <v/>
+      <c r="T77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U77" s="8" t="n">
         <v/>
@@ -6939,57 +6941,57 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2484.89</v>
+        <v>2466.91</v>
       </c>
       <c r="C78" t="n">
-        <v>2522.37</v>
+        <v>2483.72</v>
       </c>
       <c r="D78" t="n">
-        <v>2443.7</v>
+        <v>2406.91</v>
       </c>
       <c r="E78" t="n">
-        <v>2466.91</v>
+        <v>2437.1</v>
       </c>
       <c r="F78" t="n">
-        <v>-18.03</v>
+        <v>-29.82</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0121</v>
       </c>
       <c r="H78" t="n">
-        <v>78.67</v>
+        <v>76.81</v>
       </c>
       <c r="I78" t="n">
-        <v>2375.9</v>
+        <v>2365.04</v>
       </c>
       <c r="J78" t="n">
-        <v>2424.97</v>
+        <v>2380.19</v>
       </c>
       <c r="K78" t="n">
-        <v>2452.23</v>
+        <v>2427.58</v>
       </c>
       <c r="L78" t="n">
-        <v>2479.49</v>
+        <v>2474.97</v>
       </c>
       <c r="M78" t="n">
-        <v>2517.65</v>
+        <v>2506.25</v>
       </c>
       <c r="N78" t="n">
-        <v>2555.82</v>
+        <v>2537.52</v>
       </c>
       <c r="O78" t="n">
-        <v>2572.18</v>
+        <v>2601.04</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -6999,18 +7001,16 @@
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T78" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="n">
+        <v/>
       </c>
       <c r="U78" s="8" t="n">
         <v/>
@@ -7025,57 +7025,57 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2466.91</v>
+        <v>2437.14</v>
       </c>
       <c r="C79" t="n">
-        <v>2483.72</v>
+        <v>2663.05</v>
       </c>
       <c r="D79" t="n">
-        <v>2406.91</v>
+        <v>2435.29</v>
       </c>
       <c r="E79" t="n">
-        <v>2437.1</v>
+        <v>2514.73</v>
       </c>
       <c r="F79" t="n">
-        <v>-29.82</v>
+        <v>77.64</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.0121</v>
+        <v>0.0319</v>
       </c>
       <c r="H79" t="n">
-        <v>76.81</v>
+        <v>227.76</v>
       </c>
       <c r="I79" t="n">
-        <v>2365.04</v>
+        <v>2330.09</v>
       </c>
       <c r="J79" t="n">
-        <v>2380.19</v>
+        <v>2356.18</v>
       </c>
       <c r="K79" t="n">
-        <v>2427.58</v>
+        <v>2398.69</v>
       </c>
       <c r="L79" t="n">
-        <v>2474.97</v>
+        <v>2441.21</v>
       </c>
       <c r="M79" t="n">
-        <v>2506.25</v>
+        <v>2475.51</v>
       </c>
       <c r="N79" t="n">
-        <v>2537.52</v>
+        <v>2509.8</v>
       </c>
       <c r="O79" t="n">
-        <v>2601.04</v>
+        <v>2560.53</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7083,83 +7083,83 @@
       <c r="Q79" s="6" t="n">
         <v/>
       </c>
-      <c r="R79" s="6" t="inlineStr">
+      <c r="R79" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S79" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U79" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S79" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U79" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V79" s="8" t="n">
-        <v/>
+      <c r="V79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W79" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2437.14</v>
+        <v>2514.77</v>
       </c>
       <c r="C80" t="n">
-        <v>2663.05</v>
+        <v>2544.47</v>
       </c>
       <c r="D80" t="n">
-        <v>2435.29</v>
+        <v>2508.8</v>
       </c>
       <c r="E80" t="n">
-        <v>2514.73</v>
+        <v>2525.94</v>
       </c>
       <c r="F80" t="n">
-        <v>77.64</v>
+        <v>11.21</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.0319</v>
+        <v>0.0045</v>
       </c>
       <c r="H80" t="n">
-        <v>227.76</v>
+        <v>35.67</v>
       </c>
       <c r="I80" t="n">
-        <v>2330.09</v>
+        <v>2207.52</v>
       </c>
       <c r="J80" t="n">
-        <v>2356.18</v>
+        <v>2269.75</v>
       </c>
       <c r="K80" t="n">
-        <v>2398.69</v>
+        <v>2400.85</v>
       </c>
       <c r="L80" t="n">
-        <v>2441.21</v>
+        <v>2531.95</v>
       </c>
       <c r="M80" t="n">
-        <v>2475.51</v>
+        <v>2628.62</v>
       </c>
       <c r="N80" t="n">
-        <v>2509.8</v>
+        <v>2725.28</v>
       </c>
       <c r="O80" t="n">
-        <v>2560.53</v>
+        <v>2890.82</v>
       </c>
       <c r="P80" s="6" t="n">
         <v/>
@@ -7170,93 +7170,97 @@
       <c r="R80" s="6" t="n">
         <v/>
       </c>
-      <c r="S80" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T80" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U80" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V80" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S80" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U80" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V80" s="8" t="n">
+        <v/>
       </c>
       <c r="W80" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr"/>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2514.77</v>
+        <v>2525.94</v>
       </c>
       <c r="C81" t="n">
-        <v>2544.47</v>
+        <v>2526.85</v>
       </c>
       <c r="D81" t="n">
-        <v>2508.8</v>
+        <v>2462.84</v>
       </c>
       <c r="E81" t="n">
-        <v>2525.94</v>
+        <v>2477.02</v>
       </c>
       <c r="F81" t="n">
-        <v>11.21</v>
+        <v>-48.92</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0194</v>
       </c>
       <c r="H81" t="n">
-        <v>35.67</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>2207.52</v>
+        <v>2473.13</v>
       </c>
       <c r="J81" t="n">
-        <v>2269.75</v>
+        <v>2489.93</v>
       </c>
       <c r="K81" t="n">
-        <v>2400.85</v>
+        <v>2508.11</v>
       </c>
       <c r="L81" t="n">
-        <v>2531.95</v>
+        <v>2526.29</v>
       </c>
       <c r="M81" t="n">
-        <v>2628.62</v>
+        <v>2543.78</v>
       </c>
       <c r="N81" t="n">
-        <v>2725.28</v>
+        <v>2561.27</v>
       </c>
       <c r="O81" t="n">
-        <v>2890.82</v>
-      </c>
-      <c r="P81" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q81" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R81" s="6" t="n">
-        <v/>
+        <v>2580.14</v>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T81" s="8" t="n">
@@ -7268,148 +7272,148 @@
       <c r="V81" s="8" t="n">
         <v/>
       </c>
-      <c r="W81" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W81" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2525.94</v>
+        <v>2476.6</v>
       </c>
       <c r="C82" t="n">
-        <v>2526.85</v>
+        <v>2612.4</v>
       </c>
       <c r="D82" t="n">
-        <v>2462.84</v>
+        <v>2465.43</v>
       </c>
       <c r="E82" t="n">
-        <v>2477.02</v>
+        <v>2514.41</v>
       </c>
       <c r="F82" t="n">
-        <v>-48.92</v>
+        <v>37.39</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>-0.0194</v>
+        <v>0.0151</v>
       </c>
       <c r="H82" t="n">
-        <v>64.01000000000001</v>
+        <v>146.98</v>
       </c>
       <c r="I82" t="n">
-        <v>2473.13</v>
+        <v>2398.83</v>
       </c>
       <c r="J82" t="n">
-        <v>2489.93</v>
+        <v>2404.09</v>
       </c>
       <c r="K82" t="n">
-        <v>2508.11</v>
+        <v>2445.01</v>
       </c>
       <c r="L82" t="n">
-        <v>2526.29</v>
+        <v>2485.93</v>
       </c>
       <c r="M82" t="n">
-        <v>2543.78</v>
+        <v>2509.03</v>
       </c>
       <c r="N82" t="n">
-        <v>2561.27</v>
+        <v>2532.12</v>
       </c>
       <c r="O82" t="n">
-        <v>2580.14</v>
-      </c>
-      <c r="P82" s="6" t="inlineStr">
+        <v>2590.87</v>
+      </c>
+      <c r="P82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R82" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S82" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q82" s="6" t="inlineStr">
+      <c r="U82" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R82" s="6" t="inlineStr">
+      <c r="V82" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S82" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U82" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V82" s="8" t="n">
-        <v/>
-      </c>
       <c r="W82" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr"/>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2476.6</v>
+        <v>2514.36</v>
       </c>
       <c r="C83" t="n">
-        <v>2612.4</v>
+        <v>2519.32</v>
       </c>
       <c r="D83" t="n">
-        <v>2465.43</v>
+        <v>2357.96</v>
       </c>
       <c r="E83" t="n">
-        <v>2514.41</v>
+        <v>2399.09</v>
       </c>
       <c r="F83" t="n">
-        <v>37.39</v>
+        <v>-115.32</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.0459</v>
       </c>
       <c r="H83" t="n">
-        <v>146.98</v>
+        <v>161.36</v>
       </c>
       <c r="I83" t="n">
-        <v>2398.83</v>
+        <v>2318.45</v>
       </c>
       <c r="J83" t="n">
-        <v>2404.09</v>
+        <v>2355.18</v>
       </c>
       <c r="K83" t="n">
-        <v>2445.01</v>
+        <v>2440.92</v>
       </c>
       <c r="L83" t="n">
-        <v>2485.93</v>
+        <v>2526.66</v>
       </c>
       <c r="M83" t="n">
-        <v>2509.03</v>
+        <v>2587.9</v>
       </c>
       <c r="N83" t="n">
-        <v>2532.12</v>
+        <v>2649.13</v>
       </c>
       <c r="O83" t="n">
-        <v>2590.87</v>
+        <v>2759.38</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
@@ -7417,87 +7421,79 @@
       <c r="Q83" s="6" t="n">
         <v/>
       </c>
-      <c r="R83" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S83" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T83" s="8" t="inlineStr">
+      <c r="R83" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U83" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V83" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S83" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U83" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V83" s="8" t="n">
+        <v/>
       </c>
       <c r="W83" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2514.36</v>
+        <v>2399.06</v>
       </c>
       <c r="C84" t="n">
-        <v>2519.32</v>
+        <v>2426.93</v>
       </c>
       <c r="D84" t="n">
-        <v>2357.96</v>
+        <v>2368.74</v>
       </c>
       <c r="E84" t="n">
-        <v>2399.09</v>
+        <v>2416.12</v>
       </c>
       <c r="F84" t="n">
-        <v>-115.32</v>
+        <v>17.03</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-0.0459</v>
+        <v>0.0071</v>
       </c>
       <c r="H84" t="n">
-        <v>161.36</v>
+        <v>58.19</v>
       </c>
       <c r="I84" t="n">
-        <v>2318.45</v>
+        <v>2196.6</v>
       </c>
       <c r="J84" t="n">
-        <v>2355.18</v>
+        <v>2217.95</v>
       </c>
       <c r="K84" t="n">
-        <v>2440.92</v>
+        <v>2318.41</v>
       </c>
       <c r="L84" t="n">
-        <v>2526.66</v>
+        <v>2418.86</v>
       </c>
       <c r="M84" t="n">
-        <v>2587.9</v>
+        <v>2479.77</v>
       </c>
       <c r="N84" t="n">
-        <v>2649.13</v>
+        <v>2540.67</v>
       </c>
       <c r="O84" t="n">
-        <v>2759.38</v>
+        <v>2680.68</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
@@ -7505,14 +7501,12 @@
       <c r="Q84" s="6" t="n">
         <v/>
       </c>
-      <c r="R84" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R84" s="6" t="n">
+        <v/>
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T84" s="8" t="n">
@@ -7529,55 +7523,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr"/>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2399.06</v>
+        <v>2416.17</v>
       </c>
       <c r="C85" t="n">
-        <v>2426.93</v>
+        <v>2480.74</v>
       </c>
       <c r="D85" t="n">
-        <v>2368.74</v>
+        <v>2412.19</v>
       </c>
       <c r="E85" t="n">
-        <v>2416.12</v>
+        <v>2447.11</v>
       </c>
       <c r="F85" t="n">
-        <v>17.03</v>
+        <v>30.99</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0128</v>
       </c>
       <c r="H85" t="n">
-        <v>58.19</v>
+        <v>68.55</v>
       </c>
       <c r="I85" t="n">
-        <v>2196.6</v>
+        <v>2310.54</v>
       </c>
       <c r="J85" t="n">
-        <v>2217.95</v>
+        <v>2367.07</v>
       </c>
       <c r="K85" t="n">
-        <v>2318.41</v>
+        <v>2387.02</v>
       </c>
       <c r="L85" t="n">
-        <v>2418.86</v>
+        <v>2406.98</v>
       </c>
       <c r="M85" t="n">
-        <v>2479.77</v>
+        <v>2445.22</v>
       </c>
       <c r="N85" t="n">
-        <v>2540.67</v>
+        <v>2483.46</v>
       </c>
       <c r="O85" t="n">
-        <v>2680.68</v>
+        <v>2485.12</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7588,13 +7586,15 @@
       <c r="R85" s="6" t="n">
         <v/>
       </c>
-      <c r="S85" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T85" s="8" t="n">
-        <v/>
+      <c r="S85" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U85" s="8" t="n">
         <v/>
@@ -7609,57 +7609,57 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2416.17</v>
+        <v>2447.11</v>
       </c>
       <c r="C86" t="n">
-        <v>2480.74</v>
+        <v>2643.96</v>
       </c>
       <c r="D86" t="n">
-        <v>2412.19</v>
+        <v>2435.15</v>
       </c>
       <c r="E86" t="n">
-        <v>2447.11</v>
+        <v>2611.35</v>
       </c>
       <c r="F86" t="n">
-        <v>30.99</v>
+        <v>164.24</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>68.55</v>
+        <v>208.81</v>
       </c>
       <c r="I86" t="n">
-        <v>2310.54</v>
+        <v>2343.64</v>
       </c>
       <c r="J86" t="n">
-        <v>2367.07</v>
+        <v>2378.88</v>
       </c>
       <c r="K86" t="n">
-        <v>2387.02</v>
+        <v>2412.83</v>
       </c>
       <c r="L86" t="n">
-        <v>2406.98</v>
+        <v>2446.78</v>
       </c>
       <c r="M86" t="n">
-        <v>2445.22</v>
+        <v>2481.38</v>
       </c>
       <c r="N86" t="n">
-        <v>2483.46</v>
+        <v>2515.98</v>
       </c>
       <c r="O86" t="n">
-        <v>2485.12</v>
+        <v>2549.29</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7677,73 +7677,73 @@
       </c>
       <c r="T86" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U86" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V86" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U86" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V86" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W86" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W86" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2447.11</v>
+        <v>2611.46</v>
       </c>
       <c r="C87" t="n">
-        <v>2643.96</v>
+        <v>2659.72</v>
       </c>
       <c r="D87" t="n">
-        <v>2435.15</v>
+        <v>2602.74</v>
       </c>
       <c r="E87" t="n">
-        <v>2611.35</v>
+        <v>2631.96</v>
       </c>
       <c r="F87" t="n">
-        <v>164.24</v>
+        <v>20.62</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>208.81</v>
+        <v>56.98</v>
       </c>
       <c r="I87" t="n">
-        <v>2343.64</v>
+        <v>2226.33</v>
       </c>
       <c r="J87" t="n">
-        <v>2378.88</v>
+        <v>2438.43</v>
       </c>
       <c r="K87" t="n">
-        <v>2412.83</v>
+        <v>2506.94</v>
       </c>
       <c r="L87" t="n">
-        <v>2446.78</v>
+        <v>2575.45</v>
       </c>
       <c r="M87" t="n">
-        <v>2481.38</v>
+        <v>2715.75</v>
       </c>
       <c r="N87" t="n">
-        <v>2515.98</v>
+        <v>2856.06</v>
       </c>
       <c r="O87" t="n">
-        <v>2549.29</v>
+        <v>2852.78</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
@@ -7756,23 +7756,17 @@
       </c>
       <c r="S87" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V87" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U87" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V87" s="8" t="n">
+        <v/>
       </c>
       <c r="W87" s="9" t="inlineStr">
         <is>
@@ -7784,59 +7778,63 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2611.46</v>
+        <v>2632.01</v>
       </c>
       <c r="C88" t="n">
-        <v>2659.72</v>
+        <v>2647.87</v>
       </c>
       <c r="D88" t="n">
-        <v>2602.74</v>
+        <v>2564.43</v>
       </c>
       <c r="E88" t="n">
-        <v>2631.96</v>
+        <v>2643</v>
       </c>
       <c r="F88" t="n">
-        <v>20.62</v>
+        <v>11.03</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0042</v>
       </c>
       <c r="H88" t="n">
-        <v>56.98</v>
+        <v>83.44</v>
       </c>
       <c r="I88" t="n">
-        <v>2226.33</v>
+        <v>2545.76</v>
       </c>
       <c r="J88" t="n">
-        <v>2438.43</v>
+        <v>2575.35</v>
       </c>
       <c r="K88" t="n">
-        <v>2506.94</v>
+        <v>2603.47</v>
       </c>
       <c r="L88" t="n">
-        <v>2575.45</v>
+        <v>2631.6</v>
       </c>
       <c r="M88" t="n">
-        <v>2715.75</v>
+        <v>2660.45</v>
       </c>
       <c r="N88" t="n">
-        <v>2856.06</v>
+        <v>2689.31</v>
       </c>
       <c r="O88" t="n">
-        <v>2852.78</v>
+        <v>2716.7</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
       </c>
-      <c r="Q88" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R88" s="6" t="n">
-        <v/>
+      <c r="Q88" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S88" s="10" t="inlineStr">
         <is>
@@ -7857,141 +7855,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr"/>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2632.01</v>
+        <v>2642.78</v>
       </c>
       <c r="C89" t="n">
-        <v>2647.87</v>
+        <v>2805.5</v>
       </c>
       <c r="D89" t="n">
-        <v>2564.43</v>
+        <v>2642.78</v>
       </c>
       <c r="E89" t="n">
-        <v>2643</v>
+        <v>2776.47</v>
       </c>
       <c r="F89" t="n">
-        <v>11.03</v>
+        <v>133.47</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0505</v>
       </c>
       <c r="H89" t="n">
-        <v>83.44</v>
+        <v>162.72</v>
       </c>
       <c r="I89" t="n">
-        <v>2545.76</v>
+        <v>2480.99</v>
       </c>
       <c r="J89" t="n">
-        <v>2575.35</v>
+        <v>2577.98</v>
       </c>
       <c r="K89" t="n">
-        <v>2603.47</v>
+        <v>2601.28</v>
       </c>
       <c r="L89" t="n">
-        <v>2631.6</v>
+        <v>2624.58</v>
       </c>
       <c r="M89" t="n">
-        <v>2660.45</v>
+        <v>2684.72</v>
       </c>
       <c r="N89" t="n">
-        <v>2689.31</v>
+        <v>2744.86</v>
       </c>
       <c r="O89" t="n">
-        <v>2716.7</v>
+        <v>2731.31</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
       </c>
-      <c r="Q89" s="6" t="inlineStr">
+      <c r="Q89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R89" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S89" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R89" s="6" t="inlineStr">
+      <c r="U89" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V89" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S89" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U89" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V89" s="8" t="n">
-        <v/>
-      </c>
       <c r="W89" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2642.78</v>
+        <v>2753.25</v>
       </c>
       <c r="C90" t="n">
-        <v>2805.5</v>
+        <v>2771.17</v>
       </c>
       <c r="D90" t="n">
-        <v>2642.78</v>
+        <v>2751.39</v>
       </c>
       <c r="E90" t="n">
-        <v>2776.47</v>
+        <v>2756.74</v>
       </c>
       <c r="F90" t="n">
-        <v>133.47</v>
+        <v>-19.73</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.0505</v>
+        <v>-0.0071</v>
       </c>
       <c r="H90" t="n">
-        <v>162.72</v>
+        <v>19.78</v>
       </c>
       <c r="I90" t="n">
-        <v>2480.99</v>
+        <v>2480.07</v>
       </c>
       <c r="J90" t="n">
-        <v>2577.98</v>
+        <v>2639.92</v>
       </c>
       <c r="K90" t="n">
-        <v>2601.28</v>
+        <v>2695.11</v>
       </c>
       <c r="L90" t="n">
-        <v>2624.58</v>
+        <v>2750.3</v>
       </c>
       <c r="M90" t="n">
-        <v>2684.72</v>
+        <v>2857.83</v>
       </c>
       <c r="N90" t="n">
-        <v>2744.86</v>
+        <v>2965.35</v>
       </c>
       <c r="O90" t="n">
-        <v>2731.31</v>
+        <v>2968.22</v>
       </c>
       <c r="P90" s="6" t="n">
         <v/>
@@ -8004,108 +8004,24 @@
       </c>
       <c r="S90" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U90" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U90" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V90" s="8" t="n">
+        <v/>
       </c>
       <c r="W90" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>2775.96</v>
-      </c>
-      <c r="C91" t="n">
-        <v>2776.61</v>
-      </c>
-      <c r="D91" t="n">
-        <v>2718.93</v>
-      </c>
-      <c r="E91" t="n">
-        <v>2739.44</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-37.03</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>-0.0133</v>
-      </c>
-      <c r="H91" t="n">
-        <v>57.68</v>
-      </c>
-      <c r="I91" t="n">
-        <v>2480.07</v>
-      </c>
-      <c r="J91" t="n">
-        <v>2639.92</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2695.11</v>
-      </c>
-      <c r="L91" t="n">
-        <v>2750.3</v>
-      </c>
-      <c r="M91" t="n">
-        <v>2857.83</v>
-      </c>
-      <c r="N91" t="n">
-        <v>2965.35</v>
-      </c>
-      <c r="O91" t="n">
-        <v>2968.22</v>
-      </c>
-      <c r="P91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S91" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V91" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W91" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -7958,19 +7958,19 @@
         <v>2771.17</v>
       </c>
       <c r="D90" t="n">
-        <v>2751.39</v>
+        <v>2749.16</v>
       </c>
       <c r="E90" t="n">
-        <v>2756.74</v>
+        <v>2746.42</v>
       </c>
       <c r="F90" t="n">
-        <v>-19.73</v>
+        <v>-30.05</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0071</v>
+        <v>-0.0108</v>
       </c>
       <c r="H90" t="n">
-        <v>19.78</v>
+        <v>22.01</v>
       </c>
       <c r="I90" t="n">
         <v>2480.07</v>
@@ -8002,9 +8002,9 @@
       <c r="R90" s="6" t="n">
         <v/>
       </c>
-      <c r="S90" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S90" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T90" s="8" t="n">

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -7958,19 +7958,19 @@
         <v>2771.17</v>
       </c>
       <c r="D90" t="n">
-        <v>2749.16</v>
+        <v>2746.55</v>
       </c>
       <c r="E90" t="n">
-        <v>2746.42</v>
+        <v>2759.37</v>
       </c>
       <c r="F90" t="n">
-        <v>-30.05</v>
+        <v>-17.1</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0062</v>
       </c>
       <c r="H90" t="n">
-        <v>22.01</v>
+        <v>24.62</v>
       </c>
       <c r="I90" t="n">
         <v>2480.07</v>
@@ -8002,9 +8002,9 @@
       <c r="R90" s="6" t="n">
         <v/>
       </c>
-      <c r="S90" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S90" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T90" s="8" t="n">

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -7961,13 +7961,13 @@
         <v>2746.55</v>
       </c>
       <c r="E90" t="n">
-        <v>2759.37</v>
+        <v>2768.92</v>
       </c>
       <c r="F90" t="n">
-        <v>-17.1</v>
+        <v>-7.55</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0027</v>
       </c>
       <c r="H90" t="n">
         <v>24.62</v>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X90"/>
+  <dimension ref="A1:X91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7948,29 +7948,29 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2753.25</v>
+        <v>2776.58</v>
       </c>
       <c r="C90" t="n">
-        <v>2771.17</v>
+        <v>2776.89</v>
       </c>
       <c r="D90" t="n">
-        <v>2746.55</v>
+        <v>2715.72</v>
       </c>
       <c r="E90" t="n">
-        <v>2768.92</v>
+        <v>2752.63</v>
       </c>
       <c r="F90" t="n">
-        <v>-7.55</v>
+        <v>-23.84</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0086</v>
       </c>
       <c r="H90" t="n">
-        <v>24.62</v>
+        <v>61.17</v>
       </c>
       <c r="I90" t="n">
         <v>2480.07</v>
@@ -8022,6 +8022,92 @@
         </is>
       </c>
       <c r="X90" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2753.25</v>
+      </c>
+      <c r="C91" t="n">
+        <v>2785.63</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2708.66</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2712.68</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-39.95</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-0.0145</v>
+      </c>
+      <c r="H91" t="n">
+        <v>76.97</v>
+      </c>
+      <c r="I91" t="n">
+        <v>2654.54</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2694.62</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2722.05</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2749.47</v>
+      </c>
+      <c r="M91" t="n">
+        <v>2783.22</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2816.97</v>
+      </c>
+      <c r="O91" t="n">
+        <v>2838.06</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S91" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V91" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W91" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -8040,19 +8040,19 @@
         <v>2785.63</v>
       </c>
       <c r="D91" t="n">
-        <v>2708.66</v>
+        <v>2650.82</v>
       </c>
       <c r="E91" t="n">
-        <v>2712.68</v>
+        <v>2688.5</v>
       </c>
       <c r="F91" t="n">
-        <v>-39.95</v>
+        <v>-64.13</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.0145</v>
+        <v>-0.0233</v>
       </c>
       <c r="H91" t="n">
-        <v>76.97</v>
+        <v>134.81</v>
       </c>
       <c r="I91" t="n">
         <v>2654.54</v>
@@ -8075,15 +8075,19 @@
       <c r="O91" t="n">
         <v>2838.06</v>
       </c>
-      <c r="P91" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q91" s="6" t="n">
-        <v/>
+      <c r="P91" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S91" s="7" t="inlineStr">
@@ -8102,14 +8106,14 @@
       <c r="V91" s="8" t="n">
         <v/>
       </c>
-      <c r="W91" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W91" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1564.61</v>
+        <v>1576.59</v>
       </c>
       <c r="C2" t="n">
-        <v>1590.2</v>
+        <v>1607.87</v>
       </c>
       <c r="D2" t="n">
-        <v>1510.51</v>
+        <v>1561.97</v>
       </c>
       <c r="E2" t="n">
-        <v>1576.62</v>
+        <v>1571.59</v>
       </c>
       <c r="F2" t="n">
-        <v>11.8</v>
+        <v>-5.03</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0075</v>
+        <v>-0.0032</v>
       </c>
       <c r="H2" t="n">
-        <v>79.69</v>
+        <v>45.89</v>
       </c>
       <c r="I2" t="n">
-        <v>1406.91</v>
+        <v>1430.81</v>
       </c>
       <c r="J2" t="n">
-        <v>1425.25</v>
+        <v>1510.05</v>
       </c>
       <c r="K2" t="n">
-        <v>1502.38</v>
+        <v>1536.77</v>
       </c>
       <c r="L2" t="n">
-        <v>1579.52</v>
+        <v>1563.48</v>
       </c>
       <c r="M2" t="n">
-        <v>1627.25</v>
+        <v>1616.46</v>
       </c>
       <c r="N2" t="n">
-        <v>1674.98</v>
+        <v>1669.44</v>
       </c>
       <c r="O2" t="n">
-        <v>1781.51</v>
+        <v>1669.89</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,7 +690,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -709,57 +709,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1576.59</v>
+        <v>1571.56</v>
       </c>
       <c r="C3" t="n">
-        <v>1607.87</v>
+        <v>1585.22</v>
       </c>
       <c r="D3" t="n">
-        <v>1561.97</v>
+        <v>1548.76</v>
       </c>
       <c r="E3" t="n">
-        <v>1571.59</v>
+        <v>1570.36</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.03</v>
+        <v>-1.23</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.0008</v>
       </c>
       <c r="H3" t="n">
-        <v>45.89</v>
+        <v>36.46</v>
       </c>
       <c r="I3" t="n">
-        <v>1430.81</v>
+        <v>1516.08</v>
       </c>
       <c r="J3" t="n">
-        <v>1510.05</v>
+        <v>1519.03</v>
       </c>
       <c r="K3" t="n">
-        <v>1536.77</v>
+        <v>1548.64</v>
       </c>
       <c r="L3" t="n">
-        <v>1563.48</v>
+        <v>1578.25</v>
       </c>
       <c r="M3" t="n">
-        <v>1616.46</v>
+        <v>1594.53</v>
       </c>
       <c r="N3" t="n">
-        <v>1669.44</v>
+        <v>1610.82</v>
       </c>
       <c r="O3" t="n">
-        <v>1669.89</v>
+        <v>1653.76</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,7 +772,7 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -791,57 +791,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1571.56</v>
+        <v>1569.99</v>
       </c>
       <c r="C4" t="n">
-        <v>1585.22</v>
+        <v>1633.65</v>
       </c>
       <c r="D4" t="n">
-        <v>1548.76</v>
+        <v>1550.04</v>
       </c>
       <c r="E4" t="n">
-        <v>1570.36</v>
+        <v>1610.21</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.23</v>
+        <v>39.84</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0254</v>
       </c>
       <c r="H4" t="n">
-        <v>36.46</v>
+        <v>83.61</v>
       </c>
       <c r="I4" t="n">
-        <v>1516.08</v>
+        <v>1512.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1519.03</v>
+        <v>1535.59</v>
       </c>
       <c r="K4" t="n">
-        <v>1548.64</v>
+        <v>1552.13</v>
       </c>
       <c r="L4" t="n">
-        <v>1578.25</v>
+        <v>1568.68</v>
       </c>
       <c r="M4" t="n">
-        <v>1594.53</v>
+        <v>1588.59</v>
       </c>
       <c r="N4" t="n">
-        <v>1610.82</v>
+        <v>1608.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1653.76</v>
+        <v>1621.68</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -849,81 +849,85 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1569.99</v>
+        <v>1610.16</v>
       </c>
       <c r="C5" t="n">
-        <v>1633.65</v>
+        <v>1611.35</v>
       </c>
       <c r="D5" t="n">
-        <v>1550.04</v>
+        <v>1549.25</v>
       </c>
       <c r="E5" t="n">
-        <v>1610.21</v>
+        <v>1569.58</v>
       </c>
       <c r="F5" t="n">
-        <v>39.84</v>
+        <v>-40.62</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0254</v>
+        <v>-0.0252</v>
       </c>
       <c r="H5" t="n">
-        <v>83.61</v>
+        <v>62.1</v>
       </c>
       <c r="I5" t="n">
-        <v>1512.3</v>
+        <v>1466.43</v>
       </c>
       <c r="J5" t="n">
-        <v>1535.59</v>
+        <v>1535.78</v>
       </c>
       <c r="K5" t="n">
-        <v>1552.13</v>
+        <v>1568.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1568.68</v>
+        <v>1601.02</v>
       </c>
       <c r="M5" t="n">
-        <v>1588.59</v>
+        <v>1652.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1608.5</v>
+        <v>1703</v>
       </c>
       <c r="O5" t="n">
-        <v>1621.68</v>
+        <v>1717.25</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,83 +937,81 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1610.16</v>
+        <v>1569.91</v>
       </c>
       <c r="C6" t="n">
-        <v>1611.35</v>
+        <v>1642.45</v>
       </c>
       <c r="D6" t="n">
-        <v>1549.25</v>
+        <v>1551.14</v>
       </c>
       <c r="E6" t="n">
-        <v>1569.58</v>
+        <v>1608.96</v>
       </c>
       <c r="F6" t="n">
-        <v>-40.62</v>
+        <v>39.38</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0252</v>
+        <v>0.0251</v>
       </c>
       <c r="H6" t="n">
-        <v>62.1</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>1466.43</v>
+        <v>1487.16</v>
       </c>
       <c r="J6" t="n">
-        <v>1535.78</v>
+        <v>1502.13</v>
       </c>
       <c r="K6" t="n">
-        <v>1568.4</v>
+        <v>1538.54</v>
       </c>
       <c r="L6" t="n">
-        <v>1601.02</v>
+        <v>1574.94</v>
       </c>
       <c r="M6" t="n">
-        <v>1652.01</v>
+        <v>1600.63</v>
       </c>
       <c r="N6" t="n">
-        <v>1703</v>
+        <v>1626.32</v>
       </c>
       <c r="O6" t="n">
-        <v>1717.25</v>
+        <v>1673.44</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,21 +1019,23 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1041,59 +1045,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1569.91</v>
+        <v>1609.01</v>
       </c>
       <c r="C7" t="n">
-        <v>1642.45</v>
+        <v>1720.34</v>
       </c>
       <c r="D7" t="n">
-        <v>1551.14</v>
+        <v>1595.94</v>
       </c>
       <c r="E7" t="n">
-        <v>1608.96</v>
+        <v>1698.17</v>
       </c>
       <c r="F7" t="n">
-        <v>39.38</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0554</v>
       </c>
       <c r="H7" t="n">
-        <v>91.31999999999999</v>
+        <v>124.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1487.16</v>
+        <v>1459.82</v>
       </c>
       <c r="J7" t="n">
-        <v>1502.13</v>
+        <v>1523.73</v>
       </c>
       <c r="K7" t="n">
-        <v>1538.54</v>
+        <v>1563.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1574.94</v>
+        <v>1602.88</v>
       </c>
       <c r="M7" t="n">
-        <v>1600.63</v>
+        <v>1654.62</v>
       </c>
       <c r="N7" t="n">
-        <v>1626.32</v>
+        <v>1706.36</v>
       </c>
       <c r="O7" t="n">
-        <v>1673.44</v>
+        <v>1733.77</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1104,19 +1104,19 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V7" s="8" t="n">
@@ -1132,50 +1132,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1609.01</v>
+        <v>1698.42</v>
       </c>
       <c r="C8" t="n">
-        <v>1720.34</v>
+        <v>1772.54</v>
       </c>
       <c r="D8" t="n">
-        <v>1595.94</v>
+        <v>1693.04</v>
       </c>
       <c r="E8" t="n">
-        <v>1698.17</v>
+        <v>1756.52</v>
       </c>
       <c r="F8" t="n">
-        <v>89.20999999999999</v>
+        <v>58.35</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0344</v>
       </c>
       <c r="H8" t="n">
-        <v>124.4</v>
+        <v>79.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1459.82</v>
+        <v>1471.54</v>
       </c>
       <c r="J8" t="n">
-        <v>1523.73</v>
+        <v>1593.78</v>
       </c>
       <c r="K8" t="n">
-        <v>1563.3</v>
+        <v>1635.97</v>
       </c>
       <c r="L8" t="n">
-        <v>1602.88</v>
+        <v>1678.16</v>
       </c>
       <c r="M8" t="n">
-        <v>1654.62</v>
+        <v>1760.37</v>
       </c>
       <c r="N8" t="n">
-        <v>1706.36</v>
+        <v>1842.59</v>
       </c>
       <c r="O8" t="n">
-        <v>1733.77</v>
+        <v>1844.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1186,20 +1186,18 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1214,50 +1212,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1698.42</v>
+        <v>1756.58</v>
       </c>
       <c r="C9" t="n">
-        <v>1772.54</v>
+        <v>1804.59</v>
       </c>
       <c r="D9" t="n">
-        <v>1693.04</v>
+        <v>1743.56</v>
       </c>
       <c r="E9" t="n">
-        <v>1756.52</v>
+        <v>1779.03</v>
       </c>
       <c r="F9" t="n">
-        <v>58.35</v>
+        <v>22.51</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.0128</v>
       </c>
       <c r="H9" t="n">
-        <v>79.5</v>
+        <v>61.02</v>
       </c>
       <c r="I9" t="n">
-        <v>1471.54</v>
+        <v>1613.53</v>
       </c>
       <c r="J9" t="n">
-        <v>1593.78</v>
+        <v>1688.88</v>
       </c>
       <c r="K9" t="n">
-        <v>1635.97</v>
+        <v>1716.77</v>
       </c>
       <c r="L9" t="n">
-        <v>1678.16</v>
+        <v>1744.65</v>
       </c>
       <c r="M9" t="n">
-        <v>1760.37</v>
+        <v>1796.27</v>
       </c>
       <c r="N9" t="n">
-        <v>1842.59</v>
+        <v>1847.89</v>
       </c>
       <c r="O9" t="n">
-        <v>1844.75</v>
+        <v>1852.05</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1268,7 +1266,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1294,50 +1292,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1756.58</v>
+        <v>1779.04</v>
       </c>
       <c r="C10" t="n">
-        <v>1804.59</v>
+        <v>1805.91</v>
       </c>
       <c r="D10" t="n">
-        <v>1743.56</v>
+        <v>1749.14</v>
       </c>
       <c r="E10" t="n">
-        <v>1779.03</v>
+        <v>1783.01</v>
       </c>
       <c r="F10" t="n">
-        <v>22.51</v>
+        <v>3.97</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.0022</v>
       </c>
       <c r="H10" t="n">
-        <v>61.02</v>
+        <v>56.78</v>
       </c>
       <c r="I10" t="n">
-        <v>1613.53</v>
+        <v>1682.54</v>
       </c>
       <c r="J10" t="n">
-        <v>1688.88</v>
+        <v>1720.49</v>
       </c>
       <c r="K10" t="n">
-        <v>1716.77</v>
+        <v>1748.52</v>
       </c>
       <c r="L10" t="n">
-        <v>1744.65</v>
+        <v>1776.55</v>
       </c>
       <c r="M10" t="n">
-        <v>1796.27</v>
+        <v>1809.55</v>
       </c>
       <c r="N10" t="n">
-        <v>1847.89</v>
+        <v>1842.54</v>
       </c>
       <c r="O10" t="n">
-        <v>1852.05</v>
+        <v>1865.61</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1348,15 +1346,13 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1374,67 +1370,73 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779.04</v>
+        <v>1783</v>
       </c>
       <c r="C11" t="n">
-        <v>1805.91</v>
+        <v>1829.51</v>
       </c>
       <c r="D11" t="n">
-        <v>1749.14</v>
+        <v>1728.97</v>
       </c>
       <c r="E11" t="n">
-        <v>1783.01</v>
+        <v>1797.57</v>
       </c>
       <c r="F11" t="n">
-        <v>3.97</v>
+        <v>14.57</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>56.78</v>
+        <v>100.55</v>
       </c>
       <c r="I11" t="n">
-        <v>1682.54</v>
+        <v>1692.36</v>
       </c>
       <c r="J11" t="n">
-        <v>1720.49</v>
+        <v>1728.97</v>
       </c>
       <c r="K11" t="n">
-        <v>1748.52</v>
+        <v>1754.62</v>
       </c>
       <c r="L11" t="n">
-        <v>1776.55</v>
+        <v>1780.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1809.55</v>
+        <v>1811.39</v>
       </c>
       <c r="N11" t="n">
-        <v>1842.54</v>
+        <v>1842.52</v>
       </c>
       <c r="O11" t="n">
-        <v>1865.61</v>
+        <v>1862.69</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1447,78 +1449,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1783</v>
+        <v>1797.56</v>
       </c>
       <c r="C12" t="n">
-        <v>1829.51</v>
+        <v>1810.33</v>
       </c>
       <c r="D12" t="n">
-        <v>1728.97</v>
+        <v>1756.71</v>
       </c>
       <c r="E12" t="n">
-        <v>1797.57</v>
+        <v>1768.51</v>
       </c>
       <c r="F12" t="n">
-        <v>14.57</v>
+        <v>-29.06</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0162</v>
       </c>
       <c r="H12" t="n">
-        <v>100.55</v>
+        <v>53.62</v>
       </c>
       <c r="I12" t="n">
-        <v>1692.36</v>
+        <v>1628.42</v>
       </c>
       <c r="J12" t="n">
-        <v>1728.97</v>
+        <v>1706.19</v>
       </c>
       <c r="K12" t="n">
-        <v>1754.62</v>
+        <v>1747.3</v>
       </c>
       <c r="L12" t="n">
-        <v>1780.27</v>
+        <v>1788.41</v>
       </c>
       <c r="M12" t="n">
-        <v>1811.39</v>
+        <v>1847.85</v>
       </c>
       <c r="N12" t="n">
-        <v>1842.52</v>
+        <v>1907.29</v>
       </c>
       <c r="O12" t="n">
-        <v>1862.69</v>
+        <v>1930.06</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1533,57 +1533,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1797.56</v>
+        <v>1768.39</v>
       </c>
       <c r="C13" t="n">
-        <v>1810.33</v>
+        <v>1782.86</v>
       </c>
       <c r="D13" t="n">
-        <v>1756.71</v>
+        <v>1711.9</v>
       </c>
       <c r="E13" t="n">
-        <v>1768.51</v>
+        <v>1742.68</v>
       </c>
       <c r="F13" t="n">
-        <v>-29.06</v>
+        <v>-25.83</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0162</v>
+        <v>-0.0146</v>
       </c>
       <c r="H13" t="n">
-        <v>53.62</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>1628.42</v>
+        <v>1703.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1706.19</v>
+        <v>1707.39</v>
       </c>
       <c r="K13" t="n">
-        <v>1747.3</v>
+        <v>1741.7</v>
       </c>
       <c r="L13" t="n">
-        <v>1788.41</v>
+        <v>1776.02</v>
       </c>
       <c r="M13" t="n">
-        <v>1847.85</v>
+        <v>1795.32</v>
       </c>
       <c r="N13" t="n">
-        <v>1907.29</v>
+        <v>1814.62</v>
       </c>
       <c r="O13" t="n">
-        <v>1930.06</v>
+        <v>1863.95</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1591,12 +1591,14 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1615,57 +1617,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1768.39</v>
+        <v>1742.66</v>
       </c>
       <c r="C14" t="n">
-        <v>1782.86</v>
+        <v>1760.21</v>
       </c>
       <c r="D14" t="n">
-        <v>1711.9</v>
+        <v>1721.3</v>
       </c>
       <c r="E14" t="n">
-        <v>1742.68</v>
+        <v>1744.48</v>
       </c>
       <c r="F14" t="n">
-        <v>-25.83</v>
+        <v>1.81</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0146</v>
+        <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>70.95999999999999</v>
+        <v>38.91</v>
       </c>
       <c r="I14" t="n">
-        <v>1703.1</v>
+        <v>1640.94</v>
       </c>
       <c r="J14" t="n">
-        <v>1707.39</v>
+        <v>1669.37</v>
       </c>
       <c r="K14" t="n">
-        <v>1741.7</v>
+        <v>1707.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1776.02</v>
+        <v>1745.03</v>
       </c>
       <c r="M14" t="n">
-        <v>1795.32</v>
+        <v>1778.16</v>
       </c>
       <c r="N14" t="n">
-        <v>1814.62</v>
+        <v>1811.29</v>
       </c>
       <c r="O14" t="n">
-        <v>1863.95</v>
+        <v>1853.82</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1673,14 +1675,12 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1699,57 +1699,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1742.66</v>
+        <v>1744.47</v>
       </c>
       <c r="C15" t="n">
-        <v>1760.21</v>
+        <v>1809.76</v>
       </c>
       <c r="D15" t="n">
-        <v>1721.3</v>
+        <v>1736.72</v>
       </c>
       <c r="E15" t="n">
-        <v>1744.48</v>
+        <v>1795.69</v>
       </c>
       <c r="F15" t="n">
-        <v>1.81</v>
+        <v>51.21</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.001</v>
+        <v>0.0294</v>
       </c>
       <c r="H15" t="n">
-        <v>38.91</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1640.94</v>
+        <v>1682.39</v>
       </c>
       <c r="J15" t="n">
-        <v>1669.37</v>
+        <v>1707.44</v>
       </c>
       <c r="K15" t="n">
-        <v>1707.2</v>
+        <v>1725.03</v>
       </c>
       <c r="L15" t="n">
-        <v>1745.03</v>
+        <v>1742.62</v>
       </c>
       <c r="M15" t="n">
-        <v>1778.16</v>
+        <v>1763.94</v>
       </c>
       <c r="N15" t="n">
-        <v>1811.29</v>
+        <v>1785.26</v>
       </c>
       <c r="O15" t="n">
-        <v>1853.82</v>
+        <v>1799.11</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1762,76 +1762,78 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1744.47</v>
+        <v>1795.82</v>
       </c>
       <c r="C16" t="n">
-        <v>1809.76</v>
+        <v>1827.83</v>
       </c>
       <c r="D16" t="n">
-        <v>1736.72</v>
+        <v>1786.3</v>
       </c>
       <c r="E16" t="n">
-        <v>1795.69</v>
+        <v>1788.1</v>
       </c>
       <c r="F16" t="n">
-        <v>51.21</v>
+        <v>-7.59</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0294</v>
+        <v>-0.0042</v>
       </c>
       <c r="H16" t="n">
-        <v>73.04000000000001</v>
+        <v>41.54</v>
       </c>
       <c r="I16" t="n">
-        <v>1682.39</v>
+        <v>1663.69</v>
       </c>
       <c r="J16" t="n">
-        <v>1707.44</v>
+        <v>1733.88</v>
       </c>
       <c r="K16" t="n">
-        <v>1725.03</v>
+        <v>1759.18</v>
       </c>
       <c r="L16" t="n">
-        <v>1742.62</v>
+        <v>1784.47</v>
       </c>
       <c r="M16" t="n">
-        <v>1763.94</v>
+        <v>1832.21</v>
       </c>
       <c r="N16" t="n">
-        <v>1785.26</v>
+        <v>1879.95</v>
       </c>
       <c r="O16" t="n">
-        <v>1799.11</v>
+        <v>1882.79</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1842,80 +1844,78 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1795.82</v>
+        <v>1787.57</v>
       </c>
       <c r="C17" t="n">
-        <v>1827.83</v>
+        <v>1824.98</v>
       </c>
       <c r="D17" t="n">
-        <v>1786.3</v>
+        <v>1779.64</v>
       </c>
       <c r="E17" t="n">
-        <v>1788.1</v>
+        <v>1805.79</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.59</v>
+        <v>17.69</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>41.54</v>
+        <v>45.34</v>
       </c>
       <c r="I17" t="n">
-        <v>1663.69</v>
+        <v>1744.76</v>
       </c>
       <c r="J17" t="n">
-        <v>1733.88</v>
+        <v>1737.08</v>
       </c>
       <c r="K17" t="n">
-        <v>1759.18</v>
+        <v>1767.33</v>
       </c>
       <c r="L17" t="n">
-        <v>1784.47</v>
+        <v>1797.58</v>
       </c>
       <c r="M17" t="n">
-        <v>1832.21</v>
+        <v>1808.87</v>
       </c>
       <c r="N17" t="n">
-        <v>1879.95</v>
+        <v>1820.15</v>
       </c>
       <c r="O17" t="n">
-        <v>1882.79</v>
+        <v>1869.37</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1926,16 +1926,20 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1947,81 +1951,83 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1787.57</v>
+        <v>1805.76</v>
       </c>
       <c r="C18" t="n">
-        <v>1824.98</v>
+        <v>1842.46</v>
       </c>
       <c r="D18" t="n">
-        <v>1779.64</v>
+        <v>1749.35</v>
       </c>
       <c r="E18" t="n">
-        <v>1805.79</v>
+        <v>1773.5</v>
       </c>
       <c r="F18" t="n">
-        <v>17.69</v>
+        <v>-32.29</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>-0.0179</v>
       </c>
       <c r="H18" t="n">
-        <v>45.34</v>
+        <v>93.11</v>
       </c>
       <c r="I18" t="n">
-        <v>1744.76</v>
+        <v>1734.29</v>
       </c>
       <c r="J18" t="n">
-        <v>1737.08</v>
+        <v>1762.18</v>
       </c>
       <c r="K18" t="n">
-        <v>1767.33</v>
+        <v>1783.12</v>
       </c>
       <c r="L18" t="n">
-        <v>1797.58</v>
+        <v>1804.05</v>
       </c>
       <c r="M18" t="n">
-        <v>1808.87</v>
+        <v>1828.46</v>
       </c>
       <c r="N18" t="n">
-        <v>1820.15</v>
+        <v>1852.87</v>
       </c>
       <c r="O18" t="n">
-        <v>1869.37</v>
+        <v>1870.32</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2040,77 +2046,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1805.76</v>
+        <v>1773.47</v>
       </c>
       <c r="C19" t="n">
-        <v>1842.46</v>
+        <v>1894.06</v>
       </c>
       <c r="D19" t="n">
-        <v>1749.35</v>
+        <v>1772.02</v>
       </c>
       <c r="E19" t="n">
-        <v>1773.5</v>
+        <v>1889.48</v>
       </c>
       <c r="F19" t="n">
-        <v>-32.29</v>
+        <v>115.98</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0654</v>
       </c>
       <c r="H19" t="n">
-        <v>93.11</v>
+        <v>122.04</v>
       </c>
       <c r="I19" t="n">
-        <v>1734.29</v>
+        <v>1656.24</v>
       </c>
       <c r="J19" t="n">
-        <v>1762.18</v>
+        <v>1669.19</v>
       </c>
       <c r="K19" t="n">
-        <v>1783.12</v>
+        <v>1726.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1804.05</v>
+        <v>1784.7</v>
       </c>
       <c r="M19" t="n">
-        <v>1828.46</v>
+        <v>1820.05</v>
       </c>
       <c r="N19" t="n">
-        <v>1852.87</v>
+        <v>1855.41</v>
       </c>
       <c r="O19" t="n">
-        <v>1870.32</v>
+        <v>1935.56</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2119,59 +2123,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1773.47</v>
+        <v>1889.5</v>
       </c>
       <c r="C20" t="n">
-        <v>1894.06</v>
+        <v>1944.16</v>
       </c>
       <c r="D20" t="n">
-        <v>1772.02</v>
+        <v>1863.64</v>
       </c>
       <c r="E20" t="n">
-        <v>1889.48</v>
+        <v>1916.94</v>
       </c>
       <c r="F20" t="n">
-        <v>115.98</v>
+        <v>27.46</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0654</v>
+        <v>0.0145</v>
       </c>
       <c r="H20" t="n">
-        <v>122.04</v>
+        <v>80.53</v>
       </c>
       <c r="I20" t="n">
-        <v>1656.24</v>
+        <v>1649.97</v>
       </c>
       <c r="J20" t="n">
-        <v>1669.19</v>
+        <v>1795.66</v>
       </c>
       <c r="K20" t="n">
-        <v>1726.95</v>
+        <v>1828.46</v>
       </c>
       <c r="L20" t="n">
-        <v>1784.7</v>
+        <v>1861.26</v>
       </c>
       <c r="M20" t="n">
-        <v>1820.05</v>
+        <v>1950.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1855.41</v>
+        <v>2039.74</v>
       </c>
       <c r="O20" t="n">
-        <v>1935.56</v>
+        <v>2016.11</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2182,20 +2182,18 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2210,50 +2208,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1889.5</v>
+        <v>1916.98</v>
       </c>
       <c r="C21" t="n">
-        <v>1944.16</v>
+        <v>1927.09</v>
       </c>
       <c r="D21" t="n">
-        <v>1863.64</v>
+        <v>1856.78</v>
       </c>
       <c r="E21" t="n">
-        <v>1916.94</v>
+        <v>1863.19</v>
       </c>
       <c r="F21" t="n">
-        <v>27.46</v>
+        <v>-53.75</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0145</v>
+        <v>-0.028</v>
       </c>
       <c r="H21" t="n">
-        <v>80.53</v>
+        <v>70.31</v>
       </c>
       <c r="I21" t="n">
-        <v>1649.97</v>
+        <v>1783.11</v>
       </c>
       <c r="J21" t="n">
-        <v>1795.66</v>
+        <v>1842.94</v>
       </c>
       <c r="K21" t="n">
-        <v>1828.46</v>
+        <v>1876.68</v>
       </c>
       <c r="L21" t="n">
-        <v>1861.26</v>
+        <v>1910.42</v>
       </c>
       <c r="M21" t="n">
-        <v>1950.5</v>
+        <v>1957.21</v>
       </c>
       <c r="N21" t="n">
-        <v>2039.74</v>
+        <v>2003.99</v>
       </c>
       <c r="O21" t="n">
-        <v>2016.11</v>
+        <v>2024.69</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2261,18 +2259,18 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2285,55 +2283,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1916.98</v>
+        <v>1863.22</v>
       </c>
       <c r="C22" t="n">
-        <v>1927.09</v>
+        <v>1869.07</v>
       </c>
       <c r="D22" t="n">
-        <v>1856.78</v>
+        <v>1803.05</v>
       </c>
       <c r="E22" t="n">
-        <v>1863.19</v>
+        <v>1840.99</v>
       </c>
       <c r="F22" t="n">
-        <v>-53.75</v>
+        <v>-22.21</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.028</v>
+        <v>-0.0119</v>
       </c>
       <c r="H22" t="n">
-        <v>70.31</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>1783.11</v>
+        <v>1786.47</v>
       </c>
       <c r="J22" t="n">
-        <v>1842.94</v>
+        <v>1778.51</v>
       </c>
       <c r="K22" t="n">
-        <v>1876.68</v>
+        <v>1828.04</v>
       </c>
       <c r="L22" t="n">
-        <v>1910.42</v>
+        <v>1877.56</v>
       </c>
       <c r="M22" t="n">
-        <v>1957.21</v>
+        <v>1898.35</v>
       </c>
       <c r="N22" t="n">
-        <v>2003.99</v>
+        <v>1919.13</v>
       </c>
       <c r="O22" t="n">
-        <v>2024.69</v>
+        <v>1997.4</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2346,7 +2348,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2374,50 +2376,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1863.22</v>
+        <v>1841.1</v>
       </c>
       <c r="C23" t="n">
-        <v>1869.07</v>
+        <v>1864.13</v>
       </c>
       <c r="D23" t="n">
-        <v>1803.05</v>
+        <v>1836.61</v>
       </c>
       <c r="E23" t="n">
-        <v>1840.99</v>
+        <v>1861.39</v>
       </c>
       <c r="F23" t="n">
-        <v>-22.21</v>
+        <v>20.4</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0111</v>
       </c>
       <c r="H23" t="n">
-        <v>66.01000000000001</v>
+        <v>27.52</v>
       </c>
       <c r="I23" t="n">
-        <v>1786.47</v>
+        <v>1737.04</v>
       </c>
       <c r="J23" t="n">
-        <v>1778.51</v>
+        <v>1777.44</v>
       </c>
       <c r="K23" t="n">
-        <v>1828.04</v>
+        <v>1807.98</v>
       </c>
       <c r="L23" t="n">
-        <v>1877.56</v>
+        <v>1838.52</v>
       </c>
       <c r="M23" t="n">
-        <v>1898.35</v>
+        <v>1873.99</v>
       </c>
       <c r="N23" t="n">
-        <v>1919.13</v>
+        <v>1909.47</v>
       </c>
       <c r="O23" t="n">
-        <v>1997.4</v>
+        <v>1935.08</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2425,19 +2427,19 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2451,57 +2453,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1841.1</v>
+        <v>1861.42</v>
       </c>
       <c r="C24" t="n">
-        <v>1864.13</v>
+        <v>1877.03</v>
       </c>
       <c r="D24" t="n">
-        <v>1836.61</v>
+        <v>1852.73</v>
       </c>
       <c r="E24" t="n">
-        <v>1861.39</v>
+        <v>1871.51</v>
       </c>
       <c r="F24" t="n">
-        <v>20.4</v>
+        <v>10.12</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0054</v>
       </c>
       <c r="H24" t="n">
-        <v>27.52</v>
+        <v>24.3</v>
       </c>
       <c r="I24" t="n">
-        <v>1737.04</v>
+        <v>1809.09</v>
       </c>
       <c r="J24" t="n">
-        <v>1777.44</v>
+        <v>1839.38</v>
       </c>
       <c r="K24" t="n">
-        <v>1807.98</v>
+        <v>1847.63</v>
       </c>
       <c r="L24" t="n">
-        <v>1838.52</v>
+        <v>1855.88</v>
       </c>
       <c r="M24" t="n">
-        <v>1873.99</v>
+        <v>1875.15</v>
       </c>
       <c r="N24" t="n">
-        <v>1909.47</v>
+        <v>1894.43</v>
       </c>
       <c r="O24" t="n">
-        <v>1935.08</v>
+        <v>1891.66</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2512,7 +2514,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2533,231 +2535,227 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1861.42</v>
+        <v>1871.28</v>
       </c>
       <c r="C25" t="n">
-        <v>1877.03</v>
+        <v>1916.24</v>
       </c>
       <c r="D25" t="n">
-        <v>1852.73</v>
+        <v>1842.82</v>
       </c>
       <c r="E25" t="n">
-        <v>1871.51</v>
+        <v>1903.76</v>
       </c>
       <c r="F25" t="n">
-        <v>10.12</v>
+        <v>32.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0172</v>
       </c>
       <c r="H25" t="n">
-        <v>24.3</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>1809.09</v>
+        <v>1828.42</v>
       </c>
       <c r="J25" t="n">
-        <v>1839.38</v>
+        <v>1850.52</v>
       </c>
       <c r="K25" t="n">
-        <v>1847.63</v>
+        <v>1859.36</v>
       </c>
       <c r="L25" t="n">
-        <v>1855.88</v>
+        <v>1868.19</v>
       </c>
       <c r="M25" t="n">
-        <v>1875.15</v>
+        <v>1883.66</v>
       </c>
       <c r="N25" t="n">
-        <v>1894.43</v>
+        <v>1899.13</v>
       </c>
       <c r="O25" t="n">
-        <v>1891.66</v>
+        <v>1901.34</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1871.28</v>
+        <v>1903.69</v>
       </c>
       <c r="C26" t="n">
-        <v>1916.24</v>
+        <v>1949.55</v>
       </c>
       <c r="D26" t="n">
-        <v>1842.82</v>
+        <v>1900.07</v>
       </c>
       <c r="E26" t="n">
-        <v>1903.76</v>
+        <v>1928.38</v>
       </c>
       <c r="F26" t="n">
-        <v>32.25</v>
+        <v>24.62</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0129</v>
       </c>
       <c r="H26" t="n">
-        <v>73.43000000000001</v>
+        <v>49.48</v>
       </c>
       <c r="I26" t="n">
-        <v>1828.42</v>
+        <v>1769.39</v>
       </c>
       <c r="J26" t="n">
-        <v>1850.52</v>
+        <v>1842.45</v>
       </c>
       <c r="K26" t="n">
-        <v>1859.36</v>
+        <v>1867.05</v>
       </c>
       <c r="L26" t="n">
-        <v>1868.19</v>
+        <v>1891.64</v>
       </c>
       <c r="M26" t="n">
-        <v>1883.66</v>
+        <v>1940.47</v>
       </c>
       <c r="N26" t="n">
-        <v>1899.13</v>
+        <v>1989.3</v>
       </c>
       <c r="O26" t="n">
-        <v>1901.34</v>
+        <v>1989.67</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1903.69</v>
+        <v>1928.2</v>
       </c>
       <c r="C27" t="n">
-        <v>1949.55</v>
+        <v>1955.15</v>
       </c>
       <c r="D27" t="n">
-        <v>1900.07</v>
+        <v>1909.61</v>
       </c>
       <c r="E27" t="n">
-        <v>1928.38</v>
+        <v>1933.49</v>
       </c>
       <c r="F27" t="n">
-        <v>24.62</v>
+        <v>5.11</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0026</v>
       </c>
       <c r="H27" t="n">
-        <v>49.48</v>
+        <v>45.54</v>
       </c>
       <c r="I27" t="n">
-        <v>1769.39</v>
+        <v>1850.58</v>
       </c>
       <c r="J27" t="n">
-        <v>1842.45</v>
+        <v>1880.69</v>
       </c>
       <c r="K27" t="n">
-        <v>1867.05</v>
+        <v>1903.64</v>
       </c>
       <c r="L27" t="n">
-        <v>1891.64</v>
+        <v>1926.6</v>
       </c>
       <c r="M27" t="n">
-        <v>1940.47</v>
+        <v>1953.12</v>
       </c>
       <c r="N27" t="n">
-        <v>1989.3</v>
+        <v>1979.65</v>
       </c>
       <c r="O27" t="n">
-        <v>1989.67</v>
+        <v>1999.03</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2768,14 +2766,14 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U27" s="8" t="n">
@@ -2794,69 +2792,71 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1928.2</v>
+        <v>1933.47</v>
       </c>
       <c r="C28" t="n">
-        <v>1955.15</v>
+        <v>1940.28</v>
       </c>
       <c r="D28" t="n">
-        <v>1909.61</v>
+        <v>1868.52</v>
       </c>
       <c r="E28" t="n">
-        <v>1933.49</v>
+        <v>1877.1</v>
       </c>
       <c r="F28" t="n">
-        <v>5.11</v>
+        <v>-56.39</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0292</v>
       </c>
       <c r="H28" t="n">
-        <v>45.54</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>1850.58</v>
+        <v>1864.07</v>
       </c>
       <c r="J28" t="n">
-        <v>1880.69</v>
+        <v>1888.51</v>
       </c>
       <c r="K28" t="n">
-        <v>1903.64</v>
+        <v>1910.72</v>
       </c>
       <c r="L28" t="n">
-        <v>1926.6</v>
+        <v>1932.93</v>
       </c>
       <c r="M28" t="n">
-        <v>1953.12</v>
+        <v>1956.26</v>
       </c>
       <c r="N28" t="n">
-        <v>1979.65</v>
+        <v>1979.58</v>
       </c>
       <c r="O28" t="n">
-        <v>1999.03</v>
+        <v>2000.68</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2864,9 +2864,9 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2874,65 +2874,63 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1933.47</v>
+        <v>1877.1</v>
       </c>
       <c r="C29" t="n">
-        <v>1940.28</v>
+        <v>1907.54</v>
       </c>
       <c r="D29" t="n">
-        <v>1868.52</v>
+        <v>1846.82</v>
       </c>
       <c r="E29" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="F29" t="n">
-        <v>-56.39</v>
+        <v>-16.92</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0292</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>71.76000000000001</v>
+        <v>60.72</v>
       </c>
       <c r="I29" t="n">
-        <v>1864.07</v>
+        <v>1796.76</v>
       </c>
       <c r="J29" t="n">
-        <v>1888.51</v>
+        <v>1791.69</v>
       </c>
       <c r="K29" t="n">
-        <v>1910.72</v>
+        <v>1841.22</v>
       </c>
       <c r="L29" t="n">
-        <v>1932.93</v>
+        <v>1890.75</v>
       </c>
       <c r="M29" t="n">
-        <v>1956.26</v>
+        <v>1912.98</v>
       </c>
       <c r="N29" t="n">
-        <v>1979.58</v>
+        <v>1935.21</v>
       </c>
       <c r="O29" t="n">
-        <v>2000.68</v>
+        <v>2012.05</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2956,50 +2954,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1877.1</v>
+        <v>1860.18</v>
       </c>
       <c r="C30" t="n">
-        <v>1907.54</v>
+        <v>1875.14</v>
       </c>
       <c r="D30" t="n">
-        <v>1846.82</v>
+        <v>1849.83</v>
       </c>
       <c r="E30" t="n">
-        <v>1860.18</v>
+        <v>1873.22</v>
       </c>
       <c r="F30" t="n">
-        <v>-16.92</v>
+        <v>13.05</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.007</v>
       </c>
       <c r="H30" t="n">
-        <v>60.72</v>
+        <v>25.32</v>
       </c>
       <c r="I30" t="n">
-        <v>1796.76</v>
+        <v>1786.1</v>
       </c>
       <c r="J30" t="n">
-        <v>1791.69</v>
+        <v>1790.95</v>
       </c>
       <c r="K30" t="n">
-        <v>1841.22</v>
+        <v>1829.82</v>
       </c>
       <c r="L30" t="n">
-        <v>1890.75</v>
+        <v>1868.68</v>
       </c>
       <c r="M30" t="n">
-        <v>1912.98</v>
+        <v>1890.54</v>
       </c>
       <c r="N30" t="n">
-        <v>1935.21</v>
+        <v>1912.39</v>
       </c>
       <c r="O30" t="n">
-        <v>2012.05</v>
+        <v>1968.26</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3007,14 +3005,12 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3031,55 +3027,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1860.18</v>
+        <v>1873.24</v>
       </c>
       <c r="C31" t="n">
-        <v>1875.14</v>
+        <v>1963.25</v>
       </c>
       <c r="D31" t="n">
-        <v>1849.83</v>
+        <v>1872.38</v>
       </c>
       <c r="E31" t="n">
-        <v>1873.22</v>
+        <v>1953.41</v>
       </c>
       <c r="F31" t="n">
-        <v>13.05</v>
+        <v>80.19</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0428</v>
       </c>
       <c r="H31" t="n">
-        <v>25.32</v>
+        <v>90.86</v>
       </c>
       <c r="I31" t="n">
-        <v>1786.1</v>
+        <v>1824.51</v>
       </c>
       <c r="J31" t="n">
-        <v>1790.95</v>
+        <v>1853.27</v>
       </c>
       <c r="K31" t="n">
-        <v>1829.82</v>
+        <v>1860.56</v>
       </c>
       <c r="L31" t="n">
-        <v>1868.68</v>
+        <v>1867.85</v>
       </c>
       <c r="M31" t="n">
-        <v>1890.54</v>
+        <v>1885.88</v>
       </c>
       <c r="N31" t="n">
-        <v>1912.39</v>
+        <v>1903.91</v>
       </c>
       <c r="O31" t="n">
-        <v>1968.26</v>
+        <v>1900.46</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3090,179 +3090,179 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1873.24</v>
+        <v>1953.41</v>
       </c>
       <c r="C32" t="n">
-        <v>1963.25</v>
+        <v>1976.46</v>
       </c>
       <c r="D32" t="n">
-        <v>1872.38</v>
+        <v>1882.42</v>
       </c>
       <c r="E32" t="n">
-        <v>1953.41</v>
+        <v>1890.61</v>
       </c>
       <c r="F32" t="n">
-        <v>80.19</v>
+        <v>-62.8</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0428</v>
+        <v>-0.0321</v>
       </c>
       <c r="H32" t="n">
-        <v>90.86</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>1824.51</v>
+        <v>1781.52</v>
       </c>
       <c r="J32" t="n">
-        <v>1853.27</v>
+        <v>1880.35</v>
       </c>
       <c r="K32" t="n">
-        <v>1860.56</v>
+        <v>1907.98</v>
       </c>
       <c r="L32" t="n">
-        <v>1867.85</v>
+        <v>1935.61</v>
       </c>
       <c r="M32" t="n">
-        <v>1885.88</v>
+        <v>1998.84</v>
       </c>
       <c r="N32" t="n">
-        <v>1903.91</v>
+        <v>2062.07</v>
       </c>
       <c r="O32" t="n">
-        <v>1900.46</v>
+        <v>2054.11</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1953.41</v>
+        <v>1890.63</v>
       </c>
       <c r="C33" t="n">
-        <v>1976.46</v>
+        <v>1926.5</v>
       </c>
       <c r="D33" t="n">
-        <v>1882.42</v>
+        <v>1856.34</v>
       </c>
       <c r="E33" t="n">
-        <v>1890.61</v>
+        <v>1919.95</v>
       </c>
       <c r="F33" t="n">
-        <v>-62.8</v>
+        <v>29.33</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0321</v>
+        <v>0.0155</v>
       </c>
       <c r="H33" t="n">
-        <v>94.04000000000001</v>
+        <v>70.16</v>
       </c>
       <c r="I33" t="n">
-        <v>1781.52</v>
+        <v>1788.38</v>
       </c>
       <c r="J33" t="n">
-        <v>1880.35</v>
+        <v>1777.16</v>
       </c>
       <c r="K33" t="n">
-        <v>1907.98</v>
+        <v>1843.59</v>
       </c>
       <c r="L33" t="n">
-        <v>1935.61</v>
+        <v>1910.03</v>
       </c>
       <c r="M33" t="n">
-        <v>1998.84</v>
+        <v>1937.63</v>
       </c>
       <c r="N33" t="n">
-        <v>2062.07</v>
+        <v>1965.24</v>
       </c>
       <c r="O33" t="n">
-        <v>2054.11</v>
+        <v>2070.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3281,57 +3281,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1890.63</v>
+        <v>1919.99</v>
       </c>
       <c r="C34" t="n">
-        <v>1926.5</v>
+        <v>1929.9</v>
       </c>
       <c r="D34" t="n">
-        <v>1856.34</v>
+        <v>1873.62</v>
       </c>
       <c r="E34" t="n">
-        <v>1919.95</v>
+        <v>1908.52</v>
       </c>
       <c r="F34" t="n">
-        <v>29.33</v>
+        <v>-11.43</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0155</v>
+        <v>-0.006</v>
       </c>
       <c r="H34" t="n">
-        <v>70.16</v>
+        <v>56.28</v>
       </c>
       <c r="I34" t="n">
-        <v>1788.38</v>
+        <v>1786.18</v>
       </c>
       <c r="J34" t="n">
-        <v>1777.16</v>
+        <v>1864.05</v>
       </c>
       <c r="K34" t="n">
-        <v>1843.59</v>
+        <v>1884.87</v>
       </c>
       <c r="L34" t="n">
-        <v>1910.03</v>
+        <v>1905.69</v>
       </c>
       <c r="M34" t="n">
-        <v>1937.63</v>
+        <v>1955.03</v>
       </c>
       <c r="N34" t="n">
-        <v>1965.24</v>
+        <v>2004.37</v>
       </c>
       <c r="O34" t="n">
-        <v>2070.5</v>
+        <v>1996.67</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3339,10 +3339,12 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3363,57 +3365,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1919.99</v>
+        <v>1908.59</v>
       </c>
       <c r="C35" t="n">
-        <v>1929.9</v>
+        <v>1934.58</v>
       </c>
       <c r="D35" t="n">
-        <v>1873.62</v>
+        <v>1892.2</v>
       </c>
       <c r="E35" t="n">
-        <v>1908.52</v>
+        <v>1917.37</v>
       </c>
       <c r="F35" t="n">
-        <v>-11.43</v>
+        <v>8.85</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0046</v>
       </c>
       <c r="H35" t="n">
-        <v>56.28</v>
+        <v>42.38</v>
       </c>
       <c r="I35" t="n">
-        <v>1786.18</v>
+        <v>1817.34</v>
       </c>
       <c r="J35" t="n">
-        <v>1864.05</v>
+        <v>1855.62</v>
       </c>
       <c r="K35" t="n">
-        <v>1884.87</v>
+        <v>1880.38</v>
       </c>
       <c r="L35" t="n">
-        <v>1905.69</v>
+        <v>1905.14</v>
       </c>
       <c r="M35" t="n">
-        <v>1955.03</v>
+        <v>1936.66</v>
       </c>
       <c r="N35" t="n">
-        <v>2004.37</v>
+        <v>1968.18</v>
       </c>
       <c r="O35" t="n">
-        <v>1996.67</v>
+        <v>1986.18</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3421,12 +3423,10 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3445,72 +3445,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1908.59</v>
+        <v>1917.14</v>
       </c>
       <c r="C36" t="n">
-        <v>1934.58</v>
+        <v>1933.78</v>
       </c>
       <c r="D36" t="n">
-        <v>1892.2</v>
+        <v>1847.47</v>
       </c>
       <c r="E36" t="n">
-        <v>1917.37</v>
+        <v>1860.35</v>
       </c>
       <c r="F36" t="n">
-        <v>8.85</v>
+        <v>-57.03</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0046</v>
+        <v>-0.0297</v>
       </c>
       <c r="H36" t="n">
-        <v>42.38</v>
+        <v>86.31</v>
       </c>
       <c r="I36" t="n">
-        <v>1817.34</v>
+        <v>1849.82</v>
       </c>
       <c r="J36" t="n">
-        <v>1855.62</v>
+        <v>1876.99</v>
       </c>
       <c r="K36" t="n">
-        <v>1880.38</v>
+        <v>1896.18</v>
       </c>
       <c r="L36" t="n">
-        <v>1905.14</v>
+        <v>1915.38</v>
       </c>
       <c r="M36" t="n">
-        <v>1936.66</v>
+        <v>1938.56</v>
       </c>
       <c r="N36" t="n">
-        <v>1968.18</v>
+        <v>1961.75</v>
       </c>
       <c r="O36" t="n">
-        <v>1986.18</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>1976.96</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3522,9 +3524,9 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3532,67 +3534,63 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1917.14</v>
+        <v>1860.37</v>
       </c>
       <c r="C37" t="n">
-        <v>1933.78</v>
+        <v>1873.17</v>
       </c>
       <c r="D37" t="n">
-        <v>1847.47</v>
+        <v>1821.49</v>
       </c>
       <c r="E37" t="n">
-        <v>1860.35</v>
+        <v>1843.42</v>
       </c>
       <c r="F37" t="n">
-        <v>-57.03</v>
+        <v>-16.93</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0297</v>
+        <v>-0.0091</v>
       </c>
       <c r="H37" t="n">
-        <v>86.31</v>
+        <v>51.69</v>
       </c>
       <c r="I37" t="n">
-        <v>1849.82</v>
+        <v>1761.16</v>
       </c>
       <c r="J37" t="n">
-        <v>1876.99</v>
+        <v>1758.9</v>
       </c>
       <c r="K37" t="n">
-        <v>1896.18</v>
+        <v>1817.19</v>
       </c>
       <c r="L37" t="n">
-        <v>1915.38</v>
+        <v>1875.48</v>
       </c>
       <c r="M37" t="n">
-        <v>1938.56</v>
+        <v>1903.5</v>
       </c>
       <c r="N37" t="n">
-        <v>1961.75</v>
+        <v>1931.52</v>
       </c>
       <c r="O37" t="n">
-        <v>1976.96</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
+        <v>2020.09</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3616,50 +3614,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1860.37</v>
+        <v>1843.42</v>
       </c>
       <c r="C38" t="n">
-        <v>1873.17</v>
+        <v>1895.77</v>
       </c>
       <c r="D38" t="n">
-        <v>1821.49</v>
+        <v>1842.15</v>
       </c>
       <c r="E38" t="n">
-        <v>1843.42</v>
+        <v>1882.52</v>
       </c>
       <c r="F38" t="n">
-        <v>-16.93</v>
+        <v>39.1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0091</v>
+        <v>0.0212</v>
       </c>
       <c r="H38" t="n">
-        <v>51.69</v>
+        <v>53.61</v>
       </c>
       <c r="I38" t="n">
-        <v>1761.16</v>
+        <v>1769.8</v>
       </c>
       <c r="J38" t="n">
-        <v>1758.9</v>
+        <v>1789.78</v>
       </c>
       <c r="K38" t="n">
-        <v>1817.19</v>
+        <v>1817.57</v>
       </c>
       <c r="L38" t="n">
-        <v>1875.48</v>
+        <v>1845.37</v>
       </c>
       <c r="M38" t="n">
-        <v>1903.5</v>
+        <v>1869.26</v>
       </c>
       <c r="N38" t="n">
-        <v>1931.52</v>
+        <v>1893.15</v>
       </c>
       <c r="O38" t="n">
-        <v>2020.09</v>
+        <v>1924.86</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3667,22 +3665,24 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3691,79 +3691,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1843.42</v>
+        <v>1882.78</v>
       </c>
       <c r="C39" t="n">
-        <v>1895.77</v>
+        <v>1883.44</v>
       </c>
       <c r="D39" t="n">
-        <v>1842.15</v>
+        <v>1827.7</v>
       </c>
       <c r="E39" t="n">
-        <v>1882.52</v>
+        <v>1858.26</v>
       </c>
       <c r="F39" t="n">
-        <v>39.1</v>
+        <v>-24.27</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0212</v>
+        <v>-0.0129</v>
       </c>
       <c r="H39" t="n">
-        <v>53.61</v>
+        <v>55.74</v>
       </c>
       <c r="I39" t="n">
-        <v>1769.8</v>
+        <v>1788.54</v>
       </c>
       <c r="J39" t="n">
-        <v>1789.78</v>
+        <v>1835.69</v>
       </c>
       <c r="K39" t="n">
-        <v>1817.57</v>
+        <v>1855.72</v>
       </c>
       <c r="L39" t="n">
-        <v>1845.37</v>
+        <v>1875.74</v>
       </c>
       <c r="M39" t="n">
-        <v>1869.26</v>
+        <v>1909.33</v>
       </c>
       <c r="N39" t="n">
-        <v>1893.15</v>
+        <v>1942.91</v>
       </c>
       <c r="O39" t="n">
-        <v>1924.86</v>
+        <v>1949.38</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3773,76 +3777,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1882.78</v>
+        <v>1858.22</v>
       </c>
       <c r="C40" t="n">
-        <v>1883.44</v>
+        <v>1879.54</v>
       </c>
       <c r="D40" t="n">
-        <v>1827.7</v>
+        <v>1847.17</v>
       </c>
       <c r="E40" t="n">
-        <v>1858.26</v>
+        <v>1868.39</v>
       </c>
       <c r="F40" t="n">
-        <v>-24.27</v>
+        <v>10.13</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0129</v>
+        <v>0.0055</v>
       </c>
       <c r="H40" t="n">
-        <v>55.74</v>
+        <v>32.36</v>
       </c>
       <c r="I40" t="n">
-        <v>1788.54</v>
+        <v>1771.96</v>
       </c>
       <c r="J40" t="n">
-        <v>1835.69</v>
+        <v>1803.86</v>
       </c>
       <c r="K40" t="n">
-        <v>1855.72</v>
+        <v>1830.39</v>
       </c>
       <c r="L40" t="n">
-        <v>1875.74</v>
+        <v>1856.91</v>
       </c>
       <c r="M40" t="n">
-        <v>1909.33</v>
+        <v>1886.13</v>
       </c>
       <c r="N40" t="n">
-        <v>1942.91</v>
+        <v>1915.34</v>
       </c>
       <c r="O40" t="n">
-        <v>1949.38</v>
+        <v>1939.18</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3859,55 +3855,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1858.22</v>
+        <v>1868.49</v>
       </c>
       <c r="C41" t="n">
-        <v>1879.54</v>
+        <v>1922.64</v>
       </c>
       <c r="D41" t="n">
-        <v>1847.17</v>
+        <v>1854.34</v>
       </c>
       <c r="E41" t="n">
-        <v>1868.39</v>
+        <v>1906.53</v>
       </c>
       <c r="F41" t="n">
-        <v>10.13</v>
+        <v>38.14</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0204</v>
       </c>
       <c r="H41" t="n">
-        <v>32.36</v>
+        <v>68.3</v>
       </c>
       <c r="I41" t="n">
-        <v>1771.96</v>
+        <v>1814.81</v>
       </c>
       <c r="J41" t="n">
-        <v>1803.86</v>
+        <v>1838.54</v>
       </c>
       <c r="K41" t="n">
-        <v>1830.39</v>
+        <v>1852.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1856.91</v>
+        <v>1865.87</v>
       </c>
       <c r="M41" t="n">
-        <v>1886.13</v>
+        <v>1884.57</v>
       </c>
       <c r="N41" t="n">
-        <v>1915.34</v>
+        <v>1903.26</v>
       </c>
       <c r="O41" t="n">
-        <v>1939.18</v>
+        <v>1911.9</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3918,78 +3918,80 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W41" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1868.49</v>
+        <v>1906.44</v>
       </c>
       <c r="C42" t="n">
-        <v>1922.64</v>
+        <v>1917.7</v>
       </c>
       <c r="D42" t="n">
-        <v>1854.34</v>
+        <v>1890.96</v>
       </c>
       <c r="E42" t="n">
-        <v>1906.53</v>
+        <v>1902.06</v>
       </c>
       <c r="F42" t="n">
-        <v>38.14</v>
+        <v>-4.47</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0204</v>
+        <v>-0.0023</v>
       </c>
       <c r="H42" t="n">
-        <v>68.3</v>
+        <v>26.74</v>
       </c>
       <c r="I42" t="n">
-        <v>1814.81</v>
+        <v>1786.04</v>
       </c>
       <c r="J42" t="n">
-        <v>1838.54</v>
+        <v>1847.24</v>
       </c>
       <c r="K42" t="n">
-        <v>1852.2</v>
+        <v>1872.38</v>
       </c>
       <c r="L42" t="n">
-        <v>1865.87</v>
+        <v>1897.51</v>
       </c>
       <c r="M42" t="n">
-        <v>1884.57</v>
+        <v>1940.68</v>
       </c>
       <c r="N42" t="n">
-        <v>1903.26</v>
+        <v>1983.84</v>
       </c>
       <c r="O42" t="n">
-        <v>1911.9</v>
+        <v>1990.94</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4000,80 +4002,78 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1906.44</v>
+        <v>1902.14</v>
       </c>
       <c r="C43" t="n">
-        <v>1917.7</v>
+        <v>1937.17</v>
       </c>
       <c r="D43" t="n">
-        <v>1890.96</v>
+        <v>1893.08</v>
       </c>
       <c r="E43" t="n">
-        <v>1902.06</v>
+        <v>1913.28</v>
       </c>
       <c r="F43" t="n">
-        <v>-4.47</v>
+        <v>11.22</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0059</v>
       </c>
       <c r="H43" t="n">
-        <v>26.74</v>
+        <v>44.08</v>
       </c>
       <c r="I43" t="n">
-        <v>1786.04</v>
+        <v>1864.23</v>
       </c>
       <c r="J43" t="n">
-        <v>1847.24</v>
+        <v>1874.18</v>
       </c>
       <c r="K43" t="n">
-        <v>1872.38</v>
+        <v>1888.69</v>
       </c>
       <c r="L43" t="n">
-        <v>1897.51</v>
+        <v>1903.19</v>
       </c>
       <c r="M43" t="n">
-        <v>1940.68</v>
+        <v>1915.43</v>
       </c>
       <c r="N43" t="n">
-        <v>1983.84</v>
+        <v>1927.66</v>
       </c>
       <c r="O43" t="n">
-        <v>1990.94</v>
+        <v>1944.44</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4084,16 +4084,20 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4103,59 +4107,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1902.14</v>
+        <v>1913.32</v>
       </c>
       <c r="C44" t="n">
-        <v>1937.17</v>
+        <v>1924.62</v>
       </c>
       <c r="D44" t="n">
-        <v>1893.08</v>
+        <v>1911.48</v>
       </c>
       <c r="E44" t="n">
-        <v>1913.28</v>
+        <v>1915.53</v>
       </c>
       <c r="F44" t="n">
-        <v>11.22</v>
+        <v>2.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0012</v>
       </c>
       <c r="H44" t="n">
-        <v>44.08</v>
+        <v>13.13</v>
       </c>
       <c r="I44" t="n">
-        <v>1864.23</v>
+        <v>1849</v>
       </c>
       <c r="J44" t="n">
-        <v>1874.18</v>
+        <v>1868.27</v>
       </c>
       <c r="K44" t="n">
-        <v>1888.69</v>
+        <v>1891.24</v>
       </c>
       <c r="L44" t="n">
-        <v>1903.19</v>
+        <v>1914.2</v>
       </c>
       <c r="M44" t="n">
-        <v>1915.43</v>
+        <v>1935.32</v>
       </c>
       <c r="N44" t="n">
-        <v>1927.66</v>
+        <v>1956.44</v>
       </c>
       <c r="O44" t="n">
-        <v>1944.44</v>
+        <v>1981.25</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4166,20 +4166,16 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4189,55 +4185,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1913.32</v>
+        <v>1915.46</v>
       </c>
       <c r="C45" t="n">
-        <v>1924.62</v>
+        <v>1935.53</v>
       </c>
       <c r="D45" t="n">
-        <v>1911.48</v>
+        <v>1907.03</v>
       </c>
       <c r="E45" t="n">
-        <v>1915.53</v>
+        <v>1908.68</v>
       </c>
       <c r="F45" t="n">
-        <v>2.25</v>
+        <v>-6.85</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0036</v>
       </c>
       <c r="H45" t="n">
-        <v>13.13</v>
+        <v>28.5</v>
       </c>
       <c r="I45" t="n">
-        <v>1849</v>
+        <v>1898.35</v>
       </c>
       <c r="J45" t="n">
-        <v>1868.27</v>
+        <v>1901.14</v>
       </c>
       <c r="K45" t="n">
-        <v>1891.24</v>
+        <v>1908.97</v>
       </c>
       <c r="L45" t="n">
-        <v>1914.2</v>
+        <v>1916.79</v>
       </c>
       <c r="M45" t="n">
-        <v>1935.32</v>
+        <v>1922.1</v>
       </c>
       <c r="N45" t="n">
-        <v>1956.44</v>
+        <v>1927.4</v>
       </c>
       <c r="O45" t="n">
-        <v>1981.25</v>
+        <v>1937.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4245,19 +4245,25 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4269,70 +4275,74 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1915.46</v>
+        <v>1908.72</v>
       </c>
       <c r="C46" t="n">
-        <v>1935.53</v>
+        <v>1928.99</v>
       </c>
       <c r="D46" t="n">
-        <v>1907.03</v>
+        <v>1866.79</v>
       </c>
       <c r="E46" t="n">
-        <v>1908.68</v>
+        <v>1871.28</v>
       </c>
       <c r="F46" t="n">
-        <v>-6.85</v>
+        <v>-37.4</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0196</v>
       </c>
       <c r="H46" t="n">
-        <v>28.5</v>
+        <v>62.2</v>
       </c>
       <c r="I46" t="n">
-        <v>1898.35</v>
+        <v>1878.52</v>
       </c>
       <c r="J46" t="n">
-        <v>1901.14</v>
+        <v>1873.88</v>
       </c>
       <c r="K46" t="n">
-        <v>1908.97</v>
+        <v>1894.43</v>
       </c>
       <c r="L46" t="n">
-        <v>1916.79</v>
+        <v>1914.98</v>
       </c>
       <c r="M46" t="n">
-        <v>1922.1</v>
+        <v>1922.93</v>
       </c>
       <c r="N46" t="n">
-        <v>1927.4</v>
+        <v>1930.89</v>
       </c>
       <c r="O46" t="n">
-        <v>1937.75</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>1964.03</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4342,97 +4352,83 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1908.72</v>
+        <v>1871.26</v>
       </c>
       <c r="C47" t="n">
-        <v>1928.99</v>
+        <v>1895.75</v>
       </c>
       <c r="D47" t="n">
-        <v>1866.79</v>
+        <v>1852.84</v>
       </c>
       <c r="E47" t="n">
-        <v>1871.28</v>
+        <v>1881.37</v>
       </c>
       <c r="F47" t="n">
-        <v>-37.4</v>
+        <v>10.09</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0196</v>
+        <v>0.0054</v>
       </c>
       <c r="H47" t="n">
-        <v>62.2</v>
+        <v>42.91</v>
       </c>
       <c r="I47" t="n">
-        <v>1878.52</v>
+        <v>1804.59</v>
       </c>
       <c r="J47" t="n">
-        <v>1873.88</v>
+        <v>1795.77</v>
       </c>
       <c r="K47" t="n">
-        <v>1894.43</v>
+        <v>1840.18</v>
       </c>
       <c r="L47" t="n">
-        <v>1914.98</v>
+        <v>1884.59</v>
       </c>
       <c r="M47" t="n">
-        <v>1922.93</v>
+        <v>1902.38</v>
       </c>
       <c r="N47" t="n">
-        <v>1930.89</v>
+        <v>1920.18</v>
       </c>
       <c r="O47" t="n">
-        <v>1964.03</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>1991.2</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4445,55 +4441,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1871.26</v>
+        <v>1881.37</v>
       </c>
       <c r="C48" t="n">
-        <v>1895.75</v>
+        <v>1921.78</v>
       </c>
       <c r="D48" t="n">
-        <v>1852.84</v>
+        <v>1873.35</v>
       </c>
       <c r="E48" t="n">
-        <v>1881.37</v>
+        <v>1878.14</v>
       </c>
       <c r="F48" t="n">
-        <v>10.09</v>
+        <v>-3.24</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0017</v>
       </c>
       <c r="H48" t="n">
-        <v>42.91</v>
+        <v>48.43</v>
       </c>
       <c r="I48" t="n">
-        <v>1804.59</v>
+        <v>1809.93</v>
       </c>
       <c r="J48" t="n">
-        <v>1795.77</v>
+        <v>1842</v>
       </c>
       <c r="K48" t="n">
-        <v>1840.18</v>
+        <v>1859.92</v>
       </c>
       <c r="L48" t="n">
-        <v>1884.59</v>
+        <v>1877.83</v>
       </c>
       <c r="M48" t="n">
-        <v>1902.38</v>
+        <v>1902.83</v>
       </c>
       <c r="N48" t="n">
-        <v>1920.18</v>
+        <v>1927.82</v>
       </c>
       <c r="O48" t="n">
-        <v>1991.2</v>
+        <v>1938.66</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4506,11 +4506,13 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4525,57 +4527,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1881.37</v>
+        <v>1878.19</v>
       </c>
       <c r="C49" t="n">
-        <v>1921.78</v>
+        <v>1898.23</v>
       </c>
       <c r="D49" t="n">
-        <v>1873.35</v>
+        <v>1861.92</v>
       </c>
       <c r="E49" t="n">
-        <v>1878.14</v>
+        <v>1883.99</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.24</v>
+        <v>5.86</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0017</v>
+        <v>0.0031</v>
       </c>
       <c r="H49" t="n">
-        <v>48.43</v>
+        <v>36.3</v>
       </c>
       <c r="I49" t="n">
-        <v>1809.93</v>
+        <v>1824.92</v>
       </c>
       <c r="J49" t="n">
-        <v>1842</v>
+        <v>1819.99</v>
       </c>
       <c r="K49" t="n">
-        <v>1859.92</v>
+        <v>1853.92</v>
       </c>
       <c r="L49" t="n">
-        <v>1877.83</v>
+        <v>1887.85</v>
       </c>
       <c r="M49" t="n">
-        <v>1902.83</v>
+        <v>1902.35</v>
       </c>
       <c r="N49" t="n">
-        <v>1927.82</v>
+        <v>1916.85</v>
       </c>
       <c r="O49" t="n">
-        <v>1938.66</v>
+        <v>1970.2</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4588,13 +4590,11 @@
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4609,57 +4609,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1878.19</v>
+        <v>1884.02</v>
       </c>
       <c r="C50" t="n">
-        <v>1898.23</v>
+        <v>1889.27</v>
       </c>
       <c r="D50" t="n">
-        <v>1861.92</v>
+        <v>1862.56</v>
       </c>
       <c r="E50" t="n">
-        <v>1883.99</v>
+        <v>1880.65</v>
       </c>
       <c r="F50" t="n">
-        <v>5.86</v>
+        <v>-3.34</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0031</v>
+        <v>-0.0018</v>
       </c>
       <c r="H50" t="n">
-        <v>36.3</v>
+        <v>26.71</v>
       </c>
       <c r="I50" t="n">
-        <v>1824.92</v>
+        <v>1825.62</v>
       </c>
       <c r="J50" t="n">
-        <v>1819.99</v>
+        <v>1849.65</v>
       </c>
       <c r="K50" t="n">
-        <v>1853.92</v>
+        <v>1865.84</v>
       </c>
       <c r="L50" t="n">
-        <v>1887.85</v>
+        <v>1882.03</v>
       </c>
       <c r="M50" t="n">
-        <v>1902.35</v>
+        <v>1902.14</v>
       </c>
       <c r="N50" t="n">
-        <v>1916.85</v>
+        <v>1922.26</v>
       </c>
       <c r="O50" t="n">
-        <v>1970.2</v>
+        <v>1934.53</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4667,10 +4667,12 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4698,50 +4700,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1884.02</v>
+        <v>1880.61</v>
       </c>
       <c r="C51" t="n">
-        <v>1889.27</v>
+        <v>1884.72</v>
       </c>
       <c r="D51" t="n">
-        <v>1862.56</v>
+        <v>1874.33</v>
       </c>
       <c r="E51" t="n">
-        <v>1880.65</v>
+        <v>1880.91</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.34</v>
+        <v>0.26</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0018</v>
+        <v>0.0001</v>
       </c>
       <c r="H51" t="n">
-        <v>26.71</v>
+        <v>10.39</v>
       </c>
       <c r="I51" t="n">
-        <v>1825.62</v>
+        <v>1835.86</v>
       </c>
       <c r="J51" t="n">
-        <v>1849.65</v>
+        <v>1856.31</v>
       </c>
       <c r="K51" t="n">
-        <v>1865.84</v>
+        <v>1867.3</v>
       </c>
       <c r="L51" t="n">
-        <v>1882.03</v>
+        <v>1878.28</v>
       </c>
       <c r="M51" t="n">
-        <v>1902.14</v>
+        <v>1894</v>
       </c>
       <c r="N51" t="n">
-        <v>1922.26</v>
+        <v>1909.72</v>
       </c>
       <c r="O51" t="n">
-        <v>1934.53</v>
+        <v>1915.98</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4749,14 +4751,12 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4775,74 +4775,80 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1880.61</v>
+        <v>1880.89</v>
       </c>
       <c r="C52" t="n">
-        <v>1884.72</v>
+        <v>1889.61</v>
       </c>
       <c r="D52" t="n">
-        <v>1874.33</v>
+        <v>1867.89</v>
       </c>
       <c r="E52" t="n">
-        <v>1880.91</v>
+        <v>1873.94</v>
       </c>
       <c r="F52" t="n">
-        <v>0.26</v>
+        <v>-6.97</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0037</v>
       </c>
       <c r="H52" t="n">
-        <v>10.39</v>
+        <v>21.71</v>
       </c>
       <c r="I52" t="n">
-        <v>1835.86</v>
+        <v>1863.94</v>
       </c>
       <c r="J52" t="n">
-        <v>1856.31</v>
+        <v>1871.21</v>
       </c>
       <c r="K52" t="n">
-        <v>1867.3</v>
+        <v>1875.71</v>
       </c>
       <c r="L52" t="n">
-        <v>1878.28</v>
+        <v>1880.22</v>
       </c>
       <c r="M52" t="n">
-        <v>1894</v>
+        <v>1886.1</v>
       </c>
       <c r="N52" t="n">
-        <v>1909.72</v>
+        <v>1891.99</v>
       </c>
       <c r="O52" t="n">
-        <v>1915.98</v>
+        <v>1895.11</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4857,145 +4863,141 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1880.89</v>
+        <v>1873.97</v>
       </c>
       <c r="C53" t="n">
-        <v>1889.61</v>
+        <v>1916.66</v>
       </c>
       <c r="D53" t="n">
-        <v>1867.89</v>
+        <v>1870.75</v>
       </c>
       <c r="E53" t="n">
-        <v>1873.94</v>
+        <v>1912.2</v>
       </c>
       <c r="F53" t="n">
-        <v>-6.97</v>
+        <v>38.26</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0204</v>
       </c>
       <c r="H53" t="n">
-        <v>21.71</v>
+        <v>45.91</v>
       </c>
       <c r="I53" t="n">
-        <v>1863.94</v>
+        <v>1846.18</v>
       </c>
       <c r="J53" t="n">
-        <v>1871.21</v>
+        <v>1849.83</v>
       </c>
       <c r="K53" t="n">
-        <v>1875.71</v>
+        <v>1863.09</v>
       </c>
       <c r="L53" t="n">
-        <v>1880.22</v>
+        <v>1876.35</v>
       </c>
       <c r="M53" t="n">
-        <v>1886.1</v>
+        <v>1884.8</v>
       </c>
       <c r="N53" t="n">
-        <v>1891.99</v>
+        <v>1893.25</v>
       </c>
       <c r="O53" t="n">
-        <v>1895.11</v>
+        <v>1911.32</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1873.97</v>
+        <v>1912.21</v>
       </c>
       <c r="C54" t="n">
-        <v>1916.66</v>
+        <v>1920.52</v>
       </c>
       <c r="D54" t="n">
-        <v>1870.75</v>
+        <v>1884.48</v>
       </c>
       <c r="E54" t="n">
-        <v>1912.2</v>
+        <v>1916.46</v>
       </c>
       <c r="F54" t="n">
-        <v>38.26</v>
+        <v>4.26</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0204</v>
+        <v>0.0022</v>
       </c>
       <c r="H54" t="n">
-        <v>45.91</v>
+        <v>36.05</v>
       </c>
       <c r="I54" t="n">
-        <v>1846.18</v>
+        <v>1824.84</v>
       </c>
       <c r="J54" t="n">
-        <v>1849.83</v>
+        <v>1875.54</v>
       </c>
       <c r="K54" t="n">
-        <v>1863.09</v>
+        <v>1889.25</v>
       </c>
       <c r="L54" t="n">
-        <v>1876.35</v>
+        <v>1902.95</v>
       </c>
       <c r="M54" t="n">
-        <v>1884.8</v>
+        <v>1935.16</v>
       </c>
       <c r="N54" t="n">
-        <v>1893.25</v>
+        <v>1967.36</v>
       </c>
       <c r="O54" t="n">
-        <v>1911.32</v>
+        <v>1962.57</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5003,28 +5005,24 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
@@ -5036,50 +5034,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1912.21</v>
+        <v>1916.43</v>
       </c>
       <c r="C55" t="n">
-        <v>1920.52</v>
+        <v>2327.7</v>
       </c>
       <c r="D55" t="n">
-        <v>1884.48</v>
+        <v>1905.08</v>
       </c>
       <c r="E55" t="n">
-        <v>1916.46</v>
+        <v>2251.46</v>
       </c>
       <c r="F55" t="n">
-        <v>4.26</v>
+        <v>335</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0022</v>
+        <v>0.1748</v>
       </c>
       <c r="H55" t="n">
-        <v>36.05</v>
+        <v>422.62</v>
       </c>
       <c r="I55" t="n">
-        <v>1824.84</v>
+        <v>1848.43</v>
       </c>
       <c r="J55" t="n">
-        <v>1875.54</v>
+        <v>1887.39</v>
       </c>
       <c r="K55" t="n">
-        <v>1889.25</v>
+        <v>1898.44</v>
       </c>
       <c r="L55" t="n">
-        <v>1902.95</v>
+        <v>1909.48</v>
       </c>
       <c r="M55" t="n">
-        <v>1935.16</v>
+        <v>1934.48</v>
       </c>
       <c r="N55" t="n">
-        <v>1967.36</v>
+        <v>1959.48</v>
       </c>
       <c r="O55" t="n">
-        <v>1962.57</v>
+        <v>1956.57</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5087,24 +5085,28 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
@@ -5116,50 +5118,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1916.43</v>
+        <v>2251.44</v>
       </c>
       <c r="C56" t="n">
-        <v>2327.7</v>
+        <v>2357.23</v>
       </c>
       <c r="D56" t="n">
-        <v>1905.08</v>
+        <v>2222.57</v>
       </c>
       <c r="E56" t="n">
-        <v>2251.46</v>
+        <v>2326.38</v>
       </c>
       <c r="F56" t="n">
-        <v>335</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.1748</v>
+        <v>0.0333</v>
       </c>
       <c r="H56" t="n">
-        <v>422.62</v>
+        <v>134.65</v>
       </c>
       <c r="I56" t="n">
-        <v>1848.43</v>
+        <v>1482.46</v>
       </c>
       <c r="J56" t="n">
-        <v>1887.39</v>
+        <v>1896.37</v>
       </c>
       <c r="K56" t="n">
-        <v>1898.44</v>
+        <v>2040.15</v>
       </c>
       <c r="L56" t="n">
-        <v>1909.48</v>
+        <v>2183.92</v>
       </c>
       <c r="M56" t="n">
-        <v>1934.48</v>
+        <v>2462.77</v>
       </c>
       <c r="N56" t="n">
-        <v>1959.48</v>
+        <v>2741.61</v>
       </c>
       <c r="O56" t="n">
-        <v>1956.57</v>
+        <v>2750.32</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5170,25 +5172,21 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
@@ -5200,50 +5198,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2251.44</v>
+        <v>2326.38</v>
       </c>
       <c r="C57" t="n">
-        <v>2357.23</v>
+        <v>2545.88</v>
       </c>
       <c r="D57" t="n">
-        <v>2222.57</v>
+        <v>2324.71</v>
       </c>
       <c r="E57" t="n">
-        <v>2326.38</v>
+        <v>2515.28</v>
       </c>
       <c r="F57" t="n">
-        <v>74.93000000000001</v>
+        <v>188.9</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0333</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>134.65</v>
+        <v>221.17</v>
       </c>
       <c r="I57" t="n">
-        <v>1482.46</v>
+        <v>2087.92</v>
       </c>
       <c r="J57" t="n">
-        <v>1896.37</v>
+        <v>2209.97</v>
       </c>
       <c r="K57" t="n">
-        <v>2040.15</v>
+        <v>2259.06</v>
       </c>
       <c r="L57" t="n">
-        <v>2183.92</v>
+        <v>2308.14</v>
       </c>
       <c r="M57" t="n">
-        <v>2462.77</v>
+        <v>2393.71</v>
       </c>
       <c r="N57" t="n">
-        <v>2741.61</v>
+        <v>2479.28</v>
       </c>
       <c r="O57" t="n">
-        <v>2750.32</v>
+        <v>2491.88</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5254,21 +5252,25 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5280,50 +5282,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2326.38</v>
+        <v>2515.39</v>
       </c>
       <c r="C58" t="n">
-        <v>2545.88</v>
+        <v>2528.9</v>
       </c>
       <c r="D58" t="n">
-        <v>2324.71</v>
+        <v>2389.9</v>
       </c>
       <c r="E58" t="n">
-        <v>2515.28</v>
+        <v>2424.25</v>
       </c>
       <c r="F58" t="n">
-        <v>188.9</v>
+        <v>-91.03</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0362</v>
       </c>
       <c r="H58" t="n">
-        <v>221.17</v>
+        <v>138.99</v>
       </c>
       <c r="I58" t="n">
-        <v>2087.92</v>
+        <v>2103.54</v>
       </c>
       <c r="J58" t="n">
-        <v>2209.97</v>
+        <v>2334.1</v>
       </c>
       <c r="K58" t="n">
-        <v>2259.06</v>
+        <v>2404.7</v>
       </c>
       <c r="L58" t="n">
-        <v>2308.14</v>
+        <v>2475.29</v>
       </c>
       <c r="M58" t="n">
-        <v>2393.71</v>
+        <v>2625.87</v>
       </c>
       <c r="N58" t="n">
-        <v>2479.28</v>
+        <v>2776.45</v>
       </c>
       <c r="O58" t="n">
-        <v>2491.88</v>
+        <v>2767.05</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5331,83 +5333,83 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2515.39</v>
+        <v>2424.22</v>
       </c>
       <c r="C59" t="n">
-        <v>2528.9</v>
+        <v>2483.93</v>
       </c>
       <c r="D59" t="n">
-        <v>2389.9</v>
+        <v>2357.14</v>
       </c>
       <c r="E59" t="n">
-        <v>2424.25</v>
+        <v>2463.82</v>
       </c>
       <c r="F59" t="n">
-        <v>-91.03</v>
+        <v>39.56</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0362</v>
+        <v>0.0163</v>
       </c>
       <c r="H59" t="n">
-        <v>138.99</v>
+        <v>126.79</v>
       </c>
       <c r="I59" t="n">
-        <v>2103.54</v>
+        <v>2250.91</v>
       </c>
       <c r="J59" t="n">
-        <v>2334.1</v>
+        <v>2267.68</v>
       </c>
       <c r="K59" t="n">
-        <v>2404.7</v>
+        <v>2354.75</v>
       </c>
       <c r="L59" t="n">
-        <v>2475.29</v>
+        <v>2441.83</v>
       </c>
       <c r="M59" t="n">
-        <v>2625.87</v>
+        <v>2493.75</v>
       </c>
       <c r="N59" t="n">
-        <v>2776.45</v>
+        <v>2545.67</v>
       </c>
       <c r="O59" t="n">
-        <v>2767.05</v>
+        <v>2667.89</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5415,14 +5417,12 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5448,50 +5448,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2424.22</v>
+        <v>2463.64</v>
       </c>
       <c r="C60" t="n">
-        <v>2483.93</v>
+        <v>2531.74</v>
       </c>
       <c r="D60" t="n">
-        <v>2357.14</v>
+        <v>2425.39</v>
       </c>
       <c r="E60" t="n">
-        <v>2463.82</v>
+        <v>2481.83</v>
       </c>
       <c r="F60" t="n">
-        <v>39.56</v>
+        <v>18.02</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0163</v>
+        <v>0.0073</v>
       </c>
       <c r="H60" t="n">
-        <v>126.79</v>
+        <v>106.36</v>
       </c>
       <c r="I60" t="n">
-        <v>2250.91</v>
+        <v>2230.35</v>
       </c>
       <c r="J60" t="n">
-        <v>2267.68</v>
+        <v>2358.67</v>
       </c>
       <c r="K60" t="n">
-        <v>2354.75</v>
+        <v>2400.42</v>
       </c>
       <c r="L60" t="n">
-        <v>2441.83</v>
+        <v>2442.18</v>
       </c>
       <c r="M60" t="n">
-        <v>2493.75</v>
+        <v>2527.21</v>
       </c>
       <c r="N60" t="n">
-        <v>2545.67</v>
+        <v>2612.25</v>
       </c>
       <c r="O60" t="n">
-        <v>2667.89</v>
+        <v>2610.72</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5502,13 +5502,15 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5521,59 +5523,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2463.64</v>
+        <v>2481.78</v>
       </c>
       <c r="C61" t="n">
-        <v>2531.74</v>
+        <v>2531.08</v>
       </c>
       <c r="D61" t="n">
-        <v>2425.39</v>
+        <v>2416.6</v>
       </c>
       <c r="E61" t="n">
-        <v>2481.83</v>
+        <v>2443.16</v>
       </c>
       <c r="F61" t="n">
-        <v>18.02</v>
+        <v>-38.67</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0073</v>
+        <v>-0.0156</v>
       </c>
       <c r="H61" t="n">
-        <v>106.36</v>
+        <v>114.48</v>
       </c>
       <c r="I61" t="n">
-        <v>2230.35</v>
+        <v>2319.03</v>
       </c>
       <c r="J61" t="n">
-        <v>2358.67</v>
+        <v>2377.11</v>
       </c>
       <c r="K61" t="n">
-        <v>2400.42</v>
+        <v>2428.65</v>
       </c>
       <c r="L61" t="n">
-        <v>2442.18</v>
+        <v>2480.2</v>
       </c>
       <c r="M61" t="n">
-        <v>2527.21</v>
+        <v>2535.01</v>
       </c>
       <c r="N61" t="n">
-        <v>2612.25</v>
+        <v>2589.82</v>
       </c>
       <c r="O61" t="n">
-        <v>2610.72</v>
+        <v>2638.1</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5581,18 +5579,18 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5605,55 +5603,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2481.78</v>
+        <v>2442.49</v>
       </c>
       <c r="C62" t="n">
-        <v>2531.08</v>
+        <v>2514.67</v>
       </c>
       <c r="D62" t="n">
-        <v>2416.6</v>
+        <v>2432.51</v>
       </c>
       <c r="E62" t="n">
-        <v>2443.16</v>
+        <v>2506.26</v>
       </c>
       <c r="F62" t="n">
-        <v>-38.67</v>
+        <v>63.1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0156</v>
+        <v>0.0258</v>
       </c>
       <c r="H62" t="n">
-        <v>114.48</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="I62" t="n">
-        <v>2319.03</v>
+        <v>2302.12</v>
       </c>
       <c r="J62" t="n">
-        <v>2377.11</v>
+        <v>2313.34</v>
       </c>
       <c r="K62" t="n">
-        <v>2428.65</v>
+        <v>2385.92</v>
       </c>
       <c r="L62" t="n">
-        <v>2480.2</v>
+        <v>2458.5</v>
       </c>
       <c r="M62" t="n">
-        <v>2535.01</v>
+        <v>2500.4</v>
       </c>
       <c r="N62" t="n">
-        <v>2589.82</v>
+        <v>2542.3</v>
       </c>
       <c r="O62" t="n">
-        <v>2638.1</v>
+        <v>2645.57</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5661,19 +5663,19 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
@@ -5687,57 +5689,57 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2442.49</v>
+        <v>2506.24</v>
       </c>
       <c r="C63" t="n">
-        <v>2514.67</v>
+        <v>2564.27</v>
       </c>
       <c r="D63" t="n">
-        <v>2432.51</v>
+        <v>2481.94</v>
       </c>
       <c r="E63" t="n">
-        <v>2506.26</v>
+        <v>2510.41</v>
       </c>
       <c r="F63" t="n">
-        <v>63.1</v>
+        <v>4.15</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0258</v>
+        <v>0.0017</v>
       </c>
       <c r="H63" t="n">
-        <v>82.15000000000001</v>
+        <v>82.33</v>
       </c>
       <c r="I63" t="n">
-        <v>2302.12</v>
+        <v>2350.36</v>
       </c>
       <c r="J63" t="n">
-        <v>2313.34</v>
+        <v>2440.44</v>
       </c>
       <c r="K63" t="n">
-        <v>2385.92</v>
+        <v>2465.18</v>
       </c>
       <c r="L63" t="n">
-        <v>2458.5</v>
+        <v>2489.93</v>
       </c>
       <c r="M63" t="n">
-        <v>2500.4</v>
+        <v>2547.34</v>
       </c>
       <c r="N63" t="n">
-        <v>2542.3</v>
+        <v>2604.75</v>
       </c>
       <c r="O63" t="n">
-        <v>2645.57</v>
+        <v>2596.82</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5748,14 +5750,14 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U63" s="8" t="n">
@@ -5769,78 +5771,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2506.24</v>
+        <v>2510.67</v>
       </c>
       <c r="C64" t="n">
-        <v>2564.27</v>
+        <v>2534.01</v>
       </c>
       <c r="D64" t="n">
-        <v>2481.94</v>
+        <v>2408.72</v>
       </c>
       <c r="E64" t="n">
-        <v>2510.41</v>
+        <v>2442.54</v>
       </c>
       <c r="F64" t="n">
-        <v>4.15</v>
+        <v>-67.87</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.027</v>
       </c>
       <c r="H64" t="n">
-        <v>82.33</v>
+        <v>125.29</v>
       </c>
       <c r="I64" t="n">
-        <v>2350.36</v>
+        <v>2399.62</v>
       </c>
       <c r="J64" t="n">
-        <v>2440.44</v>
+        <v>2421.73</v>
       </c>
       <c r="K64" t="n">
-        <v>2465.18</v>
+        <v>2469.25</v>
       </c>
       <c r="L64" t="n">
-        <v>2489.93</v>
+        <v>2516.76</v>
       </c>
       <c r="M64" t="n">
-        <v>2547.34</v>
+        <v>2551.57</v>
       </c>
       <c r="N64" t="n">
-        <v>2604.75</v>
+        <v>2586.39</v>
       </c>
       <c r="O64" t="n">
-        <v>2596.82</v>
+        <v>2646.6</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S64" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5853,72 +5853,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2510.67</v>
+        <v>2442.56</v>
       </c>
       <c r="C65" t="n">
-        <v>2534.01</v>
+        <v>2459.63</v>
       </c>
       <c r="D65" t="n">
-        <v>2408.72</v>
+        <v>2430.81</v>
       </c>
       <c r="E65" t="n">
-        <v>2442.54</v>
+        <v>2457.69</v>
       </c>
       <c r="F65" t="n">
-        <v>-67.87</v>
+        <v>15.15</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.027</v>
+        <v>0.0062</v>
       </c>
       <c r="H65" t="n">
-        <v>125.29</v>
+        <v>28.82</v>
       </c>
       <c r="I65" t="n">
-        <v>2399.62</v>
+        <v>2283.43</v>
       </c>
       <c r="J65" t="n">
-        <v>2421.73</v>
+        <v>2302.83</v>
       </c>
       <c r="K65" t="n">
-        <v>2469.25</v>
+        <v>2379.89</v>
       </c>
       <c r="L65" t="n">
-        <v>2516.76</v>
+        <v>2456.95</v>
       </c>
       <c r="M65" t="n">
-        <v>2551.57</v>
+        <v>2505.18</v>
       </c>
       <c r="N65" t="n">
-        <v>2586.39</v>
+        <v>2553.41</v>
       </c>
       <c r="O65" t="n">
-        <v>2646.6</v>
+        <v>2659.3</v>
       </c>
       <c r="P65" s="6" t="n">
         <v/>
       </c>
-      <c r="Q65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v/>
       </c>
       <c r="S65" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T65" s="8" t="n">
@@ -5937,84 +5937,96 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2442.56</v>
+        <v>2457.69</v>
       </c>
       <c r="C66" t="n">
-        <v>2459.63</v>
+        <v>2532.96</v>
       </c>
       <c r="D66" t="n">
-        <v>2430.81</v>
+        <v>2389.47</v>
       </c>
       <c r="E66" t="n">
-        <v>2457.69</v>
+        <v>2417.94</v>
       </c>
       <c r="F66" t="n">
-        <v>15.15</v>
+        <v>-39.75</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0062</v>
+        <v>-0.0162</v>
       </c>
       <c r="H66" t="n">
-        <v>28.82</v>
+        <v>143.49</v>
       </c>
       <c r="I66" t="n">
-        <v>2283.43</v>
+        <v>2401.99</v>
       </c>
       <c r="J66" t="n">
-        <v>2302.83</v>
+        <v>2435.1</v>
       </c>
       <c r="K66" t="n">
-        <v>2379.89</v>
+        <v>2443.28</v>
       </c>
       <c r="L66" t="n">
-        <v>2456.95</v>
+        <v>2451.45</v>
       </c>
       <c r="M66" t="n">
-        <v>2505.18</v>
+        <v>2472.1</v>
       </c>
       <c r="N66" t="n">
-        <v>2553.41</v>
+        <v>2492.74</v>
       </c>
       <c r="O66" t="n">
-        <v>2659.3</v>
-      </c>
-      <c r="P66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q66" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R66" s="6" t="n">
-        <v/>
+        <v>2488.45</v>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S66" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T66" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U66" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V66" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W66" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V66" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W66" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -6026,85 +6038,75 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2457.69</v>
+        <v>2417.9</v>
       </c>
       <c r="C67" t="n">
-        <v>2532.96</v>
+        <v>2488.92</v>
       </c>
       <c r="D67" t="n">
-        <v>2389.47</v>
+        <v>2401.81</v>
       </c>
       <c r="E67" t="n">
-        <v>2417.94</v>
+        <v>2466.82</v>
       </c>
       <c r="F67" t="n">
-        <v>-39.75</v>
+        <v>48.88</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.0202</v>
       </c>
       <c r="H67" t="n">
-        <v>143.49</v>
+        <v>87.11</v>
       </c>
       <c r="I67" t="n">
-        <v>2401.99</v>
+        <v>2245.98</v>
       </c>
       <c r="J67" t="n">
-        <v>2435.1</v>
+        <v>2252.81</v>
       </c>
       <c r="K67" t="n">
-        <v>2443.28</v>
+        <v>2346.19</v>
       </c>
       <c r="L67" t="n">
-        <v>2451.45</v>
+        <v>2439.58</v>
       </c>
       <c r="M67" t="n">
-        <v>2472.1</v>
+        <v>2489.68</v>
       </c>
       <c r="N67" t="n">
-        <v>2492.74</v>
+        <v>2539.79</v>
       </c>
       <c r="O67" t="n">
-        <v>2488.45</v>
-      </c>
-      <c r="P67" s="6" t="inlineStr">
+        <v>2676.45</v>
+      </c>
+      <c r="P67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R67" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S67" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T67" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q67" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R67" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S67" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U67" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V67" s="8" t="n">
+        <v/>
       </c>
       <c r="W67" s="11" t="inlineStr">
         <is>
@@ -6113,76 +6115,78 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2417.9</v>
+        <v>2466.58</v>
       </c>
       <c r="C68" t="n">
-        <v>2488.92</v>
+        <v>2484.4</v>
       </c>
       <c r="D68" t="n">
-        <v>2401.81</v>
+        <v>2383.8</v>
       </c>
       <c r="E68" t="n">
-        <v>2466.82</v>
+        <v>2417.84</v>
       </c>
       <c r="F68" t="n">
-        <v>48.88</v>
+        <v>-48.98</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.0202</v>
+        <v>-0.0199</v>
       </c>
       <c r="H68" t="n">
-        <v>87.11</v>
+        <v>100.6</v>
       </c>
       <c r="I68" t="n">
-        <v>2245.98</v>
+        <v>2314.69</v>
       </c>
       <c r="J68" t="n">
-        <v>2252.81</v>
+        <v>2390.43</v>
       </c>
       <c r="K68" t="n">
-        <v>2346.19</v>
+        <v>2423.26</v>
       </c>
       <c r="L68" t="n">
-        <v>2439.58</v>
+        <v>2456.09</v>
       </c>
       <c r="M68" t="n">
-        <v>2489.68</v>
+        <v>2510.38</v>
       </c>
       <c r="N68" t="n">
-        <v>2539.79</v>
+        <v>2564.66</v>
       </c>
       <c r="O68" t="n">
-        <v>2676.45</v>
+        <v>2576.04</v>
       </c>
       <c r="P68" s="6" t="n">
         <v/>
       </c>
-      <c r="Q68" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R68" s="6" t="n">
-        <v/>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S68" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T68" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T68" s="8" t="n">
+        <v/>
       </c>
       <c r="U68" s="8" t="n">
         <v/>
@@ -6195,74 +6199,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2466.58</v>
+        <v>2417.83</v>
       </c>
       <c r="C69" t="n">
-        <v>2484.4</v>
+        <v>2427.4</v>
       </c>
       <c r="D69" t="n">
-        <v>2383.8</v>
+        <v>2356.19</v>
       </c>
       <c r="E69" t="n">
-        <v>2417.84</v>
+        <v>2391.5</v>
       </c>
       <c r="F69" t="n">
-        <v>-48.98</v>
+        <v>-26.34</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.0109</v>
       </c>
       <c r="H69" t="n">
-        <v>100.6</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>2314.69</v>
+        <v>2283.21</v>
       </c>
       <c r="J69" t="n">
-        <v>2390.43</v>
+        <v>2309.12</v>
       </c>
       <c r="K69" t="n">
-        <v>2423.26</v>
+        <v>2367.54</v>
       </c>
       <c r="L69" t="n">
-        <v>2456.09</v>
+        <v>2425.97</v>
       </c>
       <c r="M69" t="n">
-        <v>2510.38</v>
+        <v>2468.14</v>
       </c>
       <c r="N69" t="n">
-        <v>2564.66</v>
+        <v>2510.31</v>
       </c>
       <c r="O69" t="n">
-        <v>2576.04</v>
+        <v>2584.99</v>
       </c>
       <c r="P69" s="6" t="n">
         <v/>
       </c>
-      <c r="Q69" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q69" s="6" t="n">
+        <v/>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S69" s="7" t="inlineStr">
+      <c r="S69" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -6286,50 +6284,50 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2417.83</v>
+        <v>2391.6</v>
       </c>
       <c r="C70" t="n">
-        <v>2427.4</v>
+        <v>2526.95</v>
       </c>
       <c r="D70" t="n">
-        <v>2356.19</v>
+        <v>2370.42</v>
       </c>
       <c r="E70" t="n">
-        <v>2391.5</v>
+        <v>2508.02</v>
       </c>
       <c r="F70" t="n">
-        <v>-26.34</v>
+        <v>116.52</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-0.0109</v>
+        <v>0.0487</v>
       </c>
       <c r="H70" t="n">
-        <v>71.20999999999999</v>
+        <v>156.53</v>
       </c>
       <c r="I70" t="n">
-        <v>2283.21</v>
+        <v>2284.97</v>
       </c>
       <c r="J70" t="n">
-        <v>2309.12</v>
+        <v>2320.14</v>
       </c>
       <c r="K70" t="n">
-        <v>2367.54</v>
+        <v>2355.89</v>
       </c>
       <c r="L70" t="n">
-        <v>2425.97</v>
+        <v>2391.65</v>
       </c>
       <c r="M70" t="n">
-        <v>2468.14</v>
+        <v>2427.11</v>
       </c>
       <c r="N70" t="n">
-        <v>2510.31</v>
+        <v>2462.57</v>
       </c>
       <c r="O70" t="n">
-        <v>2584.99</v>
+        <v>2498.61</v>
       </c>
       <c r="P70" s="6" t="n">
         <v/>
@@ -6337,28 +6335,32 @@
       <c r="Q70" s="6" t="n">
         <v/>
       </c>
-      <c r="R70" s="6" t="inlineStr">
+      <c r="R70" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V70" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S70" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T70" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U70" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V70" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W70" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W70" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X70" t="inlineStr"/>
@@ -6366,50 +6368,50 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2391.6</v>
+        <v>2508.02</v>
       </c>
       <c r="C71" t="n">
-        <v>2526.95</v>
+        <v>2545.62</v>
       </c>
       <c r="D71" t="n">
-        <v>2370.42</v>
+        <v>2432.35</v>
       </c>
       <c r="E71" t="n">
-        <v>2508.02</v>
+        <v>2456.08</v>
       </c>
       <c r="F71" t="n">
-        <v>116.52</v>
+        <v>-51.94</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0487</v>
+        <v>-0.0207</v>
       </c>
       <c r="H71" t="n">
-        <v>156.53</v>
+        <v>113.27</v>
       </c>
       <c r="I71" t="n">
-        <v>2284.97</v>
+        <v>2213.88</v>
       </c>
       <c r="J71" t="n">
-        <v>2320.14</v>
+        <v>2381.16</v>
       </c>
       <c r="K71" t="n">
-        <v>2355.89</v>
+        <v>2429.75</v>
       </c>
       <c r="L71" t="n">
-        <v>2391.65</v>
+        <v>2478.35</v>
       </c>
       <c r="M71" t="n">
-        <v>2427.11</v>
+        <v>2586.29</v>
       </c>
       <c r="N71" t="n">
-        <v>2462.57</v>
+        <v>2694.22</v>
       </c>
       <c r="O71" t="n">
-        <v>2498.61</v>
+        <v>2683.48</v>
       </c>
       <c r="P71" s="6" t="n">
         <v/>
@@ -6422,78 +6424,76 @@
       </c>
       <c r="S71" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T71" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U71" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V71" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T71" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U71" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V71" s="8" t="n">
+        <v/>
       </c>
       <c r="W71" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr"/>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2508.02</v>
+        <v>2455.99</v>
       </c>
       <c r="C72" t="n">
-        <v>2545.62</v>
+        <v>2492.01</v>
       </c>
       <c r="D72" t="n">
-        <v>2432.35</v>
+        <v>2445.69</v>
       </c>
       <c r="E72" t="n">
-        <v>2456.08</v>
+        <v>2480.74</v>
       </c>
       <c r="F72" t="n">
-        <v>-51.94</v>
+        <v>24.66</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.0207</v>
+        <v>0.01</v>
       </c>
       <c r="H72" t="n">
-        <v>113.27</v>
+        <v>46.32</v>
       </c>
       <c r="I72" t="n">
-        <v>2213.88</v>
+        <v>2319.08</v>
       </c>
       <c r="J72" t="n">
-        <v>2381.16</v>
+        <v>2326.35</v>
       </c>
       <c r="K72" t="n">
-        <v>2429.75</v>
+        <v>2399.44</v>
       </c>
       <c r="L72" t="n">
-        <v>2478.35</v>
+        <v>2472.53</v>
       </c>
       <c r="M72" t="n">
-        <v>2586.29</v>
+        <v>2512.71</v>
       </c>
       <c r="N72" t="n">
-        <v>2694.22</v>
+        <v>2552.89</v>
       </c>
       <c r="O72" t="n">
-        <v>2683.48</v>
+        <v>2658.89</v>
       </c>
       <c r="P72" s="6" t="n">
         <v/>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T72" s="8" t="n">
@@ -6532,50 +6532,50 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2455.99</v>
+        <v>2480.82</v>
       </c>
       <c r="C73" t="n">
-        <v>2492.01</v>
+        <v>2525.32</v>
       </c>
       <c r="D73" t="n">
-        <v>2445.69</v>
+        <v>2468.19</v>
       </c>
       <c r="E73" t="n">
-        <v>2480.74</v>
+        <v>2514.55</v>
       </c>
       <c r="F73" t="n">
-        <v>24.66</v>
+        <v>33.81</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0136</v>
       </c>
       <c r="H73" t="n">
-        <v>46.32</v>
+        <v>57.13</v>
       </c>
       <c r="I73" t="n">
-        <v>2319.08</v>
+        <v>2399.37</v>
       </c>
       <c r="J73" t="n">
-        <v>2326.35</v>
+        <v>2440.36</v>
       </c>
       <c r="K73" t="n">
-        <v>2399.44</v>
+        <v>2457.58</v>
       </c>
       <c r="L73" t="n">
-        <v>2472.53</v>
+        <v>2474.79</v>
       </c>
       <c r="M73" t="n">
-        <v>2512.71</v>
+        <v>2503.9</v>
       </c>
       <c r="N73" t="n">
-        <v>2552.89</v>
+        <v>2533</v>
       </c>
       <c r="O73" t="n">
-        <v>2658.89</v>
+        <v>2538.33</v>
       </c>
       <c r="P73" s="6" t="n">
         <v/>
@@ -6586,13 +6586,15 @@
       <c r="R73" s="6" t="n">
         <v/>
       </c>
-      <c r="S73" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T73" s="8" t="n">
-        <v/>
+      <c r="S73" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T73" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U73" s="8" t="n">
         <v/>
@@ -6605,59 +6607,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2480.82</v>
+        <v>2514.58</v>
       </c>
       <c r="C74" t="n">
-        <v>2525.32</v>
+        <v>2534.86</v>
       </c>
       <c r="D74" t="n">
-        <v>2468.19</v>
+        <v>2466.91</v>
       </c>
       <c r="E74" t="n">
-        <v>2514.55</v>
+        <v>2490.96</v>
       </c>
       <c r="F74" t="n">
-        <v>33.81</v>
+        <v>-23.59</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0094</v>
       </c>
       <c r="H74" t="n">
-        <v>57.13</v>
+        <v>67.95</v>
       </c>
       <c r="I74" t="n">
-        <v>2399.37</v>
+        <v>2411.07</v>
       </c>
       <c r="J74" t="n">
-        <v>2440.36</v>
+        <v>2466.32</v>
       </c>
       <c r="K74" t="n">
-        <v>2457.58</v>
+        <v>2485.99</v>
       </c>
       <c r="L74" t="n">
-        <v>2474.79</v>
+        <v>2505.65</v>
       </c>
       <c r="M74" t="n">
-        <v>2503.9</v>
+        <v>2543.11</v>
       </c>
       <c r="N74" t="n">
-        <v>2533</v>
+        <v>2580.57</v>
       </c>
       <c r="O74" t="n">
-        <v>2538.33</v>
+        <v>2582.45</v>
       </c>
       <c r="P74" s="6" t="n">
         <v/>
@@ -6665,18 +6663,18 @@
       <c r="Q74" s="6" t="n">
         <v/>
       </c>
-      <c r="R74" s="6" t="n">
-        <v/>
+      <c r="R74" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S74" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T74" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T74" s="8" t="n">
+        <v/>
       </c>
       <c r="U74" s="8" t="n">
         <v/>
@@ -6689,55 +6687,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr"/>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2514.58</v>
+        <v>2490.92</v>
       </c>
       <c r="C75" t="n">
-        <v>2534.86</v>
+        <v>2506.75</v>
       </c>
       <c r="D75" t="n">
-        <v>2466.91</v>
+        <v>2441.33</v>
       </c>
       <c r="E75" t="n">
-        <v>2490.96</v>
+        <v>2484.94</v>
       </c>
       <c r="F75" t="n">
-        <v>-23.59</v>
+        <v>-6.02</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0024</v>
       </c>
       <c r="H75" t="n">
-        <v>67.95</v>
+        <v>65.42</v>
       </c>
       <c r="I75" t="n">
-        <v>2411.07</v>
+        <v>2398.96</v>
       </c>
       <c r="J75" t="n">
-        <v>2466.32</v>
+        <v>2418.04</v>
       </c>
       <c r="K75" t="n">
-        <v>2485.99</v>
+        <v>2456.98</v>
       </c>
       <c r="L75" t="n">
-        <v>2505.65</v>
+        <v>2495.92</v>
       </c>
       <c r="M75" t="n">
-        <v>2543.11</v>
+        <v>2524.93</v>
       </c>
       <c r="N75" t="n">
-        <v>2580.57</v>
+        <v>2553.94</v>
       </c>
       <c r="O75" t="n">
-        <v>2582.45</v>
+        <v>2602.81</v>
       </c>
       <c r="P75" s="6" t="n">
         <v/>
@@ -6747,12 +6749,12 @@
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S75" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S75" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T75" s="8" t="n">
@@ -6771,57 +6773,57 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2490.92</v>
+        <v>2484.89</v>
       </c>
       <c r="C76" t="n">
-        <v>2506.75</v>
+        <v>2522.37</v>
       </c>
       <c r="D76" t="n">
-        <v>2441.33</v>
+        <v>2443.7</v>
       </c>
       <c r="E76" t="n">
-        <v>2484.94</v>
+        <v>2466.91</v>
       </c>
       <c r="F76" t="n">
-        <v>-6.02</v>
+        <v>-18.03</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0073</v>
       </c>
       <c r="H76" t="n">
-        <v>65.42</v>
+        <v>78.67</v>
       </c>
       <c r="I76" t="n">
-        <v>2398.96</v>
+        <v>2375.9</v>
       </c>
       <c r="J76" t="n">
-        <v>2418.04</v>
+        <v>2424.97</v>
       </c>
       <c r="K76" t="n">
-        <v>2456.98</v>
+        <v>2452.23</v>
       </c>
       <c r="L76" t="n">
-        <v>2495.92</v>
+        <v>2479.49</v>
       </c>
       <c r="M76" t="n">
-        <v>2524.93</v>
+        <v>2517.65</v>
       </c>
       <c r="N76" t="n">
-        <v>2553.94</v>
+        <v>2555.82</v>
       </c>
       <c r="O76" t="n">
-        <v>2602.81</v>
+        <v>2572.18</v>
       </c>
       <c r="P76" s="6" t="n">
         <v/>
@@ -6834,13 +6836,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S76" s="7" t="inlineStr">
+      <c r="S76" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T76" s="8" t="n">
-        <v/>
+      <c r="T76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U76" s="8" t="n">
         <v/>
@@ -6855,57 +6859,57 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2484.89</v>
+        <v>2466.91</v>
       </c>
       <c r="C77" t="n">
-        <v>2522.37</v>
+        <v>2483.72</v>
       </c>
       <c r="D77" t="n">
-        <v>2443.7</v>
+        <v>2406.91</v>
       </c>
       <c r="E77" t="n">
-        <v>2466.91</v>
+        <v>2437.1</v>
       </c>
       <c r="F77" t="n">
-        <v>-18.03</v>
+        <v>-29.82</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.0073</v>
+        <v>-0.0121</v>
       </c>
       <c r="H77" t="n">
-        <v>78.67</v>
+        <v>76.81</v>
       </c>
       <c r="I77" t="n">
-        <v>2375.9</v>
+        <v>2365.04</v>
       </c>
       <c r="J77" t="n">
-        <v>2424.97</v>
+        <v>2380.19</v>
       </c>
       <c r="K77" t="n">
-        <v>2452.23</v>
+        <v>2427.58</v>
       </c>
       <c r="L77" t="n">
-        <v>2479.49</v>
+        <v>2474.97</v>
       </c>
       <c r="M77" t="n">
-        <v>2517.65</v>
+        <v>2506.25</v>
       </c>
       <c r="N77" t="n">
-        <v>2555.82</v>
+        <v>2537.52</v>
       </c>
       <c r="O77" t="n">
-        <v>2572.18</v>
+        <v>2601.04</v>
       </c>
       <c r="P77" s="6" t="n">
         <v/>
@@ -6915,18 +6919,16 @@
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S77" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T77" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S77" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T77" s="8" t="n">
+        <v/>
       </c>
       <c r="U77" s="8" t="n">
         <v/>
@@ -6941,57 +6943,57 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2466.91</v>
+        <v>2437.14</v>
       </c>
       <c r="C78" t="n">
-        <v>2483.72</v>
+        <v>2663.05</v>
       </c>
       <c r="D78" t="n">
-        <v>2406.91</v>
+        <v>2435.29</v>
       </c>
       <c r="E78" t="n">
-        <v>2437.1</v>
+        <v>2514.73</v>
       </c>
       <c r="F78" t="n">
-        <v>-29.82</v>
+        <v>77.64</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-0.0121</v>
+        <v>0.0319</v>
       </c>
       <c r="H78" t="n">
-        <v>76.81</v>
+        <v>227.76</v>
       </c>
       <c r="I78" t="n">
-        <v>2365.04</v>
+        <v>2330.09</v>
       </c>
       <c r="J78" t="n">
-        <v>2380.19</v>
+        <v>2356.18</v>
       </c>
       <c r="K78" t="n">
-        <v>2427.58</v>
+        <v>2398.69</v>
       </c>
       <c r="L78" t="n">
-        <v>2474.97</v>
+        <v>2441.21</v>
       </c>
       <c r="M78" t="n">
-        <v>2506.25</v>
+        <v>2475.51</v>
       </c>
       <c r="N78" t="n">
-        <v>2537.52</v>
+        <v>2509.8</v>
       </c>
       <c r="O78" t="n">
-        <v>2601.04</v>
+        <v>2560.53</v>
       </c>
       <c r="P78" s="6" t="n">
         <v/>
@@ -6999,83 +7001,83 @@
       <c r="Q78" s="6" t="n">
         <v/>
       </c>
-      <c r="R78" s="6" t="inlineStr">
+      <c r="R78" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S78" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U78" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S78" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T78" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U78" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V78" s="8" t="n">
-        <v/>
+      <c r="V78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W78" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2437.14</v>
+        <v>2514.77</v>
       </c>
       <c r="C79" t="n">
-        <v>2663.05</v>
+        <v>2544.47</v>
       </c>
       <c r="D79" t="n">
-        <v>2435.29</v>
+        <v>2508.8</v>
       </c>
       <c r="E79" t="n">
-        <v>2514.73</v>
+        <v>2525.94</v>
       </c>
       <c r="F79" t="n">
-        <v>77.64</v>
+        <v>11.21</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.0319</v>
+        <v>0.0045</v>
       </c>
       <c r="H79" t="n">
-        <v>227.76</v>
+        <v>35.67</v>
       </c>
       <c r="I79" t="n">
-        <v>2330.09</v>
+        <v>2207.52</v>
       </c>
       <c r="J79" t="n">
-        <v>2356.18</v>
+        <v>2269.75</v>
       </c>
       <c r="K79" t="n">
-        <v>2398.69</v>
+        <v>2400.85</v>
       </c>
       <c r="L79" t="n">
-        <v>2441.21</v>
+        <v>2531.95</v>
       </c>
       <c r="M79" t="n">
-        <v>2475.51</v>
+        <v>2628.62</v>
       </c>
       <c r="N79" t="n">
-        <v>2509.8</v>
+        <v>2725.28</v>
       </c>
       <c r="O79" t="n">
-        <v>2560.53</v>
+        <v>2890.82</v>
       </c>
       <c r="P79" s="6" t="n">
         <v/>
@@ -7088,91 +7090,95 @@
       </c>
       <c r="S79" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T79" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U79" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V79" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T79" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U79" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V79" s="8" t="n">
+        <v/>
       </c>
       <c r="W79" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr"/>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2514.77</v>
+        <v>2525.94</v>
       </c>
       <c r="C80" t="n">
-        <v>2544.47</v>
+        <v>2526.85</v>
       </c>
       <c r="D80" t="n">
-        <v>2508.8</v>
+        <v>2462.84</v>
       </c>
       <c r="E80" t="n">
-        <v>2525.94</v>
+        <v>2477.02</v>
       </c>
       <c r="F80" t="n">
-        <v>11.21</v>
+        <v>-48.92</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.0045</v>
+        <v>-0.0194</v>
       </c>
       <c r="H80" t="n">
-        <v>35.67</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>2207.52</v>
+        <v>2473.13</v>
       </c>
       <c r="J80" t="n">
-        <v>2269.75</v>
+        <v>2489.93</v>
       </c>
       <c r="K80" t="n">
-        <v>2400.85</v>
+        <v>2508.11</v>
       </c>
       <c r="L80" t="n">
-        <v>2531.95</v>
+        <v>2526.29</v>
       </c>
       <c r="M80" t="n">
-        <v>2628.62</v>
+        <v>2543.78</v>
       </c>
       <c r="N80" t="n">
-        <v>2725.28</v>
+        <v>2561.27</v>
       </c>
       <c r="O80" t="n">
-        <v>2890.82</v>
-      </c>
-      <c r="P80" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q80" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R80" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S80" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>2580.14</v>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S80" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T80" s="8" t="n">
@@ -7184,148 +7190,148 @@
       <c r="V80" s="8" t="n">
         <v/>
       </c>
-      <c r="W80" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W80" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2525.94</v>
+        <v>2476.6</v>
       </c>
       <c r="C81" t="n">
-        <v>2526.85</v>
+        <v>2612.4</v>
       </c>
       <c r="D81" t="n">
-        <v>2462.84</v>
+        <v>2465.43</v>
       </c>
       <c r="E81" t="n">
-        <v>2477.02</v>
+        <v>2514.41</v>
       </c>
       <c r="F81" t="n">
-        <v>-48.92</v>
+        <v>37.39</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.0194</v>
+        <v>0.0151</v>
       </c>
       <c r="H81" t="n">
-        <v>64.01000000000001</v>
+        <v>146.98</v>
       </c>
       <c r="I81" t="n">
-        <v>2473.13</v>
+        <v>2398.83</v>
       </c>
       <c r="J81" t="n">
-        <v>2489.93</v>
+        <v>2404.09</v>
       </c>
       <c r="K81" t="n">
-        <v>2508.11</v>
+        <v>2445.01</v>
       </c>
       <c r="L81" t="n">
-        <v>2526.29</v>
+        <v>2485.93</v>
       </c>
       <c r="M81" t="n">
-        <v>2543.78</v>
+        <v>2509.03</v>
       </c>
       <c r="N81" t="n">
-        <v>2561.27</v>
+        <v>2532.12</v>
       </c>
       <c r="O81" t="n">
-        <v>2580.14</v>
-      </c>
-      <c r="P81" s="6" t="inlineStr">
+        <v>2590.87</v>
+      </c>
+      <c r="P81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R81" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S81" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T81" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q81" s="6" t="inlineStr">
+      <c r="U81" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R81" s="6" t="inlineStr">
+      <c r="V81" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S81" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T81" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U81" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V81" s="8" t="n">
-        <v/>
-      </c>
       <c r="W81" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr"/>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2476.6</v>
+        <v>2514.36</v>
       </c>
       <c r="C82" t="n">
-        <v>2612.4</v>
+        <v>2519.32</v>
       </c>
       <c r="D82" t="n">
-        <v>2465.43</v>
+        <v>2357.96</v>
       </c>
       <c r="E82" t="n">
-        <v>2514.41</v>
+        <v>2399.09</v>
       </c>
       <c r="F82" t="n">
-        <v>37.39</v>
+        <v>-115.32</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.0151</v>
+        <v>-0.0459</v>
       </c>
       <c r="H82" t="n">
-        <v>146.98</v>
+        <v>161.36</v>
       </c>
       <c r="I82" t="n">
-        <v>2398.83</v>
+        <v>2318.45</v>
       </c>
       <c r="J82" t="n">
-        <v>2404.09</v>
+        <v>2355.18</v>
       </c>
       <c r="K82" t="n">
-        <v>2445.01</v>
+        <v>2440.92</v>
       </c>
       <c r="L82" t="n">
-        <v>2485.93</v>
+        <v>2526.66</v>
       </c>
       <c r="M82" t="n">
-        <v>2509.03</v>
+        <v>2587.9</v>
       </c>
       <c r="N82" t="n">
-        <v>2532.12</v>
+        <v>2649.13</v>
       </c>
       <c r="O82" t="n">
-        <v>2590.87</v>
+        <v>2759.38</v>
       </c>
       <c r="P82" s="6" t="n">
         <v/>
@@ -7333,87 +7339,79 @@
       <c r="Q82" s="6" t="n">
         <v/>
       </c>
-      <c r="R82" s="6" t="n">
-        <v/>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S82" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T82" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T82" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U82" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V82" s="8" t="n">
+        <v/>
       </c>
       <c r="W82" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2514.36</v>
+        <v>2399.06</v>
       </c>
       <c r="C83" t="n">
-        <v>2519.32</v>
+        <v>2426.93</v>
       </c>
       <c r="D83" t="n">
-        <v>2357.96</v>
+        <v>2368.74</v>
       </c>
       <c r="E83" t="n">
-        <v>2399.09</v>
+        <v>2416.12</v>
       </c>
       <c r="F83" t="n">
-        <v>-115.32</v>
+        <v>17.03</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>-0.0459</v>
+        <v>0.0071</v>
       </c>
       <c r="H83" t="n">
-        <v>161.36</v>
+        <v>58.19</v>
       </c>
       <c r="I83" t="n">
-        <v>2318.45</v>
+        <v>2196.6</v>
       </c>
       <c r="J83" t="n">
-        <v>2355.18</v>
+        <v>2217.95</v>
       </c>
       <c r="K83" t="n">
-        <v>2440.92</v>
+        <v>2318.41</v>
       </c>
       <c r="L83" t="n">
-        <v>2526.66</v>
+        <v>2418.86</v>
       </c>
       <c r="M83" t="n">
-        <v>2587.9</v>
+        <v>2479.77</v>
       </c>
       <c r="N83" t="n">
-        <v>2649.13</v>
+        <v>2540.67</v>
       </c>
       <c r="O83" t="n">
-        <v>2759.38</v>
+        <v>2680.68</v>
       </c>
       <c r="P83" s="6" t="n">
         <v/>
@@ -7421,14 +7419,12 @@
       <c r="Q83" s="6" t="n">
         <v/>
       </c>
-      <c r="R83" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S83" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R83" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S83" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T83" s="8" t="n">
@@ -7445,55 +7441,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr"/>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2399.06</v>
+        <v>2416.17</v>
       </c>
       <c r="C84" t="n">
-        <v>2426.93</v>
+        <v>2480.74</v>
       </c>
       <c r="D84" t="n">
-        <v>2368.74</v>
+        <v>2412.19</v>
       </c>
       <c r="E84" t="n">
-        <v>2416.12</v>
+        <v>2447.11</v>
       </c>
       <c r="F84" t="n">
-        <v>17.03</v>
+        <v>30.99</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0128</v>
       </c>
       <c r="H84" t="n">
-        <v>58.19</v>
+        <v>68.55</v>
       </c>
       <c r="I84" t="n">
-        <v>2196.6</v>
+        <v>2310.54</v>
       </c>
       <c r="J84" t="n">
-        <v>2217.95</v>
+        <v>2367.07</v>
       </c>
       <c r="K84" t="n">
-        <v>2318.41</v>
+        <v>2387.02</v>
       </c>
       <c r="L84" t="n">
-        <v>2418.86</v>
+        <v>2406.98</v>
       </c>
       <c r="M84" t="n">
-        <v>2479.77</v>
+        <v>2445.22</v>
       </c>
       <c r="N84" t="n">
-        <v>2540.67</v>
+        <v>2483.46</v>
       </c>
       <c r="O84" t="n">
-        <v>2680.68</v>
+        <v>2485.12</v>
       </c>
       <c r="P84" s="6" t="n">
         <v/>
@@ -7506,11 +7506,13 @@
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T84" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T84" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U84" s="8" t="n">
         <v/>
@@ -7525,57 +7527,57 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2416.17</v>
+        <v>2447.11</v>
       </c>
       <c r="C85" t="n">
-        <v>2480.74</v>
+        <v>2643.96</v>
       </c>
       <c r="D85" t="n">
-        <v>2412.19</v>
+        <v>2435.15</v>
       </c>
       <c r="E85" t="n">
-        <v>2447.11</v>
+        <v>2611.35</v>
       </c>
       <c r="F85" t="n">
-        <v>30.99</v>
+        <v>164.24</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.0128</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>68.55</v>
+        <v>208.81</v>
       </c>
       <c r="I85" t="n">
-        <v>2310.54</v>
+        <v>2343.64</v>
       </c>
       <c r="J85" t="n">
-        <v>2367.07</v>
+        <v>2378.88</v>
       </c>
       <c r="K85" t="n">
-        <v>2387.02</v>
+        <v>2412.83</v>
       </c>
       <c r="L85" t="n">
-        <v>2406.98</v>
+        <v>2446.78</v>
       </c>
       <c r="M85" t="n">
-        <v>2445.22</v>
+        <v>2481.38</v>
       </c>
       <c r="N85" t="n">
-        <v>2483.46</v>
+        <v>2515.98</v>
       </c>
       <c r="O85" t="n">
-        <v>2485.12</v>
+        <v>2549.29</v>
       </c>
       <c r="P85" s="6" t="n">
         <v/>
@@ -7586,80 +7588,80 @@
       <c r="R85" s="6" t="n">
         <v/>
       </c>
-      <c r="S85" s="10" t="inlineStr">
+      <c r="S85" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T85" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U85" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V85" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U85" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V85" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W85" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W85" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2447.11</v>
+        <v>2611.46</v>
       </c>
       <c r="C86" t="n">
-        <v>2643.96</v>
+        <v>2659.72</v>
       </c>
       <c r="D86" t="n">
-        <v>2435.15</v>
+        <v>2602.74</v>
       </c>
       <c r="E86" t="n">
-        <v>2611.35</v>
+        <v>2631.96</v>
       </c>
       <c r="F86" t="n">
-        <v>164.24</v>
+        <v>20.62</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>208.81</v>
+        <v>56.98</v>
       </c>
       <c r="I86" t="n">
-        <v>2343.64</v>
+        <v>2226.33</v>
       </c>
       <c r="J86" t="n">
-        <v>2378.88</v>
+        <v>2438.43</v>
       </c>
       <c r="K86" t="n">
-        <v>2412.83</v>
+        <v>2506.94</v>
       </c>
       <c r="L86" t="n">
-        <v>2446.78</v>
+        <v>2575.45</v>
       </c>
       <c r="M86" t="n">
-        <v>2481.38</v>
+        <v>2715.75</v>
       </c>
       <c r="N86" t="n">
-        <v>2515.98</v>
+        <v>2856.06</v>
       </c>
       <c r="O86" t="n">
-        <v>2549.29</v>
+        <v>2852.78</v>
       </c>
       <c r="P86" s="6" t="n">
         <v/>
@@ -7670,25 +7672,19 @@
       <c r="R86" s="6" t="n">
         <v/>
       </c>
-      <c r="S86" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V86" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S86" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T86" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U86" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V86" s="8" t="n">
+        <v/>
       </c>
       <c r="W86" s="9" t="inlineStr">
         <is>
@@ -7700,61 +7696,65 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2611.46</v>
+        <v>2632.01</v>
       </c>
       <c r="C87" t="n">
-        <v>2659.72</v>
+        <v>2647.87</v>
       </c>
       <c r="D87" t="n">
-        <v>2602.74</v>
+        <v>2564.43</v>
       </c>
       <c r="E87" t="n">
-        <v>2631.96</v>
+        <v>2643</v>
       </c>
       <c r="F87" t="n">
-        <v>20.62</v>
+        <v>11.03</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.0042</v>
       </c>
       <c r="H87" t="n">
-        <v>56.98</v>
+        <v>83.44</v>
       </c>
       <c r="I87" t="n">
-        <v>2226.33</v>
+        <v>2545.76</v>
       </c>
       <c r="J87" t="n">
-        <v>2438.43</v>
+        <v>2575.35</v>
       </c>
       <c r="K87" t="n">
-        <v>2506.94</v>
+        <v>2603.47</v>
       </c>
       <c r="L87" t="n">
-        <v>2575.45</v>
+        <v>2631.6</v>
       </c>
       <c r="M87" t="n">
-        <v>2715.75</v>
+        <v>2660.45</v>
       </c>
       <c r="N87" t="n">
-        <v>2856.06</v>
+        <v>2689.31</v>
       </c>
       <c r="O87" t="n">
-        <v>2852.78</v>
+        <v>2716.7</v>
       </c>
       <c r="P87" s="6" t="n">
         <v/>
       </c>
-      <c r="Q87" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R87" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S87" s="10" t="inlineStr">
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S87" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -7773,141 +7773,143 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr"/>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2632.01</v>
+        <v>2642.78</v>
       </c>
       <c r="C88" t="n">
-        <v>2647.87</v>
+        <v>2805.5</v>
       </c>
       <c r="D88" t="n">
-        <v>2564.43</v>
+        <v>2642.78</v>
       </c>
       <c r="E88" t="n">
-        <v>2643</v>
+        <v>2776.47</v>
       </c>
       <c r="F88" t="n">
-        <v>11.03</v>
+        <v>133.47</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0505</v>
       </c>
       <c r="H88" t="n">
-        <v>83.44</v>
+        <v>162.72</v>
       </c>
       <c r="I88" t="n">
-        <v>2545.76</v>
+        <v>2480.99</v>
       </c>
       <c r="J88" t="n">
-        <v>2575.35</v>
+        <v>2577.98</v>
       </c>
       <c r="K88" t="n">
-        <v>2603.47</v>
+        <v>2601.28</v>
       </c>
       <c r="L88" t="n">
-        <v>2631.6</v>
+        <v>2624.58</v>
       </c>
       <c r="M88" t="n">
-        <v>2660.45</v>
+        <v>2684.72</v>
       </c>
       <c r="N88" t="n">
-        <v>2689.31</v>
+        <v>2744.86</v>
       </c>
       <c r="O88" t="n">
-        <v>2716.7</v>
+        <v>2731.31</v>
       </c>
       <c r="P88" s="6" t="n">
         <v/>
       </c>
-      <c r="Q88" s="6" t="inlineStr">
+      <c r="Q88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R88" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S88" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T88" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R88" s="6" t="inlineStr">
+      <c r="U88" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V88" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S88" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U88" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V88" s="8" t="n">
-        <v/>
-      </c>
       <c r="W88" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2642.78</v>
+        <v>2776.58</v>
       </c>
       <c r="C89" t="n">
-        <v>2805.5</v>
+        <v>2776.89</v>
       </c>
       <c r="D89" t="n">
-        <v>2642.78</v>
+        <v>2715.72</v>
       </c>
       <c r="E89" t="n">
-        <v>2776.47</v>
+        <v>2752.63</v>
       </c>
       <c r="F89" t="n">
-        <v>133.47</v>
+        <v>-23.84</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.0505</v>
+        <v>-0.0086</v>
       </c>
       <c r="H89" t="n">
-        <v>162.72</v>
+        <v>61.17</v>
       </c>
       <c r="I89" t="n">
-        <v>2480.99</v>
+        <v>2480.07</v>
       </c>
       <c r="J89" t="n">
-        <v>2577.98</v>
+        <v>2639.92</v>
       </c>
       <c r="K89" t="n">
-        <v>2601.28</v>
+        <v>2695.11</v>
       </c>
       <c r="L89" t="n">
-        <v>2624.58</v>
+        <v>2750.3</v>
       </c>
       <c r="M89" t="n">
-        <v>2684.72</v>
+        <v>2857.83</v>
       </c>
       <c r="N89" t="n">
-        <v>2744.86</v>
+        <v>2965.35</v>
       </c>
       <c r="O89" t="n">
-        <v>2731.31</v>
+        <v>2968.22</v>
       </c>
       <c r="P89" s="6" t="n">
         <v/>
@@ -7918,97 +7920,103 @@
       <c r="R89" s="6" t="n">
         <v/>
       </c>
-      <c r="S89" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U89" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S89" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U89" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V89" s="8" t="n">
+        <v/>
       </c>
       <c r="W89" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr"/>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2776.58</v>
+        <v>2752.75</v>
       </c>
       <c r="C90" t="n">
-        <v>2776.89</v>
+        <v>2787.96</v>
       </c>
       <c r="D90" t="n">
-        <v>2715.72</v>
+        <v>2636.91</v>
       </c>
       <c r="E90" t="n">
-        <v>2752.63</v>
+        <v>2684.69</v>
       </c>
       <c r="F90" t="n">
-        <v>-23.84</v>
+        <v>-67.94</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0247</v>
       </c>
       <c r="H90" t="n">
-        <v>61.17</v>
+        <v>151.05</v>
       </c>
       <c r="I90" t="n">
-        <v>2480.07</v>
+        <v>2654.54</v>
       </c>
       <c r="J90" t="n">
-        <v>2639.92</v>
+        <v>2694.62</v>
       </c>
       <c r="K90" t="n">
-        <v>2695.11</v>
+        <v>2722.05</v>
       </c>
       <c r="L90" t="n">
-        <v>2750.3</v>
+        <v>2749.47</v>
       </c>
       <c r="M90" t="n">
-        <v>2857.83</v>
+        <v>2783.22</v>
       </c>
       <c r="N90" t="n">
-        <v>2965.35</v>
+        <v>2816.97</v>
       </c>
       <c r="O90" t="n">
-        <v>2968.22</v>
-      </c>
-      <c r="P90" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q90" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R90" s="6" t="n">
-        <v/>
+        <v>2838.06</v>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S90" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T90" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T90" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U90" s="8" t="n">
         <v/>
@@ -8016,89 +8024,81 @@
       <c r="V90" s="8" t="n">
         <v/>
       </c>
-      <c r="W90" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W90" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2753.25</v>
+        <v>2684.09</v>
       </c>
       <c r="C91" t="n">
-        <v>2785.63</v>
+        <v>2698.47</v>
       </c>
       <c r="D91" t="n">
-        <v>2650.82</v>
+        <v>2635.16</v>
       </c>
       <c r="E91" t="n">
-        <v>2688.5</v>
+        <v>2685.44</v>
       </c>
       <c r="F91" t="n">
-        <v>-64.13</v>
+        <v>0.75</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.0233</v>
+        <v>0.0003</v>
       </c>
       <c r="H91" t="n">
-        <v>134.81</v>
+        <v>63.31</v>
       </c>
       <c r="I91" t="n">
-        <v>2654.54</v>
+        <v>2485.86</v>
       </c>
       <c r="J91" t="n">
-        <v>2694.62</v>
+        <v>2519.77</v>
       </c>
       <c r="K91" t="n">
-        <v>2722.05</v>
+        <v>2609.17</v>
       </c>
       <c r="L91" t="n">
-        <v>2749.47</v>
+        <v>2698.56</v>
       </c>
       <c r="M91" t="n">
-        <v>2783.22</v>
+        <v>2760.22</v>
       </c>
       <c r="N91" t="n">
-        <v>2816.97</v>
+        <v>2821.87</v>
       </c>
       <c r="O91" t="n">
-        <v>2838.06</v>
-      </c>
-      <c r="P91" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q91" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R91" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S91" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>2939.01</v>
+      </c>
+      <c r="P91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R91" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S91" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="n">
+        <v/>
       </c>
       <c r="U91" s="8" t="n">
         <v/>

--- a/three_gate/analysis/ETH_daily.xlsx
+++ b/three_gate/analysis/ETH_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1576.59</v>
+        <v>1610.16</v>
       </c>
       <c r="C2" t="n">
-        <v>1607.87</v>
+        <v>1611.35</v>
       </c>
       <c r="D2" t="n">
-        <v>1561.97</v>
+        <v>1549.25</v>
       </c>
       <c r="E2" t="n">
-        <v>1571.59</v>
+        <v>1569.58</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.03</v>
+        <v>-40.62</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0032</v>
+        <v>-0.0252</v>
       </c>
       <c r="H2" t="n">
-        <v>45.89</v>
+        <v>62.1</v>
       </c>
       <c r="I2" t="n">
-        <v>1430.81</v>
+        <v>1466.43</v>
       </c>
       <c r="J2" t="n">
-        <v>1510.05</v>
+        <v>1535.78</v>
       </c>
       <c r="K2" t="n">
-        <v>1536.77</v>
+        <v>1568.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1563.48</v>
+        <v>1601.02</v>
       </c>
       <c r="M2" t="n">
-        <v>1616.46</v>
+        <v>1652.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1669.44</v>
+        <v>1703</v>
       </c>
       <c r="O2" t="n">
-        <v>1669.89</v>
+        <v>1717.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,12 +685,14 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -709,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1571.56</v>
+        <v>1569.91</v>
       </c>
       <c r="C3" t="n">
-        <v>1585.22</v>
+        <v>1642.45</v>
       </c>
       <c r="D3" t="n">
-        <v>1548.76</v>
+        <v>1551.14</v>
       </c>
       <c r="E3" t="n">
-        <v>1570.36</v>
+        <v>1608.96</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.23</v>
+        <v>39.38</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0008</v>
+        <v>0.0251</v>
       </c>
       <c r="H3" t="n">
-        <v>36.46</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>1516.08</v>
+        <v>1487.16</v>
       </c>
       <c r="J3" t="n">
-        <v>1519.03</v>
+        <v>1502.13</v>
       </c>
       <c r="K3" t="n">
-        <v>1548.64</v>
+        <v>1538.54</v>
       </c>
       <c r="L3" t="n">
-        <v>1578.25</v>
+        <v>1574.94</v>
       </c>
       <c r="M3" t="n">
-        <v>1594.53</v>
+        <v>1600.63</v>
       </c>
       <c r="N3" t="n">
-        <v>1610.82</v>
+        <v>1626.32</v>
       </c>
       <c r="O3" t="n">
-        <v>1653.76</v>
+        <v>1673.44</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,14 +774,18 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -789,59 +795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1569.99</v>
+        <v>1609.01</v>
       </c>
       <c r="C4" t="n">
-        <v>1633.65</v>
+        <v>1720.34</v>
       </c>
       <c r="D4" t="n">
-        <v>1550.04</v>
+        <v>1595.94</v>
       </c>
       <c r="E4" t="n">
-        <v>1610.21</v>
+        <v>1698.17</v>
       </c>
       <c r="F4" t="n">
-        <v>39.84</v>
+        <v>89.20999999999999</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0254</v>
+        <v>0.0554</v>
       </c>
       <c r="H4" t="n">
-        <v>83.61</v>
+        <v>124.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1512.3</v>
+        <v>1459.82</v>
       </c>
       <c r="J4" t="n">
-        <v>1535.59</v>
+        <v>1523.73</v>
       </c>
       <c r="K4" t="n">
-        <v>1552.13</v>
+        <v>1563.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1568.68</v>
+        <v>1602.88</v>
       </c>
       <c r="M4" t="n">
-        <v>1588.59</v>
+        <v>1654.62</v>
       </c>
       <c r="N4" t="n">
-        <v>1608.5</v>
+        <v>1706.36</v>
       </c>
       <c r="O4" t="n">
-        <v>1621.68</v>
+        <v>1733.77</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -849,30 +851,26 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -884,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1610.16</v>
+        <v>1698.42</v>
       </c>
       <c r="C5" t="n">
-        <v>1611.35</v>
+        <v>1772.54</v>
       </c>
       <c r="D5" t="n">
-        <v>1549.25</v>
+        <v>1693.04</v>
       </c>
       <c r="E5" t="n">
-        <v>1569.58</v>
+        <v>1756.52</v>
       </c>
       <c r="F5" t="n">
-        <v>-40.62</v>
+        <v>58.35</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0252</v>
+        <v>0.0344</v>
       </c>
       <c r="H5" t="n">
-        <v>62.1</v>
+        <v>79.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1466.43</v>
+        <v>1471.54</v>
       </c>
       <c r="J5" t="n">
-        <v>1535.78</v>
+        <v>1593.78</v>
       </c>
       <c r="K5" t="n">
-        <v>1568.4</v>
+        <v>1635.97</v>
       </c>
       <c r="L5" t="n">
-        <v>1601.02</v>
+        <v>1678.16</v>
       </c>
       <c r="M5" t="n">
-        <v>1652.01</v>
+        <v>1760.37</v>
       </c>
       <c r="N5" t="n">
-        <v>1703</v>
+        <v>1842.59</v>
       </c>
       <c r="O5" t="n">
-        <v>1717.25</v>
+        <v>1844.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,19 +933,19 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -959,59 +957,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1569.91</v>
+        <v>1756.58</v>
       </c>
       <c r="C6" t="n">
-        <v>1642.45</v>
+        <v>1804.59</v>
       </c>
       <c r="D6" t="n">
-        <v>1551.14</v>
+        <v>1743.56</v>
       </c>
       <c r="E6" t="n">
-        <v>1608.96</v>
+        <v>1779.03</v>
       </c>
       <c r="F6" t="n">
-        <v>39.38</v>
+        <v>22.51</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0251</v>
+        <v>0.0128</v>
       </c>
       <c r="H6" t="n">
-        <v>91.31999999999999</v>
+        <v>61.02</v>
       </c>
       <c r="I6" t="n">
-        <v>1487.16</v>
+        <v>1613.53</v>
       </c>
       <c r="J6" t="n">
-        <v>1502.13</v>
+        <v>1688.88</v>
       </c>
       <c r="K6" t="n">
-        <v>1538.54</v>
+        <v>1716.77</v>
       </c>
       <c r="L6" t="n">
-        <v>1574.94</v>
+        <v>1744.65</v>
       </c>
       <c r="M6" t="n">
-        <v>1600.63</v>
+        <v>1796.27</v>
       </c>
       <c r="N6" t="n">
-        <v>1626.32</v>
+        <v>1847.89</v>
       </c>
       <c r="O6" t="n">
-        <v>1673.44</v>
+        <v>1852.05</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1022,7 +1016,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1032,10 +1026,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1050,50 +1042,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1609.01</v>
+        <v>1779.04</v>
       </c>
       <c r="C7" t="n">
-        <v>1720.34</v>
+        <v>1805.91</v>
       </c>
       <c r="D7" t="n">
-        <v>1595.94</v>
+        <v>1749.14</v>
       </c>
       <c r="E7" t="n">
-        <v>1698.17</v>
+        <v>1783.01</v>
       </c>
       <c r="F7" t="n">
-        <v>89.20999999999999</v>
+        <v>3.97</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0554</v>
+        <v>0.0022</v>
       </c>
       <c r="H7" t="n">
-        <v>124.4</v>
+        <v>56.78</v>
       </c>
       <c r="I7" t="n">
-        <v>1459.82</v>
+        <v>1682.54</v>
       </c>
       <c r="J7" t="n">
-        <v>1523.73</v>
+        <v>1720.49</v>
       </c>
       <c r="K7" t="n">
-        <v>1563.3</v>
+        <v>1748.52</v>
       </c>
       <c r="L7" t="n">
-        <v>1602.88</v>
+        <v>1776.55</v>
       </c>
       <c r="M7" t="n">
-        <v>1654.62</v>
+        <v>1809.55</v>
       </c>
       <c r="N7" t="n">
-        <v>1706.36</v>
+        <v>1842.54</v>
       </c>
       <c r="O7" t="n">
-        <v>1733.77</v>
+        <v>1865.61</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1104,20 +1096,16 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1132,61 +1120,65 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1698.42</v>
+        <v>1783</v>
       </c>
       <c r="C8" t="n">
-        <v>1772.54</v>
+        <v>1829.51</v>
       </c>
       <c r="D8" t="n">
-        <v>1693.04</v>
+        <v>1728.97</v>
       </c>
       <c r="E8" t="n">
-        <v>1756.52</v>
+        <v>1797.57</v>
       </c>
       <c r="F8" t="n">
-        <v>58.35</v>
+        <v>14.57</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0344</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>79.5</v>
+        <v>100.55</v>
       </c>
       <c r="I8" t="n">
-        <v>1471.54</v>
+        <v>1692.36</v>
       </c>
       <c r="J8" t="n">
-        <v>1593.78</v>
+        <v>1728.97</v>
       </c>
       <c r="K8" t="n">
-        <v>1635.97</v>
+        <v>1754.62</v>
       </c>
       <c r="L8" t="n">
-        <v>1678.16</v>
+        <v>1780.27</v>
       </c>
       <c r="M8" t="n">
-        <v>1760.37</v>
+        <v>1811.39</v>
       </c>
       <c r="N8" t="n">
-        <v>1842.59</v>
+        <v>1842.52</v>
       </c>
       <c r="O8" t="n">
-        <v>1844.75</v>
+        <v>1862.69</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1207,55 +1199,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1756.58</v>
+        <v>1797.56</v>
       </c>
       <c r="C9" t="n">
-        <v>1804.59</v>
+        <v>1810.33</v>
       </c>
       <c r="D9" t="n">
-        <v>1743.56</v>
+        <v>1756.71</v>
       </c>
       <c r="E9" t="n">
-        <v>1779.03</v>
+        <v>1768.51</v>
       </c>
       <c r="F9" t="n">
-        <v>22.51</v>
+        <v>-29.06</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0128</v>
+        <v>-0.0162</v>
       </c>
       <c r="H9" t="n">
-        <v>61.02</v>
+        <v>53.62</v>
       </c>
       <c r="I9" t="n">
-        <v>1613.53</v>
+        <v>1628.42</v>
       </c>
       <c r="J9" t="n">
-        <v>1688.88</v>
+        <v>1706.19</v>
       </c>
       <c r="K9" t="n">
-        <v>1716.77</v>
+        <v>1747.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1744.65</v>
+        <v>1788.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1796.27</v>
+        <v>1847.85</v>
       </c>
       <c r="N9" t="n">
-        <v>1847.89</v>
+        <v>1907.29</v>
       </c>
       <c r="O9" t="n">
-        <v>1852.05</v>
+        <v>1930.06</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1268,13 +1264,11 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1287,55 +1281,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779.04</v>
+        <v>1768.39</v>
       </c>
       <c r="C10" t="n">
-        <v>1805.91</v>
+        <v>1782.86</v>
       </c>
       <c r="D10" t="n">
-        <v>1749.14</v>
+        <v>1711.9</v>
       </c>
       <c r="E10" t="n">
-        <v>1783.01</v>
+        <v>1742.68</v>
       </c>
       <c r="F10" t="n">
-        <v>3.97</v>
+        <v>-25.83</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0022</v>
+        <v>-0.0146</v>
       </c>
       <c r="H10" t="n">
-        <v>56.78</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1682.54</v>
+        <v>1703.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1720.49</v>
+        <v>1707.39</v>
       </c>
       <c r="K10" t="n">
-        <v>1748.52</v>
+        <v>1741.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1776.55</v>
+        <v>1776.02</v>
       </c>
       <c r="M10" t="n">
-        <v>1809.55</v>
+        <v>1795.32</v>
       </c>
       <c r="N10" t="n">
-        <v>1842.54</v>
+        <v>1814.62</v>
       </c>
       <c r="O10" t="n">
-        <v>1865.61</v>
+        <v>1863.95</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1343,12 +1341,14 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1365,78 +1365,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1783</v>
+        <v>1742.66</v>
       </c>
       <c r="C11" t="n">
-        <v>1829.51</v>
+        <v>1760.21</v>
       </c>
       <c r="D11" t="n">
-        <v>1728.97</v>
+        <v>1721.3</v>
       </c>
       <c r="E11" t="n">
-        <v>1797.57</v>
+        <v>1744.48</v>
       </c>
       <c r="F11" t="n">
-        <v>14.57</v>
+        <v>1.81</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>100.55</v>
+        <v>38.91</v>
       </c>
       <c r="I11" t="n">
-        <v>1692.36</v>
+        <v>1640.94</v>
       </c>
       <c r="J11" t="n">
-        <v>1728.97</v>
+        <v>1669.37</v>
       </c>
       <c r="K11" t="n">
-        <v>1754.62</v>
+        <v>1707.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1780.27</v>
+        <v>1745.03</v>
       </c>
       <c r="M11" t="n">
-        <v>1811.39</v>
+        <v>1778.16</v>
       </c>
       <c r="N11" t="n">
-        <v>1842.52</v>
+        <v>1811.29</v>
       </c>
       <c r="O11" t="n">
-        <v>1862.69</v>
+        <v>1853.82</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1458,50 +1456,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1797.56</v>
+        <v>1744.47</v>
       </c>
       <c r="C12" t="n">
-        <v>1810.33</v>
+        <v>1809.76</v>
       </c>
       <c r="D12" t="n">
-        <v>1756.71</v>
+        <v>1736.72</v>
       </c>
       <c r="E12" t="n">
-        <v>1768.51</v>
+        <v>1795.69</v>
       </c>
       <c r="F12" t="n">
-        <v>-29.06</v>
+        <v>51.21</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0162</v>
+        <v>0.0294</v>
       </c>
       <c r="H12" t="n">
-        <v>53.62</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>1628.42</v>
+        <v>1682.39</v>
       </c>
       <c r="J12" t="n">
-        <v>1706.19</v>
+        <v>1707.44</v>
       </c>
       <c r="K12" t="n">
-        <v>1747.3</v>
+        <v>1725.03</v>
       </c>
       <c r="L12" t="n">
-        <v>1788.41</v>
+        <v>1742.62</v>
       </c>
       <c r="M12" t="n">
-        <v>1847.85</v>
+        <v>1763.94</v>
       </c>
       <c r="N12" t="n">
-        <v>1907.29</v>
+        <v>1785.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1930.06</v>
+        <v>1799.11</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1514,76 +1512,78 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1768.39</v>
+        <v>1795.82</v>
       </c>
       <c r="C13" t="n">
-        <v>1782.86</v>
+        <v>1827.83</v>
       </c>
       <c r="D13" t="n">
-        <v>1711.9</v>
+        <v>1786.3</v>
       </c>
       <c r="E13" t="n">
-        <v>1742.68</v>
+        <v>1788.1</v>
       </c>
       <c r="F13" t="n">
-        <v>-25.83</v>
+        <v>-7.59</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0146</v>
+        <v>-0.0042</v>
       </c>
       <c r="H13" t="n">
-        <v>70.95999999999999</v>
+        <v>41.54</v>
       </c>
       <c r="I13" t="n">
-        <v>1703.1</v>
+        <v>1663.69</v>
       </c>
       <c r="J13" t="n">
-        <v>1707.39</v>
+        <v>1733.88</v>
       </c>
       <c r="K13" t="n">
-        <v>1741.7</v>
+        <v>1759.18</v>
       </c>
       <c r="L13" t="n">
-        <v>1776.02</v>
+        <v>1784.47</v>
       </c>
       <c r="M13" t="n">
-        <v>1795.32</v>
+        <v>1832.21</v>
       </c>
       <c r="N13" t="n">
-        <v>1814.62</v>
+        <v>1879.95</v>
       </c>
       <c r="O13" t="n">
-        <v>1863.95</v>
+        <v>1882.79</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1591,14 +1591,12 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1617,57 +1615,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1742.66</v>
+        <v>1787.57</v>
       </c>
       <c r="C14" t="n">
-        <v>1760.21</v>
+        <v>1824.98</v>
       </c>
       <c r="D14" t="n">
-        <v>1721.3</v>
+        <v>1779.64</v>
       </c>
       <c r="E14" t="n">
-        <v>1744.48</v>
+        <v>1805.79</v>
       </c>
       <c r="F14" t="n">
-        <v>1.81</v>
+        <v>17.69</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.001</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>38.91</v>
+        <v>45.34</v>
       </c>
       <c r="I14" t="n">
-        <v>1640.94</v>
+        <v>1744.76</v>
       </c>
       <c r="J14" t="n">
-        <v>1669.37</v>
+        <v>1737.08</v>
       </c>
       <c r="K14" t="n">
-        <v>1707.2</v>
+        <v>1767.33</v>
       </c>
       <c r="L14" t="n">
-        <v>1745.03</v>
+        <v>1797.58</v>
       </c>
       <c r="M14" t="n">
-        <v>1778.16</v>
+        <v>1808.87</v>
       </c>
       <c r="N14" t="n">
-        <v>1811.29</v>
+        <v>1820.15</v>
       </c>
       <c r="O14" t="n">
-        <v>1853.82</v>
+        <v>1869.37</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1680,14 +1678,18 @@
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1699,70 +1701,74 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1744.47</v>
+        <v>1805.76</v>
       </c>
       <c r="C15" t="n">
-        <v>1809.76</v>
+        <v>1842.46</v>
       </c>
       <c r="D15" t="n">
-        <v>1736.72</v>
+        <v>1749.35</v>
       </c>
       <c r="E15" t="n">
-        <v>1795.69</v>
+        <v>1773.5</v>
       </c>
       <c r="F15" t="n">
-        <v>51.21</v>
+        <v>-32.29</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0294</v>
+        <v>-0.0179</v>
       </c>
       <c r="H15" t="n">
-        <v>73.04000000000001</v>
+        <v>93.11</v>
       </c>
       <c r="I15" t="n">
-        <v>1682.39</v>
+        <v>1734.29</v>
       </c>
       <c r="J15" t="n">
-        <v>1707.44</v>
+        <v>1762.18</v>
       </c>
       <c r="K15" t="n">
-        <v>1725.03</v>
+        <v>1783.12</v>
       </c>
       <c r="L15" t="n">
-        <v>1742.62</v>
+        <v>1804.05</v>
       </c>
       <c r="M15" t="n">
-        <v>1763.94</v>
+        <v>1828.46</v>
       </c>
       <c r="N15" t="n">
-        <v>1785.26</v>
+        <v>1852.87</v>
       </c>
       <c r="O15" t="n">
-        <v>1799.11</v>
+        <v>1870.32</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -1770,70 +1776,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1795.82</v>
+        <v>1773.47</v>
       </c>
       <c r="C16" t="n">
-        <v>1827.83</v>
+        <v>1894.06</v>
       </c>
       <c r="D16" t="n">
-        <v>1786.3</v>
+        <v>1772.02</v>
       </c>
       <c r="E16" t="n">
-        <v>1788.1</v>
+        <v>1889.48</v>
       </c>
       <c r="F16" t="n">
-        <v>-7.59</v>
+        <v>115.98</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0042</v>
+        <v>0.0654</v>
       </c>
       <c r="H16" t="n">
-        <v>41.54</v>
+        <v>122.04</v>
       </c>
       <c r="I16" t="n">
-        <v>1663.69</v>
+        <v>1656.24</v>
       </c>
       <c r="J16" t="n">
-        <v>1733.88</v>
+        <v>1669.19</v>
       </c>
       <c r="K16" t="n">
-        <v>1759.18</v>
+        <v>1726.95</v>
       </c>
       <c r="L16" t="n">
-        <v>1784.47</v>
+        <v>1784.7</v>
       </c>
       <c r="M16" t="n">
-        <v>1832.21</v>
+        <v>1820.05</v>
       </c>
       <c r="N16" t="n">
-        <v>1879.95</v>
+        <v>1855.41</v>
       </c>
       <c r="O16" t="n">
-        <v>1882.79</v>
+        <v>1935.56</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1844,16 +1850,20 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1863,59 +1873,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17"